--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/5/26)</t>
+          <t>Hiring AEs? (9/6/26)</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.365labs.com/car</t>
+          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
         </is>
       </c>
     </row>
@@ -9826,9 +9826,9 @@
           <t>Digital dashboards and signage for public safety - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F304" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F304" s="8" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="F1" s="59" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/5/26)</t>
+          <t>Hiring AEs? (9/6/26)</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="F1" s="65" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/5/26)</t>
+          <t>Hiring AEs? (9/6/26)</t>
         </is>
       </c>
     </row>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="F1" s="71" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/5/26)</t>
+          <t>Hiring AEs? (9/6/26)</t>
         </is>
       </c>
     </row>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="F10" s="74" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.affordablehousi</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/5/26)</t>
+          <t>Hiring AEs? (9/6/26)</t>
         </is>
       </c>
     </row>
@@ -24646,7 +24646,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/5/26)</t>
+          <t>Hiring AEs? (9/6/26)</t>
         </is>
       </c>
     </row>
@@ -24916,7 +24916,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://zencity.io/careers</t>
+          <t>Unknown - HTTP 403 for https://zencity.io/careers</t>
         </is>
       </c>
     </row>
@@ -29774,7 +29774,7 @@
       </c>
       <c r="F175" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 500 for https://lcptracker.com/care</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -31728,7 +31728,7 @@
       </c>
       <c r="F241" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://passportworkforce.c</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -31872,7 +31872,7 @@
       </c>
       <c r="F246" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.geographicsolut</t>
         </is>
       </c>
     </row>
@@ -38524,7 +38524,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/5/26)</t>
+          <t>Hiring AEs? (9/6/26)</t>
         </is>
       </c>
     </row>
@@ -43034,7 +43034,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/5/26)</t>
+          <t>Hiring AEs? (9/6/26)</t>
         </is>
       </c>
     </row>
@@ -47130,7 +47130,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/5/26)</t>
+          <t>Hiring AEs? (9/6/26)</t>
         </is>
       </c>
     </row>
@@ -47430,7 +47430,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.modeshift.com/c</t>
+          <t>Unknown - HTTP 403 for https://www.modeshift.com/c</t>
         </is>
       </c>
     </row>
@@ -48056,7 +48056,7 @@
       </c>
       <c r="F32" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.enghouse.com/ca</t>
+          <t>Unknown - HTTP 403 for https://www.enghouse.com/ca</t>
         </is>
       </c>
     </row>
@@ -50140,7 +50140,7 @@
       </c>
       <c r="F102" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.hanoverdisplays</t>
+          <t>Unknown - HTTP 403 for https://www.hanoverdisplays</t>
         </is>
       </c>
     </row>
@@ -50558,7 +50558,7 @@
       </c>
       <c r="F116" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://qryde.com/employmen</t>
+          <t>Unknown - HTTP 403 for https://qryde.com/employmen</t>
         </is>
       </c>
     </row>
@@ -50936,9 +50936,9 @@
           <t>On-demand transit software converting fixed routes to demand-response for agencies</t>
         </is>
       </c>
-      <c r="F129" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 403 for https://pantonium.com/caree</t>
         </is>
       </c>
     </row>
@@ -53002,7 +53002,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/5/26)</t>
+          <t>Hiring AEs? (9/6/26)</t>
         </is>
       </c>
     </row>
@@ -53720,9 +53720,9 @@
           <t>Adaptive smart street lighting sensors and CMS for municipalities</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -56532,7 +56532,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/5/26)</t>
+          <t>Hiring AEs? (9/6/26)</t>
         </is>
       </c>
     </row>
@@ -58168,7 +58168,7 @@
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -58378,7 +58378,7 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.grab.careers/en</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -60056,7 +60056,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/5/26)</t>
+          <t>Hiring AEs? (9/6/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/6/26)</t>
+          <t>Hiring AEs? (9/7/26)</t>
         </is>
       </c>
     </row>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="F1" s="59" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/6/26)</t>
+          <t>Hiring AEs? (9/7/26)</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="F1" s="65" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/6/26)</t>
+          <t>Hiring AEs? (9/7/26)</t>
         </is>
       </c>
     </row>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="F1" s="71" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/6/26)</t>
+          <t>Hiring AEs? (9/7/26)</t>
         </is>
       </c>
     </row>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/6/26)</t>
+          <t>Hiring AEs? (9/7/26)</t>
         </is>
       </c>
     </row>
@@ -24646,7 +24646,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/6/26)</t>
+          <t>Hiring AEs? (9/7/26)</t>
         </is>
       </c>
     </row>
@@ -28024,7 +28024,7 @@
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>Yes - Business Development Manager (Winnipeg)</t>
+          <t>Yes - Account Executive - CES (London)</t>
         </is>
       </c>
     </row>
@@ -30716,7 +30716,7 @@
       </c>
       <c r="F207" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (London)</t>
+          <t>Yes - Account Executive (Singapore, Singapo)</t>
         </is>
       </c>
     </row>
@@ -31728,7 +31728,7 @@
       </c>
       <c r="F241" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - HTTP 403 for https://passportworkforce.c</t>
         </is>
       </c>
     </row>
@@ -31872,7 +31872,7 @@
       </c>
       <c r="F246" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.geographicsolut</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -38524,7 +38524,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/6/26)</t>
+          <t>Hiring AEs? (9/7/26)</t>
         </is>
       </c>
     </row>
@@ -42170,7 +42170,7 @@
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Manager (Barcelona)</t>
+          <t>Yes - Account Executive (Barcelona)</t>
         </is>
       </c>
     </row>
@@ -43034,7 +43034,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/6/26)</t>
+          <t>Hiring AEs? (9/7/26)</t>
         </is>
       </c>
     </row>
@@ -46492,7 +46492,7 @@
       </c>
       <c r="F118" s="34" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -47130,7 +47130,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/6/26)</t>
+          <t>Hiring AEs? (9/7/26)</t>
         </is>
       </c>
     </row>
@@ -50936,9 +50936,9 @@
           <t>On-demand transit software converting fixed routes to demand-response for agencies</t>
         </is>
       </c>
-      <c r="F129" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - HTTP 403 for https://pantonium.com/caree</t>
+      <c r="F129" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -52004,7 +52004,7 @@
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -53002,7 +53002,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/6/26)</t>
+          <t>Hiring AEs? (9/7/26)</t>
         </is>
       </c>
     </row>
@@ -53720,9 +53720,9 @@
           <t>Adaptive smart street lighting sensors and CMS for municipalities</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -54382,7 +54382,7 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Business Development Specialist only</t>
+          <t>Sales (non-AE) - Business Analyst - Customer Succes only</t>
         </is>
       </c>
     </row>
@@ -54500,9 +54500,9 @@
           <t>Grid software, ADMS and transmission equipment for public and investor utilities</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -56410,7 +56410,7 @@
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -56532,7 +56532,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/6/26)</t>
+          <t>Hiring AEs? (9/7/26)</t>
         </is>
       </c>
     </row>
@@ -58168,7 +58168,7 @@
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -58586,9 +58586,9 @@
           <t>Alcatraz AI Rock: 3D facial authentication and tailgating detection device that replaces or augments badge readers at secure doors, integrating with existing access control systems.</t>
         </is>
       </c>
-      <c r="F70" s="51" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F70" s="52" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -60056,7 +60056,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/6/26)</t>
+          <t>Hiring AEs? (9/7/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/7/26)</t>
+          <t>Hiring AEs? (9/8/26)</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
+          <t>Unknown - HTTP 202 for https://www.365labs.com/car</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 503 for https://norix.com/about-us/</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="F1" s="59" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/7/26)</t>
+          <t>Hiring AEs? (9/8/26)</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="F1" s="65" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/7/26)</t>
+          <t>Hiring AEs? (9/8/26)</t>
         </is>
       </c>
     </row>
@@ -14986,9 +14986,9 @@
           <t>No-code IT service management, asset management, project portfolio, and integration platform for universities, school districts, and government agencies - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F20" s="69" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Associate Customer Success Manager only</t>
+      <c r="F20" s="68" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="F1" s="71" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/7/26)</t>
+          <t>Hiring AEs? (9/8/26)</t>
         </is>
       </c>
     </row>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="F10" s="74" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.affordablehousi</t>
         </is>
       </c>
     </row>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/7/26)</t>
+          <t>Hiring AEs? (9/8/26)</t>
         </is>
       </c>
     </row>
@@ -23064,7 +23064,7 @@
       </c>
       <c r="F188" s="16" t="inlineStr">
         <is>
-          <t>Yes - Account Executive, Enterprise - Ce (United States - Re)</t>
+          <t>Yes - Account Executive, CMRL - MX (Mexico - Remote)</t>
         </is>
       </c>
     </row>
@@ -24646,7 +24646,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/7/26)</t>
+          <t>Hiring AEs? (9/8/26)</t>
         </is>
       </c>
     </row>
@@ -24916,7 +24916,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://zencity.io/careers</t>
+          <t>Unknown - HTTP 202 for https://zencity.io/careers</t>
         </is>
       </c>
     </row>
@@ -27932,9 +27932,9 @@
           <t>Objective Build planning and building consent software for government regulators</t>
         </is>
       </c>
-      <c r="F113" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Business Development Manager (Reading)</t>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Account Director only</t>
         </is>
       </c>
     </row>
@@ -30570,7 +30570,7 @@
       </c>
       <c r="F202" s="21" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no jobs parsed from iCIMS portal</t>
         </is>
       </c>
     </row>
@@ -31728,7 +31728,7 @@
       </c>
       <c r="F241" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://passportworkforce.c</t>
+          <t>Unknown - HTTP 202 for https://passportworkforce.c</t>
         </is>
       </c>
     </row>
@@ -38524,7 +38524,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/7/26)</t>
+          <t>Hiring AEs? (9/8/26)</t>
         </is>
       </c>
     </row>
@@ -42648,9 +42648,9 @@
           <t>Event volunteer scheduling and check-in for festivals and public events</t>
         </is>
       </c>
-      <c r="F139" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive Level 2 (Remote, US)</t>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -43034,7 +43034,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/7/26)</t>
+          <t>Hiring AEs? (9/8/26)</t>
         </is>
       </c>
     </row>
@@ -43924,9 +43924,9 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -44338,7 +44338,7 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>Yes - Strategic Sales Director - Enterpr</t>
+          <t>Yes - Sales Account Executive – Mid-Mark</t>
         </is>
       </c>
     </row>
@@ -44908,7 +44908,7 @@
       </c>
       <c r="F64" s="35" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Customer Success Manager only</t>
+          <t>Sales (non-AE) - Customer Success Manager (CA) only</t>
         </is>
       </c>
     </row>
@@ -47130,7 +47130,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/7/26)</t>
+          <t>Hiring AEs? (9/8/26)</t>
         </is>
       </c>
     </row>
@@ -47430,7 +47430,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.modeshift.com/c</t>
+          <t>Unknown - HTTP 202 for https://www.modeshift.com/c</t>
         </is>
       </c>
     </row>
@@ -48056,7 +48056,7 @@
       </c>
       <c r="F32" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.enghouse.com/ca</t>
+          <t>Unknown - HTTP 202 for https://www.enghouse.com/ca</t>
         </is>
       </c>
     </row>
@@ -50140,7 +50140,7 @@
       </c>
       <c r="F102" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.hanoverdisplays</t>
+          <t>Unknown - HTTP 202 for https://www.hanoverdisplays</t>
         </is>
       </c>
     </row>
@@ -50558,7 +50558,7 @@
       </c>
       <c r="F116" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://qryde.com/employmen</t>
+          <t>Unknown - HTTP 202 for https://qryde.com/employmen</t>
         </is>
       </c>
     </row>
@@ -52862,7 +52862,7 @@
       </c>
       <c r="F197" s="10" t="inlineStr">
         <is>
-          <t>Yes - Strategic Sales Director - Enterpr</t>
+          <t>Yes - Sales Account Executive – Mid-Mark</t>
         </is>
       </c>
     </row>
@@ -53002,7 +53002,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/7/26)</t>
+          <t>Hiring AEs? (9/8/26)</t>
         </is>
       </c>
     </row>
@@ -56410,7 +56410,7 @@
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -56532,7 +56532,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/7/26)</t>
+          <t>Hiring AEs? (9/8/26)</t>
         </is>
       </c>
     </row>
@@ -58016,9 +58016,9 @@
           <t>Baggage handling systems and terminal logistics for airports</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -58378,7 +58378,7 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.grab.careers/en</t>
         </is>
       </c>
     </row>
@@ -58586,9 +58586,9 @@
           <t>Alcatraz AI Rock: 3D facial authentication and tailgating detection device that replaces or augments badge readers at secure doors, integrating with existing access control systems.</t>
         </is>
       </c>
-      <c r="F70" s="52" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F70" s="51" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -60056,7 +60056,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/7/26)</t>
+          <t>Hiring AEs? (9/8/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'General Gov'!$A$1:$F$489</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Parks &amp; Rec'!$A$1:$F$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'K-12 Schools'!$A$1:$F$139</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Transit &amp; Parking'!$A$1:$F$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Transit &amp; Parking'!$A$1:$F$192</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Utilities &amp; Energy'!$A$1:$F$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Airports &amp; Aviation'!$A$1:$F$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Courts &amp; Justice'!$A$1:$F$36</definedName>
@@ -943,7 +943,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/10/26)</t>
+          <t>Hiring AEs? (9/11/26)</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Cloud fire department suite: pre-incident planning, RMS, scheduling, and response</t>
+          <t>Cloud fire department suite: pre-incident planning, RMS, scheduling, and response - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Evacuation management and real-time incident mapping for fire and emergency agencies</t>
+          <t>Evacuation management and real-time incident mapping for fire and emergency agencies - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Cloud checklist and compliance management: vehicle checks, SCBA, PPE, and narcotics for 1,400+ agencies</t>
+          <t>Cloud checklist and compliance management: vehicle checks, SCBA, PPE, and narcotics for 1,400+ agencies - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Digital dashboards and signage for public safety - exhibited at IACP 2026</t>
+          <t>Digital dashboards and signage for public safety - exhibited at IACP 2026, IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Wildfire and all-hazard situational awareness analytics for fire agencies</t>
+          <t>Wildfire and all-hazard situational awareness analytics for fire agencies - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>SCBA, thermal imagers and turnout gear for fire departments</t>
+          <t>SCBA, thermal imagers and turnout gear for fire departments - exhibited at WEFTEC 2026, IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Fire apparatus and electric fire trucks for municipal departments</t>
+          <t>Fire apparatus and electric fire trucks for municipal departments - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Radios, 911 call handling, CAD, and video security (Avigilon) for public safety - exhibited at Michigan Sheriffs Association 2026</t>
+          <t>Radios, 911 call handling, CAD, and video security (Avigilon) for public safety - exhibited at Michigan Sheriffs Association 2026, IAFC FRI 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Autonomous drones for police DFR programs and public-sector inspection - exhibited at NLC City Summit 2026</t>
+          <t>Autonomous drones for police DFR programs and public-sector inspection - exhibited at NLC City Summit 2026, IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Cloud-native CAD and records management (RMS) for law enforcement</t>
+          <t>Cloud-native CAD and records management (RMS) for law enforcement - exhibited at APCO 2026</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Data integration and real-time intelligence platform for police and city agencies</t>
+          <t>Data integration and real-time intelligence platform for police and city agencies - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>CAD/911, RMS, and jail software suite - one of the big three public safety platforms (Superion+TriTech merger) - exhibited at GFOA 2026, NLC City Summit 2026, Michigan Sheriffs Association 2026</t>
+          <t>CAD/911, RMS, and jail software suite - one of the big three public safety platforms (Superion+TriTech merger) - exhibited at GFOA 2026, NLC City Summit 2026, Michigan Sheriffs Association 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>CAD/RMS and growing public safety suite via acquisitions</t>
+          <t>CAD/RMS and growing public safety suite via acquisitions - exhibited at APCO 2026</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Browser-based CAD, RMS, mobile, and jail software for police and fire/EMS</t>
+          <t>Browser-based CAD, RMS, mobile, and jail software for police and fire/EMS - exhibited at APCO 2026</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>AI-forward CAD, RMS, and case management for law enforcement and prosecutors</t>
+          <t>AI-forward CAD, RMS, and case management for law enforcement and prosecutors - exhibited at APCO 2026</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>State-specific policy manuals, training, and wellness content for public safety</t>
+          <t>State-specific policy manuals, training, and wellness content for public safety - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Training LMS, scheduling, and readiness software (TargetSolutions, Guardian Tracking)</t>
+          <t>Training LMS, scheduling, and readiness software (TargetSolutions, Guardian Tracking) - exhibited at IAFC FRI 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Cloud shift scheduling for police, sheriff, corrections, and dispatch</t>
+          <t>Cloud shift scheduling for police, sheriff, corrections, and dispatch - exhibited at APCO 2026</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Outsourced extra-duty detail administration plus Jivasoft scheduling software</t>
+          <t>Outsourced extra-duty detail administration plus Jivasoft scheduling software - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Vehicle history data tools for police - exhibited at IACP 2026</t>
+          <t>Vehicle history data tools for police - exhibited at IACP 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>Software for first responder agencies - exhibited at IACP 2026</t>
+          <t>Software for first responder agencies - exhibited at IACP 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F131" s="10" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>Integrated CAD, RMS, JMS and finance software for local government - exhibited at North Carolina Sheriffs' Association 2026</t>
+          <t>Integrated CAD, RMS, JMS and finance software for local government - exhibited at North Carolina Sheriffs' Association 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>CAD, RMS, mobile and citizen reporting for public safety agencies</t>
+          <t>CAD, RMS, mobile and citizen reporting for public safety agencies - exhibited at APCO 2026</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>Digital evidence management and 911 recording for public safety agencies</t>
+          <t>Digital evidence management and 911 recording for public safety agencies - exhibited at APCO 2026</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>ePCR, records, and analytics connecting EMS, fire, and hospitals</t>
+          <t>ePCR, records, and analytics connecting EMS, fire, and hospitals - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F167" s="10" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Incident records and ePCR data platform for EMS and fire agencies</t>
+          <t>Incident records and ePCR data platform for EMS and fire agencies - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>Intelligent 911 platform streaming device location and data to dispatch</t>
+          <t>Intelligent 911 platform streaming device location and data to dispatch - exhibited at APCO 2026</t>
         </is>
       </c>
       <c r="F169" s="9" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Emergency dispatch protocols and ProQA software for 911 centers</t>
+          <t>Emergency dispatch protocols and ProQA software for 911 centers - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>AI voice agents answering non-emergency calls for 911 centers</t>
+          <t>AI voice agents answering non-emergency calls for 911 centers - exhibited at APCO 2026</t>
         </is>
       </c>
       <c r="F175" s="7" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>ActiveAlert dispatch alerting and response apps for fire, EMS, and LE</t>
+          <t>ActiveAlert dispatch alerting and response apps for fire, EMS, and LE - exhibited at APCO 2026</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - board is another company's - not read</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Ambulance revenue cycle software and billing for EMS agencies</t>
+          <t>Ambulance revenue cycle software and billing for EMS agencies - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>Mobile incident command and response for fire/EMS departments</t>
+          <t>Mobile incident command and response for fire/EMS departments - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F185" s="10" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Automated voice dispatch and station alerting for fire/EMS</t>
+          <t>Automated voice dispatch and station alerting for fire/EMS - exhibited at APCO 2026</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>Phoenix G2 fire/EMS station alerting systems for departments</t>
+          <t>Phoenix G2 fire/EMS station alerting systems for departments - exhibited at APCO 2026</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Fire/EMS station alerting and dispatch integration for municipalities</t>
+          <t>Fire/EMS station alerting and dispatch integration for municipalities - exhibited at IAFC FRI 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>Dispatch consoles, paging and station alerting for EMS and fire</t>
+          <t>Dispatch consoles, paging and station alerting for EMS and fire - exhibited at APCO 2026</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>911 GIS data, indoor mapping and location services for PSAPs</t>
+          <t>911 GIS data, indoor mapping and location services for PSAPs - exhibited at APCO 2026</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>Public safety CAD, RMS, jail software - exhibited at IACP 2026</t>
+          <t>Public safety CAD, RMS, jail software - exhibited at IACP 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F295" s="7" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>Critical incident mapping data for responders - exhibited at IACP 2026</t>
+          <t>Critical incident mapping data for responders - exhibited at IACP 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="E301" s="5" t="inlineStr">
         <is>
-          <t>Online citizen police report filing - exhibited at IACP 2026</t>
+          <t>Online citizen police report filing - exhibited at IACP 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F301" s="7" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>Mobile incident collaboration software for responders - exhibited at IACP 2026</t>
+          <t>Mobile incident collaboration software for responders - exhibited at IACP 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="E321" s="5" t="inlineStr">
         <is>
-          <t>Public safety asset and fleet management software - exhibited at IACP 2026</t>
+          <t>Public safety asset and fleet management software - exhibited at IACP 2026, IAFC FRI 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F321" s="7" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="E327" s="5" t="inlineStr">
         <is>
-          <t>EMS/fire inventory and asset management software - exhibited at IACP 2026</t>
+          <t>EMS/fire inventory and asset management software - exhibited at IACP 2026, IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F327" s="7" t="inlineStr">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="E339" s="5" t="inlineStr">
         <is>
-          <t>Public safety scheduling and overtime software - exhibited at IACP 2026</t>
+          <t>Public safety scheduling and overtime software - exhibited at IACP 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F339" s="7" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>Public safety scheduling and workforce software - exhibited at IACP 2026</t>
+          <t>Public safety scheduling and workforce software - exhibited at IACP 2026, IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/10/26)</t>
+          <t>Hiring AEs? (9/11/26)</t>
         </is>
       </c>
     </row>
@@ -11847,7 +11847,7 @@
       </c>
       <c r="F26" s="65" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Senior Solutions Architect, Govern only</t>
+          <t>Sales (non-AE) - GTM Strategy &amp; Operations Lead only</t>
         </is>
       </c>
     </row>
@@ -12450,7 +12450,7 @@
       </c>
       <c r="E48" s="61" t="inlineStr">
         <is>
-          <t>EHR and care coordination for behavioral health and human services, incl. county agencies - exhibited at NatCon 2026</t>
+          <t>EHR and care coordination for behavioral health and human services, incl. county agencies - exhibited at NatCon 2026, NACCHO 360 2026</t>
         </is>
       </c>
       <c r="F48" s="63" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Digital substance use disorder prevention, intervention, and recovery support platform for treatment providers, state and county health agencies, drug courts, and Medicaid plans - exhibited at NatCon 2026</t>
+          <t>Digital substance use disorder prevention, intervention, and recovery support platform for treatment providers, state and county health agencies, drug courts, and Medicaid plans - exhibited at NatCon 2026, NACCHO 360 2026</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="E60" s="61" t="inlineStr">
         <is>
-          <t>Behavioral health and wellbeing content, screening, and care-navigation platform deployed by public health departments, health plans, and health systems for their communities - exhibited at NatCon 2026</t>
+          <t>Behavioral health and wellbeing content, screening, and care-navigation platform deployed by public health departments, health plans, and health systems for their communities - exhibited at NatCon 2026, NACCHO 360 2026</t>
         </is>
       </c>
       <c r="F60" s="63" t="inlineStr">
@@ -12981,9 +12981,9 @@
           <t>Human services EHR and care coordination software for behavioral health, residential, vocational rehab, and food assistance providers - exhibited at NatCon 2026</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Customer Success Manager only</t>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -13611,7 +13611,7 @@
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>Yes - Strategic Sales Director - West Co (United States)</t>
+          <t>Yes - Strategic Sales Director (United States)</t>
         </is>
       </c>
     </row>
@@ -13636,7 +13636,7 @@
       </c>
       <c r="E92" s="61" t="inlineStr">
         <is>
-          <t>Social care referral and closed-loop network for government agencies - exhibited at Healthcare IT Connect 2026</t>
+          <t>Social care referral and closed-loop network for government agencies - exhibited at Healthcare IT Connect 2026, NACCHO 360 2026</t>
         </is>
       </c>
       <c r="F92" s="63" t="inlineStr">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="E98" s="61" t="inlineStr">
         <is>
-          <t>Case management, intake, referral, and grant tracking software for public and nonprofit human services programs - exhibited at NatCon 2026</t>
+          <t>Case management, intake, referral, and grant tracking software for public and nonprofit human services programs - exhibited at NatCon 2026, NACCHO 360 2026</t>
         </is>
       </c>
       <c r="F98" s="64" t="inlineStr">
@@ -14419,7 +14419,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/10/26)</t>
+          <t>Hiring AEs? (9/11/26)</t>
         </is>
       </c>
     </row>
@@ -15023,9 +15023,9 @@
           <t>Digital textbook and courseware delivery platform for colleges, universities, and school districts - exhibited at NACUBO 2026</t>
         </is>
       </c>
-      <c r="F22" s="69" t="inlineStr">
-        <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+      <c r="F22" s="70" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sales Support - Keyholder only</t>
         </is>
       </c>
     </row>
@@ -15055,7 +15055,7 @@
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive - Benelux (United Kingdom)</t>
+          <t>Yes - Senior Account Executive - Parchme (United States)</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="F60" s="69" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17025,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/10/26)</t>
+          <t>Hiring AEs? (9/11/26)</t>
         </is>
       </c>
     </row>
@@ -17493,7 +17493,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/10/26)</t>
+          <t>Hiring AEs? (9/11/26)</t>
         </is>
       </c>
     </row>
@@ -17548,12 +17548,12 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Routing, in-cab fleet tech, and resident apps for waste operations</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive - Municipalities</t>
+          <t>Routing, in-cab fleet tech, and resident apps for waste operations - exhibited at SWANA WASTECON 2025</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
       </c>
     </row>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Enterprise software and vehicle technology for waste and recycling operators</t>
+          <t>Enterprise software and vehicle technology for waste and recycling operators - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
       <c r="F4" s="16" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>AI robotic sorting systems for recycling facilities (MRFs)</t>
+          <t>AI robotic sorting systems for recycling facilities (MRFs) - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -17758,7 +17758,7 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>Carts and bins with embedded RFID/telematics for collection programs</t>
+          <t>Carts and bins with embedded RFID/telematics for collection programs - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
@@ -17848,7 +17848,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>ArcGIS route optimization for waste/recycling collection and postal/utility fleets (FedEx-owned, 2025) - exhibited at AWWA ACE 2026</t>
+          <t>ArcGIS route optimization for waste/recycling collection and postal/utility fleets (FedEx-owned, 2025) - exhibited at AWWA ACE 2026, SWANA WASTECON 2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -17908,7 +17908,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Material recovery facility systems and sorting robots for municipal recycling</t>
+          <t>Material recovery facility systems and sorting robots for municipal recycling - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -18290,7 +18290,7 @@
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>Resident-facing recycling education and collection reminder apps for municipalities</t>
+          <t>Resident-facing recycling education and collection reminder apps for municipalities - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Roll-out carts and container systems for municipal collection programs</t>
+          <t>Roll-out carts and container systems for municipal collection programs - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -19204,7 +19204,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>AI dashcams (EDGE/PULSE) for automated pothole and road-defect detection for public works</t>
+          <t>AI dashcams (EDGE/PULSE) for automated pothole and road-defect detection for public works - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -19714,7 +19714,7 @@
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>Connected-vehicle ITS and the Glance smart-city platform: signal monitoring, preemption, school beacons</t>
+          <t>Connected-vehicle ITS and the Glance smart-city platform: signal monitoring, preemption, school beacons - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F76" s="17" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="E96" s="13" t="inlineStr">
         <is>
-          <t>Safety Cloud digital alerting for DOT, fire and public works fleets</t>
+          <t>Safety Cloud digital alerting for DOT, fire and public works fleets - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
@@ -20636,7 +20636,7 @@
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>Water infrastructure: pumps, treatment, smart meters (Sensus), and analytics - exhibited at AWWA ACE 2026</t>
+          <t>Water infrastructure: pumps, treatment, smart meters (Sensus), and analytics - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>Water meters and ORION AMI networks for utilities - exhibited at AWWA ACE 2026</t>
+          <t>Water meters and ORION AMI networks for utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F108" s="16" t="inlineStr">
@@ -20696,7 +20696,7 @@
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>Hydrants, valves, and acoustic leak detection for water systems - exhibited at AWWA ACE 2026</t>
+          <t>Hydrants, valves, and acoustic leak detection for water systems - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
@@ -20756,7 +20756,7 @@
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>Permitting, compliance, and workflow software for water utilities - exhibited at AWWA ACE 2026</t>
+          <t>Permitting, compliance, and workflow software for water utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="E114" s="13" t="inlineStr">
         <is>
-          <t>Satellite-based leak detection and underground pipe assessment - exhibited at AWWA ACE 2026</t>
+          <t>Satellite-based leak detection and underground pipe assessment - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F114" s="15" t="inlineStr">
@@ -20876,7 +20876,7 @@
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>AI defect detection and coding for sewer inspection video - exhibited at AWWA ACE 2026</t>
+          <t>AI defect detection and coding for sewer inspection video - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F115" s="10" t="inlineStr">
@@ -20906,7 +20906,7 @@
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>Robotic sewer inspection and condition assessment services - exhibited at AWWA ACE 2026</t>
+          <t>Robotic sewer inspection and condition assessment services - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F116" s="16" t="inlineStr">
@@ -20996,7 +20996,7 @@
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>AI CCTV sewer and stormwater pipe condition assessment for councils and utilities</t>
+          <t>AI CCTV sewer and stormwater pipe condition assessment for councils and utilities - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>Water data management (AQUARIUS, WaterTrax) for utilities and environmental agencies - exhibited at AWWA ACE 2026</t>
+          <t>Water data management (AQUARIUS, WaterTrax) for utilities and environmental agencies - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F128" s="15" t="inlineStr">
@@ -21296,7 +21296,7 @@
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>Water quality instrumentation and analytics for municipal water and wastewater plants</t>
+          <t>Water quality instrumentation and analytics for municipal water and wastewater plants - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
@@ -21326,12 +21326,12 @@
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>Water quality and level monitoring instruments for agencies and utilities - exhibited at AWWA ACE 2026</t>
-        </is>
-      </c>
-      <c r="F130" s="15" t="inlineStr">
-        <is>
-          <t>Unknown - HTTP 520 for https://in-situ.com/careers</t>
+          <t>Water quality and level monitoring instruments for agencies and utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+        </is>
+      </c>
+      <c r="F130" s="16" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -21416,7 +21416,7 @@
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>Acoustic leak detection and district metering systems for water utilities - exhibited at AWWA ACE 2026</t>
+          <t>Acoustic leak detection and district metering systems for water utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>Sewer inspection cameras, trucks and software for municipal collection systems - exhibited at Maryland Municipal League 2026</t>
+          <t>Sewer inspection cameras, trucks and software for municipal collection systems - exhibited at Maryland Municipal League 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F139" s="10" t="inlineStr">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>Sewer inspection crawlers and push cameras for municipal wastewater agencies</t>
+          <t>Sewer inspection crawlers and push cameras for municipal wastewater agencies - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F140" s="15" t="inlineStr">
@@ -21656,7 +21656,7 @@
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>Sewer inspection data and reporting software for municipalities and contractors</t>
+          <t>Sewer inspection data and reporting software for municipalities and contractors - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>Sewer flow monitoring and I&amp;I analytics for municipal wastewater utilities</t>
+          <t>Sewer flow monitoring and I&amp;I analytics for municipal wastewater utilities - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
@@ -21746,7 +21746,7 @@
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>SL-RAT acoustic sewer line assessment tools for municipal sewer agencies</t>
+          <t>SL-RAT acoustic sewer line assessment tools for municipal sewer agencies - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F144" s="15" t="inlineStr">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>AI operations and forecasting software for water and wastewater utilities - exhibited at AWWA ACE 2026</t>
+          <t>AI operations and forecasting software for water and wastewater utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F145" s="10" t="inlineStr">
@@ -21926,7 +21926,7 @@
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
-          <t>VTScada SCADA software for municipal water and wastewater systems</t>
+          <t>VTScada SCADA software for municipal water and wastewater systems - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F150" s="15" t="inlineStr">
@@ -21986,7 +21986,7 @@
       </c>
       <c r="E152" s="13" t="inlineStr">
         <is>
-          <t>LeadCAST lead service line and digital delivery software for water utilities - exhibited at AWWA ACE 2026</t>
+          <t>LeadCAST lead service line and digital delivery software for water utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F152" s="15" t="inlineStr">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="E158" s="13" t="inlineStr">
         <is>
-          <t>Pump station control and optimization analytics for municipal water and wastewater utilities - exhibited at AWWA ACE 2026</t>
+          <t>Pump station control and optimization analytics for municipal water and wastewater utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F158" s="15" t="inlineStr">
@@ -22192,7 +22192,7 @@
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>AquaTwin digital twin software for water and sewer hydraulic modeling, surge analysis, and asset management, sold to water utilities and engineering consultants - exhibited at AWWA ACE 2026</t>
+          <t>AquaTwin digital twin software for water and sewer hydraulic modeling, surge analysis, and asset management, sold to water utilities and engineering consultants - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F159" s="10" t="inlineStr">
@@ -22246,7 +22246,7 @@
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>Operations data logging, sampling, and regulatory compliance reporting software for water and wastewater systems - exhibited at AWWA ACE 2026</t>
+          <t>Operations data logging, sampling, and regulatory compliance reporting software for water and wastewater systems - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
@@ -22362,7 +22362,7 @@
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>Cloud SCADA monitoring, alarming and analytics software for water and wastewater utilities, treatment plants and lift stations - exhibited at AWWA ACE 2026</t>
+          <t>Cloud SCADA monitoring, alarming and analytics software for water and wastewater utilities, treatment plants and lift stations - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
@@ -22532,7 +22532,7 @@
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>AI water loss and non-revenue water analytics that detect leaks, bursts and consumption anomalies from utility meter and SCADA data - exhibited at AWWA ACE 2026</t>
+          <t>AI water loss and non-revenue water analytics that detect leaks, bursts and consumption anomalies from utility meter and SCADA data - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>ArcGIS - the mapping and asset data backbone of most public works departments - exhibited at NLC City Summit 2026, AWWA ACE 2026, IAAO 2026, NASCIO 2026</t>
+          <t>ArcGIS - the mapping and asset data backbone of most public works departments - exhibited at NLC City Summit 2026, AWWA ACE 2026, IAAO 2026, NASCIO 2026, WEFTEC 2026, IAFC FRI 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F174" s="15" t="inlineStr">
@@ -22646,7 +22646,7 @@
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>IoT telematics and video safety for government fleets (public co) - exhibited at NLC City Summit 2026, PRIMA 2026, NAFA I&amp;E 2026</t>
+          <t>IoT telematics and video safety for government fleets (public co) - exhibited at NLC City Summit 2026, PRIMA 2026, NAFA I&amp;E 2026, NAPT Summit 2026, SWANA WASTECON 2025</t>
         </is>
       </c>
       <c r="F175" s="10" t="inlineStr">
@@ -23036,7 +23036,7 @@
       </c>
       <c r="E188" s="13" t="inlineStr">
         <is>
-          <t>AI fleet platform: telematics, dashcams, spend - with a dedicated public-sector offering - exhibited at NAFA I&amp;E 2026</t>
+          <t>AI fleet platform: telematics, dashcams, spend - with a dedicated public-sector offering - exhibited at NAFA I&amp;E 2026, SWANA WASTECON 2025</t>
         </is>
       </c>
       <c r="F188" s="16" t="inlineStr">
@@ -23156,7 +23156,7 @@
       </c>
       <c r="E192" s="13" t="inlineStr">
         <is>
-          <t>Cloud EAM/CMMS with asset planning and 311 for public works and water utilities - exhibited at AWWA ACE 2026</t>
+          <t>Cloud EAM/CMMS with asset planning and 311 for public works and water utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F192" s="15" t="inlineStr">
@@ -23572,12 +23572,12 @@
       </c>
       <c r="E206" s="13" t="inlineStr">
         <is>
-          <t>Hexagon spin-off: geospatial, EAM, project controls, physical security, and public-safety CAD (~7,200 staff)</t>
+          <t>Hexagon spin-off: geospatial, EAM, project controls, physical security, and public-safety CAD (~7,200 staff) - exhibited at APCO 2026</t>
         </is>
       </c>
       <c r="F206" s="15" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -23602,7 +23602,7 @@
       </c>
       <c r="E207" s="5" t="inlineStr">
         <is>
-          <t>Global engineering and program management for public infrastructure (47K staff, $12B rev); owns StreetLight transportation analytics - exhibited at AWWA ACE 2026</t>
+          <t>Global engineering and program management for public infrastructure (47K staff, $12B rev); owns StreetLight transportation analytics - exhibited at AWWA ACE 2026, WEFTEC 2026, SWANA WASTECON 2025</t>
         </is>
       </c>
       <c r="F207" s="7" t="inlineStr">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>Mobile field inspection and asset data collection for public works</t>
+          <t>Mobile field inspection and asset data collection for public works - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
@@ -24623,7 +24623,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/10/26)</t>
+          <t>Hiring AEs? (9/11/26)</t>
         </is>
       </c>
     </row>
@@ -24708,7 +24708,7 @@
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>Municipal websites, 311/CRM, mass notification, and agenda software - exhibited at NLC City Summit 2026, AWWA ACE 2026, 3CMA 2026</t>
+          <t>Municipal websites, 311/CRM, mass notification, and agenda software - exhibited at NLC City Summit 2026, AWWA ACE 2026, 3CMA 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F4" s="22" t="inlineStr">
@@ -25961,7 +25961,7 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -26884,7 +26884,7 @@
       </c>
       <c r="E78" s="19" t="inlineStr">
         <is>
-          <t>Permitting, budgeting, procurement, and asset management cloud suite (Cox-owned) - exhibited at GFOA 2026, NLC City Summit 2026, NACE 2026, AWWA ACE 2026, GMIS International 2026, Maryland Municipal League 2026</t>
+          <t>Permitting, budgeting, procurement, and asset management cloud suite (Cox-owned) - exhibited at GFOA 2026, NLC City Summit 2026, NACE 2026, AWWA ACE 2026, GMIS International 2026, Maryland Municipal League 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F78" s="23" t="inlineStr">
@@ -28230,12 +28230,12 @@
       </c>
       <c r="E124" s="19" t="inlineStr">
         <is>
-          <t>The govtech giant: ERP, courts, public safety, permitting, and payments - exhibited at GFOA 2026, NLC City Summit 2026, PSHRA 2026, AWWA ACE 2026, IAAO 2026, NASCIO 2026, GMIS International 2026, NACM 2026, APPA Probation 2026, Iowa State Association of Counties 2026, Maryland Municipal League 2026</t>
-        </is>
-      </c>
-      <c r="F124" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>The govtech giant: ERP, courts, public safety, permitting, and payments - exhibited at GFOA 2026, NLC City Summit 2026, PSHRA 2026, AWWA ACE 2026, IAAO 2026, NASCIO 2026, GMIS International 2026, NACM 2026, APPA Probation 2026, Iowa State Association of Counties 2026, Maryland Municipal League 2026, IAFC FRI 2026, APCO 2026, NAPT Summit 2026</t>
+        </is>
+      </c>
+      <c r="F124" s="23" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -28415,7 +28415,7 @@
       </c>
       <c r="F130" s="21" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -29836,7 +29836,7 @@
       </c>
       <c r="E178" s="19" t="inlineStr">
         <is>
-          <t>Public-sector software suites with embedded payments: permitting, courts, utilities, DMV (NASDAQ: IIIV) - exhibited at GFOA 2026, NACM 2026</t>
+          <t>Public-sector software suites with embedded payments: permitting, courts, utilities, DMV (NASDAQ: IIIV) - exhibited at GFOA 2026, NACM 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F178" s="21" t="inlineStr">
@@ -30109,9 +30109,9 @@
           <t>Supplier ratings and performance reviews platform for public-sector buyers</t>
         </is>
       </c>
-      <c r="F187" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F187" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -30141,7 +30141,7 @@
       </c>
       <c r="F188" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://municibid.com/caree</t>
+          <t>Unknown - HTTP 404 for https://municibid.com/caree</t>
         </is>
       </c>
     </row>
@@ -30843,7 +30843,7 @@
       </c>
       <c r="F212" s="23" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (London)</t>
+          <t>Yes - Account Executive (Singapore, Singapo)</t>
         </is>
       </c>
     </row>
@@ -31168,7 +31168,7 @@
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>Payment gateway and processing for government billers and agencies</t>
+          <t>Payment gateway and processing for government billers and agencies - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
       <c r="F223" s="7" t="inlineStr">
@@ -31381,7 +31381,7 @@
       </c>
       <c r="F230" s="21" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -32561,9 +32561,9 @@
           <t>Local government ERP including payroll and personnel modules - exhibited at GFOA 2026, Maryland Municipal League 2026</t>
         </is>
       </c>
-      <c r="F270" s="21" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F270" s="22" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Client Success Manager only</t>
         </is>
       </c>
     </row>
@@ -32829,7 +32829,7 @@
       </c>
       <c r="F279" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -32889,7 +32889,7 @@
       </c>
       <c r="F281" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -33794,7 +33794,7 @@
       </c>
       <c r="E313" s="5" t="inlineStr">
         <is>
-          <t>Strategy execution and integrated plan management for agencies and enterprises - exhibited at NLC City Summit 2026</t>
+          <t>Strategy execution and integrated plan management for agencies and enterprises - exhibited at NLC City Summit 2026, NACCHO 360 2026</t>
         </is>
       </c>
       <c r="F313" s="7" t="inlineStr">
@@ -37474,7 +37474,7 @@
       </c>
       <c r="E442" s="19" t="inlineStr">
         <is>
-          <t>UKG Ready and NOVAtime time-and-attendance reseller and implementation partner for local government - exhibited at NACo 2026, NRPA 2026, GFOA 2026</t>
+          <t>UKG Ready and NOVAtime time-and-attendance reseller and implementation partner for local government - exhibited at NACo 2026, NRPA 2026, GFOA 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F442" s="21" t="inlineStr">
@@ -38707,7 +38707,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/10/26)</t>
+          <t>Hiring AEs? (9/11/26)</t>
         </is>
       </c>
     </row>
@@ -42023,9 +42023,9 @@
           <t>Lodging occupancy and vacation-rental benchmarking data for DMOs</t>
         </is>
       </c>
-      <c r="F112" s="28" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F112" s="27" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - DMO Partnerships Manager only</t>
         </is>
       </c>
     </row>
@@ -42989,7 +42989,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/10/26)</t>
+          <t>Hiring AEs? (9/11/26)</t>
         </is>
       </c>
     </row>
@@ -43224,7 +43224,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Panic button (Alyssa's Law), anonymous tips, and monitoring for schools and communities</t>
+          <t>Panic button (Alyssa's Law), anonymous tips, and monitoring for schools and communities - exhibited at NAPT Summit 2026</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -44258,7 +44258,7 @@
       </c>
       <c r="E44" s="31" t="inlineStr">
         <is>
-          <t>Vetted small-vehicle student rides supplementing district bus fleets</t>
+          <t>Vetted small-vehicle student rides supplementing district bus fleets - exhibited at NAPT Summit 2026</t>
         </is>
       </c>
       <c r="F44" s="33" t="inlineStr">
@@ -44378,7 +44378,7 @@
       </c>
       <c r="E48" s="31" t="inlineStr">
         <is>
-          <t>Student transportation routing and fleet software for districts</t>
+          <t>Student transportation routing and fleet software for districts - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
       <c r="F48" s="34" t="inlineStr">
@@ -44558,7 +44558,7 @@
       </c>
       <c r="E54" s="31" t="inlineStr">
         <is>
-          <t>Contracted school bus transportation services for K-12 districts</t>
+          <t>Contracted school bus transportation services for K-12 districts - exhibited at NAPT Summit 2026</t>
         </is>
       </c>
       <c r="F54" s="34" t="inlineStr">
@@ -44648,7 +44648,7 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>School bus camera and DVR surveillance systems for districts</t>
+          <t>School bus camera and DVR surveillance systems for districts - exhibited at NAPT Summit 2026</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="E60" s="31" t="inlineStr">
         <is>
-          <t>School buses and electric Jouley buses for K-12 districts</t>
+          <t>School buses and electric Jouley buses for K-12 districts - exhibited at NAPT Summit 2026</t>
         </is>
       </c>
       <c r="F60" s="34" t="inlineStr">
@@ -45546,7 +45546,7 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Alternative student transportation for school districts (formerly ALC Schools): contracted vehicles and drivers for students a yellow bus cannot serve, with dispatch and tracking for the district</t>
+          <t>Alternative student transportation for school districts (formerly ALC Schools): contracted vehicles and drivers for students a yellow bus cannot serve, with dispatch and tracking for the district - exhibited at NAPT Summit 2026</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
@@ -47046,7 +47046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F201"/>
+  <dimension ref="A1:F192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -47085,7 +47085,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/10/26)</t>
+          <t>Hiring AEs? (9/11/26)</t>
         </is>
       </c>
     </row>
@@ -47440,7 +47440,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Fare collection, ticketing, and passenger information SaaS for transit agencies (ex-Ubitransport; US office NYC)</t>
+          <t>Fare collection, ticketing, and passenger information SaaS for transit agencies (ex-Ubitransport; US office NYC) - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -47598,16 +47598,16 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Unwire</t>
+          <t>FAIRTIQ</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>Bern, Switzerland</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>2003</v>
+        <v>2016</v>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
@@ -47616,28 +47616,28 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Mobile ticketing and MaaS platform for transit agencies in US and Europe</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Check-in/be-out mobile fare payment for public transport authorities</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Sales &amp; Business Development Manag</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="37" t="inlineStr">
         <is>
-          <t>FAIRTIQ</t>
+          <t>Ridango</t>
         </is>
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>Bern, Switzerland</t>
+          <t>Tallinn, Estonia</t>
         </is>
       </c>
       <c r="C20" s="38" t="n">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="D20" s="37" t="inlineStr">
         <is>
@@ -47646,28 +47646,28 @@
       </c>
       <c r="E20" s="37" t="inlineStr">
         <is>
-          <t>Check-in/be-out mobile fare payment for public transport authorities</t>
+          <t>Account-based fare collection and validators for public transit operators</t>
         </is>
       </c>
       <c r="F20" s="39" t="inlineStr">
         <is>
-          <t>Yes - Sales &amp; Business Development Manag</t>
+          <t>Yes - Senior Enterprise Account Executiv (Spain, Spain)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Ridango</t>
+          <t>Moovit</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Tallinn, Estonia</t>
+          <t>Tel Aviv, Israel</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
@@ -47676,37 +47676,37 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Account-based fare collection and validators for public transit operators</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Senior Enterprise Account Executiv (Spain, Spain)</t>
+          <t>MaaS and ticketing platform licensed to transit agencies and cities</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="37" t="inlineStr">
         <is>
-          <t>Moovit</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="B22" s="37" t="inlineStr">
         <is>
-          <t>Tel Aviv, Israel</t>
+          <t>Woodbury, NY</t>
         </is>
       </c>
       <c r="C22" s="38" t="n">
-        <v>2011</v>
+        <v>1988</v>
       </c>
       <c r="D22" s="37" t="inlineStr">
         <is>
-          <t>Fare &amp; Payments</t>
+          <t>Fleet &amp; Operations</t>
         </is>
       </c>
       <c r="E22" s="37" t="inlineStr">
         <is>
-          <t>MaaS and ticketing platform licensed to transit agencies and cities</t>
+          <t>Bus ITS: CAD/AVL, real-time passenger info, and fleet health</t>
         </is>
       </c>
       <c r="F22" s="40" t="inlineStr">
@@ -47718,16 +47718,16 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Optibus</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Woodbury, NY</t>
+          <t>Tel Aviv, Israel</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>1988</v>
+        <v>2014</v>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
@@ -47736,24 +47736,24 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Bus ITS: CAD/AVL, real-time passenger info, and fleet health</t>
+          <t>AI scheduling, rostering, and planning platform for bus networks</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="37" t="inlineStr">
         <is>
-          <t>Optibus</t>
+          <t>Swiftly</t>
         </is>
       </c>
       <c r="B24" s="37" t="inlineStr">
         <is>
-          <t>Tel Aviv, Israel</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="C24" s="38" t="n">
@@ -47766,28 +47766,28 @@
       </c>
       <c r="E24" s="37" t="inlineStr">
         <is>
-          <t>AI scheduling, rostering, and planning platform for bus networks</t>
-        </is>
-      </c>
-      <c r="F24" s="40" t="inlineStr">
-        <is>
-          <t>None found</t>
+          <t>Real-time transit data: arrival predictions and on-time performance</t>
+        </is>
+      </c>
+      <c r="F24" s="39" t="inlineStr">
+        <is>
+          <t>Yes - Senior Account Manager (United States)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Swiftly</t>
+          <t>INIT</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Chesapeake, VA</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>2014</v>
+        <v>1983</v>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
@@ -47796,28 +47796,28 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Real-time transit data: arrival predictions and on-time performance</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Senior Account Manager (United States)</t>
+          <t>CAD/AVL, dispatching, service planning, and fare collection for transit agencies (INIT SE, Karlsruhe)</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 404 for https://www.initse.com/enus</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="37" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>Avail Technologies</t>
         </is>
       </c>
       <c r="B26" s="37" t="inlineStr">
         <is>
-          <t>Chesapeake, VA</t>
+          <t>State College, PA</t>
         </is>
       </c>
       <c r="C26" s="38" t="n">
-        <v>1983</v>
+        <v>1999</v>
       </c>
       <c r="D26" s="37" t="inlineStr">
         <is>
@@ -47826,28 +47826,28 @@
       </c>
       <c r="E26" s="37" t="inlineStr">
         <is>
-          <t>CAD/AVL, dispatching, service planning, and fare collection for transit agencies (INIT SE, Karlsruhe)</t>
+          <t>myAvail enterprise transit management ITS and CAD/AVL for mid-size US agencies</t>
         </is>
       </c>
       <c r="F26" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://www.initse.com/enus</t>
+          <t>Unknown - HTTP 404 for https://availtec.com/career</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Avail Technologies</t>
+          <t>GIRO</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>State College, PA</t>
+          <t>Montreal, QC, Canada</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>1999</v>
+        <v>1979</v>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
@@ -47856,28 +47856,28 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>myAvail enterprise transit management ITS and CAD/AVL for mid-size US agencies</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - HTTP 404 for https://availtec.com/career</t>
+          <t>HASTUS scheduling, run-cutting, and rostering for transit agencies and postal operators</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Director, Strategic Business Devel only</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="37" t="inlineStr">
         <is>
-          <t>GIRO</t>
+          <t>IVU Traffic Technologies</t>
         </is>
       </c>
       <c r="B28" s="37" t="inlineStr">
         <is>
-          <t>Montreal, QC, Canada</t>
+          <t>Berlin, Germany</t>
         </is>
       </c>
       <c r="C28" s="38" t="n">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="D28" s="37" t="inlineStr">
         <is>
@@ -47886,28 +47886,28 @@
       </c>
       <c r="E28" s="37" t="inlineStr">
         <is>
-          <t>HASTUS scheduling, run-cutting, and rostering for transit agencies and postal operators</t>
-        </is>
-      </c>
-      <c r="F28" s="41" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Director, Strategic Business Devel only</t>
+          <t>IVU.suite planning, scheduling, dispatch, and ticketing for transit and rail operators</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 404 for https://www.ivu.com/career</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>IVU Traffic Technologies</t>
+          <t>Modaxo</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>1976</v>
+        <v>2020</v>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
@@ -47916,28 +47916,28 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>IVU.suite planning, scheduling, dispatch, and ticketing for transit and rail operators</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - HTTP 404 for https://www.ivu.com/career</t>
+          <t>Holding group of ~34 transit software brands under Constellation (Trapeze, Vontas, TransTrack, TripSpark, TransLoc)</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sales &amp; Marketing Director only</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="37" t="inlineStr">
         <is>
-          <t>Modaxo</t>
+          <t>Vontas</t>
         </is>
       </c>
       <c r="B30" s="37" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Cedar Rapids, IA</t>
         </is>
       </c>
       <c r="C30" s="38" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D30" s="37" t="inlineStr">
         <is>
@@ -47946,28 +47946,28 @@
       </c>
       <c r="E30" s="37" t="inlineStr">
         <is>
-          <t>Holding group of ~34 transit software brands under Constellation (Trapeze, Vontas, TransTrack, TripSpark, TransLoc)</t>
-        </is>
-      </c>
-      <c r="F30" s="41" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Sales &amp; Marketing Director only</t>
+          <t>Transit dispatch, CAD/AVL, and communications software (Modaxo brand, ex-Trapeze ITS)</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Vontas</t>
+          <t>Enghouse Transportation</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA</t>
+          <t>Markham, ON, Canada</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>2021</v>
+        <v>1984</v>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
@@ -47976,28 +47976,28 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Transit dispatch, CAD/AVL, and communications software (Modaxo brand, ex-Trapeze ITS)</t>
+          <t>Transit CAD/AVL, route optimization, and fare collection for agencies and DOTs (TSX: ENGH)</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 202 for https://www.enghouse.com/ca</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="37" t="inlineStr">
         <is>
-          <t>Enghouse Transportation</t>
+          <t>Consat</t>
         </is>
       </c>
       <c r="B32" s="37" t="inlineStr">
         <is>
-          <t>Markham, ON, Canada</t>
+          <t>Partille, Sweden</t>
         </is>
       </c>
       <c r="C32" s="38" t="n">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="D32" s="37" t="inlineStr">
         <is>
@@ -48006,28 +48006,28 @@
       </c>
       <c r="E32" s="37" t="inlineStr">
         <is>
-          <t>Transit CAD/AVL, route optimization, and fare collection for agencies and DOTs (TSX: ENGH)</t>
+          <t>Consat Telematics real-time CAD/AVL, passenger info, and electromobility analytics (NA office Sudbury ON)</t>
         </is>
       </c>
       <c r="F32" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.enghouse.com/ca</t>
+          <t>Unknown - HTTP 404 for https://www.consat.com/care</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Consat</t>
+          <t>GMV</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Partille, Sweden</t>
+          <t>Madrid, Spain</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
@@ -48036,28 +48036,28 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Consat Telematics real-time CAD/AVL, passenger info, and electromobility analytics (NA office Sudbury ON)</t>
+          <t>Transit ITS, CAD/AVL, and fare collection (GMV Syncromatics in North America; LA and Houston)</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://www.consat.com/care</t>
+          <t>Unknown - HTTP 404 for https://www.gmv.com/en/care</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="37" t="inlineStr">
         <is>
-          <t>GMV</t>
+          <t>TransTrack Solutions Group</t>
         </is>
       </c>
       <c r="B34" s="37" t="inlineStr">
         <is>
-          <t>Madrid, Spain</t>
+          <t>Cedar Rapids, IA</t>
         </is>
       </c>
       <c r="C34" s="38" t="n">
-        <v>1984</v>
+        <v>2000</v>
       </c>
       <c r="D34" s="37" t="inlineStr">
         <is>
@@ -48066,28 +48066,28 @@
       </c>
       <c r="E34" s="37" t="inlineStr">
         <is>
-          <t>Transit ITS, CAD/AVL, and fare collection (GMV Syncromatics in North America; LA and Houston)</t>
+          <t>Transit performance data warehousing, BI, and automated NTD reporting (Modaxo brand) - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
       <c r="F34" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://www.gmv.com/en/care</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TransTrack Solutions Group</t>
+          <t>CSched</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA</t>
+          <t>Laval, QC, Canada</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>2000</v>
+        <v>2008</v>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
@@ -48096,29 +48096,23 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Transit performance data warehousing, BI, and automated NTD reporting (Modaxo brand)</t>
+          <t>Transit scheduling consulting and exclusive North American HASTUS reseller (acquired by CIMA+, 2026)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="37" t="inlineStr">
         <is>
-          <t>CSched</t>
-        </is>
-      </c>
-      <c r="B36" s="37" t="inlineStr">
-        <is>
-          <t>Laval, QC, Canada</t>
-        </is>
-      </c>
-      <c r="C36" s="38" t="n">
-        <v>2008</v>
-      </c>
+          <t>Transit-Systems (TSL)</t>
+        </is>
+      </c>
+      <c r="B36" s="37" t="n"/>
+      <c r="C36" s="38" t="n"/>
       <c r="D36" s="37" t="inlineStr">
         <is>
           <t>Fleet &amp; Operations</t>
@@ -48126,28 +48120,28 @@
       </c>
       <c r="E36" s="37" t="inlineStr">
         <is>
-          <t>Transit scheduling consulting and exclusive North American HASTUS reseller (acquired by CIMA+, 2026)</t>
+          <t>Cloud CAD/AVL and in-vehicle tech for transit agencies and campus systems (SDVOSB)</t>
         </is>
       </c>
       <c r="F36" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TransitCheck</t>
+          <t>Connixt</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Rocklin, CA</t>
+          <t>Cerritos, CA</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
@@ -48156,23 +48150,29 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Tablet-based electronic vehicle inspection (EVIR) for transit, school bus, and fleets (Revecorp)</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>iMarq mobile asset maintenance and MRO platform for transit, rail, and fleets</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="37" t="inlineStr">
         <is>
-          <t>Transit-Systems (TSL)</t>
-        </is>
-      </c>
-      <c r="B38" s="37" t="n"/>
-      <c r="C38" s="38" t="n"/>
+          <t>Interloc Solutions</t>
+        </is>
+      </c>
+      <c r="B38" s="37" t="inlineStr">
+        <is>
+          <t>Folsom, CA</t>
+        </is>
+      </c>
+      <c r="C38" s="38" t="n">
+        <v>2005</v>
+      </c>
       <c r="D38" s="37" t="inlineStr">
         <is>
           <t>Fleet &amp; Operations</t>
@@ -48180,28 +48180,28 @@
       </c>
       <c r="E38" s="37" t="inlineStr">
         <is>
-          <t>Cloud CAD/AVL and in-vehicle tech for transit agencies and campus systems (SDVOSB)</t>
+          <t>IBM Maximo consulting plus Mobile Informer EAM for transit agencies, airports, and utilities</t>
         </is>
       </c>
       <c r="F38" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 404 for https://www.interlocsolutio</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Connixt</t>
+          <t>Wi-Tronix</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Cerritos, CA</t>
+          <t>Bolingbrook, IL</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>2015</v>
+        <v>2004</v>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
@@ -48210,28 +48210,28 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>iMarq mobile asset maintenance and MRO platform for transit, rail, and fleets</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>AI locomotive telematics, video analytics, and diagnostics for railroads and passenger rail</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="37" t="inlineStr">
         <is>
-          <t>Interloc Solutions</t>
+          <t>Quester Tangent</t>
         </is>
       </c>
       <c r="B40" s="37" t="inlineStr">
         <is>
-          <t>Folsom, CA</t>
+          <t>Saanichton, BC, Canada</t>
         </is>
       </c>
       <c r="C40" s="38" t="n">
-        <v>2005</v>
+        <v>1983</v>
       </c>
       <c r="D40" s="37" t="inlineStr">
         <is>
@@ -48240,24 +48240,24 @@
       </c>
       <c r="E40" s="37" t="inlineStr">
         <is>
-          <t>IBM Maximo consulting plus Mobile Informer EAM for transit agencies, airports, and utilities</t>
+          <t>Trainwise onboard train control/monitoring and Fleetwise wayside fleet management for transit</t>
         </is>
       </c>
       <c r="F40" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://www.interlocsolutio</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Wi-Tronix</t>
+          <t>Tracsis</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL</t>
+          <t>Leeds, UK</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
@@ -48270,28 +48270,28 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>AI locomotive telematics, video analytics, and diagnostics for railroads and passenger rail</t>
+          <t>Rail and transit software: crew/vehicle scheduling, remote condition monitoring, and analytics (AIM: TRCS)</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - page too small - likely JS-rendered</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="37" t="inlineStr">
         <is>
-          <t>Quester Tangent</t>
+          <t>Railroad Software</t>
         </is>
       </c>
       <c r="B42" s="37" t="inlineStr">
         <is>
-          <t>Saanichton, BC, Canada</t>
+          <t>Cumming, GA</t>
         </is>
       </c>
       <c r="C42" s="38" t="n">
-        <v>1983</v>
+        <v>2012</v>
       </c>
       <c r="D42" s="37" t="inlineStr">
         <is>
@@ -48300,28 +48300,28 @@
       </c>
       <c r="E42" s="37" t="inlineStr">
         <is>
-          <t>Trainwise onboard train control/monitoring and Fleetwise wayside fleet management for transit</t>
+          <t>Rail terminal management, track inspection, and crew compliance for short lines and commuter rail</t>
         </is>
       </c>
       <c r="F42" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Tracsis</t>
+          <t>Willowglen Systems</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Leeds, UK</t>
+          <t>Edmonton, AB, Canada</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>2004</v>
+        <v>1971</v>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
@@ -48330,28 +48330,28 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Rail and transit software: crew/vehicle scheduling, remote condition monitoring, and analytics (AIM: TRCS)</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page too small - likely JS-rendered</t>
+          <t>SCADA systems and the SentientQ automation platform for rail transit, LRT, and utilities</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Business Development Manager</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="37" t="inlineStr">
         <is>
-          <t>Railroad Software</t>
+          <t>Piper Networks</t>
         </is>
       </c>
       <c r="B44" s="37" t="inlineStr">
         <is>
-          <t>Cumming, GA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="C44" s="38" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D44" s="37" t="inlineStr">
         <is>
@@ -48360,28 +48360,28 @@
       </c>
       <c r="E44" s="37" t="inlineStr">
         <is>
-          <t>Rail terminal management, track inspection, and crew compliance for short lines and commuter rail</t>
+          <t>Ultra-wideband train positioning, worker protection, and ATP for transit agencies (NYC MTA)</t>
         </is>
       </c>
       <c r="F44" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Willowglen Systems</t>
+          <t>SIL4 Systems</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Edmonton, AB, Canada</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>1971</v>
+        <v>2009</v>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
@@ -48390,28 +48390,28 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>SCADA systems and the SentientQ automation platform for rail transit, LRT, and utilities</t>
-        </is>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Business Development Manager</t>
+          <t>Safety-critical SIL4 onboard computing, event recorders, and rail safety-case consulting</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="37" t="inlineStr">
         <is>
-          <t>Piper Networks</t>
+          <t>Cylus</t>
         </is>
       </c>
       <c r="B46" s="37" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Tel Aviv, Israel</t>
         </is>
       </c>
       <c r="C46" s="38" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="D46" s="37" t="inlineStr">
         <is>
@@ -48420,7 +48420,7 @@
       </c>
       <c r="E46" s="37" t="inlineStr">
         <is>
-          <t>Ultra-wideband train positioning, worker protection, and ATP for transit agencies (NYC MTA)</t>
+          <t>CylusOne rail OT cybersecurity: threat detection for signaling, trackside, and onboard networks</t>
         </is>
       </c>
       <c r="F46" s="40" t="inlineStr">
@@ -48432,16 +48432,16 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>SIL4 Systems</t>
+          <t>Citiri</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>2009</v>
+        <v>2018</v>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Safety-critical SIL4 onboard computing, event recorders, and rail safety-case consulting</t>
+          <t>CitiriOS owner scope management and operational readiness (ORAT) for transit, airports, and utilities</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -48462,17 +48462,15 @@
     <row r="48">
       <c r="A48" s="37" t="inlineStr">
         <is>
-          <t>Cylus</t>
+          <t>ConnX</t>
         </is>
       </c>
       <c r="B48" s="37" t="inlineStr">
         <is>
-          <t>Tel Aviv, Israel</t>
-        </is>
-      </c>
-      <c r="C48" s="38" t="n">
-        <v>2017</v>
-      </c>
+          <t>Plainsboro, NJ</t>
+        </is>
+      </c>
+      <c r="C48" s="38" t="n"/>
       <c r="D48" s="37" t="inlineStr">
         <is>
           <t>Fleet &amp; Operations</t>
@@ -48480,7 +48478,7 @@
       </c>
       <c r="E48" s="37" t="inlineStr">
         <is>
-          <t>CylusOne rail OT cybersecurity: threat detection for signaling, trackside, and onboard networks</t>
+          <t>ConnX Maestro unified communications and contact center for transit agencies (SEPTA)</t>
         </is>
       </c>
       <c r="F48" s="40" t="inlineStr">
@@ -48492,16 +48490,16 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Citiri</t>
+          <t>CSiT (CSinTrans)</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Montreal, QC, Canada</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
@@ -48510,7 +48508,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>CitiriOS owner scope management and operational readiness (ORAT) for transit, airports, and utilities</t>
+          <t>TRANSIS operations management, passenger info, and control-center integration (NY MTA Genius winner)</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -48522,12 +48520,12 @@
     <row r="50">
       <c r="A50" s="37" t="inlineStr">
         <is>
-          <t>ConnX</t>
+          <t>Knaq</t>
         </is>
       </c>
       <c r="B50" s="37" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="C50" s="38" t="n"/>
@@ -48538,28 +48536,28 @@
       </c>
       <c r="E50" s="37" t="inlineStr">
         <is>
-          <t>ConnX Maestro unified communications and contact center for transit agencies (SEPTA)</t>
+          <t>Non-invasive sensors and cloud analytics for elevator, escalator, and HVAC uptime in transit stations</t>
         </is>
       </c>
       <c r="F50" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>CSiT (CSinTrans)</t>
+          <t>ROK Brothers</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Montreal, QC, Canada</t>
+          <t>Millersville, MD</t>
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>2011</v>
+        <v>1993</v>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
@@ -48568,7 +48566,7 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>TRANSIS operations management, passenger info, and control-center integration (NY MTA Genius winner)</t>
+          <t>Managed cellular connectivity, routers, and failover for transit fleets and remote assets</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -48580,12 +48578,12 @@
     <row r="52">
       <c r="A52" s="37" t="inlineStr">
         <is>
-          <t>Knaq</t>
+          <t>In A Blink</t>
         </is>
       </c>
       <c r="B52" s="37" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Pointe-Claire, QC, Canada</t>
         </is>
       </c>
       <c r="C52" s="38" t="n"/>
@@ -48596,7 +48594,7 @@
       </c>
       <c r="E52" s="37" t="inlineStr">
         <is>
-          <t>Non-invasive sensors and cloud analytics for elevator, escalator, and HVAC uptime in transit stations</t>
+          <t>Virtual Optical Fiber high-speed data offload between transit vehicles and depots</t>
         </is>
       </c>
       <c r="F52" s="40" t="inlineStr">
@@ -48608,16 +48606,16 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>ROK Brothers</t>
+          <t>LYT</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Millersville, MD</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>1993</v>
+        <v>2016</v>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
@@ -48626,27 +48624,29 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Managed cellular connectivity, routers, and failover for transit fleets and remote assets</t>
+          <t>AI transit signal priority and emergency preemption for cities and agencies (MBTA, King County) - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="37" t="inlineStr">
         <is>
-          <t>In A Blink</t>
+          <t>Sahay AI</t>
         </is>
       </c>
       <c r="B54" s="37" t="inlineStr">
         <is>
-          <t>Pointe-Claire, QC, Canada</t>
-        </is>
-      </c>
-      <c r="C54" s="38" t="n"/>
+          <t>Philadelphia, PA</t>
+        </is>
+      </c>
+      <c r="C54" s="38" t="n">
+        <v>2023</v>
+      </c>
       <c r="D54" s="37" t="inlineStr">
         <is>
           <t>Fleet &amp; Operations</t>
@@ -48654,7 +48654,7 @@
       </c>
       <c r="E54" s="37" t="inlineStr">
         <is>
-          <t>Virtual Optical Fiber high-speed data offload between transit vehicles and depots</t>
+          <t>AI smart inspection for rail infrastructure: sensor robot plus defect detection and predictive maintenance</t>
         </is>
       </c>
       <c r="F54" s="40" t="inlineStr">
@@ -48666,16 +48666,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>LYT</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>San Jose, CA</t>
-        </is>
-      </c>
+          <t>Transify</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n"/>
       <c r="C55" s="6" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
@@ -48684,28 +48680,28 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>AI transit signal priority and emergency preemption for cities and agencies (MBTA, King County)</t>
+          <t>Bus service performance analytics and visualization built on APC ridership data</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="37" t="inlineStr">
         <is>
-          <t>Sahay AI</t>
+          <t>AngelTrax</t>
         </is>
       </c>
       <c r="B56" s="37" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Dothan, AL</t>
         </is>
       </c>
       <c r="C56" s="38" t="n">
-        <v>2023</v>
+        <v>2006</v>
       </c>
       <c r="D56" s="37" t="inlineStr">
         <is>
@@ -48714,24 +48710,28 @@
       </c>
       <c r="E56" s="37" t="inlineStr">
         <is>
-          <t>AI smart inspection for rail infrastructure: sensor robot plus defect detection and predictive maintenance</t>
-        </is>
-      </c>
-      <c r="F56" s="40" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Mobile video surveillance, DVRs, and MotoTrax analytics for transit, school, and municipal fleets - exhibited at CTAA EXPO 2026, NAPT Summit 2026</t>
+        </is>
+      </c>
+      <c r="F56" s="39" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Transify</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="n"/>
+          <t>Safety Vision</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
       <c r="C57" s="6" t="n">
-        <v>2020</v>
+        <v>1993</v>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
@@ -48740,28 +48740,28 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Bus service performance analytics and visualization built on APC ridership data</t>
+          <t>Mobile video surveillance and fleet safety cameras for mass transit, school buses, and police - exhibited at CTAA EXPO 2026, NAPT Summit 2026, SWANA WASTECON 2025</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="37" t="inlineStr">
         <is>
-          <t>AngelTrax</t>
+          <t>r2p</t>
         </is>
       </c>
       <c r="B58" s="37" t="inlineStr">
         <is>
-          <t>Dothan, AL</t>
+          <t>Flensburg, Germany</t>
         </is>
       </c>
       <c r="C58" s="38" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D58" s="37" t="inlineStr">
         <is>
@@ -48770,28 +48770,28 @@
       </c>
       <c r="E58" s="37" t="inlineStr">
         <is>
-          <t>Mobile video surveillance, DVRs, and MotoTrax analytics for transit, school, and municipal fleets</t>
-        </is>
-      </c>
-      <c r="F58" s="39" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Onboard transit systems: Horizon CCTV, NetSpire passenger info, iConnex real-time (US in Buffalo NY)</t>
+        </is>
+      </c>
+      <c r="F58" s="40" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Safety Vision</t>
+          <t>Rosco Vision</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Jamaica, NY</t>
         </is>
       </c>
       <c r="C59" s="6" t="n">
-        <v>1993</v>
+        <v>1907</v>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
@@ -48800,7 +48800,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Mobile video surveillance and fleet safety cameras for mass transit, school buses, and police</t>
+          <t>Vehicle safety vision: e-mirrors, backup cameras, and fleet recording for transit and school buses - exhibited at CTAA EXPO 2026, NAPT Summit 2026</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -48812,16 +48812,16 @@
     <row r="60">
       <c r="A60" s="37" t="inlineStr">
         <is>
-          <t>r2p</t>
+          <t>Gatekeeper Systems</t>
         </is>
       </c>
       <c r="B60" s="37" t="inlineStr">
         <is>
-          <t>Flensburg, Germany</t>
+          <t>Abbotsford, BC, Canada</t>
         </is>
       </c>
       <c r="C60" s="38" t="n">
-        <v>2007</v>
+        <v>1997</v>
       </c>
       <c r="D60" s="37" t="inlineStr">
         <is>
@@ -48830,28 +48830,28 @@
       </c>
       <c r="E60" s="37" t="inlineStr">
         <is>
-          <t>Onboard transit systems: Horizon CCTV, NetSpire passenger info, iConnex real-time (US in Buffalo NY)</t>
+          <t>Intelligent video, AI stop-arm analytics, and cloud safety platforms for transit and school districts - exhibited at CTAA EXPO 2026, NAPT Summit 2026</t>
         </is>
       </c>
       <c r="F60" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Rosco Vision</t>
+          <t>March Networks</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Jamaica, NY</t>
+          <t>Ottawa, ON, Canada</t>
         </is>
       </c>
       <c r="C61" s="6" t="n">
-        <v>1907</v>
+        <v>2000</v>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
@@ -48860,28 +48860,28 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Vehicle safety vision: e-mirrors, backup cameras, and fleet recording for transit and school buses</t>
+          <t>Enterprise IP video surveillance and AI analytics for transit, banking, and government</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 404 for https://apply.workable.com/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="37" t="inlineStr">
         <is>
-          <t>Gatekeeper Systems</t>
+          <t>Streamax America</t>
         </is>
       </c>
       <c r="B62" s="37" t="inlineStr">
         <is>
-          <t>Abbotsford, BC, Canada</t>
+          <t>Shenzhen, China</t>
         </is>
       </c>
       <c r="C62" s="38" t="n">
-        <v>1997</v>
+        <v>2002</v>
       </c>
       <c r="D62" s="37" t="inlineStr">
         <is>
@@ -48890,28 +48890,28 @@
       </c>
       <c r="E62" s="37" t="inlineStr">
         <is>
-          <t>Intelligent video, AI stop-arm analytics, and cloud safety platforms for transit and school districts</t>
+          <t>AI dashcams, MDVRs, and fleet video telematics for transit, school bus, and commercial fleets (US: Houston)</t>
         </is>
       </c>
       <c r="F62" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>March Networks</t>
+          <t>Protran Technology</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Ottawa, ON, Canada</t>
+          <t>Cherry Hill, NJ</t>
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
@@ -48920,28 +48920,28 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Enterprise IP video surveillance and AI analytics for transit, banking, and government</t>
+          <t>Transit worker safety: track-worker warning, collision avoidance, and Safe Turn Alert (Harsco/Enviri)</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://apply.workable.com/</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="37" t="inlineStr">
         <is>
-          <t>Streamax America</t>
+          <t>Xovis</t>
         </is>
       </c>
       <c r="B64" s="37" t="inlineStr">
         <is>
-          <t>Shenzhen, China</t>
+          <t>Zollikofen, Switzerland</t>
         </is>
       </c>
       <c r="C64" s="38" t="n">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="D64" s="37" t="inlineStr">
         <is>
@@ -48950,28 +48950,28 @@
       </c>
       <c r="E64" s="37" t="inlineStr">
         <is>
-          <t>AI dashcams, MDVRs, and fleet video telematics for transit, school bus, and commercial fleets (US: Houston)</t>
+          <t>3D AI people-flow sensors for passenger counting, queue, and dwell in transit hubs and airports</t>
         </is>
       </c>
       <c r="F64" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Protran Technology</t>
+          <t>Infodev EDI</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Cherry Hill, NJ</t>
+          <t>Quebec City, QC, Canada</t>
         </is>
       </c>
       <c r="C65" s="6" t="n">
-        <v>1999</v>
+        <v>1993</v>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
@@ -48980,28 +48980,28 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Transit worker safety: track-worker warning, collision avoidance, and Safe Turn Alert (Harsco/Enviri)</t>
+          <t>Automatic passenger counting sensors and analytics for ~450 transit clients in 50 countries</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="37" t="inlineStr">
         <is>
-          <t>Xovis</t>
+          <t>Urban Transportation Associates</t>
         </is>
       </c>
       <c r="B66" s="37" t="inlineStr">
         <is>
-          <t>Zollikofen, Switzerland</t>
+          <t>Cincinnati, OH</t>
         </is>
       </c>
       <c r="C66" s="38" t="n">
-        <v>2008</v>
+        <v>1981</v>
       </c>
       <c r="D66" s="37" t="inlineStr">
         <is>
@@ -49010,28 +49010,28 @@
       </c>
       <c r="E66" s="37" t="inlineStr">
         <is>
-          <t>3D AI people-flow sensors for passenger counting, queue, and dwell in transit hubs and airports</t>
+          <t>Automatic passenger counting hardware and analysis software for bus, rail, and paratransit</t>
         </is>
       </c>
       <c r="F66" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Infodev EDI</t>
+          <t>Visual Counter</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Quebec City, QC, Canada</t>
+          <t>Madrid, Spain</t>
         </is>
       </c>
       <c r="C67" s="6" t="n">
-        <v>1993</v>
+        <v>2002</v>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
@@ -49040,28 +49040,28 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Automatic passenger counting sensors and analytics for ~450 transit clients in 50 countries</t>
+          <t>People and passenger counting sensors with VC.TRANSIT analytics for transit and stations</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="37" t="inlineStr">
         <is>
-          <t>Urban Transportation Associates</t>
+          <t>Lytx</t>
         </is>
       </c>
       <c r="B68" s="37" t="inlineStr">
         <is>
-          <t>Cincinnati, OH</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="C68" s="38" t="n">
-        <v>1981</v>
+        <v>1998</v>
       </c>
       <c r="D68" s="37" t="inlineStr">
         <is>
@@ -49070,28 +49070,28 @@
       </c>
       <c r="E68" s="37" t="inlineStr">
         <is>
-          <t>Automatic passenger counting hardware and analysis software for bus, rail, and paratransit</t>
+          <t>Video telematics and driver safety for municipal and transit fleets - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
       <c r="F68" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Visual Counter</t>
+          <t>Netradyne</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Madrid, Spain</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="C69" s="6" t="n">
-        <v>2002</v>
+        <v>2015</v>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
@@ -49100,28 +49100,28 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>People and passenger counting sensors with VC.TRANSIT analytics for transit and stations</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>AI dashcam and driver coaching for public fleets</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive, Mid-Market (USA)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="37" t="inlineStr">
         <is>
-          <t>Lytx</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="B70" s="37" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Irvine, CA</t>
         </is>
       </c>
       <c r="C70" s="38" t="n">
-        <v>1998</v>
+        <v>1981</v>
       </c>
       <c r="D70" s="37" t="inlineStr">
         <is>
@@ -49130,28 +49130,28 @@
       </c>
       <c r="E70" s="37" t="inlineStr">
         <is>
-          <t>Video telematics and driver safety for municipal and transit fleets</t>
+          <t>Telematics devices and fleet tracking software for public fleets</t>
         </is>
       </c>
       <c r="F70" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no jobs parsed from iCIMS portal</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Netradyne</t>
+          <t>RTA Fleet Management</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Phoenix, AZ</t>
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>2015</v>
+        <v>1979</v>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
@@ -49160,28 +49160,28 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>AI dashcam and driver coaching for public fleets</t>
+          <t>Fleet maintenance software for cities, counties and transit agencies</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive, Mid-Market (USA)</t>
+          <t>Yes - Account Executive (Remote Worker)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="37" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>Chevin Fleet Solutions</t>
         </is>
       </c>
       <c r="B72" s="37" t="inlineStr">
         <is>
-          <t>Irvine, CA</t>
+          <t>Mount Laurel, NJ</t>
         </is>
       </c>
       <c r="C72" s="38" t="n">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="D72" s="37" t="inlineStr">
         <is>
@@ -49190,24 +49190,24 @@
       </c>
       <c r="E72" s="37" t="inlineStr">
         <is>
-          <t>Telematics devices and fleet tracking software for public fleets</t>
+          <t>FleetWave fleet asset management for public sector fleets</t>
         </is>
       </c>
       <c r="F72" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no jobs parsed from iCIMS portal</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>RTA Fleet Management</t>
+          <t>Dossier Systems</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Phoenix, AZ</t>
+          <t>Burlington, NJ</t>
         </is>
       </c>
       <c r="C73" s="6" t="n">
@@ -49220,28 +49220,28 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Fleet maintenance software for cities, counties and transit agencies</t>
-        </is>
-      </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+          <t>Fleet maintenance management software for transit and government fleets</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="37" t="inlineStr">
         <is>
-          <t>Chevin Fleet Solutions</t>
+          <t>Agile Fleet</t>
         </is>
       </c>
       <c r="B74" s="37" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ</t>
+          <t>Chantilly, VA</t>
         </is>
       </c>
       <c r="C74" s="38" t="n">
-        <v>1990</v>
+        <v>2005</v>
       </c>
       <c r="D74" s="37" t="inlineStr">
         <is>
@@ -49250,28 +49250,28 @@
       </c>
       <c r="E74" s="37" t="inlineStr">
         <is>
-          <t>FleetWave fleet asset management for public sector fleets</t>
+          <t>FleetCommander motor pool and vehicle sharing for agencies</t>
         </is>
       </c>
       <c r="F74" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Dossier Systems</t>
+          <t>Fleet Complete</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Burlington, NJ</t>
+          <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
       <c r="C75" s="6" t="n">
-        <v>1979</v>
+        <v>2000</v>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
@@ -49280,28 +49280,28 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Fleet maintenance management software for transit and government fleets</t>
-        </is>
-      </c>
-      <c r="F75" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Telematics and asset tracking for municipal and utility fleets</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="37" t="inlineStr">
         <is>
-          <t>Agile Fleet</t>
+          <t>Utilimarc</t>
         </is>
       </c>
       <c r="B76" s="37" t="inlineStr">
         <is>
-          <t>Chantilly, VA</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="C76" s="38" t="n">
-        <v>2005</v>
+        <v>1997</v>
       </c>
       <c r="D76" s="37" t="inlineStr">
         <is>
@@ -49310,7 +49310,7 @@
       </c>
       <c r="E76" s="37" t="inlineStr">
         <is>
-          <t>FleetCommander motor pool and vehicle sharing for agencies</t>
+          <t>Fleet data analytics and benchmarking for public and utility fleets</t>
         </is>
       </c>
       <c r="F76" s="40" t="inlineStr">
@@ -49322,16 +49322,16 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Fleet Complete</t>
+          <t>Whip Around</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Toronto, Ontario, Canada</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="C77" s="6" t="n">
-        <v>2000</v>
+        <v>2016</v>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
@@ -49340,28 +49340,28 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Telematics and asset tracking for municipal and utility fleets</t>
+          <t>Digital vehicle inspections and maintenance for municipal fleets</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="37" t="inlineStr">
         <is>
-          <t>Utilimarc</t>
+          <t>Ridecell</t>
         </is>
       </c>
       <c r="B78" s="37" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="C78" s="38" t="n">
-        <v>1997</v>
+        <v>2009</v>
       </c>
       <c r="D78" s="37" t="inlineStr">
         <is>
@@ -49370,28 +49370,28 @@
       </c>
       <c r="E78" s="37" t="inlineStr">
         <is>
-          <t>Fleet data analytics and benchmarking for public and utility fleets</t>
+          <t>Fleet automation and motor pool platform for public agencies</t>
         </is>
       </c>
       <c r="F78" s="40" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Whip Around</t>
+          <t>Omnitracs</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Westlake, TX</t>
         </is>
       </c>
       <c r="C79" s="6" t="n">
-        <v>2016</v>
+        <v>1988</v>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
@@ -49400,28 +49400,28 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Digital vehicle inspections and maintenance for municipal fleets</t>
+          <t>Fleet telematics and compliance software incl. government fleets</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="37" t="inlineStr">
         <is>
-          <t>Ridecell</t>
+          <t>Apollo Video Technology</t>
         </is>
       </c>
       <c r="B80" s="37" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Bothell, WA</t>
         </is>
       </c>
       <c r="C80" s="38" t="n">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="D80" s="37" t="inlineStr">
         <is>
@@ -49430,28 +49430,28 @@
       </c>
       <c r="E80" s="37" t="inlineStr">
         <is>
-          <t>Fleet automation and motor pool platform for public agencies</t>
+          <t>Onboard surveillance and video management for transit fleets</t>
         </is>
       </c>
       <c r="F80" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Omnitracs</t>
+          <t>Passio Technologies</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Westlake, TX</t>
+          <t>Alpharetta, GA</t>
         </is>
       </c>
       <c r="C81" s="6" t="n">
-        <v>1988</v>
+        <v>2009</v>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
@@ -49460,28 +49460,28 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Fleet telematics and compliance software incl. government fleets</t>
+          <t>AVL, passenger counting and rider apps for transit agencies</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="37" t="inlineStr">
         <is>
-          <t>Apollo Video Technology</t>
+          <t>Vix Technology</t>
         </is>
       </c>
       <c r="B82" s="37" t="inlineStr">
         <is>
-          <t>Bothell, WA</t>
+          <t>Perth, Australia</t>
         </is>
       </c>
       <c r="C82" s="38" t="n">
-        <v>2004</v>
+        <v>1985</v>
       </c>
       <c r="D82" s="37" t="inlineStr">
         <is>
@@ -49490,28 +49490,28 @@
       </c>
       <c r="E82" s="37" t="inlineStr">
         <is>
-          <t>Onboard surveillance and video management for transit fleets</t>
-        </is>
-      </c>
-      <c r="F82" s="40" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Fare collection and transit operations systems for agencies</t>
+        </is>
+      </c>
+      <c r="F82" s="41" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Solution Architect only</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Passio Technologies</t>
+          <t>Bytemark</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Alpharetta, GA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="C83" s="6" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
@@ -49520,28 +49520,28 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>AVL, passenger counting and rider apps for transit agencies</t>
+          <t>Mobile ticketing and account-based fare systems for transit</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="37" t="inlineStr">
         <is>
-          <t>Vix Technology</t>
+          <t>Liftango</t>
         </is>
       </c>
       <c r="B84" s="37" t="inlineStr">
         <is>
-          <t>Perth, Australia</t>
+          <t>Newcastle, Australia</t>
         </is>
       </c>
       <c r="C84" s="38" t="n">
-        <v>1985</v>
+        <v>2016</v>
       </c>
       <c r="D84" s="37" t="inlineStr">
         <is>
@@ -49550,28 +49550,28 @@
       </c>
       <c r="E84" s="37" t="inlineStr">
         <is>
-          <t>Fare collection and transit operations systems for agencies</t>
-        </is>
-      </c>
-      <c r="F84" s="41" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Solution Architect only</t>
+          <t>On-demand transit and shared mobility software for public agencies</t>
+        </is>
+      </c>
+      <c r="F84" s="40" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Bytemark</t>
+          <t>Padam Mobility</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Paris, France</t>
         </is>
       </c>
       <c r="C85" s="6" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
@@ -49580,28 +49580,28 @@
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Mobile ticketing and account-based fare systems for transit</t>
+          <t>Demand-responsive transport software for transit authorities</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="37" t="inlineStr">
         <is>
-          <t>Spare Labs</t>
+          <t>Flowbird</t>
         </is>
       </c>
       <c r="B86" s="37" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Moorestown, NJ</t>
         </is>
       </c>
       <c r="C86" s="38" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="D86" s="37" t="inlineStr">
         <is>
@@ -49610,28 +49610,28 @@
       </c>
       <c r="E86" s="37" t="inlineStr">
         <is>
-          <t>Demand-responsive transit and paratransit platform for agencies</t>
+          <t>Parking meters, kiosks and transit fare systems for cities</t>
         </is>
       </c>
       <c r="F86" s="40" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Liftango</t>
+          <t>CivicSmart</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Newcastle, Australia</t>
+          <t>Milwaukee, WI</t>
         </is>
       </c>
       <c r="C87" s="6" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
@@ -49640,7 +49640,7 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>On-demand transit and shared mobility software for public agencies</t>
+          <t>Smart parking meters and occupancy analytics for municipalities</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
@@ -49652,16 +49652,16 @@
     <row r="88">
       <c r="A88" s="37" t="inlineStr">
         <is>
-          <t>Padam Mobility</t>
+          <t>PayByPhone</t>
         </is>
       </c>
       <c r="B88" s="37" t="inlineStr">
         <is>
-          <t>Paris, France</t>
+          <t>Vancouver, BC, Canada</t>
         </is>
       </c>
       <c r="C88" s="38" t="n">
-        <v>2014</v>
+        <v>2001</v>
       </c>
       <c r="D88" s="37" t="inlineStr">
         <is>
@@ -49670,28 +49670,28 @@
       </c>
       <c r="E88" s="37" t="inlineStr">
         <is>
-          <t>Demand-responsive transport software for transit authorities</t>
-        </is>
-      </c>
-      <c r="F88" s="40" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Mobile parking payments for city and municipal parking operators</t>
+        </is>
+      </c>
+      <c r="F88" s="39" t="inlineStr">
+        <is>
+          <t>Yes - Corporate Sales Executive</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Flowbird</t>
+          <t>gtechna</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Moorestown, NJ</t>
+          <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
       <c r="C89" s="6" t="n">
-        <v>2018</v>
+        <v>1994</v>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Parking meters, kiosks and transit fare systems for cities</t>
+          <t>Parking enforcement, citation and permit software for cities</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -49712,16 +49712,16 @@
     <row r="90">
       <c r="A90" s="37" t="inlineStr">
         <is>
-          <t>CivicSmart</t>
+          <t>SKIDATA</t>
         </is>
       </c>
       <c r="B90" s="37" t="inlineStr">
         <is>
-          <t>Milwaukee, WI</t>
+          <t>Salzburg, Austria</t>
         </is>
       </c>
       <c r="C90" s="38" t="n">
-        <v>2015</v>
+        <v>1977</v>
       </c>
       <c r="D90" s="37" t="inlineStr">
         <is>
@@ -49730,28 +49730,28 @@
       </c>
       <c r="E90" s="37" t="inlineStr">
         <is>
-          <t>Smart parking meters and occupancy analytics for municipalities</t>
+          <t>Parking access and revenue control systems for public garages</t>
         </is>
       </c>
       <c r="F90" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>PayByPhone</t>
+          <t>Amano McGann</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="C91" s="6" t="n">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
@@ -49760,118 +49760,118 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Mobile parking payments for city and municipal parking operators</t>
-        </is>
-      </c>
-      <c r="F91" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Corporate Sales Executive</t>
+          <t>PARCS equipment and revenue control for municipal and airport parking</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="37" t="inlineStr">
         <is>
-          <t>gtechna</t>
+          <t>Verra Mobility</t>
         </is>
       </c>
       <c r="B92" s="37" t="inlineStr">
         <is>
-          <t>Montreal, Quebec, Canada</t>
+          <t>Mesa, AZ</t>
         </is>
       </c>
       <c r="C92" s="38" t="n">
-        <v>1994</v>
+        <v>1987</v>
       </c>
       <c r="D92" s="37" t="inlineStr">
         <is>
-          <t>Fleet &amp; Operations</t>
+          <t>Rider Experience</t>
         </is>
       </c>
       <c r="E92" s="37" t="inlineStr">
         <is>
-          <t>Parking enforcement, citation and permit software for cities</t>
-        </is>
-      </c>
-      <c r="F92" s="40" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Automated enforcement: school-zone speed, red-light, and bus-lane cameras - exhibited at North Carolina Sheriffs' Association 2026</t>
+        </is>
+      </c>
+      <c r="F92" s="39" t="inlineStr">
+        <is>
+          <t>Yes - Strategic Account Executive (North Carolina_Rem)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>SKIDATA</t>
+          <t>Hayden AI</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Salzburg, Austria</t>
+          <t>Oakland, CA</t>
         </is>
       </c>
       <c r="C93" s="6" t="n">
-        <v>1977</v>
+        <v>2019</v>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Fleet &amp; Operations</t>
+          <t>Rider Experience</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Parking access and revenue control systems for public garages</t>
+          <t>Bus-mounted AI cameras enforcing bus lanes and stops for transit agencies</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="37" t="inlineStr">
         <is>
-          <t>Amano McGann</t>
+          <t>Transit</t>
         </is>
       </c>
       <c r="B94" s="37" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Montreal, QC, Canada</t>
         </is>
       </c>
       <c r="C94" s="38" t="n">
-        <v>1998</v>
+        <v>2012</v>
       </c>
       <c r="D94" s="37" t="inlineStr">
         <is>
-          <t>Fleet &amp; Operations</t>
+          <t>Rider Experience</t>
         </is>
       </c>
       <c r="E94" s="37" t="inlineStr">
         <is>
-          <t>PARCS equipment and revenue control for municipal and airport parking</t>
+          <t>Multimodal trip planning app plus a paid agency suite (white-label apps, sponsored Royale, rider data) - exhibited at CTAA EXPO 2026, NAPT Summit 2026</t>
         </is>
       </c>
       <c r="F94" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>Verra Mobility</t>
+          <t>Papercast</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Mesa, AZ</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="C95" s="6" t="n">
-        <v>1987</v>
+        <v>2016</v>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
@@ -49880,28 +49880,28 @@
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Automated enforcement: school-zone speed, red-light, and bus-lane cameras - exhibited at North Carolina Sheriffs' Association 2026</t>
+          <t>Solar e-paper real-time passenger information displays and cloud CMS for bus stops and stations</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>Yes - Strategic Account Executive (North Carolina_Rem)</t>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="37" t="inlineStr">
         <is>
-          <t>Hayden AI</t>
+          <t>Connectpoint</t>
         </is>
       </c>
       <c r="B96" s="37" t="inlineStr">
         <is>
-          <t>Oakland, CA</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="C96" s="38" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="D96" s="37" t="inlineStr">
         <is>
@@ -49910,24 +49910,24 @@
       </c>
       <c r="E96" s="37" t="inlineStr">
         <is>
-          <t>Bus-mounted AI cameras enforcing bus lanes and stops for transit agencies</t>
+          <t>ePaper Digital Bus Stop, SmartStop kiosks, and CPAM content management for transit agencies</t>
         </is>
       </c>
       <c r="F96" s="40" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Transit</t>
+          <t>Peak Transit</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Montreal, QC, Canada</t>
+          <t>San Luis Obispo, CA</t>
         </is>
       </c>
       <c r="C97" s="6" t="n">
@@ -49940,28 +49940,28 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Multimodal trip planning app plus a paid agency suite (white-label apps, sponsored Royale, rider data)</t>
+          <t>CAD/AVL, rider apps, APC, and digital signage for agencies, universities, and airports</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="37" t="inlineStr">
         <is>
-          <t>Papercast</t>
+          <t>Luminator Technology Group</t>
         </is>
       </c>
       <c r="B98" s="37" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Plano, TX</t>
         </is>
       </c>
       <c r="C98" s="38" t="n">
-        <v>2016</v>
+        <v>1929</v>
       </c>
       <c r="D98" s="37" t="inlineStr">
         <is>
@@ -49970,28 +49970,28 @@
       </c>
       <c r="E98" s="37" t="inlineStr">
         <is>
-          <t>Solar e-paper real-time passenger information displays and cloud CMS for bus stops and stations</t>
-        </is>
-      </c>
-      <c r="F98" s="39" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Destination signs, LED/LCD passenger displays, onboard infotainment, and CCTV for bus and rail</t>
+        </is>
+      </c>
+      <c r="F98" s="41" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sales Backoffice Specialist only</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Connectpoint</t>
+          <t>Aesys</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Seriate, Italy</t>
         </is>
       </c>
       <c r="C99" s="6" t="n">
-        <v>2014</v>
+        <v>1977</v>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
@@ -50000,28 +50000,28 @@
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>ePaper Digital Bus Stop, SmartStop kiosks, and CPAM content management for transit agencies</t>
+          <t>LED and LCD passenger information displays for bus, rail, airports, and VMS traffic signs - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="37" t="inlineStr">
         <is>
-          <t>Peak Transit</t>
+          <t>Hanover Displays</t>
         </is>
       </c>
       <c r="B100" s="37" t="inlineStr">
         <is>
-          <t>San Luis Obispo, CA</t>
+          <t>Lewes, UK</t>
         </is>
       </c>
       <c r="C100" s="38" t="n">
-        <v>2012</v>
+        <v>1985</v>
       </c>
       <c r="D100" s="37" t="inlineStr">
         <is>
@@ -50030,29 +50030,27 @@
       </c>
       <c r="E100" s="37" t="inlineStr">
         <is>
-          <t>CAD/AVL, rider apps, APC, and digital signage for agencies, universities, and airports</t>
+          <t>Bus destination displays, controllers, and next-stop passenger information systems</t>
         </is>
       </c>
       <c r="F100" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 202 for https://www.hanoverdisplays</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Luminator Technology Group</t>
+          <t>SignAgent</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Plano, TX</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="n">
-        <v>1929</v>
-      </c>
+          <t>Burlington, ON, Canada</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="n"/>
       <c r="D101" s="5" t="inlineStr">
         <is>
           <t>Rider Experience</t>
@@ -50060,28 +50058,28 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Destination signs, LED/LCD passenger displays, onboard infotainment, and CCTV for bus and rail</t>
-        </is>
-      </c>
-      <c r="F101" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Sales Backoffice Specialist only</t>
+          <t>Cloud wayfinding and signage asset management for transit systems, airports, and campuses</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="37" t="inlineStr">
         <is>
-          <t>Aesys</t>
+          <t>Basemap</t>
         </is>
       </c>
       <c r="B102" s="37" t="inlineStr">
         <is>
-          <t>Seriate, Italy</t>
+          <t>Guildford, UK</t>
         </is>
       </c>
       <c r="C102" s="38" t="n">
-        <v>1977</v>
+        <v>2013</v>
       </c>
       <c r="D102" s="37" t="inlineStr">
         <is>
@@ -50090,7 +50088,7 @@
       </c>
       <c r="E102" s="37" t="inlineStr">
         <is>
-          <t>LED and LCD passenger information displays for bus, rail, airports, and VMS traffic signs</t>
+          <t>TRACC travel-time and accessibility analysis plus transport datasets for government transport agencies</t>
         </is>
       </c>
       <c r="F102" s="40" t="inlineStr">
@@ -50102,16 +50100,16 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Hanover Displays</t>
+          <t>Axon Vibe</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Lewes, UK</t>
+          <t>Lucerne, Switzerland</t>
         </is>
       </c>
       <c r="C103" s="6" t="n">
-        <v>1985</v>
+        <v>2014</v>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
@@ -50120,27 +50118,29 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Bus destination displays, controllers, and next-stop passenger information systems</t>
+          <t>Mobility behavior platform powering operator apps: journey detection, BIBO ticketing (built the MTA app)</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.hanoverdisplays</t>
+          <t>Unknown - HTTP 404 for https://axonvibe.com/career</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="37" t="inlineStr">
         <is>
-          <t>SignAgent</t>
+          <t>BusPas</t>
         </is>
       </c>
       <c r="B104" s="37" t="inlineStr">
         <is>
-          <t>Burlington, ON, Canada</t>
-        </is>
-      </c>
-      <c r="C104" s="38" t="n"/>
+          <t>Longueuil, QC, Canada</t>
+        </is>
+      </c>
+      <c r="C104" s="38" t="n">
+        <v>2017</v>
+      </c>
       <c r="D104" s="37" t="inlineStr">
         <is>
           <t>Rider Experience</t>
@@ -50148,24 +50148,24 @@
       </c>
       <c r="E104" s="37" t="inlineStr">
         <is>
-          <t>Cloud wayfinding and signage asset management for transit systems, airports, and campuses</t>
+          <t>Solar smart bus stops with edge AI plus the ORA platform: signage, lane enforcement, passenger counting</t>
         </is>
       </c>
       <c r="F104" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Basemap</t>
+          <t>WaySine</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Guildford, UK</t>
+          <t>Aiea, HI</t>
         </is>
       </c>
       <c r="C105" s="6" t="n">
@@ -50178,28 +50178,28 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>TRACC travel-time and accessibility analysis plus transport datasets for government transport agencies</t>
+          <t>Solar real-time arrival signs, e-paper displays, and voice announcement units for 40+ agencies - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="37" t="inlineStr">
         <is>
-          <t>Axon Vibe</t>
+          <t>Actionfigure</t>
         </is>
       </c>
       <c r="B106" s="37" t="inlineStr">
         <is>
-          <t>Lucerne, Switzerland</t>
+          <t>Washington, District of Columbia</t>
         </is>
       </c>
       <c r="C106" s="38" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D106" s="37" t="inlineStr">
         <is>
@@ -50208,67 +50208,67 @@
       </c>
       <c r="E106" s="37" t="inlineStr">
         <is>
-          <t>Mobility behavior platform powering operator apps: journey detection, BIBO ticketing (built the MTA app)</t>
+          <t>Real-time transit display screens and rider information for agencies and cities</t>
         </is>
       </c>
       <c r="F106" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://axonvibe.com/career</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>BusPas</t>
+          <t>Via</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Longueuil, QC, Canada</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="C107" s="6" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Rider Experience</t>
+          <t>Demand-Response &amp; AV</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>Solar smart bus stops with edge AI plus the ORA platform: signage, lane enforcement, passenger counting</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>On-demand transit, paratransit, and network planning software for agencies - exhibited at CTAA EXPO 2026</t>
+        </is>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive, Western Europe (Paris)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="37" t="inlineStr">
         <is>
-          <t>WaySine</t>
+          <t>Line Mobility</t>
         </is>
       </c>
       <c r="B108" s="37" t="inlineStr">
         <is>
-          <t>Aiea, HI</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C108" s="38" t="n">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="D108" s="37" t="inlineStr">
         <is>
-          <t>Rider Experience</t>
+          <t>Demand-Response &amp; AV</t>
         </is>
       </c>
       <c r="E108" s="37" t="inlineStr">
         <is>
-          <t>Solar real-time arrival signs, e-paper displays, and voice announcement units for 40+ agencies</t>
+          <t>Elevated automated transit pods on prefabricated guideways (ex-skyTran team) for cities and campuses</t>
         </is>
       </c>
       <c r="F108" s="40" t="inlineStr">
@@ -50280,76 +50280,76 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Actionfigure</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Washington, District of Columbia</t>
+          <t>Vancouver, BC, Canada</t>
         </is>
       </c>
       <c r="C109" s="6" t="n">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Rider Experience</t>
+          <t>Demand-Response &amp; AV</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>Real-time transit display screens and rider information for agencies and cities</t>
+          <t>AI microtransit and ADA paratransit operations: scheduling, dispatch, rider app, analytics - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="37" t="inlineStr">
         <is>
-          <t>Hopthru</t>
+          <t>RideCo</t>
         </is>
       </c>
       <c r="B110" s="37" t="inlineStr">
         <is>
-          <t>Seattle, Washington</t>
+          <t>Waterloo, ON, Canada</t>
         </is>
       </c>
       <c r="C110" s="38" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="D110" s="37" t="inlineStr">
         <is>
-          <t>Rider Experience</t>
+          <t>Demand-Response &amp; AV</t>
         </is>
       </c>
       <c r="E110" s="37" t="inlineStr">
         <is>
-          <t>Ridership and passenger counting analytics for public transit agencies</t>
-        </is>
-      </c>
-      <c r="F110" s="40" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>On-demand microtransit software with rider/driver apps and AI dispatch for large agencies - exhibited at CTAA EXPO 2026</t>
+        </is>
+      </c>
+      <c r="F110" s="39" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Via</t>
+          <t>The Routing Company</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="C111" s="6" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
@@ -50358,28 +50358,28 @@
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>On-demand transit, paratransit, and network planning software for agencies</t>
-        </is>
-      </c>
-      <c r="F111" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive, Western Europe (Paris)</t>
+          <t>Pingo microtransit and on-demand transit routing software for agencies and cities</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="37" t="inlineStr">
         <is>
-          <t>Line Mobility</t>
+          <t>UZURV</t>
         </is>
       </c>
       <c r="B112" s="37" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Richmond, VA</t>
         </is>
       </c>
       <c r="C112" s="38" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="D112" s="37" t="inlineStr">
         <is>
@@ -50388,28 +50388,28 @@
       </c>
       <c r="E112" s="37" t="inlineStr">
         <is>
-          <t>Elevated automated transit pods on prefabricated guideways (ex-skyTran team) for cities and campuses</t>
+          <t>Assisted-mobility platform and driver network delivering ADA paratransit and door-through-door trips - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
       <c r="F112" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Spare</t>
+          <t>QRyde by HBSS</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Lowell, MA</t>
         </is>
       </c>
       <c r="C113" s="6" t="n">
-        <v>2015</v>
+        <v>2003</v>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
@@ -50418,28 +50418,28 @@
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>AI microtransit and ADA paratransit operations: scheduling, dispatch, rider app, analytics</t>
+          <t>Brokered transportation scheduling and dispatch for statewide FTA agencies and rural/NEMT providers</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - HTTP 202 for https://qryde.com/employmen</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="37" t="inlineStr">
         <is>
-          <t>RideCo</t>
+          <t>IT Curves</t>
         </is>
       </c>
       <c r="B114" s="37" t="inlineStr">
         <is>
-          <t>Waterloo, ON, Canada</t>
+          <t>Rockville, MD</t>
         </is>
       </c>
       <c r="C114" s="38" t="n">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="D114" s="37" t="inlineStr">
         <is>
@@ -50448,28 +50448,28 @@
       </c>
       <c r="E114" s="37" t="inlineStr">
         <is>
-          <t>On-demand microtransit software with rider/driver apps and AI dispatch for large agencies</t>
-        </is>
-      </c>
-      <c r="F114" s="39" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Transit management software for paratransit, demand-response, microtransit, and taxi fleets - exhibited at CTAA EXPO 2026</t>
+        </is>
+      </c>
+      <c r="F114" s="40" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>The Routing Company</t>
+          <t>TSS Paratransit</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Glendale, CA</t>
         </is>
       </c>
       <c r="C115" s="6" t="n">
-        <v>2020</v>
+        <v>2002</v>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
@@ -50478,28 +50478,28 @@
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>Pingo microtransit and on-demand transit routing software for agencies and cities</t>
+          <t>5M platform: ADA paratransit registration, reservations, scheduling, routing, and auditing</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="37" t="inlineStr">
         <is>
-          <t>UZURV</t>
+          <t>May Mobility</t>
         </is>
       </c>
       <c r="B116" s="37" t="inlineStr">
         <is>
-          <t>Richmond, VA</t>
+          <t>Ann Arbor, MI</t>
         </is>
       </c>
       <c r="C116" s="38" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D116" s="37" t="inlineStr">
         <is>
@@ -50508,28 +50508,28 @@
       </c>
       <c r="E116" s="37" t="inlineStr">
         <is>
-          <t>Assisted-mobility platform and driver network delivering ADA paratransit and door-through-door trips</t>
+          <t>Autonomous vehicle technology and driverless shuttle service for transit agencies and cities</t>
         </is>
       </c>
       <c r="F116" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>QRyde by HBSS</t>
+          <t>Beep</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Lowell, MA</t>
+          <t>Orlando, FL</t>
         </is>
       </c>
       <c r="C117" s="6" t="n">
-        <v>2003</v>
+        <v>2019</v>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
@@ -50538,28 +50538,28 @@
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>Brokered transportation scheduling and dispatch for statewide FTA agencies and rural/NEMT providers</t>
-        </is>
-      </c>
-      <c r="F117" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - HTTP 202 for https://qryde.com/employmen</t>
+          <t>Turnkey autonomous shuttle operations for transit agencies, airports, and communities</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="37" t="inlineStr">
         <is>
-          <t>IT Curves</t>
+          <t>ADASTEC</t>
         </is>
       </c>
       <c r="B118" s="37" t="inlineStr">
         <is>
-          <t>Rockville, MD</t>
+          <t>East Lansing, MI</t>
         </is>
       </c>
       <c r="C118" s="38" t="n">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="D118" s="37" t="inlineStr">
         <is>
@@ -50568,7 +50568,7 @@
       </c>
       <c r="E118" s="37" t="inlineStr">
         <is>
-          <t>Transit management software for paratransit, demand-response, microtransit, and taxi fleets</t>
+          <t>flowride.ai SAE Level-4 automated driving software retrofitted onto full-size electric transit buses</t>
         </is>
       </c>
       <c r="F118" s="40" t="inlineStr">
@@ -50580,16 +50580,16 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>TSS Paratransit</t>
+          <t>Imagry</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Glendale, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="C119" s="6" t="n">
-        <v>2002</v>
+        <v>2015</v>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
@@ -50598,28 +50598,28 @@
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>5M platform: ADA paratransit registration, reservations, scheduling, routing, and auditing</t>
+          <t>HD-mapless vision-based autonomous driving software for buses and shuttles (Israel's first AV buses)</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="37" t="inlineStr">
         <is>
-          <t>May Mobility</t>
+          <t>SilverRide</t>
         </is>
       </c>
       <c r="B120" s="37" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="C120" s="38" t="n">
-        <v>2017</v>
+        <v>2006</v>
       </c>
       <c r="D120" s="37" t="inlineStr">
         <is>
@@ -50628,28 +50628,28 @@
       </c>
       <c r="E120" s="37" t="inlineStr">
         <is>
-          <t>Autonomous vehicle technology and driverless shuttle service for transit agencies and cities</t>
+          <t>Assisted senior and accessible transportation platform serving agency paratransit overflow in 35+ metros</t>
         </is>
       </c>
       <c r="F120" s="40" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Beep</t>
+          <t>Ontra Mobility</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Orlando, FL</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="C121" s="6" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
@@ -50658,28 +50658,28 @@
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>Turnkey autonomous shuttle operations for transit agencies, airports, and communities</t>
-        </is>
-      </c>
-      <c r="F121" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+          <t>AI transit network planning and optimization plus white-label rider app (YC S24; DDOT, Fresno)</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="37" t="inlineStr">
         <is>
-          <t>ADASTEC</t>
+          <t>RideShark</t>
         </is>
       </c>
       <c r="B122" s="37" t="inlineStr">
         <is>
-          <t>East Lansing, MI</t>
+          <t>Ottawa, ON, Canada</t>
         </is>
       </c>
       <c r="C122" s="38" t="n">
-        <v>2018</v>
+        <v>2008</v>
       </c>
       <c r="D122" s="37" t="inlineStr">
         <is>
@@ -50688,29 +50688,27 @@
       </c>
       <c r="E122" s="37" t="inlineStr">
         <is>
-          <t>flowride.ai SAE Level-4 automated driving software retrofitted onto full-size electric transit buses</t>
+          <t>White-label multimodal TDM and commute platform for regional agencies, employers, and campuses</t>
         </is>
       </c>
       <c r="F122" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 404 for https://www.rideshark.com/c</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Imagry</t>
+          <t>Ecolane</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="n">
-        <v>2015</v>
-      </c>
+          <t>Wayne, PA</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="n"/>
       <c r="D123" s="5" t="inlineStr">
         <is>
           <t>Demand-Response &amp; AV</t>
@@ -50718,29 +50716,23 @@
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>HD-mapless vision-based autonomous driving software for buses and shuttles (Israel's first AV buses)</t>
+          <t>Paratransit and microtransit scheduling software for public transit agencies</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="37" t="inlineStr">
         <is>
-          <t>SilverRide</t>
-        </is>
-      </c>
-      <c r="B124" s="37" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="C124" s="38" t="n">
-        <v>2006</v>
-      </c>
+          <t>CTS Software (TripMaster)</t>
+        </is>
+      </c>
+      <c r="B124" s="37" t="n"/>
+      <c r="C124" s="38" t="n"/>
       <c r="D124" s="37" t="inlineStr">
         <is>
           <t>Demand-Response &amp; AV</t>
@@ -50748,29 +50740,27 @@
       </c>
       <c r="E124" s="37" t="inlineStr">
         <is>
-          <t>Assisted senior and accessible transportation platform serving agency paratransit overflow in 35+ metros</t>
+          <t>TripMaster paratransit scheduling and dispatch software for public transit providers</t>
         </is>
       </c>
       <c r="F124" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Ontra Mobility</t>
+          <t>Pantonium</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="n">
-        <v>2023</v>
-      </c>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="n"/>
       <c r="D125" s="5" t="inlineStr">
         <is>
           <t>Demand-Response &amp; AV</t>
@@ -50778,28 +50768,28 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>AI transit network planning and optimization plus white-label rider app (YC S24; DDOT, Fresno)</t>
+          <t>On-demand transit software converting fixed routes to demand-response for agencies</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="37" t="inlineStr">
         <is>
-          <t>RideShark</t>
+          <t>Blaise Transit</t>
         </is>
       </c>
       <c r="B126" s="37" t="inlineStr">
         <is>
-          <t>Ottawa, ON, Canada</t>
+          <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
       <c r="C126" s="38" t="n">
-        <v>2008</v>
+        <v>2017</v>
       </c>
       <c r="D126" s="37" t="inlineStr">
         <is>
@@ -50808,28 +50798,28 @@
       </c>
       <c r="E126" s="37" t="inlineStr">
         <is>
-          <t>White-label multimodal TDM and commute platform for regional agencies, employers, and campuses</t>
+          <t>Demand-responsive transit dispatch and booking software for transit agencies - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
       <c r="F126" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://www.rideshark.com/c</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>Liberty Mobility Now</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Foster City, CA</t>
+          <t>Lincoln, NE</t>
         </is>
       </c>
       <c r="C127" s="6" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
@@ -50838,27 +50828,29 @@
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>Purpose-built driverless robotaxi service (Amazon-owned); consumer-paid rides, live in Las Vegas, SF, Austin, Miami, Atlanta, LA</t>
+          <t>Rural microtransit technology and service delivery for small transit agencies</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://boards-api.greenhou</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="37" t="inlineStr">
         <is>
-          <t>Ecolane</t>
+          <t>Circuit</t>
         </is>
       </c>
       <c r="B128" s="37" t="inlineStr">
         <is>
-          <t>Wayne, PA</t>
-        </is>
-      </c>
-      <c r="C128" s="38" t="n"/>
+          <t>Fort Lauderdale, FL</t>
+        </is>
+      </c>
+      <c r="C128" s="38" t="n">
+        <v>2011</v>
+      </c>
       <c r="D128" s="37" t="inlineStr">
         <is>
           <t>Demand-Response &amp; AV</t>
@@ -50866,23 +50858,29 @@
       </c>
       <c r="E128" s="37" t="inlineStr">
         <is>
-          <t>Paratransit and microtransit scheduling software for public transit agencies</t>
+          <t>Electric on-demand shuttle service contracted by cities and transit agencies - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F128" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>CTS Software (TripMaster)</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="n"/>
-      <c r="C129" s="6" t="n"/>
+          <t>Freebee</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>Miami, FL</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="n">
+        <v>2012</v>
+      </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
           <t>Demand-Response &amp; AV</t>
@@ -50890,27 +50888,29 @@
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>TripMaster paratransit scheduling and dispatch software for public transit providers</t>
+          <t>On-demand electric shuttle programs operated for municipalities and agencies</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="37" t="inlineStr">
         <is>
-          <t>Pantonium</t>
+          <t>door2door</t>
         </is>
       </c>
       <c r="B130" s="37" t="inlineStr">
         <is>
-          <t>Toronto, Ontario, Canada</t>
-        </is>
-      </c>
-      <c r="C130" s="38" t="n"/>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="C130" s="38" t="n">
+        <v>2012</v>
+      </c>
       <c r="D130" s="37" t="inlineStr">
         <is>
           <t>Demand-Response &amp; AV</t>
@@ -50918,24 +50918,24 @@
       </c>
       <c r="E130" s="37" t="inlineStr">
         <is>
-          <t>On-demand transit software converting fixed routes to demand-response for agencies</t>
-        </is>
-      </c>
-      <c r="F130" s="39" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>On-demand ridepooling and mobility analytics software for public transit authorities</t>
+        </is>
+      </c>
+      <c r="F130" s="40" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Blaise Transit</t>
+          <t>Shotl</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Montreal, Quebec, Canada</t>
+          <t>Barcelona, Spain</t>
         </is>
       </c>
       <c r="C131" s="6" t="n">
@@ -50948,28 +50948,28 @@
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>Demand-responsive transit dispatch and booking software for transit agencies</t>
+          <t>On-demand shared shuttle platform for municipalities and transit operators</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="37" t="inlineStr">
         <is>
-          <t>Liberty Mobility Now</t>
+          <t>MOIA</t>
         </is>
       </c>
       <c r="B132" s="37" t="inlineStr">
         <is>
-          <t>Lincoln, NE</t>
+          <t>Hamburg, Germany</t>
         </is>
       </c>
       <c r="C132" s="38" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D132" s="37" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
       </c>
       <c r="E132" s="37" t="inlineStr">
         <is>
-          <t>Rural microtransit technology and service delivery for small transit agencies</t>
+          <t>Ridepooling operations and autonomous shuttle services for public transport partners</t>
         </is>
       </c>
       <c r="F132" s="40" t="inlineStr">
@@ -50990,16 +50990,12 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>Circuit</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>Fort Lauderdale, FL</t>
-        </is>
-      </c>
+          <t>TripShot</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n"/>
       <c r="C133" s="6" t="n">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
@@ -51008,28 +51004,24 @@
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>Electric on-demand shuttle service contracted by cities and transit agencies</t>
+          <t>Transit operations, on-demand and shuttle management software for agencies and campuses</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="37" t="inlineStr">
         <is>
-          <t>Freebee</t>
-        </is>
-      </c>
-      <c r="B134" s="37" t="inlineStr">
-        <is>
-          <t>Miami, FL</t>
-        </is>
-      </c>
+          <t>MJM Innovations</t>
+        </is>
+      </c>
+      <c r="B134" s="37" t="n"/>
       <c r="C134" s="38" t="n">
-        <v>2012</v>
+        <v>1998</v>
       </c>
       <c r="D134" s="37" t="inlineStr">
         <is>
@@ -51038,28 +51030,28 @@
       </c>
       <c r="E134" s="37" t="inlineStr">
         <is>
-          <t>On-demand electric shuttle programs operated for municipalities and agencies</t>
+          <t>ADA paratransit eligibility, call center and mobility management technology for agencies</t>
         </is>
       </c>
       <c r="F134" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>door2door</t>
+          <t>Glydways</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>South San Francisco, CA</t>
         </is>
       </c>
       <c r="C135" s="6" t="n">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
@@ -51068,28 +51060,28 @@
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>On-demand ridepooling and mobility analytics software for public transit authorities</t>
+          <t>Autonomous small-vehicle transit systems built for public transit agencies</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="37" t="inlineStr">
         <is>
-          <t>Shotl</t>
+          <t>Swyft Cities</t>
         </is>
       </c>
       <c r="B136" s="37" t="inlineStr">
         <is>
-          <t>Barcelona, Spain</t>
+          <t>Mountain View, CA</t>
         </is>
       </c>
       <c r="C136" s="38" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="D136" s="37" t="inlineStr">
         <is>
@@ -51098,7 +51090,7 @@
       </c>
       <c r="E136" s="37" t="inlineStr">
         <is>
-          <t>On-demand shared shuttle platform for municipalities and transit operators</t>
+          <t>Whoosh autonomous cable-driven transit pods for cities and campuses</t>
         </is>
       </c>
       <c r="F136" s="40" t="inlineStr">
@@ -51110,16 +51102,16 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>MOIA</t>
+          <t>EasyMile</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Hamburg, Germany</t>
+          <t>Toulouse, France</t>
         </is>
       </c>
       <c r="C137" s="6" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
@@ -51128,23 +51120,29 @@
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>Ridepooling operations and autonomous shuttle services for public transport partners</t>
+          <t>Autonomous shuttles and driverless technology deployed with transit agencies</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="37" t="inlineStr">
         <is>
-          <t>TripShot</t>
-        </is>
-      </c>
-      <c r="B138" s="37" t="n"/>
-      <c r="C138" s="38" t="n"/>
+          <t>Navya</t>
+        </is>
+      </c>
+      <c r="B138" s="37" t="inlineStr">
+        <is>
+          <t>Villeurbanne, France</t>
+        </is>
+      </c>
+      <c r="C138" s="38" t="n">
+        <v>2014</v>
+      </c>
       <c r="D138" s="37" t="inlineStr">
         <is>
           <t>Demand-Response &amp; AV</t>
@@ -51152,7 +51150,7 @@
       </c>
       <c r="E138" s="37" t="inlineStr">
         <is>
-          <t>Transit operations, on-demand and shuttle management software for agencies and campuses</t>
+          <t>Autonomous shuttle vehicles for public transport and campus deployments</t>
         </is>
       </c>
       <c r="F138" s="40" t="inlineStr">
@@ -51164,12 +51162,16 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>MJM Innovations</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="n"/>
+          <t>HOLON</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
       <c r="C139" s="6" t="n">
-        <v>1998</v>
+        <v>2022</v>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
@@ -51178,7 +51180,7 @@
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>ADA paratransit eligibility, call center and mobility management technology for agencies</t>
+          <t>Purpose-built autonomous mover shuttles for transit agencies and airports</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
@@ -51190,16 +51192,16 @@
     <row r="140">
       <c r="A140" s="37" t="inlineStr">
         <is>
-          <t>Glydways</t>
+          <t>Karsan</t>
         </is>
       </c>
       <c r="B140" s="37" t="inlineStr">
         <is>
-          <t>South San Francisco, CA</t>
+          <t>Bursa, Turkey</t>
         </is>
       </c>
       <c r="C140" s="38" t="n">
-        <v>2016</v>
+        <v>1966</v>
       </c>
       <c r="D140" s="37" t="inlineStr">
         <is>
@@ -51208,28 +51210,28 @@
       </c>
       <c r="E140" s="37" t="inlineStr">
         <is>
-          <t>Autonomous small-vehicle transit systems built for public transit agencies</t>
+          <t>Electric and autonomous buses sold to public transit operators worldwide</t>
         </is>
       </c>
       <c r="F140" s="40" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Swyft Cities</t>
+          <t>Aurrigo</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Mountain View, CA</t>
+          <t>Coventry, United Kingdom</t>
         </is>
       </c>
       <c r="C141" s="6" t="n">
-        <v>2021</v>
+        <v>1993</v>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
@@ -51238,28 +51240,28 @@
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>Whoosh autonomous cable-driven transit pods for cities and campuses</t>
+          <t>Autonomous shuttles and airport ground-handling vehicles for public operators</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="37" t="inlineStr">
         <is>
-          <t>EasyMile</t>
+          <t>2getthere</t>
         </is>
       </c>
       <c r="B142" s="37" t="inlineStr">
         <is>
-          <t>Toulouse, France</t>
+          <t>Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="C142" s="38" t="n">
-        <v>2014</v>
+        <v>1984</v>
       </c>
       <c r="D142" s="37" t="inlineStr">
         <is>
@@ -51268,28 +51270,28 @@
       </c>
       <c r="E142" s="37" t="inlineStr">
         <is>
-          <t>Autonomous shuttles and driverless technology deployed with transit agencies</t>
+          <t>Automated people mover and group rapid transit systems for public authorities</t>
         </is>
       </c>
       <c r="F142" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Navya</t>
+          <t>Perrone Robotics</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Villeurbanne, France</t>
+          <t>Charlottesville, VA</t>
         </is>
       </c>
       <c r="C143" s="6" t="n">
-        <v>2014</v>
+        <v>2003</v>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
@@ -51298,28 +51300,28 @@
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>Autonomous shuttle vehicles for public transport and campus deployments</t>
+          <t>Autonomous vehicle software and retrofitted shuttles for transit agency pilots</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="37" t="inlineStr">
         <is>
-          <t>HOLON</t>
+          <t>Oxa</t>
         </is>
       </c>
       <c r="B144" s="37" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Oxford, United Kingdom</t>
         </is>
       </c>
       <c r="C144" s="38" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="D144" s="37" t="inlineStr">
         <is>
@@ -51328,28 +51330,28 @@
       </c>
       <c r="E144" s="37" t="inlineStr">
         <is>
-          <t>Purpose-built autonomous mover shuttles for transit agencies and airports</t>
+          <t>Autonomy software powering driverless shuttles for transit and airport operators</t>
         </is>
       </c>
       <c r="F144" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Karsan</t>
+          <t>Auve Tech</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Bursa, Turkey</t>
+          <t>Tallinn, Estonia</t>
         </is>
       </c>
       <c r="C145" s="6" t="n">
-        <v>1966</v>
+        <v>2019</v>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
@@ -51358,28 +51360,28 @@
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>Electric and autonomous buses sold to public transit operators worldwide</t>
+          <t>Autonomous last-mile shuttles sold to cities and public transport operators</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="37" t="inlineStr">
         <is>
-          <t>Aurrigo</t>
+          <t>Ohmio Automotion</t>
         </is>
       </c>
       <c r="B146" s="37" t="inlineStr">
         <is>
-          <t>Coventry, United Kingdom</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="C146" s="38" t="n">
-        <v>1993</v>
+        <v>2017</v>
       </c>
       <c r="D146" s="37" t="inlineStr">
         <is>
@@ -51388,67 +51390,67 @@
       </c>
       <c r="E146" s="37" t="inlineStr">
         <is>
-          <t>Autonomous shuttles and airport ground-handling vehicles for public operators</t>
+          <t>Autonomous shuttles for public transport agencies, airports and campuses</t>
         </is>
       </c>
       <c r="F146" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>2getthere</t>
+          <t>Passport</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Utrecht, Netherlands</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="C147" s="6" t="n">
-        <v>1984</v>
+        <v>2010</v>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>Demand-Response &amp; AV</t>
+          <t>Parking &amp; Curb</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>Automated people mover and group rapid transit systems for public authorities</t>
+          <t>Mobile parking payments, digital permits, and curb platform for cities</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="37" t="inlineStr">
         <is>
-          <t>Perrone Robotics</t>
+          <t>ParkMobile</t>
         </is>
       </c>
       <c r="B148" s="37" t="inlineStr">
         <is>
-          <t>Charlottesville, VA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="C148" s="38" t="n">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="D148" s="37" t="inlineStr">
         <is>
-          <t>Demand-Response &amp; AV</t>
+          <t>Parking &amp; Curb</t>
         </is>
       </c>
       <c r="E148" s="37" t="inlineStr">
         <is>
-          <t>Autonomous vehicle software and retrofitted shuttles for transit agency pilots</t>
+          <t>Leading mobile parking payments app (EasyPark Group)</t>
         </is>
       </c>
       <c r="F148" s="40" t="inlineStr">
@@ -51460,70 +51462,72 @@
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Forterra</t>
+          <t>IPS Group</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>Clarksburg, MD</t>
-        </is>
-      </c>
-      <c r="C149" s="6" t="n"/>
+          <t>San Diego, CA</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="n">
+        <v>1994</v>
+      </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>Demand-Response &amp; AV</t>
+          <t>Parking &amp; Curb</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>Autonomous driving systems for government fleets including transit and defense vehicles</t>
-        </is>
-      </c>
-      <c r="F149" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Smart single-space parking meters and enforcement systems</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sr. Client Success Manager only</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="37" t="inlineStr">
         <is>
-          <t>Oxa</t>
+          <t>Automotus</t>
         </is>
       </c>
       <c r="B150" s="37" t="inlineStr">
         <is>
-          <t>Oxford, United Kingdom</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="C150" s="38" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="D150" s="37" t="inlineStr">
         <is>
-          <t>Demand-Response &amp; AV</t>
+          <t>Parking &amp; Curb</t>
         </is>
       </c>
       <c r="E150" s="37" t="inlineStr">
         <is>
-          <t>Autonomy software powering driverless shuttles for transit and airport operators</t>
+          <t>Computer vision curb management and automated loading-zone payments</t>
         </is>
       </c>
       <c r="F150" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>WeRide</t>
+          <t>Populus</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>Guangzhou, China</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="C151" s="6" t="n">
@@ -51531,121 +51535,123 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>Demand-Response &amp; AV</t>
+          <t>Parking &amp; Curb</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>Autonomous robobuses and robotaxis deployed with transit authorities and cities</t>
+          <t>Curb and mobility data platform for pricing and street policy</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="37" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>Premium Parking</t>
         </is>
       </c>
       <c r="B152" s="37" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>New Orleans, LA</t>
         </is>
       </c>
       <c r="C152" s="38" t="n">
-        <v>2020</v>
+        <v>2005</v>
       </c>
       <c r="D152" s="37" t="inlineStr">
         <is>
-          <t>Demand-Response &amp; AV</t>
+          <t>Parking &amp; Curb</t>
         </is>
       </c>
       <c r="E152" s="37" t="inlineStr">
         <is>
-          <t>Driverless vehicle technology for shared autonomous mobility services</t>
+          <t>Gateless LPR parking operations (GLIDEPARCS) for private lots, universities, and some municipalities</t>
         </is>
       </c>
       <c r="F152" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - page too small - likely JS-rendered</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>Auve Tech</t>
+          <t>VenTek International</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Tallinn, Estonia</t>
+          <t>Petaluma, CA</t>
         </is>
       </c>
       <c r="C153" s="6" t="n">
-        <v>2019</v>
+        <v>1993</v>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>Demand-Response &amp; AV</t>
+          <t>Parking &amp; Curb</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>Autonomous last-mile shuttles sold to cities and public transport operators</t>
+          <t>Self-service pay stations and venVUE revenue software for park entrance fees and parking (roots to 1950s)</t>
         </is>
       </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="37" t="inlineStr">
         <is>
-          <t>Ohmio Automotion</t>
+          <t>Autura</t>
         </is>
       </c>
       <c r="B154" s="37" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
-        </is>
-      </c>
-      <c r="C154" s="38" t="n"/>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="C154" s="38" t="n">
+        <v>2002</v>
+      </c>
       <c r="D154" s="37" t="inlineStr">
         <is>
-          <t>Demand-Response &amp; AV</t>
+          <t>Parking &amp; Curb</t>
         </is>
       </c>
       <c r="E154" s="37" t="inlineStr">
         <is>
-          <t>Autonomous shuttles for public transport agencies, airports and campuses</t>
+          <t>Towing lifecycle software for city towing programs and impound management (ex-AutoReturn + TSD)</t>
         </is>
       </c>
       <c r="F154" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Passport</t>
+          <t>T2 Systems</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="C155" s="6" t="n">
-        <v>2010</v>
+        <v>1994</v>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
@@ -51654,28 +51660,28 @@
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>Mobile parking payments, digital permits, and curb platform for cities</t>
-        </is>
-      </c>
-      <c r="F155" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Parking permits, enforcement, PARCS, and pay stations for universities and cities (Verra Mobility)</t>
+        </is>
+      </c>
+      <c r="F155" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="37" t="inlineStr">
         <is>
-          <t>ParkMobile</t>
+          <t>Municipal Parking Services</t>
         </is>
       </c>
       <c r="B156" s="37" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Golden Valley, MN</t>
         </is>
       </c>
       <c r="C156" s="38" t="n">
-        <v>2008</v>
+        <v>2013</v>
       </c>
       <c r="D156" s="37" t="inlineStr">
         <is>
@@ -51684,28 +51690,28 @@
       </c>
       <c r="E156" s="37" t="inlineStr">
         <is>
-          <t>Leading mobile parking payments app (EasyPark Group)</t>
+          <t>Sentry solar smart kiosks and vision-based automated parking enforcement</t>
         </is>
       </c>
       <c r="F156" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>IPS Group</t>
+          <t>Arrive</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Stockholm, Sweden</t>
         </is>
       </c>
       <c r="C157" s="6" t="n">
-        <v>1994</v>
+        <v>2001</v>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
@@ -51714,28 +51720,28 @@
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>Smart single-space parking meters and enforcement systems</t>
-        </is>
-      </c>
-      <c r="F157" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Sr. Client Success Manager only</t>
+          <t>Mobility and curb/parking technology platform - exhibited at APTA 2026</t>
+        </is>
+      </c>
+      <c r="F157" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Junior B2B Account Executive (Prague)</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="37" t="inlineStr">
         <is>
-          <t>Automotus</t>
+          <t>POM (Parking Operations Management)</t>
         </is>
       </c>
       <c r="B158" s="37" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Russellville, Arkansas</t>
         </is>
       </c>
       <c r="C158" s="38" t="n">
-        <v>2017</v>
+        <v>1976</v>
       </c>
       <c r="D158" s="37" t="inlineStr">
         <is>
@@ -51744,28 +51750,28 @@
       </c>
       <c r="E158" s="37" t="inlineStr">
         <is>
-          <t>Computer vision curb management and automated loading-zone payments</t>
+          <t>Single-space smart parking meters and pay stations for municipalities</t>
         </is>
       </c>
       <c r="F158" s="40" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Populus</t>
+          <t>Tannery Creek Systems</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Aurora, Ontario, Canada</t>
         </is>
       </c>
       <c r="C159" s="6" t="n">
-        <v>2017</v>
+        <v>1996</v>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
@@ -51774,7 +51780,7 @@
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>Curb and mobility data platform for pricing and street policy</t>
+          <t>Sentry parking enforcement and permit software for municipalities</t>
         </is>
       </c>
       <c r="F159" s="7" t="inlineStr">
@@ -51786,16 +51792,16 @@
     <row r="160">
       <c r="A160" s="37" t="inlineStr">
         <is>
-          <t>Premium Parking</t>
+          <t>Nwave Technologies</t>
         </is>
       </c>
       <c r="B160" s="37" t="inlineStr">
         <is>
-          <t>New Orleans, LA</t>
+          <t>London, United Kingdom</t>
         </is>
       </c>
       <c r="C160" s="38" t="n">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="D160" s="37" t="inlineStr">
         <is>
@@ -51804,28 +51810,28 @@
       </c>
       <c r="E160" s="37" t="inlineStr">
         <is>
-          <t>Gateless LPR parking operations (GLIDEPARCS) for private lots, universities, and some municipalities</t>
+          <t>Wireless parking occupancy sensors for city and campus parking</t>
         </is>
       </c>
       <c r="F160" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page too small - likely JS-rendered</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>VenTek International</t>
+          <t>Fybr</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Petaluma, CA</t>
+          <t>St. Louis, Missouri</t>
         </is>
       </c>
       <c r="C161" s="6" t="n">
-        <v>1993</v>
+        <v>2011</v>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
@@ -51834,7 +51840,7 @@
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>Self-service pay stations and venVUE revenue software for park entrance fees and parking (roots to 1950s)</t>
+          <t>IoT parking sensors and smart city occupancy data for municipalities</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
@@ -51846,16 +51852,16 @@
     <row r="162">
       <c r="A162" s="37" t="inlineStr">
         <is>
-          <t>Autura</t>
+          <t>eleven-x</t>
         </is>
       </c>
       <c r="B162" s="37" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Waterloo, Ontario, Canada</t>
         </is>
       </c>
       <c r="C162" s="38" t="n">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="D162" s="37" t="inlineStr">
         <is>
@@ -51864,28 +51870,28 @@
       </c>
       <c r="E162" s="37" t="inlineStr">
         <is>
-          <t>Towing lifecycle software for city towing programs and impound management (ex-AutoReturn + TSD)</t>
+          <t>Smart parking sensors and LoRaWAN networks for cities</t>
         </is>
       </c>
       <c r="F162" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>T2 Systems</t>
+          <t>Park Assist</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>New York, New York</t>
         </is>
       </c>
       <c r="C163" s="6" t="n">
-        <v>1994</v>
+        <v>1999</v>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
@@ -51894,28 +51900,28 @@
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>Parking permits, enforcement, PARCS, and pay stations for universities and cities (Verra Mobility)</t>
-        </is>
-      </c>
-      <c r="F163" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Camera-based parking guidance and space monitoring for public garages</t>
+        </is>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="37" t="inlineStr">
         <is>
-          <t>Municipal Parking Services</t>
+          <t>Whoosh</t>
         </is>
       </c>
       <c r="B164" s="37" t="inlineStr">
         <is>
-          <t>Golden Valley, MN</t>
+          <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
       <c r="C164" s="38" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="D164" s="37" t="inlineStr">
         <is>
@@ -51924,7 +51930,7 @@
       </c>
       <c r="E164" s="37" t="inlineStr">
         <is>
-          <t>Sentry solar smart kiosks and vision-based automated parking enforcement</t>
+          <t>Parking payments, permits and enforcement software for municipalities</t>
         </is>
       </c>
       <c r="F164" s="40" t="inlineStr">
@@ -51936,16 +51942,16 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>Arrive</t>
+          <t>Data Ticket</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Stockholm, Sweden</t>
+          <t>Poway, California</t>
         </is>
       </c>
       <c r="C165" s="6" t="n">
-        <v>2001</v>
+        <v>1987</v>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
@@ -51954,28 +51960,28 @@
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>Mobility and curb/parking technology platform - exhibited at APTA 2026</t>
-        </is>
-      </c>
-      <c r="F165" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Junior B2B Account Executive (Prague)</t>
+          <t>Citation processing, adjudication and collections for California municipalities</t>
+        </is>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="37" t="inlineStr">
         <is>
-          <t>POM (Parking Operations Management)</t>
+          <t>Turbo Data Systems</t>
         </is>
       </c>
       <c r="B166" s="37" t="inlineStr">
         <is>
-          <t>Russellville, Arkansas</t>
+          <t>Tustin, California</t>
         </is>
       </c>
       <c r="C166" s="38" t="n">
-        <v>1976</v>
+        <v>1985</v>
       </c>
       <c r="D166" s="37" t="inlineStr">
         <is>
@@ -51984,28 +51990,28 @@
       </c>
       <c r="E166" s="37" t="inlineStr">
         <is>
-          <t>Single-space smart parking meters and pay stations for municipalities</t>
+          <t>Parking citation processing and permit services for California cities</t>
         </is>
       </c>
       <c r="F166" s="40" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>Tannery Creek Systems</t>
+          <t>Complus Data Innovations</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>Aurora, Ontario, Canada</t>
+          <t>Tarrytown, New York</t>
         </is>
       </c>
       <c r="C167" s="6" t="n">
-        <v>1996</v>
+        <v>1990</v>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
@@ -52014,7 +52020,7 @@
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>Sentry parking enforcement and permit software for municipalities</t>
+          <t>Parking ticket issuance and citation processing for municipalities</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
@@ -52026,16 +52032,16 @@
     <row r="168">
       <c r="A168" s="37" t="inlineStr">
         <is>
-          <t>Nwave Technologies</t>
+          <t>AIMS Parking (EDC Corporation)</t>
         </is>
       </c>
       <c r="B168" s="37" t="inlineStr">
         <is>
-          <t>London, United Kingdom</t>
+          <t>Rancho Cordova, California</t>
         </is>
       </c>
       <c r="C168" s="38" t="n">
-        <v>2015</v>
+        <v>1979</v>
       </c>
       <c r="D168" s="37" t="inlineStr">
         <is>
@@ -52044,7 +52050,7 @@
       </c>
       <c r="E168" s="37" t="inlineStr">
         <is>
-          <t>Wireless parking occupancy sensors for city and campus parking</t>
+          <t>Parking citation, permit and enforcement management software for agencies</t>
         </is>
       </c>
       <c r="F168" s="40" t="inlineStr">
@@ -52056,25 +52062,21 @@
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>Fybr</t>
-        </is>
-      </c>
-      <c r="B169" s="5" t="inlineStr">
-        <is>
-          <t>St. Louis, Missouri</t>
-        </is>
-      </c>
+          <t>Acapela Group</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="n"/>
       <c r="C169" s="6" t="n">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>Parking &amp; Curb</t>
+          <t>Suppliers &amp; Services</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>IoT parking sensors and smart city occupancy data for municipalities</t>
+          <t>Text-to-speech voice software - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
@@ -52086,115 +52088,101 @@
     <row r="170">
       <c r="A170" s="37" t="inlineStr">
         <is>
-          <t>eleven-x</t>
+          <t>Activu Corporation</t>
         </is>
       </c>
       <c r="B170" s="37" t="inlineStr">
         <is>
-          <t>Waterloo, Ontario, Canada</t>
+          <t>Rockaway, NJ</t>
         </is>
       </c>
       <c r="C170" s="38" t="n">
-        <v>2013</v>
+        <v>1983</v>
       </c>
       <c r="D170" s="37" t="inlineStr">
         <is>
-          <t>Parking &amp; Curb</t>
+          <t>Suppliers &amp; Services</t>
         </is>
       </c>
       <c r="E170" s="37" t="inlineStr">
         <is>
-          <t>Smart parking sensors and LoRaWAN networks for cities</t>
+          <t>Control room video wall visualization software - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F170" s="40" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Park Assist</t>
-        </is>
-      </c>
-      <c r="B171" s="5" t="inlineStr">
-        <is>
-          <t>New York, New York</t>
-        </is>
-      </c>
+          <t>Almaviva</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="n"/>
       <c r="C171" s="6" t="n">
-        <v>1999</v>
+        <v>2005</v>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>Parking &amp; Curb</t>
+          <t>Suppliers &amp; Services</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>Camera-based parking guidance and space monitoring for public garages</t>
+          <t>Transit IT, ticketing and mobility systems - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="37" t="inlineStr">
         <is>
-          <t>CurbIQ</t>
-        </is>
-      </c>
-      <c r="B172" s="37" t="inlineStr">
-        <is>
-          <t>Toronto, Ontario, Canada</t>
-        </is>
-      </c>
+          <t>Aurionpro</t>
+        </is>
+      </c>
+      <c r="B172" s="37" t="n"/>
       <c r="C172" s="38" t="n">
-        <v>2020</v>
+        <v>1997</v>
       </c>
       <c r="D172" s="37" t="inlineStr">
         <is>
-          <t>Parking &amp; Curb</t>
+          <t>Suppliers &amp; Services</t>
         </is>
       </c>
       <c r="E172" s="37" t="inlineStr">
         <is>
-          <t>Curb inventory, regulation digitization and curb management for cities</t>
+          <t>Transit fare collection and ticketing software - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F172" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>Whoosh</t>
-        </is>
-      </c>
-      <c r="B173" s="5" t="inlineStr">
-        <is>
-          <t>Ottawa, Ontario, Canada</t>
-        </is>
-      </c>
-      <c r="C173" s="6" t="n">
-        <v>2021</v>
-      </c>
+          <t>BatOnRoute - School and Staff Transport App</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="n"/>
+      <c r="C173" s="6" t="n"/>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>Parking &amp; Curb</t>
+          <t>Suppliers &amp; Services</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>Parking payments, permits and enforcement software for municipalities</t>
+          <t>School and staff transport tracking app - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F173" s="7" t="inlineStr">
@@ -52206,25 +52194,19 @@
     <row r="174">
       <c r="A174" s="37" t="inlineStr">
         <is>
-          <t>Data Ticket</t>
-        </is>
-      </c>
-      <c r="B174" s="37" t="inlineStr">
-        <is>
-          <t>Poway, California</t>
-        </is>
-      </c>
-      <c r="C174" s="38" t="n">
-        <v>1987</v>
-      </c>
+          <t>Bentley Systems</t>
+        </is>
+      </c>
+      <c r="B174" s="37" t="n"/>
+      <c r="C174" s="38" t="n"/>
       <c r="D174" s="37" t="inlineStr">
         <is>
-          <t>Parking &amp; Curb</t>
+          <t>Suppliers &amp; Services</t>
         </is>
       </c>
       <c r="E174" s="37" t="inlineStr">
         <is>
-          <t>Citation processing, adjudication and collections for California municipalities</t>
+          <t>Infrastructure engineering and asset software - exhibited at APTA 2026, AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F174" s="40" t="inlineStr">
@@ -52236,25 +52218,21 @@
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>Turbo Data Systems</t>
-        </is>
-      </c>
-      <c r="B175" s="5" t="inlineStr">
-        <is>
-          <t>Tustin, California</t>
-        </is>
-      </c>
+          <t>ETA</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="n"/>
       <c r="C175" s="6" t="n">
-        <v>1985</v>
+        <v>2003</v>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>Parking &amp; Curb</t>
+          <t>Suppliers &amp; Services</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>Parking citation processing and permit services for California cities</t>
+          <t>Transit CAD/AVL and asset management software - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F175" s="7" t="inlineStr">
@@ -52266,72 +52244,62 @@
     <row r="176">
       <c r="A176" s="37" t="inlineStr">
         <is>
-          <t>Complus Data Innovations</t>
-        </is>
-      </c>
-      <c r="B176" s="37" t="inlineStr">
-        <is>
-          <t>Tarrytown, New York</t>
-        </is>
-      </c>
+          <t>FLEETWATCH by S &amp; A Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="B176" s="37" t="n"/>
       <c r="C176" s="38" t="n">
-        <v>1990</v>
+        <v>1970</v>
       </c>
       <c r="D176" s="37" t="inlineStr">
         <is>
-          <t>Parking &amp; Curb</t>
+          <t>Suppliers &amp; Services</t>
         </is>
       </c>
       <c r="E176" s="37" t="inlineStr">
         <is>
-          <t>Parking ticket issuance and citation processing for municipalities</t>
+          <t>Fuel and fleet management systems - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F176" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>AIMS Parking (EDC Corporation)</t>
-        </is>
-      </c>
-      <c r="B177" s="5" t="inlineStr">
-        <is>
-          <t>Rancho Cordova, California</t>
-        </is>
-      </c>
-      <c r="C177" s="6" t="n">
-        <v>1979</v>
-      </c>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="n"/>
+      <c r="C177" s="6" t="n"/>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>Parking &amp; Curb</t>
+          <t>Suppliers &amp; Services</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>Parking citation, permit and enforcement management software for agencies</t>
+          <t>Enterprise software and IT for agencies - exhibited at APTA 2026, GFOA 2026, NASWA 2025, APHSA 2026, AIRA 2026, MESC 2026, NAMPI 2026</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="37" t="inlineStr">
         <is>
-          <t>Acapela Group</t>
+          <t>INIT Innovations in Transportation, Inc.</t>
         </is>
       </c>
       <c r="B178" s="37" t="n"/>
       <c r="C178" s="38" t="n">
-        <v>2003</v>
+        <v>1983</v>
       </c>
       <c r="D178" s="37" t="inlineStr">
         <is>
@@ -52340,7 +52308,7 @@
       </c>
       <c r="E178" s="37" t="inlineStr">
         <is>
-          <t>Text-to-speech voice software - exhibited at APTA 2026</t>
+          <t>Transit ITS, fare collection, scheduling software - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F178" s="40" t="inlineStr">
@@ -52352,16 +52320,12 @@
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>Activu Corporation</t>
-        </is>
-      </c>
-      <c r="B179" s="5" t="inlineStr">
-        <is>
-          <t>Rockaway, NJ</t>
-        </is>
-      </c>
+          <t>INTANGLES USA INC</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="n"/>
       <c r="C179" s="6" t="n">
-        <v>1983</v>
+        <v>2014</v>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
@@ -52370,7 +52334,7 @@
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>Control room video wall visualization software - exhibited at APTA 2026</t>
+          <t>AI predictive fleet analytics platform - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
@@ -52382,12 +52346,16 @@
     <row r="180">
       <c r="A180" s="37" t="inlineStr">
         <is>
-          <t>Almaviva</t>
-        </is>
-      </c>
-      <c r="B180" s="37" t="n"/>
+          <t>Indra Group</t>
+        </is>
+      </c>
+      <c r="B180" s="37" t="inlineStr">
+        <is>
+          <t>Madrid, Spain</t>
+        </is>
+      </c>
       <c r="C180" s="38" t="n">
-        <v>2005</v>
+        <v>1993</v>
       </c>
       <c r="D180" s="37" t="inlineStr">
         <is>
@@ -52396,7 +52364,7 @@
       </c>
       <c r="E180" s="37" t="inlineStr">
         <is>
-          <t>Transit IT, ticketing and mobility systems - exhibited at APTA 2026</t>
+          <t>Ticketing, traffic and transit management systems - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F180" s="40" t="inlineStr">
@@ -52408,13 +52376,11 @@
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>Aurionpro</t>
+          <t>Intellicene</t>
         </is>
       </c>
       <c r="B181" s="5" t="n"/>
-      <c r="C181" s="6" t="n">
-        <v>1997</v>
-      </c>
+      <c r="C181" s="6" t="n"/>
       <c r="D181" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -52422,19 +52388,19 @@
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>Transit fare collection and ticketing software - exhibited at APTA 2026</t>
+          <t>Security and intelligence analytics software - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="37" t="inlineStr">
         <is>
-          <t>BatOnRoute - School and Staff Transport App</t>
+          <t>Lux Modus</t>
         </is>
       </c>
       <c r="B182" s="37" t="n"/>
@@ -52446,7 +52412,7 @@
       </c>
       <c r="E182" s="37" t="inlineStr">
         <is>
-          <t>School and staff transport tracking app - exhibited at APTA 2026</t>
+          <t>LiDAR 3D digital twin capture for transit - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F182" s="40" t="inlineStr">
@@ -52458,7 +52424,7 @@
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>MOEV Inc.</t>
         </is>
       </c>
       <c r="B183" s="5" t="n"/>
@@ -52470,7 +52436,7 @@
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure engineering and asset software - exhibited at APTA 2026, AWWA ACE 2026</t>
+          <t>Smart EV charging management software - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
@@ -52482,7 +52448,7 @@
     <row r="184">
       <c r="A184" s="37" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>Onward Health</t>
         </is>
       </c>
       <c r="B184" s="37" t="n"/>
@@ -52494,7 +52460,7 @@
       </c>
       <c r="E184" s="37" t="inlineStr">
         <is>
-          <t>Transit CAD/AVL and asset management software - exhibited at APTA 2026</t>
+          <t>Medical transportation ride management software - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F184" s="40" t="inlineStr">
@@ -52506,13 +52472,11 @@
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>FLEETWATCH by S &amp; A Systems, Inc.</t>
+          <t>Pulse Transit Software</t>
         </is>
       </c>
       <c r="B185" s="5" t="n"/>
-      <c r="C185" s="6" t="n">
-        <v>1970</v>
-      </c>
+      <c r="C185" s="6" t="n"/>
       <c r="D185" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -52520,23 +52484,25 @@
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>Fuel and fleet management systems - exhibited at APTA 2026</t>
+          <t>Transit operations software - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="37" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>PureTech Systems, Inc.</t>
         </is>
       </c>
       <c r="B186" s="37" t="n"/>
-      <c r="C186" s="38" t="n"/>
+      <c r="C186" s="38" t="n">
+        <v>2004</v>
+      </c>
       <c r="D186" s="37" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -52544,7 +52510,7 @@
       </c>
       <c r="E186" s="37" t="inlineStr">
         <is>
-          <t>Enterprise software and IT for agencies - exhibited at APTA 2026, GFOA 2026, NASWA 2025, APHSA 2026, AIRA 2026, MESC 2026, NAMPI 2026</t>
+          <t>AI video analytics perimeter security software - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F186" s="40" t="inlineStr">
@@ -52556,7 +52522,7 @@
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>INIT Innovations in Transportation, Inc.</t>
+          <t>Redstone Technologies LLC</t>
         </is>
       </c>
       <c r="B187" s="5" t="n"/>
@@ -52568,7 +52534,7 @@
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>Transit ITS, fare collection, scheduling software - exhibited at APTA 2026</t>
+          <t>Rail/transit software, AI and asset monitoring - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
@@ -52580,13 +52546,11 @@
     <row r="188">
       <c r="A188" s="37" t="inlineStr">
         <is>
-          <t>INTANGLES USA INC</t>
+          <t>Strategic Mapping</t>
         </is>
       </c>
       <c r="B188" s="37" t="n"/>
-      <c r="C188" s="38" t="n">
-        <v>2014</v>
-      </c>
+      <c r="C188" s="38" t="n"/>
       <c r="D188" s="37" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -52594,29 +52558,23 @@
       </c>
       <c r="E188" s="37" t="inlineStr">
         <is>
-          <t>AI predictive fleet analytics platform - exhibited at APTA 2026</t>
+          <t>Transit CAD/AVL, APC, passenger information systems - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F188" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>Indra Group</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="inlineStr">
-        <is>
-          <t>Madrid, Spain</t>
-        </is>
-      </c>
-      <c r="C189" s="6" t="n">
-        <v>1993</v>
-      </c>
+          <t>TSO Mobile</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="n"/>
+      <c r="C189" s="6" t="n"/>
       <c r="D189" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -52624,23 +52582,29 @@
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>Ticketing, traffic and transit management systems - exhibited at APTA 2026</t>
-        </is>
-      </c>
-      <c r="F189" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>GPS fleet tracking and telematics software - exhibited at APTA 2026</t>
+        </is>
+      </c>
+      <c r="F189" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Sales Account Executive – Mid-Mark</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="37" t="inlineStr">
         <is>
-          <t>Intellicene</t>
-        </is>
-      </c>
-      <c r="B190" s="37" t="n"/>
-      <c r="C190" s="38" t="n"/>
+          <t>The Mobility House</t>
+        </is>
+      </c>
+      <c r="B190" s="37" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="C190" s="38" t="n">
+        <v>2009</v>
+      </c>
       <c r="D190" s="37" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -52648,19 +52612,19 @@
       </c>
       <c r="E190" s="37" t="inlineStr">
         <is>
-          <t>Security and intelligence analytics software - exhibited at APTA 2026</t>
+          <t>EV fleet charge management software - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F190" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>Lux Modus</t>
+          <t>Uber Technologies, Inc.</t>
         </is>
       </c>
       <c r="B191" s="5" t="n"/>
@@ -52672,7 +52636,7 @@
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>LiDAR 3D digital twin capture for transit - exhibited at APTA 2026</t>
+          <t>On-demand mobility platform for agency partnerships - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
@@ -52684,7 +52648,7 @@
     <row r="192">
       <c r="A192" s="37" t="inlineStr">
         <is>
-          <t>MOEV Inc.</t>
+          <t>Uptale USA, Inc.</t>
         </is>
       </c>
       <c r="B192" s="37" t="n"/>
@@ -52696,7 +52660,7 @@
       </c>
       <c r="E192" s="37" t="inlineStr">
         <is>
-          <t>Smart EV charging management software - exhibited at APTA 2026</t>
+          <t>Immersive VR training software platform - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F192" s="40" t="inlineStr">
@@ -52705,232 +52669,8 @@
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="5" t="inlineStr">
-        <is>
-          <t>Onward Health</t>
-        </is>
-      </c>
-      <c r="B193" s="5" t="n"/>
-      <c r="C193" s="6" t="n"/>
-      <c r="D193" s="5" t="inlineStr">
-        <is>
-          <t>Suppliers &amp; Services</t>
-        </is>
-      </c>
-      <c r="E193" s="5" t="inlineStr">
-        <is>
-          <t>Medical transportation ride management software - exhibited at APTA 2026</t>
-        </is>
-      </c>
-      <c r="F193" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="37" t="inlineStr">
-        <is>
-          <t>Pulse Transit Software</t>
-        </is>
-      </c>
-      <c r="B194" s="37" t="n"/>
-      <c r="C194" s="38" t="n"/>
-      <c r="D194" s="37" t="inlineStr">
-        <is>
-          <t>Suppliers &amp; Services</t>
-        </is>
-      </c>
-      <c r="E194" s="37" t="inlineStr">
-        <is>
-          <t>Transit operations software - exhibited at APTA 2026</t>
-        </is>
-      </c>
-      <c r="F194" s="40" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="5" t="inlineStr">
-        <is>
-          <t>PureTech Systems, Inc.</t>
-        </is>
-      </c>
-      <c r="B195" s="5" t="n"/>
-      <c r="C195" s="6" t="n">
-        <v>2004</v>
-      </c>
-      <c r="D195" s="5" t="inlineStr">
-        <is>
-          <t>Suppliers &amp; Services</t>
-        </is>
-      </c>
-      <c r="E195" s="5" t="inlineStr">
-        <is>
-          <t>AI video analytics perimeter security software - exhibited at APTA 2026</t>
-        </is>
-      </c>
-      <c r="F195" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="37" t="inlineStr">
-        <is>
-          <t>Redstone Technologies LLC</t>
-        </is>
-      </c>
-      <c r="B196" s="37" t="n"/>
-      <c r="C196" s="38" t="n"/>
-      <c r="D196" s="37" t="inlineStr">
-        <is>
-          <t>Suppliers &amp; Services</t>
-        </is>
-      </c>
-      <c r="E196" s="37" t="inlineStr">
-        <is>
-          <t>Rail/transit software, AI and asset monitoring - exhibited at APTA 2026</t>
-        </is>
-      </c>
-      <c r="F196" s="40" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="5" t="inlineStr">
-        <is>
-          <t>Strategic Mapping</t>
-        </is>
-      </c>
-      <c r="B197" s="5" t="n"/>
-      <c r="C197" s="6" t="n"/>
-      <c r="D197" s="5" t="inlineStr">
-        <is>
-          <t>Suppliers &amp; Services</t>
-        </is>
-      </c>
-      <c r="E197" s="5" t="inlineStr">
-        <is>
-          <t>Transit CAD/AVL, APC, passenger information systems - exhibited at APTA 2026</t>
-        </is>
-      </c>
-      <c r="F197" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="37" t="inlineStr">
-        <is>
-          <t>TSO Mobile</t>
-        </is>
-      </c>
-      <c r="B198" s="37" t="n"/>
-      <c r="C198" s="38" t="n"/>
-      <c r="D198" s="37" t="inlineStr">
-        <is>
-          <t>Suppliers &amp; Services</t>
-        </is>
-      </c>
-      <c r="E198" s="37" t="inlineStr">
-        <is>
-          <t>GPS fleet tracking and telematics software - exhibited at APTA 2026</t>
-        </is>
-      </c>
-      <c r="F198" s="39" t="inlineStr">
-        <is>
-          <t>Yes - Sales Account Executive – Mid-Mark</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="5" t="inlineStr">
-        <is>
-          <t>The Mobility House</t>
-        </is>
-      </c>
-      <c r="B199" s="5" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="C199" s="6" t="n">
-        <v>2009</v>
-      </c>
-      <c r="D199" s="5" t="inlineStr">
-        <is>
-          <t>Suppliers &amp; Services</t>
-        </is>
-      </c>
-      <c r="E199" s="5" t="inlineStr">
-        <is>
-          <t>EV fleet charge management software - exhibited at APTA 2026</t>
-        </is>
-      </c>
-      <c r="F199" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="37" t="inlineStr">
-        <is>
-          <t>Uber Technologies, Inc.</t>
-        </is>
-      </c>
-      <c r="B200" s="37" t="n"/>
-      <c r="C200" s="38" t="n"/>
-      <c r="D200" s="37" t="inlineStr">
-        <is>
-          <t>Suppliers &amp; Services</t>
-        </is>
-      </c>
-      <c r="E200" s="37" t="inlineStr">
-        <is>
-          <t>On-demand mobility platform for agency partnerships - exhibited at APTA 2026</t>
-        </is>
-      </c>
-      <c r="F200" s="40" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="5" t="inlineStr">
-        <is>
-          <t>Uptale USA, Inc.</t>
-        </is>
-      </c>
-      <c r="B201" s="5" t="n"/>
-      <c r="C201" s="6" t="n"/>
-      <c r="D201" s="5" t="inlineStr">
-        <is>
-          <t>Suppliers &amp; Services</t>
-        </is>
-      </c>
-      <c r="E201" s="5" t="inlineStr">
-        <is>
-          <t>Immersive VR training software platform - exhibited at APTA 2026</t>
-        </is>
-      </c>
-      <c r="F201" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F201"/>
+  <autoFilter ref="A1:F192"/>
   <dataValidations count="1">
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid category" error="Pick one of: Fare &amp; Payments, Fleet &amp; Operations, Rider Experience, Demand-Response &amp; AV, Parking &amp; Curb, Suppliers &amp; Services" type="list">
       <formula1>"Fare &amp; Payments,Fleet &amp; Operations,Rider Experience,Demand-Response &amp; AV,Parking &amp; Curb,Suppliers &amp; Services"</formula1>
@@ -52987,7 +52727,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/10/26)</t>
+          <t>Hiring AEs? (9/11/26)</t>
         </is>
       </c>
     </row>
@@ -54545,9 +54285,9 @@
           <t>Metering, CIS, billing and grid analytics for public power utilities</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 301 for https://www.oracle.com/corp</t>
         </is>
       </c>
     </row>
@@ -55237,7 +54977,7 @@
       </c>
       <c r="F76" s="45" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -56517,7 +56257,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/10/26)</t>
+          <t>Hiring AEs? (9/11/26)</t>
         </is>
       </c>
     </row>
@@ -56987,9 +56727,9 @@
           <t>Aviation design and simulation software (AviPLAN, AeroTURN, GuideSIGN) used by airport planners for aircraft movement, apron layout and airside safety analysis.</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Manager</t>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -57100,7 +56840,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>First-In fire station alerting and emergency dispatch systems for airport ARFF stations, including aircraft emergency alerting endpoints and turnout timers.</t>
+          <t>First-In fire station alerting and emergency dispatch systems for airport ARFF stations, including aircraft emergency alerting endpoints and turnout timers. - exhibited at IAFC FRI 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -57403,9 +57143,9 @@
           <t>Airport weather observation systems and runway condition sensors for airports - exhibited at NACE 2026</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -59854,7 +59594,7 @@
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>Shuttle and demand-response transit tech for airports and municipalities</t>
+          <t>Shuttle and demand-response transit tech for airports and municipalities - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
@@ -60041,7 +59781,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/10/26)</t>
+          <t>Hiring AEs? (9/11/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -267,8 +267,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -943,7 +943,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/11/26)</t>
+          <t>Hiring AEs? (9/12/26)</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.365labs.com/car</t>
+          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
         </is>
       </c>
     </row>
@@ -5893,9 +5893,9 @@
           <t>Incident records and ePCR data platform for EMS and fire agencies - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
-      <c r="F168" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F168" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>Unknown - board is another company's - not read</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="F260" s="11" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - State Partnerships Manager (Austin only</t>
+          <t>Sales (non-AE) - State Partnerships Manager only</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10304,9 @@
         </is>
       </c>
       <c r="B324" s="2" t="n"/>
-      <c r="C324" s="3" t="n"/>
+      <c r="C324" s="3" t="n">
+        <v>2013</v>
+      </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -11135,7 +11137,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/11/26)</t>
+          <t>Hiring AEs? (9/12/26)</t>
         </is>
       </c>
     </row>
@@ -12423,9 +12425,9 @@
           <t>Care coordination and PDMP network software (PMP AWARxE, OpenBeds) for states, counties, and health systems (Appriss lineage)</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Bamboo Bridge Strategic Account Ma</t>
         </is>
       </c>
     </row>
@@ -12981,9 +12983,9 @@
           <t>Human services EHR and care coordination software for behavioral health, residential, vocational rehab, and food assistance providers - exhibited at NatCon 2026</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14421,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/11/26)</t>
+          <t>Hiring AEs? (9/12/26)</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16075,7 @@
       </c>
       <c r="F60" s="69" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17027,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/11/26)</t>
+          <t>Hiring AEs? (9/12/26)</t>
         </is>
       </c>
     </row>
@@ -17493,7 +17495,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/11/26)</t>
+          <t>Hiring AEs? (9/12/26)</t>
         </is>
       </c>
     </row>
@@ -20759,9 +20761,9 @@
           <t>Permitting, compliance, and workflow software for water utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F111" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Strategic Account Executive - USA</t>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Solutions Engineer only</t>
         </is>
       </c>
     </row>
@@ -20936,7 +20938,7 @@
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>Floodplain management software: NFIP/CRS compliance, elevation certificates; $26.3M Series B</t>
+          <t>Floodplain management software: NFIP/CRS compliance, elevation certificates; $26.3M Series B - exhibited at StormCon 2026</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
@@ -21326,7 +21328,7 @@
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>Water quality and level monitoring instruments for agencies and utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+          <t>Water quality and level monitoring instruments for agencies and utilities - exhibited at AWWA ACE 2026, WEFTEC 2026, StormCon 2026</t>
         </is>
       </c>
       <c r="F130" s="16" t="inlineStr">
@@ -21716,7 +21718,7 @@
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>Sewer flow monitoring and I&amp;I analytics for municipal wastewater utilities - exhibited at WEFTEC 2026</t>
+          <t>Sewer flow monitoring and I&amp;I analytics for municipal wastewater utilities - exhibited at WEFTEC 2026, StormCon 2026</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
@@ -24623,7 +24625,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/11/26)</t>
+          <t>Hiring AEs? (9/12/26)</t>
         </is>
       </c>
     </row>
@@ -24708,12 +24710,12 @@
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>Municipal websites, 311/CRM, mass notification, and agenda software - exhibited at NLC City Summit 2026, AWWA ACE 2026, 3CMA 2026, WEFTEC 2026</t>
+          <t>Municipal websites, 311/CRM, mass notification, and agenda software - exhibited at NLC City Summit 2026, AWWA ACE 2026, 3CMA 2026, WEFTEC 2026, StormCon 2026</t>
         </is>
       </c>
       <c r="F4" s="22" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24773,7 @@
           <t>Community surveys, benchmarking, and budget simulation (owns National Research Center)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Madison, WI)</t>
         </is>
@@ -24893,7 +24895,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://zencity.io/careers</t>
+          <t>Unknown - HTTP 403 for https://zencity.io/careers</t>
         </is>
       </c>
     </row>
@@ -25011,7 +25013,7 @@
           <t>Community participation platform: surveys, ideation, participatory budgeting (ex-CitizenLab) - exhibited at 3CMA 2026</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -25551,7 +25553,7 @@
           <t>Citizen identity and digital service portals (CitizenOne) plus digital trust/signatures (Notarius)</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Représentant du développement des  only</t>
         </is>
@@ -26019,7 +26021,7 @@
           <t>Workflow automation, online forms and eSignature for state/local agencies - exhibited at Healthcare IT Connect 2026</t>
         </is>
       </c>
-      <c r="F48" s="22" t="inlineStr">
+      <c r="F48" s="23" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
@@ -26197,7 +26199,7 @@
           <t>Digital experience platform and forms for government; UK vendor with US clients</t>
         </is>
       </c>
-      <c r="F54" s="23" t="inlineStr">
+      <c r="F54" s="22" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -26377,7 +26379,7 @@
           <t>Cloud apps for permits, code enforcement and citizen requests in small cities</t>
         </is>
       </c>
-      <c r="F60" s="23" t="inlineStr">
+      <c r="F60" s="22" t="inlineStr">
         <is>
           <t>Yes - Sales Account Executive - Smart XE</t>
         </is>
@@ -26435,7 +26437,7 @@
           <t>GIS, asset and citizen-facing software for small and rural local governments</t>
         </is>
       </c>
-      <c r="F62" s="22" t="inlineStr">
+      <c r="F62" s="23" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -26887,7 +26889,7 @@
           <t>Permitting, budgeting, procurement, and asset management cloud suite (Cox-owned) - exhibited at GFOA 2026, NLC City Summit 2026, NACE 2026, AWWA ACE 2026, GMIS International 2026, Maryland Municipal League 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F78" s="23" t="inlineStr">
+      <c r="F78" s="22" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive (US | Illinois | Ch)</t>
         </is>
@@ -26947,7 +26949,7 @@
           <t>AI permitting and licensing platform: 24/7 resident assistant, AI code-compliance review - exhibited at NLC City Summit 2026, Maryland Municipal League 2026</t>
         </is>
       </c>
-      <c r="F80" s="23" t="inlineStr">
+      <c r="F80" s="22" t="inlineStr">
         <is>
           <t>Yes - Business Development Manager (New York, NY)</t>
         </is>
@@ -27007,7 +27009,7 @@
           <t>Special event, film, and complex permit approval workflow SaaS for cities</t>
         </is>
       </c>
-      <c r="F82" s="23" t="inlineStr">
+      <c r="F82" s="22" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -27367,7 +27369,7 @@
           <t>ProjectDox electronic plan review for building, fire, planning, and public works agencies</t>
         </is>
       </c>
-      <c r="F94" s="23" t="inlineStr">
+      <c r="F94" s="22" t="inlineStr">
         <is>
           <t>Yes - Account Executive (GovTech SaaS)</t>
         </is>
@@ -27887,7 +27889,7 @@
           <t>Electronic plan review software for building and public works departments</t>
         </is>
       </c>
-      <c r="F112" s="23" t="inlineStr">
+      <c r="F112" s="22" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -28059,7 +28061,7 @@
           <t>Objective Build planning and building consent software for government regulators</t>
         </is>
       </c>
-      <c r="F118" s="22" t="inlineStr">
+      <c r="F118" s="23" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Account Director only</t>
         </is>
@@ -28233,7 +28235,7 @@
           <t>The govtech giant: ERP, courts, public safety, permitting, and payments - exhibited at GFOA 2026, NLC City Summit 2026, PSHRA 2026, AWWA ACE 2026, IAAO 2026, NASCIO 2026, GMIS International 2026, NACM 2026, APPA Probation 2026, Iowa State Association of Counties 2026, Maryland Municipal League 2026, IAFC FRI 2026, APCO 2026, NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F124" s="23" t="inlineStr">
+      <c r="F124" s="22" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -28353,7 +28355,7 @@
           <t>Local government ERP: financials, property tax, assessing, utility billing - Michigan standard going national - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F128" s="23" t="inlineStr">
+      <c r="F128" s="22" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -28473,7 +28475,7 @@
           <t>AI workflow for county assessors: deed processing, exemptions, taxpayer communication (YC S17) - exhibited at NLC City Summit 2026, IAAO 2026</t>
         </is>
       </c>
-      <c r="F132" s="22" t="inlineStr">
+      <c r="F132" s="23" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager (West Coa only</t>
         </is>
@@ -28533,7 +28535,7 @@
           <t>VIP public-sector ERP for Ohio-area local governments; 100% employee-owned - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F134" s="22" t="inlineStr">
+      <c r="F134" s="23" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -28745,7 +28747,7 @@
       </c>
       <c r="F141" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Business Development Officer only</t>
+          <t>Sales (non-AE) - Senior Business Development Office only</t>
         </is>
       </c>
     </row>
@@ -29301,7 +29303,7 @@
           <t>Cloud ERP for cities and counties covering finance, budgeting, utility billing, payroll, permitting, licensing and code enforcement, built on Oracle NetSuite - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F160" s="23" t="inlineStr">
+      <c r="F160" s="22" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -29599,7 +29601,7 @@
           <t>Bill presentment and payments for governments and utilities (public co) - exhibited at GFOA 2026, NAHRO 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F170" s="23" t="inlineStr">
+      <c r="F170" s="22" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -29779,7 +29781,7 @@
           <t>Source-to-contract procurement ecosystem (BidNet Direct, Periscope S2G; ex-mdf commerce)</t>
         </is>
       </c>
-      <c r="F176" s="23" t="inlineStr">
+      <c r="F176" s="22" t="inlineStr">
         <is>
           <t>Yes - Account Executive (United States)</t>
         </is>
@@ -30079,7 +30081,7 @@
           <t>Supplier onboarding and payee identity verification preventing payments fraud for gov and higher-ed - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F186" s="23" t="inlineStr">
+      <c r="F186" s="22" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -30109,9 +30111,9 @@
           <t>Supplier ratings and performance reviews platform for public-sector buyers</t>
         </is>
       </c>
-      <c r="F187" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -30493,7 +30495,7 @@
           <t>Expense management and payment software - exhibited at NIGP 2026, NACUBO 2026</t>
         </is>
       </c>
-      <c r="F200" s="23" t="inlineStr">
+      <c r="F200" s="22" t="inlineStr">
         <is>
           <t>Yes - Account Executive - Midmarket (rem (Atlanta, GA)</t>
         </is>
@@ -30841,7 +30843,7 @@
           <t>Source-to-pay suite with public sector practice serving states and agencies</t>
         </is>
       </c>
-      <c r="F212" s="23" t="inlineStr">
+      <c r="F212" s="22" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Singapore, Singapo)</t>
         </is>
@@ -30933,7 +30935,7 @@
       </c>
       <c r="F215" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive – Hea (United States)</t>
+          <t>Yes - Enterprise Account Executive (United States)</t>
         </is>
       </c>
     </row>
@@ -31733,7 +31735,7 @@
           <t>Benefits administration and enrollment built exclusively for public-sector employers - exhibited at SALGBA 2026</t>
         </is>
       </c>
-      <c r="F242" s="22" t="inlineStr">
+      <c r="F242" s="23" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -31855,7 +31857,7 @@
       </c>
       <c r="F246" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://passportworkforce.c</t>
+          <t>Unknown - HTTP 403 for https://passportworkforce.c</t>
         </is>
       </c>
     </row>
@@ -31913,7 +31915,7 @@
           <t>Digital heart health app and monitoring - exhibited at NACo 2026, PSHRA 2026, SALGBA 2026</t>
         </is>
       </c>
-      <c r="F248" s="22" t="inlineStr">
+      <c r="F248" s="23" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Associate Director, Client Success only</t>
         </is>
@@ -31937,9 +31939,9 @@
           <t>EHS compliance software and services - exhibited at ICMA 2025</t>
         </is>
       </c>
-      <c r="F249" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive - Automotive (Atlanta, GA)</t>
+      <c r="F249" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -32203,7 +32205,7 @@
           <t>Time, attendance and scheduling for government, education and public safety - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F258" s="23" t="inlineStr">
+      <c r="F258" s="22" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -32501,7 +32503,7 @@
           <t>License verification and workforce compliance for agencies and regulators</t>
         </is>
       </c>
-      <c r="F268" s="23" t="inlineStr">
+      <c r="F268" s="22" t="inlineStr">
         <is>
           <t>Yes - Sales Executive - Central Region ( (Remote - US)</t>
         </is>
@@ -32561,9 +32563,9 @@
           <t>Local government ERP including payroll and personnel modules - exhibited at GFOA 2026, Maryland Municipal League 2026</t>
         </is>
       </c>
-      <c r="F270" s="22" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Client Success Manager only</t>
+      <c r="F270" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sales Development Representative only</t>
         </is>
       </c>
     </row>
@@ -32829,7 +32831,7 @@
       </c>
       <c r="F279" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -33437,7 +33439,7 @@
           <t>Work management and collaboration software - exhibited at NACo 2026</t>
         </is>
       </c>
-      <c r="F300" s="23" t="inlineStr">
+      <c r="F300" s="22" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -33489,7 +33491,7 @@
           <t>Cybersecurity software and network security platforms - exhibited at IACP 2026, NASCIO 2026, CoSN 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F302" s="23" t="inlineStr">
+      <c r="F302" s="22" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -33549,7 +33551,7 @@
           <t>Claude, sold to state and local agencies through GSA and cooperative vehicles alongside its commercial business</t>
         </is>
       </c>
-      <c r="F304" s="23" t="inlineStr">
+      <c r="F304" s="22" t="inlineStr">
         <is>
           <t>Yes - Account Executive, AI Native (New York City, NY;)</t>
         </is>
@@ -33827,7 +33829,7 @@
           <t>Strategic planning, performance measurement, and public dashboards built for local government</t>
         </is>
       </c>
-      <c r="F314" s="23" t="inlineStr">
+      <c r="F314" s="22" t="inlineStr">
         <is>
           <t>Yes - Senior Account Executive - Public  (Canada)</t>
         </is>
@@ -33887,7 +33889,7 @@
           <t>Policy and rulemaking workflow: draft, route, approve, and track regulations for agencies</t>
         </is>
       </c>
-      <c r="F316" s="23" t="inlineStr">
+      <c r="F316" s="22" t="inlineStr">
         <is>
           <t>Yes - Strategic Account Executive - West (Remote)</t>
         </is>
@@ -34001,7 +34003,7 @@
           <t>Public affairs and legislative tracking software - exhibited at NACo 2026, NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F320" s="23" t="inlineStr">
+      <c r="F320" s="22" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Washington D.C.)</t>
         </is>
@@ -34173,7 +34175,7 @@
           <t>Governance, performance and risk management platform for public sector organizations</t>
         </is>
       </c>
-      <c r="F326" s="22" t="inlineStr">
+      <c r="F326" s="23" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -34819,7 +34821,7 @@
           <t>Digital ballot scanning, tabulation and audit systems for election offices</t>
         </is>
       </c>
-      <c r="F348" s="22" t="inlineStr">
+      <c r="F348" s="23" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -35239,7 +35241,7 @@
           <t>Ballot tracking, electronic ballot delivery and election tools for jurisdictions</t>
         </is>
       </c>
-      <c r="F362" s="22" t="inlineStr">
+      <c r="F362" s="23" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -35533,7 +35535,7 @@
           <t>Ballot printing and election materials for county boards of elections - exhibited at Maryland Municipal League 2026</t>
         </is>
       </c>
-      <c r="F372" s="23" t="inlineStr">
+      <c r="F372" s="22" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -36259,7 +36261,7 @@
           <t>Web-based mapping, demographic, and consumer data visualization application for university and public library patrons - exhibited at PLA 2026</t>
         </is>
       </c>
-      <c r="F398" s="23" t="inlineStr">
+      <c r="F398" s="22" t="inlineStr">
         <is>
           <t>Yes - Senior Account Executive - B2B Saa</t>
         </is>
@@ -36529,7 +36531,7 @@
           <t>Research databases, ebook collections and discovery software licensed to public libraries, academic libraries, schools and healthcare organizations - exhibited at PLA 2026</t>
         </is>
       </c>
-      <c r="F408" s="23" t="inlineStr">
+      <c r="F408" s="22" t="inlineStr">
         <is>
           <t>Yes - Regional Sales Manager, AMC – Virg</t>
         </is>
@@ -38081,7 +38083,7 @@
           <t>Payment processing platform - exhibited at ICMA 2025</t>
         </is>
       </c>
-      <c r="F466" s="23" t="inlineStr">
+      <c r="F466" s="22" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -38229,7 +38231,7 @@
           <t>Construction project management software - exhibited at ICMA 2025, PWX 2026</t>
         </is>
       </c>
-      <c r="F472" s="22" t="inlineStr">
+      <c r="F472" s="23" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -38707,7 +38709,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/11/26)</t>
+          <t>Hiring AEs? (9/12/26)</t>
         </is>
       </c>
     </row>
@@ -41427,7 +41429,7 @@
       </c>
       <c r="F92" s="29" t="inlineStr">
         <is>
-          <t>Yes - Account Manager (Remote - Canada)</t>
+          <t>Yes - Sr. Account Manager - Pacific West (Remote - Californi)</t>
         </is>
       </c>
     </row>
@@ -42989,7 +42991,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/11/26)</t>
+          <t>Hiring AEs? (9/12/26)</t>
         </is>
       </c>
     </row>
@@ -43049,7 +43051,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>Yes - Sales Executive, Cross-Sell (North (Remote Worker - N/)</t>
+          <t>Yes - Senior Sales Executive (VA/WV/OH) (Remote Worker - N/)</t>
         </is>
       </c>
     </row>
@@ -43553,7 +43555,7 @@
       </c>
       <c r="F20" s="33" t="inlineStr">
         <is>
-          <t>Yes - Account Executive - Canada (Toronto, Ontario)</t>
+          <t>Yes - Commercial Account Executive - Cen (Dallas, Texas)</t>
         </is>
       </c>
     </row>
@@ -46281,7 +46283,7 @@
       </c>
       <c r="F112" s="35" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Inside Sales Account Executive - M only</t>
+          <t>Sales (non-AE) - Senior Salesforce Developer only</t>
         </is>
       </c>
     </row>
@@ -47085,7 +47087,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/11/26)</t>
+          <t>Hiring AEs? (9/12/26)</t>
         </is>
       </c>
     </row>
@@ -47385,7 +47387,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.modeshift.com/c</t>
+          <t>Unknown - HTTP 403 for https://www.modeshift.com/c</t>
         </is>
       </c>
     </row>
@@ -47981,7 +47983,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.enghouse.com/ca</t>
+          <t>Unknown - HTTP 403 for https://www.enghouse.com/ca</t>
         </is>
       </c>
     </row>
@@ -48835,7 +48837,7 @@
       </c>
       <c r="F60" s="40" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -50035,7 +50037,7 @@
       </c>
       <c r="F100" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.hanoverdisplays</t>
+          <t>Unknown - HTTP 403 for https://www.hanoverdisplays</t>
         </is>
       </c>
     </row>
@@ -50423,7 +50425,7 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://qryde.com/employmen</t>
+          <t>Unknown - HTTP 403 for https://qryde.com/employmen</t>
         </is>
       </c>
     </row>
@@ -50771,9 +50773,9 @@
           <t>On-demand transit software converting fixed routes to demand-response for agencies</t>
         </is>
       </c>
-      <c r="F125" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -52391,9 +52393,9 @@
           <t>Security and intelligence analytics software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F181" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F181" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Enterprise Sales Executive – New L (2 Locations)</t>
         </is>
       </c>
     </row>
@@ -52727,7 +52729,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/11/26)</t>
+          <t>Hiring AEs? (9/12/26)</t>
         </is>
       </c>
     </row>
@@ -54285,9 +54287,9 @@
           <t>Metering, CIS, billing and grid analytics for public power utilities</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - HTTP 301 for https://www.oracle.com/corp</t>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -54977,7 +54979,7 @@
       </c>
       <c r="F76" s="45" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -56257,7 +56259,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/11/26)</t>
+          <t>Hiring AEs? (9/12/26)</t>
         </is>
       </c>
     </row>
@@ -57741,9 +57743,9 @@
           <t>Baggage handling systems and terminal logistics for airports</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -59327,9 +59329,9 @@
           <t>Parking operations, payments and analytics for airports and venues</t>
         </is>
       </c>
-      <c r="F104" s="52" t="inlineStr">
-        <is>
-          <t>Yes - Associate Account Executive (Dallas)</t>
+      <c r="F104" s="53" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Client Success Manager only</t>
         </is>
       </c>
     </row>
@@ -59781,7 +59783,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/11/26)</t>
+          <t>Hiring AEs? (9/12/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -230,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -357,7 +357,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="25" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -943,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/12/26)</t>
+          <t>Hiring AEs? (9/13/26)</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
+          <t>Unknown - HTTP 202 for https://www.365labs.com/car</t>
         </is>
       </c>
     </row>
@@ -5893,9 +5892,9 @@
           <t>Incident records and ePCR data platform for EMS and fire agencies - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
-      <c r="F168" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11137,7 +11136,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/12/26)</t>
+          <t>Hiring AEs? (9/13/26)</t>
         </is>
       </c>
     </row>
@@ -11189,7 +11188,7 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11213,7 +11212,7 @@
       </c>
       <c r="F4" s="63" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11285,7 +11284,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -11309,7 +11308,7 @@
       </c>
       <c r="F8" s="63" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -12137,7 +12136,7 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -12161,7 +12160,7 @@
       </c>
       <c r="F38" s="63" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14420,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/12/26)</t>
+          <t>Hiring AEs? (9/13/26)</t>
         </is>
       </c>
     </row>
@@ -17027,7 +17026,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/12/26)</t>
+          <t>Hiring AEs? (9/13/26)</t>
         </is>
       </c>
     </row>
@@ -17431,9 +17430,9 @@
           <t>GURU site selection, property data and property tax mapping platform for economic development organizations and assessor offices - exhibited at IEDC 2026</t>
         </is>
       </c>
-      <c r="F16" s="76" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F16" s="75" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -17495,7 +17494,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/12/26)</t>
+          <t>Hiring AEs? (9/13/26)</t>
         </is>
       </c>
     </row>
@@ -22511,9 +22510,9 @@
           <t>Network data analytics software for water utilities covering leakage, infiltration, energy use and capital planning - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
-      <c r="F170" s="16" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F170" s="15" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -24625,7 +24624,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/12/26)</t>
+          <t>Hiring AEs? (9/13/26)</t>
         </is>
       </c>
     </row>
@@ -24895,7 +24894,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://zencity.io/careers</t>
+          <t>Unknown - HTTP 202 for https://zencity.io/careers</t>
         </is>
       </c>
     </row>
@@ -26199,9 +26198,9 @@
           <t>Digital experience platform and forms for government; UK vendor with US clients</t>
         </is>
       </c>
-      <c r="F54" s="22" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F54" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -30111,9 +30110,9 @@
           <t>Supplier ratings and performance reviews platform for public-sector buyers</t>
         </is>
       </c>
-      <c r="F187" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F187" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -30845,7 +30844,7 @@
       </c>
       <c r="F212" s="22" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Singapore, Singapo)</t>
+          <t>Yes - Account Executive (London)</t>
         </is>
       </c>
     </row>
@@ -31857,7 +31856,7 @@
       </c>
       <c r="F246" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://passportworkforce.c</t>
+          <t>Unknown - HTTP 202 for https://passportworkforce.c</t>
         </is>
       </c>
     </row>
@@ -31967,7 +31966,7 @@
       </c>
       <c r="F250" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -32175,9 +32174,9 @@
           <t>Employee benefits, enrollment and HR services for public sector employers</t>
         </is>
       </c>
-      <c r="F257" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F257" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Account Manager (3 Locations)</t>
         </is>
       </c>
     </row>
@@ -32297,7 +32296,7 @@
       </c>
       <c r="F261" s="7" t="inlineStr">
         <is>
-          <t>Unknown - board is another company's - not read</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -33771,7 +33770,7 @@
       </c>
       <c r="F312" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -38709,7 +38708,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/12/26)</t>
+          <t>Hiring AEs? (9/13/26)</t>
         </is>
       </c>
     </row>
@@ -42991,7 +42990,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/12/26)</t>
+          <t>Hiring AEs? (9/13/26)</t>
         </is>
       </c>
     </row>
@@ -47087,7 +47086,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/12/26)</t>
+          <t>Hiring AEs? (9/13/26)</t>
         </is>
       </c>
     </row>
@@ -47387,7 +47386,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.modeshift.com/c</t>
+          <t>Unknown - HTTP 202 for https://www.modeshift.com/c</t>
         </is>
       </c>
     </row>
@@ -47983,7 +47982,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.enghouse.com/ca</t>
+          <t>Unknown - HTTP 202 for https://www.enghouse.com/ca</t>
         </is>
       </c>
     </row>
@@ -49797,7 +49796,7 @@
       </c>
       <c r="F92" s="39" t="inlineStr">
         <is>
-          <t>Yes - Strategic Account Executive (North Carolina_Rem)</t>
+          <t>Yes - Strategic Account Executive (Tennessee_Remote_C)</t>
         </is>
       </c>
     </row>
@@ -50037,7 +50036,7 @@
       </c>
       <c r="F100" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.hanoverdisplays</t>
+          <t>Unknown - HTTP 202 for https://www.hanoverdisplays</t>
         </is>
       </c>
     </row>
@@ -50773,9 +50772,9 @@
           <t>On-demand transit software converting fixed routes to demand-response for agencies</t>
         </is>
       </c>
-      <c r="F125" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -52729,7 +52728,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/12/26)</t>
+          <t>Hiring AEs? (9/13/26)</t>
         </is>
       </c>
     </row>
@@ -55543,7 +55542,7 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>Yes - Senior Account Executive (Portland, ME)</t>
+          <t>Yes - Enterprise Account Executive (Portland, ME)</t>
         </is>
       </c>
     </row>
@@ -56259,7 +56258,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/12/26)</t>
+          <t>Hiring AEs? (9/13/26)</t>
         </is>
       </c>
     </row>
@@ -57357,7 +57356,7 @@
       </c>
       <c r="F38" s="51" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -58375,7 +58374,7 @@
       </c>
       <c r="F72" s="51" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -59783,7 +59782,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/12/26)</t>
+          <t>Hiring AEs? (9/13/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/13/26)</t>
+          <t>Hiring AEs? (9/14/26)</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.365labs.com/car</t>
+          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 500 for https://www.lenslock.com/ca</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/13/26)</t>
+          <t>Hiring AEs? (9/14/26)</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/13/26)</t>
+          <t>Hiring AEs? (9/14/26)</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/13/26)</t>
+          <t>Hiring AEs? (9/14/26)</t>
         </is>
       </c>
     </row>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/13/26)</t>
+          <t>Hiring AEs? (9/14/26)</t>
         </is>
       </c>
     </row>
@@ -22682,7 +22682,7 @@
       </c>
       <c r="F176" s="16" t="inlineStr">
         <is>
-          <t>Yes - Business Development Manager (Remo (Sydney, Australia )</t>
+          <t>Yes - Partner Account Manager (Remote - Canada)</t>
         </is>
       </c>
     </row>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="F220" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 503 for https://www.sawatchlabs.com</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/13/26)</t>
+          <t>Hiring AEs? (9/14/26)</t>
         </is>
       </c>
     </row>
@@ -24894,7 +24894,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://zencity.io/careers</t>
+          <t>Unknown - HTTP 403 for https://zencity.io/careers</t>
         </is>
       </c>
     </row>
@@ -31856,7 +31856,7 @@
       </c>
       <c r="F246" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://passportworkforce.c</t>
+          <t>Unknown - HTTP 403 for https://passportworkforce.c</t>
         </is>
       </c>
     </row>
@@ -32176,7 +32176,7 @@
       </c>
       <c r="F257" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Manager (3 Locations)</t>
+          <t>Yes - Account Manager (Denver, Colorado)</t>
         </is>
       </c>
     </row>
@@ -34174,9 +34174,9 @@
           <t>Governance, performance and risk management platform for public sector organizations</t>
         </is>
       </c>
-      <c r="F326" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F326" s="22" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -38708,7 +38708,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/13/26)</t>
+          <t>Hiring AEs? (9/14/26)</t>
         </is>
       </c>
     </row>
@@ -42990,7 +42990,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/13/26)</t>
+          <t>Hiring AEs? (9/14/26)</t>
         </is>
       </c>
     </row>
@@ -47086,7 +47086,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/13/26)</t>
+          <t>Hiring AEs? (9/14/26)</t>
         </is>
       </c>
     </row>
@@ -47386,7 +47386,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.modeshift.com/c</t>
+          <t>Unknown - HTTP 403 for https://www.modeshift.com/c</t>
         </is>
       </c>
     </row>
@@ -47982,7 +47982,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.enghouse.com/ca</t>
+          <t>Unknown - HTTP 403 for https://www.enghouse.com/ca</t>
         </is>
       </c>
     </row>
@@ -49796,7 +49796,7 @@
       </c>
       <c r="F92" s="39" t="inlineStr">
         <is>
-          <t>Yes - Strategic Account Executive (Tennessee_Remote_C)</t>
+          <t>Yes - Strategic Account Executive (North Carolina_Rem)</t>
         </is>
       </c>
     </row>
@@ -50036,7 +50036,7 @@
       </c>
       <c r="F100" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.hanoverdisplays</t>
+          <t>Unknown - HTTP 403 for https://www.hanoverdisplays</t>
         </is>
       </c>
     </row>
@@ -52728,7 +52728,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/13/26)</t>
+          <t>Hiring AEs? (9/14/26)</t>
         </is>
       </c>
     </row>
@@ -56258,7 +56258,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/13/26)</t>
+          <t>Hiring AEs? (9/14/26)</t>
         </is>
       </c>
     </row>
@@ -58374,7 +58374,7 @@
       </c>
       <c r="F72" s="51" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -59782,7 +59782,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/13/26)</t>
+          <t>Hiring AEs? (9/14/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/14/26)</t>
+          <t>Hiring AEs? (9/16/26)</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 404 for https://www.ndi-rs.com/care</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 500 for https://www.lenslock.com/ca</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>Yes - Business Development Manager - LAT (São Paulo, Brazil)</t>
+          <t>Yes - Business Development Manager (Rome, Rome, Italy)</t>
         </is>
       </c>
     </row>
@@ -4350,9 +4350,9 @@
           <t>Cyber-over-RF counter-drone detect, track, and mitigate systems for LE, prisons, and infrastructure</t>
         </is>
       </c>
-      <c r="F115" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F115" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -5232,9 +5232,9 @@
           <t>Video review and analytics software used by police investigators</t>
         </is>
       </c>
-      <c r="F146" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/14/26)</t>
+          <t>Hiring AEs? (9/16/26)</t>
         </is>
       </c>
     </row>
@@ -13192,9 +13192,9 @@
           <t>AI clinical documentation and chart auditing platform purpose-built for behavioral health providers including CCBHCs and human services organizations - exhibited at NatCon 2026</t>
         </is>
       </c>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - VP of Revenue only</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/14/26)</t>
+          <t>Hiring AEs? (9/16/26)</t>
         </is>
       </c>
     </row>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (US - Remote)</t>
+          <t>Yes - Account Executive, EMEA (UK - Remote)</t>
         </is>
       </c>
     </row>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="F72" s="70" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Vice President, Sales only</t>
+          <t>Sales (non-AE) - Senior Solutions Engineer only</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/14/26)</t>
+          <t>Hiring AEs? (9/16/26)</t>
         </is>
       </c>
     </row>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/14/26)</t>
+          <t>Hiring AEs? (9/16/26)</t>
         </is>
       </c>
     </row>
@@ -17642,9 +17642,9 @@
           <t>AI recycling-sorting robots and real-time bale/line data</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive - Climate Tech ( (Remote East Coast )</t>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -22682,7 +22682,7 @@
       </c>
       <c r="F176" s="16" t="inlineStr">
         <is>
-          <t>Yes - Partner Account Manager (Remote - Canada)</t>
+          <t>Yes - Partner Account Manager UK&amp;I (London, England - )</t>
         </is>
       </c>
     </row>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="F220" s="15" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 503 for https://www.sawatchlabs.com</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/14/26)</t>
+          <t>Hiring AEs? (9/16/26)</t>
         </is>
       </c>
     </row>
@@ -26022,7 +26022,7 @@
       </c>
       <c r="F48" s="23" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Customer Success Manager only</t>
+          <t>Sales (non-AE) - Sales Development Representative only</t>
         </is>
       </c>
     </row>
@@ -26380,7 +26380,7 @@
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t>Yes - Sales Account Executive - Smart XE</t>
+          <t>Yes - Sales Account Executive - GovTech</t>
         </is>
       </c>
     </row>
@@ -33582,7 +33582,7 @@
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Account Director - Tokyo only</t>
+          <t>Sales (non-AE) - Account Director, Large Enterprise only</t>
         </is>
       </c>
     </row>
@@ -38708,7 +38708,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/14/26)</t>
+          <t>Hiring AEs? (9/16/26)</t>
         </is>
       </c>
     </row>
@@ -39122,7 +39122,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Howell, MI)</t>
+          <t>Yes - Account Executive (Hillsboro, TX)</t>
         </is>
       </c>
     </row>
@@ -40526,9 +40526,9 @@
           <t>Space and facility booking platform used by municipal and campus facilities</t>
         </is>
       </c>
-      <c r="F62" s="27" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Director, Sales (Hybrid / Boston,  only</t>
+      <c r="F62" s="28" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -42990,7 +42990,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/14/26)</t>
+          <t>Hiring AEs? (9/16/26)</t>
         </is>
       </c>
     </row>
@@ -43050,7 +43050,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>Yes - Senior Sales Executive (VA/WV/OH) (Remote Worker - N/)</t>
+          <t>Yes - Sales Executive - Pacific Northwes (Remote Worker - N/)</t>
         </is>
       </c>
     </row>
@@ -44862,9 +44862,9 @@
           <t>Electric school bus fleet-as-a-service subscriptions for districts</t>
         </is>
       </c>
-      <c r="F64" s="35" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Customer Success Manager (CA) only</t>
+      <c r="F64" s="34" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -45252,9 +45252,9 @@
           <t>Synergy SIS, MTSS and analytics for K-12 school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Sales Representative (Mesa)</t>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -45372,9 +45372,9 @@
           <t>K-12 ERP, nutrition, payments and forms platform for districts</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Associate Client Success Manager only</t>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -46136,9 +46136,9 @@
           <t>Digital hall pass, tardy tracking, behavior management, and campus engagement platform for K-12 schools and districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F107" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Chief Revenue Officer (CRO) only</t>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Account Manager (INTERNAL APPLICAN</t>
         </is>
       </c>
     </row>
@@ -46280,9 +46280,9 @@
           <t>Library, technology asset, and facilities management software for K-12 school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F112" s="35" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Senior Salesforce Developer only</t>
+      <c r="F112" s="34" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -47086,7 +47086,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/14/26)</t>
+          <t>Hiring AEs? (9/16/26)</t>
         </is>
       </c>
     </row>
@@ -47502,7 +47502,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -49344,9 +49344,9 @@
           <t>Digital vehicle inspections and maintenance for municipal fleets</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Operations Manager, Customer Succe only</t>
         </is>
       </c>
     </row>
@@ -49796,7 +49796,7 @@
       </c>
       <c r="F92" s="39" t="inlineStr">
         <is>
-          <t>Yes - Strategic Account Executive (North Carolina_Rem)</t>
+          <t>Yes - Strategic Account Executive (Tennessee_Remote_C)</t>
         </is>
       </c>
     </row>
@@ -52728,7 +52728,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/14/26)</t>
+          <t>Hiring AEs? (9/16/26)</t>
         </is>
       </c>
     </row>
@@ -56258,7 +56258,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/14/26)</t>
+          <t>Hiring AEs? (9/16/26)</t>
         </is>
       </c>
     </row>
@@ -57742,9 +57742,9 @@
           <t>Baggage handling systems and terminal logistics for airports</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -58044,7 +58044,7 @@
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>Yes - Senior Account Executive</t>
+          <t>Yes - Senior Account Executive - West &amp;</t>
         </is>
       </c>
     </row>
@@ -58554,7 +58554,7 @@
       </c>
       <c r="F78" s="52" t="inlineStr">
         <is>
-          <t>Yes - Technical Sales Representative, So</t>
+          <t>Yes - Account Manager Molecular Diagnost</t>
         </is>
       </c>
     </row>
@@ -59782,7 +59782,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/14/26)</t>
+          <t>Hiring AEs? (9/16/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -286,9 +286,9 @@
     <xf numFmtId="1" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/16/26)</t>
+          <t>Hiring AEs? (9/17/26)</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/16/26)</t>
+          <t>Hiring AEs? (9/17/26)</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/16/26)</t>
+          <t>Hiring AEs? (9/17/26)</t>
         </is>
       </c>
     </row>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="F72" s="70" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Senior Solutions Engineer only</t>
+          <t>Sales (non-AE) - Vice President, Sales only</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/16/26)</t>
+          <t>Hiring AEs? (9/17/26)</t>
         </is>
       </c>
     </row>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/16/26)</t>
+          <t>Hiring AEs? (9/17/26)</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Solutions Engineer only</t>
+          <t>Sales (non-AE) - Senior Customer Success Manager only</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/16/26)</t>
+          <t>Hiring AEs? (9/17/26)</t>
         </is>
       </c>
     </row>
@@ -26380,7 +26380,7 @@
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t>Yes - Sales Account Executive - GovTech</t>
+          <t>Yes - Outbound Sales Representative-iWor</t>
         </is>
       </c>
     </row>
@@ -31856,7 +31856,7 @@
       </c>
       <c r="F246" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://passportworkforce.c</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -33720,9 +33720,9 @@
           <t>Symmetri AI operations platform for critical infrastructure operators in water, energy, telecom and healthcare - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
-      <c r="F310" s="21" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F310" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Technical Sales Engineer only</t>
         </is>
       </c>
     </row>
@@ -36530,9 +36530,9 @@
           <t>Research databases, ebook collections and discovery software licensed to public libraries, academic libraries, schools and healthcare organizations - exhibited at PLA 2026</t>
         </is>
       </c>
-      <c r="F408" s="22" t="inlineStr">
-        <is>
-          <t>Yes - Regional Sales Manager, AMC – Virg</t>
+      <c r="F408" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Customer Account Specialist, FOLIO only</t>
         </is>
       </c>
     </row>
@@ -38708,7 +38708,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/16/26)</t>
+          <t>Hiring AEs? (9/17/26)</t>
         </is>
       </c>
     </row>
@@ -39122,7 +39122,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Hillsboro, TX)</t>
+          <t>Yes - Account Executive (Shreveport, LA)</t>
         </is>
       </c>
     </row>
@@ -42384,9 +42384,9 @@
           <t>ShoWare ticketing and guest experience for municipal arenas and attractions</t>
         </is>
       </c>
-      <c r="F124" s="28" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F124" s="27" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Head of Sales only</t>
         </is>
       </c>
     </row>
@@ -42990,7 +42990,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/16/26)</t>
+          <t>Hiring AEs? (9/17/26)</t>
         </is>
       </c>
     </row>
@@ -43020,7 +43020,7 @@
       </c>
       <c r="F2" s="33" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Remote - US)</t>
+          <t>Sales (non-AE) - Senior Manager, Global Deal Desk only</t>
         </is>
       </c>
     </row>
@@ -43050,7 +43050,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>Yes - Sales Executive - Pacific Northwes (Remote Worker - N/)</t>
+          <t>Yes - Sales Executive, Cross-Sell (North (Remote Worker - N/)</t>
         </is>
       </c>
     </row>
@@ -43198,7 +43198,7 @@
           <t>Cloud web filtering and student safety monitoring - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F8" s="33" t="inlineStr">
+      <c r="F8" s="35" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Large/Enterpris (United States of A)</t>
         </is>
@@ -43258,7 +43258,7 @@
           <t>Web filtering and student safety monitoring for school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F10" s="33" t="inlineStr">
+      <c r="F10" s="35" t="inlineStr">
         <is>
           <t>Yes - Account Manager (REMOTE, United Kin)</t>
         </is>
@@ -43378,7 +43378,7 @@
           <t>AI web filtering and student threat detection for K-12 districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F14" s="35" t="inlineStr">
+      <c r="F14" s="33" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -43552,7 +43552,7 @@
           <t>Cloud video security and sensors for schools and public agencies</t>
         </is>
       </c>
-      <c r="F20" s="33" t="inlineStr">
+      <c r="F20" s="35" t="inlineStr">
         <is>
           <t>Yes - Commercial Account Executive - Cen (Dallas, Texas)</t>
         </is>
@@ -43732,7 +43732,7 @@
           <t>AI-based weapons screening gateways for schools, venues and public buildings</t>
         </is>
       </c>
-      <c r="F26" s="33" t="inlineStr">
+      <c r="F26" s="35" t="inlineStr">
         <is>
           <t>Yes - Regional Sales Manager (Boston, Massachuse)</t>
         </is>
@@ -43910,7 +43910,7 @@
           <t>Emergency mass notification hardware and software for schools and agencies - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F32" s="33" t="inlineStr">
+      <c r="F32" s="35" t="inlineStr">
         <is>
           <t>Yes - Regional Account Manager - Educati (Baltimore, MD)</t>
         </is>
@@ -44234,7 +44234,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 404 for https://www.ridezum.com/com</t>
         </is>
       </c>
     </row>
@@ -44262,7 +44262,7 @@
           <t>Vetted small-vehicle student rides supplementing district bus fleets - exhibited at NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F44" s="33" t="inlineStr">
+      <c r="F44" s="35" t="inlineStr">
         <is>
           <t>Yes - Regional Account Manager (Remote USA)</t>
         </is>
@@ -45162,7 +45162,7 @@
           <t>Student information system and school business/ERP suite for K-12 districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F74" s="35" t="inlineStr">
+      <c r="F74" s="33" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Technical Special only</t>
         </is>
@@ -45342,7 +45342,7 @@
           <t>Cloud SIS and LMS for K-12 districts and charter networks</t>
         </is>
       </c>
-      <c r="F80" s="33" t="inlineStr">
+      <c r="F80" s="35" t="inlineStr">
         <is>
           <t>Yes - Account Executive</t>
         </is>
@@ -45520,7 +45520,7 @@
           <t>School bus routing, fleet and student transportation software for districts</t>
         </is>
       </c>
-      <c r="F86" s="33" t="inlineStr">
+      <c r="F86" s="35" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -45640,7 +45640,7 @@
           <t>Website, CMS and mass communications platform for school districts</t>
         </is>
       </c>
-      <c r="F90" s="35" t="inlineStr">
+      <c r="F90" s="33" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -45700,7 +45700,7 @@
           <t>Family engagement, attendance and communications platform for districts</t>
         </is>
       </c>
-      <c r="F92" s="33" t="inlineStr">
+      <c r="F92" s="35" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Future Opportun (Remote)</t>
         </is>
@@ -45820,7 +45820,7 @@
           <t>K-12 hiring, applicant tracking and talent matching for districts</t>
         </is>
       </c>
-      <c r="F96" s="35" t="inlineStr">
+      <c r="F96" s="33" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -46388,7 +46388,7 @@
           <t>AI browser extension that generates lesson plans, quizzes, and student feedback inside Google Workspace and LMS tools for teachers and school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F116" s="33" t="inlineStr">
+      <c r="F116" s="35" t="inlineStr">
         <is>
           <t>Yes - Mid-Market Account Executive (Remote)</t>
         </is>
@@ -46612,7 +46612,7 @@
           <t>AI platform for K-12 districts giving teachers lesson and assessment generation tools and students guided AI, with district-level policy and privacy controls - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F124" s="35" t="inlineStr">
+      <c r="F124" s="33" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Senior Customer Success Manager -  only</t>
         </is>
@@ -46778,7 +46778,7 @@
           <t>Browser-delivered virtual computer labs, classroom AI safety controls and work-based learning software for school districts and colleges - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F130" s="33" t="inlineStr">
+      <c r="F130" s="35" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -47086,7 +47086,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/16/26)</t>
+          <t>Hiring AEs? (9/17/26)</t>
         </is>
       </c>
     </row>
@@ -47502,7 +47502,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -49796,7 +49796,7 @@
       </c>
       <c r="F92" s="39" t="inlineStr">
         <is>
-          <t>Yes - Strategic Account Executive (Tennessee_Remote_C)</t>
+          <t>Yes - Strategic Account Executive (North Carolina_Rem)</t>
         </is>
       </c>
     </row>
@@ -52728,7 +52728,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/16/26)</t>
+          <t>Hiring AEs? (9/17/26)</t>
         </is>
       </c>
     </row>
@@ -54438,7 +54438,7 @@
       </c>
       <c r="F58" s="45" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -56258,7 +56258,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/16/26)</t>
+          <t>Hiring AEs? (9/17/26)</t>
         </is>
       </c>
     </row>
@@ -57862,9 +57862,9 @@
           <t>Self-service kiosks, bag drop and passenger processing for airports</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 404 for https://www.embross.com/car</t>
         </is>
       </c>
     </row>
@@ -58554,7 +58554,7 @@
       </c>
       <c r="F78" s="52" t="inlineStr">
         <is>
-          <t>Yes - Account Manager Molecular Diagnost</t>
+          <t>Yes - Sales Account Manager</t>
         </is>
       </c>
     </row>
@@ -59782,7 +59782,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/16/26)</t>
+          <t>Hiring AEs? (9/17/26)</t>
         </is>
       </c>
     </row>
@@ -60298,7 +60298,7 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (Stat (United States)</t>
+          <t>Yes - Enterprise Account Executive (Stat (New York, New York)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/17/26)</t>
+          <t>Hiring AEs? (9/18/26)</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
         </is>
       </c>
     </row>
@@ -3870,9 +3870,9 @@
           <t>OfficerTRAK off-duty detail management: scheduling, billing, insurance - exhibited at NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Business Development Manager - Mid (Charlotte, North C)</t>
         </is>
       </c>
     </row>
@@ -5982,9 +5982,9 @@
           <t>Assistive AI for 911 centers: transcription, translation, text-to-911, and video</t>
         </is>
       </c>
-      <c r="F171" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/17/26)</t>
+          <t>Hiring AEs? (9/18/26)</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/17/26)</t>
+          <t>Hiring AEs? (9/18/26)</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/17/26)</t>
+          <t>Hiring AEs? (9/18/26)</t>
         </is>
       </c>
     </row>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/17/26)</t>
+          <t>Hiring AEs? (9/18/26)</t>
         </is>
       </c>
     </row>
@@ -18878,9 +18878,9 @@
           <t>Traffic data collection and smart intersection technology</t>
         </is>
       </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>Yes - Enterprise Account Executive, Opti (Southeastern USA)</t>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Technical Customer Success Manager only</t>
         </is>
       </c>
     </row>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>Yes - Key Account Manager (Budapest, Hungary)</t>
+          <t>Yes - Executive Sales Representative - N (12 Locations)</t>
         </is>
       </c>
     </row>
@@ -22650,9 +22650,9 @@
           <t>IoT telematics and video safety for government fleets (public co) - exhibited at NLC City Summit 2026, PRIMA 2026, NAFA I&amp;E 2026, NAPT Summit 2026, SWANA WASTECON 2025</t>
         </is>
       </c>
-      <c r="F175" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/17/26)</t>
+          <t>Hiring AEs? (9/18/26)</t>
         </is>
       </c>
     </row>
@@ -31112,9 +31112,9 @@
           <t>Tax collection, auctions and payment processing software for governments - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F221" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive (United States (Rem)</t>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -31856,7 +31856,7 @@
       </c>
       <c r="F246" s="21" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - HTTP 403 for https://passportworkforce.c</t>
         </is>
       </c>
     </row>
@@ -38708,7 +38708,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/17/26)</t>
+          <t>Hiring AEs? (9/18/26)</t>
         </is>
       </c>
     </row>
@@ -39902,7 +39902,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -42054,9 +42054,9 @@
           <t>Short-term rental market data for tourism offices and city agencies</t>
         </is>
       </c>
-      <c r="F113" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive (Barcelona)</t>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sales Manager - Uplisting only</t>
         </is>
       </c>
     </row>
@@ -42990,7 +42990,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/17/26)</t>
+          <t>Hiring AEs? (9/18/26)</t>
         </is>
       </c>
     </row>
@@ -43020,7 +43020,7 @@
       </c>
       <c r="F2" s="33" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Senior Manager, Global Deal Desk only</t>
+          <t>Sales (non-AE) - Director, GTM Finance only</t>
         </is>
       </c>
     </row>
@@ -43050,7 +43050,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>Yes - Sales Executive, Cross-Sell (North (Remote Worker - N/)</t>
+          <t>Yes - Senior Sales Executive (VA/WV/OH) (Remote Worker - N/)</t>
         </is>
       </c>
     </row>
@@ -43880,9 +43880,9 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -44234,7 +44234,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://www.ridezum.com/com</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -47086,7 +47086,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/17/26)</t>
+          <t>Hiring AEs? (9/18/26)</t>
         </is>
       </c>
     </row>
@@ -52728,7 +52728,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/17/26)</t>
+          <t>Hiring AEs? (9/18/26)</t>
         </is>
       </c>
     </row>
@@ -54438,7 +54438,7 @@
       </c>
       <c r="F58" s="45" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - HTTP 504 for https://www.sedata.com/care</t>
         </is>
       </c>
     </row>
@@ -56258,7 +56258,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/17/26)</t>
+          <t>Hiring AEs? (9/18/26)</t>
         </is>
       </c>
     </row>
@@ -57742,9 +57742,9 @@
           <t>Baggage handling systems and terminal logistics for airports</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -57862,9 +57862,9 @@
           <t>Self-service kiosks, bag drop and passenger processing for airports</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - HTTP 404 for https://www.embross.com/car</t>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -57894,7 +57894,7 @@
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -58044,7 +58044,7 @@
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>Yes - Senior Account Executive - West &amp;</t>
+          <t>Yes - Senior Account Executive</t>
         </is>
       </c>
     </row>
@@ -59782,7 +59782,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/17/26)</t>
+          <t>Hiring AEs? (9/18/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/18/26)</t>
+          <t>Hiring AEs? (9/19/26)</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
+          <t>Unknown - HTTP 202 for https://www.365labs.com/car</t>
         </is>
       </c>
     </row>
@@ -3750,9 +3750,9 @@
           <t>Officer performance management and research-based early intervention (First Sign)</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -8018,9 +8018,9 @@
           <t>Intercept and Defender full-body transmission X-ray scanners for jails, courthouses, and borders - exhibited at Michigan Sheriffs Association 2026</t>
         </is>
       </c>
-      <c r="F239" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F239" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/18/26)</t>
+          <t>Hiring AEs? (9/19/26)</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/18/26)</t>
+          <t>Hiring AEs? (9/19/26)</t>
         </is>
       </c>
     </row>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 404 for https://www.kuali.co/about-</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/18/26)</t>
+          <t>Hiring AEs? (9/19/26)</t>
         </is>
       </c>
     </row>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/18/26)</t>
+          <t>Hiring AEs? (9/19/26)</t>
         </is>
       </c>
     </row>
@@ -17672,9 +17672,9 @@
           <t>AI waste-recognition cameras and analytics for sorting plants</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Director of Sales only</t>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -22650,9 +22650,9 @@
           <t>IoT telematics and video safety for government fleets (public co) - exhibited at NLC City Summit 2026, PRIMA 2026, NAFA I&amp;E 2026, NAPT Summit 2026, SWANA WASTECON 2025</t>
         </is>
       </c>
-      <c r="F175" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F175" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -22682,7 +22682,7 @@
       </c>
       <c r="F176" s="16" t="inlineStr">
         <is>
-          <t>Yes - Partner Account Manager UK&amp;I (London, England - )</t>
+          <t>Yes - Business Development Manager - Mob (Denver, Colorado -)</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/18/26)</t>
+          <t>Hiring AEs? (9/19/26)</t>
         </is>
       </c>
     </row>
@@ -24894,7 +24894,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://zencity.io/careers</t>
+          <t>Unknown - HTTP 202 for https://zencity.io/careers</t>
         </is>
       </c>
     </row>
@@ -26918,9 +26918,9 @@
           <t>Community development permitting and licensing software (founded as BasicGov)</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Business Development Representativ only</t>
         </is>
       </c>
     </row>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="F182" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://www.governmentwindo</t>
+          <t>Unknown - HTTP 403 for https://www.governmentwindo</t>
         </is>
       </c>
     </row>
@@ -31856,7 +31856,7 @@
       </c>
       <c r="F246" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://passportworkforce.c</t>
+          <t>Unknown - HTTP 202 for https://passportworkforce.c</t>
         </is>
       </c>
     </row>
@@ -32564,7 +32564,7 @@
       </c>
       <c r="F270" s="23" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Sales Development Representative only</t>
+          <t>Sales (non-AE) - Client Success Manager only</t>
         </is>
       </c>
     </row>
@@ -38708,7 +38708,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/18/26)</t>
+          <t>Hiring AEs? (9/19/26)</t>
         </is>
       </c>
     </row>
@@ -39542,7 +39542,7 @@
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Manager (GameChanger Remote)</t>
+          <t>Yes - Account Executive (GameChanger Remote)</t>
         </is>
       </c>
     </row>
@@ -39902,7 +39902,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -40080,9 +40080,9 @@
           <t>Camp management and registration software for camps including municipal programs</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Customer Success Manager - Mid Mar only</t>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -40260,9 +40260,9 @@
           <t>Campground reservation and management software for public and private campgrounds</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
-        <is>
-          <t>Yes - National Outbound Sales Account Ex</t>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Manager, Account Management only</t>
         </is>
       </c>
     </row>
@@ -42990,7 +42990,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/18/26)</t>
+          <t>Hiring AEs? (9/19/26)</t>
         </is>
       </c>
     </row>
@@ -43168,9 +43168,9 @@
           <t>Device filtering, classroom management, and student wellness (Beacon)</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - New Business Executive - Strategic only</t>
         </is>
       </c>
     </row>
@@ -43260,7 +43260,7 @@
       </c>
       <c r="F10" s="35" t="inlineStr">
         <is>
-          <t>Yes - Account Manager (REMOTE, United Kin)</t>
+          <t>Yes - Account Executive (Austin, Texas, Uni)</t>
         </is>
       </c>
     </row>
@@ -43880,9 +43880,9 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -47086,7 +47086,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/18/26)</t>
+          <t>Hiring AEs? (9/19/26)</t>
         </is>
       </c>
     </row>
@@ -47386,7 +47386,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.modeshift.com/c</t>
+          <t>Unknown - HTTP 202 for https://www.modeshift.com/c</t>
         </is>
       </c>
     </row>
@@ -47982,7 +47982,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.enghouse.com/ca</t>
+          <t>Unknown - HTTP 202 for https://www.enghouse.com/ca</t>
         </is>
       </c>
     </row>
@@ -49796,7 +49796,7 @@
       </c>
       <c r="F92" s="39" t="inlineStr">
         <is>
-          <t>Yes - Strategic Account Executive (North Carolina_Rem)</t>
+          <t>Yes - Strategic Account Executive (Tennessee_Remote_C)</t>
         </is>
       </c>
     </row>
@@ -50036,7 +50036,7 @@
       </c>
       <c r="F100" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.hanoverdisplays</t>
+          <t>Unknown - HTTP 202 for https://www.hanoverdisplays</t>
         </is>
       </c>
     </row>
@@ -50424,7 +50424,7 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://qryde.com/employmen</t>
+          <t>Unknown - HTTP 202 for https://qryde.com/employmen</t>
         </is>
       </c>
     </row>
@@ -52728,7 +52728,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/18/26)</t>
+          <t>Hiring AEs? (9/19/26)</t>
         </is>
       </c>
     </row>
@@ -54438,7 +54438,7 @@
       </c>
       <c r="F58" s="45" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 504 for https://www.sedata.com/care</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -56258,7 +56258,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/18/26)</t>
+          <t>Hiring AEs? (9/19/26)</t>
         </is>
       </c>
     </row>
@@ -56728,9 +56728,9 @@
           <t>Aviation design and simulation software (AviPLAN, AeroTURN, GuideSIGN) used by airport planners for aircraft movement, apron layout and airside safety analysis.</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Customer Success Representative only</t>
         </is>
       </c>
     </row>
@@ -57742,9 +57742,9 @@
           <t>Baggage handling systems and terminal logistics for airports</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -57894,7 +57894,7 @@
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -59782,7 +59782,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/18/26)</t>
+          <t>Hiring AEs? (9/19/26)</t>
         </is>
       </c>
     </row>
@@ -60298,7 +60298,7 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (Stat (New York, New York)</t>
+          <t>Yes - Enterprise Account Executive (Stat (United States)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/19/26)</t>
+          <t>Hiring AEs? (9/20/26)</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.365labs.com/car</t>
+          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/19/26)</t>
+          <t>Hiring AEs? (9/20/26)</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/19/26)</t>
+          <t>Hiring AEs? (9/20/26)</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/19/26)</t>
+          <t>Hiring AEs? (9/20/26)</t>
         </is>
       </c>
     </row>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/19/26)</t>
+          <t>Hiring AEs? (9/20/26)</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/19/26)</t>
+          <t>Hiring AEs? (9/20/26)</t>
         </is>
       </c>
     </row>
@@ -24894,7 +24894,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://zencity.io/careers</t>
+          <t>Unknown - HTTP 403 for https://zencity.io/careers</t>
         </is>
       </c>
     </row>
@@ -31856,7 +31856,7 @@
       </c>
       <c r="F246" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://passportworkforce.c</t>
+          <t>Unknown - HTTP 403 for https://passportworkforce.c</t>
         </is>
       </c>
     </row>
@@ -34354,7 +34354,7 @@
       </c>
       <c r="F332" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -38708,7 +38708,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/19/26)</t>
+          <t>Hiring AEs? (9/20/26)</t>
         </is>
       </c>
     </row>
@@ -42990,7 +42990,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/19/26)</t>
+          <t>Hiring AEs? (9/20/26)</t>
         </is>
       </c>
     </row>
@@ -47086,7 +47086,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/19/26)</t>
+          <t>Hiring AEs? (9/20/26)</t>
         </is>
       </c>
     </row>
@@ -47386,7 +47386,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.modeshift.com/c</t>
+          <t>Unknown - HTTP 403 for https://www.modeshift.com/c</t>
         </is>
       </c>
     </row>
@@ -47982,7 +47982,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.enghouse.com/ca</t>
+          <t>Unknown - HTTP 403 for https://www.enghouse.com/ca</t>
         </is>
       </c>
     </row>
@@ -50036,7 +50036,7 @@
       </c>
       <c r="F100" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.hanoverdisplays</t>
+          <t>Unknown - HTTP 403 for https://www.hanoverdisplays</t>
         </is>
       </c>
     </row>
@@ -50424,7 +50424,7 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://qryde.com/employmen</t>
+          <t>Unknown - HTTP 403 for https://qryde.com/employmen</t>
         </is>
       </c>
     </row>
@@ -52728,7 +52728,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/19/26)</t>
+          <t>Hiring AEs? (9/20/26)</t>
         </is>
       </c>
     </row>
@@ -56258,7 +56258,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/19/26)</t>
+          <t>Hiring AEs? (9/20/26)</t>
         </is>
       </c>
     </row>
@@ -59782,7 +59782,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/19/26)</t>
+          <t>Hiring AEs? (9/20/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Parks &amp; Rec'!$A$1:$F$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'K-12 Schools'!$A$1:$F$139</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Transit &amp; Parking'!$A$1:$F$192</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Utilities &amp; Energy'!$A$1:$F$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Utilities &amp; Energy'!$A$1:$F$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Airports &amp; Aviation'!$A$1:$F$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Courts &amp; Justice'!$A$1:$F$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Health &amp; Human Services'!$A$1:$F$117</definedName>
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/20/26)</t>
+          <t>Hiring AEs? (9/21/26)</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 504 for https://leotechnologies.com</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/20/26)</t>
+          <t>Hiring AEs? (9/21/26)</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/20/26)</t>
+          <t>Hiring AEs? (9/21/26)</t>
         </is>
       </c>
     </row>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://www.kuali.co/about-</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/20/26)</t>
+          <t>Hiring AEs? (9/21/26)</t>
         </is>
       </c>
     </row>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/20/26)</t>
+          <t>Hiring AEs? (9/21/26)</t>
         </is>
       </c>
     </row>
@@ -19628,9 +19628,9 @@
           <t>AI cameras detecting phone use, seatbelt, and speed violations for road authorities</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Sales Executive - Automated Speed</t>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/20/26)</t>
+          <t>Hiring AEs? (9/21/26)</t>
         </is>
       </c>
     </row>
@@ -28264,9 +28264,9 @@
           <t>Procurement, budgeting, and grants suite - Bonfire, Questica, eCivis (formerly GTY) - exhibited at NACUBO 2026, GFOA 2026</t>
         </is>
       </c>
-      <c r="F125" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Solutions Consultant only</t>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="F182" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.governmentwindo</t>
+          <t>Unknown - HTTP 404 for https://www.governmentwindo</t>
         </is>
       </c>
     </row>
@@ -34354,7 +34354,7 @@
       </c>
       <c r="F332" s="21" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -38708,7 +38708,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/20/26)</t>
+          <t>Hiring AEs? (9/21/26)</t>
         </is>
       </c>
     </row>
@@ -42990,7 +42990,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/20/26)</t>
+          <t>Hiring AEs? (9/21/26)</t>
         </is>
       </c>
     </row>
@@ -47086,7 +47086,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/20/26)</t>
+          <t>Hiring AEs? (9/21/26)</t>
         </is>
       </c>
     </row>
@@ -49796,7 +49796,7 @@
       </c>
       <c r="F92" s="39" t="inlineStr">
         <is>
-          <t>Yes - Strategic Account Executive (Tennessee_Remote_C)</t>
+          <t>Yes - Strategic Account Executive (North Carolina_Rem)</t>
         </is>
       </c>
     </row>
@@ -51726,7 +51726,7 @@
       </c>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>Yes - Junior B2B Account Executive (Prague)</t>
+          <t>Yes - Account Manager (Helsinki)</t>
         </is>
       </c>
     </row>
@@ -52689,7 +52689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -52728,7 +52728,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/20/26)</t>
+          <t>Hiring AEs? (9/21/26)</t>
         </is>
       </c>
     </row>
@@ -55369,46 +55369,44 @@
     <row r="90">
       <c r="A90" s="43" t="inlineStr">
         <is>
-          <t>Cayenta</t>
+          <t>Heron Power</t>
         </is>
       </c>
       <c r="B90" s="43" t="inlineStr">
         <is>
-          <t>Burnaby, Canada</t>
-        </is>
-      </c>
-      <c r="C90" s="44" t="n">
-        <v>1983</v>
-      </c>
+          <t>Scotts Valley, CA</t>
+        </is>
+      </c>
+      <c r="C90" s="44" t="n"/>
       <c r="D90" s="43" t="inlineStr">
         <is>
-          <t>Billing &amp; Customer Systems</t>
+          <t>Grid &amp; Energy</t>
         </is>
       </c>
       <c r="E90" s="43" t="inlineStr">
         <is>
-          <t>Customer information, billing, financials, and work management software for municipal, cooperative, and investor-owned electric, water, gas, and fiber utilities - exhibited at AWWA ACE 2026</t>
-        </is>
-      </c>
-      <c r="F90" s="45" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Solid-state transformers and grid power electronics, sold to data centre and solar-plus-storage developers</t>
+        </is>
+      </c>
+      <c r="F90" s="47" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Head of Sales only</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Silverblaze</t>
+          <t>Cayenta</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Richmond Hill, Canada</t>
+          <t>Burnaby, Canada</t>
         </is>
       </c>
       <c r="C91" s="6" t="n">
-        <v>1999</v>
+        <v>1983</v>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
@@ -55417,7 +55415,7 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Customer self-service portals, mobile apps, and smart meter analytics for electric, water, gas, and multi-service utilities - exhibited at AWWA ACE 2026</t>
+          <t>Customer information, billing, financials, and work management software for municipal, cooperative, and investor-owned electric, water, gas, and fiber utilities - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
@@ -55429,46 +55427,46 @@
     <row r="92">
       <c r="A92" s="43" t="inlineStr">
         <is>
-          <t>Sitetracker</t>
+          <t>Silverblaze</t>
         </is>
       </c>
       <c r="B92" s="43" t="inlineStr">
         <is>
-          <t>Montclair, NJ</t>
+          <t>Richmond Hill, Canada</t>
         </is>
       </c>
       <c r="C92" s="44" t="n">
-        <v>2013</v>
+        <v>1999</v>
       </c>
       <c r="D92" s="43" t="inlineStr">
         <is>
-          <t>Broadband &amp; Connectivity</t>
+          <t>Billing &amp; Customer Systems</t>
         </is>
       </c>
       <c r="E92" s="43" t="inlineStr">
         <is>
-          <t>SaaS deployment, project, and asset lifecycle management for infrastructure programs; sold to agencies via Carahsoft (SEWP V, NASPO)</t>
+          <t>Customer self-service portals, mobile apps, and smart meter analytics for electric, water, gas, and multi-service utilities - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F92" s="45" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>AirWorks</t>
+          <t>Sitetracker</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Montclair, NJ</t>
         </is>
       </c>
       <c r="C93" s="6" t="n">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
@@ -55477,28 +55475,28 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>AI converting aerial and lidar data into CAD basemaps and site plans; on SEWP V, NCPA, OMNIA contracts</t>
+          <t>SaaS deployment, project, and asset lifecycle management for infrastructure programs; sold to agencies via Carahsoft (SEWP V, NASPO)</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="43" t="inlineStr">
         <is>
-          <t>Calix</t>
+          <t>AirWorks</t>
         </is>
       </c>
       <c r="B94" s="43" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="C94" s="44" t="n">
-        <v>1999</v>
+        <v>2017</v>
       </c>
       <c r="D94" s="43" t="inlineStr">
         <is>
@@ -55507,28 +55505,28 @@
       </c>
       <c r="E94" s="43" t="inlineStr">
         <is>
-          <t>Broadband access platform and cloud software with a dedicated municipal and public-power utility segment</t>
+          <t>AI converting aerial and lidar data into CAD basemaps and site plans; on SEWP V, NCPA, OMNIA contracts</t>
         </is>
       </c>
       <c r="F94" s="45" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>VETRO</t>
+          <t>Calix</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Portland, Maine</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="C95" s="6" t="n">
-        <v>2015</v>
+        <v>1999</v>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
@@ -55537,28 +55535,28 @@
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Fiber network mapping and design platform for municipal ISPs and broadband offices</t>
-        </is>
-      </c>
-      <c r="F95" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Enterprise Account Executive (Portland, ME)</t>
+          <t>Broadband access platform and cloud software with a dedicated municipal and public-power utility segment</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="43" t="inlineStr">
         <is>
-          <t>IQGeo</t>
+          <t>VETRO</t>
         </is>
       </c>
       <c r="B96" s="43" t="inlineStr">
         <is>
-          <t>Cambridge, United Kingdom</t>
+          <t>Portland, Maine</t>
         </is>
       </c>
       <c r="C96" s="44" t="n">
-        <v>2002</v>
+        <v>2015</v>
       </c>
       <c r="D96" s="43" t="inlineStr">
         <is>
@@ -55567,28 +55565,28 @@
       </c>
       <c r="E96" s="43" t="inlineStr">
         <is>
-          <t>Geospatial network design and field software for telecom and public utilities</t>
-        </is>
-      </c>
-      <c r="F96" s="47" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Sales Engineer only</t>
+          <t>Fiber network mapping and design platform for municipal ISPs and broadband offices</t>
+        </is>
+      </c>
+      <c r="F96" s="46" t="inlineStr">
+        <is>
+          <t>Yes - Enterprise Account Executive (Portland, ME)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Render Networks</t>
+          <t>IQGeo</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Melbourne, Australia</t>
+          <t>Cambridge, United Kingdom</t>
         </is>
       </c>
       <c r="C97" s="6" t="n">
-        <v>2015</v>
+        <v>2002</v>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
@@ -55597,28 +55595,28 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Geospatial fiber construction management for network builders and public programs</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Geospatial network design and field software for telecom and public utilities</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sales Engineer only</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="43" t="inlineStr">
         <is>
-          <t>CostQuest Associates</t>
+          <t>Render Networks</t>
         </is>
       </c>
       <c r="B98" s="43" t="inlineStr">
         <is>
-          <t>Cincinnati, Ohio</t>
+          <t>Melbourne, Australia</t>
         </is>
       </c>
       <c r="C98" s="44" t="n">
-        <v>2002</v>
+        <v>2015</v>
       </c>
       <c r="D98" s="43" t="inlineStr">
         <is>
@@ -55627,7 +55625,7 @@
       </c>
       <c r="E98" s="43" t="inlineStr">
         <is>
-          <t>Broadband serviceable location fabric and cost models for NTIA and states</t>
+          <t>Geospatial fiber construction management for network builders and public programs</t>
         </is>
       </c>
       <c r="F98" s="45" t="inlineStr">
@@ -55639,16 +55637,16 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Ookla</t>
+          <t>CostQuest Associates</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Seattle, Washington</t>
+          <t>Cincinnati, Ohio</t>
         </is>
       </c>
       <c r="C99" s="6" t="n">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
@@ -55657,28 +55655,28 @@
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Speed test and broadband coverage data licensed to broadband offices and regulators</t>
-        </is>
-      </c>
-      <c r="F99" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Broadband serviceable location fabric and cost models for NTIA and states</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="43" t="inlineStr">
         <is>
-          <t>Ready.net</t>
+          <t>Ookla</t>
         </is>
       </c>
       <c r="B100" s="43" t="inlineStr">
         <is>
-          <t>San Francisco, California</t>
+          <t>Seattle, Washington</t>
         </is>
       </c>
       <c r="C100" s="44" t="n">
-        <v>2020</v>
+        <v>2006</v>
       </c>
       <c r="D100" s="43" t="inlineStr">
         <is>
@@ -55687,28 +55685,28 @@
       </c>
       <c r="E100" s="43" t="inlineStr">
         <is>
-          <t>Broadband grant, challenge process and mapping software for state broadband offices</t>
-        </is>
-      </c>
-      <c r="F100" s="47" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Product Solutions Engineer only</t>
+          <t>Speed test and broadband coverage data licensed to broadband offices and regulators</t>
+        </is>
+      </c>
+      <c r="F100" s="46" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Adtran</t>
+          <t>Ready.net</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Huntsville, Alabama</t>
+          <t>San Francisco, California</t>
         </is>
       </c>
       <c r="C101" s="6" t="n">
-        <v>1985</v>
+        <v>2020</v>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
@@ -55717,28 +55715,28 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Fiber access and broadband network equipment for municipal and rural providers</t>
-        </is>
-      </c>
-      <c r="F101" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Sales Director NSP (2 Locations)</t>
+          <t>Broadband grant, challenge process and mapping software for state broadband offices</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Product Solutions Engineer only</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="43" t="inlineStr">
         <is>
-          <t>DZS</t>
+          <t>Adtran</t>
         </is>
       </c>
       <c r="B102" s="43" t="inlineStr">
         <is>
-          <t>Plano, Texas</t>
+          <t>Huntsville, Alabama</t>
         </is>
       </c>
       <c r="C102" s="44" t="n">
-        <v>1999</v>
+        <v>1985</v>
       </c>
       <c r="D102" s="43" t="inlineStr">
         <is>
@@ -55747,27 +55745,29 @@
       </c>
       <c r="E102" s="43" t="inlineStr">
         <is>
-          <t>Broadband access platforms for municipal utilities and public network operators</t>
-        </is>
-      </c>
-      <c r="F102" s="45" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Fiber access and broadband network equipment for municipal and rural providers</t>
+        </is>
+      </c>
+      <c r="F102" s="46" t="inlineStr">
+        <is>
+          <t>Yes - Sales Director NSP (2 Locations)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Clearfield</t>
+          <t>DZS</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Brooklyn Park, Minnesota</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="n"/>
+          <t>Plano, Texas</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>1999</v>
+      </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
           <t>Broadband &amp; Connectivity</t>
@@ -55775,7 +55775,7 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Fiber management and connectivity products for municipal and community broadband</t>
+          <t>Broadband access platforms for municipal utilities and public network operators</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
@@ -55787,17 +55787,15 @@
     <row r="104">
       <c r="A104" s="43" t="inlineStr">
         <is>
-          <t>Cambium Networks</t>
+          <t>Clearfield</t>
         </is>
       </c>
       <c r="B104" s="43" t="inlineStr">
         <is>
-          <t>Rolling Meadows, Illinois</t>
-        </is>
-      </c>
-      <c r="C104" s="44" t="n">
-        <v>2011</v>
-      </c>
+          <t>Brooklyn Park, Minnesota</t>
+        </is>
+      </c>
+      <c r="C104" s="44" t="n"/>
       <c r="D104" s="43" t="inlineStr">
         <is>
           <t>Broadband &amp; Connectivity</t>
@@ -55805,28 +55803,28 @@
       </c>
       <c r="E104" s="43" t="inlineStr">
         <is>
-          <t>Fixed wireless and Wi-Fi networks for cities, schools and public agencies</t>
+          <t>Fiber management and connectivity products for municipal and community broadband</t>
         </is>
       </c>
       <c r="F104" s="45" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Tarana Wireless</t>
+          <t>Cambium Networks</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Milpitas, California</t>
+          <t>Rolling Meadows, Illinois</t>
         </is>
       </c>
       <c r="C105" s="6" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
@@ -55835,28 +55833,28 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Next-gen fixed wireless access gear for municipal and rural broadband projects</t>
+          <t>Fixed wireless and Wi-Fi networks for cities, schools and public agencies</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="43" t="inlineStr">
         <is>
-          <t>Katapult Engineering</t>
+          <t>Tarana Wireless</t>
         </is>
       </c>
       <c r="B106" s="43" t="inlineStr">
         <is>
-          <t>Harrisburg, Pennsylvania</t>
+          <t>Milpitas, California</t>
         </is>
       </c>
       <c r="C106" s="44" t="n">
-        <v>1991</v>
+        <v>2009</v>
       </c>
       <c r="D106" s="43" t="inlineStr">
         <is>
@@ -55865,27 +55863,29 @@
       </c>
       <c r="E106" s="43" t="inlineStr">
         <is>
-          <t>Pole attachment and make-ready survey software for utilities and broadband builds</t>
+          <t>Next-gen fixed wireless access gear for municipal and rural broadband projects</t>
         </is>
       </c>
       <c r="F106" s="45" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>ikeGPS</t>
+          <t>Katapult Engineering</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Wellington, New Zealand</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="n"/>
+          <t>Harrisburg, Pennsylvania</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="n">
+        <v>1991</v>
+      </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
           <t>Broadband &amp; Connectivity</t>
@@ -55893,29 +55893,27 @@
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>Pole measurement and joint-use data software for utilities and network builders</t>
+          <t>Pole attachment and make-ready survey software for utilities and broadband builds</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://ikegps.com/open-pos</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="43" t="inlineStr">
         <is>
-          <t>Alden Systems</t>
+          <t>ikeGPS</t>
         </is>
       </c>
       <c r="B108" s="43" t="inlineStr">
         <is>
-          <t>Birmingham, Alabama</t>
-        </is>
-      </c>
-      <c r="C108" s="44" t="n">
-        <v>1995</v>
-      </c>
+          <t>Wellington, New Zealand</t>
+        </is>
+      </c>
+      <c r="C108" s="44" t="n"/>
       <c r="D108" s="43" t="inlineStr">
         <is>
           <t>Broadband &amp; Connectivity</t>
@@ -55923,28 +55921,28 @@
       </c>
       <c r="E108" s="43" t="inlineStr">
         <is>
-          <t>Joint use pole asset and attachment management for utilities and municipalities</t>
+          <t>Pole measurement and joint-use data software for utilities and network builders</t>
         </is>
       </c>
       <c r="F108" s="45" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 404 for https://ikegps.com/open-pos</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>3-GIS</t>
+          <t>Alden Systems</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Decatur, Alabama</t>
+          <t>Birmingham, Alabama</t>
         </is>
       </c>
       <c r="C109" s="6" t="n">
-        <v>2005</v>
+        <v>1995</v>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
@@ -55953,7 +55951,7 @@
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>Fiber network design and asset management for public and municipal broadband</t>
+          <t>Joint use pole asset and attachment management for utilities and municipalities</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
@@ -55965,16 +55963,16 @@
     <row r="110">
       <c r="A110" s="43" t="inlineStr">
         <is>
-          <t>Biarri Networks</t>
+          <t>3-GIS</t>
         </is>
       </c>
       <c r="B110" s="43" t="inlineStr">
         <is>
-          <t>Melbourne, Australia</t>
+          <t>Decatur, Alabama</t>
         </is>
       </c>
       <c r="C110" s="44" t="n">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="D110" s="43" t="inlineStr">
         <is>
@@ -55983,7 +55981,7 @@
       </c>
       <c r="E110" s="43" t="inlineStr">
         <is>
-          <t>Automated fiber network design software for broadband programs and operators</t>
+          <t>Fiber network design and asset management for public and municipal broadband</t>
         </is>
       </c>
       <c r="F110" s="45" t="inlineStr">
@@ -55995,15 +55993,17 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Comsof</t>
+          <t>Biarri Networks</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Ghent, Belgium</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="n"/>
+          <t>Melbourne, Australia</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="n">
+        <v>2009</v>
+      </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
           <t>Broadband &amp; Connectivity</t>
@@ -56011,29 +56011,27 @@
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>Fiber and utility network planning software for public broadband deployments</t>
+          <t>Automated fiber network design software for broadband programs and operators</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="43" t="inlineStr">
         <is>
-          <t>Vitruvi Software</t>
+          <t>Comsof</t>
         </is>
       </c>
       <c r="B112" s="43" t="inlineStr">
         <is>
-          <t>Kelowna, Canada</t>
-        </is>
-      </c>
-      <c r="C112" s="44" t="n">
-        <v>2016</v>
-      </c>
+          <t>Ghent, Belgium</t>
+        </is>
+      </c>
+      <c r="C112" s="44" t="n"/>
       <c r="D112" s="43" t="inlineStr">
         <is>
           <t>Broadband &amp; Connectivity</t>
@@ -56041,7 +56039,7 @@
       </c>
       <c r="E112" s="43" t="inlineStr">
         <is>
-          <t>Construction management platform for fiber and municipal infrastructure builds</t>
+          <t>Fiber and utility network planning software for public broadband deployments</t>
         </is>
       </c>
       <c r="F112" s="45" t="inlineStr">
@@ -56053,16 +56051,16 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>OSPInsight</t>
+          <t>Vitruvi Software</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Salt Lake City, Utah</t>
+          <t>Kelowna, Canada</t>
         </is>
       </c>
       <c r="C113" s="6" t="n">
-        <v>1996</v>
+        <v>2016</v>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
@@ -56071,7 +56069,7 @@
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>Outside plant fiber management software for municipal utilities and ISPs</t>
+          <t>Construction management platform for fiber and municipal infrastructure builds</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
@@ -56083,16 +56081,16 @@
     <row r="114">
       <c r="A114" s="43" t="inlineStr">
         <is>
-          <t>Federated Wireless</t>
+          <t>OSPInsight</t>
         </is>
       </c>
       <c r="B114" s="43" t="inlineStr">
         <is>
-          <t>Arlington, Virginia</t>
+          <t>Salt Lake City, Utah</t>
         </is>
       </c>
       <c r="C114" s="44" t="n">
-        <v>2012</v>
+        <v>1996</v>
       </c>
       <c r="D114" s="43" t="inlineStr">
         <is>
@@ -56101,7 +56099,7 @@
       </c>
       <c r="E114" s="43" t="inlineStr">
         <is>
-          <t>CBRS shared spectrum services for municipal and public agency networks</t>
+          <t>Outside plant fiber management software for municipal utilities and ISPs</t>
         </is>
       </c>
       <c r="F114" s="45" t="inlineStr">
@@ -56113,16 +56111,16 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Celona</t>
+          <t>Federated Wireless</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>San Jose, California</t>
+          <t>Arlington, Virginia</t>
         </is>
       </c>
       <c r="C115" s="6" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
@@ -56131,28 +56129,28 @@
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>Private 5G/LTE networks for government agencies, campuses and utilities</t>
+          <t>CBRS shared spectrum services for municipal and public agency networks</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="43" t="inlineStr">
         <is>
-          <t>SiFi Networks</t>
+          <t>Celona</t>
         </is>
       </c>
       <c r="B116" s="43" t="inlineStr">
         <is>
-          <t>Fullerton, California</t>
+          <t>San Jose, California</t>
         </is>
       </c>
       <c r="C116" s="44" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="D116" s="43" t="inlineStr">
         <is>
@@ -56161,47 +56159,77 @@
       </c>
       <c r="E116" s="43" t="inlineStr">
         <is>
-          <t>Privately funded citywide open-access fiber built in partnership with municipalities</t>
+          <t>Private 5G/LTE networks for government agencies, campuses and utilities</t>
         </is>
       </c>
       <c r="F116" s="45" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
+          <t>SiFi Networks</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Fullerton, California</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>Broadband &amp; Connectivity</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>Privately funded citywide open-access fiber built in partnership with municipalities</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="43" t="inlineStr">
+        <is>
           <t>Boldyn Networks</t>
         </is>
       </c>
-      <c r="B117" s="5" t="inlineStr">
+      <c r="B118" s="43" t="inlineStr">
         <is>
           <t>New York, New York</t>
         </is>
       </c>
-      <c r="C117" s="6" t="n">
+      <c r="C118" s="44" t="n">
         <v>2023</v>
       </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="D118" s="43" t="inlineStr">
         <is>
           <t>Broadband &amp; Connectivity</t>
         </is>
       </c>
-      <c r="E117" s="5" t="inlineStr">
+      <c r="E118" s="43" t="inlineStr">
         <is>
           <t>Neutral-host wireless and fiber networks for transit authorities and cities - exhibited at NACUBO 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F117" s="7" t="inlineStr">
+      <c r="F118" s="45" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F117"/>
+  <autoFilter ref="A1:F118"/>
   <dataValidations count="1">
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid category" error="Pick one of: Street Lighting &amp; Poles, Grid &amp; Energy, Suppliers &amp; Services, Billing &amp; Customer Systems, Broadband &amp; Connectivity" type="list">
       <formula1>"Street Lighting &amp; Poles,Grid &amp; Energy,Suppliers &amp; Services,Billing &amp; Customer Systems,Broadband &amp; Connectivity"</formula1>
@@ -56258,7 +56286,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/20/26)</t>
+          <t>Hiring AEs? (9/21/26)</t>
         </is>
       </c>
     </row>
@@ -56728,9 +56756,9 @@
           <t>Aviation design and simulation software (AviPLAN, AeroTURN, GuideSIGN) used by airport planners for aircraft movement, apron layout and airside safety analysis.</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Customer Success Representative only</t>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Account Manager (Sales)</t>
         </is>
       </c>
     </row>
@@ -59782,7 +59810,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/20/26)</t>
+          <t>Hiring AEs? (9/21/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -246,9 +246,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/21/26)</t>
+          <t>Hiring AEs? (9/22/26)</t>
         </is>
       </c>
     </row>
@@ -1120,9 +1120,9 @@
           <t>Wildfire spread modeling and risk analytics used by CAL FIRE and major utilities</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Sr. Manager, FP&amp;A &amp; Sales Operatio only</t>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
           <t>Exterior retardant/foam systems and app-based wildfire defense for homes and HOAs</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>Yes - Territory Manager - LA (Los Angeles, CA)</t>
         </is>
@@ -1330,7 +1330,7 @@
           <t>Actively tethered situational awareness drones with unlimited flight time for fire/PS</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Engineer only</t>
         </is>
@@ -1414,7 +1414,7 @@
           <t>Cloud fire and EMS records management for departments of all sizes</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -1650,7 +1650,7 @@
           <t>Satellite vegetation intelligence for wildfire risk at utilities and agencies</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive, Cana (Remote, Canada)</t>
         </is>
@@ -2070,7 +2070,7 @@
           <t>License plate readers, gunshot detection, and drone-as-first-responder (Aerodome)</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Senior Deal Desk Analyst only</t>
         </is>
@@ -2130,7 +2130,7 @@
           <t>911-response and tactical drones staged on police and fire station rooftops</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, DFR (Remote (Select Sta)</t>
         </is>
@@ -2190,7 +2190,7 @@
           <t>Data integration and real-time intelligence platform for police and city agencies - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr">
         <is>
           <t>Yes - Federal Account Executive (Washington, D.C.)</t>
         </is>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
           <t>Incident reporting and case management for law enforcement, campus, and healthcare security</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -2670,7 +2670,7 @@
           <t>AI audio/video/document redaction (CaseGuard Studio) for police, courts, and gov</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F59" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Arlington, VA)</t>
         </is>
@@ -2940,7 +2940,7 @@
           <t>Digital investigation suite for cleansing and evidencing comms data (UK + US LE)</t>
         </is>
       </c>
-      <c r="F68" s="11" t="inlineStr">
+      <c r="F68" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -2970,7 +2970,7 @@
           <t>Investigation database: pawn/secondhand transactions plus ballistics ID for agencies - exhibited at Michigan Sheriffs Association 2026</t>
         </is>
       </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="F69" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -3090,7 +3090,7 @@
           <t>Cloud cameras, access control, and sensors with a dedicated SLED sales org - exhibited at EDUCAUSE 2026, Maryland Municipal League 2026</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="F73" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, France (London)</t>
         </is>
@@ -3330,7 +3330,7 @@
           <t>Drone-as-first-responder software and hardware auto-launching to 911 calls</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F81" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive</t>
         </is>
@@ -3570,7 +3570,7 @@
           <t>Bird and drone detection radars (ELVIRA, IRIS) for airports, security, and C-UAS</t>
         </is>
       </c>
-      <c r="F89" s="10" t="inlineStr">
+      <c r="F89" s="9" t="inlineStr">
         <is>
           <t>Yes - Regional Account Manager - Nordics (Nordics)</t>
         </is>
@@ -3720,7 +3720,7 @@
           <t>Training LMS, scheduling, and readiness software (TargetSolutions, Guardian Tracking) - exhibited at IAFC FRI 2026, APCO 2026</t>
         </is>
       </c>
-      <c r="F94" s="11" t="inlineStr">
+      <c r="F94" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -3810,7 +3810,7 @@
           <t>Scheduling and workforce management for police, corrections, and 911</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -3870,7 +3870,7 @@
           <t>OfficerTRAK off-duty detail management: scheduling, billing, insurance - exhibited at NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F99" s="10" t="inlineStr">
+      <c r="F99" s="9" t="inlineStr">
         <is>
           <t>Yes - Business Development Manager - Mid (Charlotte, North C)</t>
         </is>
@@ -3930,7 +3930,7 @@
           <t>Online application and recruiting platform for police and civil service hiring</t>
         </is>
       </c>
-      <c r="F101" s="9" t="inlineStr">
+      <c r="F101" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -4350,7 +4350,7 @@
           <t>Cyber-over-RF counter-drone detect, track, and mitigate systems for LE, prisons, and infrastructure</t>
         </is>
       </c>
-      <c r="F115" s="10" t="inlineStr">
+      <c r="F115" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -4738,7 +4738,7 @@
           <t>Retail crime intelligence and reporting platform - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F129" s="10" t="inlineStr">
+      <c r="F129" s="9" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Manager (Biling (Remote - United St)</t>
         </is>
@@ -4788,7 +4788,7 @@
           <t>Software for first responder agencies - exhibited at IACP 2026, APCO 2026</t>
         </is>
       </c>
-      <c r="F131" s="10" t="inlineStr">
+      <c r="F131" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (United States)</t>
         </is>
@@ -4842,7 +4842,7 @@
           <t>AI investigations platform for law enforcement - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F133" s="10" t="inlineStr">
+      <c r="F133" s="9" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive</t>
         </is>
@@ -5382,7 +5382,7 @@
           <t>FBI-certified mobile fingerprint scanners for police and government</t>
         </is>
       </c>
-      <c r="F151" s="9" t="inlineStr">
+      <c r="F151" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -5412,7 +5412,7 @@
           <t>Data integration and investigative analytics for police and government</t>
         </is>
       </c>
-      <c r="F152" s="11" t="inlineStr">
+      <c r="F152" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Forward Deployed Enablement Engine only</t>
         </is>
@@ -5862,7 +5862,7 @@
           <t>ePCR, records, and analytics connecting EMS, fire, and hospitals - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
-      <c r="F167" s="10" t="inlineStr">
+      <c r="F167" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Remote, US (TN/KY))</t>
         </is>
@@ -5922,7 +5922,7 @@
           <t>Intelligent 911 platform streaming device location and data to dispatch - exhibited at APCO 2026</t>
         </is>
       </c>
-      <c r="F169" s="9" t="inlineStr">
+      <c r="F169" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Director, Customer Solutions Engin only</t>
         </is>
@@ -5982,9 +5982,9 @@
           <t>Assistive AI for 911 centers: transcription, translation, text-to-911, and video</t>
         </is>
       </c>
-      <c r="F171" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F171" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
           <t>Pediatric emergency dosing system and app for EMS agencies</t>
         </is>
       </c>
-      <c r="F181" s="10" t="inlineStr">
+      <c r="F181" s="9" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive</t>
         </is>
@@ -6402,7 +6402,7 @@
           <t>Mobile incident command and response for fire/EMS departments - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
-      <c r="F185" s="10" t="inlineStr">
+      <c r="F185" s="9" t="inlineStr">
         <is>
           <t>Yes - Regional Account Executive</t>
         </is>
@@ -6582,7 +6582,7 @@
           <t>911 call routing, Viper call handling and NG911 for PSAPs</t>
         </is>
       </c>
-      <c r="F191" s="10" t="inlineStr">
+      <c r="F191" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -6702,7 +6702,7 @@
           <t>AI triage and quality assurance for emergency dispatch centers</t>
         </is>
       </c>
-      <c r="F195" s="9" t="inlineStr">
+      <c r="F195" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - GTM Engineer only</t>
         </is>
@@ -6968,7 +6968,7 @@
           <t>SARA situational awareness and mass notification for schools, senior living, and gov facilities</t>
         </is>
       </c>
-      <c r="F204" s="11" t="inlineStr">
+      <c r="F204" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -7538,7 +7538,7 @@
           <t>CID Net inmate calling (450+ facilities), facility monitoring, and family apps</t>
         </is>
       </c>
-      <c r="F223" s="9" t="inlineStr">
+      <c r="F223" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 504 for https://leotechnologies.com</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8636,7 @@
           <t>Data and case-management tools for state corrections and supervision agencies</t>
         </is>
       </c>
-      <c r="F260" s="11" t="inlineStr">
+      <c r="F260" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - State Partnerships Manager only</t>
         </is>
@@ -9458,9 +9458,9 @@
           <t>Digital forensics and investigation management software - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F289" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F289" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sales Operations &amp; GTM Systems Man only</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9584,7 @@
           <t>AI police report writing and investigation software - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F294" s="11" t="inlineStr">
+      <c r="F294" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -10660,7 +10660,7 @@
           <t>DigiTICKET electronic citation software - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F338" s="11" t="inlineStr">
+      <c r="F338" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/21/26)</t>
+          <t>Hiring AEs? (9/22/26)</t>
         </is>
       </c>
     </row>
@@ -11488,7 +11488,7 @@
       </c>
       <c r="F14" s="64" t="inlineStr">
         <is>
-          <t>Yes - Strategic Account Executive, Marke (Remote – United St)</t>
+          <t>Yes - Commercial Account Executive (Remote – United St)</t>
         </is>
       </c>
     </row>
@@ -12424,7 +12424,7 @@
           <t>Care coordination and PDMP network software (PMP AWARxE, OpenBeds) for states, counties, and health systems (Appriss lineage)</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F47" s="9" t="inlineStr">
         <is>
           <t>Yes - Bamboo Bridge Strategic Account Ma</t>
         </is>
@@ -12766,9 +12766,9 @@
           <t>Digital substance use disorder prevention, intervention, and recovery support platform for treatment providers, state and county health agencies, drug courts, and Medicaid plans - exhibited at NatCon 2026, NACCHO 360 2026</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Sales Director, Public Sector &amp; Pr (US)</t>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Senior Customer Success Consultant only</t>
         </is>
       </c>
     </row>
@@ -12982,7 +12982,7 @@
           <t>Human services EHR and care coordination software for behavioral health, residential, vocational rehab, and food assistance providers - exhibited at NatCon 2026</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
@@ -13192,7 +13192,7 @@
           <t>AI clinical documentation and chart auditing platform purpose-built for behavioral health providers including CCBHCs and human services organizations - exhibited at NatCon 2026</t>
         </is>
       </c>
-      <c r="F75" s="9" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - VP of Revenue only</t>
         </is>
@@ -13246,7 +13246,7 @@
           <t>Accredited continuing-education, AI practice simulation and certification platform for behavioral health clinicians and the organizations that employ them - exhibited at NatCon 2026</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="F77" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -13610,7 +13610,7 @@
           <t>Social care coordination network connecting health and social service referrals for govs and payers - exhibited at MESC 2026</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>Yes - Strategic Sales Director (United States)</t>
         </is>
@@ -13730,7 +13730,7 @@
           <t>Clarity HMIS and homelessness response systems for counties and CoCs</t>
         </is>
       </c>
-      <c r="F95" s="9" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Solutions Consultant only</t>
         </is>
@@ -14018,7 +14018,7 @@
           <t>EHR and case management software for PACE programs, State Units on Aging, Area Agencies on Aging and community-based aging services organizations - exhibited at USAging 2026</t>
         </is>
       </c>
-      <c r="F105" s="10" t="inlineStr">
+      <c r="F105" s="9" t="inlineStr">
         <is>
           <t>Yes - Sales Director, PACE (Remote Worker - N/)</t>
         </is>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/21/26)</t>
+          <t>Hiring AEs? (9/22/26)</t>
         </is>
       </c>
     </row>
@@ -14588,7 +14588,7 @@
           <t>Course evaluation, survey, and AI feedback analysis software - Blue, MLY, and Metrics That Matter - for universities and corporate learning teams - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Yes - Junior Account Manager</t>
         </is>
@@ -15024,9 +15024,9 @@
           <t>Digital textbook and courseware delivery platform for colleges, universities, and school districts - exhibited at NACUBO 2026</t>
         </is>
       </c>
-      <c r="F22" s="70" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Sales Support - Keyholder only</t>
+      <c r="F22" s="69" t="inlineStr">
+        <is>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -15054,9 +15054,9 @@
           <t>Canvas learning management system plus assessment and credentialing software for universities, school districts, and government training programs - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Senior Account Executive - Parchme (United States)</t>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Senior Account Executive - BizGov (United States)</t>
         </is>
       </c>
     </row>
@@ -15934,7 +15934,7 @@
           <t>Residence life and student housing management software covering applications, room assignment, billing and community programming for universities and colleges - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="F55" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, EMEA (UK - Remote)</t>
         </is>
@@ -16520,7 +16520,7 @@
           <t>Degree planning, advising, transfer pathway and registration software for public universities, community colleges and private institutions - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Solutions Consultant only</t>
         </is>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/21/26)</t>
+          <t>Hiring AEs? (9/22/26)</t>
         </is>
       </c>
     </row>
@@ -17296,7 +17296,7 @@
           <t>Grant and program administration software for affordable housing, disaster recovery, vouchers and energy rebate programs run by local and state agencies - exhibited at NAHRO 2026</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>Yes - Technical Account Manager, Strateg (Atlanta)</t>
         </is>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/21/26)</t>
+          <t>Hiring AEs? (9/22/26)</t>
         </is>
       </c>
     </row>
@@ -17552,7 +17552,7 @@
           <t>Routing, in-cab fleet tech, and resident apps for waste operations - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
@@ -17612,7 +17612,7 @@
           <t>AI robotic sorting systems for recycling facilities (MRFs) - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Director, Commercial Origination &amp; only</t>
         </is>
@@ -18266,7 +18266,7 @@
           <t>Waste collection route optimization and sensor platform for municipalities</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -18968,7 +18968,7 @@
           <t>School bus stop-arm cameras with violator-funded safety programs</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Lead Salesforce Developer only</t>
         </is>
@@ -19328,7 +19328,7 @@
           <t>SmartSensor radar vehicle detection for intersections and highways</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Manager (Great Lakes) only</t>
         </is>
@@ -20640,7 +20640,7 @@
           <t>Water infrastructure: pumps, treatment, smart meters (Sensus), and analytics - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F107" s="10" t="inlineStr">
+      <c r="F107" s="9" t="inlineStr">
         <is>
           <t>Yes - Executive Sales Representative - N (12 Locations)</t>
         </is>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="F108" s="16" t="inlineStr">
         <is>
-          <t>Yes - Account Manager- Private Water (4 Locations)</t>
+          <t>Yes - Municipal Account Manager- South (3 Locations)</t>
         </is>
       </c>
     </row>
@@ -20700,7 +20700,7 @@
           <t>Hydrants, valves, and acoustic leak detection for water systems - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F109" s="10" t="inlineStr">
+      <c r="F109" s="9" t="inlineStr">
         <is>
           <t>Yes - Jr. Sales Representative (Remote - Tennessee)</t>
         </is>
@@ -20760,7 +20760,7 @@
           <t>Permitting, compliance, and workflow software for water utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F111" s="9" t="inlineStr">
+      <c r="F111" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Senior Customer Success Manager only</t>
         </is>
@@ -20880,7 +20880,7 @@
           <t>AI defect detection and coding for sewer inspection video - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F115" s="10" t="inlineStr">
+      <c r="F115" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Enterprise (Remote)</t>
         </is>
@@ -21000,7 +21000,7 @@
           <t>AI CCTV sewer and stormwater pipe condition assessment for councils and utilities - exhibited at WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F119" s="10" t="inlineStr">
+      <c r="F119" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -21600,7 +21600,7 @@
           <t>Sewer inspection cameras, trucks and software for municipal collection systems - exhibited at Maryland Municipal League 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F139" s="10" t="inlineStr">
+      <c r="F139" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -21780,7 +21780,7 @@
           <t>AI operations and forecasting software for water and wastewater utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F145" s="10" t="inlineStr">
+      <c r="F145" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -21840,7 +21840,7 @@
           <t>Generative design software for water and wastewater treatment plant projects</t>
         </is>
       </c>
-      <c r="F147" s="9" t="inlineStr">
+      <c r="F147" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -22196,7 +22196,7 @@
           <t>AquaTwin digital twin software for water and sewer hydraulic modeling, surge analysis, and asset management, sold to water utilities and engineering consultants - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F159" s="10" t="inlineStr">
+      <c r="F159" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -22650,7 +22650,7 @@
           <t>IoT telematics and video safety for government fleets (public co) - exhibited at NLC City Summit 2026, PRIMA 2026, NAFA I&amp;E 2026, NAPT Summit 2026, SWANA WASTECON 2025</t>
         </is>
       </c>
-      <c r="F175" s="10" t="inlineStr">
+      <c r="F175" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -22710,7 +22710,7 @@
           <t>Asset and work order management for DPWs (part of OpenGov)</t>
         </is>
       </c>
-      <c r="F177" s="10" t="inlineStr">
+      <c r="F177" s="9" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive (US | Illinois | Ch)</t>
         </is>
@@ -23010,7 +23010,7 @@
           <t>Fleet maintenance SaaS: work orders, inspections, fuel for commercial and gov fleets - exhibited at NAFA I&amp;E 2026</t>
         </is>
       </c>
-      <c r="F187" s="10" t="inlineStr">
+      <c r="F187" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Mid-Market (Remote)</t>
         </is>
@@ -23490,7 +23490,7 @@
           <t>collectiveFleet low-code fleet, equipment, and motor pool management for police and municipal fleets</t>
         </is>
       </c>
-      <c r="F203" s="9" t="inlineStr">
+      <c r="F203" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -23726,7 +23726,7 @@
           <t>Cloud CMMS for municipal facilities, water plants and public works</t>
         </is>
       </c>
-      <c r="F211" s="10" t="inlineStr">
+      <c r="F211" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (United Kingdom)</t>
         </is>
@@ -24026,7 +24026,7 @@
           <t>GIS-based asset and work management for local government and utilities - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
-      <c r="F221" s="10" t="inlineStr">
+      <c r="F221" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Utilities (Homeoffice)</t>
         </is>
@@ -24086,7 +24086,7 @@
           <t>Combined field service and enterprise asset management cloud for water, gas and electric utilities and municipal public works departments - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
-      <c r="F223" s="9" t="inlineStr">
+      <c r="F223" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/21/26)</t>
+          <t>Hiring AEs? (9/22/26)</t>
         </is>
       </c>
     </row>
@@ -24682,7 +24682,7 @@
           <t>Resident communications (govDelivery), meeting and agenda management, digital services; destination marketing as Simpleview, now Granicus Destinations - exhibited at 3CMA 2026, GMIS International 2026, APHSA 2026</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Yes - Local Government Account Executive</t>
         </is>
@@ -25102,7 +25102,7 @@
           <t>Social media management and archiving for government and public safety (Graham Media)</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>Yes - Sales Account Executive (USA (Remote))</t>
         </is>
@@ -25522,7 +25522,7 @@
           <t>311/citizen requests, code enforcement, and notifications for ~600 small and mid-size govs - exhibited at 3CMA 2026</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -25582,7 +25582,7 @@
           <t>Telephone and virtual town hall mass-engagement platform for county officials and agencies</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -25642,7 +25642,7 @@
           <t>Interpretation management and delivery platform (video/phone) used by courts and agencies</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Director of Sales only</t>
         </is>
@@ -26228,7 +26228,7 @@
           <t>Emergency and routine mass notification for cities, counties and schools</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
@@ -26858,7 +26858,7 @@
           <t>Permitting, licensing, and code enforcement platform for state and local government - exhibited at NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="F77" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Remote Based - US)</t>
         </is>
@@ -26918,7 +26918,7 @@
           <t>Community development permitting and licensing software (founded as BasicGov)</t>
         </is>
       </c>
-      <c r="F79" s="9" t="inlineStr">
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Business Development Representativ only</t>
         </is>
@@ -26978,7 +26978,7 @@
           <t>AI cameras on city fleet vehicles detect blight, graffiti, dumping for code enforcement - exhibited at NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F81" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Remote)</t>
         </is>
@@ -27038,7 +27038,7 @@
           <t>Cloud e-permitting and community development software for ~500 local governments (Finnish-born)</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="F83" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -27098,7 +27098,7 @@
           <t>Municipal operations software: permitting, licensing, code enforcement; NJ-rooted, going national - exhibited at NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F85" s="10" t="inlineStr">
+      <c r="F85" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive</t>
         </is>
@@ -27218,7 +27218,7 @@
           <t>Cloud permitting, licensing, code enforcement, and GIS workflows for local governments - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F89" s="10" t="inlineStr">
+      <c r="F89" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive</t>
         </is>
@@ -27278,7 +27278,7 @@
           <t>AI permitting and plan review: automated GIS/code compliance checks (Hernando County cut reviews 30 days to 2)</t>
         </is>
       </c>
-      <c r="F91" s="9" t="inlineStr">
+      <c r="F91" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -27916,7 +27916,7 @@
           <t>Digital plan review automation layered on agency permitting systems</t>
         </is>
       </c>
-      <c r="F113" s="9" t="inlineStr">
+      <c r="F113" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -28150,7 +28150,7 @@
           <t>Regulatory, licensing and planning software for public sector authorities - exhibited at PLA 2026</t>
         </is>
       </c>
-      <c r="F121" s="10" t="inlineStr">
+      <c r="F121" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive - CES (London)</t>
         </is>
@@ -28264,9 +28264,9 @@
           <t>Procurement, budgeting, and grants suite - Bonfire, Questica, eCivis (formerly GTY) - exhibited at NACUBO 2026, GFOA 2026</t>
         </is>
       </c>
-      <c r="F125" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Solutions Consultant only</t>
         </is>
       </c>
     </row>
@@ -28324,7 +28324,7 @@
           <t>Treasury platform for local government finance teams: AI reconciliation and cash forecasting - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F127" s="9" t="inlineStr">
+      <c r="F127" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Business Development Representativ only</t>
         </is>
@@ -28444,7 +28444,7 @@
           <t>Cloud treasury: debt management, GASB 87/96 lease accounting, and cash management for gov finance - exhibited at NACUBO 2026, GFOA 2026</t>
         </is>
       </c>
-      <c r="F131" s="10" t="inlineStr">
+      <c r="F131" s="9" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive (Charlotte, NC)</t>
         </is>
@@ -28474,9 +28474,9 @@
           <t>AI workflow for county assessors: deed processing, exemptions, taxpayer communication (YC S17) - exhibited at NLC City Summit 2026, IAAO 2026</t>
         </is>
       </c>
-      <c r="F132" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Customer Success Manager (West Coa only</t>
+      <c r="F132" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive</t>
         </is>
       </c>
     </row>
@@ -28684,9 +28684,9 @@
           <t>Aerial imagery and property data analytics for county assessors, GIS, and insurers - exhibited at IAAO 2026</t>
         </is>
       </c>
-      <c r="F139" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F139" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -28744,7 +28744,7 @@
           <t>cashVest liquidity analytics and treasury intelligence for counties, munis, and schools</t>
         </is>
       </c>
-      <c r="F141" s="9" t="inlineStr">
+      <c r="F141" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Senior Business Development Office only</t>
         </is>
@@ -28804,7 +28804,7 @@
           <t>HR, finance and ERP software - exhibited at APTA 2026, ICMA 2025, NACo 2026, NACUBO 2026, GFOA 2026, PSHRA 2026, NASCIO 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F143" s="10" t="inlineStr">
+      <c r="F143" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Japan, Tokyo)</t>
         </is>
@@ -28924,7 +28924,7 @@
           <t>Parcel mapping, GIS and assessment systems for county governments</t>
         </is>
       </c>
-      <c r="F147" s="10" t="inlineStr">
+      <c r="F147" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -29272,7 +29272,7 @@
           <t>Fund accounting and ERP software for cities and local governments, covering financials, payroll, utility billing and municipal court - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F159" s="10" t="inlineStr">
+      <c r="F159" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -29392,7 +29392,7 @@
           <t>Portfolio of vertical software businesses selling ERP, utility billing and public sector operations systems to local governments and utilities - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F163" s="10" t="inlineStr">
+      <c r="F163" s="9" t="inlineStr">
         <is>
           <t>Yes - (Remote) Sr Account Executive (26 Locations)</t>
         </is>
@@ -29510,7 +29510,7 @@
           <t>Free search marketplace for cooperative contracts (formerly CoProcure)</t>
         </is>
       </c>
-      <c r="F167" s="9" t="inlineStr">
+      <c r="F167" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -29630,7 +29630,7 @@
           <t>Electronic billing and payments for local government and utilities - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F171" s="10" t="inlineStr">
+      <c r="F171" s="9" t="inlineStr">
         <is>
           <t>Yes - Mid Market Account Executive (Boston, MA)</t>
         </is>
@@ -30050,7 +30050,7 @@
           <t>Source-to-pay eProcurement suite with dedicated public sector and higher-ed verticals - exhibited at NACUBO 2026, GFOA 2026</t>
         </is>
       </c>
-      <c r="F185" s="10" t="inlineStr">
+      <c r="F185" s="9" t="inlineStr">
         <is>
           <t>Yes - Strategic Account Manager (Remote)</t>
         </is>
@@ -30110,7 +30110,7 @@
           <t>Supplier ratings and performance reviews platform for public-sector buyers</t>
         </is>
       </c>
-      <c r="F187" s="9" t="inlineStr">
+      <c r="F187" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -30290,7 +30290,7 @@
           <t>AI-native ConcourseOS: procurement, permitting, courts, and billing across 450+ agencies (Bessemer-backed) - exhibited at NIGP 2026</t>
         </is>
       </c>
-      <c r="F193" s="9" t="inlineStr">
+      <c r="F193" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Founding GTM Engineer only</t>
         </is>
@@ -30468,7 +30468,7 @@
           <t>AI public-sector GTM intelligence: buying signals from gov/school board meetings, budgets, RFPs - sold to vendors selling to gov</t>
         </is>
       </c>
-      <c r="F199" s="10" t="inlineStr">
+      <c r="F199" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive - Mid Market (United States)</t>
         </is>
@@ -30578,7 +30578,7 @@
           <t>EProcurement and bid notification platforms for North American public buyers</t>
         </is>
       </c>
-      <c r="F203" s="10" t="inlineStr">
+      <c r="F203" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (United States)</t>
         </is>
@@ -30932,7 +30932,7 @@
           <t>Contract lifecycle management with FedRAMP and state/local government customers</t>
         </is>
       </c>
-      <c r="F215" s="10" t="inlineStr">
+      <c r="F215" s="9" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive (United States)</t>
         </is>
@@ -31352,7 +31352,7 @@
           <t>Cash and digital payments for child support, tolls and government billers</t>
         </is>
       </c>
-      <c r="F229" s="10" t="inlineStr">
+      <c r="F229" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Credit Unions/B (Remote)</t>
         </is>
@@ -31524,7 +31524,7 @@
           <t>Bill payment kiosks, portals, mobile apps and IVR for municipal agencies and utilities collecting resident payments - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F235" s="10" t="inlineStr">
+      <c r="F235" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -31674,9 +31674,9 @@
           <t>Pension, OPEB, and labor cost analytics for governments</t>
         </is>
       </c>
-      <c r="F240" s="21" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F240" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive</t>
         </is>
       </c>
     </row>
@@ -31884,7 +31884,7 @@
           <t>Earned wage access platform for employers - exhibited at NACo 2026</t>
         </is>
       </c>
-      <c r="F247" s="10" t="inlineStr">
+      <c r="F247" s="9" t="inlineStr">
         <is>
           <t>Yes - Business Development Manager (NYC Headquarters)</t>
         </is>
@@ -31994,7 +31994,7 @@
           <t>Payroll and HR software - exhibited at AB Show 2026</t>
         </is>
       </c>
-      <c r="F251" s="10" t="inlineStr">
+      <c r="F251" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -32114,7 +32114,7 @@
           <t>Pension, unemployment insurance and workforce systems for state agencies - exhibited at SNA ANC 2027</t>
         </is>
       </c>
-      <c r="F255" s="10" t="inlineStr">
+      <c r="F255" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -32174,7 +32174,7 @@
           <t>Employee benefits, enrollment and HR services for public sector employers</t>
         </is>
       </c>
-      <c r="F257" s="10" t="inlineStr">
+      <c r="F257" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Denver, Colorado)</t>
         </is>
@@ -32472,7 +32472,7 @@
           <t>Document-driven workflow for government procurement, budget and HR processes</t>
         </is>
       </c>
-      <c r="F267" s="9" t="inlineStr">
+      <c r="F267" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
@@ -33178,7 +33178,7 @@
           <t>Deathcare technology suite including cemetery and memorial management software</t>
         </is>
       </c>
-      <c r="F291" s="9" t="inlineStr">
+      <c r="F291" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -33520,7 +33520,7 @@
           <t>Endpoint management and security platform - exhibited at NACo 2026, NASCIO 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F303" s="9" t="inlineStr">
+      <c r="F303" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Business Analyst - Salesforce only</t>
         </is>
@@ -33580,7 +33580,7 @@
           <t>ChatGPT and the API, sold to public sector including named state and local government roles</t>
         </is>
       </c>
-      <c r="F305" s="9" t="inlineStr">
+      <c r="F305" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Account Director, Large Enterprise only</t>
         </is>
@@ -33858,7 +33858,7 @@
           <t>Strategic plan and KPI reporting (balanced scorecard) for local governments and enterprises</t>
         </is>
       </c>
-      <c r="F315" s="10" t="inlineStr">
+      <c r="F315" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -34174,9 +34174,9 @@
           <t>Governance, performance and risk management platform for public sector organizations</t>
         </is>
       </c>
-      <c r="F326" s="22" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F326" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -34910,7 +34910,7 @@
           <t>Open-source voting systems and risk-limiting audit tools for election offices</t>
         </is>
       </c>
-      <c r="F351" s="10" t="inlineStr">
+      <c r="F351" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Field Sales (United States)</t>
         </is>
@@ -37450,7 +37450,7 @@
           <t>Planning, budgeting and forecasting software - exhibited at ICMA 2025, NACUBO 2026, GFOA 2026</t>
         </is>
       </c>
-      <c r="F441" s="9" t="inlineStr">
+      <c r="F441" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -37558,7 +37558,7 @@
           <t>Purchasing card audit and compliance monitoring - exhibited at NIGP 2026</t>
         </is>
       </c>
-      <c r="F445" s="10" t="inlineStr">
+      <c r="F445" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -38356,7 +38356,7 @@
           <t>CRM and case management cloud software - exhibited at NACo 2026, NIGP 2026, NASWA 2025, NASCIO 2026, APHSA 2026, NatCon 2026, EDUCAUSE 2026, Healthcare IT Connect 2026, MESC 2026</t>
         </is>
       </c>
-      <c r="F477" s="10" t="inlineStr">
+      <c r="F477" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -38708,7 +38708,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/21/26)</t>
+          <t>Hiring AEs? (9/22/26)</t>
         </is>
       </c>
     </row>
@@ -38766,7 +38766,7 @@
           <t>Parks &amp; rec program management and booking platform founded by early Uber employees</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive (San Francisco, CA)</t>
         </is>
@@ -39120,7 +39120,7 @@
           <t>Parks and recreation management software; brands NextRec (formerly PerfectMind), Vermont Systems, RecDesk and ePACT - exhibited at AB Show 2026, NRPA 2026</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Shreveport, LA)</t>
         </is>
@@ -39540,9 +39540,9 @@
           <t>Youth sports scorekeeping and streaming app - exhibited at NRPA 2026</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive (GameChanger Remote)</t>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -39840,7 +39840,7 @@
           <t>Club and league management platform for youth soccer organizations</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -40200,7 +40200,7 @@
           <t>Campground, park and license reservation systems for state park agencies</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Platform Solutions Engineer only</t>
         </is>
@@ -40260,7 +40260,7 @@
           <t>Campground reservation and management software for public and private campgrounds</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Manager, Account Management only</t>
         </is>
@@ -40556,7 +40556,7 @@
           <t>Sports facility and program management for municipal and community facilities</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -40676,7 +40676,7 @@
           <t>AI drowning-detection and lifeguard assist for public aquatic centers</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -40856,7 +40856,7 @@
           <t>Central irrigation control and smart controllers for municipal parks</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="F73" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -41396,7 +41396,7 @@
           <t>Weather safety platform: WBGT heat monitoring, lightning alerts, stations and sirens for parks and athletics</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, SLED (Perry Weather Offi)</t>
         </is>
@@ -42056,7 +42056,7 @@
       </c>
       <c r="F113" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Sales Manager - Uplisting only</t>
+          <t>Yes - Account Manager (Barcelona)</t>
         </is>
       </c>
     </row>
@@ -42294,7 +42294,7 @@
           <t>Event management SaaS: vendor applications, ticketing, maps, and sponsors for festivals and city events</t>
         </is>
       </c>
-      <c r="F121" s="10" t="inlineStr">
+      <c r="F121" s="9" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive</t>
         </is>
@@ -42354,7 +42354,7 @@
           <t>Venue and event management for convention centers and public authorities</t>
         </is>
       </c>
-      <c r="F123" s="9" t="inlineStr">
+      <c r="F123" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Director of Solutions Engineering only</t>
         </is>
@@ -42534,7 +42534,7 @@
           <t>Venue management, ticketing and POS for aquatic centers and attractions</t>
         </is>
       </c>
-      <c r="F129" s="10" t="inlineStr">
+      <c r="F129" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive - Mid-Market and (London, United Kin)</t>
         </is>
@@ -42772,7 +42772,7 @@
           <t>Event volunteer scheduling and check-in for festivals and public events</t>
         </is>
       </c>
-      <c r="F137" s="10" t="inlineStr">
+      <c r="F137" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive Level 2 (Remote, US)</t>
         </is>
@@ -42990,7 +42990,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/21/26)</t>
+          <t>Hiring AEs? (9/22/26)</t>
         </is>
       </c>
     </row>
@@ -43048,9 +43048,9 @@
           <t>CrisisAlert wearable panic buttons for school staff; 18M+ people covered</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Senior Sales Executive (VA/WV/OH) (Remote Worker - N/)</t>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Sales Executive - Pacific Northwes (Remote Worker - N/)</t>
         </is>
       </c>
     </row>
@@ -43168,7 +43168,7 @@
           <t>Device filtering, classroom management, and student wellness (Beacon)</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - New Business Executive - Strategic only</t>
         </is>
@@ -43702,7 +43702,7 @@
           <t>AI weapons detection and screening for schools and public buildings</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -43880,7 +43880,7 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -44292,7 +44292,7 @@
           <t>School bus telematics, electronic inspections, and ridership tracking</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="9" t="inlineStr">
         <is>
           <t>Yes - Sales Account Executive – Mid-Mark</t>
         </is>
@@ -44324,7 +44324,7 @@
       </c>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -45012,7 +45012,7 @@
           <t>Unified school-home communication platform - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F69" s="9" t="inlineStr">
+      <c r="F69" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -45132,7 +45132,7 @@
           <t>Capital program management and purchasing/AP compliance for 140+ California districts</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="F73" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -45550,7 +45550,7 @@
           <t>Alternative student transportation for school districts (formerly ALC Schools): contracted vehicles and drivers for students a yellow bus cannot serve, with dispatch and tracking for the district - exhibited at NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F87" s="10" t="inlineStr">
+      <c r="F87" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Southern Califo (Remote Southern Ca)</t>
         </is>
@@ -45670,7 +45670,7 @@
           <t>School and district websites, apps and communications for public schools</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>Yes - Sales Executive (Remote Worker - N/)</t>
         </is>
@@ -45760,9 +45760,9 @@
           <t>Absence, substitute placement and time tracking for school districts</t>
         </is>
       </c>
-      <c r="F94" s="34" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F94" s="35" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive (Remote Worker - N/)</t>
         </is>
       </c>
     </row>
@@ -45910,7 +45910,7 @@
           <t>Dismissal, attendance and school safety workflow platform for districts</t>
         </is>
       </c>
-      <c r="F99" s="10" t="inlineStr">
+      <c r="F99" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -45970,7 +45970,7 @@
           <t>Single sign-on, rostering and usage analytics for public school districts - exhibited at CoSN 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F101" s="10" t="inlineStr">
+      <c r="F101" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -46136,7 +46136,7 @@
           <t>Digital hall pass, tardy tracking, behavior management, and campus engagement platform for K-12 schools and districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F107" s="10" t="inlineStr">
+      <c r="F107" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Manager (INTERNAL APPLICAN</t>
         </is>
@@ -46198,7 +46198,7 @@
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - HTTP 404 for https://boards-api.greenhou</t>
         </is>
       </c>
     </row>
@@ -46280,9 +46280,9 @@
           <t>Library, technology asset, and facilities management software for K-12 school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F112" s="34" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F112" s="33" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Inside Sales Account Executive only</t>
         </is>
       </c>
     </row>
@@ -46528,7 +46528,7 @@
           <t>Classroom browser monitoring, web filtering and student wellbeing alerting software for K-12 schools and districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F121" s="10" t="inlineStr">
+      <c r="F121" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -46642,7 +46642,7 @@
           <t>Student survey, MTSS, behavior analytics and early-warning software for K-12 school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F125" s="10" t="inlineStr">
+      <c r="F125" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -46806,7 +46806,7 @@
           <t>Phone-free school software that blocks distracting apps during class and records attendance for K-12 districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F131" s="10" t="inlineStr">
+      <c r="F131" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -46972,7 +46972,7 @@
           <t>AI service desk and service operations platform unifying IT, facilities, HR and transportation requests for K-12 districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F137" s="10" t="inlineStr">
+      <c r="F137" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -47086,7 +47086,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/21/26)</t>
+          <t>Hiring AEs? (9/22/26)</t>
         </is>
       </c>
     </row>
@@ -47144,7 +47144,7 @@
           <t>Justride fare payments SaaS used by hundreds of agencies</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager - UK only</t>
         </is>
@@ -47620,7 +47620,7 @@
           <t>Check-in/be-out mobile fare payment for public transport authorities</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>Yes - Sales &amp; Business Development Manag</t>
         </is>
@@ -47860,7 +47860,7 @@
           <t>HASTUS scheduling, run-cutting, and rostering for transit agencies and postal operators</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Director, Strategic Business Devel only</t>
         </is>
@@ -47920,7 +47920,7 @@
           <t>Holding group of ~34 transit software brands under Constellation (Trapeze, Vontas, TransTrack, TripSpark, TransLoc)</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales &amp; Marketing Director only</t>
         </is>
@@ -48154,7 +48154,7 @@
           <t>iMarq mobile asset maintenance and MRO platform for transit, rail, and fleets</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -48334,7 +48334,7 @@
           <t>SCADA systems and the SentientQ automation platform for rail transit, LRT, and utilities</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr">
         <is>
           <t>Yes - Business Development Manager</t>
         </is>
@@ -49104,7 +49104,7 @@
           <t>AI dashcam and driver coaching for public fleets</t>
         </is>
       </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="F69" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Mid-Market (USA)</t>
         </is>
@@ -49164,7 +49164,7 @@
           <t>Fleet maintenance software for cities, counties and transit agencies</t>
         </is>
       </c>
-      <c r="F71" s="10" t="inlineStr">
+      <c r="F71" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Remote Worker)</t>
         </is>
@@ -49224,7 +49224,7 @@
           <t>Fleet maintenance management software for transit and government fleets</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="F73" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -49344,7 +49344,7 @@
           <t>Digital vehicle inspections and maintenance for municipal fleets</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Operations Manager, Customer Succe only</t>
         </is>
@@ -49796,7 +49796,7 @@
       </c>
       <c r="F92" s="39" t="inlineStr">
         <is>
-          <t>Yes - Strategic Account Executive (North Carolina_Rem)</t>
+          <t>Yes - Mass Market Account Executive (Arizona_Remote)</t>
         </is>
       </c>
     </row>
@@ -49884,7 +49884,7 @@
           <t>Solar e-paper real-time passenger information displays and cloud CMS for bus stops and stations</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="F95" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -50242,7 +50242,7 @@
           <t>On-demand transit, paratransit, and network planning software for agencies - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F107" s="10" t="inlineStr">
+      <c r="F107" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Western Europe (Paris)</t>
         </is>
@@ -50542,7 +50542,7 @@
           <t>Turnkey autonomous shuttle operations for transit agencies, airports, and communities</t>
         </is>
       </c>
-      <c r="F117" s="9" t="inlineStr">
+      <c r="F117" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -51484,7 +51484,7 @@
           <t>Smart single-space parking meters and enforcement systems</t>
         </is>
       </c>
-      <c r="F149" s="9" t="inlineStr">
+      <c r="F149" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sr. Client Success Manager only</t>
         </is>
@@ -51664,7 +51664,7 @@
           <t>Parking permits, enforcement, PARCS, and pay stations for universities and cities (Verra Mobility)</t>
         </is>
       </c>
-      <c r="F155" s="10" t="inlineStr">
+      <c r="F155" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -51724,9 +51724,9 @@
           <t>Mobility and curb/parking technology platform - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F157" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Manager (Helsinki)</t>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Junior B2B Account Executive (Prague)</t>
         </is>
       </c>
     </row>
@@ -52392,7 +52392,7 @@
           <t>Security and intelligence analytics software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F181" s="10" t="inlineStr">
+      <c r="F181" s="9" t="inlineStr">
         <is>
           <t>Yes - Enterprise Sales Executive – New L (2 Locations)</t>
         </is>
@@ -52586,7 +52586,7 @@
           <t>GPS fleet tracking and telematics software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F189" s="10" t="inlineStr">
+      <c r="F189" s="9" t="inlineStr">
         <is>
           <t>Yes - Sales Account Executive – Mid-Mark</t>
         </is>
@@ -52728,7 +52728,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/21/26)</t>
+          <t>Hiring AEs? (9/22/26)</t>
         </is>
       </c>
     </row>
@@ -52846,7 +52846,7 @@
           <t>Autonomous off-grid solar streetlights with remote monitoring; 1,000+ municipalities, 43 states (French parent)</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -53386,7 +53386,7 @@
           <t>Aluminum and steel lighting poles for municipal and DOT projects</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -53446,7 +53446,7 @@
           <t>Adaptive smart street lighting sensors and CMS for municipalities</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -53506,7 +53506,7 @@
           <t>Street lighting luminaires and connected controls for public authorities</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -53986,7 +53986,7 @@
           <t>Exterior LED site and streetscape lighting for public projects</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -54046,7 +54046,7 @@
           <t>Pole-mounted sensors + AI (Gridscope) detecting grid faults, vegetation strikes, and wildfire-risk events</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
@@ -54106,7 +54106,7 @@
           <t>Satellite + AI vegetation management (IVMS) and climate/asset risk SaaS for utilities</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Business Analyst - Customer Succes only</t>
         </is>
@@ -54166,7 +54166,7 @@
           <t>EV ARC transportable solar EV charging and storage for government fleets (Nasdaq: BEEM; ex-Envision Solar)</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -54286,7 +54286,7 @@
           <t>Metering, CIS, billing and grid analytics for public power utilities</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -54466,7 +54466,7 @@
           <t>Smart grid AMI and grid analytics for public power utilities and co-ops</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Office &amp; Sales Support Coordinator only</t>
         </is>
@@ -54706,7 +54706,7 @@
           <t>DERMS and virtual power plant programs for utilities including public power</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Engineer only</t>
         </is>
@@ -54946,7 +54946,7 @@
           <t>Utility bill management and energy analytics for cities, counties and schools</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F75" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive</t>
         </is>
@@ -55184,7 +55184,7 @@
           <t>Outage notification, billing, and omnichannel customer communication platform for investor-owned, municipal, and cooperative utilities - exhibited at APPA Public Power 2026</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="F83" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (US - Remote)</t>
         </is>
@@ -55598,7 +55598,7 @@
           <t>Geospatial network design and field software for telecom and public utilities</t>
         </is>
       </c>
-      <c r="F97" s="9" t="inlineStr">
+      <c r="F97" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Engineer only</t>
         </is>
@@ -55718,7 +55718,7 @@
           <t>Broadband grant, challenge process and mapping software for state broadband offices</t>
         </is>
       </c>
-      <c r="F101" s="9" t="inlineStr">
+      <c r="F101" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Product Solutions Engineer only</t>
         </is>
@@ -56286,7 +56286,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/21/26)</t>
+          <t>Hiring AEs? (9/22/26)</t>
         </is>
       </c>
     </row>
@@ -56756,7 +56756,7 @@
           <t>Aviation design and simulation software (AviPLAN, AeroTURN, GuideSIGN) used by airport planners for aircraft movement, apron layout and airside safety analysis.</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Sales)</t>
         </is>
@@ -57172,7 +57172,7 @@
           <t>Airport weather observation systems and runway condition sensors for airports - exhibited at NACE 2026</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -57232,7 +57232,7 @@
           <t>Bird-strike avoidance radar and wildlife management systems for airports</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -57352,7 +57352,7 @@
           <t>ARINC airport systems portfolio: vMUSE common-use passenger processing, SelfPass biometrics, self bag drop, AODB/resource management, FIDS and airport communications sold to airport authorities.</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -57590,7 +57590,7 @@
           <t>Passenger flow, queue measurement and airport revenue software for airport operators</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="9" t="inlineStr">
         <is>
           <t>Yes - Sales Director Americas (US-based within th)</t>
         </is>
@@ -57710,7 +57710,7 @@
           <t>Gate, docking guidance and apron systems for airport operators</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -57890,7 +57890,7 @@
           <t>Self-service kiosks, bag drop and passenger processing for airports</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="F55" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -58070,7 +58070,7 @@
           <t>Airport IQ operations, property and lease management software for airports</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="F61" s="9" t="inlineStr">
         <is>
           <t>Yes - Senior Account Executive</t>
         </is>
@@ -58610,7 +58610,7 @@
           <t>Biometric identity, TSA PreCheck enrollment and airport boarding systems</t>
         </is>
       </c>
-      <c r="F79" s="10" t="inlineStr">
+      <c r="F79" s="9" t="inlineStr">
         <is>
           <t>Yes - Key Account Manager - Smart Biomet</t>
         </is>
@@ -58670,7 +58670,7 @@
           <t>Biometric identity lanes operated under airport and TSA agreements</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F81" s="9" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive (C1 - (New York, New York)</t>
         </is>
@@ -58790,7 +58790,7 @@
           <t>Perimeter intrusion detection and fence sensors for airports and utilities</t>
         </is>
       </c>
-      <c r="F85" s="10" t="inlineStr">
+      <c r="F85" s="9" t="inlineStr">
         <is>
           <t>Yes - Business Development Manager (Ottawa, Ontario, C)</t>
         </is>
@@ -59028,7 +59028,7 @@
           <t>Automated vehicle inspection portals for airports, borders and government</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F93" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -59148,7 +59148,7 @@
           <t>Computer-vision checkout-free parking payment platform (drive-in/drive-out billing) plus parking operations and revenue management for airports; owner of SP+.</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Remote USA)</t>
         </is>
@@ -59326,7 +59326,7 @@
           <t>Airport parking reservations and demand channel for airport operators</t>
         </is>
       </c>
-      <c r="F103" s="10" t="inlineStr">
+      <c r="F103" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -59386,7 +59386,7 @@
           <t>Full-service automated parking operations for cities and airports</t>
         </is>
       </c>
-      <c r="F105" s="9" t="inlineStr">
+      <c r="F105" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Development Representative only</t>
         </is>
@@ -59506,7 +59506,7 @@
           <t>AVI readers and ground transportation management systems for airports</t>
         </is>
       </c>
-      <c r="F109" s="10" t="inlineStr">
+      <c r="F109" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -59746,7 +59746,7 @@
           <t>Web-based capital program and construction project management software (cost, contracts, documents, scheduling) used by airport owner-operators and public agencies.</t>
         </is>
       </c>
-      <c r="F117" s="10" t="inlineStr">
+      <c r="F117" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -59810,7 +59810,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/21/26)</t>
+          <t>Hiring AEs? (9/22/26)</t>
         </is>
       </c>
     </row>
@@ -60146,7 +60146,7 @@
           <t>Digital courtroom recording and speech recognition systems for courts</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -60264,7 +60264,7 @@
           <t>Criminal justice data collection and public dashboards for counties and states</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -60324,7 +60324,7 @@
           <t>Cloud ediscovery and litigation platform for law firms, corporations, county DAs, and state AGs - exhibited at IMLA 2026, NASCIO 2026</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive (Stat (United States)</t>
         </is>
@@ -60384,7 +60384,7 @@
           <t>PROSECUTORbyKarpel case management software for prosecutor offices - exhibited at IMLA 2026</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Remote Worker - N/)</t>
         </is>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -246,9 +246,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -296,8 +296,8 @@
     <xf numFmtId="1" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/22/26)</t>
+          <t>Hiring AEs? (9/23/26)</t>
         </is>
       </c>
     </row>
@@ -1120,9 +1120,9 @@
           <t>Wildfire spread modeling and risk analytics used by CAL FIRE and major utilities</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sr. Manager, FP&amp;A &amp; Sales Operatio only</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
           <t>Exterior retardant/foam systems and app-based wildfire defense for homes and HOAs</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Yes - Territory Manager - LA (Los Angeles, CA)</t>
         </is>
@@ -1330,7 +1330,7 @@
           <t>Actively tethered situational awareness drones with unlimited flight time for fire/PS</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Engineer only</t>
         </is>
@@ -1414,7 +1414,7 @@
           <t>Cloud fire and EMS records management for departments of all sizes</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -1650,7 +1650,7 @@
           <t>Satellite vegetation intelligence for wildfire risk at utilities and agencies</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive, Cana (Remote, Canada)</t>
         </is>
@@ -2070,7 +2070,7 @@
           <t>License plate readers, gunshot detection, and drone-as-first-responder (Aerodome)</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Senior Deal Desk Analyst only</t>
         </is>
@@ -2130,7 +2130,7 @@
           <t>911-response and tactical drones staged on police and fire station rooftops</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive, DFR (Remote (Select Sta)</t>
         </is>
@@ -2190,7 +2190,7 @@
           <t>Data integration and real-time intelligence platform for police and city agencies - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>Yes - Federal Account Executive (Washington, D.C.)</t>
         </is>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (U.S. (Remote))</t>
+          <t>Yes - Account Executive - ECC (U.S. (Remote))</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
           <t>Incident reporting and case management for law enforcement, campus, and healthcare security</t>
         </is>
       </c>
-      <c r="F55" s="11" t="inlineStr">
+      <c r="F55" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -2670,7 +2670,7 @@
           <t>AI audio/video/document redaction (CaseGuard Studio) for police, courts, and gov</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
+      <c r="F59" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Arlington, VA)</t>
         </is>
@@ -2940,7 +2940,7 @@
           <t>Digital investigation suite for cleansing and evidencing comms data (UK + US LE)</t>
         </is>
       </c>
-      <c r="F68" s="10" t="inlineStr">
+      <c r="F68" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -2970,7 +2970,7 @@
           <t>Investigation database: pawn/secondhand transactions plus ballistics ID for agencies - exhibited at Michigan Sheriffs Association 2026</t>
         </is>
       </c>
-      <c r="F69" s="9" t="inlineStr">
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -3090,7 +3090,7 @@
           <t>Cloud cameras, access control, and sensors with a dedicated SLED sales org - exhibited at EDUCAUSE 2026, Maryland Municipal League 2026</t>
         </is>
       </c>
-      <c r="F73" s="9" t="inlineStr">
+      <c r="F73" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive, France (London)</t>
         </is>
@@ -3330,7 +3330,7 @@
           <t>Drone-as-first-responder software and hardware auto-launching to 911 calls</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr">
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive</t>
         </is>
@@ -3570,7 +3570,7 @@
           <t>Bird and drone detection radars (ELVIRA, IRIS) for airports, security, and C-UAS</t>
         </is>
       </c>
-      <c r="F89" s="9" t="inlineStr">
+      <c r="F89" s="10" t="inlineStr">
         <is>
           <t>Yes - Regional Account Manager - Nordics (Nordics)</t>
         </is>
@@ -3720,7 +3720,7 @@
           <t>Training LMS, scheduling, and readiness software (TargetSolutions, Guardian Tracking) - exhibited at IAFC FRI 2026, APCO 2026</t>
         </is>
       </c>
-      <c r="F94" s="10" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -3810,7 +3810,7 @@
           <t>Scheduling and workforce management for police, corrections, and 911</t>
         </is>
       </c>
-      <c r="F97" s="9" t="inlineStr">
+      <c r="F97" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -3870,7 +3870,7 @@
           <t>OfficerTRAK off-duty detail management: scheduling, billing, insurance - exhibited at NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F99" s="9" t="inlineStr">
+      <c r="F99" s="10" t="inlineStr">
         <is>
           <t>Yes - Business Development Manager - Mid (Charlotte, North C)</t>
         </is>
@@ -3930,7 +3930,7 @@
           <t>Online application and recruiting platform for police and civil service hiring</t>
         </is>
       </c>
-      <c r="F101" s="11" t="inlineStr">
+      <c r="F101" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -4350,7 +4350,7 @@
           <t>Cyber-over-RF counter-drone detect, track, and mitigate systems for LE, prisons, and infrastructure</t>
         </is>
       </c>
-      <c r="F115" s="9" t="inlineStr">
+      <c r="F115" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -4738,7 +4738,7 @@
           <t>Retail crime intelligence and reporting platform - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F129" s="9" t="inlineStr">
+      <c r="F129" s="10" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Manager (Biling (Remote - United St)</t>
         </is>
@@ -4788,7 +4788,7 @@
           <t>Software for first responder agencies - exhibited at IACP 2026, APCO 2026</t>
         </is>
       </c>
-      <c r="F131" s="9" t="inlineStr">
+      <c r="F131" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive (United States)</t>
         </is>
@@ -4842,7 +4842,7 @@
           <t>AI investigations platform for law enforcement - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F133" s="9" t="inlineStr">
+      <c r="F133" s="10" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive</t>
         </is>
@@ -5382,7 +5382,7 @@
           <t>FBI-certified mobile fingerprint scanners for police and government</t>
         </is>
       </c>
-      <c r="F151" s="11" t="inlineStr">
+      <c r="F151" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -5412,7 +5412,7 @@
           <t>Data integration and investigative analytics for police and government</t>
         </is>
       </c>
-      <c r="F152" s="10" t="inlineStr">
+      <c r="F152" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Forward Deployed Enablement Engine only</t>
         </is>
@@ -5862,7 +5862,7 @@
           <t>ePCR, records, and analytics connecting EMS, fire, and hospitals - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
-      <c r="F167" s="9" t="inlineStr">
+      <c r="F167" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Remote, US (TN/KY))</t>
         </is>
@@ -5922,7 +5922,7 @@
           <t>Intelligent 911 platform streaming device location and data to dispatch - exhibited at APCO 2026</t>
         </is>
       </c>
-      <c r="F169" s="11" t="inlineStr">
+      <c r="F169" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Director, Customer Solutions Engin only</t>
         </is>
@@ -5982,7 +5982,7 @@
           <t>Assistive AI for 911 centers: transcription, translation, text-to-911, and video</t>
         </is>
       </c>
-      <c r="F171" s="9" t="inlineStr">
+      <c r="F171" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -6282,7 +6282,7 @@
           <t>Pediatric emergency dosing system and app for EMS agencies</t>
         </is>
       </c>
-      <c r="F181" s="9" t="inlineStr">
+      <c r="F181" s="10" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive</t>
         </is>
@@ -6402,7 +6402,7 @@
           <t>Mobile incident command and response for fire/EMS departments - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
-      <c r="F185" s="9" t="inlineStr">
+      <c r="F185" s="10" t="inlineStr">
         <is>
           <t>Yes - Regional Account Executive</t>
         </is>
@@ -6582,7 +6582,7 @@
           <t>911 call routing, Viper call handling and NG911 for PSAPs</t>
         </is>
       </c>
-      <c r="F191" s="9" t="inlineStr">
+      <c r="F191" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -6702,7 +6702,7 @@
           <t>AI triage and quality assurance for emergency dispatch centers</t>
         </is>
       </c>
-      <c r="F195" s="11" t="inlineStr">
+      <c r="F195" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - GTM Engineer only</t>
         </is>
@@ -6968,7 +6968,7 @@
           <t>SARA situational awareness and mass notification for schools, senior living, and gov facilities</t>
         </is>
       </c>
-      <c r="F204" s="10" t="inlineStr">
+      <c r="F204" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -7538,7 +7538,7 @@
           <t>CID Net inmate calling (450+ facilities), facility monitoring, and family apps</t>
         </is>
       </c>
-      <c r="F223" s="11" t="inlineStr">
+      <c r="F223" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -8636,7 +8636,7 @@
           <t>Data and case-management tools for state corrections and supervision agencies</t>
         </is>
       </c>
-      <c r="F260" s="10" t="inlineStr">
+      <c r="F260" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - State Partnerships Manager only</t>
         </is>
@@ -9458,7 +9458,7 @@
           <t>Digital forensics and investigation management software - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F289" s="11" t="inlineStr">
+      <c r="F289" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Operations &amp; GTM Systems Man only</t>
         </is>
@@ -9584,7 +9584,7 @@
           <t>AI police report writing and investigation software - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F294" s="10" t="inlineStr">
+      <c r="F294" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -10660,7 +10660,7 @@
           <t>DigiTICKET electronic citation software - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F338" s="10" t="inlineStr">
+      <c r="F338" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/22/26)</t>
+          <t>Hiring AEs? (9/23/26)</t>
         </is>
       </c>
     </row>
@@ -11488,7 +11488,7 @@
       </c>
       <c r="F14" s="64" t="inlineStr">
         <is>
-          <t>Yes - Commercial Account Executive (Remote – United St)</t>
+          <t>Yes - Strategic Account Executive, Marke (Remote – United St)</t>
         </is>
       </c>
     </row>
@@ -12424,7 +12424,7 @@
           <t>Care coordination and PDMP network software (PMP AWARxE, OpenBeds) for states, counties, and health systems (Appriss lineage)</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>Yes - Bamboo Bridge Strategic Account Ma</t>
         </is>
@@ -12766,7 +12766,7 @@
           <t>Digital substance use disorder prevention, intervention, and recovery support platform for treatment providers, state and county health agencies, drug courts, and Medicaid plans - exhibited at NatCon 2026, NACCHO 360 2026</t>
         </is>
       </c>
-      <c r="F59" s="11" t="inlineStr">
+      <c r="F59" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Senior Customer Success Consultant only</t>
         </is>
@@ -12982,7 +12982,7 @@
           <t>Human services EHR and care coordination software for behavioral health, residential, vocational rehab, and food assistance providers - exhibited at NatCon 2026</t>
         </is>
       </c>
-      <c r="F67" s="11" t="inlineStr">
+      <c r="F67" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
@@ -13192,7 +13192,7 @@
           <t>AI clinical documentation and chart auditing platform purpose-built for behavioral health providers including CCBHCs and human services organizations - exhibited at NatCon 2026</t>
         </is>
       </c>
-      <c r="F75" s="11" t="inlineStr">
+      <c r="F75" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - VP of Revenue only</t>
         </is>
@@ -13246,7 +13246,7 @@
           <t>Accredited continuing-education, AI practice simulation and certification platform for behavioral health clinicians and the organizations that employ them - exhibited at NatCon 2026</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr">
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -13610,7 +13610,7 @@
           <t>Social care coordination network connecting health and social service referrals for govs and payers - exhibited at MESC 2026</t>
         </is>
       </c>
-      <c r="F91" s="9" t="inlineStr">
+      <c r="F91" s="10" t="inlineStr">
         <is>
           <t>Yes - Strategic Sales Director (United States)</t>
         </is>
@@ -13730,7 +13730,7 @@
           <t>Clarity HMIS and homelessness response systems for counties and CoCs</t>
         </is>
       </c>
-      <c r="F95" s="11" t="inlineStr">
+      <c r="F95" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Solutions Consultant only</t>
         </is>
@@ -14018,7 +14018,7 @@
           <t>EHR and case management software for PACE programs, State Units on Aging, Area Agencies on Aging and community-based aging services organizations - exhibited at USAging 2026</t>
         </is>
       </c>
-      <c r="F105" s="9" t="inlineStr">
+      <c r="F105" s="10" t="inlineStr">
         <is>
           <t>Yes - Sales Director, PACE (Remote Worker - N/)</t>
         </is>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/22/26)</t>
+          <t>Hiring AEs? (9/23/26)</t>
         </is>
       </c>
     </row>
@@ -14588,7 +14588,7 @@
           <t>Course evaluation, survey, and AI feedback analysis software - Blue, MLY, and Metrics That Matter - for universities and corporate learning teams - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Yes - Junior Account Manager</t>
         </is>
@@ -15024,9 +15024,9 @@
           <t>Digital textbook and courseware delivery platform for colleges, universities, and school districts - exhibited at NACUBO 2026</t>
         </is>
       </c>
-      <c r="F22" s="69" t="inlineStr">
-        <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+      <c r="F22" s="70" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sales Support - Keyholder only</t>
         </is>
       </c>
     </row>
@@ -15054,9 +15054,9 @@
           <t>Canvas learning management system plus assessment and credentialing software for universities, school districts, and government training programs - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>Yes - Senior Account Executive - BizGov (United States)</t>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Senior Account Executive - Canvas  (United States)</t>
         </is>
       </c>
     </row>
@@ -15934,7 +15934,7 @@
           <t>Residence life and student housing management software covering applications, room assignment, billing and community programming for universities and colleges - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive, EMEA (UK - Remote)</t>
         </is>
@@ -16520,7 +16520,7 @@
           <t>Degree planning, advising, transfer pathway and registration software for public universities, community colleges and private institutions - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F77" s="11" t="inlineStr">
+      <c r="F77" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Solutions Consultant only</t>
         </is>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/22/26)</t>
+          <t>Hiring AEs? (9/23/26)</t>
         </is>
       </c>
     </row>
@@ -17296,7 +17296,7 @@
           <t>Grant and program administration software for affordable housing, disaster recovery, vouchers and energy rebate programs run by local and state agencies - exhibited at NAHRO 2026</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Yes - Technical Account Manager, Strateg (Atlanta)</t>
         </is>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/22/26)</t>
+          <t>Hiring AEs? (9/23/26)</t>
         </is>
       </c>
     </row>
@@ -17552,7 +17552,7 @@
           <t>Routing, in-cab fleet tech, and resident apps for waste operations - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
@@ -17612,7 +17612,7 @@
           <t>AI robotic sorting systems for recycling facilities (MRFs) - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Director, Commercial Origination &amp; only</t>
         </is>
@@ -18266,7 +18266,7 @@
           <t>Waste collection route optimization and sensor platform for municipalities</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -18648,7 +18648,7 @@
       </c>
       <c r="F40" s="16" t="inlineStr">
         <is>
-          <t>Yes - Regional Sales Manager (2 Locations)</t>
+          <t>Yes - Outside Sales Representative (4 Locations)</t>
         </is>
       </c>
     </row>
@@ -18968,7 +18968,7 @@
           <t>School bus stop-arm cameras with violator-funded safety programs</t>
         </is>
       </c>
-      <c r="F51" s="11" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Lead Salesforce Developer only</t>
         </is>
@@ -19328,7 +19328,7 @@
           <t>SmartSensor radar vehicle detection for intersections and highways</t>
         </is>
       </c>
-      <c r="F63" s="11" t="inlineStr">
+      <c r="F63" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Manager (Great Lakes) only</t>
         </is>
@@ -20640,7 +20640,7 @@
           <t>Water infrastructure: pumps, treatment, smart meters (Sensus), and analytics - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F107" s="9" t="inlineStr">
+      <c r="F107" s="10" t="inlineStr">
         <is>
           <t>Yes - Executive Sales Representative - N (12 Locations)</t>
         </is>
@@ -20700,7 +20700,7 @@
           <t>Hydrants, valves, and acoustic leak detection for water systems - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F109" s="9" t="inlineStr">
+      <c r="F109" s="10" t="inlineStr">
         <is>
           <t>Yes - Jr. Sales Representative (Remote - Tennessee)</t>
         </is>
@@ -20760,7 +20760,7 @@
           <t>Permitting, compliance, and workflow software for water utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F111" s="11" t="inlineStr">
+      <c r="F111" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Senior Customer Success Manager only</t>
         </is>
@@ -20880,7 +20880,7 @@
           <t>AI defect detection and coding for sewer inspection video - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F115" s="9" t="inlineStr">
+      <c r="F115" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Enterprise (Remote)</t>
         </is>
@@ -21000,7 +21000,7 @@
           <t>AI CCTV sewer and stormwater pipe condition assessment for councils and utilities - exhibited at WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F119" s="9" t="inlineStr">
+      <c r="F119" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -21600,7 +21600,7 @@
           <t>Sewer inspection cameras, trucks and software for municipal collection systems - exhibited at Maryland Municipal League 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F139" s="9" t="inlineStr">
+      <c r="F139" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -21780,7 +21780,7 @@
           <t>AI operations and forecasting software for water and wastewater utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F145" s="9" t="inlineStr">
+      <c r="F145" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -21840,7 +21840,7 @@
           <t>Generative design software for water and wastewater treatment plant projects</t>
         </is>
       </c>
-      <c r="F147" s="11" t="inlineStr">
+      <c r="F147" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -22196,7 +22196,7 @@
           <t>AquaTwin digital twin software for water and sewer hydraulic modeling, surge analysis, and asset management, sold to water utilities and engineering consultants - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F159" s="9" t="inlineStr">
+      <c r="F159" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -22650,7 +22650,7 @@
           <t>IoT telematics and video safety for government fleets (public co) - exhibited at NLC City Summit 2026, PRIMA 2026, NAFA I&amp;E 2026, NAPT Summit 2026, SWANA WASTECON 2025</t>
         </is>
       </c>
-      <c r="F175" s="9" t="inlineStr">
+      <c r="F175" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -22710,7 +22710,7 @@
           <t>Asset and work order management for DPWs (part of OpenGov)</t>
         </is>
       </c>
-      <c r="F177" s="9" t="inlineStr">
+      <c r="F177" s="10" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive (US | Illinois | Ch)</t>
         </is>
@@ -23010,7 +23010,7 @@
           <t>Fleet maintenance SaaS: work orders, inspections, fuel for commercial and gov fleets - exhibited at NAFA I&amp;E 2026</t>
         </is>
       </c>
-      <c r="F187" s="9" t="inlineStr">
+      <c r="F187" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Mid-Market (Remote)</t>
         </is>
@@ -23490,7 +23490,7 @@
           <t>collectiveFleet low-code fleet, equipment, and motor pool management for police and municipal fleets</t>
         </is>
       </c>
-      <c r="F203" s="11" t="inlineStr">
+      <c r="F203" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -23726,7 +23726,7 @@
           <t>Cloud CMMS for municipal facilities, water plants and public works</t>
         </is>
       </c>
-      <c r="F211" s="9" t="inlineStr">
+      <c r="F211" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive (United Kingdom)</t>
         </is>
@@ -24026,7 +24026,7 @@
           <t>GIS-based asset and work management for local government and utilities - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
-      <c r="F221" s="9" t="inlineStr">
+      <c r="F221" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Utilities (Homeoffice)</t>
         </is>
@@ -24086,7 +24086,7 @@
           <t>Combined field service and enterprise asset management cloud for water, gas and electric utilities and municipal public works departments - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
-      <c r="F223" s="11" t="inlineStr">
+      <c r="F223" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/22/26)</t>
+          <t>Hiring AEs? (9/23/26)</t>
         </is>
       </c>
     </row>
@@ -24682,7 +24682,7 @@
           <t>Resident communications (govDelivery), meeting and agenda management, digital services; destination marketing as Simpleview, now Granicus Destinations - exhibited at 3CMA 2026, GMIS International 2026, APHSA 2026</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Yes - Local Government Account Executive</t>
         </is>
@@ -25102,7 +25102,7 @@
           <t>Social media management and archiving for government and public safety (Graham Media)</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>Yes - Sales Account Executive (USA (Remote))</t>
         </is>
@@ -25522,7 +25522,7 @@
           <t>311/citizen requests, code enforcement, and notifications for ~600 small and mid-size govs - exhibited at 3CMA 2026</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -25582,7 +25582,7 @@
           <t>Telephone and virtual town hall mass-engagement platform for county officials and agencies</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -25642,7 +25642,7 @@
           <t>Interpretation management and delivery platform (video/phone) used by courts and agencies</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Director of Sales only</t>
         </is>
@@ -26228,7 +26228,7 @@
           <t>Emergency and routine mass notification for cities, counties and schools</t>
         </is>
       </c>
-      <c r="F55" s="11" t="inlineStr">
+      <c r="F55" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
@@ -26858,7 +26858,7 @@
           <t>Permitting, licensing, and code enforcement platform for state and local government - exhibited at NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr">
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Remote Based - US)</t>
         </is>
@@ -26918,7 +26918,7 @@
           <t>Community development permitting and licensing software (founded as BasicGov)</t>
         </is>
       </c>
-      <c r="F79" s="11" t="inlineStr">
+      <c r="F79" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Business Development Representativ only</t>
         </is>
@@ -26978,7 +26978,7 @@
           <t>AI cameras on city fleet vehicles detect blight, graffiti, dumping for code enforcement - exhibited at NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr">
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Remote)</t>
         </is>
@@ -27038,7 +27038,7 @@
           <t>Cloud e-permitting and community development software for ~500 local governments (Finnish-born)</t>
         </is>
       </c>
-      <c r="F83" s="9" t="inlineStr">
+      <c r="F83" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -27098,7 +27098,7 @@
           <t>Municipal operations software: permitting, licensing, code enforcement; NJ-rooted, going national - exhibited at NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F85" s="9" t="inlineStr">
+      <c r="F85" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive</t>
         </is>
@@ -27218,7 +27218,7 @@
           <t>Cloud permitting, licensing, code enforcement, and GIS workflows for local governments - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F89" s="9" t="inlineStr">
+      <c r="F89" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive</t>
         </is>
@@ -27278,7 +27278,7 @@
           <t>AI permitting and plan review: automated GIS/code compliance checks (Hernando County cut reviews 30 days to 2)</t>
         </is>
       </c>
-      <c r="F91" s="11" t="inlineStr">
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -27916,7 +27916,7 @@
           <t>Digital plan review automation layered on agency permitting systems</t>
         </is>
       </c>
-      <c r="F113" s="11" t="inlineStr">
+      <c r="F113" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -28150,7 +28150,7 @@
           <t>Regulatory, licensing and planning software for public sector authorities - exhibited at PLA 2026</t>
         </is>
       </c>
-      <c r="F121" s="9" t="inlineStr">
+      <c r="F121" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive - CES (London)</t>
         </is>
@@ -28264,7 +28264,7 @@
           <t>Procurement, budgeting, and grants suite - Bonfire, Questica, eCivis (formerly GTY) - exhibited at NACUBO 2026, GFOA 2026</t>
         </is>
       </c>
-      <c r="F125" s="11" t="inlineStr">
+      <c r="F125" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Solutions Consultant only</t>
         </is>
@@ -28324,7 +28324,7 @@
           <t>Treasury platform for local government finance teams: AI reconciliation and cash forecasting - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F127" s="11" t="inlineStr">
+      <c r="F127" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Business Development Representativ only</t>
         </is>
@@ -28444,7 +28444,7 @@
           <t>Cloud treasury: debt management, GASB 87/96 lease accounting, and cash management for gov finance - exhibited at NACUBO 2026, GFOA 2026</t>
         </is>
       </c>
-      <c r="F131" s="9" t="inlineStr">
+      <c r="F131" s="10" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive (Charlotte, NC)</t>
         </is>
@@ -28684,7 +28684,7 @@
           <t>Aerial imagery and property data analytics for county assessors, GIS, and insurers - exhibited at IAAO 2026</t>
         </is>
       </c>
-      <c r="F139" s="9" t="inlineStr">
+      <c r="F139" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -28744,7 +28744,7 @@
           <t>cashVest liquidity analytics and treasury intelligence for counties, munis, and schools</t>
         </is>
       </c>
-      <c r="F141" s="11" t="inlineStr">
+      <c r="F141" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Senior Business Development Office only</t>
         </is>
@@ -28804,7 +28804,7 @@
           <t>HR, finance and ERP software - exhibited at APTA 2026, ICMA 2025, NACo 2026, NACUBO 2026, GFOA 2026, PSHRA 2026, NASCIO 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F143" s="9" t="inlineStr">
+      <c r="F143" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Japan, Tokyo)</t>
         </is>
@@ -28924,7 +28924,7 @@
           <t>Parcel mapping, GIS and assessment systems for county governments</t>
         </is>
       </c>
-      <c r="F147" s="9" t="inlineStr">
+      <c r="F147" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -29272,7 +29272,7 @@
           <t>Fund accounting and ERP software for cities and local governments, covering financials, payroll, utility billing and municipal court - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F159" s="9" t="inlineStr">
+      <c r="F159" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -29392,7 +29392,7 @@
           <t>Portfolio of vertical software businesses selling ERP, utility billing and public sector operations systems to local governments and utilities - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F163" s="9" t="inlineStr">
+      <c r="F163" s="10" t="inlineStr">
         <is>
           <t>Yes - (Remote) Sr Account Executive (26 Locations)</t>
         </is>
@@ -29510,7 +29510,7 @@
           <t>Free search marketplace for cooperative contracts (formerly CoProcure)</t>
         </is>
       </c>
-      <c r="F167" s="11" t="inlineStr">
+      <c r="F167" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -29630,7 +29630,7 @@
           <t>Electronic billing and payments for local government and utilities - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F171" s="9" t="inlineStr">
+      <c r="F171" s="10" t="inlineStr">
         <is>
           <t>Yes - Mid Market Account Executive (Boston, MA)</t>
         </is>
@@ -30050,9 +30050,9 @@
           <t>Source-to-pay eProcurement suite with dedicated public sector and higher-ed verticals - exhibited at NACUBO 2026, GFOA 2026</t>
         </is>
       </c>
-      <c r="F185" s="9" t="inlineStr">
-        <is>
-          <t>Yes - Strategic Account Manager (Remote)</t>
+      <c r="F185" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive/Enterprise Accou</t>
         </is>
       </c>
     </row>
@@ -30110,7 +30110,7 @@
           <t>Supplier ratings and performance reviews platform for public-sector buyers</t>
         </is>
       </c>
-      <c r="F187" s="11" t="inlineStr">
+      <c r="F187" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -30290,7 +30290,7 @@
           <t>AI-native ConcourseOS: procurement, permitting, courts, and billing across 450+ agencies (Bessemer-backed) - exhibited at NIGP 2026</t>
         </is>
       </c>
-      <c r="F193" s="11" t="inlineStr">
+      <c r="F193" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Founding GTM Engineer only</t>
         </is>
@@ -30468,7 +30468,7 @@
           <t>AI public-sector GTM intelligence: buying signals from gov/school board meetings, budgets, RFPs - sold to vendors selling to gov</t>
         </is>
       </c>
-      <c r="F199" s="9" t="inlineStr">
+      <c r="F199" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive - Mid Market (United States)</t>
         </is>
@@ -30578,7 +30578,7 @@
           <t>EProcurement and bid notification platforms for North American public buyers</t>
         </is>
       </c>
-      <c r="F203" s="9" t="inlineStr">
+      <c r="F203" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive (United States)</t>
         </is>
@@ -30844,7 +30844,7 @@
       </c>
       <c r="F212" s="22" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (London)</t>
+          <t>Yes - Account Executive (Singapore, Singapo)</t>
         </is>
       </c>
     </row>
@@ -30932,7 +30932,7 @@
           <t>Contract lifecycle management with FedRAMP and state/local government customers</t>
         </is>
       </c>
-      <c r="F215" s="9" t="inlineStr">
+      <c r="F215" s="10" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive (United States)</t>
         </is>
@@ -31352,7 +31352,7 @@
           <t>Cash and digital payments for child support, tolls and government billers</t>
         </is>
       </c>
-      <c r="F229" s="9" t="inlineStr">
+      <c r="F229" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Credit Unions/B (Remote)</t>
         </is>
@@ -31524,7 +31524,7 @@
           <t>Bill payment kiosks, portals, mobile apps and IVR for municipal agencies and utilities collecting resident payments - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F235" s="9" t="inlineStr">
+      <c r="F235" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -31884,7 +31884,7 @@
           <t>Earned wage access platform for employers - exhibited at NACo 2026</t>
         </is>
       </c>
-      <c r="F247" s="9" t="inlineStr">
+      <c r="F247" s="10" t="inlineStr">
         <is>
           <t>Yes - Business Development Manager (NYC Headquarters)</t>
         </is>
@@ -31994,7 +31994,7 @@
           <t>Payroll and HR software - exhibited at AB Show 2026</t>
         </is>
       </c>
-      <c r="F251" s="9" t="inlineStr">
+      <c r="F251" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -32114,7 +32114,7 @@
           <t>Pension, unemployment insurance and workforce systems for state agencies - exhibited at SNA ANC 2027</t>
         </is>
       </c>
-      <c r="F255" s="9" t="inlineStr">
+      <c r="F255" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -32174,7 +32174,7 @@
           <t>Employee benefits, enrollment and HR services for public sector employers</t>
         </is>
       </c>
-      <c r="F257" s="9" t="inlineStr">
+      <c r="F257" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Denver, Colorado)</t>
         </is>
@@ -32472,7 +32472,7 @@
           <t>Document-driven workflow for government procurement, budget and HR processes</t>
         </is>
       </c>
-      <c r="F267" s="11" t="inlineStr">
+      <c r="F267" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
@@ -33178,7 +33178,7 @@
           <t>Deathcare technology suite including cemetery and memorial management software</t>
         </is>
       </c>
-      <c r="F291" s="11" t="inlineStr">
+      <c r="F291" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -33520,7 +33520,7 @@
           <t>Endpoint management and security platform - exhibited at NACo 2026, NASCIO 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F303" s="11" t="inlineStr">
+      <c r="F303" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Business Analyst - Salesforce only</t>
         </is>
@@ -33580,7 +33580,7 @@
           <t>ChatGPT and the API, sold to public sector including named state and local government roles</t>
         </is>
       </c>
-      <c r="F305" s="11" t="inlineStr">
+      <c r="F305" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Account Director, Large Enterprise only</t>
         </is>
@@ -33858,7 +33858,7 @@
           <t>Strategic plan and KPI reporting (balanced scorecard) for local governments and enterprises</t>
         </is>
       </c>
-      <c r="F315" s="9" t="inlineStr">
+      <c r="F315" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -34910,7 +34910,7 @@
           <t>Open-source voting systems and risk-limiting audit tools for election offices</t>
         </is>
       </c>
-      <c r="F351" s="9" t="inlineStr">
+      <c r="F351" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Field Sales (United States)</t>
         </is>
@@ -37450,7 +37450,7 @@
           <t>Planning, budgeting and forecasting software - exhibited at ICMA 2025, NACUBO 2026, GFOA 2026</t>
         </is>
       </c>
-      <c r="F441" s="11" t="inlineStr">
+      <c r="F441" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -37558,7 +37558,7 @@
           <t>Purchasing card audit and compliance monitoring - exhibited at NIGP 2026</t>
         </is>
       </c>
-      <c r="F445" s="9" t="inlineStr">
+      <c r="F445" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -38356,7 +38356,7 @@
           <t>CRM and case management cloud software - exhibited at NACo 2026, NIGP 2026, NASWA 2025, NASCIO 2026, APHSA 2026, NatCon 2026, EDUCAUSE 2026, Healthcare IT Connect 2026, MESC 2026</t>
         </is>
       </c>
-      <c r="F477" s="9" t="inlineStr">
+      <c r="F477" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -38708,7 +38708,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/22/26)</t>
+          <t>Hiring AEs? (9/23/26)</t>
         </is>
       </c>
     </row>
@@ -38766,7 +38766,7 @@
           <t>Parks &amp; rec program management and booking platform founded by early Uber employees</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive (San Francisco, CA)</t>
         </is>
@@ -39120,7 +39120,7 @@
           <t>Parks and recreation management software; brands NextRec (formerly PerfectMind), Vermont Systems, RecDesk and ePACT - exhibited at AB Show 2026, NRPA 2026</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Shreveport, LA)</t>
         </is>
@@ -39360,9 +39360,9 @@
           <t>Team and league management apps for youth sports, with a business tier for rec orgs</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Account Manager, Large Market (Remote)</t>
         </is>
       </c>
     </row>
@@ -39840,7 +39840,7 @@
           <t>Club and league management platform for youth soccer organizations</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -40200,7 +40200,7 @@
           <t>Campground, park and license reservation systems for state park agencies</t>
         </is>
       </c>
-      <c r="F51" s="11" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Platform Solutions Engineer only</t>
         </is>
@@ -40260,7 +40260,7 @@
           <t>Campground reservation and management software for public and private campgrounds</t>
         </is>
       </c>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="F53" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Manager, Account Management only</t>
         </is>
@@ -40556,7 +40556,7 @@
           <t>Sports facility and program management for municipal and community facilities</t>
         </is>
       </c>
-      <c r="F63" s="11" t="inlineStr">
+      <c r="F63" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -40676,7 +40676,7 @@
           <t>AI drowning-detection and lifeguard assist for public aquatic centers</t>
         </is>
       </c>
-      <c r="F67" s="11" t="inlineStr">
+      <c r="F67" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -40856,7 +40856,7 @@
           <t>Central irrigation control and smart controllers for municipal parks</t>
         </is>
       </c>
-      <c r="F73" s="9" t="inlineStr">
+      <c r="F73" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -41396,7 +41396,7 @@
           <t>Weather safety platform: WBGT heat monitoring, lightning alerts, stations and sirens for parks and athletics</t>
         </is>
       </c>
-      <c r="F91" s="9" t="inlineStr">
+      <c r="F91" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive, SLED (Perry Weather Offi)</t>
         </is>
@@ -42054,7 +42054,7 @@
           <t>Short-term rental market data for tourism offices and city agencies</t>
         </is>
       </c>
-      <c r="F113" s="9" t="inlineStr">
+      <c r="F113" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Barcelona)</t>
         </is>
@@ -42294,7 +42294,7 @@
           <t>Event management SaaS: vendor applications, ticketing, maps, and sponsors for festivals and city events</t>
         </is>
       </c>
-      <c r="F121" s="9" t="inlineStr">
+      <c r="F121" s="10" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive</t>
         </is>
@@ -42354,7 +42354,7 @@
           <t>Venue and event management for convention centers and public authorities</t>
         </is>
       </c>
-      <c r="F123" s="11" t="inlineStr">
+      <c r="F123" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Director of Solutions Engineering only</t>
         </is>
@@ -42534,7 +42534,7 @@
           <t>Venue management, ticketing and POS for aquatic centers and attractions</t>
         </is>
       </c>
-      <c r="F129" s="9" t="inlineStr">
+      <c r="F129" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive - Mid-Market and (London, United Kin)</t>
         </is>
@@ -42772,7 +42772,7 @@
           <t>Event volunteer scheduling and check-in for festivals and public events</t>
         </is>
       </c>
-      <c r="F137" s="9" t="inlineStr">
+      <c r="F137" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive Level 2 (Remote, US)</t>
         </is>
@@ -42990,7 +42990,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/22/26)</t>
+          <t>Hiring AEs? (9/23/26)</t>
         </is>
       </c>
     </row>
@@ -43048,7 +43048,7 @@
           <t>CrisisAlert wearable panic buttons for school staff; 18M+ people covered</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Yes - Sales Executive - Pacific Northwes (Remote Worker - N/)</t>
         </is>
@@ -43168,7 +43168,7 @@
           <t>Device filtering, classroom management, and student wellness (Beacon)</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - New Business Executive - Strategic only</t>
         </is>
@@ -43702,7 +43702,7 @@
           <t>AI weapons detection and screening for schools and public buildings</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -43880,7 +43880,7 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -44292,7 +44292,7 @@
           <t>School bus telematics, electronic inspections, and ridership tracking</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>Yes - Sales Account Executive – Mid-Mark</t>
         </is>
@@ -45012,7 +45012,7 @@
           <t>Unified school-home communication platform - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F69" s="11" t="inlineStr">
+      <c r="F69" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -45132,7 +45132,7 @@
           <t>Capital program management and purchasing/AP compliance for 140+ California districts</t>
         </is>
       </c>
-      <c r="F73" s="9" t="inlineStr">
+      <c r="F73" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -45550,7 +45550,7 @@
           <t>Alternative student transportation for school districts (formerly ALC Schools): contracted vehicles and drivers for students a yellow bus cannot serve, with dispatch and tracking for the district - exhibited at NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F87" s="9" t="inlineStr">
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Southern Califo (Remote Southern Ca)</t>
         </is>
@@ -45670,7 +45670,7 @@
           <t>School and district websites, apps and communications for public schools</t>
         </is>
       </c>
-      <c r="F91" s="9" t="inlineStr">
+      <c r="F91" s="10" t="inlineStr">
         <is>
           <t>Yes - Sales Executive (Remote Worker - N/)</t>
         </is>
@@ -45910,7 +45910,7 @@
           <t>Dismissal, attendance and school safety workflow platform for districts</t>
         </is>
       </c>
-      <c r="F99" s="9" t="inlineStr">
+      <c r="F99" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -45970,9 +45970,9 @@
           <t>Single sign-on, rostering and usage analytics for public school districts - exhibited at CoSN 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F101" s="9" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -46136,7 +46136,7 @@
           <t>Digital hall pass, tardy tracking, behavior management, and campus engagement platform for K-12 schools and districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F107" s="9" t="inlineStr">
+      <c r="F107" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Manager (INTERNAL APPLICAN</t>
         </is>
@@ -46198,7 +46198,7 @@
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://boards-api.greenhou</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -46528,7 +46528,7 @@
           <t>Classroom browser monitoring, web filtering and student wellbeing alerting software for K-12 schools and districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F121" s="9" t="inlineStr">
+      <c r="F121" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -46642,7 +46642,7 @@
           <t>Student survey, MTSS, behavior analytics and early-warning software for K-12 school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F125" s="9" t="inlineStr">
+      <c r="F125" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -46806,7 +46806,7 @@
           <t>Phone-free school software that blocks distracting apps during class and records attendance for K-12 districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F131" s="9" t="inlineStr">
+      <c r="F131" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -46972,7 +46972,7 @@
           <t>AI service desk and service operations platform unifying IT, facilities, HR and transportation requests for K-12 districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F137" s="9" t="inlineStr">
+      <c r="F137" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -47086,7 +47086,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/22/26)</t>
+          <t>Hiring AEs? (9/23/26)</t>
         </is>
       </c>
     </row>
@@ -47116,7 +47116,7 @@
       </c>
       <c r="F2" s="39" t="inlineStr">
         <is>
-          <t>Yes - Account Manager - East Coast (2 Locations)</t>
+          <t>Unknown - HTTP 520 for https://cubic.wd1.myworkday</t>
         </is>
       </c>
     </row>
@@ -47144,7 +47144,7 @@
           <t>Justride fare payments SaaS used by hundreds of agencies</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager - UK only</t>
         </is>
@@ -47174,7 +47174,7 @@
           <t>Mobile fare payment app covering 200+ North American agencies</t>
         </is>
       </c>
-      <c r="F4" s="40" t="inlineStr">
+      <c r="F4" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -47234,7 +47234,7 @@
           <t>Automated fare collection plus parking and rail signalling systems (US office Lowell, MA)</t>
         </is>
       </c>
-      <c r="F6" s="40" t="inlineStr">
+      <c r="F6" s="39" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.scheidt-bachman</t>
         </is>
@@ -47294,7 +47294,7 @@
           <t>Account-based ticketing and open-loop EMV fare collection in 150+ cities (BPC Group)</t>
         </is>
       </c>
-      <c r="F8" s="40" t="inlineStr">
+      <c r="F8" s="39" t="inlineStr">
         <is>
           <t>Unknown - board is another company's - not read</t>
         </is>
@@ -47354,7 +47354,7 @@
           <t>KubaPay cloud fare collection and account-based ticketing in 500+ cities (ICM group, not Cubic)</t>
         </is>
       </c>
-      <c r="F10" s="40" t="inlineStr">
+      <c r="F10" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -47414,7 +47414,7 @@
           <t>Automated fare collection and tolling/ITS for US agencies (LA, Bay Area, DC); Samsung SDS lineage</t>
         </is>
       </c>
-      <c r="F12" s="40" t="inlineStr">
+      <c r="F12" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -47472,7 +47472,7 @@
           <t>Fareboxes, validators, and the Universal Platform for automated fare management</t>
         </is>
       </c>
-      <c r="F14" s="40" t="inlineStr">
+      <c r="F14" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -47530,7 +47530,7 @@
           <t>Transit scheduling, fare and paratransit software for public operators</t>
         </is>
       </c>
-      <c r="F16" s="40" t="inlineStr">
+      <c r="F16" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -47590,7 +47590,7 @@
           <t>Tolling operations and back-office payment services for toll agencies</t>
         </is>
       </c>
-      <c r="F18" s="40" t="inlineStr">
+      <c r="F18" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -47620,7 +47620,7 @@
           <t>Check-in/be-out mobile fare payment for public transport authorities</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Yes - Sales &amp; Business Development Manag</t>
         </is>
@@ -47650,7 +47650,7 @@
           <t>Account-based fare collection and validators for public transit operators</t>
         </is>
       </c>
-      <c r="F20" s="39" t="inlineStr">
+      <c r="F20" s="40" t="inlineStr">
         <is>
           <t>Yes - Senior Enterprise Account Executiv (Spain, Spain)</t>
         </is>
@@ -47710,7 +47710,7 @@
           <t>Bus ITS: CAD/AVL, real-time passenger info, and fleet health</t>
         </is>
       </c>
-      <c r="F22" s="40" t="inlineStr">
+      <c r="F22" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -47770,7 +47770,7 @@
           <t>Real-time transit data: arrival predictions and on-time performance</t>
         </is>
       </c>
-      <c r="F24" s="39" t="inlineStr">
+      <c r="F24" s="40" t="inlineStr">
         <is>
           <t>Yes - Senior Account Manager (United States)</t>
         </is>
@@ -47830,7 +47830,7 @@
           <t>myAvail enterprise transit management ITS and CAD/AVL for mid-size US agencies</t>
         </is>
       </c>
-      <c r="F26" s="40" t="inlineStr">
+      <c r="F26" s="39" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://availtec.com/career</t>
         </is>
@@ -47860,7 +47860,7 @@
           <t>HASTUS scheduling, run-cutting, and rostering for transit agencies and postal operators</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Director, Strategic Business Devel only</t>
         </is>
@@ -47890,7 +47890,7 @@
           <t>IVU.suite planning, scheduling, dispatch, and ticketing for transit and rail operators</t>
         </is>
       </c>
-      <c r="F28" s="40" t="inlineStr">
+      <c r="F28" s="39" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.ivu.com/career</t>
         </is>
@@ -47920,7 +47920,7 @@
           <t>Holding group of ~34 transit software brands under Constellation (Trapeze, Vontas, TransTrack, TripSpark, TransLoc)</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales &amp; Marketing Director only</t>
         </is>
@@ -47950,7 +47950,7 @@
           <t>Transit dispatch, CAD/AVL, and communications software (Modaxo brand, ex-Trapeze ITS)</t>
         </is>
       </c>
-      <c r="F30" s="40" t="inlineStr">
+      <c r="F30" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48010,7 +48010,7 @@
           <t>Consat Telematics real-time CAD/AVL, passenger info, and electromobility analytics (NA office Sudbury ON)</t>
         </is>
       </c>
-      <c r="F32" s="40" t="inlineStr">
+      <c r="F32" s="39" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.consat.com/care</t>
         </is>
@@ -48070,7 +48070,7 @@
           <t>Transit performance data warehousing, BI, and automated NTD reporting (Modaxo brand) - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F34" s="40" t="inlineStr">
+      <c r="F34" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -48124,7 +48124,7 @@
           <t>Cloud CAD/AVL and in-vehicle tech for transit agencies and campus systems (SDVOSB)</t>
         </is>
       </c>
-      <c r="F36" s="40" t="inlineStr">
+      <c r="F36" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48154,7 +48154,7 @@
           <t>iMarq mobile asset maintenance and MRO platform for transit, rail, and fleets</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -48184,7 +48184,7 @@
           <t>IBM Maximo consulting plus Mobile Informer EAM for transit agencies, airports, and utilities</t>
         </is>
       </c>
-      <c r="F38" s="40" t="inlineStr">
+      <c r="F38" s="39" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.interlocsolutio</t>
         </is>
@@ -48244,7 +48244,7 @@
           <t>Trainwise onboard train control/monitoring and Fleetwise wayside fleet management for transit</t>
         </is>
       </c>
-      <c r="F40" s="40" t="inlineStr">
+      <c r="F40" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48304,7 +48304,7 @@
           <t>Rail terminal management, track inspection, and crew compliance for short lines and commuter rail</t>
         </is>
       </c>
-      <c r="F42" s="40" t="inlineStr">
+      <c r="F42" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48334,7 +48334,7 @@
           <t>SCADA systems and the SentientQ automation platform for rail transit, LRT, and utilities</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>Yes - Business Development Manager</t>
         </is>
@@ -48364,7 +48364,7 @@
           <t>Ultra-wideband train positioning, worker protection, and ATP for transit agencies (NYC MTA)</t>
         </is>
       </c>
-      <c r="F44" s="40" t="inlineStr">
+      <c r="F44" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48424,7 +48424,7 @@
           <t>CylusOne rail OT cybersecurity: threat detection for signaling, trackside, and onboard networks</t>
         </is>
       </c>
-      <c r="F46" s="40" t="inlineStr">
+      <c r="F46" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48482,7 +48482,7 @@
           <t>ConnX Maestro unified communications and contact center for transit agencies (SEPTA)</t>
         </is>
       </c>
-      <c r="F48" s="40" t="inlineStr">
+      <c r="F48" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48540,7 +48540,7 @@
           <t>Non-invasive sensors and cloud analytics for elevator, escalator, and HVAC uptime in transit stations</t>
         </is>
       </c>
-      <c r="F50" s="40" t="inlineStr">
+      <c r="F50" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48598,7 +48598,7 @@
           <t>Virtual Optical Fiber high-speed data offload between transit vehicles and depots</t>
         </is>
       </c>
-      <c r="F52" s="40" t="inlineStr">
+      <c r="F52" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48658,7 +48658,7 @@
           <t>AI smart inspection for rail infrastructure: sensor robot plus defect detection and predictive maintenance</t>
         </is>
       </c>
-      <c r="F54" s="40" t="inlineStr">
+      <c r="F54" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48714,7 +48714,7 @@
           <t>Mobile video surveillance, DVRs, and MotoTrax analytics for transit, school, and municipal fleets - exhibited at CTAA EXPO 2026, NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F56" s="39" t="inlineStr">
+      <c r="F56" s="40" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -48774,7 +48774,7 @@
           <t>Onboard transit systems: Horizon CCTV, NetSpire passenger info, iConnex real-time (US in Buffalo NY)</t>
         </is>
       </c>
-      <c r="F58" s="40" t="inlineStr">
+      <c r="F58" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48834,7 +48834,7 @@
           <t>Intelligent video, AI stop-arm analytics, and cloud safety platforms for transit and school districts - exhibited at CTAA EXPO 2026, NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F60" s="40" t="inlineStr">
+      <c r="F60" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48894,7 +48894,7 @@
           <t>AI dashcams, MDVRs, and fleet video telematics for transit, school bus, and commercial fleets (US: Houston)</t>
         </is>
       </c>
-      <c r="F62" s="40" t="inlineStr">
+      <c r="F62" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48954,7 +48954,7 @@
           <t>3D AI people-flow sensors for passenger counting, queue, and dwell in transit hubs and airports</t>
         </is>
       </c>
-      <c r="F64" s="40" t="inlineStr">
+      <c r="F64" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49014,7 +49014,7 @@
           <t>Automatic passenger counting hardware and analysis software for bus, rail, and paratransit</t>
         </is>
       </c>
-      <c r="F66" s="40" t="inlineStr">
+      <c r="F66" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -49074,7 +49074,7 @@
           <t>Video telematics and driver safety for municipal and transit fleets - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
-      <c r="F68" s="40" t="inlineStr">
+      <c r="F68" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49104,7 +49104,7 @@
           <t>AI dashcam and driver coaching for public fleets</t>
         </is>
       </c>
-      <c r="F69" s="9" t="inlineStr">
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Mid-Market (USA)</t>
         </is>
@@ -49134,7 +49134,7 @@
           <t>Telematics devices and fleet tracking software for public fleets</t>
         </is>
       </c>
-      <c r="F70" s="40" t="inlineStr">
+      <c r="F70" s="39" t="inlineStr">
         <is>
           <t>Unknown - no jobs parsed from iCIMS portal</t>
         </is>
@@ -49164,7 +49164,7 @@
           <t>Fleet maintenance software for cities, counties and transit agencies</t>
         </is>
       </c>
-      <c r="F71" s="9" t="inlineStr">
+      <c r="F71" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Remote Worker)</t>
         </is>
@@ -49194,7 +49194,7 @@
           <t>FleetWave fleet asset management for public sector fleets</t>
         </is>
       </c>
-      <c r="F72" s="40" t="inlineStr">
+      <c r="F72" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49224,7 +49224,7 @@
           <t>Fleet maintenance management software for transit and government fleets</t>
         </is>
       </c>
-      <c r="F73" s="9" t="inlineStr">
+      <c r="F73" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -49254,7 +49254,7 @@
           <t>FleetCommander motor pool and vehicle sharing for agencies</t>
         </is>
       </c>
-      <c r="F74" s="40" t="inlineStr">
+      <c r="F74" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -49314,7 +49314,7 @@
           <t>Fleet data analytics and benchmarking for public and utility fleets</t>
         </is>
       </c>
-      <c r="F76" s="40" t="inlineStr">
+      <c r="F76" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -49344,7 +49344,7 @@
           <t>Digital vehicle inspections and maintenance for municipal fleets</t>
         </is>
       </c>
-      <c r="F77" s="11" t="inlineStr">
+      <c r="F77" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Operations Manager, Customer Succe only</t>
         </is>
@@ -49374,7 +49374,7 @@
           <t>Fleet automation and motor pool platform for public agencies</t>
         </is>
       </c>
-      <c r="F78" s="40" t="inlineStr">
+      <c r="F78" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49434,7 +49434,7 @@
           <t>Onboard surveillance and video management for transit fleets</t>
         </is>
       </c>
-      <c r="F80" s="40" t="inlineStr">
+      <c r="F80" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -49554,7 +49554,7 @@
           <t>On-demand transit and shared mobility software for public agencies</t>
         </is>
       </c>
-      <c r="F84" s="40" t="inlineStr">
+      <c r="F84" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -49614,7 +49614,7 @@
           <t>Parking meters, kiosks and transit fare systems for cities</t>
         </is>
       </c>
-      <c r="F86" s="40" t="inlineStr">
+      <c r="F86" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49674,7 +49674,7 @@
           <t>Mobile parking payments for city and municipal parking operators</t>
         </is>
       </c>
-      <c r="F88" s="39" t="inlineStr">
+      <c r="F88" s="40" t="inlineStr">
         <is>
           <t>Yes - Corporate Sales Executive</t>
         </is>
@@ -49734,7 +49734,7 @@
           <t>Parking access and revenue control systems for public garages</t>
         </is>
       </c>
-      <c r="F90" s="40" t="inlineStr">
+      <c r="F90" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49794,7 +49794,7 @@
           <t>Automated enforcement: school-zone speed, red-light, and bus-lane cameras - exhibited at North Carolina Sheriffs' Association 2026</t>
         </is>
       </c>
-      <c r="F92" s="39" t="inlineStr">
+      <c r="F92" s="40" t="inlineStr">
         <is>
           <t>Yes - Mass Market Account Executive (Arizona_Remote)</t>
         </is>
@@ -49854,7 +49854,7 @@
           <t>Multimodal trip planning app plus a paid agency suite (white-label apps, sponsored Royale, rider data) - exhibited at CTAA EXPO 2026, NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F94" s="40" t="inlineStr">
+      <c r="F94" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49884,7 +49884,7 @@
           <t>Solar e-paper real-time passenger information displays and cloud CMS for bus stops and stations</t>
         </is>
       </c>
-      <c r="F95" s="9" t="inlineStr">
+      <c r="F95" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -49914,7 +49914,7 @@
           <t>ePaper Digital Bus Stop, SmartStop kiosks, and CPAM content management for transit agencies</t>
         </is>
       </c>
-      <c r="F96" s="40" t="inlineStr">
+      <c r="F96" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50034,7 +50034,7 @@
           <t>Bus destination displays, controllers, and next-stop passenger information systems</t>
         </is>
       </c>
-      <c r="F100" s="40" t="inlineStr">
+      <c r="F100" s="39" t="inlineStr">
         <is>
           <t>Unknown - HTTP 403 for https://www.hanoverdisplays</t>
         </is>
@@ -50092,7 +50092,7 @@
           <t>TRACC travel-time and accessibility analysis plus transport datasets for government transport agencies</t>
         </is>
       </c>
-      <c r="F102" s="40" t="inlineStr">
+      <c r="F102" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50152,7 +50152,7 @@
           <t>Solar smart bus stops with edge AI plus the ORA platform: signage, lane enforcement, passenger counting</t>
         </is>
       </c>
-      <c r="F104" s="40" t="inlineStr">
+      <c r="F104" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50212,7 +50212,7 @@
           <t>Real-time transit display screens and rider information for agencies and cities</t>
         </is>
       </c>
-      <c r="F106" s="40" t="inlineStr">
+      <c r="F106" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50242,7 +50242,7 @@
           <t>On-demand transit, paratransit, and network planning software for agencies - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F107" s="9" t="inlineStr">
+      <c r="F107" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Western Europe (Paris)</t>
         </is>
@@ -50272,7 +50272,7 @@
           <t>Elevated automated transit pods on prefabricated guideways (ex-skyTran team) for cities and campuses</t>
         </is>
       </c>
-      <c r="F108" s="40" t="inlineStr">
+      <c r="F108" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50332,7 +50332,7 @@
           <t>On-demand microtransit software with rider/driver apps and AI dispatch for large agencies - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F110" s="39" t="inlineStr">
+      <c r="F110" s="40" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -50392,7 +50392,7 @@
           <t>Assisted-mobility platform and driver network delivering ADA paratransit and door-through-door trips - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F112" s="40" t="inlineStr">
+      <c r="F112" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50452,7 +50452,7 @@
           <t>Transit management software for paratransit, demand-response, microtransit, and taxi fleets - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F114" s="40" t="inlineStr">
+      <c r="F114" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50512,7 +50512,7 @@
           <t>Autonomous vehicle technology and driverless shuttle service for transit agencies and cities</t>
         </is>
       </c>
-      <c r="F116" s="40" t="inlineStr">
+      <c r="F116" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -50542,9 +50542,9 @@
           <t>Turnkey autonomous shuttle operations for transit agencies, airports, and communities</t>
         </is>
       </c>
-      <c r="F117" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -50572,7 +50572,7 @@
           <t>flowride.ai SAE Level-4 automated driving software retrofitted onto full-size electric transit buses</t>
         </is>
       </c>
-      <c r="F118" s="40" t="inlineStr">
+      <c r="F118" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50632,7 +50632,7 @@
           <t>Assisted senior and accessible transportation platform serving agency paratransit overflow in 35+ metros</t>
         </is>
       </c>
-      <c r="F120" s="40" t="inlineStr">
+      <c r="F120" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50692,7 +50692,7 @@
           <t>White-label multimodal TDM and commute platform for regional agencies, employers, and campuses</t>
         </is>
       </c>
-      <c r="F122" s="40" t="inlineStr">
+      <c r="F122" s="39" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.rideshark.com/c</t>
         </is>
@@ -50744,7 +50744,7 @@
           <t>TripMaster paratransit scheduling and dispatch software for public transit providers</t>
         </is>
       </c>
-      <c r="F124" s="40" t="inlineStr">
+      <c r="F124" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50802,7 +50802,7 @@
           <t>Demand-responsive transit dispatch and booking software for transit agencies - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F126" s="40" t="inlineStr">
+      <c r="F126" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50862,7 +50862,7 @@
           <t>Electric on-demand shuttle service contracted by cities and transit agencies - exhibited at WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F128" s="40" t="inlineStr">
+      <c r="F128" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -50922,7 +50922,7 @@
           <t>On-demand ridepooling and mobility analytics software for public transit authorities</t>
         </is>
       </c>
-      <c r="F130" s="40" t="inlineStr">
+      <c r="F130" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50982,7 +50982,7 @@
           <t>Ridepooling operations and autonomous shuttle services for public transport partners</t>
         </is>
       </c>
-      <c r="F132" s="40" t="inlineStr">
+      <c r="F132" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51034,7 +51034,7 @@
           <t>ADA paratransit eligibility, call center and mobility management technology for agencies</t>
         </is>
       </c>
-      <c r="F134" s="40" t="inlineStr">
+      <c r="F134" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51094,7 +51094,7 @@
           <t>Whoosh autonomous cable-driven transit pods for cities and campuses</t>
         </is>
       </c>
-      <c r="F136" s="40" t="inlineStr">
+      <c r="F136" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51154,7 +51154,7 @@
           <t>Autonomous shuttle vehicles for public transport and campus deployments</t>
         </is>
       </c>
-      <c r="F138" s="40" t="inlineStr">
+      <c r="F138" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51214,7 +51214,7 @@
           <t>Electric and autonomous buses sold to public transit operators worldwide</t>
         </is>
       </c>
-      <c r="F140" s="40" t="inlineStr">
+      <c r="F140" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51274,7 +51274,7 @@
           <t>Automated people mover and group rapid transit systems for public authorities</t>
         </is>
       </c>
-      <c r="F142" s="40" t="inlineStr">
+      <c r="F142" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -51334,7 +51334,7 @@
           <t>Autonomy software powering driverless shuttles for transit and airport operators</t>
         </is>
       </c>
-      <c r="F144" s="40" t="inlineStr">
+      <c r="F144" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -51394,7 +51394,7 @@
           <t>Autonomous shuttles for public transport agencies, airports and campuses</t>
         </is>
       </c>
-      <c r="F146" s="40" t="inlineStr">
+      <c r="F146" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51454,7 +51454,7 @@
           <t>Leading mobile parking payments app (EasyPark Group)</t>
         </is>
       </c>
-      <c r="F148" s="40" t="inlineStr">
+      <c r="F148" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -51484,9 +51484,9 @@
           <t>Smart single-space parking meters and enforcement systems</t>
         </is>
       </c>
-      <c r="F149" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Sr. Client Success Manager only</t>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -51514,7 +51514,7 @@
           <t>Computer vision curb management and automated loading-zone payments</t>
         </is>
       </c>
-      <c r="F150" s="40" t="inlineStr">
+      <c r="F150" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -51574,7 +51574,7 @@
           <t>Gateless LPR parking operations (GLIDEPARCS) for private lots, universities, and some municipalities</t>
         </is>
       </c>
-      <c r="F152" s="40" t="inlineStr">
+      <c r="F152" s="39" t="inlineStr">
         <is>
           <t>Unknown - page too small - likely JS-rendered</t>
         </is>
@@ -51634,7 +51634,7 @@
           <t>Towing lifecycle software for city towing programs and impound management (ex-AutoReturn + TSD)</t>
         </is>
       </c>
-      <c r="F154" s="40" t="inlineStr">
+      <c r="F154" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -51664,7 +51664,7 @@
           <t>Parking permits, enforcement, PARCS, and pay stations for universities and cities (Verra Mobility)</t>
         </is>
       </c>
-      <c r="F155" s="9" t="inlineStr">
+      <c r="F155" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -51694,7 +51694,7 @@
           <t>Sentry solar smart kiosks and vision-based automated parking enforcement</t>
         </is>
       </c>
-      <c r="F156" s="40" t="inlineStr">
+      <c r="F156" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51724,7 +51724,7 @@
           <t>Mobility and curb/parking technology platform - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F157" s="9" t="inlineStr">
+      <c r="F157" s="10" t="inlineStr">
         <is>
           <t>Yes - Junior B2B Account Executive (Prague)</t>
         </is>
@@ -51754,7 +51754,7 @@
           <t>Single-space smart parking meters and pay stations for municipalities</t>
         </is>
       </c>
-      <c r="F158" s="40" t="inlineStr">
+      <c r="F158" s="39" t="inlineStr">
         <is>
           <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
@@ -51814,7 +51814,7 @@
           <t>Wireless parking occupancy sensors for city and campus parking</t>
         </is>
       </c>
-      <c r="F160" s="40" t="inlineStr">
+      <c r="F160" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51874,7 +51874,7 @@
           <t>Smart parking sensors and LoRaWAN networks for cities</t>
         </is>
       </c>
-      <c r="F162" s="40" t="inlineStr">
+      <c r="F162" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -51934,7 +51934,7 @@
           <t>Parking payments, permits and enforcement software for municipalities</t>
         </is>
       </c>
-      <c r="F164" s="40" t="inlineStr">
+      <c r="F164" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51994,7 +51994,7 @@
           <t>Parking citation processing and permit services for California cities</t>
         </is>
       </c>
-      <c r="F166" s="40" t="inlineStr">
+      <c r="F166" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52054,7 +52054,7 @@
           <t>Parking citation, permit and enforcement management software for agencies</t>
         </is>
       </c>
-      <c r="F168" s="40" t="inlineStr">
+      <c r="F168" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52110,7 +52110,7 @@
           <t>Control room video wall visualization software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F170" s="40" t="inlineStr">
+      <c r="F170" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -52162,7 +52162,7 @@
           <t>Transit fare collection and ticketing software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F172" s="40" t="inlineStr">
+      <c r="F172" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52210,7 +52210,7 @@
           <t>Infrastructure engineering and asset software - exhibited at APTA 2026, AWWA ACE 2026</t>
         </is>
       </c>
-      <c r="F174" s="40" t="inlineStr">
+      <c r="F174" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52262,7 +52262,7 @@
           <t>Fuel and fleet management systems - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F176" s="40" t="inlineStr">
+      <c r="F176" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -52312,7 +52312,7 @@
           <t>Transit ITS, fare collection, scheduling software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F178" s="40" t="inlineStr">
+      <c r="F178" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52368,7 +52368,7 @@
           <t>Ticketing, traffic and transit management systems - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F180" s="40" t="inlineStr">
+      <c r="F180" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52392,7 +52392,7 @@
           <t>Security and intelligence analytics software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F181" s="9" t="inlineStr">
+      <c r="F181" s="10" t="inlineStr">
         <is>
           <t>Yes - Enterprise Sales Executive – New L (2 Locations)</t>
         </is>
@@ -52416,7 +52416,7 @@
           <t>LiDAR 3D digital twin capture for transit - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F182" s="40" t="inlineStr">
+      <c r="F182" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52464,7 +52464,7 @@
           <t>Medical transportation ride management software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F184" s="40" t="inlineStr">
+      <c r="F184" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52514,7 +52514,7 @@
           <t>AI video analytics perimeter security software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F186" s="40" t="inlineStr">
+      <c r="F186" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -52562,7 +52562,7 @@
           <t>Transit CAD/AVL, APC, passenger information systems - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F188" s="40" t="inlineStr">
+      <c r="F188" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52586,7 +52586,7 @@
           <t>GPS fleet tracking and telematics software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F189" s="9" t="inlineStr">
+      <c r="F189" s="10" t="inlineStr">
         <is>
           <t>Yes - Sales Account Executive – Mid-Mark</t>
         </is>
@@ -52616,7 +52616,7 @@
           <t>EV fleet charge management software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F190" s="40" t="inlineStr">
+      <c r="F190" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -52664,7 +52664,7 @@
           <t>Immersive VR training software platform - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F192" s="40" t="inlineStr">
+      <c r="F192" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52728,7 +52728,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/22/26)</t>
+          <t>Hiring AEs? (9/23/26)</t>
         </is>
       </c>
     </row>
@@ -52846,7 +52846,7 @@
           <t>Autonomous off-grid solar streetlights with remote monitoring; 1,000+ municipalities, 43 states (French parent)</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -53386,7 +53386,7 @@
           <t>Aluminum and steel lighting poles for municipal and DOT projects</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -53446,7 +53446,7 @@
           <t>Adaptive smart street lighting sensors and CMS for municipalities</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -53506,7 +53506,7 @@
           <t>Street lighting luminaires and connected controls for public authorities</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -53986,7 +53986,7 @@
           <t>Exterior LED site and streetscape lighting for public projects</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -54046,7 +54046,7 @@
           <t>Pole-mounted sensors + AI (Gridscope) detecting grid faults, vegetation strikes, and wildfire-risk events</t>
         </is>
       </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="F45" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
@@ -54106,7 +54106,7 @@
           <t>Satellite + AI vegetation management (IVMS) and climate/asset risk SaaS for utilities</t>
         </is>
       </c>
-      <c r="F47" s="11" t="inlineStr">
+      <c r="F47" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Business Analyst - Customer Succes only</t>
         </is>
@@ -54166,7 +54166,7 @@
           <t>EV ARC transportable solar EV charging and storage for government fleets (Nasdaq: BEEM; ex-Envision Solar)</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -54286,7 +54286,7 @@
           <t>Metering, CIS, billing and grid analytics for public power utilities</t>
         </is>
       </c>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="F53" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -54438,7 +54438,7 @@
       </c>
       <c r="F58" s="45" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -54466,7 +54466,7 @@
           <t>Smart grid AMI and grid analytics for public power utilities and co-ops</t>
         </is>
       </c>
-      <c r="F59" s="11" t="inlineStr">
+      <c r="F59" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Office &amp; Sales Support Coordinator only</t>
         </is>
@@ -54706,7 +54706,7 @@
           <t>DERMS and virtual power plant programs for utilities including public power</t>
         </is>
       </c>
-      <c r="F67" s="11" t="inlineStr">
+      <c r="F67" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Engineer only</t>
         </is>
@@ -54946,7 +54946,7 @@
           <t>Utility bill management and energy analytics for cities, counties and schools</t>
         </is>
       </c>
-      <c r="F75" s="9" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive</t>
         </is>
@@ -55184,7 +55184,7 @@
           <t>Outage notification, billing, and omnichannel customer communication platform for investor-owned, municipal, and cooperative utilities - exhibited at APPA Public Power 2026</t>
         </is>
       </c>
-      <c r="F83" s="9" t="inlineStr">
+      <c r="F83" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Executive (US - Remote)</t>
         </is>
@@ -55598,7 +55598,7 @@
           <t>Geospatial network design and field software for telecom and public utilities</t>
         </is>
       </c>
-      <c r="F97" s="11" t="inlineStr">
+      <c r="F97" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Engineer only</t>
         </is>
@@ -55718,7 +55718,7 @@
           <t>Broadband grant, challenge process and mapping software for state broadband offices</t>
         </is>
       </c>
-      <c r="F101" s="11" t="inlineStr">
+      <c r="F101" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Product Solutions Engineer only</t>
         </is>
@@ -56194,7 +56194,7 @@
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - HTTP 404 for https://sifinetworks.com/co</t>
         </is>
       </c>
     </row>
@@ -56286,7 +56286,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/22/26)</t>
+          <t>Hiring AEs? (9/23/26)</t>
         </is>
       </c>
     </row>
@@ -56756,7 +56756,7 @@
           <t>Aviation design and simulation software (AviPLAN, AeroTURN, GuideSIGN) used by airport planners for aircraft movement, apron layout and airside safety analysis.</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Sales)</t>
         </is>
@@ -57172,7 +57172,7 @@
           <t>Airport weather observation systems and runway condition sensors for airports - exhibited at NACE 2026</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -57232,7 +57232,7 @@
           <t>Bird-strike avoidance radar and wildlife management systems for airports</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -57352,7 +57352,7 @@
           <t>ARINC airport systems portfolio: vMUSE common-use passenger processing, SelfPass biometrics, self bag drop, AODB/resource management, FIDS and airport communications sold to airport authorities.</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -57590,7 +57590,7 @@
           <t>Passenger flow, queue measurement and airport revenue software for airport operators</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>Yes - Sales Director Americas (US-based within th)</t>
         </is>
@@ -57710,7 +57710,7 @@
           <t>Gate, docking guidance and apron systems for airport operators</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -57890,7 +57890,7 @@
           <t>Self-service kiosks, bag drop and passenger processing for airports</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -58070,7 +58070,7 @@
           <t>Airport IQ operations, property and lease management software for airports</t>
         </is>
       </c>
-      <c r="F61" s="9" t="inlineStr">
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>Yes - Senior Account Executive</t>
         </is>
@@ -58610,7 +58610,7 @@
           <t>Biometric identity, TSA PreCheck enrollment and airport boarding systems</t>
         </is>
       </c>
-      <c r="F79" s="9" t="inlineStr">
+      <c r="F79" s="10" t="inlineStr">
         <is>
           <t>Yes - Key Account Manager - Smart Biomet</t>
         </is>
@@ -58670,7 +58670,7 @@
           <t>Biometric identity lanes operated under airport and TSA agreements</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr">
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive (C1 - (New York, New York)</t>
         </is>
@@ -58790,7 +58790,7 @@
           <t>Perimeter intrusion detection and fence sensors for airports and utilities</t>
         </is>
       </c>
-      <c r="F85" s="9" t="inlineStr">
+      <c r="F85" s="10" t="inlineStr">
         <is>
           <t>Yes - Business Development Manager (Ottawa, Ontario, C)</t>
         </is>
@@ -59028,7 +59028,7 @@
           <t>Automated vehicle inspection portals for airports, borders and government</t>
         </is>
       </c>
-      <c r="F93" s="9" t="inlineStr">
+      <c r="F93" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -59148,7 +59148,7 @@
           <t>Computer-vision checkout-free parking payment platform (drive-in/drive-out billing) plus parking operations and revenue management for airports; owner of SP+.</t>
         </is>
       </c>
-      <c r="F97" s="9" t="inlineStr">
+      <c r="F97" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Remote USA)</t>
         </is>
@@ -59326,7 +59326,7 @@
           <t>Airport parking reservations and demand channel for airport operators</t>
         </is>
       </c>
-      <c r="F103" s="9" t="inlineStr">
+      <c r="F103" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -59386,7 +59386,7 @@
           <t>Full-service automated parking operations for cities and airports</t>
         </is>
       </c>
-      <c r="F105" s="11" t="inlineStr">
+      <c r="F105" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Development Representative only</t>
         </is>
@@ -59506,7 +59506,7 @@
           <t>AVI readers and ground transportation management systems for airports</t>
         </is>
       </c>
-      <c r="F109" s="9" t="inlineStr">
+      <c r="F109" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -59746,7 +59746,7 @@
           <t>Web-based capital program and construction project management software (cost, contracts, documents, scheduling) used by airport owner-operators and public agencies.</t>
         </is>
       </c>
-      <c r="F117" s="9" t="inlineStr">
+      <c r="F117" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -59810,7 +59810,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/22/26)</t>
+          <t>Hiring AEs? (9/23/26)</t>
         </is>
       </c>
     </row>
@@ -60146,7 +60146,7 @@
           <t>Digital courtroom recording and speech recognition systems for courts</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -60264,7 +60264,7 @@
           <t>Criminal justice data collection and public dashboards for counties and states</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -60324,7 +60324,7 @@
           <t>Cloud ediscovery and litigation platform for law firms, corporations, county DAs, and state AGs - exhibited at IMLA 2026, NASCIO 2026</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive (Stat (United States)</t>
         </is>
@@ -60384,7 +60384,7 @@
           <t>PROSECUTORbyKarpel case management software for prosecutor offices - exhibited at IMLA 2026</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Remote Worker - N/)</t>
         </is>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -296,8 +296,8 @@
     <xf numFmtId="1" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/23/26)</t>
+          <t>Hiring AEs? (9/25/26)</t>
         </is>
       </c>
     </row>
@@ -2100,9 +2100,9 @@
           <t>Autonomous drones for police DFR programs and public-sector inspection - exhibited at NLC City Summit 2026, IAFC FRI 2026</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>Yes - Account Executive, Corporate Secur (2 Locations)</t>
+          <t>Yes - Account Executive, Federal Civilia (US Remote)</t>
         </is>
       </c>
     </row>
@@ -3330,9 +3330,9 @@
           <t>Drone-as-first-responder software and hardware auto-launching to 911 calls</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive</t>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>Yes - Associate Sales Executive (Waltham, MA)</t>
+          <t>Yes - Senior Sales Executive (2 Locations)</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -6282,9 +6282,9 @@
           <t>Pediatric emergency dosing system and app for EMS agencies</t>
         </is>
       </c>
-      <c r="F181" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Enterprise Account Executive</t>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/23/26)</t>
+          <t>Hiring AEs? (9/25/26)</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 500 for https://company.getinsured.</t>
         </is>
       </c>
     </row>
@@ -12904,9 +12904,9 @@
           <t>Crisis response, closed-loop referral, care management, and bed board software for behavioral health agencies - exhibited at NatCon 2026</t>
         </is>
       </c>
-      <c r="F64" s="63" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F64" s="65" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - VP of Customer Success only</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/23/26)</t>
+          <t>Hiring AEs? (9/25/26)</t>
         </is>
       </c>
     </row>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="F72" s="70" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Vice President, Sales only</t>
+          <t>Sales (non-AE) - Senior Solutions Engineer only</t>
         </is>
       </c>
     </row>
@@ -16760,9 +16760,9 @@
           <t>Student billing, payments, net price calculator, and pre-collections software for colleges and universities - exhibited at NACUBO 2026</t>
         </is>
       </c>
-      <c r="F86" s="69" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F86" s="70" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/23/26)</t>
+          <t>Hiring AEs? (9/25/26)</t>
         </is>
       </c>
     </row>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/23/26)</t>
+          <t>Hiring AEs? (9/25/26)</t>
         </is>
       </c>
     </row>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - non-JSON response</t>
         </is>
       </c>
     </row>
@@ -22712,7 +22712,7 @@
       </c>
       <c r="F177" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (US | Illinois | Ch)</t>
+          <t>Yes - Enterprise Account Executive (US | Massachusetts)</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/23/26)</t>
+          <t>Hiring AEs? (9/25/26)</t>
         </is>
       </c>
     </row>
@@ -24684,7 +24684,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>Yes - Local Government Account Executive</t>
+          <t>Yes - Enterprise Account Executive - Col</t>
         </is>
       </c>
     </row>
@@ -26690,9 +26690,9 @@
           <t>Social media management, listening, archiving and community engagement platform built for government communications teams - exhibited at 3CMA 2026</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -26858,9 +26858,9 @@
           <t>Permitting, licensing, and code enforcement platform for state and local government - exhibited at NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive (Remote Based - US)</t>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Business Development Representativ only</t>
         </is>
       </c>
     </row>
@@ -26890,7 +26890,7 @@
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (US | Illinois | Ch)</t>
+          <t>Yes - Enterprise Account Executive (US | Massachusetts)</t>
         </is>
       </c>
     </row>
@@ -30844,7 +30844,7 @@
       </c>
       <c r="F212" s="22" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Singapore, Singapo)</t>
+          <t>Yes - Account Executive (London)</t>
         </is>
       </c>
     </row>
@@ -35212,7 +35212,7 @@
       </c>
       <c r="F361" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 404 for https://www.easyvotesolutio</t>
         </is>
       </c>
     </row>
@@ -36530,9 +36530,9 @@
           <t>Research databases, ebook collections and discovery software licensed to public libraries, academic libraries, schools and healthcare organizations - exhibited at PLA 2026</t>
         </is>
       </c>
-      <c r="F408" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Customer Account Specialist, FOLIO only</t>
+      <c r="F408" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Regional Sales Manager, K12 &amp; Publ</t>
         </is>
       </c>
     </row>
@@ -38708,7 +38708,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/23/26)</t>
+          <t>Hiring AEs? (9/25/26)</t>
         </is>
       </c>
     </row>
@@ -42536,7 +42536,7 @@
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive - Mid-Market and (London, United Kin)</t>
+          <t>Yes - Enterprise Account Executive - AME (Austin, Texas)</t>
         </is>
       </c>
     </row>
@@ -42990,7 +42990,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/23/26)</t>
+          <t>Hiring AEs? (9/25/26)</t>
         </is>
       </c>
     </row>
@@ -43880,9 +43880,9 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -47086,7 +47086,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/23/26)</t>
+          <t>Hiring AEs? (9/25/26)</t>
         </is>
       </c>
     </row>
@@ -47116,7 +47116,7 @@
       </c>
       <c r="F2" s="39" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 520 for https://cubic.wd1.myworkday</t>
+          <t>Yes - Account Manager - East Coast (2 Locations)</t>
         </is>
       </c>
     </row>
@@ -47174,7 +47174,7 @@
           <t>Mobile fare payment app covering 200+ North American agencies</t>
         </is>
       </c>
-      <c r="F4" s="39" t="inlineStr">
+      <c r="F4" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -47234,7 +47234,7 @@
           <t>Automated fare collection plus parking and rail signalling systems (US office Lowell, MA)</t>
         </is>
       </c>
-      <c r="F6" s="39" t="inlineStr">
+      <c r="F6" s="40" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.scheidt-bachman</t>
         </is>
@@ -47294,7 +47294,7 @@
           <t>Account-based ticketing and open-loop EMV fare collection in 150+ cities (BPC Group)</t>
         </is>
       </c>
-      <c r="F8" s="39" t="inlineStr">
+      <c r="F8" s="40" t="inlineStr">
         <is>
           <t>Unknown - board is another company's - not read</t>
         </is>
@@ -47354,7 +47354,7 @@
           <t>KubaPay cloud fare collection and account-based ticketing in 500+ cities (ICM group, not Cubic)</t>
         </is>
       </c>
-      <c r="F10" s="39" t="inlineStr">
+      <c r="F10" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -47414,7 +47414,7 @@
           <t>Automated fare collection and tolling/ITS for US agencies (LA, Bay Area, DC); Samsung SDS lineage</t>
         </is>
       </c>
-      <c r="F12" s="39" t="inlineStr">
+      <c r="F12" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -47472,7 +47472,7 @@
           <t>Fareboxes, validators, and the Universal Platform for automated fare management</t>
         </is>
       </c>
-      <c r="F14" s="39" t="inlineStr">
+      <c r="F14" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -47502,7 +47502,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -47530,7 +47530,7 @@
           <t>Transit scheduling, fare and paratransit software for public operators</t>
         </is>
       </c>
-      <c r="F16" s="39" t="inlineStr">
+      <c r="F16" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -47590,7 +47590,7 @@
           <t>Tolling operations and back-office payment services for toll agencies</t>
         </is>
       </c>
-      <c r="F18" s="39" t="inlineStr">
+      <c r="F18" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -47650,7 +47650,7 @@
           <t>Account-based fare collection and validators for public transit operators</t>
         </is>
       </c>
-      <c r="F20" s="40" t="inlineStr">
+      <c r="F20" s="39" t="inlineStr">
         <is>
           <t>Yes - Senior Enterprise Account Executiv (Spain, Spain)</t>
         </is>
@@ -47710,7 +47710,7 @@
           <t>Bus ITS: CAD/AVL, real-time passenger info, and fleet health</t>
         </is>
       </c>
-      <c r="F22" s="39" t="inlineStr">
+      <c r="F22" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -47770,7 +47770,7 @@
           <t>Real-time transit data: arrival predictions and on-time performance</t>
         </is>
       </c>
-      <c r="F24" s="40" t="inlineStr">
+      <c r="F24" s="39" t="inlineStr">
         <is>
           <t>Yes - Senior Account Manager (United States)</t>
         </is>
@@ -47830,7 +47830,7 @@
           <t>myAvail enterprise transit management ITS and CAD/AVL for mid-size US agencies</t>
         </is>
       </c>
-      <c r="F26" s="39" t="inlineStr">
+      <c r="F26" s="40" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://availtec.com/career</t>
         </is>
@@ -47890,7 +47890,7 @@
           <t>IVU.suite planning, scheduling, dispatch, and ticketing for transit and rail operators</t>
         </is>
       </c>
-      <c r="F28" s="39" t="inlineStr">
+      <c r="F28" s="40" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.ivu.com/career</t>
         </is>
@@ -47950,7 +47950,7 @@
           <t>Transit dispatch, CAD/AVL, and communications software (Modaxo brand, ex-Trapeze ITS)</t>
         </is>
       </c>
-      <c r="F30" s="39" t="inlineStr">
+      <c r="F30" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48010,7 +48010,7 @@
           <t>Consat Telematics real-time CAD/AVL, passenger info, and electromobility analytics (NA office Sudbury ON)</t>
         </is>
       </c>
-      <c r="F32" s="39" t="inlineStr">
+      <c r="F32" s="40" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.consat.com/care</t>
         </is>
@@ -48070,7 +48070,7 @@
           <t>Transit performance data warehousing, BI, and automated NTD reporting (Modaxo brand) - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F34" s="39" t="inlineStr">
+      <c r="F34" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -48124,7 +48124,7 @@
           <t>Cloud CAD/AVL and in-vehicle tech for transit agencies and campus systems (SDVOSB)</t>
         </is>
       </c>
-      <c r="F36" s="39" t="inlineStr">
+      <c r="F36" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48184,7 +48184,7 @@
           <t>IBM Maximo consulting plus Mobile Informer EAM for transit agencies, airports, and utilities</t>
         </is>
       </c>
-      <c r="F38" s="39" t="inlineStr">
+      <c r="F38" s="40" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.interlocsolutio</t>
         </is>
@@ -48244,7 +48244,7 @@
           <t>Trainwise onboard train control/monitoring and Fleetwise wayside fleet management for transit</t>
         </is>
       </c>
-      <c r="F40" s="39" t="inlineStr">
+      <c r="F40" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48304,7 +48304,7 @@
           <t>Rail terminal management, track inspection, and crew compliance for short lines and commuter rail</t>
         </is>
       </c>
-      <c r="F42" s="39" t="inlineStr">
+      <c r="F42" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48364,7 +48364,7 @@
           <t>Ultra-wideband train positioning, worker protection, and ATP for transit agencies (NYC MTA)</t>
         </is>
       </c>
-      <c r="F44" s="39" t="inlineStr">
+      <c r="F44" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48424,7 +48424,7 @@
           <t>CylusOne rail OT cybersecurity: threat detection for signaling, trackside, and onboard networks</t>
         </is>
       </c>
-      <c r="F46" s="39" t="inlineStr">
+      <c r="F46" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48482,7 +48482,7 @@
           <t>ConnX Maestro unified communications and contact center for transit agencies (SEPTA)</t>
         </is>
       </c>
-      <c r="F48" s="39" t="inlineStr">
+      <c r="F48" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48540,7 +48540,7 @@
           <t>Non-invasive sensors and cloud analytics for elevator, escalator, and HVAC uptime in transit stations</t>
         </is>
       </c>
-      <c r="F50" s="39" t="inlineStr">
+      <c r="F50" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48598,7 +48598,7 @@
           <t>Virtual Optical Fiber high-speed data offload between transit vehicles and depots</t>
         </is>
       </c>
-      <c r="F52" s="39" t="inlineStr">
+      <c r="F52" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48658,7 +48658,7 @@
           <t>AI smart inspection for rail infrastructure: sensor robot plus defect detection and predictive maintenance</t>
         </is>
       </c>
-      <c r="F54" s="39" t="inlineStr">
+      <c r="F54" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48714,7 +48714,7 @@
           <t>Mobile video surveillance, DVRs, and MotoTrax analytics for transit, school, and municipal fleets - exhibited at CTAA EXPO 2026, NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F56" s="40" t="inlineStr">
+      <c r="F56" s="39" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -48774,7 +48774,7 @@
           <t>Onboard transit systems: Horizon CCTV, NetSpire passenger info, iConnex real-time (US in Buffalo NY)</t>
         </is>
       </c>
-      <c r="F58" s="39" t="inlineStr">
+      <c r="F58" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48834,7 +48834,7 @@
           <t>Intelligent video, AI stop-arm analytics, and cloud safety platforms for transit and school districts - exhibited at CTAA EXPO 2026, NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F60" s="39" t="inlineStr">
+      <c r="F60" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48894,7 +48894,7 @@
           <t>AI dashcams, MDVRs, and fleet video telematics for transit, school bus, and commercial fleets (US: Houston)</t>
         </is>
       </c>
-      <c r="F62" s="39" t="inlineStr">
+      <c r="F62" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48954,7 +48954,7 @@
           <t>3D AI people-flow sensors for passenger counting, queue, and dwell in transit hubs and airports</t>
         </is>
       </c>
-      <c r="F64" s="39" t="inlineStr">
+      <c r="F64" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49014,7 +49014,7 @@
           <t>Automatic passenger counting hardware and analysis software for bus, rail, and paratransit</t>
         </is>
       </c>
-      <c r="F66" s="39" t="inlineStr">
+      <c r="F66" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -49074,7 +49074,7 @@
           <t>Video telematics and driver safety for municipal and transit fleets - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
-      <c r="F68" s="39" t="inlineStr">
+      <c r="F68" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49134,7 +49134,7 @@
           <t>Telematics devices and fleet tracking software for public fleets</t>
         </is>
       </c>
-      <c r="F70" s="39" t="inlineStr">
+      <c r="F70" s="40" t="inlineStr">
         <is>
           <t>Unknown - no jobs parsed from iCIMS portal</t>
         </is>
@@ -49194,7 +49194,7 @@
           <t>FleetWave fleet asset management for public sector fleets</t>
         </is>
       </c>
-      <c r="F72" s="39" t="inlineStr">
+      <c r="F72" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49254,7 +49254,7 @@
           <t>FleetCommander motor pool and vehicle sharing for agencies</t>
         </is>
       </c>
-      <c r="F74" s="39" t="inlineStr">
+      <c r="F74" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -49314,7 +49314,7 @@
           <t>Fleet data analytics and benchmarking for public and utility fleets</t>
         </is>
       </c>
-      <c r="F76" s="39" t="inlineStr">
+      <c r="F76" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -49374,7 +49374,7 @@
           <t>Fleet automation and motor pool platform for public agencies</t>
         </is>
       </c>
-      <c r="F78" s="39" t="inlineStr">
+      <c r="F78" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49434,7 +49434,7 @@
           <t>Onboard surveillance and video management for transit fleets</t>
         </is>
       </c>
-      <c r="F80" s="39" t="inlineStr">
+      <c r="F80" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -49554,7 +49554,7 @@
           <t>On-demand transit and shared mobility software for public agencies</t>
         </is>
       </c>
-      <c r="F84" s="39" t="inlineStr">
+      <c r="F84" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -49614,7 +49614,7 @@
           <t>Parking meters, kiosks and transit fare systems for cities</t>
         </is>
       </c>
-      <c r="F86" s="39" t="inlineStr">
+      <c r="F86" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49674,7 +49674,7 @@
           <t>Mobile parking payments for city and municipal parking operators</t>
         </is>
       </c>
-      <c r="F88" s="40" t="inlineStr">
+      <c r="F88" s="39" t="inlineStr">
         <is>
           <t>Yes - Corporate Sales Executive</t>
         </is>
@@ -49734,7 +49734,7 @@
           <t>Parking access and revenue control systems for public garages</t>
         </is>
       </c>
-      <c r="F90" s="39" t="inlineStr">
+      <c r="F90" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49794,7 +49794,7 @@
           <t>Automated enforcement: school-zone speed, red-light, and bus-lane cameras - exhibited at North Carolina Sheriffs' Association 2026</t>
         </is>
       </c>
-      <c r="F92" s="40" t="inlineStr">
+      <c r="F92" s="39" t="inlineStr">
         <is>
           <t>Yes - Mass Market Account Executive (Arizona_Remote)</t>
         </is>
@@ -49854,7 +49854,7 @@
           <t>Multimodal trip planning app plus a paid agency suite (white-label apps, sponsored Royale, rider data) - exhibited at CTAA EXPO 2026, NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F94" s="39" t="inlineStr">
+      <c r="F94" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49914,7 +49914,7 @@
           <t>ePaper Digital Bus Stop, SmartStop kiosks, and CPAM content management for transit agencies</t>
         </is>
       </c>
-      <c r="F96" s="39" t="inlineStr">
+      <c r="F96" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -49976,7 +49976,7 @@
       </c>
       <c r="F98" s="41" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Sales Backoffice Specialist only</t>
+          <t>Sales (non-AE) - Sales Backoffice Specialist with G only</t>
         </is>
       </c>
     </row>
@@ -50034,7 +50034,7 @@
           <t>Bus destination displays, controllers, and next-stop passenger information systems</t>
         </is>
       </c>
-      <c r="F100" s="39" t="inlineStr">
+      <c r="F100" s="40" t="inlineStr">
         <is>
           <t>Unknown - HTTP 403 for https://www.hanoverdisplays</t>
         </is>
@@ -50092,7 +50092,7 @@
           <t>TRACC travel-time and accessibility analysis plus transport datasets for government transport agencies</t>
         </is>
       </c>
-      <c r="F102" s="39" t="inlineStr">
+      <c r="F102" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50152,7 +50152,7 @@
           <t>Solar smart bus stops with edge AI plus the ORA platform: signage, lane enforcement, passenger counting</t>
         </is>
       </c>
-      <c r="F104" s="39" t="inlineStr">
+      <c r="F104" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50212,7 +50212,7 @@
           <t>Real-time transit display screens and rider information for agencies and cities</t>
         </is>
       </c>
-      <c r="F106" s="39" t="inlineStr">
+      <c r="F106" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50272,7 +50272,7 @@
           <t>Elevated automated transit pods on prefabricated guideways (ex-skyTran team) for cities and campuses</t>
         </is>
       </c>
-      <c r="F108" s="39" t="inlineStr">
+      <c r="F108" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50332,7 +50332,7 @@
           <t>On-demand microtransit software with rider/driver apps and AI dispatch for large agencies - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F110" s="40" t="inlineStr">
+      <c r="F110" s="39" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -50392,7 +50392,7 @@
           <t>Assisted-mobility platform and driver network delivering ADA paratransit and door-through-door trips - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F112" s="39" t="inlineStr">
+      <c r="F112" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50452,7 +50452,7 @@
           <t>Transit management software for paratransit, demand-response, microtransit, and taxi fleets - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F114" s="39" t="inlineStr">
+      <c r="F114" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50512,7 +50512,7 @@
           <t>Autonomous vehicle technology and driverless shuttle service for transit agencies and cities</t>
         </is>
       </c>
-      <c r="F116" s="39" t="inlineStr">
+      <c r="F116" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -50572,7 +50572,7 @@
           <t>flowride.ai SAE Level-4 automated driving software retrofitted onto full-size electric transit buses</t>
         </is>
       </c>
-      <c r="F118" s="39" t="inlineStr">
+      <c r="F118" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50632,7 +50632,7 @@
           <t>Assisted senior and accessible transportation platform serving agency paratransit overflow in 35+ metros</t>
         </is>
       </c>
-      <c r="F120" s="39" t="inlineStr">
+      <c r="F120" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50692,7 +50692,7 @@
           <t>White-label multimodal TDM and commute platform for regional agencies, employers, and campuses</t>
         </is>
       </c>
-      <c r="F122" s="39" t="inlineStr">
+      <c r="F122" s="40" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.rideshark.com/c</t>
         </is>
@@ -50744,7 +50744,7 @@
           <t>TripMaster paratransit scheduling and dispatch software for public transit providers</t>
         </is>
       </c>
-      <c r="F124" s="39" t="inlineStr">
+      <c r="F124" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50802,7 +50802,7 @@
           <t>Demand-responsive transit dispatch and booking software for transit agencies - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F126" s="39" t="inlineStr">
+      <c r="F126" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50862,7 +50862,7 @@
           <t>Electric on-demand shuttle service contracted by cities and transit agencies - exhibited at WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F128" s="39" t="inlineStr">
+      <c r="F128" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -50922,7 +50922,7 @@
           <t>On-demand ridepooling and mobility analytics software for public transit authorities</t>
         </is>
       </c>
-      <c r="F130" s="39" t="inlineStr">
+      <c r="F130" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50982,7 +50982,7 @@
           <t>Ridepooling operations and autonomous shuttle services for public transport partners</t>
         </is>
       </c>
-      <c r="F132" s="39" t="inlineStr">
+      <c r="F132" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51034,7 +51034,7 @@
           <t>ADA paratransit eligibility, call center and mobility management technology for agencies</t>
         </is>
       </c>
-      <c r="F134" s="39" t="inlineStr">
+      <c r="F134" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51094,7 +51094,7 @@
           <t>Whoosh autonomous cable-driven transit pods for cities and campuses</t>
         </is>
       </c>
-      <c r="F136" s="39" t="inlineStr">
+      <c r="F136" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51154,7 +51154,7 @@
           <t>Autonomous shuttle vehicles for public transport and campus deployments</t>
         </is>
       </c>
-      <c r="F138" s="39" t="inlineStr">
+      <c r="F138" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51214,7 +51214,7 @@
           <t>Electric and autonomous buses sold to public transit operators worldwide</t>
         </is>
       </c>
-      <c r="F140" s="39" t="inlineStr">
+      <c r="F140" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51274,7 +51274,7 @@
           <t>Automated people mover and group rapid transit systems for public authorities</t>
         </is>
       </c>
-      <c r="F142" s="39" t="inlineStr">
+      <c r="F142" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -51334,7 +51334,7 @@
           <t>Autonomy software powering driverless shuttles for transit and airport operators</t>
         </is>
       </c>
-      <c r="F144" s="39" t="inlineStr">
+      <c r="F144" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -51394,7 +51394,7 @@
           <t>Autonomous shuttles for public transport agencies, airports and campuses</t>
         </is>
       </c>
-      <c r="F146" s="39" t="inlineStr">
+      <c r="F146" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51454,7 +51454,7 @@
           <t>Leading mobile parking payments app (EasyPark Group)</t>
         </is>
       </c>
-      <c r="F148" s="39" t="inlineStr">
+      <c r="F148" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -51514,7 +51514,7 @@
           <t>Computer vision curb management and automated loading-zone payments</t>
         </is>
       </c>
-      <c r="F150" s="39" t="inlineStr">
+      <c r="F150" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -51574,7 +51574,7 @@
           <t>Gateless LPR parking operations (GLIDEPARCS) for private lots, universities, and some municipalities</t>
         </is>
       </c>
-      <c r="F152" s="39" t="inlineStr">
+      <c r="F152" s="40" t="inlineStr">
         <is>
           <t>Unknown - page too small - likely JS-rendered</t>
         </is>
@@ -51634,7 +51634,7 @@
           <t>Towing lifecycle software for city towing programs and impound management (ex-AutoReturn + TSD)</t>
         </is>
       </c>
-      <c r="F154" s="39" t="inlineStr">
+      <c r="F154" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -51694,7 +51694,7 @@
           <t>Sentry solar smart kiosks and vision-based automated parking enforcement</t>
         </is>
       </c>
-      <c r="F156" s="39" t="inlineStr">
+      <c r="F156" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51754,7 +51754,7 @@
           <t>Single-space smart parking meters and pay stations for municipalities</t>
         </is>
       </c>
-      <c r="F158" s="39" t="inlineStr">
+      <c r="F158" s="40" t="inlineStr">
         <is>
           <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
@@ -51814,7 +51814,7 @@
           <t>Wireless parking occupancy sensors for city and campus parking</t>
         </is>
       </c>
-      <c r="F160" s="39" t="inlineStr">
+      <c r="F160" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51874,7 +51874,7 @@
           <t>Smart parking sensors and LoRaWAN networks for cities</t>
         </is>
       </c>
-      <c r="F162" s="39" t="inlineStr">
+      <c r="F162" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -51934,7 +51934,7 @@
           <t>Parking payments, permits and enforcement software for municipalities</t>
         </is>
       </c>
-      <c r="F164" s="39" t="inlineStr">
+      <c r="F164" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51994,7 +51994,7 @@
           <t>Parking citation processing and permit services for California cities</t>
         </is>
       </c>
-      <c r="F166" s="39" t="inlineStr">
+      <c r="F166" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52054,7 +52054,7 @@
           <t>Parking citation, permit and enforcement management software for agencies</t>
         </is>
       </c>
-      <c r="F168" s="39" t="inlineStr">
+      <c r="F168" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52110,7 +52110,7 @@
           <t>Control room video wall visualization software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F170" s="39" t="inlineStr">
+      <c r="F170" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -52162,7 +52162,7 @@
           <t>Transit fare collection and ticketing software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F172" s="39" t="inlineStr">
+      <c r="F172" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52210,7 +52210,7 @@
           <t>Infrastructure engineering and asset software - exhibited at APTA 2026, AWWA ACE 2026</t>
         </is>
       </c>
-      <c r="F174" s="39" t="inlineStr">
+      <c r="F174" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52262,7 +52262,7 @@
           <t>Fuel and fleet management systems - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F176" s="39" t="inlineStr">
+      <c r="F176" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -52312,7 +52312,7 @@
           <t>Transit ITS, fare collection, scheduling software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F178" s="39" t="inlineStr">
+      <c r="F178" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52340,7 +52340,7 @@
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.intangles.ai/ca</t>
         </is>
       </c>
     </row>
@@ -52368,7 +52368,7 @@
           <t>Ticketing, traffic and transit management systems - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F180" s="39" t="inlineStr">
+      <c r="F180" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52416,7 +52416,7 @@
           <t>LiDAR 3D digital twin capture for transit - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F182" s="39" t="inlineStr">
+      <c r="F182" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52464,7 +52464,7 @@
           <t>Medical transportation ride management software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F184" s="39" t="inlineStr">
+      <c r="F184" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52514,7 +52514,7 @@
           <t>AI video analytics perimeter security software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F186" s="39" t="inlineStr">
+      <c r="F186" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -52562,7 +52562,7 @@
           <t>Transit CAD/AVL, APC, passenger information systems - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F188" s="39" t="inlineStr">
+      <c r="F188" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52616,7 +52616,7 @@
           <t>EV fleet charge management software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F190" s="39" t="inlineStr">
+      <c r="F190" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -52664,7 +52664,7 @@
           <t>Immersive VR training software platform - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F192" s="39" t="inlineStr">
+      <c r="F192" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52728,7 +52728,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/23/26)</t>
+          <t>Hiring AEs? (9/25/26)</t>
         </is>
       </c>
     </row>
@@ -54198,7 +54198,7 @@
       </c>
       <c r="F50" s="45" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: ('Connection aborted.', C</t>
         </is>
       </c>
     </row>
@@ -54438,7 +54438,7 @@
       </c>
       <c r="F58" s="45" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -54796,9 +54796,9 @@
           <t>Non-contact transmission line monitoring and dynamic line ratings for utilities</t>
         </is>
       </c>
-      <c r="F70" s="45" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F70" s="47" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -56286,7 +56286,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/23/26)</t>
+          <t>Hiring AEs? (9/25/26)</t>
         </is>
       </c>
     </row>
@@ -59810,7 +59810,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/23/26)</t>
+          <t>Hiring AEs? (9/25/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/25/26)</t>
+          <t>Hiring AEs? (9/26/26)</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
         </is>
       </c>
     </row>
@@ -5982,9 +5982,9 @@
           <t>Assistive AI for 911 centers: transcription, translation, text-to-911, and video</t>
         </is>
       </c>
-      <c r="F171" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -6282,9 +6282,9 @@
           <t>Pediatric emergency dosing system and app for EMS agencies</t>
         </is>
       </c>
-      <c r="F181" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F181" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Mid-Market Account Executive</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="F297" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/25/26)</t>
+          <t>Hiring AEs? (9/26/26)</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 500 for https://company.getinsured.</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://tootris.com/careers</t>
+          <t>Unknown - page too small - likely JS-rendered</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/25/26)</t>
+          <t>Hiring AEs? (9/26/26)</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/25/26)</t>
+          <t>Hiring AEs? (9/26/26)</t>
         </is>
       </c>
     </row>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/25/26)</t>
+          <t>Hiring AEs? (9/26/26)</t>
         </is>
       </c>
     </row>
@@ -17642,9 +17642,9 @@
           <t>AI recycling-sorting robots and real-time bale/line data</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive - Climate Tech ( (Remote East Coast )</t>
         </is>
       </c>
     </row>
@@ -22340,7 +22340,7 @@
       </c>
       <c r="F164" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -23462,7 +23462,7 @@
       </c>
       <c r="F202" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/25/26)</t>
+          <t>Hiring AEs? (9/26/26)</t>
         </is>
       </c>
     </row>
@@ -38708,7 +38708,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/25/26)</t>
+          <t>Hiring AEs? (9/26/26)</t>
         </is>
       </c>
     </row>
@@ -39064,7 +39064,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -39362,7 +39362,7 @@
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Manager, Large Market (Remote)</t>
+          <t>Yes - Account Manager (Remote)</t>
         </is>
       </c>
     </row>
@@ -40916,9 +40916,9 @@
           <t>WeatherTRAK smart irrigation and water management for public agencies</t>
         </is>
       </c>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -42990,7 +42990,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/25/26)</t>
+          <t>Hiring AEs? (9/26/26)</t>
         </is>
       </c>
     </row>
@@ -43050,7 +43050,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>Yes - Sales Executive - Pacific Northwes (Remote Worker - N/)</t>
+          <t>Yes - Sales Executive, Cross-Sell (North (Remote Worker - N/)</t>
         </is>
       </c>
     </row>
@@ -44322,9 +44322,9 @@
           <t>Longtime standard for school bus routing and planning software</t>
         </is>
       </c>
-      <c r="F46" s="34" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F46" s="35" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -47086,7 +47086,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/25/26)</t>
+          <t>Hiring AEs? (9/26/26)</t>
         </is>
       </c>
     </row>
@@ -47502,7 +47502,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -52728,7 +52728,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/25/26)</t>
+          <t>Hiring AEs? (9/26/26)</t>
         </is>
       </c>
     </row>
@@ -54198,7 +54198,7 @@
       </c>
       <c r="F50" s="45" t="inlineStr">
         <is>
-          <t>Unknown - network error: ('Connection aborted.', C</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -54438,7 +54438,7 @@
       </c>
       <c r="F58" s="45" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -56286,7 +56286,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/25/26)</t>
+          <t>Hiring AEs? (9/26/26)</t>
         </is>
       </c>
     </row>
@@ -56758,7 +56758,7 @@
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Manager (Sales)</t>
+          <t>Yes - Account Manager</t>
         </is>
       </c>
     </row>
@@ -58672,7 +58672,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (C1 - (New York, New York)</t>
+          <t>Yes - Enterprise Account Executive (C1 - (Dallas, TX, United)</t>
         </is>
       </c>
     </row>
@@ -59150,7 +59150,7 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Manager (Remote USA)</t>
+          <t>Yes - Associate Account Executive (Cleve (Cleveland, Ohio, U)</t>
         </is>
       </c>
     </row>
@@ -59810,7 +59810,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/25/26)</t>
+          <t>Hiring AEs? (9/26/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/26/26)</t>
+          <t>Hiring AEs? (9/27/26)</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 500 for https://www.bullard.com/car</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
+          <t>Unknown - HTTP 202 for https://www.365labs.com/car</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="F297" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/26/26)</t>
+          <t>Hiring AEs? (9/27/26)</t>
         </is>
       </c>
     </row>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page too small - likely JS-rendered</t>
+          <t>Unknown - HTTP 403 for https://tootris.com/careers</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/26/26)</t>
+          <t>Hiring AEs? (9/27/26)</t>
         </is>
       </c>
     </row>
@@ -15364,7 +15364,7 @@
       </c>
       <c r="F34" s="69" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/26/26)</t>
+          <t>Hiring AEs? (9/27/26)</t>
         </is>
       </c>
     </row>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/26/26)</t>
+          <t>Hiring AEs? (9/27/26)</t>
         </is>
       </c>
     </row>
@@ -23696,9 +23696,9 @@
           <t>Enterprise asset and field service management for utilities and municipalities</t>
         </is>
       </c>
-      <c r="F210" s="15" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F210" s="16" t="inlineStr">
+        <is>
+          <t>Yes - Regional Account Executive, Energy (Ottawa, Ontario)</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/26/26)</t>
+          <t>Hiring AEs? (9/27/26)</t>
         </is>
       </c>
     </row>
@@ -31856,7 +31856,7 @@
       </c>
       <c r="F246" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://passportworkforce.c</t>
+          <t>Unknown - HTTP 202 for https://passportworkforce.c</t>
         </is>
       </c>
     </row>
@@ -35596,7 +35596,7 @@
       </c>
       <c r="F374" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -38708,7 +38708,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/26/26)</t>
+          <t>Hiring AEs? (9/27/26)</t>
         </is>
       </c>
     </row>
@@ -39064,7 +39064,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -42990,7 +42990,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/26/26)</t>
+          <t>Hiring AEs? (9/27/26)</t>
         </is>
       </c>
     </row>
@@ -46338,9 +46338,9 @@
           <t>Classroom communication and engagement app connecting K-12 teachers, students, and families - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F114" s="34" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F114" s="33" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Revenue Product Lead only</t>
         </is>
       </c>
     </row>
@@ -47086,7 +47086,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/26/26)</t>
+          <t>Hiring AEs? (9/27/26)</t>
         </is>
       </c>
     </row>
@@ -47386,7 +47386,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.modeshift.com/c</t>
+          <t>Unknown - HTTP 202 for https://www.modeshift.com/c</t>
         </is>
       </c>
     </row>
@@ -47982,7 +47982,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.enghouse.com/ca</t>
+          <t>Unknown - HTTP 202 for https://www.enghouse.com/ca</t>
         </is>
       </c>
     </row>
@@ -49796,7 +49796,7 @@
       </c>
       <c r="F92" s="39" t="inlineStr">
         <is>
-          <t>Yes - Mass Market Account Executive (Arizona_Remote)</t>
+          <t>Yes - Mass Market Account Executive (California_Remote)</t>
         </is>
       </c>
     </row>
@@ -50036,7 +50036,7 @@
       </c>
       <c r="F100" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.hanoverdisplays</t>
+          <t>Unknown - HTTP 202 for https://www.hanoverdisplays</t>
         </is>
       </c>
     </row>
@@ -50424,7 +50424,7 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://qryde.com/employmen</t>
+          <t>Unknown - HTTP 202 for https://qryde.com/employmen</t>
         </is>
       </c>
     </row>
@@ -52728,7 +52728,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/26/26)</t>
+          <t>Hiring AEs? (9/27/26)</t>
         </is>
       </c>
     </row>
@@ -54438,7 +54438,7 @@
       </c>
       <c r="F58" s="45" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -56286,7 +56286,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/26/26)</t>
+          <t>Hiring AEs? (9/27/26)</t>
         </is>
       </c>
     </row>
@@ -58640,9 +58640,9 @@
           <t>Airport biometric border control, e-gates and identity systems for governments</t>
         </is>
       </c>
-      <c r="F80" s="51" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F80" s="52" t="inlineStr">
+        <is>
+          <t>Yes - Sales Account Manager (3 Locations)</t>
         </is>
       </c>
     </row>
@@ -59810,7 +59810,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/26/26)</t>
+          <t>Hiring AEs? (9/27/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -21,12 +21,12 @@
     <sheet name="Housing &amp; Community Dev" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Public Safety'!$A$1:$F$355</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Public Safety'!$A$1:$F$353</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Public Works'!$A$1:$F$242</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'General Gov'!$A$1:$F$489</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'General Gov'!$A$1:$F$488</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Parks &amp; Rec'!$A$1:$F$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'K-12 Schools'!$A$1:$F$139</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Transit &amp; Parking'!$A$1:$F$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Transit &amp; Parking'!$A$1:$F$191</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Utilities &amp; Energy'!$A$1:$F$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Airports &amp; Aviation'!$A$1:$F$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Courts &amp; Justice'!$A$1:$F$36</definedName>
@@ -903,7 +903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F355"/>
+  <dimension ref="A1:F353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/27/26)</t>
+          <t>Hiring AEs? (9/28/26)</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 500 for https://www.bullard.com/car</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>Yes - Federal Account Executive (Washington, D.C.)</t>
+          <t>Yes - Account Executive, UK Law Enforcem (London, United Kin)</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>Yes - Business Development Manager (Rome, Rome, Italy)</t>
+          <t>Yes - Business Development Manager (Milan, Milano, Ita)</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>Yes - Regional Account Manager - Nordics (Nordics)</t>
+          <t>Yes - Regional Account Manager - Eastern (Poland)</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Manager (Biling (Remote - United St)</t>
+          <t>Yes - Enterprise Account Manager (Auror London Offic)</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -10151,11 +10151,13 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>LexisNexis</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="B318" s="2" t="n"/>
-      <c r="C318" s="3" t="n"/>
+      <c r="C318" s="3" t="n">
+        <v>2000</v>
+      </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -10163,25 +10165,23 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>Online police reporting and crash report software - exhibited at IACP 2026</t>
+          <t>Data analytics and investigative search platform - exhibited at NSA 2026, NASCIO 2026, AIRA 2026</t>
         </is>
       </c>
       <c r="F318" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 403 for https://risk.lexisnexis.com</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>LexisNexis Risk Solutions Government</t>
         </is>
       </c>
       <c r="B319" s="5" t="n"/>
-      <c r="C319" s="6" t="n">
-        <v>2000</v>
-      </c>
+      <c r="C319" s="6" t="n"/>
       <c r="D319" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -10189,23 +10189,25 @@
       </c>
       <c r="E319" s="5" t="inlineStr">
         <is>
-          <t>Data analytics and investigative search platform - exhibited at NSA 2026, NASCIO 2026, AIRA 2026</t>
+          <t>Investigative data and analytics for government - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F319" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://risk.lexisnexis.com</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions Government</t>
+          <t>MCM Technology LLC</t>
         </is>
       </c>
       <c r="B320" s="2" t="n"/>
-      <c r="C320" s="3" t="n"/>
+      <c r="C320" s="3" t="n">
+        <v>2001</v>
+      </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -10213,25 +10215,23 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>Investigative data and analytics for government - exhibited at IACP 2026</t>
+          <t>Public safety asset and fleet management software - exhibited at IACP 2026, IAFC FRI 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>MCM Technology LLC</t>
+          <t>NeutralAiz Inc.</t>
         </is>
       </c>
       <c r="B321" s="5" t="n"/>
-      <c r="C321" s="6" t="n">
-        <v>2001</v>
-      </c>
+      <c r="C321" s="6" t="n"/>
       <c r="D321" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -10239,19 +10239,19 @@
       </c>
       <c r="E321" s="5" t="inlineStr">
         <is>
-          <t>Public safety asset and fleet management software - exhibited at IACP 2026, IAFC FRI 2026, APCO 2026</t>
+          <t>AI public safety technology - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F321" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>NeutralAiz Inc.</t>
+          <t>New in Blue</t>
         </is>
       </c>
       <c r="B322" s="2" t="n"/>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>AI public safety technology - exhibited at IACP 2026</t>
+          <t>Police RMS/CAD, citation and safety apps - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F322" s="4" t="inlineStr">
@@ -10275,11 +10275,13 @@
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
         <is>
-          <t>New in Blue</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="B323" s="5" t="n"/>
-      <c r="C323" s="6" t="n"/>
+      <c r="C323" s="6" t="n">
+        <v>2013</v>
+      </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -10287,25 +10289,23 @@
       </c>
       <c r="E323" s="5" t="inlineStr">
         <is>
-          <t>Police RMS/CAD, citation and safety apps - exhibited at IACP 2026</t>
-        </is>
-      </c>
-      <c r="F323" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Endpoint management and IT automation software - exhibited at NSA 2026, GMIS International 2026, EDUCAUSE 2026</t>
+        </is>
+      </c>
+      <c r="F323" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>NueGOV</t>
         </is>
       </c>
       <c r="B324" s="2" t="n"/>
-      <c r="C324" s="3" t="n">
-        <v>2013</v>
-      </c>
+      <c r="C324" s="3" t="n"/>
       <c r="D324" s="2" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -10313,19 +10313,19 @@
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>Endpoint management and IT automation software - exhibited at NSA 2026, GMIS International 2026, EDUCAUSE 2026</t>
-        </is>
-      </c>
-      <c r="F324" s="8" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Enterprise software platform for government agencies - exhibited at IACP 2026</t>
+        </is>
+      </c>
+      <c r="F324" s="4" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
         <is>
-          <t>NueGOV</t>
+          <t>OSINTPilot</t>
         </is>
       </c>
       <c r="B325" s="5" t="n"/>
@@ -10337,7 +10337,7 @@
       </c>
       <c r="E325" s="5" t="inlineStr">
         <is>
-          <t>Enterprise software platform for government agencies - exhibited at IACP 2026</t>
+          <t>Open source intelligence investigation software - exhibited at NSA 2026</t>
         </is>
       </c>
       <c r="F325" s="7" t="inlineStr">
@@ -10349,7 +10349,7 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>OSINTPilot</t>
+          <t>Operative IQ</t>
         </is>
       </c>
       <c r="B326" s="2" t="n"/>
@@ -10361,7 +10361,7 @@
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>Open source intelligence investigation software - exhibited at NSA 2026</t>
+          <t>EMS/fire inventory and asset management software - exhibited at IACP 2026, IAFC FRI 2026</t>
         </is>
       </c>
       <c r="F326" s="4" t="inlineStr">
@@ -10373,7 +10373,7 @@
     <row r="327">
       <c r="A327" s="5" t="inlineStr">
         <is>
-          <t>Operative IQ</t>
+          <t>Operator XR</t>
         </is>
       </c>
       <c r="B327" s="5" t="n"/>
@@ -10385,19 +10385,19 @@
       </c>
       <c r="E327" s="5" t="inlineStr">
         <is>
-          <t>EMS/fire inventory and asset management software - exhibited at IACP 2026, IAFC FRI 2026</t>
+          <t>VR tactical training platform for police - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F327" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>Operator XR</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="B328" s="2" t="n"/>
@@ -10409,19 +10409,19 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>VR tactical training platform for police - exhibited at IACP 2026</t>
+          <t>Enterprise database, cloud and ERP software - exhibited at IACP 2026, NSA 2026, GFOA 2026</t>
         </is>
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="5" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>PeerConnect</t>
         </is>
       </c>
       <c r="B329" s="5" t="n"/>
@@ -10433,7 +10433,7 @@
       </c>
       <c r="E329" s="5" t="inlineStr">
         <is>
-          <t>Enterprise database, cloud and ERP software - exhibited at IACP 2026, NSA 2026, GFOA 2026</t>
+          <t>First responder peer support and wellness app - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F329" s="7" t="inlineStr">
@@ -10445,7 +10445,7 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>Peach Safety</t>
+          <t>Peerless VR</t>
         </is>
       </c>
       <c r="B330" s="2" t="n"/>
@@ -10457,7 +10457,7 @@
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>AI police report writing - exhibited at IACP 2026</t>
+          <t>VR training simulation for law enforcement - exhibited at IACP 2026, NSA 2026</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
@@ -10469,7 +10469,7 @@
     <row r="331">
       <c r="A331" s="5" t="inlineStr">
         <is>
-          <t>PeerConnect</t>
+          <t>Police Narratives AI</t>
         </is>
       </c>
       <c r="B331" s="5" t="n"/>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="E331" s="5" t="inlineStr">
         <is>
-          <t>First responder peer support and wellness app - exhibited at IACP 2026</t>
+          <t>AI-assisted police report writing software - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F331" s="7" t="inlineStr">
@@ -10493,7 +10493,7 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>Peerless VR</t>
+          <t>Power DMS by NEOGOV</t>
         </is>
       </c>
       <c r="B332" s="2" t="n"/>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>VR training simulation for law enforcement - exhibited at IACP 2026, NSA 2026</t>
+          <t>Policy management and accreditation software - exhibited at NSA 2026</t>
         </is>
       </c>
       <c r="F332" s="4" t="inlineStr">
@@ -10517,11 +10517,13 @@
     <row r="333">
       <c r="A333" s="5" t="inlineStr">
         <is>
-          <t>Police Narratives AI</t>
+          <t>PowerDetails</t>
         </is>
       </c>
       <c r="B333" s="5" t="n"/>
-      <c r="C333" s="6" t="n"/>
+      <c r="C333" s="6" t="n">
+        <v>2006</v>
+      </c>
       <c r="D333" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -10529,7 +10531,7 @@
       </c>
       <c r="E333" s="5" t="inlineStr">
         <is>
-          <t>AI-assisted police report writing software - exhibited at IACP 2026</t>
+          <t>Off-duty/extra-duty detail scheduling software - exhibited at IACP 2026, NSA 2026</t>
         </is>
       </c>
       <c r="F333" s="7" t="inlineStr">
@@ -10541,11 +10543,13 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>Power DMS by NEOGOV</t>
+          <t>Renvizon/ QED</t>
         </is>
       </c>
       <c r="B334" s="2" t="n"/>
-      <c r="C334" s="3" t="n"/>
+      <c r="C334" s="3" t="n">
+        <v>1974</v>
+      </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -10553,25 +10557,23 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>Policy management and accreditation software - exhibited at NSA 2026</t>
+          <t>CAD, RMS and citation software for police - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F334" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="5" t="inlineStr">
         <is>
-          <t>PowerDetails</t>
+          <t>SWORN Inc.</t>
         </is>
       </c>
       <c r="B335" s="5" t="n"/>
-      <c r="C335" s="6" t="n">
-        <v>2006</v>
-      </c>
+      <c r="C335" s="6" t="n"/>
       <c r="D335" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -10579,7 +10581,7 @@
       </c>
       <c r="E335" s="5" t="inlineStr">
         <is>
-          <t>Off-duty/extra-duty detail scheduling software - exhibited at IACP 2026, NSA 2026</t>
+          <t>Biometric monitoring and intelligence for policing - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F335" s="7" t="inlineStr">
@@ -10591,13 +10593,15 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>Renvizon/ QED</t>
-        </is>
-      </c>
-      <c r="B336" s="2" t="n"/>
-      <c r="C336" s="3" t="n">
-        <v>1974</v>
-      </c>
+          <t>Saltus Technologies</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>Tulsa, OK</t>
+        </is>
+      </c>
+      <c r="C336" s="3" t="n"/>
       <c r="D336" s="2" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -10605,19 +10609,19 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>CAD, RMS and citation software for police - exhibited at IACP 2026</t>
-        </is>
-      </c>
-      <c r="F336" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>DigiTICKET electronic citation software - exhibited at IACP 2026</t>
+        </is>
+      </c>
+      <c r="F336" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="5" t="inlineStr">
         <is>
-          <t>SWORN Inc.</t>
+          <t>Schedule Express by SafeCities™</t>
         </is>
       </c>
       <c r="B337" s="5" t="n"/>
@@ -10629,7 +10633,7 @@
       </c>
       <c r="E337" s="5" t="inlineStr">
         <is>
-          <t>Biometric monitoring and intelligence for policing - exhibited at IACP 2026</t>
+          <t>Public safety scheduling and overtime software - exhibited at IACP 2026, APCO 2026</t>
         </is>
       </c>
       <c r="F337" s="7" t="inlineStr">
@@ -10641,14 +10645,10 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>Saltus Technologies</t>
-        </is>
-      </c>
-      <c r="B338" s="2" t="inlineStr">
-        <is>
-          <t>Tulsa, OK</t>
-        </is>
-      </c>
+          <t>Simsi, Inc</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="n"/>
       <c r="C338" s="3" t="n"/>
       <c r="D338" s="2" t="inlineStr">
         <is>
@@ -10657,19 +10657,19 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>DigiTICKET electronic citation software - exhibited at IACP 2026</t>
-        </is>
-      </c>
-      <c r="F338" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+          <t>Public safety analytics and collaboration software - exhibited at IACP 2026</t>
+        </is>
+      </c>
+      <c r="F338" s="4" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="5" t="inlineStr">
         <is>
-          <t>Schedule Express by SafeCities™</t>
+          <t>SmartForce</t>
         </is>
       </c>
       <c r="B339" s="5" t="n"/>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="E339" s="5" t="inlineStr">
         <is>
-          <t>Public safety scheduling and overtime software - exhibited at IACP 2026, APCO 2026</t>
+          <t>Police training, policy and workforce software - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F339" s="7" t="inlineStr">
@@ -10693,7 +10693,7 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>Simsi, Inc</t>
+          <t>StackBench</t>
         </is>
       </c>
       <c r="B340" s="2" t="n"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>Public safety analytics and collaboration software - exhibited at IACP 2026</t>
+          <t>Custom mobile apps for police agencies - exhibited at NSA 2026, Michigan Sheriffs Association 2026</t>
         </is>
       </c>
       <c r="F340" s="4" t="inlineStr">
@@ -10717,7 +10717,7 @@
     <row r="341">
       <c r="A341" s="5" t="inlineStr">
         <is>
-          <t>SmartForce</t>
+          <t>ThePoliceApp.com</t>
         </is>
       </c>
       <c r="B341" s="5" t="n"/>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="E341" s="5" t="inlineStr">
         <is>
-          <t>Police training, policy and workforce software - exhibited at IACP 2026</t>
+          <t>Online police recruitment and application platform - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F341" s="7" t="inlineStr">
@@ -10741,7 +10741,7 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>StackBench</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="B342" s="2" t="n"/>
@@ -10753,23 +10753,25 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>Custom mobile apps for police agencies - exhibited at NSA 2026, Michigan Sheriffs Association 2026</t>
-        </is>
-      </c>
-      <c r="F342" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>CLEAR investigative data and research platform - exhibited at IACP 2026, IMLA 2026, NACM 2026, APHSA 2026</t>
+        </is>
+      </c>
+      <c r="F342" s="8" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="5" t="inlineStr">
         <is>
-          <t>ThePoliceApp.com</t>
+          <t>Tracwire, Inc</t>
         </is>
       </c>
       <c r="B343" s="5" t="n"/>
-      <c r="C343" s="6" t="n"/>
+      <c r="C343" s="6" t="n">
+        <v>2019</v>
+      </c>
       <c r="D343" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -10777,19 +10779,19 @@
       </c>
       <c r="E343" s="5" t="inlineStr">
         <is>
-          <t>Online police recruitment and application platform - exhibited at IACP 2026</t>
+          <t>Police field training and evaluation software - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F343" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>UKG Telestaff</t>
         </is>
       </c>
       <c r="B344" s="2" t="n"/>
@@ -10801,25 +10803,23 @@
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>CLEAR investigative data and research platform - exhibited at IACP 2026, IMLA 2026, NACM 2026, APHSA 2026</t>
-        </is>
-      </c>
-      <c r="F344" s="8" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Public safety scheduling and workforce software - exhibited at IACP 2026, IAFC FRI 2026</t>
+        </is>
+      </c>
+      <c r="F344" s="4" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="5" t="inlineStr">
         <is>
-          <t>Tracwire, Inc</t>
+          <t>V-Armed</t>
         </is>
       </c>
       <c r="B345" s="5" t="n"/>
-      <c r="C345" s="6" t="n">
-        <v>2019</v>
-      </c>
+      <c r="C345" s="6" t="n"/>
       <c r="D345" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -10827,19 +10827,19 @@
       </c>
       <c r="E345" s="5" t="inlineStr">
         <is>
-          <t>Police field training and evaluation software - exhibited at IACP 2026</t>
+          <t>VR training simulation platform for police - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F345" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>UKG Telestaff</t>
+          <t>VCS HR &amp; Jobs4Blue</t>
         </is>
       </c>
       <c r="B346" s="2" t="n"/>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>Public safety scheduling and workforce software - exhibited at IACP 2026, IAFC FRI 2026</t>
+          <t>Public safety HR and job board platform - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
@@ -10863,7 +10863,7 @@
     <row r="347">
       <c r="A347" s="5" t="inlineStr">
         <is>
-          <t>V-Armed</t>
+          <t>VOCAL Technologies Inc.</t>
         </is>
       </c>
       <c r="B347" s="5" t="n"/>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="E347" s="5" t="inlineStr">
         <is>
-          <t>VR training simulation platform for police - exhibited at IACP 2026</t>
+          <t>Voice and telephony DSP software - exhibited at NSA 2026</t>
         </is>
       </c>
       <c r="F347" s="7" t="inlineStr">
@@ -10887,7 +10887,7 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>VCS HR &amp; Jobs4Blue</t>
+          <t>Vetted Holdings</t>
         </is>
       </c>
       <c r="B348" s="2" t="n"/>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>Public safety HR and job board platform - exhibited at IACP 2026</t>
+          <t>Law enforcement software holding company, CAD/RMS - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F348" s="4" t="inlineStr">
@@ -10911,11 +10911,13 @@
     <row r="349">
       <c r="A349" s="5" t="inlineStr">
         <is>
-          <t>VOCAL Technologies Inc.</t>
+          <t>Visionations/CrimePad</t>
         </is>
       </c>
       <c r="B349" s="5" t="n"/>
-      <c r="C349" s="6" t="n"/>
+      <c r="C349" s="6" t="n">
+        <v>2012</v>
+      </c>
       <c r="D349" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -10923,7 +10925,7 @@
       </c>
       <c r="E349" s="5" t="inlineStr">
         <is>
-          <t>Voice and telephony DSP software - exhibited at NSA 2026</t>
+          <t>Crime scene investigation documentation software - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F349" s="7" t="inlineStr">
@@ -10935,7 +10937,7 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>Vetted Holdings</t>
+          <t>Vocalis</t>
         </is>
       </c>
       <c r="B350" s="2" t="n"/>
@@ -10947,7 +10949,7 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>Law enforcement software holding company, CAD/RMS - exhibited at IACP 2026</t>
+          <t>AI voice agents for public safety call handling - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr">
@@ -10959,13 +10961,11 @@
     <row r="351">
       <c r="A351" s="5" t="inlineStr">
         <is>
-          <t>Visionations/CrimePad</t>
+          <t>Wavepoint Solutions, LLC</t>
         </is>
       </c>
       <c r="B351" s="5" t="n"/>
-      <c r="C351" s="6" t="n">
-        <v>2012</v>
-      </c>
+      <c r="C351" s="6" t="n"/>
       <c r="D351" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="E351" s="5" t="inlineStr">
         <is>
-          <t>Crime scene investigation documentation software - exhibited at IACP 2026</t>
+          <t>Radar-based gunshot detection and bullet tracking - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F351" s="7" t="inlineStr">
@@ -10985,7 +10985,7 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>Vocalis</t>
+          <t>Whooster, Inc</t>
         </is>
       </c>
       <c r="B352" s="2" t="n"/>
@@ -10997,19 +10997,19 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>AI voice agents for public safety call handling - exhibited at IACP 2026</t>
+          <t>Investigative data search platform for law enforcement - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="5" t="inlineStr">
         <is>
-          <t>Wavepoint Solutions, LLC</t>
+          <t>eSleuth.ai</t>
         </is>
       </c>
       <c r="B353" s="5" t="n"/>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="E353" s="5" t="inlineStr">
         <is>
-          <t>Radar-based gunshot detection and bullet tracking - exhibited at IACP 2026</t>
+          <t>AI investigative analysis software - exhibited at IACP 2026</t>
         </is>
       </c>
       <c r="F353" s="7" t="inlineStr">
@@ -11030,56 +11030,8 @@
         </is>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" s="2" t="inlineStr">
-        <is>
-          <t>Whooster, Inc</t>
-        </is>
-      </c>
-      <c r="B354" s="2" t="n"/>
-      <c r="C354" s="3" t="n"/>
-      <c r="D354" s="2" t="inlineStr">
-        <is>
-          <t>Suppliers &amp; Services</t>
-        </is>
-      </c>
-      <c r="E354" s="2" t="inlineStr">
-        <is>
-          <t>Investigative data search platform for law enforcement - exhibited at IACP 2026</t>
-        </is>
-      </c>
-      <c r="F354" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" s="5" t="inlineStr">
-        <is>
-          <t>eSleuth.ai</t>
-        </is>
-      </c>
-      <c r="B355" s="5" t="n"/>
-      <c r="C355" s="6" t="n"/>
-      <c r="D355" s="5" t="inlineStr">
-        <is>
-          <t>Suppliers &amp; Services</t>
-        </is>
-      </c>
-      <c r="E355" s="5" t="inlineStr">
-        <is>
-          <t>AI investigative analysis software - exhibited at IACP 2026</t>
-        </is>
-      </c>
-      <c r="F355" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F355"/>
+  <autoFilter ref="A1:F353"/>
   <dataValidations count="1">
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid category" error="Pick one of: Fire, Police, EMS, Emergency Mgmt, Corrections, Suppliers &amp; Services" type="list">
       <formula1>"Fire,Police,EMS,Emergency Mgmt,Corrections,Suppliers &amp; Services"</formula1>
@@ -11136,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/27/26)</t>
+          <t>Hiring AEs? (9/28/26)</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/27/26)</t>
+          <t>Hiring AEs? (9/28/26)</t>
         </is>
       </c>
     </row>
@@ -17026,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/27/26)</t>
+          <t>Hiring AEs? (9/28/26)</t>
         </is>
       </c>
     </row>
@@ -17494,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/27/26)</t>
+          <t>Hiring AEs? (9/28/26)</t>
         </is>
       </c>
     </row>
@@ -18648,7 +18600,7 @@
       </c>
       <c r="F40" s="16" t="inlineStr">
         <is>
-          <t>Yes - Outside Sales Representative (4 Locations)</t>
+          <t>Yes - Regional Sales Manager (3 Locations)</t>
         </is>
       </c>
     </row>
@@ -23462,7 +23414,7 @@
       </c>
       <c r="F202" s="15" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -23726,9 +23678,9 @@
           <t>Cloud CMMS for municipal facilities, water plants and public works</t>
         </is>
       </c>
-      <c r="F211" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive (United Kingdom)</t>
+      <c r="F211" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sales Talent Community – AM &amp; AE R only</t>
         </is>
       </c>
     </row>
@@ -24585,7 +24537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F489"/>
+  <dimension ref="A1:F488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -24624,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/27/26)</t>
+          <t>Hiring AEs? (9/28/26)</t>
         </is>
       </c>
     </row>
@@ -24894,7 +24846,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://zencity.io/careers</t>
+          <t>Unknown - HTTP 202 for https://zencity.io/careers</t>
         </is>
       </c>
     </row>
@@ -25642,9 +25594,9 @@
           <t>Interpretation management and delivery platform (video/phone) used by courts and agencies</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Director of Sales only</t>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -26258,9 +26210,9 @@
           <t>CodeRED public alerting and critical event management for local jurisdictions</t>
         </is>
       </c>
-      <c r="F56" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F56" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -28414,9 +28366,9 @@
           <t>PE-backed govtech rollup: courts, land records, tax/CAMA, licensing, and citizen payments - exhibited at APPA Probation 2026, IAAO 2026, NASWA 2025, 3CMA 2026</t>
         </is>
       </c>
-      <c r="F130" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F130" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive</t>
         </is>
       </c>
     </row>
@@ -30994,7 +30946,7 @@
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -31947,12 +31899,16 @@
     <row r="250">
       <c r="A250" s="19" t="inlineStr">
         <is>
-          <t>NEOGOV &amp; PowerDMS by NEOGOV</t>
-        </is>
-      </c>
-      <c r="B250" s="19" t="n"/>
+          <t>Netchex</t>
+        </is>
+      </c>
+      <c r="B250" s="19" t="inlineStr">
+        <is>
+          <t>Covington, LA</t>
+        </is>
+      </c>
       <c r="C250" s="20" t="n">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="D250" s="19" t="inlineStr">
         <is>
@@ -31961,28 +31917,28 @@
       </c>
       <c r="E250" s="19" t="inlineStr">
         <is>
-          <t>HR, policy and training software for government - exhibited at NRPA 2026</t>
-        </is>
-      </c>
-      <c r="F250" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Payroll and HR software - exhibited at AB Show 2026</t>
+        </is>
+      </c>
+      <c r="F250" s="22" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>Netchex</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>Covington, LA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="C251" s="6" t="n">
-        <v>2003</v>
+        <v>2017</v>
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
@@ -31991,28 +31947,28 @@
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>Payroll and HR software - exhibited at AB Show 2026</t>
-        </is>
-      </c>
-      <c r="F251" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Student loan repayment and PSLF navigation benefit sold to public-service employers (NYC partnership) - exhibited at NLC City Summit 2026</t>
+        </is>
+      </c>
+      <c r="F251" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="19" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>Geographic Solutions</t>
         </is>
       </c>
       <c r="B252" s="19" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Palm Harbor, FL</t>
         </is>
       </c>
       <c r="C252" s="20" t="n">
-        <v>2017</v>
+        <v>1993</v>
       </c>
       <c r="D252" s="19" t="inlineStr">
         <is>
@@ -32021,28 +31977,28 @@
       </c>
       <c r="E252" s="19" t="inlineStr">
         <is>
-          <t>Student loan repayment and PSLF navigation benefit sold to public-service employers (NYC partnership) - exhibited at NLC City Summit 2026</t>
+          <t>Workforce case management and job-matching systems for state workforce agencies - exhibited at NASWA 2025</t>
         </is>
       </c>
       <c r="F252" s="21" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
         <is>
-          <t>Geographic Solutions</t>
+          <t>Vitech Systems Group</t>
         </is>
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>Palm Harbor, FL</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="C253" s="6" t="n">
-        <v>1993</v>
+        <v>1990</v>
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
@@ -32051,28 +32007,28 @@
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
-          <t>Workforce case management and job-matching systems for state workforce agencies - exhibited at NASWA 2025</t>
+          <t>V3locity pension and benefits administration for public retirement systems</t>
         </is>
       </c>
       <c r="F253" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="19" t="inlineStr">
         <is>
-          <t>Vitech Systems Group</t>
+          <t>Sagitec Solutions</t>
         </is>
       </c>
       <c r="B254" s="19" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Saint Paul, MN</t>
         </is>
       </c>
       <c r="C254" s="20" t="n">
-        <v>1990</v>
+        <v>2004</v>
       </c>
       <c r="D254" s="19" t="inlineStr">
         <is>
@@ -32081,28 +32037,28 @@
       </c>
       <c r="E254" s="19" t="inlineStr">
         <is>
-          <t>V3locity pension and benefits administration for public retirement systems</t>
-        </is>
-      </c>
-      <c r="F254" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Pension, unemployment insurance and workforce systems for state agencies - exhibited at SNA ANC 2027</t>
+        </is>
+      </c>
+      <c r="F254" s="22" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>Sagitec Solutions</t>
+          <t>MissionSquare Retirement</t>
         </is>
       </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
-          <t>Saint Paul, MN</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="C255" s="6" t="n">
-        <v>2004</v>
+        <v>1972</v>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
@@ -32111,28 +32067,28 @@
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
-          <t>Pension, unemployment insurance and workforce systems for state agencies - exhibited at SNA ANC 2027</t>
-        </is>
-      </c>
-      <c r="F255" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>457/401(a) retirement plan administration for public sector employers - exhibited at Maryland Municipal League 2026</t>
+        </is>
+      </c>
+      <c r="F255" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="19" t="inlineStr">
         <is>
-          <t>MissionSquare Retirement</t>
+          <t>American Fidelity</t>
         </is>
       </c>
       <c r="B256" s="19" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Oklahoma City, OK</t>
         </is>
       </c>
       <c r="C256" s="20" t="n">
-        <v>1972</v>
+        <v>1960</v>
       </c>
       <c r="D256" s="19" t="inlineStr">
         <is>
@@ -32141,28 +32097,28 @@
       </c>
       <c r="E256" s="19" t="inlineStr">
         <is>
-          <t>457/401(a) retirement plan administration for public sector employers - exhibited at Maryland Municipal League 2026</t>
-        </is>
-      </c>
-      <c r="F256" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Employee benefits, enrollment and HR services for public sector employers</t>
+        </is>
+      </c>
+      <c r="F256" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Account Manager (Denver, Colorado)</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>American Fidelity</t>
+          <t>TCP Software</t>
         </is>
       </c>
       <c r="B257" s="5" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK</t>
+          <t>Plano, TX</t>
         </is>
       </c>
       <c r="C257" s="6" t="n">
-        <v>1960</v>
+        <v>1988</v>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
@@ -32171,28 +32127,28 @@
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
-          <t>Employee benefits, enrollment and HR services for public sector employers</t>
+          <t>Time, attendance and scheduling for government, education and public safety - exhibited at GFOA 2026</t>
         </is>
       </c>
       <c r="F257" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Manager (Denver, Colorado)</t>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="19" t="inlineStr">
         <is>
-          <t>TCP Software</t>
+          <t>Avue Technologies</t>
         </is>
       </c>
       <c r="B258" s="19" t="inlineStr">
         <is>
-          <t>Plano, TX</t>
+          <t>Tacoma, WA</t>
         </is>
       </c>
       <c r="C258" s="20" t="n">
-        <v>1988</v>
+        <v>1998</v>
       </c>
       <c r="D258" s="19" t="inlineStr">
         <is>
@@ -32201,28 +32157,28 @@
       </c>
       <c r="E258" s="19" t="inlineStr">
         <is>
-          <t>Time, attendance and scheduling for government, education and public safety - exhibited at GFOA 2026</t>
-        </is>
-      </c>
-      <c r="F258" s="22" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>HR automation, position classification and hiring for government agencies</t>
+        </is>
+      </c>
+      <c r="F258" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>Avue Technologies</t>
+          <t>Acendre</t>
         </is>
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
-          <t>Tacoma, WA</t>
+          <t>Arlington, VA</t>
         </is>
       </c>
       <c r="C259" s="6" t="n">
-        <v>1998</v>
+        <v>2015</v>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
@@ -32231,7 +32187,7 @@
       </c>
       <c r="E259" s="5" t="inlineStr">
         <is>
-          <t>HR automation, position classification and hiring for government agencies</t>
+          <t>Talent management and recruiting software for government and public sector</t>
         </is>
       </c>
       <c r="F259" s="7" t="inlineStr">
@@ -32243,16 +32199,16 @@
     <row r="260">
       <c r="A260" s="19" t="inlineStr">
         <is>
-          <t>Acendre</t>
+          <t>VidCruiter</t>
         </is>
       </c>
       <c r="B260" s="19" t="inlineStr">
         <is>
-          <t>Arlington, VA</t>
+          <t>Moncton, NB, Canada</t>
         </is>
       </c>
       <c r="C260" s="20" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="D260" s="19" t="inlineStr">
         <is>
@@ -32261,28 +32217,28 @@
       </c>
       <c r="E260" s="19" t="inlineStr">
         <is>
-          <t>Talent management and recruiting software for government and public sector</t>
+          <t>Structured video interviewing and hiring workflows sold heavily to public sector</t>
         </is>
       </c>
       <c r="F260" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>VidCruiter</t>
+          <t>I/O Solutions (IOS)</t>
         </is>
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
-          <t>Moncton, NB, Canada</t>
+          <t>Westchester, IL</t>
         </is>
       </c>
       <c r="C261" s="6" t="n">
-        <v>2012</v>
+        <v>1997</v>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
@@ -32291,7 +32247,7 @@
       </c>
       <c r="E261" s="5" t="inlineStr">
         <is>
-          <t>Structured video interviewing and hiring workflows sold heavily to public sector</t>
+          <t>Public safety and civil service selection testing for government employers</t>
         </is>
       </c>
       <c r="F261" s="7" t="inlineStr">
@@ -32303,16 +32259,16 @@
     <row r="262">
       <c r="A262" s="19" t="inlineStr">
         <is>
-          <t>I/O Solutions (IOS)</t>
+          <t>National Testing Network</t>
         </is>
       </c>
       <c r="B262" s="19" t="inlineStr">
         <is>
-          <t>Westchester, IL</t>
+          <t>Bend, OR</t>
         </is>
       </c>
       <c r="C262" s="20" t="n">
-        <v>1997</v>
+        <v>2002</v>
       </c>
       <c r="D262" s="19" t="inlineStr">
         <is>
@@ -32321,7 +32277,7 @@
       </c>
       <c r="E262" s="19" t="inlineStr">
         <is>
-          <t>Public safety and civil service selection testing for government employers</t>
+          <t>Candidate recruiting and entry-level testing services for public safety agencies</t>
         </is>
       </c>
       <c r="F262" s="21" t="inlineStr">
@@ -32333,16 +32289,16 @@
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>National Testing Network</t>
+          <t>Public Safety Testing (Ergometrics)</t>
         </is>
       </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
-          <t>Bend, OR</t>
+          <t>Lynnwood, WA</t>
         </is>
       </c>
       <c r="C263" s="6" t="n">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
@@ -32351,7 +32307,7 @@
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
-          <t>Candidate recruiting and entry-level testing services for public safety agencies</t>
+          <t>Recruitment, testing and candidate pipelines for police, fire and dispatch</t>
         </is>
       </c>
       <c r="F263" s="7" t="inlineStr">
@@ -32363,16 +32319,16 @@
     <row r="264">
       <c r="A264" s="19" t="inlineStr">
         <is>
-          <t>Public Safety Testing (Ergometrics)</t>
+          <t>Fire &amp; Police Selection (FPSI)</t>
         </is>
       </c>
       <c r="B264" s="19" t="inlineStr">
         <is>
-          <t>Lynnwood, WA</t>
+          <t>Pasadena, CA</t>
         </is>
       </c>
       <c r="C264" s="20" t="n">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="D264" s="19" t="inlineStr">
         <is>
@@ -32381,29 +32337,27 @@
       </c>
       <c r="E264" s="19" t="inlineStr">
         <is>
-          <t>Recruitment, testing and candidate pipelines for police, fire and dispatch</t>
+          <t>Promotional and entry-level exams for fire and police departments</t>
         </is>
       </c>
       <c r="F264" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
         <is>
-          <t>Fire &amp; Police Selection (FPSI)</t>
+          <t>PlanIt Schedule</t>
         </is>
       </c>
       <c r="B265" s="5" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
-        </is>
-      </c>
-      <c r="C265" s="6" t="n">
-        <v>1996</v>
-      </c>
+          <t>Lewisburg, PA</t>
+        </is>
+      </c>
+      <c r="C265" s="6" t="n"/>
       <c r="D265" s="5" t="inlineStr">
         <is>
           <t>HR &amp; Workforce</t>
@@ -32411,27 +32365,29 @@
       </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
-          <t>Promotional and entry-level exams for fire and police departments</t>
+          <t>Public safety staff scheduling and time-off management for departments</t>
         </is>
       </c>
       <c r="F265" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="19" t="inlineStr">
         <is>
-          <t>PlanIt Schedule</t>
+          <t>Authorium</t>
         </is>
       </c>
       <c r="B266" s="19" t="inlineStr">
         <is>
-          <t>Lewisburg, PA</t>
-        </is>
-      </c>
-      <c r="C266" s="20" t="n"/>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="C266" s="20" t="n">
+        <v>2016</v>
+      </c>
       <c r="D266" s="19" t="inlineStr">
         <is>
           <t>HR &amp; Workforce</t>
@@ -32439,28 +32395,28 @@
       </c>
       <c r="E266" s="19" t="inlineStr">
         <is>
-          <t>Public safety staff scheduling and time-off management for departments</t>
-        </is>
-      </c>
-      <c r="F266" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Document-driven workflow for government procurement, budget and HR processes</t>
+        </is>
+      </c>
+      <c r="F266" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>Authorium</t>
+          <t>Propelus</t>
         </is>
       </c>
       <c r="B267" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="C267" s="6" t="n">
-        <v>2016</v>
+        <v>2003</v>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
@@ -32469,28 +32425,28 @@
       </c>
       <c r="E267" s="5" t="inlineStr">
         <is>
-          <t>Document-driven workflow for government procurement, budget and HR processes</t>
-        </is>
-      </c>
-      <c r="F267" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Customer Success Manager only</t>
+          <t>License verification and workforce compliance for agencies and regulators</t>
+        </is>
+      </c>
+      <c r="F267" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Sales Executive - Central Region ( (Remote - US)</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="19" t="inlineStr">
         <is>
-          <t>Propelus</t>
+          <t>Springbrook Software</t>
         </is>
       </c>
       <c r="B268" s="19" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="C268" s="20" t="n">
-        <v>2003</v>
+        <v>1985</v>
       </c>
       <c r="D268" s="19" t="inlineStr">
         <is>
@@ -32499,28 +32455,28 @@
       </c>
       <c r="E268" s="19" t="inlineStr">
         <is>
-          <t>License verification and workforce compliance for agencies and regulators</t>
-        </is>
-      </c>
-      <c r="F268" s="22" t="inlineStr">
-        <is>
-          <t>Yes - Sales Executive - Central Region ( (Remote - US)</t>
+          <t>Municipal ERP with payroll, HR and time entry for small local governments - exhibited at GFOA 2026</t>
+        </is>
+      </c>
+      <c r="F268" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>Springbrook Software</t>
+          <t>Edmunds GovTech</t>
         </is>
       </c>
       <c r="B269" s="5" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Northfield, NJ</t>
         </is>
       </c>
       <c r="C269" s="6" t="n">
-        <v>1985</v>
+        <v>1972</v>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
@@ -32529,28 +32485,28 @@
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>Municipal ERP with payroll, HR and time entry for small local governments - exhibited at GFOA 2026</t>
-        </is>
-      </c>
-      <c r="F269" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Local government ERP including payroll and personnel modules - exhibited at GFOA 2026, Maryland Municipal League 2026</t>
+        </is>
+      </c>
+      <c r="F269" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Client Success Manager only</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="19" t="inlineStr">
         <is>
-          <t>Edmunds GovTech</t>
+          <t>Black Mountain Software</t>
         </is>
       </c>
       <c r="B270" s="19" t="inlineStr">
         <is>
-          <t>Northfield, NJ</t>
+          <t>Polson, MT</t>
         </is>
       </c>
       <c r="C270" s="20" t="n">
-        <v>1972</v>
+        <v>1989</v>
       </c>
       <c r="D270" s="19" t="inlineStr">
         <is>
@@ -32559,28 +32515,28 @@
       </c>
       <c r="E270" s="19" t="inlineStr">
         <is>
-          <t>Local government ERP including payroll and personnel modules - exhibited at GFOA 2026, Maryland Municipal League 2026</t>
-        </is>
-      </c>
-      <c r="F270" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Client Success Manager only</t>
+          <t>Accounting, payroll and HR software for small towns and rural counties</t>
+        </is>
+      </c>
+      <c r="F270" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>Black Mountain Software</t>
+          <t>Harris Local Government</t>
         </is>
       </c>
       <c r="B271" s="5" t="inlineStr">
         <is>
-          <t>Polson, MT</t>
+          <t>Ottawa, ON, Canada</t>
         </is>
       </c>
       <c r="C271" s="6" t="n">
-        <v>1989</v>
+        <v>1976</v>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
@@ -32589,28 +32545,28 @@
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>Accounting, payroll and HR software for small towns and rural counties</t>
+          <t>ERP, payroll and HR systems for municipal and county government</t>
         </is>
       </c>
       <c r="F271" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 404 for https://harrislocalgov.com/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="19" t="inlineStr">
         <is>
-          <t>Harris Local Government</t>
+          <t>Fast Enterprises</t>
         </is>
       </c>
       <c r="B272" s="19" t="inlineStr">
         <is>
-          <t>Ottawa, ON, Canada</t>
+          <t>Centennial, CO</t>
         </is>
       </c>
       <c r="C272" s="20" t="n">
-        <v>1976</v>
+        <v>1998</v>
       </c>
       <c r="D272" s="19" t="inlineStr">
         <is>
@@ -32619,28 +32575,28 @@
       </c>
       <c r="E272" s="19" t="inlineStr">
         <is>
-          <t>ERP, payroll and HR systems for municipal and county government</t>
+          <t>Unemployment insurance, labor and revenue systems for state agencies - exhibited at NASWA 2025, NCSEA 2026</t>
         </is>
       </c>
       <c r="F272" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://harrislocalgov.com/</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>Fast Enterprises</t>
+          <t>SkillSmart</t>
         </is>
       </c>
       <c r="B273" s="5" t="inlineStr">
         <is>
-          <t>Centennial, CO</t>
+          <t>Rockville, MD</t>
         </is>
       </c>
       <c r="C273" s="6" t="n">
-        <v>1998</v>
+        <v>2013</v>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
@@ -32649,7 +32605,7 @@
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
-          <t>Unemployment insurance, labor and revenue systems for state agencies - exhibited at NASWA 2025, NCSEA 2026</t>
+          <t>Workforce compliance and local-hire tracking for public projects and agencies</t>
         </is>
       </c>
       <c r="F273" s="7" t="inlineStr">
@@ -32661,16 +32617,16 @@
     <row r="274">
       <c r="A274" s="19" t="inlineStr">
         <is>
-          <t>SkillSmart</t>
+          <t>Careers In Government</t>
         </is>
       </c>
       <c r="B274" s="19" t="inlineStr">
         <is>
-          <t>Rockville, MD</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="C274" s="20" t="n">
-        <v>2013</v>
+        <v>1996</v>
       </c>
       <c r="D274" s="19" t="inlineStr">
         <is>
@@ -32679,28 +32635,24 @@
       </c>
       <c r="E274" s="19" t="inlineStr">
         <is>
-          <t>Workforce compliance and local-hire tracking for public projects and agencies</t>
+          <t>Job board and employer branding for public sector hiring agencies</t>
         </is>
       </c>
       <c r="F274" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>Careers In Government</t>
-        </is>
-      </c>
-      <c r="B275" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
+          <t>Apply Government Solutions</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="n"/>
       <c r="C275" s="6" t="n">
-        <v>1996</v>
+        <v>2002</v>
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
@@ -32709,7 +32661,7 @@
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
-          <t>Job board and employer branding for public sector hiring agencies</t>
+          <t>FedHire talent acquisition and hiring management system for government agencies - exhibited at NASWA 2025</t>
         </is>
       </c>
       <c r="F275" s="7" t="inlineStr">
@@ -32721,42 +32673,46 @@
     <row r="276">
       <c r="A276" s="19" t="inlineStr">
         <is>
-          <t>Apply Government Solutions</t>
-        </is>
-      </c>
-      <c r="B276" s="19" t="n"/>
+          <t>PlotBox</t>
+        </is>
+      </c>
+      <c r="B276" s="19" t="inlineStr">
+        <is>
+          <t>Ballymena, Northern Ireland, UK</t>
+        </is>
+      </c>
       <c r="C276" s="20" t="n">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="D276" s="19" t="inlineStr">
         <is>
-          <t>HR &amp; Workforce</t>
+          <t>Cemetery Management</t>
         </is>
       </c>
       <c r="E276" s="19" t="inlineStr">
         <is>
-          <t>FedHire talent acquisition and hiring management system for government agencies - exhibited at NASWA 2025</t>
+          <t>Cloud cemetery and crematory management with georectified GIS mapping for munis and funeral groups</t>
         </is>
       </c>
       <c r="F276" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>PlotBox</t>
+          <t>CIMS Cemetery Software</t>
         </is>
       </c>
       <c r="B277" s="5" t="inlineStr">
         <is>
-          <t>Ballymena, Northern Ireland, UK</t>
+          <t>Madison, WI</t>
         </is>
       </c>
       <c r="C277" s="6" t="n">
-        <v>2012</v>
+        <v>1998</v>
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
@@ -32765,28 +32721,28 @@
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
-          <t>Cloud cemetery and crematory management with georectified GIS mapping for munis and funeral groups</t>
+          <t>Cemetery records and GIS mapping software plus drone/GPR services (Ramaker &amp; Associates)</t>
         </is>
       </c>
       <c r="F277" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="19" t="inlineStr">
         <is>
-          <t>CIMS Cemetery Software</t>
+          <t>OpusXenta</t>
         </is>
       </c>
       <c r="B278" s="19" t="inlineStr">
         <is>
-          <t>Madison, WI</t>
+          <t>Sydney, Australia</t>
         </is>
       </c>
       <c r="C278" s="20" t="n">
-        <v>1998</v>
+        <v>2016</v>
       </c>
       <c r="D278" s="19" t="inlineStr">
         <is>
@@ -32795,28 +32751,28 @@
       </c>
       <c r="E278" s="19" t="inlineStr">
         <is>
-          <t>Cemetery records and GIS mapping software plus drone/GPR services (Ramaker &amp; Associates)</t>
+          <t>Byondcloud cemetery and crematoria management software for municipal and private cemeteries</t>
         </is>
       </c>
       <c r="F278" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>OpusXenta</t>
+          <t>webCemeteries</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
         <is>
-          <t>Sydney, Australia</t>
+          <t>Kutztown, Pennsylvania</t>
         </is>
       </c>
       <c r="C279" s="6" t="n">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
@@ -32825,28 +32781,28 @@
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>Byondcloud cemetery and crematoria management software for municipal and private cemeteries</t>
+          <t>Cemetery mapping, records and website software for municipal and private cemeteries</t>
         </is>
       </c>
       <c r="F279" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="19" t="inlineStr">
         <is>
-          <t>webCemeteries</t>
+          <t>CemSites</t>
         </is>
       </c>
       <c r="B280" s="19" t="inlineStr">
         <is>
-          <t>Kutztown, Pennsylvania</t>
+          <t>Perryopolis, Pennsylvania</t>
         </is>
       </c>
       <c r="C280" s="20" t="n">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="D280" s="19" t="inlineStr">
         <is>
@@ -32855,29 +32811,27 @@
       </c>
       <c r="E280" s="19" t="inlineStr">
         <is>
-          <t>Cemetery mapping, records and website software for municipal and private cemeteries</t>
+          <t>Cemetery management, mapping and websites for city and nonprofit cemeteries</t>
         </is>
       </c>
       <c r="F280" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>CemSites</t>
+          <t>Pontem Software</t>
         </is>
       </c>
       <c r="B281" s="5" t="inlineStr">
         <is>
-          <t>Perryopolis, Pennsylvania</t>
-        </is>
-      </c>
-      <c r="C281" s="6" t="n">
-        <v>2012</v>
-      </c>
+          <t>Grand Ledge, Michigan</t>
+        </is>
+      </c>
+      <c r="C281" s="6" t="n"/>
       <c r="D281" s="5" t="inlineStr">
         <is>
           <t>Cemetery Management</t>
@@ -32885,27 +32839,29 @@
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
-          <t>Cemetery management, mapping and websites for city and nonprofit cemeteries</t>
+          <t>Cemetery Data Manager records and mapping software for municipal cemeteries</t>
         </is>
       </c>
       <c r="F281" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="19" t="inlineStr">
         <is>
-          <t>Pontem Software</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="B282" s="19" t="inlineStr">
         <is>
-          <t>Grand Ledge, Michigan</t>
-        </is>
-      </c>
-      <c r="C282" s="20" t="n"/>
+          <t>Melbourne, Australia</t>
+        </is>
+      </c>
+      <c r="C282" s="20" t="n">
+        <v>2016</v>
+      </c>
       <c r="D282" s="19" t="inlineStr">
         <is>
           <t>Cemetery Management</t>
@@ -32913,7 +32869,7 @@
       </c>
       <c r="E282" s="19" t="inlineStr">
         <is>
-          <t>Cemetery Data Manager records and mapping software for municipal cemeteries</t>
+          <t>Cloud cemetery records, mapping and digitization for municipal and private cemeteries</t>
         </is>
       </c>
       <c r="F282" s="21" t="inlineStr">
@@ -32925,16 +32881,16 @@
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>Everspot</t>
         </is>
       </c>
       <c r="B283" s="5" t="inlineStr">
         <is>
-          <t>Melbourne, Australia</t>
+          <t>Pittsburgh, Pennsylvania</t>
         </is>
       </c>
       <c r="C283" s="6" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
@@ -32943,7 +32899,7 @@
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
-          <t>Cloud cemetery records, mapping and digitization for municipal and private cemeteries</t>
+          <t>Cemetery mapping and interment records platform for cemetery operators</t>
         </is>
       </c>
       <c r="F283" s="7" t="inlineStr">
@@ -32955,17 +32911,15 @@
     <row r="284">
       <c r="A284" s="19" t="inlineStr">
         <is>
-          <t>Everspot</t>
+          <t>EverArk</t>
         </is>
       </c>
       <c r="B284" s="19" t="inlineStr">
         <is>
-          <t>Pittsburgh, Pennsylvania</t>
-        </is>
-      </c>
-      <c r="C284" s="20" t="n">
-        <v>2023</v>
-      </c>
+          <t>Rocklin, California</t>
+        </is>
+      </c>
+      <c r="C284" s="20" t="n"/>
       <c r="D284" s="19" t="inlineStr">
         <is>
           <t>Cemetery Management</t>
@@ -32973,7 +32927,7 @@
       </c>
       <c r="E284" s="19" t="inlineStr">
         <is>
-          <t>Cemetery mapping and interment records platform for cemetery operators</t>
+          <t>Digital cemetery records, mapping and memorial platform for cemetery owners</t>
         </is>
       </c>
       <c r="F284" s="21" t="inlineStr">
@@ -32985,12 +32939,12 @@
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>EverArk</t>
+          <t>Grave Discover Software</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
         <is>
-          <t>Rocklin, California</t>
+          <t>Iowa, United States</t>
         </is>
       </c>
       <c r="C285" s="6" t="n"/>
@@ -33001,7 +32955,7 @@
       </c>
       <c r="E285" s="5" t="inlineStr">
         <is>
-          <t>Digital cemetery records, mapping and memorial platform for cemetery owners</t>
+          <t>Cemetery record management and public search tools for municipal cemeteries</t>
         </is>
       </c>
       <c r="F285" s="7" t="inlineStr">
@@ -33013,15 +32967,17 @@
     <row r="286">
       <c r="A286" s="19" t="inlineStr">
         <is>
-          <t>Grave Discover Software</t>
+          <t>CemeteryFind</t>
         </is>
       </c>
       <c r="B286" s="19" t="inlineStr">
         <is>
-          <t>Iowa, United States</t>
-        </is>
-      </c>
-      <c r="C286" s="20" t="n"/>
+          <t>Alpharetta, Georgia</t>
+        </is>
+      </c>
+      <c r="C286" s="20" t="n">
+        <v>1992</v>
+      </c>
       <c r="D286" s="19" t="inlineStr">
         <is>
           <t>Cemetery Management</t>
@@ -33029,7 +32985,7 @@
       </c>
       <c r="E286" s="19" t="inlineStr">
         <is>
-          <t>Cemetery record management and public search tools for municipal cemeteries</t>
+          <t>Cemetery records digitization, mapping and search software for cemeteries</t>
         </is>
       </c>
       <c r="F286" s="21" t="inlineStr">
@@ -33041,16 +32997,16 @@
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>CemeteryFind</t>
+          <t>Legacy Mark</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
         <is>
-          <t>Alpharetta, Georgia</t>
+          <t>Chambersburg, Pennsylvania</t>
         </is>
       </c>
       <c r="C287" s="6" t="n">
-        <v>1992</v>
+        <v>1987</v>
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
@@ -33059,7 +33015,7 @@
       </c>
       <c r="E287" s="5" t="inlineStr">
         <is>
-          <t>Cemetery records digitization, mapping and search software for cemeteries</t>
+          <t>Cemetery Office Suite records and deed management software for cemeteries</t>
         </is>
       </c>
       <c r="F287" s="7" t="inlineStr">
@@ -33071,17 +33027,15 @@
     <row r="288">
       <c r="A288" s="19" t="inlineStr">
         <is>
-          <t>Legacy Mark</t>
+          <t>Memorial Business Systems</t>
         </is>
       </c>
       <c r="B288" s="19" t="inlineStr">
         <is>
-          <t>Chambersburg, Pennsylvania</t>
-        </is>
-      </c>
-      <c r="C288" s="20" t="n">
-        <v>1987</v>
-      </c>
+          <t>Franklin, Tennessee</t>
+        </is>
+      </c>
+      <c r="C288" s="20" t="n"/>
       <c r="D288" s="19" t="inlineStr">
         <is>
           <t>Cemetery Management</t>
@@ -33089,7 +33043,7 @@
       </c>
       <c r="E288" s="19" t="inlineStr">
         <is>
-          <t>Cemetery Office Suite records and deed management software for cemeteries</t>
+          <t>Nexus cemetery and funeral home management software for cemetery operators</t>
         </is>
       </c>
       <c r="F288" s="21" t="inlineStr">
@@ -33101,15 +33055,17 @@
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>Memorial Business Systems</t>
+          <t>SRS Computing</t>
         </is>
       </c>
       <c r="B289" s="5" t="inlineStr">
         <is>
-          <t>Franklin, Tennessee</t>
-        </is>
-      </c>
-      <c r="C289" s="6" t="n"/>
+          <t>Wexford, Pennsylvania</t>
+        </is>
+      </c>
+      <c r="C289" s="6" t="n">
+        <v>1999</v>
+      </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
           <t>Cemetery Management</t>
@@ -33117,29 +33073,27 @@
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>Nexus cemetery and funeral home management software for cemetery operators</t>
+          <t>Funeral home and cemetery management software including municipal cemeteries</t>
         </is>
       </c>
       <c r="F289" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - board is another company's - not read</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="19" t="inlineStr">
         <is>
-          <t>SRS Computing</t>
+          <t>Tribute Technology</t>
         </is>
       </c>
       <c r="B290" s="19" t="inlineStr">
         <is>
-          <t>Wexford, Pennsylvania</t>
-        </is>
-      </c>
-      <c r="C290" s="20" t="n">
-        <v>1999</v>
-      </c>
+          <t>Chicago, Illinois</t>
+        </is>
+      </c>
+      <c r="C290" s="20" t="n"/>
       <c r="D290" s="19" t="inlineStr">
         <is>
           <t>Cemetery Management</t>
@@ -33147,24 +33101,24 @@
       </c>
       <c r="E290" s="19" t="inlineStr">
         <is>
-          <t>Funeral home and cemetery management software including municipal cemeteries</t>
-        </is>
-      </c>
-      <c r="F290" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - board is another company's - not read</t>
+          <t>Deathcare technology suite including cemetery and memorial management software</t>
+        </is>
+      </c>
+      <c r="F290" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>Tribute Technology</t>
+          <t>All Funeral Services (Cemetery Workstation)</t>
         </is>
       </c>
       <c r="B291" s="5" t="inlineStr">
         <is>
-          <t>Chicago, Illinois</t>
+          <t>New York, New York</t>
         </is>
       </c>
       <c r="C291" s="6" t="n"/>
@@ -33175,27 +33129,29 @@
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>Deathcare technology suite including cemetery and memorial management software</t>
-        </is>
-      </c>
-      <c r="F291" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+          <t>Cloud cemetery workstation, mapping and burial records for cemetery operators</t>
+        </is>
+      </c>
+      <c r="F291" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="19" t="inlineStr">
         <is>
-          <t>All Funeral Services (Cemetery Workstation)</t>
+          <t>NewCom Technologies</t>
         </is>
       </c>
       <c r="B292" s="19" t="inlineStr">
         <is>
-          <t>New York, New York</t>
-        </is>
-      </c>
-      <c r="C292" s="20" t="n"/>
+          <t>Des Moines, Iowa</t>
+        </is>
+      </c>
+      <c r="C292" s="20" t="n">
+        <v>1995</v>
+      </c>
       <c r="D292" s="19" t="inlineStr">
         <is>
           <t>Cemetery Management</t>
@@ -33203,7 +33159,7 @@
       </c>
       <c r="E292" s="19" t="inlineStr">
         <is>
-          <t>Cloud cemetery workstation, mapping and burial records for cemetery operators</t>
+          <t>Cemetery management system for municipal and religious cemetery operators</t>
         </is>
       </c>
       <c r="F292" s="21" t="inlineStr">
@@ -33215,17 +33171,15 @@
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>NewCom Technologies</t>
+          <t>Lazarus Cemetery Mapping</t>
         </is>
       </c>
       <c r="B293" s="5" t="inlineStr">
         <is>
-          <t>Des Moines, Iowa</t>
-        </is>
-      </c>
-      <c r="C293" s="6" t="n">
-        <v>1995</v>
-      </c>
+          <t>Indiana, United States</t>
+        </is>
+      </c>
+      <c r="C293" s="6" t="n"/>
       <c r="D293" s="5" t="inlineStr">
         <is>
           <t>Cemetery Management</t>
@@ -33233,7 +33187,7 @@
       </c>
       <c r="E293" s="5" t="inlineStr">
         <is>
-          <t>Cemetery management system for municipal and religious cemetery operators</t>
+          <t>Cemetery GIS mapping and plot inventory services for municipal cemeteries</t>
         </is>
       </c>
       <c r="F293" s="7" t="inlineStr">
@@ -33245,12 +33199,12 @@
     <row r="294">
       <c r="A294" s="19" t="inlineStr">
         <is>
-          <t>Lazarus Cemetery Mapping</t>
+          <t>DEVENTit</t>
         </is>
       </c>
       <c r="B294" s="19" t="inlineStr">
         <is>
-          <t>Indiana, United States</t>
+          <t>Bunschoten-Spakenburg, Netherlands</t>
         </is>
       </c>
       <c r="C294" s="20" t="n"/>
@@ -33261,7 +33215,7 @@
       </c>
       <c r="E294" s="19" t="inlineStr">
         <is>
-          <t>Cemetery GIS mapping and plot inventory services for municipal cemeteries</t>
+          <t>CIBIS cemetery and burial administration software for municipalities</t>
         </is>
       </c>
       <c r="F294" s="21" t="inlineStr">
@@ -33273,12 +33227,12 @@
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>DEVENTit</t>
+          <t>Datawing (Life Events)</t>
         </is>
       </c>
       <c r="B295" s="5" t="inlineStr">
         <is>
-          <t>Bunschoten-Spakenburg, Netherlands</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C295" s="6" t="n"/>
@@ -33289,7 +33243,7 @@
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>CIBIS cemetery and burial administration software for municipalities</t>
+          <t>Life Events cemetery, crematoria and bereavement services software for councils</t>
         </is>
       </c>
       <c r="F295" s="7" t="inlineStr">
@@ -33301,15 +33255,17 @@
     <row r="296">
       <c r="A296" s="19" t="inlineStr">
         <is>
-          <t>Datawing (Life Events)</t>
+          <t>Axiom Cemetery Management Solutions</t>
         </is>
       </c>
       <c r="B296" s="19" t="inlineStr">
         <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="C296" s="20" t="n"/>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C296" s="20" t="n">
+        <v>1983</v>
+      </c>
       <c r="D296" s="19" t="inlineStr">
         <is>
           <t>Cemetery Management</t>
@@ -33317,7 +33273,7 @@
       </c>
       <c r="E296" s="19" t="inlineStr">
         <is>
-          <t>Life Events cemetery, crematoria and bereavement services software for councils</t>
+          <t>Axiom cemetery and funeral management software for cemetery operators</t>
         </is>
       </c>
       <c r="F296" s="21" t="inlineStr">
@@ -33329,16 +33285,16 @@
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>Axiom Cemetery Management Solutions</t>
+          <t>Resting Gardens</t>
         </is>
       </c>
       <c r="B297" s="5" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Verboort, Oregon</t>
         </is>
       </c>
       <c r="C297" s="6" t="n">
-        <v>1983</v>
+        <v>2022</v>
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
@@ -33347,7 +33303,7 @@
       </c>
       <c r="E297" s="5" t="inlineStr">
         <is>
-          <t>Axiom cemetery and funeral management software for cemetery operators</t>
+          <t>Cemetery management and family-facing memorial software for cemeteries</t>
         </is>
       </c>
       <c r="F297" s="7" t="inlineStr">
@@ -33359,17 +33315,15 @@
     <row r="298">
       <c r="A298" s="19" t="inlineStr">
         <is>
-          <t>Resting Gardens</t>
+          <t>Pérennia (Innovexia)</t>
         </is>
       </c>
       <c r="B298" s="19" t="inlineStr">
         <is>
-          <t>Verboort, Oregon</t>
-        </is>
-      </c>
-      <c r="C298" s="20" t="n">
-        <v>2022</v>
-      </c>
+          <t>Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="C298" s="20" t="n"/>
       <c r="D298" s="19" t="inlineStr">
         <is>
           <t>Cemetery Management</t>
@@ -33377,7 +33331,7 @@
       </c>
       <c r="E298" s="19" t="inlineStr">
         <is>
-          <t>Cemetery management and family-facing memorial software for cemeteries</t>
+          <t>Cemetery and funeral home management software for Quebec cemeteries and municipalities</t>
         </is>
       </c>
       <c r="F298" s="21" t="inlineStr">
@@ -33389,45 +33343,41 @@
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>Pérennia (Innovexia)</t>
+          <t>Monday.com</t>
         </is>
       </c>
       <c r="B299" s="5" t="inlineStr">
         <is>
-          <t>Quebec, Canada</t>
-        </is>
-      </c>
-      <c r="C299" s="6" t="n"/>
+          <t>Tel Aviv, Israel</t>
+        </is>
+      </c>
+      <c r="C299" s="6" t="n">
+        <v>2012</v>
+      </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>Cemetery Management</t>
+          <t>IT &amp; AI Platforms</t>
         </is>
       </c>
       <c r="E299" s="5" t="inlineStr">
         <is>
-          <t>Cemetery and funeral home management software for Quebec cemeteries and municipalities</t>
-        </is>
-      </c>
-      <c r="F299" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Work management and collaboration software - exhibited at NACo 2026</t>
+        </is>
+      </c>
+      <c r="F299" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="19" t="inlineStr">
         <is>
-          <t>Monday.com</t>
-        </is>
-      </c>
-      <c r="B300" s="19" t="inlineStr">
-        <is>
-          <t>Tel Aviv, Israel</t>
-        </is>
-      </c>
-      <c r="C300" s="20" t="n">
-        <v>2012</v>
-      </c>
+          <t>Nutanix</t>
+        </is>
+      </c>
+      <c r="B300" s="19" t="n"/>
+      <c r="C300" s="20" t="n"/>
       <c r="D300" s="19" t="inlineStr">
         <is>
           <t>IT &amp; AI Platforms</t>
@@ -33435,22 +33385,26 @@
       </c>
       <c r="E300" s="19" t="inlineStr">
         <is>
-          <t>Work management and collaboration software - exhibited at NACo 2026</t>
-        </is>
-      </c>
-      <c r="F300" s="22" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Hyperconverged cloud infrastructure software - exhibited at NACo 2026, MESC 2026</t>
+        </is>
+      </c>
+      <c r="F300" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>Nutanix</t>
-        </is>
-      </c>
-      <c r="B301" s="5" t="n"/>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="B301" s="5" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA</t>
+        </is>
+      </c>
       <c r="C301" s="6" t="n"/>
       <c r="D301" s="5" t="inlineStr">
         <is>
@@ -33459,27 +33413,29 @@
       </c>
       <c r="E301" s="5" t="inlineStr">
         <is>
-          <t>Hyperconverged cloud infrastructure software - exhibited at NACo 2026, MESC 2026</t>
-        </is>
-      </c>
-      <c r="F301" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Cybersecurity software and network security platforms - exhibited at IACP 2026, NASCIO 2026, CoSN 2026, EDUCAUSE 2026</t>
+        </is>
+      </c>
+      <c r="F301" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="19" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Tanium</t>
         </is>
       </c>
       <c r="B302" s="19" t="inlineStr">
         <is>
-          <t>Santa Clara, CA</t>
-        </is>
-      </c>
-      <c r="C302" s="20" t="n"/>
+          <t>Emeryville, CA</t>
+        </is>
+      </c>
+      <c r="C302" s="20" t="n">
+        <v>2007</v>
+      </c>
       <c r="D302" s="19" t="inlineStr">
         <is>
           <t>IT &amp; AI Platforms</t>
@@ -33487,28 +33443,28 @@
       </c>
       <c r="E302" s="19" t="inlineStr">
         <is>
-          <t>Cybersecurity software and network security platforms - exhibited at IACP 2026, NASCIO 2026, CoSN 2026, EDUCAUSE 2026</t>
+          <t>Endpoint management and security platform - exhibited at NACo 2026, NASCIO 2026, EDUCAUSE 2026</t>
         </is>
       </c>
       <c r="F302" s="22" t="inlineStr">
         <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Yes - Commercial Account Executive (Addison, TX)</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
         <is>
-          <t>Tanium</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B303" s="5" t="inlineStr">
         <is>
-          <t>Emeryville, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="C303" s="6" t="n">
-        <v>2007</v>
+        <v>2021</v>
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
@@ -33517,19 +33473,19 @@
       </c>
       <c r="E303" s="5" t="inlineStr">
         <is>
-          <t>Endpoint management and security platform - exhibited at NACo 2026, NASCIO 2026, EDUCAUSE 2026</t>
-        </is>
-      </c>
-      <c r="F303" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Business Analyst - Salesforce only</t>
+          <t>Claude, sold to state and local agencies through GSA and cooperative vehicles alongside its commercial business</t>
+        </is>
+      </c>
+      <c r="F303" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive, AI Native (New York City, NY;)</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="19" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B304" s="19" t="inlineStr">
@@ -33538,7 +33494,7 @@
         </is>
       </c>
       <c r="C304" s="20" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="D304" s="19" t="inlineStr">
         <is>
@@ -33547,28 +33503,28 @@
       </c>
       <c r="E304" s="19" t="inlineStr">
         <is>
-          <t>Claude, sold to state and local agencies through GSA and cooperative vehicles alongside its commercial business</t>
-        </is>
-      </c>
-      <c r="F304" s="22" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive, AI Native (New York City, NY;)</t>
+          <t>ChatGPT and the API, sold to public sector including named state and local government roles</t>
+        </is>
+      </c>
+      <c r="F304" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Account Director, Large Enterprise only</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Esri Canada</t>
         </is>
       </c>
       <c r="B305" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Toronto, Canada</t>
         </is>
       </c>
       <c r="C305" s="6" t="n">
-        <v>2015</v>
+        <v>1984</v>
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
@@ -33577,28 +33533,28 @@
       </c>
       <c r="E305" s="5" t="inlineStr">
         <is>
-          <t>ChatGPT and the API, sold to public sector including named state and local government roles</t>
-        </is>
-      </c>
-      <c r="F305" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Account Director, Large Enterprise only</t>
+          <t>ArcGIS geographic information system software, apps, and implementation for Canadian governments, utilities, schools, and public agencies - exhibited at IAAO 2026</t>
+        </is>
+      </c>
+      <c r="F305" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="19" t="inlineStr">
         <is>
-          <t>Esri Canada</t>
+          <t>Velosimo</t>
         </is>
       </c>
       <c r="B306" s="19" t="inlineStr">
         <is>
-          <t>Toronto, Canada</t>
+          <t>Herriman, UT</t>
         </is>
       </c>
       <c r="C306" s="20" t="n">
-        <v>1984</v>
+        <v>2018</v>
       </c>
       <c r="D306" s="19" t="inlineStr">
         <is>
@@ -33607,28 +33563,24 @@
       </c>
       <c r="E306" s="19" t="inlineStr">
         <is>
-          <t>ArcGIS geographic information system software, apps, and implementation for Canadian governments, utilities, schools, and public agencies - exhibited at IAAO 2026</t>
+          <t>No-code integration platform with prebuilt connectors linking government systems such as Accela, Tyler, and Laserfiche - exhibited at GFOA 2026</t>
         </is>
       </c>
       <c r="F306" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>Velosimo</t>
-        </is>
-      </c>
-      <c r="B307" s="5" t="inlineStr">
-        <is>
-          <t>Herriman, UT</t>
-        </is>
-      </c>
+          <t>Sectri</t>
+        </is>
+      </c>
+      <c r="B307" s="5" t="n"/>
       <c r="C307" s="6" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
@@ -33637,7 +33589,7 @@
       </c>
       <c r="E307" s="5" t="inlineStr">
         <is>
-          <t>No-code integration platform with prebuilt connectors linking government systems such as Accela, Tyler, and Laserfiche - exhibited at GFOA 2026</t>
+          <t>Cybersecurity program management and NIST CSF compliance platform for county governments and critical infrastructure agencies - exhibited at GMIS International 2026</t>
         </is>
       </c>
       <c r="F307" s="7" t="inlineStr">
@@ -33649,12 +33601,16 @@
     <row r="308">
       <c r="A308" s="19" t="inlineStr">
         <is>
-          <t>Sectri</t>
-        </is>
-      </c>
-      <c r="B308" s="19" t="n"/>
+          <t>SteelCloud</t>
+        </is>
+      </c>
+      <c r="B308" s="19" t="inlineStr">
+        <is>
+          <t>Ashburn, VA</t>
+        </is>
+      </c>
       <c r="C308" s="20" t="n">
-        <v>2017</v>
+        <v>2002</v>
       </c>
       <c r="D308" s="19" t="inlineStr">
         <is>
@@ -33663,29 +33619,23 @@
       </c>
       <c r="E308" s="19" t="inlineStr">
         <is>
-          <t>Cybersecurity program management and NIST CSF compliance platform for county governments and critical infrastructure agencies - exhibited at GMIS International 2026</t>
+          <t>ConfigOS software that automates STIG, CIS Benchmark and CMMC system hardening, remediation and compliance reporting for defense, civilian, state and local agencies - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
       <c r="F308" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
         <is>
-          <t>SteelCloud</t>
-        </is>
-      </c>
-      <c r="B309" s="5" t="inlineStr">
-        <is>
-          <t>Ashburn, VA</t>
-        </is>
-      </c>
-      <c r="C309" s="6" t="n">
-        <v>2002</v>
-      </c>
+          <t>SAND</t>
+        </is>
+      </c>
+      <c r="B309" s="5" t="n"/>
+      <c r="C309" s="6" t="n"/>
       <c r="D309" s="5" t="inlineStr">
         <is>
           <t>IT &amp; AI Platforms</t>
@@ -33693,19 +33643,19 @@
       </c>
       <c r="E309" s="5" t="inlineStr">
         <is>
-          <t>ConfigOS software that automates STIG, CIS Benchmark and CMMC system hardening, remediation and compliance reporting for defense, civilian, state and local agencies - exhibited at EDUCAUSE 2026</t>
-        </is>
-      </c>
-      <c r="F309" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Symmetri AI operations platform for critical infrastructure operators in water, energy, telecom and healthcare - exhibited at AWWA ACE 2026</t>
+        </is>
+      </c>
+      <c r="F309" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Technical Sales Engineer only</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="19" t="inlineStr">
         <is>
-          <t>SAND</t>
+          <t>Civic Roundtable</t>
         </is>
       </c>
       <c r="B310" s="19" t="n"/>
@@ -33717,19 +33667,19 @@
       </c>
       <c r="E310" s="19" t="inlineStr">
         <is>
-          <t>Symmetri AI operations platform for critical infrastructure operators in water, energy, telecom and healthcare - exhibited at AWWA ACE 2026</t>
-        </is>
-      </c>
-      <c r="F310" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Technical Sales Engineer only</t>
+          <t>Government operations platform combining shared workspaces, knowledge base, CRM and AI automation for public agencies - exhibited at APHSA 2026</t>
+        </is>
+      </c>
+      <c r="F310" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
         <is>
-          <t>Civic Roundtable</t>
+          <t>Speridian</t>
         </is>
       </c>
       <c r="B311" s="5" t="n"/>
@@ -33741,31 +33691,37 @@
       </c>
       <c r="E311" s="5" t="inlineStr">
         <is>
-          <t>Government operations platform combining shared workspaces, knowledge base, CRM and AI automation for public agencies - exhibited at APHSA 2026</t>
+          <t>IT consulting and low-code case management (CaseXellence) for public sector agencies, including state health and human services programmes, alongside banking, insurance and retail practices - exhibited at MESC 2026</t>
         </is>
       </c>
       <c r="F311" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="19" t="inlineStr">
         <is>
-          <t>Speridian</t>
-        </is>
-      </c>
-      <c r="B312" s="19" t="n"/>
-      <c r="C312" s="20" t="n"/>
+          <t>AchieveIt</t>
+        </is>
+      </c>
+      <c r="B312" s="19" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="C312" s="20" t="n">
+        <v>2010</v>
+      </c>
       <c r="D312" s="19" t="inlineStr">
         <is>
-          <t>IT &amp; AI Platforms</t>
+          <t>Strategy &amp; Performance</t>
         </is>
       </c>
       <c r="E312" s="19" t="inlineStr">
         <is>
-          <t>IT consulting and low-code case management (CaseXellence) for public sector agencies, including state health and human services programmes, alongside banking, insurance and retail practices - exhibited at MESC 2026</t>
+          <t>Strategy execution and integrated plan management for agencies and enterprises - exhibited at NLC City Summit 2026, NACCHO 360 2026</t>
         </is>
       </c>
       <c r="F312" s="21" t="inlineStr">
@@ -33777,16 +33733,16 @@
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
         <is>
-          <t>AchieveIt</t>
+          <t>Envisio</t>
         </is>
       </c>
       <c r="B313" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Vancouver, BC, Canada</t>
         </is>
       </c>
       <c r="C313" s="6" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
@@ -33795,28 +33751,28 @@
       </c>
       <c r="E313" s="5" t="inlineStr">
         <is>
-          <t>Strategy execution and integrated plan management for agencies and enterprises - exhibited at NLC City Summit 2026, NACCHO 360 2026</t>
-        </is>
-      </c>
-      <c r="F313" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Strategic planning, performance measurement, and public dashboards built for local government</t>
+        </is>
+      </c>
+      <c r="F313" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Senior Account Executive - Public  (Canada)</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="19" t="inlineStr">
         <is>
-          <t>Envisio</t>
+          <t>ClearPoint Strategy</t>
         </is>
       </c>
       <c r="B314" s="19" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Arlington, VA</t>
         </is>
       </c>
       <c r="C314" s="20" t="n">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="D314" s="19" t="inlineStr">
         <is>
@@ -33825,28 +33781,28 @@
       </c>
       <c r="E314" s="19" t="inlineStr">
         <is>
-          <t>Strategic planning, performance measurement, and public dashboards built for local government</t>
+          <t>Strategic plan and KPI reporting (balanced scorecard) for local governments and enterprises</t>
         </is>
       </c>
       <c r="F314" s="22" t="inlineStr">
         <is>
-          <t>Yes - Senior Account Executive - Public  (Canada)</t>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
         <is>
-          <t>ClearPoint Strategy</t>
+          <t>Esper</t>
         </is>
       </c>
       <c r="B315" s="5" t="inlineStr">
         <is>
-          <t>Arlington, VA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="C315" s="6" t="n">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
@@ -33855,28 +33811,28 @@
       </c>
       <c r="E315" s="5" t="inlineStr">
         <is>
-          <t>Strategic plan and KPI reporting (balanced scorecard) for local governments and enterprises</t>
+          <t>Policy and rulemaking workflow: draft, route, approve, and track regulations for agencies</t>
         </is>
       </c>
       <c r="F315" s="10" t="inlineStr">
         <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Yes - Strategic Account Executive - West (Remote)</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="19" t="inlineStr">
         <is>
-          <t>Esper</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="B316" s="19" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Los Altos, CA</t>
         </is>
       </c>
       <c r="C316" s="20" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="D316" s="19" t="inlineStr">
         <is>
@@ -33885,28 +33841,28 @@
       </c>
       <c r="E316" s="19" t="inlineStr">
         <is>
-          <t>Policy and rulemaking workflow: draft, route, approve, and track regulations for agencies</t>
-        </is>
-      </c>
-      <c r="F316" s="22" t="inlineStr">
-        <is>
-          <t>Yes - Strategic Account Executive - West (Remote)</t>
+          <t>Location and foot-traffic analytics with an active city/county economic development vertical</t>
+        </is>
+      </c>
+      <c r="F316" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 404 for https://www.placer.ai/caree</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>Legislaide</t>
         </is>
       </c>
       <c r="B317" s="5" t="inlineStr">
         <is>
-          <t>Los Altos, CA</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="C317" s="6" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
@@ -33915,28 +33871,28 @@
       </c>
       <c r="E317" s="5" t="inlineStr">
         <is>
-          <t>Location and foot-traffic analytics with an active city/county economic development vertical</t>
+          <t>AI legislative drafting, research, and ordinance database for local governments - exhibited at IMLA 2026</t>
         </is>
       </c>
       <c r="F317" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://www.placer.ai/caree</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="19" t="inlineStr">
         <is>
-          <t>Legislaide</t>
+          <t>Social Explorer</t>
         </is>
       </c>
       <c r="B318" s="19" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="C318" s="20" t="n">
-        <v>2023</v>
+        <v>1999</v>
       </c>
       <c r="D318" s="19" t="inlineStr">
         <is>
@@ -33945,7 +33901,7 @@
       </c>
       <c r="E318" s="19" t="inlineStr">
         <is>
-          <t>AI legislative drafting, research, and ordinance database for local governments - exhibited at IMLA 2026</t>
+          <t>Demographic data, mapping, and visualization with 500K+ variables for gov, academia, and planning</t>
         </is>
       </c>
       <c r="F318" s="21" t="inlineStr">
@@ -33957,17 +33913,11 @@
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>Social Explorer</t>
-        </is>
-      </c>
-      <c r="B319" s="5" t="inlineStr">
-        <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
-      <c r="C319" s="6" t="n">
-        <v>1999</v>
-      </c>
+          <t>Quorum</t>
+        </is>
+      </c>
+      <c r="B319" s="5" t="n"/>
+      <c r="C319" s="6" t="n"/>
       <c r="D319" s="5" t="inlineStr">
         <is>
           <t>Strategy &amp; Performance</t>
@@ -33975,23 +33925,29 @@
       </c>
       <c r="E319" s="5" t="inlineStr">
         <is>
-          <t>Demographic data, mapping, and visualization with 500K+ variables for gov, academia, and planning</t>
-        </is>
-      </c>
-      <c r="F319" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Public affairs and legislative tracking software - exhibited at NACo 2026, NLC City Summit 2026</t>
+        </is>
+      </c>
+      <c r="F319" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Account Manager (Washington D.C.)</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="19" t="inlineStr">
         <is>
-          <t>Quorum</t>
-        </is>
-      </c>
-      <c r="B320" s="19" t="n"/>
-      <c r="C320" s="20" t="n"/>
+          <t>EarthDaily</t>
+        </is>
+      </c>
+      <c r="B320" s="19" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, Canada</t>
+        </is>
+      </c>
+      <c r="C320" s="20" t="n">
+        <v>2021</v>
+      </c>
       <c r="D320" s="19" t="inlineStr">
         <is>
           <t>Strategy &amp; Performance</t>
@@ -33999,29 +33955,27 @@
       </c>
       <c r="E320" s="19" t="inlineStr">
         <is>
-          <t>Public affairs and legislative tracking software - exhibited at NACo 2026, NLC City Summit 2026</t>
-        </is>
-      </c>
-      <c r="F320" s="22" t="inlineStr">
-        <is>
-          <t>Yes - Account Manager (Washington D.C.)</t>
+          <t>Satellite earth-observation imagery and change-detection analytics for agencies, insurance, and ag - exhibited at NLC City Summit 2026</t>
+        </is>
+      </c>
+      <c r="F320" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>EarthDaily</t>
+          <t>Balancing Act</t>
         </is>
       </c>
       <c r="B321" s="5" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
-        </is>
-      </c>
-      <c r="C321" s="6" t="n">
-        <v>2021</v>
-      </c>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="C321" s="6" t="n"/>
       <c r="D321" s="5" t="inlineStr">
         <is>
           <t>Strategy &amp; Performance</t>
@@ -34029,27 +33983,29 @@
       </c>
       <c r="E321" s="5" t="inlineStr">
         <is>
-          <t>Satellite earth-observation imagery and change-detection analytics for agencies, insurance, and ag - exhibited at NLC City Summit 2026</t>
+          <t>Interactive budget simulation and priority-setting tools for public agencies</t>
         </is>
       </c>
       <c r="F321" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="19" t="inlineStr">
         <is>
-          <t>Balancing Act</t>
+          <t>Munetrix</t>
         </is>
       </c>
       <c r="B322" s="19" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
-        </is>
-      </c>
-      <c r="C322" s="20" t="n"/>
+          <t>Auburn Hills, MI</t>
+        </is>
+      </c>
+      <c r="C322" s="20" t="n">
+        <v>2010</v>
+      </c>
       <c r="D322" s="19" t="inlineStr">
         <is>
           <t>Strategy &amp; Performance</t>
@@ -34057,29 +34013,27 @@
       </c>
       <c r="E322" s="19" t="inlineStr">
         <is>
-          <t>Interactive budget simulation and priority-setting tools for public agencies</t>
+          <t>Municipal and school performance dashboards, benchmarking and fiscal analytics</t>
         </is>
       </c>
       <c r="F322" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
         <is>
-          <t>Munetrix</t>
+          <t>OnStrategy</t>
         </is>
       </c>
       <c r="B323" s="5" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI</t>
-        </is>
-      </c>
-      <c r="C323" s="6" t="n">
-        <v>2010</v>
-      </c>
+          <t>Reno, NV</t>
+        </is>
+      </c>
+      <c r="C323" s="6" t="n"/>
       <c r="D323" s="5" t="inlineStr">
         <is>
           <t>Strategy &amp; Performance</t>
@@ -34087,27 +34041,25 @@
       </c>
       <c r="E323" s="5" t="inlineStr">
         <is>
-          <t>Municipal and school performance dashboards, benchmarking and fiscal analytics</t>
+          <t>Strategic planning software and facilitation for government and public agencies</t>
         </is>
       </c>
       <c r="F323" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="19" t="inlineStr">
         <is>
-          <t>OnStrategy</t>
-        </is>
-      </c>
-      <c r="B324" s="19" t="inlineStr">
-        <is>
-          <t>Reno, NV</t>
-        </is>
-      </c>
-      <c r="C324" s="20" t="n"/>
+          <t>Spider Strategies</t>
+        </is>
+      </c>
+      <c r="B324" s="19" t="n"/>
+      <c r="C324" s="20" t="n">
+        <v>2003</v>
+      </c>
       <c r="D324" s="19" t="inlineStr">
         <is>
           <t>Strategy &amp; Performance</t>
@@ -34115,24 +34067,28 @@
       </c>
       <c r="E324" s="19" t="inlineStr">
         <is>
-          <t>Strategic planning software and facilitation for government and public agencies</t>
+          <t>Spider Impact balanced scorecard and KPI software used by government agencies</t>
         </is>
       </c>
       <c r="F324" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
         <is>
-          <t>Spider Strategies</t>
-        </is>
-      </c>
-      <c r="B325" s="5" t="n"/>
+          <t>Corporater</t>
+        </is>
+      </c>
+      <c r="B325" s="5" t="inlineStr">
+        <is>
+          <t>Stavanger, Norway</t>
+        </is>
+      </c>
       <c r="C325" s="6" t="n">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
@@ -34141,28 +34097,28 @@
       </c>
       <c r="E325" s="5" t="inlineStr">
         <is>
-          <t>Spider Impact balanced scorecard and KPI software used by government agencies</t>
-        </is>
-      </c>
-      <c r="F325" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Governance, performance and risk management platform for public sector organizations</t>
+        </is>
+      </c>
+      <c r="F325" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="19" t="inlineStr">
         <is>
-          <t>Corporater</t>
+          <t>QPR Software</t>
         </is>
       </c>
       <c r="B326" s="19" t="inlineStr">
         <is>
-          <t>Stavanger, Norway</t>
+          <t>Helsinki, Finland</t>
         </is>
       </c>
       <c r="C326" s="20" t="n">
-        <v>2000</v>
+        <v>1991</v>
       </c>
       <c r="D326" s="19" t="inlineStr">
         <is>
@@ -34171,28 +34127,28 @@
       </c>
       <c r="E326" s="19" t="inlineStr">
         <is>
-          <t>Governance, performance and risk management platform for public sector organizations</t>
-        </is>
-      </c>
-      <c r="F326" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+          <t>Performance management and process mining software for public administrations</t>
+        </is>
+      </c>
+      <c r="F326" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="5" t="inlineStr">
         <is>
-          <t>QPR Software</t>
+          <t>UrbanFootprint</t>
         </is>
       </c>
       <c r="B327" s="5" t="inlineStr">
         <is>
-          <t>Helsinki, Finland</t>
+          <t>Berkeley, CA</t>
         </is>
       </c>
       <c r="C327" s="6" t="n">
-        <v>1991</v>
+        <v>2014</v>
       </c>
       <c r="D327" s="5" t="inlineStr">
         <is>
@@ -34201,28 +34157,28 @@
       </c>
       <c r="E327" s="5" t="inlineStr">
         <is>
-          <t>Performance management and process mining software for public administrations</t>
+          <t>Urban intelligence and resilience analytics for government planning agencies</t>
         </is>
       </c>
       <c r="F327" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="19" t="inlineStr">
         <is>
-          <t>UrbanFootprint</t>
+          <t>Regrid</t>
         </is>
       </c>
       <c r="B328" s="19" t="inlineStr">
         <is>
-          <t>Berkeley, CA</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="C328" s="20" t="n">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="D328" s="19" t="inlineStr">
         <is>
@@ -34231,28 +34187,28 @@
       </c>
       <c r="E328" s="19" t="inlineStr">
         <is>
-          <t>Urban intelligence and resilience analytics for government planning agencies</t>
+          <t>Nationwide parcel data and property mapping licensed to government agencies</t>
         </is>
       </c>
       <c r="F328" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="5" t="inlineStr">
         <is>
-          <t>Regrid</t>
+          <t>Planet Labs</t>
         </is>
       </c>
       <c r="B329" s="5" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="C329" s="6" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="D329" s="5" t="inlineStr">
         <is>
@@ -34261,29 +34217,27 @@
       </c>
       <c r="E329" s="5" t="inlineStr">
         <is>
-          <t>Nationwide parcel data and property mapping licensed to government agencies</t>
+          <t>Daily satellite imagery and analytics sold to government agencies</t>
         </is>
       </c>
       <c r="F329" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="19" t="inlineStr">
         <is>
-          <t>Planet Labs</t>
+          <t>Maxar Intelligence</t>
         </is>
       </c>
       <c r="B330" s="19" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="C330" s="20" t="n">
-        <v>2010</v>
-      </c>
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="C330" s="20" t="n"/>
       <c r="D330" s="19" t="inlineStr">
         <is>
           <t>Strategy &amp; Performance</t>
@@ -34291,7 +34245,7 @@
       </c>
       <c r="E330" s="19" t="inlineStr">
         <is>
-          <t>Daily satellite imagery and analytics sold to government agencies</t>
+          <t>High-resolution satellite imagery and geospatial analytics for public agencies</t>
         </is>
       </c>
       <c r="F330" s="21" t="inlineStr">
@@ -34303,15 +34257,17 @@
     <row r="331">
       <c r="A331" s="5" t="inlineStr">
         <is>
-          <t>Maxar Intelligence</t>
+          <t>Vexcel Imaging</t>
         </is>
       </c>
       <c r="B331" s="5" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="C331" s="6" t="n"/>
+          <t>Graz, Austria</t>
+        </is>
+      </c>
+      <c r="C331" s="6" t="n">
+        <v>1985</v>
+      </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
           <t>Strategy &amp; Performance</t>
@@ -34319,7 +34275,7 @@
       </c>
       <c r="E331" s="5" t="inlineStr">
         <is>
-          <t>High-resolution satellite imagery and geospatial analytics for public agencies</t>
+          <t>Aerial imagery programs and geospatial data licensed to government agencies</t>
         </is>
       </c>
       <c r="F331" s="7" t="inlineStr">
@@ -34331,16 +34287,16 @@
     <row r="332">
       <c r="A332" s="19" t="inlineStr">
         <is>
-          <t>Vexcel Imaging</t>
+          <t>Nearmap</t>
         </is>
       </c>
       <c r="B332" s="19" t="inlineStr">
         <is>
-          <t>Graz, Austria</t>
+          <t>Sydney, Australia</t>
         </is>
       </c>
       <c r="C332" s="20" t="n">
-        <v>1985</v>
+        <v>2007</v>
       </c>
       <c r="D332" s="19" t="inlineStr">
         <is>
@@ -34349,7 +34305,7 @@
       </c>
       <c r="E332" s="19" t="inlineStr">
         <is>
-          <t>Aerial imagery programs and geospatial data licensed to government agencies</t>
+          <t>High-frequency aerial imagery and location content for government departments - exhibited at IAAO 2026</t>
         </is>
       </c>
       <c r="F332" s="21" t="inlineStr">
@@ -34361,16 +34317,16 @@
     <row r="333">
       <c r="A333" s="5" t="inlineStr">
         <is>
-          <t>Nearmap</t>
+          <t>Opendatasoft</t>
         </is>
       </c>
       <c r="B333" s="5" t="inlineStr">
         <is>
-          <t>Sydney, Australia</t>
+          <t>Paris, France</t>
         </is>
       </c>
       <c r="C333" s="6" t="n">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="D333" s="5" t="inlineStr">
         <is>
@@ -34379,29 +34335,23 @@
       </c>
       <c r="E333" s="5" t="inlineStr">
         <is>
-          <t>High-frequency aerial imagery and location content for government departments - exhibited at IAAO 2026</t>
+          <t>Open data portal and data sharing platform for public administrations</t>
         </is>
       </c>
       <c r="F333" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - board is another company's - not read</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="19" t="inlineStr">
         <is>
-          <t>Opendatasoft</t>
-        </is>
-      </c>
-      <c r="B334" s="19" t="inlineStr">
-        <is>
-          <t>Paris, France</t>
-        </is>
-      </c>
-      <c r="C334" s="20" t="n">
-        <v>2011</v>
-      </c>
+          <t>Junar</t>
+        </is>
+      </c>
+      <c r="B334" s="19" t="n"/>
+      <c r="C334" s="20" t="n"/>
       <c r="D334" s="19" t="inlineStr">
         <is>
           <t>Strategy &amp; Performance</t>
@@ -34409,23 +34359,29 @@
       </c>
       <c r="E334" s="19" t="inlineStr">
         <is>
-          <t>Open data portal and data sharing platform for public administrations</t>
+          <t>Open data portals and transparency dashboards for government agencies</t>
         </is>
       </c>
       <c r="F334" s="21" t="inlineStr">
         <is>
-          <t>Unknown - board is another company's - not read</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="5" t="inlineStr">
         <is>
-          <t>Junar</t>
-        </is>
-      </c>
-      <c r="B335" s="5" t="n"/>
-      <c r="C335" s="6" t="n"/>
+          <t>IdeaScale</t>
+        </is>
+      </c>
+      <c r="B335" s="5" t="inlineStr">
+        <is>
+          <t>Berkeley, CA</t>
+        </is>
+      </c>
+      <c r="C335" s="6" t="n">
+        <v>2009</v>
+      </c>
       <c r="D335" s="5" t="inlineStr">
         <is>
           <t>Strategy &amp; Performance</t>
@@ -34433,29 +34389,27 @@
       </c>
       <c r="E335" s="5" t="inlineStr">
         <is>
-          <t>Open data portals and transparency dashboards for government agencies</t>
+          <t>Innovation and idea crowdsourcing platform used by government agencies</t>
         </is>
       </c>
       <c r="F335" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="19" t="inlineStr">
         <is>
-          <t>IdeaScale</t>
+          <t>ResourceX</t>
         </is>
       </c>
       <c r="B336" s="19" t="inlineStr">
         <is>
-          <t>Berkeley, CA</t>
-        </is>
-      </c>
-      <c r="C336" s="20" t="n">
-        <v>2009</v>
-      </c>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="C336" s="20" t="n"/>
       <c r="D336" s="19" t="inlineStr">
         <is>
           <t>Strategy &amp; Performance</t>
@@ -34463,24 +34417,24 @@
       </c>
       <c r="E336" s="19" t="inlineStr">
         <is>
-          <t>Innovation and idea crowdsourcing platform used by government agencies</t>
+          <t>Priority-based budgeting and program cost analytics for local government</t>
         </is>
       </c>
       <c r="F336" s="21" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="5" t="inlineStr">
         <is>
-          <t>ResourceX</t>
+          <t>Elucd</t>
         </is>
       </c>
       <c r="B337" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="C337" s="6" t="n"/>
@@ -34491,24 +34445,24 @@
       </c>
       <c r="E337" s="5" t="inlineStr">
         <is>
-          <t>Priority-based budgeting and program cost analytics for local government</t>
+          <t>Resident sentiment measurement and community trust metrics for city leaders</t>
         </is>
       </c>
       <c r="F337" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="19" t="inlineStr">
         <is>
-          <t>Elucd</t>
+          <t>Numina</t>
         </is>
       </c>
       <c r="B338" s="19" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Brooklyn, NY</t>
         </is>
       </c>
       <c r="C338" s="20" t="n"/>
@@ -34519,7 +34473,7 @@
       </c>
       <c r="E338" s="19" t="inlineStr">
         <is>
-          <t>Resident sentiment measurement and community trust metrics for city leaders</t>
+          <t>Street-level sensors and behavior analytics for city transportation and planning teams</t>
         </is>
       </c>
       <c r="F338" s="21" t="inlineStr">
@@ -34531,44 +34485,46 @@
     <row r="339">
       <c r="A339" s="5" t="inlineStr">
         <is>
-          <t>Numina</t>
+          <t>ES&amp;S (Election Systems &amp; Software)</t>
         </is>
       </c>
       <c r="B339" s="5" t="inlineStr">
         <is>
-          <t>Brooklyn, NY</t>
-        </is>
-      </c>
-      <c r="C339" s="6" t="n"/>
+          <t>Omaha, NE</t>
+        </is>
+      </c>
+      <c r="C339" s="6" t="n">
+        <v>1979</v>
+      </c>
       <c r="D339" s="5" t="inlineStr">
         <is>
-          <t>Strategy &amp; Performance</t>
+          <t>Elections</t>
         </is>
       </c>
       <c r="E339" s="5" t="inlineStr">
         <is>
-          <t>Street-level sensors and behavior analytics for city transportation and planning teams</t>
+          <t>The largest US voting systems vendor: tabulators, ballot marking, election management (founded as AIS)</t>
         </is>
       </c>
       <c r="F339" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="19" t="inlineStr">
         <is>
-          <t>ES&amp;S (Election Systems &amp; Software)</t>
+          <t>Hart InterCivic</t>
         </is>
       </c>
       <c r="B340" s="19" t="inlineStr">
         <is>
-          <t>Omaha, NE</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="C340" s="20" t="n">
-        <v>1979</v>
+        <v>1912</v>
       </c>
       <c r="D340" s="19" t="inlineStr">
         <is>
@@ -34577,28 +34533,28 @@
       </c>
       <c r="E340" s="19" t="inlineStr">
         <is>
-          <t>The largest US voting systems vendor: tabulators, ballot marking, election management (founded as AIS)</t>
+          <t>Verity voting systems: tabulation, ballot marking, and election management for counties</t>
         </is>
       </c>
       <c r="F340" s="21" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="5" t="inlineStr">
         <is>
-          <t>Hart InterCivic</t>
+          <t>KNOWiNK</t>
         </is>
       </c>
       <c r="B341" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>St. Louis, MO</t>
         </is>
       </c>
       <c r="C341" s="6" t="n">
-        <v>1912</v>
+        <v>2011</v>
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
@@ -34607,28 +34563,28 @@
       </c>
       <c r="E341" s="5" t="inlineStr">
         <is>
-          <t>Verity voting systems: tabulation, ballot marking, and election management for counties</t>
+          <t>Poll Pad electronic poll books - the market leader - plus election-day management tools</t>
         </is>
       </c>
       <c r="F341" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 404 for https://knowink.com/careers</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="19" t="inlineStr">
         <is>
-          <t>KNOWiNK</t>
+          <t>Runbeck Election Services</t>
         </is>
       </c>
       <c r="B342" s="19" t="inlineStr">
         <is>
-          <t>St. Louis, MO</t>
+          <t>Phoenix, AZ</t>
         </is>
       </c>
       <c r="C342" s="20" t="n">
-        <v>2011</v>
+        <v>1972</v>
       </c>
       <c r="D342" s="19" t="inlineStr">
         <is>
@@ -34637,28 +34593,28 @@
       </c>
       <c r="E342" s="19" t="inlineStr">
         <is>
-          <t>Poll Pad electronic poll books - the market leader - plus election-day management tools</t>
+          <t>Mail ballot printing, sorting, and signature verification equipment for election offices</t>
         </is>
       </c>
       <c r="F342" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://knowink.com/careers</t>
+          <t>Unknown - HTTP 403 for https://runbeck.net/careers</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="5" t="inlineStr">
         <is>
-          <t>Runbeck Election Services</t>
+          <t>BallotReady</t>
         </is>
       </c>
       <c r="B343" s="5" t="inlineStr">
         <is>
-          <t>Phoenix, AZ</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="C343" s="6" t="n">
-        <v>1972</v>
+        <v>2015</v>
       </c>
       <c r="D343" s="5" t="inlineStr">
         <is>
@@ -34667,28 +34623,28 @@
       </c>
       <c r="E343" s="5" t="inlineStr">
         <is>
-          <t>Mail ballot printing, sorting, and signature verification equipment for election offices</t>
+          <t>Nonpartisan ballot, candidate, and election data (CivicEngine) for orgs, companies, and agencies</t>
         </is>
       </c>
       <c r="F343" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://runbeck.net/careers</t>
+          <t>Unknown - HTTP 404 for https://about.ballotready.o</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="19" t="inlineStr">
         <is>
-          <t>BallotReady</t>
+          <t>ContentActive (ePollBooks.app)</t>
         </is>
       </c>
       <c r="B344" s="19" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="C344" s="20" t="n">
-        <v>2015</v>
+        <v>2006</v>
       </c>
       <c r="D344" s="19" t="inlineStr">
         <is>
@@ -34697,28 +34653,28 @@
       </c>
       <c r="E344" s="19" t="inlineStr">
         <is>
-          <t>Nonpartisan ballot, candidate, and election data (CivicEngine) for orgs, companies, and agencies</t>
+          <t>TX-certified electronic poll book software for county election offices (Harris County)</t>
         </is>
       </c>
       <c r="F344" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://about.ballotready.o</t>
+          <t>Unknown - HTTP 404 for https://contentactive.com/c</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="5" t="inlineStr">
         <is>
-          <t>ContentActive (ePollBooks.app)</t>
+          <t>Vottiv</t>
         </is>
       </c>
       <c r="B345" s="5" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Provo, UT</t>
         </is>
       </c>
       <c r="C345" s="6" t="n">
-        <v>2006</v>
+        <v>2021</v>
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
@@ -34727,28 +34683,28 @@
       </c>
       <c r="E345" s="5" t="inlineStr">
         <is>
-          <t>TX-certified electronic poll book software for county election offices (Harris County)</t>
+          <t>Campaign management SaaS: voter data, canvassing, P2P texting, mail - sold to candidates not agencies - exhibited at NLC City Summit 2026</t>
         </is>
       </c>
       <c r="F345" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://contentactive.com/c</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="19" t="inlineStr">
         <is>
-          <t>Vottiv</t>
+          <t>Dominion Voting Systems</t>
         </is>
       </c>
       <c r="B346" s="19" t="inlineStr">
         <is>
-          <t>Provo, UT</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="C346" s="20" t="n">
-        <v>2021</v>
+        <v>2002</v>
       </c>
       <c r="D346" s="19" t="inlineStr">
         <is>
@@ -34757,28 +34713,28 @@
       </c>
       <c r="E346" s="19" t="inlineStr">
         <is>
-          <t>Campaign management SaaS: voter data, canvassing, P2P texting, mail - sold to candidates not agencies - exhibited at NLC City Summit 2026</t>
+          <t>Voting systems, tabulators and election management software for jurisdictions</t>
         </is>
       </c>
       <c r="F346" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="5" t="inlineStr">
         <is>
-          <t>Dominion Voting Systems</t>
+          <t>Clear Ballot Group</t>
         </is>
       </c>
       <c r="B347" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="C347" s="6" t="n">
-        <v>2002</v>
+        <v>2009</v>
       </c>
       <c r="D347" s="5" t="inlineStr">
         <is>
@@ -34787,28 +34743,28 @@
       </c>
       <c r="E347" s="5" t="inlineStr">
         <is>
-          <t>Voting systems, tabulators and election management software for jurisdictions</t>
-        </is>
-      </c>
-      <c r="F347" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+          <t>Digital ballot scanning, tabulation and audit systems for election offices</t>
+        </is>
+      </c>
+      <c r="F347" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="19" t="inlineStr">
         <is>
-          <t>Clear Ballot Group</t>
+          <t>Unisyn Voting Solutions</t>
         </is>
       </c>
       <c r="B348" s="19" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Vista, CA</t>
         </is>
       </c>
       <c r="C348" s="20" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="D348" s="19" t="inlineStr">
         <is>
@@ -34817,28 +34773,28 @@
       </c>
       <c r="E348" s="19" t="inlineStr">
         <is>
-          <t>Digital ballot scanning, tabulation and audit systems for election offices</t>
-        </is>
-      </c>
-      <c r="F348" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+          <t>OpenElect voting systems and tabulators for counties and states</t>
+        </is>
+      </c>
+      <c r="F348" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="5" t="inlineStr">
         <is>
-          <t>Unisyn Voting Solutions</t>
+          <t>MicroVote General Corporation</t>
         </is>
       </c>
       <c r="B349" s="5" t="inlineStr">
         <is>
-          <t>Vista, CA</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="C349" s="6" t="n">
-        <v>2007</v>
+        <v>1982</v>
       </c>
       <c r="D349" s="5" t="inlineStr">
         <is>
@@ -34847,28 +34803,28 @@
       </c>
       <c r="E349" s="5" t="inlineStr">
         <is>
-          <t>OpenElect voting systems and tabulators for counties and states</t>
+          <t>Electronic voting systems and election services for Midwest counties</t>
         </is>
       </c>
       <c r="F349" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="19" t="inlineStr">
         <is>
-          <t>MicroVote General Corporation</t>
+          <t>VotingWorks</t>
         </is>
       </c>
       <c r="B350" s="19" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="C350" s="20" t="n">
-        <v>1982</v>
+        <v>2018</v>
       </c>
       <c r="D350" s="19" t="inlineStr">
         <is>
@@ -34877,28 +34833,28 @@
       </c>
       <c r="E350" s="19" t="inlineStr">
         <is>
-          <t>Electronic voting systems and election services for Midwest counties</t>
-        </is>
-      </c>
-      <c r="F350" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Open-source voting systems and risk-limiting audit tools for election offices</t>
+        </is>
+      </c>
+      <c r="F350" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive, Field Sales (United States)</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="5" t="inlineStr">
         <is>
-          <t>VotingWorks</t>
+          <t>Smartmatic</t>
         </is>
       </c>
       <c r="B351" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>London, United Kingdom</t>
         </is>
       </c>
       <c r="C351" s="6" t="n">
-        <v>2018</v>
+        <v>2000</v>
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
@@ -34907,28 +34863,28 @@
       </c>
       <c r="E351" s="5" t="inlineStr">
         <is>
-          <t>Open-source voting systems and risk-limiting audit tools for election offices</t>
-        </is>
-      </c>
-      <c r="F351" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive, Field Sales (United States)</t>
+          <t>Voting technology and election management for governments worldwide</t>
+        </is>
+      </c>
+      <c r="F351" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="19" t="inlineStr">
         <is>
-          <t>Smartmatic</t>
+          <t>Scytl Election Technologies</t>
         </is>
       </c>
       <c r="B352" s="19" t="inlineStr">
         <is>
-          <t>London, United Kingdom</t>
+          <t>Barcelona, Spain</t>
         </is>
       </c>
       <c r="C352" s="20" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="D352" s="19" t="inlineStr">
         <is>
@@ -34937,7 +34893,7 @@
       </c>
       <c r="E352" s="19" t="inlineStr">
         <is>
-          <t>Voting technology and election management for governments worldwide</t>
+          <t>Election management, results reporting and online voting for governments</t>
         </is>
       </c>
       <c r="F352" s="21" t="inlineStr">
@@ -34949,16 +34905,16 @@
     <row r="353">
       <c r="A353" s="5" t="inlineStr">
         <is>
-          <t>Scytl Election Technologies</t>
+          <t>Civix</t>
         </is>
       </c>
       <c r="B353" s="5" t="inlineStr">
         <is>
-          <t>Barcelona, Spain</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="C353" s="6" t="n">
-        <v>2001</v>
+        <v>2020</v>
       </c>
       <c r="D353" s="5" t="inlineStr">
         <is>
@@ -34967,7 +34923,7 @@
       </c>
       <c r="E353" s="5" t="inlineStr">
         <is>
-          <t>Election management, results reporting and online voting for governments</t>
+          <t>Election management, results reporting and campaign finance filing for states</t>
         </is>
       </c>
       <c r="F353" s="7" t="inlineStr">
@@ -34979,16 +34935,16 @@
     <row r="354">
       <c r="A354" s="19" t="inlineStr">
         <is>
-          <t>Civix</t>
+          <t>Democracy Live</t>
         </is>
       </c>
       <c r="B354" s="19" t="inlineStr">
         <is>
-          <t>Tallahassee, FL</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="C354" s="20" t="n">
-        <v>2020</v>
+        <v>2007</v>
       </c>
       <c r="D354" s="19" t="inlineStr">
         <is>
@@ -34997,7 +34953,7 @@
       </c>
       <c r="E354" s="19" t="inlineStr">
         <is>
-          <t>Election management, results reporting and campaign finance filing for states</t>
+          <t>OmniBallot electronic ballot delivery and accessible voting for jurisdictions</t>
         </is>
       </c>
       <c r="F354" s="21" t="inlineStr">
@@ -35009,16 +34965,16 @@
     <row r="355">
       <c r="A355" s="5" t="inlineStr">
         <is>
-          <t>Democracy Live</t>
+          <t>Tenex Software Solutions</t>
         </is>
       </c>
       <c r="B355" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="C355" s="6" t="n">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="D355" s="5" t="inlineStr">
         <is>
@@ -35027,28 +34983,28 @@
       </c>
       <c r="E355" s="5" t="inlineStr">
         <is>
-          <t>OmniBallot electronic ballot delivery and accessible voting for jurisdictions</t>
+          <t>Precinct Central e-pollbooks and election management for county offices</t>
         </is>
       </c>
       <c r="F355" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="19" t="inlineStr">
         <is>
-          <t>Tenex Software Solutions</t>
+          <t>VR Systems</t>
         </is>
       </c>
       <c r="B356" s="19" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="C356" s="20" t="n">
-        <v>2011</v>
+        <v>1992</v>
       </c>
       <c r="D356" s="19" t="inlineStr">
         <is>
@@ -35057,7 +35013,7 @@
       </c>
       <c r="E356" s="19" t="inlineStr">
         <is>
-          <t>Precinct Central e-pollbooks and election management for county offices</t>
+          <t>EViD e-pollbooks and voter registration software for state and county offices</t>
         </is>
       </c>
       <c r="F356" s="21" t="inlineStr">
@@ -35069,16 +35025,16 @@
     <row r="357">
       <c r="A357" s="5" t="inlineStr">
         <is>
-          <t>VR Systems</t>
+          <t>DFM Associates</t>
         </is>
       </c>
       <c r="B357" s="5" t="inlineStr">
         <is>
-          <t>Tallahassee, FL</t>
+          <t>Costa Mesa, CA</t>
         </is>
       </c>
       <c r="C357" s="6" t="n">
-        <v>1992</v>
+        <v>1979</v>
       </c>
       <c r="D357" s="5" t="inlineStr">
         <is>
@@ -35087,28 +35043,28 @@
       </c>
       <c r="E357" s="5" t="inlineStr">
         <is>
-          <t>EViD e-pollbooks and voter registration software for state and county offices</t>
+          <t>EIMS election information management system for county election offices</t>
         </is>
       </c>
       <c r="F357" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="19" t="inlineStr">
         <is>
-          <t>DFM Associates</t>
+          <t>PCC Technology Group</t>
         </is>
       </c>
       <c r="B358" s="19" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA</t>
+          <t>Bloomfield, CT</t>
         </is>
       </c>
       <c r="C358" s="20" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="D358" s="19" t="inlineStr">
         <is>
@@ -35117,7 +35073,7 @@
       </c>
       <c r="E358" s="19" t="inlineStr">
         <is>
-          <t>EIMS election information management system for county election offices</t>
+          <t>Statewide voter registration and business registry systems for states</t>
         </is>
       </c>
       <c r="F358" s="21" t="inlineStr">
@@ -35129,16 +35085,16 @@
     <row r="359">
       <c r="A359" s="5" t="inlineStr">
         <is>
-          <t>PCC Technology Group</t>
+          <t>Konnech</t>
         </is>
       </c>
       <c r="B359" s="5" t="inlineStr">
         <is>
-          <t>Bloomfield, CT</t>
+          <t>East Lansing, MI</t>
         </is>
       </c>
       <c r="C359" s="6" t="n">
-        <v>1980</v>
+        <v>2002</v>
       </c>
       <c r="D359" s="5" t="inlineStr">
         <is>
@@ -35147,7 +35103,7 @@
       </c>
       <c r="E359" s="5" t="inlineStr">
         <is>
-          <t>Statewide voter registration and business registry systems for states</t>
+          <t>PollChief poll worker recruitment, training and logistics for election offices</t>
         </is>
       </c>
       <c r="F359" s="7" t="inlineStr">
@@ -35159,16 +35115,16 @@
     <row r="360">
       <c r="A360" s="19" t="inlineStr">
         <is>
-          <t>Konnech</t>
+          <t>EasyVote Solutions</t>
         </is>
       </c>
       <c r="B360" s="19" t="inlineStr">
         <is>
-          <t>East Lansing, MI</t>
+          <t>Cumming, GA</t>
         </is>
       </c>
       <c r="C360" s="20" t="n">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="D360" s="19" t="inlineStr">
         <is>
@@ -35177,28 +35133,28 @@
       </c>
       <c r="E360" s="19" t="inlineStr">
         <is>
-          <t>PollChief poll worker recruitment, training and logistics for election offices</t>
+          <t>Election management SaaS for county election offices, poll workers and supplies</t>
         </is>
       </c>
       <c r="F360" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 404 for https://www.easyvotesolutio</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="5" t="inlineStr">
         <is>
-          <t>EasyVote Solutions</t>
+          <t>Enhanced Voting</t>
         </is>
       </c>
       <c r="B361" s="5" t="inlineStr">
         <is>
-          <t>Cumming, GA</t>
+          <t>Rochester, NY</t>
         </is>
       </c>
       <c r="C361" s="6" t="n">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="D361" s="5" t="inlineStr">
         <is>
@@ -35207,28 +35163,28 @@
       </c>
       <c r="E361" s="5" t="inlineStr">
         <is>
-          <t>Election management SaaS for county election offices, poll workers and supplies</t>
-        </is>
-      </c>
-      <c r="F361" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - HTTP 404 for https://www.easyvotesolutio</t>
+          <t>Ballot tracking, electronic ballot delivery and election tools for jurisdictions</t>
+        </is>
+      </c>
+      <c r="F361" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="19" t="inlineStr">
         <is>
-          <t>Enhanced Voting</t>
+          <t>Voatz</t>
         </is>
       </c>
       <c r="B362" s="19" t="inlineStr">
         <is>
-          <t>Rochester, NY</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="C362" s="20" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="D362" s="19" t="inlineStr">
         <is>
@@ -35237,28 +35193,28 @@
       </c>
       <c r="E362" s="19" t="inlineStr">
         <is>
-          <t>Ballot tracking, electronic ballot delivery and election tools for jurisdictions</t>
-        </is>
-      </c>
-      <c r="F362" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+          <t>Mobile voting and ballot marking for jurisdictions and overseas voters</t>
+        </is>
+      </c>
+      <c r="F362" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="5" t="inlineStr">
         <is>
-          <t>Voatz</t>
+          <t>Simply Voting</t>
         </is>
       </c>
       <c r="B363" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Montreal, QC, Canada</t>
         </is>
       </c>
       <c r="C363" s="6" t="n">
-        <v>2014</v>
+        <v>2003</v>
       </c>
       <c r="D363" s="5" t="inlineStr">
         <is>
@@ -35267,29 +35223,27 @@
       </c>
       <c r="E363" s="5" t="inlineStr">
         <is>
-          <t>Mobile voting and ballot marking for jurisdictions and overseas voters</t>
+          <t>Hosted online voting for governments, districts and public bodies</t>
         </is>
       </c>
       <c r="F363" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="19" t="inlineStr">
         <is>
-          <t>Simply Voting</t>
+          <t>BallotTrax</t>
         </is>
       </c>
       <c r="B364" s="19" t="inlineStr">
         <is>
-          <t>Montreal, QC, Canada</t>
-        </is>
-      </c>
-      <c r="C364" s="20" t="n">
-        <v>2003</v>
-      </c>
+          <t>Centennial, CO</t>
+        </is>
+      </c>
+      <c r="C364" s="20" t="n"/>
       <c r="D364" s="19" t="inlineStr">
         <is>
           <t>Elections</t>
@@ -35297,27 +35251,29 @@
       </c>
       <c r="E364" s="19" t="inlineStr">
         <is>
-          <t>Hosted online voting for governments, districts and public bodies</t>
+          <t>Mail ballot tracking and voter notification for county election offices</t>
         </is>
       </c>
       <c r="F364" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="5" t="inlineStr">
         <is>
-          <t>BallotTrax</t>
+          <t>Democracy Works</t>
         </is>
       </c>
       <c r="B365" s="5" t="inlineStr">
         <is>
-          <t>Centennial, CO</t>
-        </is>
-      </c>
-      <c r="C365" s="6" t="n"/>
+          <t>Brooklyn, NY</t>
+        </is>
+      </c>
+      <c r="C365" s="6" t="n">
+        <v>2010</v>
+      </c>
       <c r="D365" s="5" t="inlineStr">
         <is>
           <t>Elections</t>
@@ -35325,28 +35281,28 @@
       </c>
       <c r="E365" s="5" t="inlineStr">
         <is>
-          <t>Mail ballot tracking and voter notification for county election offices</t>
+          <t>Ballot Scout mail-ballot tracking and voter data tools for election officials</t>
         </is>
       </c>
       <c r="F365" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="19" t="inlineStr">
         <is>
-          <t>Democracy Works</t>
+          <t>Caliper Corporation</t>
         </is>
       </c>
       <c r="B366" s="19" t="inlineStr">
         <is>
-          <t>Brooklyn, NY</t>
+          <t>Newton, MA</t>
         </is>
       </c>
       <c r="C366" s="20" t="n">
-        <v>2010</v>
+        <v>1983</v>
       </c>
       <c r="D366" s="19" t="inlineStr">
         <is>
@@ -35355,24 +35311,24 @@
       </c>
       <c r="E366" s="19" t="inlineStr">
         <is>
-          <t>Ballot Scout mail-ballot tracking and voter data tools for election officials</t>
+          <t>Maptitude for Redistricting used by states, counties and municipalities</t>
         </is>
       </c>
       <c r="F366" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="5" t="inlineStr">
         <is>
-          <t>Caliper Corporation</t>
+          <t>Aristotle International</t>
         </is>
       </c>
       <c r="B367" s="5" t="inlineStr">
         <is>
-          <t>Newton, MA</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="C367" s="6" t="n">
@@ -35385,28 +35341,28 @@
       </c>
       <c r="E367" s="5" t="inlineStr">
         <is>
-          <t>Maptitude for Redistricting used by states, counties and municipalities</t>
+          <t>Campaign finance disclosure and compliance systems for election agencies</t>
         </is>
       </c>
       <c r="F367" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="19" t="inlineStr">
         <is>
-          <t>Aristotle International</t>
+          <t>NetFile</t>
         </is>
       </c>
       <c r="B368" s="19" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Petaluma, CA</t>
         </is>
       </c>
       <c r="C368" s="20" t="n">
-        <v>1983</v>
+        <v>1998</v>
       </c>
       <c r="D368" s="19" t="inlineStr">
         <is>
@@ -35415,29 +35371,27 @@
       </c>
       <c r="E368" s="19" t="inlineStr">
         <is>
-          <t>Campaign finance disclosure and compliance systems for election agencies</t>
+          <t>Campaign finance and disclosure e-filing for state and local jurisdictions</t>
         </is>
       </c>
       <c r="F368" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="5" t="inlineStr">
         <is>
-          <t>NetFile</t>
+          <t>Phoenix Graphics</t>
         </is>
       </c>
       <c r="B369" s="5" t="inlineStr">
         <is>
-          <t>Petaluma, CA</t>
-        </is>
-      </c>
-      <c r="C369" s="6" t="n">
-        <v>1998</v>
-      </c>
+          <t>Rochester, NY</t>
+        </is>
+      </c>
+      <c r="C369" s="6" t="n"/>
       <c r="D369" s="5" t="inlineStr">
         <is>
           <t>Elections</t>
@@ -35445,7 +35399,7 @@
       </c>
       <c r="E369" s="5" t="inlineStr">
         <is>
-          <t>Campaign finance and disclosure e-filing for state and local jurisdictions</t>
+          <t>Ballot printing, mail ballot production and election print for jurisdictions</t>
         </is>
       </c>
       <c r="F369" s="7" t="inlineStr">
@@ -35457,12 +35411,12 @@
     <row r="370">
       <c r="A370" s="19" t="inlineStr">
         <is>
-          <t>Phoenix Graphics</t>
+          <t>SeaChange Print Innovations</t>
         </is>
       </c>
       <c r="B370" s="19" t="inlineStr">
         <is>
-          <t>Rochester, NY</t>
+          <t>Plymouth, MN</t>
         </is>
       </c>
       <c r="C370" s="20" t="n"/>
@@ -35473,7 +35427,7 @@
       </c>
       <c r="E370" s="19" t="inlineStr">
         <is>
-          <t>Ballot printing, mail ballot production and election print for jurisdictions</t>
+          <t>Vote-by-mail ballot printing, kitting and mailing for election offices</t>
         </is>
       </c>
       <c r="F370" s="21" t="inlineStr">
@@ -35485,15 +35439,17 @@
     <row r="371">
       <c r="A371" s="5" t="inlineStr">
         <is>
-          <t>SeaChange Print Innovations</t>
+          <t>Fort Orange Press</t>
         </is>
       </c>
       <c r="B371" s="5" t="inlineStr">
         <is>
-          <t>Plymouth, MN</t>
-        </is>
-      </c>
-      <c r="C371" s="6" t="n"/>
+          <t>Albany, NY</t>
+        </is>
+      </c>
+      <c r="C371" s="6" t="n">
+        <v>1902</v>
+      </c>
       <c r="D371" s="5" t="inlineStr">
         <is>
           <t>Elections</t>
@@ -35501,28 +35457,28 @@
       </c>
       <c r="E371" s="5" t="inlineStr">
         <is>
-          <t>Vote-by-mail ballot printing, kitting and mailing for election offices</t>
-        </is>
-      </c>
-      <c r="F371" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Ballot printing and election materials for county boards of elections - exhibited at Maryland Municipal League 2026</t>
+        </is>
+      </c>
+      <c r="F371" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="19" t="inlineStr">
         <is>
-          <t>Fort Orange Press</t>
+          <t>Bell and Howell</t>
         </is>
       </c>
       <c r="B372" s="19" t="inlineStr">
         <is>
-          <t>Albany, NY</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="C372" s="20" t="n">
-        <v>1902</v>
+        <v>1907</v>
       </c>
       <c r="D372" s="19" t="inlineStr">
         <is>
@@ -35531,28 +35487,28 @@
       </c>
       <c r="E372" s="19" t="inlineStr">
         <is>
-          <t>Ballot printing and election materials for county boards of elections - exhibited at Maryland Municipal League 2026</t>
-        </is>
-      </c>
-      <c r="F372" s="22" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Mail ballot sorting and inserting hardware/services for election offices</t>
+        </is>
+      </c>
+      <c r="F372" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="5" t="inlineStr">
         <is>
-          <t>Bell and Howell</t>
+          <t>Robis Elections</t>
         </is>
       </c>
       <c r="B373" s="5" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>Boise, ID</t>
         </is>
       </c>
       <c r="C373" s="6" t="n">
-        <v>1907</v>
+        <v>1991</v>
       </c>
       <c r="D373" s="5" t="inlineStr">
         <is>
@@ -35561,7 +35517,7 @@
       </c>
       <c r="E373" s="5" t="inlineStr">
         <is>
-          <t>Mail ballot sorting and inserting hardware/services for election offices</t>
+          <t>Election management and voter registration software for county clerks</t>
         </is>
       </c>
       <c r="F373" s="7" t="inlineStr">
@@ -35573,17 +35529,15 @@
     <row r="374">
       <c r="A374" s="19" t="inlineStr">
         <is>
-          <t>Robis Elections</t>
+          <t>Platinum Technology Resource</t>
         </is>
       </c>
       <c r="B374" s="19" t="inlineStr">
         <is>
-          <t>Boise, ID</t>
-        </is>
-      </c>
-      <c r="C374" s="20" t="n">
-        <v>1991</v>
-      </c>
+          <t>Springfield, IL</t>
+        </is>
+      </c>
+      <c r="C374" s="20" t="n"/>
       <c r="D374" s="19" t="inlineStr">
         <is>
           <t>Elections</t>
@@ -35591,27 +35545,29 @@
       </c>
       <c r="E374" s="19" t="inlineStr">
         <is>
-          <t>Election management and voter registration software for county clerks</t>
+          <t>Election management and results reporting for Illinois-area election authorities</t>
         </is>
       </c>
       <c r="F374" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="5" t="inlineStr">
         <is>
-          <t>Platinum Technology Resource</t>
+          <t>OSET Institute</t>
         </is>
       </c>
       <c r="B375" s="5" t="inlineStr">
         <is>
-          <t>Springfield, IL</t>
-        </is>
-      </c>
-      <c r="C375" s="6" t="n"/>
+          <t>Palo Alto, CA</t>
+        </is>
+      </c>
+      <c r="C375" s="6" t="n">
+        <v>2006</v>
+      </c>
       <c r="D375" s="5" t="inlineStr">
         <is>
           <t>Elections</t>
@@ -35619,29 +35575,27 @@
       </c>
       <c r="E375" s="5" t="inlineStr">
         <is>
-          <t>Election management and results reporting for Illinois-area election authorities</t>
+          <t>Open-source election infrastructure and voting software for public agencies</t>
         </is>
       </c>
       <c r="F375" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="19" t="inlineStr">
         <is>
-          <t>OSET Institute</t>
+          <t>Inclusion Solutions</t>
         </is>
       </c>
       <c r="B376" s="19" t="inlineStr">
         <is>
-          <t>Palo Alto, CA</t>
-        </is>
-      </c>
-      <c r="C376" s="20" t="n">
-        <v>2006</v>
-      </c>
+          <t>Evanston, IL</t>
+        </is>
+      </c>
+      <c r="C376" s="20" t="n"/>
       <c r="D376" s="19" t="inlineStr">
         <is>
           <t>Elections</t>
@@ -35649,27 +35603,29 @@
       </c>
       <c r="E376" s="19" t="inlineStr">
         <is>
-          <t>Open-source election infrastructure and voting software for public agencies</t>
+          <t>Polling place accessibility products and curbside voting kits for jurisdictions</t>
         </is>
       </c>
       <c r="F376" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="5" t="inlineStr">
         <is>
-          <t>Inclusion Solutions</t>
+          <t>TrueBallot</t>
         </is>
       </c>
       <c r="B377" s="5" t="inlineStr">
         <is>
-          <t>Evanston, IL</t>
-        </is>
-      </c>
-      <c r="C377" s="6" t="n"/>
+          <t>Bethesda, MD</t>
+        </is>
+      </c>
+      <c r="C377" s="6" t="n">
+        <v>1993</v>
+      </c>
       <c r="D377" s="5" t="inlineStr">
         <is>
           <t>Elections</t>
@@ -35677,7 +35633,7 @@
       </c>
       <c r="E377" s="5" t="inlineStr">
         <is>
-          <t>Polling place accessibility products and curbside voting kits for jurisdictions</t>
+          <t>Election administration and ballot services for public bodies and jurisdictions</t>
         </is>
       </c>
       <c r="F377" s="7" t="inlineStr">
@@ -35689,44 +35645,38 @@
     <row r="378">
       <c r="A378" s="19" t="inlineStr">
         <is>
-          <t>TrueBallot</t>
+          <t>Brainfuse</t>
         </is>
       </c>
       <c r="B378" s="19" t="inlineStr">
         <is>
-          <t>Bethesda, MD</t>
-        </is>
-      </c>
-      <c r="C378" s="20" t="n">
-        <v>1993</v>
-      </c>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="C378" s="20" t="n"/>
       <c r="D378" s="19" t="inlineStr">
         <is>
-          <t>Elections</t>
+          <t>Libraries</t>
         </is>
       </c>
       <c r="E378" s="19" t="inlineStr">
         <is>
-          <t>Election administration and ballot services for public bodies and jurisdictions</t>
+          <t>Live online tutoring, writing feedback, and test prep delivered through public libraries, school districts, and colleges - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F378" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="5" t="inlineStr">
         <is>
-          <t>Brainfuse</t>
-        </is>
-      </c>
-      <c r="B379" s="5" t="inlineStr">
-        <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
+          <t>Gale</t>
+        </is>
+      </c>
+      <c r="B379" s="5" t="n"/>
       <c r="C379" s="6" t="n"/>
       <c r="D379" s="5" t="inlineStr">
         <is>
@@ -35735,23 +35685,29 @@
       </c>
       <c r="E379" s="5" t="inlineStr">
         <is>
-          <t>Live online tutoring, writing feedback, and test prep delivered through public libraries, school districts, and colleges - exhibited at PLA 2026</t>
+          <t>Research databases, primary source archives, and ebook collections licensed to public libraries, K-12 schools, and academic institutions - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F379" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="19" t="inlineStr">
         <is>
-          <t>Gale</t>
-        </is>
-      </c>
-      <c r="B380" s="19" t="n"/>
-      <c r="C380" s="20" t="n"/>
+          <t>Library Ideas, LLC</t>
+        </is>
+      </c>
+      <c r="B380" s="19" t="inlineStr">
+        <is>
+          <t>Vienna, VA</t>
+        </is>
+      </c>
+      <c r="C380" s="20" t="n">
+        <v>2008</v>
+      </c>
       <c r="D380" s="19" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -35759,7 +35715,7 @@
       </c>
       <c r="E380" s="19" t="inlineStr">
         <is>
-          <t>Research databases, primary source archives, and ebook collections licensed to public libraries, K-12 schools, and academic institutions - exhibited at PLA 2026</t>
+          <t>Freegal music streaming, VOX audio-enabled books, ebooks, and language learning products for public libraries and schools - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F380" s="21" t="inlineStr">
@@ -35771,17 +35727,15 @@
     <row r="381">
       <c r="A381" s="5" t="inlineStr">
         <is>
-          <t>Library Ideas, LLC</t>
+          <t>medici.tv</t>
         </is>
       </c>
       <c r="B381" s="5" t="inlineStr">
         <is>
-          <t>Vienna, VA</t>
-        </is>
-      </c>
-      <c r="C381" s="6" t="n">
-        <v>2008</v>
-      </c>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="C381" s="6" t="n"/>
       <c r="D381" s="5" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -35789,7 +35743,7 @@
       </c>
       <c r="E381" s="5" t="inlineStr">
         <is>
-          <t>Freegal music streaming, VOX audio-enabled books, ebooks, and language learning products for public libraries and schools - exhibited at PLA 2026</t>
+          <t>Classical music and opera video streaming licensed to public libraries, schools, and universities for patron access - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F381" s="7" t="inlineStr">
@@ -35801,15 +35755,17 @@
     <row r="382">
       <c r="A382" s="19" t="inlineStr">
         <is>
-          <t>medici.tv</t>
+          <t>OCLC</t>
         </is>
       </c>
       <c r="B382" s="19" t="inlineStr">
         <is>
-          <t>Paris, France</t>
-        </is>
-      </c>
-      <c r="C382" s="20" t="n"/>
+          <t>Dublin, OH</t>
+        </is>
+      </c>
+      <c r="C382" s="20" t="n">
+        <v>1967</v>
+      </c>
       <c r="D382" s="19" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -35817,28 +35773,24 @@
       </c>
       <c r="E382" s="19" t="inlineStr">
         <is>
-          <t>Classical music and opera video streaming licensed to public libraries, schools, and universities for patron access - exhibited at PLA 2026</t>
+          <t>WorldCat shared cataloging, discovery, resource sharing, and library management systems for public, academic, school, and research libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F382" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="5" t="inlineStr">
         <is>
-          <t>OCLC</t>
-        </is>
-      </c>
-      <c r="B383" s="5" t="inlineStr">
-        <is>
-          <t>Dublin, OH</t>
-        </is>
-      </c>
+          <t>Recollect</t>
+        </is>
+      </c>
+      <c r="B383" s="5" t="n"/>
       <c r="C383" s="6" t="n">
-        <v>1967</v>
+        <v>2012</v>
       </c>
       <c r="D383" s="5" t="inlineStr">
         <is>
@@ -35847,25 +35799,23 @@
       </c>
       <c r="E383" s="5" t="inlineStr">
         <is>
-          <t>WorldCat shared cataloging, discovery, resource sharing, and library management systems for public, academic, school, and research libraries - exhibited at PLA 2026</t>
+          <t>Cloud digital collections management and public discovery platform for archives, public libraries, museums, and heritage sites - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F383" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="19" t="inlineStr">
         <is>
-          <t>Recollect</t>
+          <t>TIND</t>
         </is>
       </c>
       <c r="B384" s="19" t="n"/>
-      <c r="C384" s="20" t="n">
-        <v>2012</v>
-      </c>
+      <c r="C384" s="20" t="n"/>
       <c r="D384" s="19" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -35873,7 +35823,7 @@
       </c>
       <c r="E384" s="19" t="inlineStr">
         <is>
-          <t>Cloud digital collections management and public discovery platform for archives, public libraries, museums, and heritage sites - exhibited at PLA 2026</t>
+          <t>Library management, digital archive, institutional repository, and research data management systems for academic and research libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F384" s="21" t="inlineStr">
@@ -35885,11 +35835,17 @@
     <row r="385">
       <c r="A385" s="5" t="inlineStr">
         <is>
-          <t>TIND</t>
-        </is>
-      </c>
-      <c r="B385" s="5" t="n"/>
-      <c r="C385" s="6" t="n"/>
+          <t>ASLdeafined</t>
+        </is>
+      </c>
+      <c r="B385" s="5" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI</t>
+        </is>
+      </c>
+      <c r="C385" s="6" t="n">
+        <v>2008</v>
+      </c>
       <c r="D385" s="5" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -35897,7 +35853,7 @@
       </c>
       <c r="E385" s="5" t="inlineStr">
         <is>
-          <t>Library management, digital archive, institutional repository, and research data management systems for academic and research libraries - exhibited at PLA 2026</t>
+          <t>Subscription American Sign Language video lesson library and dictionary for public libraries, schools, colleges, and public safety agencies - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F385" s="7" t="inlineStr">
@@ -35909,14 +35865,10 @@
     <row r="386">
       <c r="A386" s="19" t="inlineStr">
         <is>
-          <t>ASLdeafined</t>
-        </is>
-      </c>
-      <c r="B386" s="19" t="inlineStr">
-        <is>
-          <t>Auburn Hills, MI</t>
-        </is>
-      </c>
+          <t>Gimlet</t>
+        </is>
+      </c>
+      <c r="B386" s="19" t="n"/>
       <c r="C386" s="20" t="n">
         <v>2008</v>
       </c>
@@ -35927,7 +35879,7 @@
       </c>
       <c r="E386" s="19" t="inlineStr">
         <is>
-          <t>Subscription American Sign Language video lesson library and dictionary for public libraries, schools, colleges, and public safety agencies - exhibited at PLA 2026</t>
+          <t>Hosted reference desk statistics tracking and reporting software for public and academic libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F386" s="21" t="inlineStr">
@@ -35939,13 +35891,15 @@
     <row r="387">
       <c r="A387" s="5" t="inlineStr">
         <is>
-          <t>Gimlet</t>
-        </is>
-      </c>
-      <c r="B387" s="5" t="n"/>
-      <c r="C387" s="6" t="n">
-        <v>2008</v>
-      </c>
+          <t>Library Market</t>
+        </is>
+      </c>
+      <c r="B387" s="5" t="inlineStr">
+        <is>
+          <t>Jonesboro, AR</t>
+        </is>
+      </c>
+      <c r="C387" s="6" t="n"/>
       <c r="D387" s="5" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -35953,7 +35907,7 @@
       </c>
       <c r="E387" s="5" t="inlineStr">
         <is>
-          <t>Hosted reference desk statistics tracking and reporting software for public and academic libraries - exhibited at PLA 2026</t>
+          <t>Library website design, event and room booking calendars, and branding services for public libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F387" s="7" t="inlineStr">
@@ -35965,12 +35919,12 @@
     <row r="388">
       <c r="A388" s="19" t="inlineStr">
         <is>
-          <t>Library Market</t>
+          <t>Meescan Inc.</t>
         </is>
       </c>
       <c r="B388" s="19" t="inlineStr">
         <is>
-          <t>Jonesboro, AR</t>
+          <t>Abbotsford, BC, Canada</t>
         </is>
       </c>
       <c r="C388" s="20" t="n"/>
@@ -35981,27 +35935,29 @@
       </c>
       <c r="E388" s="19" t="inlineStr">
         <is>
-          <t>Library website design, event and room booking calendars, and branding services for public libraries - exhibited at PLA 2026</t>
+          <t>Self-checkout software, kiosks, and RFID equipment for public, academic, and school libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F388" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="5" t="inlineStr">
         <is>
-          <t>Meescan Inc.</t>
+          <t>OverDrive</t>
         </is>
       </c>
       <c r="B389" s="5" t="inlineStr">
         <is>
-          <t>Abbotsford, BC, Canada</t>
-        </is>
-      </c>
-      <c r="C389" s="6" t="n"/>
+          <t>Cleveland, OH</t>
+        </is>
+      </c>
+      <c r="C389" s="6" t="n">
+        <v>1986</v>
+      </c>
       <c r="D389" s="5" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -36009,7 +35965,7 @@
       </c>
       <c r="E389" s="5" t="inlineStr">
         <is>
-          <t>Self-checkout software, kiosks, and RFID equipment for public, academic, and school libraries - exhibited at PLA 2026</t>
+          <t>Digital ebook, audiobook, and video lending platform for public libraries, K-12 schools, and academic institutions - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F389" s="7" t="inlineStr">
@@ -36021,16 +35977,16 @@
     <row r="390">
       <c r="A390" s="19" t="inlineStr">
         <is>
-          <t>OverDrive</t>
+          <t>The Library Corporation</t>
         </is>
       </c>
       <c r="B390" s="19" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>Inwood, WV</t>
         </is>
       </c>
       <c r="C390" s="20" t="n">
-        <v>1986</v>
+        <v>1974</v>
       </c>
       <c r="D390" s="19" t="inlineStr">
         <is>
@@ -36039,7 +35995,7 @@
       </c>
       <c r="E390" s="19" t="inlineStr">
         <is>
-          <t>Digital ebook, audiobook, and video lending platform for public libraries, K-12 schools, and academic institutions - exhibited at PLA 2026</t>
+          <t>Integrated library system, cataloging, and patron discovery software for public, school, and academic libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F390" s="21" t="inlineStr">
@@ -36051,17 +36007,15 @@
     <row r="391">
       <c r="A391" s="5" t="inlineStr">
         <is>
-          <t>The Library Corporation</t>
+          <t>Assabet Interactive</t>
         </is>
       </c>
       <c r="B391" s="5" t="inlineStr">
         <is>
-          <t>Inwood, WV</t>
-        </is>
-      </c>
-      <c r="C391" s="6" t="n">
-        <v>1974</v>
-      </c>
+          <t>Concord, MA</t>
+        </is>
+      </c>
+      <c r="C391" s="6" t="n"/>
       <c r="D391" s="5" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -36069,24 +36023,24 @@
       </c>
       <c r="E391" s="5" t="inlineStr">
         <is>
-          <t>Integrated library system, cataloging, and patron discovery software for public, school, and academic libraries - exhibited at PLA 2026</t>
+          <t>Event calendar, room booking, museum pass, and Library of Things modules for public library websites - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F391" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="19" t="inlineStr">
         <is>
-          <t>Assabet Interactive</t>
+          <t>collectionHQ</t>
         </is>
       </c>
       <c r="B392" s="19" t="inlineStr">
         <is>
-          <t>Concord, MA</t>
+          <t>Edinburgh, United Kingdom</t>
         </is>
       </c>
       <c r="C392" s="20" t="n"/>
@@ -36097,7 +36051,7 @@
       </c>
       <c r="E392" s="19" t="inlineStr">
         <is>
-          <t>Event calendar, room booking, museum pass, and Library of Things modules for public library websites - exhibited at PLA 2026</t>
+          <t>Evidence-based collection analytics and management software for public and academic libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F392" s="21" t="inlineStr">
@@ -36109,14 +36063,10 @@
     <row r="393">
       <c r="A393" s="5" t="inlineStr">
         <is>
-          <t>collectionHQ</t>
-        </is>
-      </c>
-      <c r="B393" s="5" t="inlineStr">
-        <is>
-          <t>Edinburgh, United Kingdom</t>
-        </is>
-      </c>
+          <t>Decodable Reads</t>
+        </is>
+      </c>
+      <c r="B393" s="5" t="n"/>
       <c r="C393" s="6" t="n"/>
       <c r="D393" s="5" t="inlineStr">
         <is>
@@ -36125,7 +36075,7 @@
       </c>
       <c r="E393" s="5" t="inlineStr">
         <is>
-          <t>Evidence-based collection analytics and management software for public and academic libraries - exhibited at PLA 2026</t>
+          <t>Phonics and decodable-text literacy platform for library reading programs, K-4 classrooms, and families - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F393" s="7" t="inlineStr">
@@ -36137,7 +36087,7 @@
     <row r="394">
       <c r="A394" s="19" t="inlineStr">
         <is>
-          <t>Decodable Reads</t>
+          <t>hoopla digital</t>
         </is>
       </c>
       <c r="B394" s="19" t="n"/>
@@ -36149,7 +36099,7 @@
       </c>
       <c r="E394" s="19" t="inlineStr">
         <is>
-          <t>Phonics and decodable-text literacy platform for library reading programs, K-4 classrooms, and families - exhibited at PLA 2026</t>
+          <t>Digital lending platform giving public library patrons instant access to ebooks, audiobooks, comics, music, and video - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F394" s="21" t="inlineStr">
@@ -36161,10 +36111,14 @@
     <row r="395">
       <c r="A395" s="5" t="inlineStr">
         <is>
-          <t>hoopla digital</t>
-        </is>
-      </c>
-      <c r="B395" s="5" t="n"/>
+          <t>Lightbox Learning</t>
+        </is>
+      </c>
+      <c r="B395" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
       <c r="C395" s="6" t="n"/>
       <c r="D395" s="5" t="inlineStr">
         <is>
@@ -36173,7 +36127,7 @@
       </c>
       <c r="E395" s="5" t="inlineStr">
         <is>
-          <t>Digital lending platform giving public library patrons instant access to ebooks, audiobooks, comics, music, and video - exhibited at PLA 2026</t>
+          <t>Interactive multimedia ebook collections for K-12 classrooms and public libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F395" s="7" t="inlineStr">
@@ -36185,7 +36139,7 @@
     <row r="396">
       <c r="A396" s="19" t="inlineStr">
         <is>
-          <t>Lightbox Learning</t>
+          <t>Playgarden Prep Online</t>
         </is>
       </c>
       <c r="B396" s="19" t="inlineStr">
@@ -36201,7 +36155,7 @@
       </c>
       <c r="E396" s="19" t="inlineStr">
         <is>
-          <t>Interactive multimedia ebook collections for K-12 classrooms and public libraries - exhibited at PLA 2026</t>
+          <t>Online preschool curriculum with video lessons and live classes, licensed to public libraries and hospitals and sold to families - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F396" s="21" t="inlineStr">
@@ -36213,7 +36167,7 @@
     <row r="397">
       <c r="A397" s="5" t="inlineStr">
         <is>
-          <t>Playgarden Prep Online</t>
+          <t>SimplyAnalytics</t>
         </is>
       </c>
       <c r="B397" s="5" t="inlineStr">
@@ -36229,27 +36183,25 @@
       </c>
       <c r="E397" s="5" t="inlineStr">
         <is>
-          <t>Online preschool curriculum with video lessons and live classes, licensed to public libraries and hospitals and sold to families - exhibited at PLA 2026</t>
-        </is>
-      </c>
-      <c r="F397" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Web-based mapping, demographic, and consumer data visualization application for university and public library patrons - exhibited at PLA 2026</t>
+        </is>
+      </c>
+      <c r="F397" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Senior Account Executive - B2B Saa</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="19" t="inlineStr">
         <is>
-          <t>SimplyAnalytics</t>
-        </is>
-      </c>
-      <c r="B398" s="19" t="inlineStr">
-        <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
-      <c r="C398" s="20" t="n"/>
+          <t>AtoZdatabases</t>
+        </is>
+      </c>
+      <c r="B398" s="19" t="n"/>
+      <c r="C398" s="20" t="n">
+        <v>2010</v>
+      </c>
       <c r="D398" s="19" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -36257,25 +36209,23 @@
       </c>
       <c r="E398" s="19" t="inlineStr">
         <is>
-          <t>Web-based mapping, demographic, and consumer data visualization application for university and public library patrons - exhibited at PLA 2026</t>
-        </is>
-      </c>
-      <c r="F398" s="22" t="inlineStr">
-        <is>
-          <t>Yes - Senior Account Executive - B2B Saa</t>
+          <t>Business and consumer reference and marketing database licensed to public libraries, academic institutions, and government agencies for patron job search and small business research - exhibited at PLA 2026</t>
+        </is>
+      </c>
+      <c r="F398" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="5" t="inlineStr">
         <is>
-          <t>AtoZdatabases</t>
+          <t>Communico</t>
         </is>
       </c>
       <c r="B399" s="5" t="n"/>
-      <c r="C399" s="6" t="n">
-        <v>2010</v>
-      </c>
+      <c r="C399" s="6" t="n"/>
       <c r="D399" s="5" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -36283,7 +36233,7 @@
       </c>
       <c r="E399" s="5" t="inlineStr">
         <is>
-          <t>Business and consumer reference and marketing database licensed to public libraries, academic institutions, and government agencies for patron job search and small business research - exhibited at PLA 2026</t>
+          <t>Cloud suite for libraries covering website CMS, event and room booking, appointments, digital signage, mobile apps, kiosks, and discovery search - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F399" s="7" t="inlineStr">
@@ -36295,7 +36245,7 @@
     <row r="400">
       <c r="A400" s="19" t="inlineStr">
         <is>
-          <t>Communico</t>
+          <t>Digitalia</t>
         </is>
       </c>
       <c r="B400" s="19" t="n"/>
@@ -36307,7 +36257,7 @@
       </c>
       <c r="E400" s="19" t="inlineStr">
         <is>
-          <t>Cloud suite for libraries covering website CMS, event and room booking, appointments, digital signage, mobile apps, kiosks, and discovery search - exhibited at PLA 2026</t>
+          <t>Spanish and Portuguese language ebook, ejournal, and ecollection subscriptions licensed to libraries and academic institutions - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F400" s="21" t="inlineStr">
@@ -36319,7 +36269,7 @@
     <row r="401">
       <c r="A401" s="5" t="inlineStr">
         <is>
-          <t>Digitalia</t>
+          <t>Infobase</t>
         </is>
       </c>
       <c r="B401" s="5" t="n"/>
@@ -36331,23 +36281,29 @@
       </c>
       <c r="E401" s="5" t="inlineStr">
         <is>
-          <t>Spanish and Portuguese language ebook, ejournal, and ecollection subscriptions licensed to libraries and academic institutions - exhibited at PLA 2026</t>
+          <t>Reference databases, streaming video, and career research content licensed to K-12 schools, colleges, public libraries, and employers - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F401" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="19" t="inlineStr">
         <is>
-          <t>Infobase</t>
-        </is>
-      </c>
-      <c r="B402" s="19" t="n"/>
-      <c r="C402" s="20" t="n"/>
+          <t>LLMC</t>
+        </is>
+      </c>
+      <c r="B402" s="19" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN</t>
+        </is>
+      </c>
+      <c r="C402" s="20" t="n">
+        <v>1976</v>
+      </c>
       <c r="D402" s="19" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -36355,28 +36311,24 @@
       </c>
       <c r="E402" s="19" t="inlineStr">
         <is>
-          <t>Reference databases, streaming video, and career research content licensed to K-12 schools, colleges, public libraries, and employers - exhibited at PLA 2026</t>
+          <t>Digitized archive of legal, legislative, and government documents licensed by subscription to law, academic, and public libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F402" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="5" t="inlineStr">
         <is>
-          <t>LLMC</t>
-        </is>
-      </c>
-      <c r="B403" s="5" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN</t>
-        </is>
-      </c>
+          <t>Simplicity ILS</t>
+        </is>
+      </c>
+      <c r="B403" s="5" t="n"/>
       <c r="C403" s="6" t="n">
-        <v>1976</v>
+        <v>2020</v>
       </c>
       <c r="D403" s="5" t="inlineStr">
         <is>
@@ -36385,7 +36337,7 @@
       </c>
       <c r="E403" s="5" t="inlineStr">
         <is>
-          <t>Digitized archive of legal, legislative, and government documents licensed by subscription to law, academic, and public libraries - exhibited at PLA 2026</t>
+          <t>Cloud integrated library system covering cataloging, circulation, patron management, and reporting for public and academic libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F403" s="7" t="inlineStr">
@@ -36397,12 +36349,16 @@
     <row r="404">
       <c r="A404" s="19" t="inlineStr">
         <is>
-          <t>Simplicity ILS</t>
-        </is>
-      </c>
-      <c r="B404" s="19" t="n"/>
+          <t>SirsiDynix</t>
+        </is>
+      </c>
+      <c r="B404" s="19" t="inlineStr">
+        <is>
+          <t>Lehi, UT</t>
+        </is>
+      </c>
       <c r="C404" s="20" t="n">
-        <v>2020</v>
+        <v>2005</v>
       </c>
       <c r="D404" s="19" t="inlineStr">
         <is>
@@ -36411,7 +36367,7 @@
       </c>
       <c r="E404" s="19" t="inlineStr">
         <is>
-          <t>Cloud integrated library system covering cataloging, circulation, patron management, and reporting for public and academic libraries - exhibited at PLA 2026</t>
+          <t>Integrated library system, discovery, and mobile software for public, academic, school, and government libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F404" s="21" t="inlineStr">
@@ -36423,16 +36379,16 @@
     <row r="405">
       <c r="A405" s="5" t="inlineStr">
         <is>
-          <t>SirsiDynix</t>
+          <t>AWE Learning</t>
         </is>
       </c>
       <c r="B405" s="5" t="inlineStr">
         <is>
-          <t>Lehi, UT</t>
+          <t>Chester, PA</t>
         </is>
       </c>
       <c r="C405" s="6" t="n">
-        <v>2005</v>
+        <v>1994</v>
       </c>
       <c r="D405" s="5" t="inlineStr">
         <is>
@@ -36441,29 +36397,27 @@
       </c>
       <c r="E405" s="5" t="inlineStr">
         <is>
-          <t>Integrated library system, discovery, and mobile software for public, academic, school, and government libraries - exhibited at PLA 2026</t>
+          <t>Early Literacy Station and AfterSchool Edge learning workstations preloaded with ad-free, offline early literacy content for public libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F405" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="19" t="inlineStr">
         <is>
-          <t>AWE Learning</t>
+          <t>Comprise Technologies, Inc.</t>
         </is>
       </c>
       <c r="B406" s="19" t="inlineStr">
         <is>
-          <t>Chester, PA</t>
-        </is>
-      </c>
-      <c r="C406" s="20" t="n">
-        <v>1994</v>
-      </c>
+          <t>Navesink, NJ</t>
+        </is>
+      </c>
+      <c r="C406" s="20" t="n"/>
       <c r="D406" s="19" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -36471,24 +36425,24 @@
       </c>
       <c r="E406" s="19" t="inlineStr">
         <is>
-          <t>Early Literacy Station and AfterSchool Edge learning workstations preloaded with ad-free, offline early literacy content for public libraries - exhibited at PLA 2026</t>
+          <t>Print, copy, PC session and payment management software with self-service kiosks for public libraries, schools and municipal agencies - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F406" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="5" t="inlineStr">
         <is>
-          <t>Comprise Technologies, Inc.</t>
+          <t>EBSCO Information Services</t>
         </is>
       </c>
       <c r="B407" s="5" t="inlineStr">
         <is>
-          <t>Navesink, NJ</t>
+          <t>Ipswich, MA</t>
         </is>
       </c>
       <c r="C407" s="6" t="n"/>
@@ -36499,27 +36453,25 @@
       </c>
       <c r="E407" s="5" t="inlineStr">
         <is>
-          <t>Print, copy, PC session and payment management software with self-service kiosks for public libraries, schools and municipal agencies - exhibited at PLA 2026</t>
-        </is>
-      </c>
-      <c r="F407" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Research databases, ebook collections and discovery software licensed to public libraries, academic libraries, schools and healthcare organizations - exhibited at PLA 2026</t>
+        </is>
+      </c>
+      <c r="F407" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Regional Sales Manager, K12 &amp; Publ</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="19" t="inlineStr">
         <is>
-          <t>EBSCO Information Services</t>
-        </is>
-      </c>
-      <c r="B408" s="19" t="inlineStr">
-        <is>
-          <t>Ipswich, MA</t>
-        </is>
-      </c>
-      <c r="C408" s="20" t="n"/>
+          <t>Innovative</t>
+        </is>
+      </c>
+      <c r="B408" s="19" t="n"/>
+      <c r="C408" s="20" t="n">
+        <v>1978</v>
+      </c>
       <c r="D408" s="19" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -36527,24 +36479,28 @@
       </c>
       <c r="E408" s="19" t="inlineStr">
         <is>
-          <t>Research databases, ebook collections and discovery software licensed to public libraries, academic libraries, schools and healthcare organizations - exhibited at PLA 2026</t>
-        </is>
-      </c>
-      <c r="F408" s="22" t="inlineStr">
-        <is>
-          <t>Yes - Regional Sales Manager, K12 &amp; Publ</t>
+          <t>Sierra and Polaris integrated library systems plus the Vega discovery and patron engagement suite for public libraries and consortia - exhibited at PLA 2026</t>
+        </is>
+      </c>
+      <c r="F408" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="5" t="inlineStr">
         <is>
-          <t>Innovative</t>
-        </is>
-      </c>
-      <c r="B409" s="5" t="n"/>
+          <t>LocalHop</t>
+        </is>
+      </c>
+      <c r="B409" s="5" t="inlineStr">
+        <is>
+          <t>Pontiac, MI</t>
+        </is>
+      </c>
       <c r="C409" s="6" t="n">
-        <v>1978</v>
+        <v>2015</v>
       </c>
       <c r="D409" s="5" t="inlineStr">
         <is>
@@ -36553,7 +36509,7 @@
       </c>
       <c r="E409" s="5" t="inlineStr">
         <is>
-          <t>Sierra and Polaris integrated library systems plus the Vega discovery and patron engagement suite for public libraries and consortia - exhibited at PLA 2026</t>
+          <t>Event programming, room reservation and activity pass software for public library systems - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F409" s="7" t="inlineStr">
@@ -36565,16 +36521,16 @@
     <row r="410">
       <c r="A410" s="19" t="inlineStr">
         <is>
-          <t>LocalHop</t>
+          <t>PressReader</t>
         </is>
       </c>
       <c r="B410" s="19" t="inlineStr">
         <is>
-          <t>Pontiac, MI</t>
+          <t>Vancouver, Canada</t>
         </is>
       </c>
       <c r="C410" s="20" t="n">
-        <v>2015</v>
+        <v>1999</v>
       </c>
       <c r="D410" s="19" t="inlineStr">
         <is>
@@ -36583,29 +36539,27 @@
       </c>
       <c r="E410" s="19" t="inlineStr">
         <is>
-          <t>Event programming, room reservation and activity pass software for public library systems - exhibited at PLA 2026</t>
+          <t>All-you-can-read digital newspaper and magazine subscription licensed to public libraries, schools, hotels, airlines and hospitals - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F410" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="5" t="inlineStr">
         <is>
-          <t>PressReader</t>
+          <t>SOLUS</t>
         </is>
       </c>
       <c r="B411" s="5" t="inlineStr">
         <is>
-          <t>Vancouver, Canada</t>
-        </is>
-      </c>
-      <c r="C411" s="6" t="n">
-        <v>1999</v>
-      </c>
+          <t>Glasgow, United Kingdom</t>
+        </is>
+      </c>
+      <c r="C411" s="6" t="n"/>
       <c r="D411" s="5" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -36613,27 +36567,29 @@
       </c>
       <c r="E411" s="5" t="inlineStr">
         <is>
-          <t>All-you-can-read digital newspaper and magazine subscription licensed to public libraries, schools, hotels, airlines and hospitals - exhibited at PLA 2026</t>
+          <t>Patron mobile apps, event and room booking and discovery websites for public libraries and library consortia - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F411" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="19" t="inlineStr">
         <is>
-          <t>SOLUS</t>
+          <t>Transparent Language</t>
         </is>
       </c>
       <c r="B412" s="19" t="inlineStr">
         <is>
-          <t>Glasgow, United Kingdom</t>
-        </is>
-      </c>
-      <c r="C412" s="20" t="n"/>
+          <t>Nashua, NH</t>
+        </is>
+      </c>
+      <c r="C412" s="20" t="n">
+        <v>1991</v>
+      </c>
       <c r="D412" s="19" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -36641,28 +36597,28 @@
       </c>
       <c r="E412" s="19" t="inlineStr">
         <is>
-          <t>Patron mobile apps, event and room booking and discovery websites for public libraries and library consortia - exhibited at PLA 2026</t>
+          <t>Online language learning courses in 140+ languages licensed to public libraries, schools, government agencies and businesses - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F412" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="5" t="inlineStr">
         <is>
-          <t>Transparent Language</t>
+          <t>Beanstack</t>
         </is>
       </c>
       <c r="B413" s="5" t="inlineStr">
         <is>
-          <t>Nashua, NH</t>
+          <t>Arlington, VA</t>
         </is>
       </c>
       <c r="C413" s="6" t="n">
-        <v>1991</v>
+        <v>2013</v>
       </c>
       <c r="D413" s="5" t="inlineStr">
         <is>
@@ -36671,29 +36627,27 @@
       </c>
       <c r="E413" s="5" t="inlineStr">
         <is>
-          <t>Online language learning courses in 140+ languages licensed to public libraries, schools, government agencies and businesses - exhibited at PLA 2026</t>
+          <t>Reading challenge, logging and engagement analytics software for public libraries and school districts - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F413" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - board is another company's - not read</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="19" t="inlineStr">
         <is>
-          <t>Beanstack</t>
+          <t>EnvisionWare</t>
         </is>
       </c>
       <c r="B414" s="19" t="inlineStr">
         <is>
-          <t>Arlington, VA</t>
-        </is>
-      </c>
-      <c r="C414" s="20" t="n">
-        <v>2013</v>
-      </c>
+          <t>Alpharetta, GA</t>
+        </is>
+      </c>
+      <c r="C414" s="20" t="n"/>
       <c r="D414" s="19" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -36701,27 +36655,29 @@
       </c>
       <c r="E414" s="19" t="inlineStr">
         <is>
-          <t>Reading challenge, logging and engagement analytics software for public libraries and school districts - exhibited at PLA 2026</t>
+          <t>Library self-service software and hardware for print management, PC reservation, RFID checkout, automated material handling, holds lockers and patron payments - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F414" s="21" t="inlineStr">
         <is>
-          <t>Unknown - board is another company's - not read</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="5" t="inlineStr">
         <is>
-          <t>EnvisionWare</t>
+          <t>Insignia Software</t>
         </is>
       </c>
       <c r="B415" s="5" t="inlineStr">
         <is>
-          <t>Alpharetta, GA</t>
-        </is>
-      </c>
-      <c r="C415" s="6" t="n"/>
+          <t>Edmonton, Canada</t>
+        </is>
+      </c>
+      <c r="C415" s="6" t="n">
+        <v>1999</v>
+      </c>
       <c r="D415" s="5" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -36729,29 +36685,23 @@
       </c>
       <c r="E415" s="5" t="inlineStr">
         <is>
-          <t>Library self-service software and hardware for print management, PC reservation, RFID checkout, automated material handling, holds lockers and patron payments - exhibited at PLA 2026</t>
+          <t>Integrated library system, student information system and resource manager for K-12, public, academic and corporate libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F415" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="19" t="inlineStr">
         <is>
-          <t>Insignia Software</t>
-        </is>
-      </c>
-      <c r="B416" s="19" t="inlineStr">
-        <is>
-          <t>Edmonton, Canada</t>
-        </is>
-      </c>
-      <c r="C416" s="20" t="n">
-        <v>1999</v>
-      </c>
+          <t>LOTE4Kids</t>
+        </is>
+      </c>
+      <c r="B416" s="19" t="n"/>
+      <c r="C416" s="20" t="n"/>
       <c r="D416" s="19" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -36759,22 +36709,26 @@
       </c>
       <c r="E416" s="19" t="inlineStr">
         <is>
-          <t>Integrated library system, student information system and resource manager for K-12, public, academic and corporate libraries - exhibited at PLA 2026</t>
+          <t>Subscription digital library of narrated children's picture books in 115+ languages, licensed to public libraries and schools - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F416" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="5" t="inlineStr">
         <is>
-          <t>LOTE4Kids</t>
-        </is>
-      </c>
-      <c r="B417" s="5" t="n"/>
+          <t>myfilmfriend</t>
+        </is>
+      </c>
+      <c r="B417" s="5" t="inlineStr">
+        <is>
+          <t>Potsdam, Germany</t>
+        </is>
+      </c>
       <c r="C417" s="6" t="n"/>
       <c r="D417" s="5" t="inlineStr">
         <is>
@@ -36783,7 +36737,7 @@
       </c>
       <c r="E417" s="5" t="inlineStr">
         <is>
-          <t>Subscription digital library of narrated children's picture books in 115+ languages, licensed to public libraries and schools - exhibited at PLA 2026</t>
+          <t>Curated film and documentary streaming service licensed to public libraries for their cardholders - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F417" s="7" t="inlineStr">
@@ -36795,15 +36749,17 @@
     <row r="418">
       <c r="A418" s="19" t="inlineStr">
         <is>
-          <t>myfilmfriend</t>
+          <t>Springshare</t>
         </is>
       </c>
       <c r="B418" s="19" t="inlineStr">
         <is>
-          <t>Potsdam, Germany</t>
-        </is>
-      </c>
-      <c r="C418" s="20" t="n"/>
+          <t>Miami, FL</t>
+        </is>
+      </c>
+      <c r="C418" s="20" t="n">
+        <v>2007</v>
+      </c>
       <c r="D418" s="19" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -36811,24 +36767,24 @@
       </c>
       <c r="E418" s="19" t="inlineStr">
         <is>
-          <t>Curated film and documentary streaming service licensed to public libraries for their cardholders - exhibited at PLA 2026</t>
+          <t>LibGuides, LibCal, LibAnswers and related web, scheduling, reference and analytics software for public, academic and school libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F418" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="5" t="inlineStr">
         <is>
-          <t>Springshare</t>
+          <t>BiblioCommons</t>
         </is>
       </c>
       <c r="B419" s="5" t="inlineStr">
         <is>
-          <t>Miami, FL</t>
+          <t>Mississauga, Canada</t>
         </is>
       </c>
       <c r="C419" s="6" t="n">
@@ -36841,28 +36797,28 @@
       </c>
       <c r="E419" s="5" t="inlineStr">
         <is>
-          <t>LibGuides, LibCal, LibAnswers and related web, scheduling, reference and analytics software for public, academic and school libraries - exhibited at PLA 2026</t>
+          <t>Patron-facing catalog discovery, website, mobile app, events calendar and email marketing platform for public library systems - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F419" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="19" t="inlineStr">
         <is>
-          <t>BiblioCommons</t>
+          <t>LibLime</t>
         </is>
       </c>
       <c r="B420" s="19" t="inlineStr">
         <is>
-          <t>Mississauga, Canada</t>
+          <t>Rockville, MD</t>
         </is>
       </c>
       <c r="C420" s="20" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="D420" s="19" t="inlineStr">
         <is>
@@ -36871,7 +36827,7 @@
       </c>
       <c r="E420" s="19" t="inlineStr">
         <is>
-          <t>Patron-facing catalog discovery, website, mobile app, events calendar and email marketing platform for public library systems - exhibited at PLA 2026</t>
+          <t>Bibliovation cloud library services platform for cataloging, circulation, acquisitions and discovery at public, academic and consortium libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F420" s="21" t="inlineStr">
@@ -36883,17 +36839,11 @@
     <row r="421">
       <c r="A421" s="5" t="inlineStr">
         <is>
-          <t>LibLime</t>
-        </is>
-      </c>
-      <c r="B421" s="5" t="inlineStr">
-        <is>
-          <t>Rockville, MD</t>
-        </is>
-      </c>
-      <c r="C421" s="6" t="n">
-        <v>2005</v>
-      </c>
+          <t>MakeMake</t>
+        </is>
+      </c>
+      <c r="B421" s="5" t="n"/>
+      <c r="C421" s="6" t="n"/>
       <c r="D421" s="5" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -36901,7 +36851,7 @@
       </c>
       <c r="E421" s="5" t="inlineStr">
         <is>
-          <t>Bibliovation cloud library services platform for cataloging, circulation, acquisitions and discovery at public, academic and consortium libraries - exhibited at PLA 2026</t>
+          <t>Spanish-language children's ebook and digital reading collection licensed to public libraries and schools - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F421" s="7" t="inlineStr">
@@ -36913,10 +36863,14 @@
     <row r="422">
       <c r="A422" s="19" t="inlineStr">
         <is>
-          <t>MakeMake</t>
-        </is>
-      </c>
-      <c r="B422" s="19" t="n"/>
+          <t>NewsBank</t>
+        </is>
+      </c>
+      <c r="B422" s="19" t="inlineStr">
+        <is>
+          <t>Naples, FL</t>
+        </is>
+      </c>
       <c r="C422" s="20" t="n"/>
       <c r="D422" s="19" t="inlineStr">
         <is>
@@ -36925,7 +36879,7 @@
       </c>
       <c r="E422" s="19" t="inlineStr">
         <is>
-          <t>Spanish-language children's ebook and digital reading collection licensed to public libraries and schools - exhibited at PLA 2026</t>
+          <t>Licensed news archive and full-text research databases for public libraries, school districts, community colleges, universities and government libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F422" s="21" t="inlineStr">
@@ -36937,15 +36891,17 @@
     <row r="423">
       <c r="A423" s="5" t="inlineStr">
         <is>
-          <t>NewsBank</t>
+          <t>Quipu Group</t>
         </is>
       </c>
       <c r="B423" s="5" t="inlineStr">
         <is>
-          <t>Naples, FL</t>
-        </is>
-      </c>
-      <c r="C423" s="6" t="n"/>
+          <t>San Marcos, CA</t>
+        </is>
+      </c>
+      <c r="C423" s="6" t="n">
+        <v>2005</v>
+      </c>
       <c r="D423" s="5" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -36953,7 +36909,7 @@
       </c>
       <c r="E423" s="5" t="inlineStr">
         <is>
-          <t>Licensed news archive and full-text research databases for public libraries, school districts, community colleges, universities and government libraries - exhibited at PLA 2026</t>
+          <t>Online library card registration, card renewal, museum pass reservation and patron incident tracking software for public libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F423" s="7" t="inlineStr">
@@ -36965,17 +36921,11 @@
     <row r="424">
       <c r="A424" s="19" t="inlineStr">
         <is>
-          <t>Quipu Group</t>
-        </is>
-      </c>
-      <c r="B424" s="19" t="inlineStr">
-        <is>
-          <t>San Marcos, CA</t>
-        </is>
-      </c>
-      <c r="C424" s="20" t="n">
-        <v>2005</v>
-      </c>
+          <t>StackMap</t>
+        </is>
+      </c>
+      <c r="B424" s="19" t="n"/>
+      <c r="C424" s="20" t="n"/>
       <c r="D424" s="19" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -36983,7 +36933,7 @@
       </c>
       <c r="E424" s="19" t="inlineStr">
         <is>
-          <t>Online library card registration, card renewal, museum pass reservation and patron incident tracking software for public libraries - exhibited at PLA 2026</t>
+          <t>Indoor wayfinding and shelf-level mapping software that plugs into library catalogs and discovery layers to route patrons to items - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F424" s="21" t="inlineStr">
@@ -36995,11 +36945,17 @@
     <row r="425">
       <c r="A425" s="5" t="inlineStr">
         <is>
-          <t>StackMap</t>
-        </is>
-      </c>
-      <c r="B425" s="5" t="n"/>
-      <c r="C425" s="6" t="n"/>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="B425" s="5" t="inlineStr">
+        <is>
+          <t>Marlborough, United Kingdom</t>
+        </is>
+      </c>
+      <c r="C425" s="6" t="n">
+        <v>1990</v>
+      </c>
       <c r="D425" s="5" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -37007,29 +36963,27 @@
       </c>
       <c r="E425" s="5" t="inlineStr">
         <is>
-          <t>Indoor wayfinding and shelf-level mapping software that plugs into library catalogs and discovery layers to route patrons to items - exhibited at PLA 2026</t>
+          <t>Quartex digital collections publishing platform and licensed primary-source archive databases for public and academic libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F425" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="19" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>Book Systems</t>
         </is>
       </c>
       <c r="B426" s="19" t="inlineStr">
         <is>
-          <t>Marlborough, United Kingdom</t>
-        </is>
-      </c>
-      <c r="C426" s="20" t="n">
-        <v>1990</v>
-      </c>
+          <t>Huntsville, AL</t>
+        </is>
+      </c>
+      <c r="C426" s="20" t="n"/>
       <c r="D426" s="19" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -37037,7 +36991,7 @@
       </c>
       <c r="E426" s="19" t="inlineStr">
         <is>
-          <t>Quartex digital collections publishing platform and licensed primary-source archive databases for public and academic libraries - exhibited at PLA 2026</t>
+          <t>Atriuum cloud integrated library system and Booktracks asset tracking for public, school, academic and special libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F426" s="21" t="inlineStr">
@@ -37049,12 +37003,12 @@
     <row r="427">
       <c r="A427" s="5" t="inlineStr">
         <is>
-          <t>Book Systems</t>
+          <t>Librarica</t>
         </is>
       </c>
       <c r="B427" s="5" t="inlineStr">
         <is>
-          <t>Huntsville, AL</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="C427" s="6" t="n"/>
@@ -37065,27 +37019,25 @@
       </c>
       <c r="E427" s="5" t="inlineStr">
         <is>
-          <t>Atriuum cloud integrated library system and Booktracks asset tracking for public, school, academic and special libraries - exhibited at PLA 2026</t>
+          <t>CASSIE public computer session management and SPOT print and hotspot management software for public and academic libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F427" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="19" t="inlineStr">
         <is>
-          <t>Librarica</t>
-        </is>
-      </c>
-      <c r="B428" s="19" t="inlineStr">
-        <is>
-          <t>Dallas, TX</t>
-        </is>
-      </c>
-      <c r="C428" s="20" t="n"/>
+          <t>Mango Languages</t>
+        </is>
+      </c>
+      <c r="B428" s="19" t="n"/>
+      <c r="C428" s="20" t="n">
+        <v>2007</v>
+      </c>
       <c r="D428" s="19" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -37093,24 +37045,28 @@
       </c>
       <c r="E428" s="19" t="inlineStr">
         <is>
-          <t>CASSIE public computer session management and SPOT print and hotspot management software for public and academic libraries - exhibited at PLA 2026</t>
+          <t>Language learning platform in 70+ languages licensed by public libraries, school districts, universities and government agencies - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F428" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="5" t="inlineStr">
         <is>
-          <t>Mango Languages</t>
-        </is>
-      </c>
-      <c r="B429" s="5" t="n"/>
+          <t>Niche Academy</t>
+        </is>
+      </c>
+      <c r="B429" s="5" t="inlineStr">
+        <is>
+          <t>Lehi, UT</t>
+        </is>
+      </c>
       <c r="C429" s="6" t="n">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="D429" s="5" t="inlineStr">
         <is>
@@ -37119,29 +37075,23 @@
       </c>
       <c r="E429" s="5" t="inlineStr">
         <is>
-          <t>Language learning platform in 70+ languages licensed by public libraries, school districts, universities and government agencies - exhibited at PLA 2026</t>
+          <t>Staff training and patron education learning platform for public and academic libraries, municipalities and parks departments - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F429" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="19" t="inlineStr">
         <is>
-          <t>Niche Academy</t>
-        </is>
-      </c>
-      <c r="B430" s="19" t="inlineStr">
-        <is>
-          <t>Lehi, UT</t>
-        </is>
-      </c>
-      <c r="C430" s="20" t="n">
-        <v>2014</v>
-      </c>
+          <t>Reader Zone</t>
+        </is>
+      </c>
+      <c r="B430" s="19" t="n"/>
+      <c r="C430" s="20" t="n"/>
       <c r="D430" s="19" t="inlineStr">
         <is>
           <t>Libraries</t>
@@ -37149,7 +37099,7 @@
       </c>
       <c r="E430" s="19" t="inlineStr">
         <is>
-          <t>Staff training and patron education learning platform for public and academic libraries, municipalities and parks departments - exhibited at PLA 2026</t>
+          <t>Reading program and challenge management software for public libraries, schools and districts - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F430" s="21" t="inlineStr">
@@ -37161,7 +37111,7 @@
     <row r="431">
       <c r="A431" s="5" t="inlineStr">
         <is>
-          <t>Reader Zone</t>
+          <t>Counting Opinions</t>
         </is>
       </c>
       <c r="B431" s="5" t="n"/>
@@ -37173,7 +37123,7 @@
       </c>
       <c r="E431" s="5" t="inlineStr">
         <is>
-          <t>Reading program and challenge management software for public libraries, schools and districts - exhibited at PLA 2026</t>
+          <t>LibPAS performance data management, LibSat patron satisfaction survey and InformsUs data collection software for public, academic, state and consortium libraries - exhibited at PLA 2026</t>
         </is>
       </c>
       <c r="F431" s="7" t="inlineStr">
@@ -37185,19 +37135,21 @@
     <row r="432">
       <c r="A432" s="19" t="inlineStr">
         <is>
-          <t>Counting Opinions</t>
+          <t>Doobert</t>
         </is>
       </c>
       <c r="B432" s="19" t="n"/>
-      <c r="C432" s="20" t="n"/>
+      <c r="C432" s="20" t="n">
+        <v>2014</v>
+      </c>
       <c r="D432" s="19" t="inlineStr">
         <is>
-          <t>Libraries</t>
+          <t>Animal Services</t>
         </is>
       </c>
       <c r="E432" s="19" t="inlineStr">
         <is>
-          <t>LibPAS performance data management, LibSat patron satisfaction survey and InformsUs data collection software for public, academic, state and consortium libraries - exhibited at PLA 2026</t>
+          <t>Transport coordination, volunteer, and foster management software for animal shelters and rescue organizations - exhibited at Animal Care Expo 2026</t>
         </is>
       </c>
       <c r="F432" s="21" t="inlineStr">
@@ -37209,12 +37161,12 @@
     <row r="433">
       <c r="A433" s="5" t="inlineStr">
         <is>
-          <t>Doobert</t>
+          <t>Shelterluv</t>
         </is>
       </c>
       <c r="B433" s="5" t="n"/>
       <c r="C433" s="6" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="D433" s="5" t="inlineStr">
         <is>
@@ -37223,7 +37175,7 @@
       </c>
       <c r="E433" s="5" t="inlineStr">
         <is>
-          <t>Transport coordination, volunteer, and foster management software for animal shelters and rescue organizations - exhibited at Animal Care Expo 2026</t>
+          <t>Animal shelter and rescue management software covering intake, medical records, adoptions, and volunteers - exhibited at Animal Care Expo 2026</t>
         </is>
       </c>
       <c r="F433" s="7" t="inlineStr">
@@ -37235,21 +37187,25 @@
     <row r="434">
       <c r="A434" s="19" t="inlineStr">
         <is>
-          <t>Shelterluv</t>
-        </is>
-      </c>
-      <c r="B434" s="19" t="n"/>
+          <t>ArcSuite AI</t>
+        </is>
+      </c>
+      <c r="B434" s="19" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
       <c r="C434" s="20" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="D434" s="19" t="inlineStr">
         <is>
-          <t>Animal Services</t>
+          <t>Suppliers &amp; Services</t>
         </is>
       </c>
       <c r="E434" s="19" t="inlineStr">
         <is>
-          <t>Animal shelter and rescue management software covering intake, medical records, adoptions, and volunteers - exhibited at Animal Care Expo 2026</t>
+          <t>No-code AI government operations platform - exhibited at NIGP 2026</t>
         </is>
       </c>
       <c r="F434" s="21" t="inlineStr">
@@ -37261,16 +37217,16 @@
     <row r="435">
       <c r="A435" s="5" t="inlineStr">
         <is>
-          <t>ArcSuite AI</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="B435" s="5" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="C435" s="6" t="n">
-        <v>2014</v>
+        <v>1998</v>
       </c>
       <c r="D435" s="5" t="inlineStr">
         <is>
@@ -37279,28 +37235,24 @@
       </c>
       <c r="E435" s="5" t="inlineStr">
         <is>
-          <t>No-code AI government operations platform - exhibited at NIGP 2026</t>
+          <t>Recreation registration and facility management software - exhibited at ICMA 2025, NRPA 2026</t>
         </is>
       </c>
       <c r="F435" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - board is another company's - not read</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="19" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="B436" s="19" t="inlineStr">
-        <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="B436" s="19" t="n"/>
       <c r="C436" s="20" t="n">
-        <v>1998</v>
+        <v>1949</v>
       </c>
       <c r="D436" s="19" t="inlineStr">
         <is>
@@ -37309,24 +37261,28 @@
       </c>
       <c r="E436" s="19" t="inlineStr">
         <is>
-          <t>Recreation registration and facility management software - exhibited at ICMA 2025, NRPA 2026</t>
+          <t>Payroll and HR management software services - exhibited at NACo 2026, PSHRA 2026, NASWA 2025</t>
         </is>
       </c>
       <c r="F436" s="21" t="inlineStr">
         <is>
-          <t>Unknown - board is another company's - not read</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="5" t="inlineStr">
         <is>
-          <t>ADP</t>
-        </is>
-      </c>
-      <c r="B437" s="5" t="n"/>
+          <t>Aatral VR AR Training</t>
+        </is>
+      </c>
+      <c r="B437" s="5" t="inlineStr">
+        <is>
+          <t>Chennai, India</t>
+        </is>
+      </c>
       <c r="C437" s="6" t="n">
-        <v>1949</v>
+        <v>2018</v>
       </c>
       <c r="D437" s="5" t="inlineStr">
         <is>
@@ -37335,28 +37291,24 @@
       </c>
       <c r="E437" s="5" t="inlineStr">
         <is>
-          <t>Payroll and HR management software services - exhibited at NACo 2026, PSHRA 2026, NASWA 2025</t>
+          <t>VR/AR immersive training solutions - exhibited at TechConnect 2026</t>
         </is>
       </c>
       <c r="F437" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="19" t="inlineStr">
         <is>
-          <t>Aatral VR AR Training</t>
-        </is>
-      </c>
-      <c r="B438" s="19" t="inlineStr">
-        <is>
-          <t>Chennai, India</t>
-        </is>
-      </c>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="B438" s="19" t="n"/>
       <c r="C438" s="20" t="n">
-        <v>2018</v>
+        <v>1982</v>
       </c>
       <c r="D438" s="19" t="inlineStr">
         <is>
@@ -37365,7 +37317,7 @@
       </c>
       <c r="E438" s="19" t="inlineStr">
         <is>
-          <t>VR/AR immersive training solutions - exhibited at TechConnect 2026</t>
+          <t>Document, creative and digital experience software - exhibited at NACo 2026, NASCIO 2026, NCSEA 2026, CoSN 2026, APHSA 2026, EDUCAUSE 2026, Healthcare IT Connect 2026, MESC 2026</t>
         </is>
       </c>
       <c r="F438" s="21" t="inlineStr">
@@ -37377,12 +37329,12 @@
     <row r="439">
       <c r="A439" s="5" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
       <c r="B439" s="5" t="n"/>
       <c r="C439" s="6" t="n">
-        <v>1982</v>
+        <v>2006</v>
       </c>
       <c r="D439" s="5" t="inlineStr">
         <is>
@@ -37391,22 +37343,26 @@
       </c>
       <c r="E439" s="5" t="inlineStr">
         <is>
-          <t>Document, creative and digital experience software - exhibited at NACo 2026, NASCIO 2026, NCSEA 2026, CoSN 2026, APHSA 2026, EDUCAUSE 2026, Healthcare IT Connect 2026, MESC 2026</t>
+          <t>Cloud computing platform - exhibited at ICMA 2025, NACM 2026, AIRA 2026, EDUCAUSE 2026</t>
         </is>
       </c>
       <c r="F439" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="19" t="inlineStr">
         <is>
-          <t>Amazon Web Services (AWS)</t>
-        </is>
-      </c>
-      <c r="B440" s="19" t="n"/>
+          <t>Anaplan</t>
+        </is>
+      </c>
+      <c r="B440" s="19" t="inlineStr">
+        <is>
+          <t>Miami, FL</t>
+        </is>
+      </c>
       <c r="C440" s="20" t="n">
         <v>2006</v>
       </c>
@@ -37417,29 +37373,27 @@
       </c>
       <c r="E440" s="19" t="inlineStr">
         <is>
-          <t>Cloud computing platform - exhibited at ICMA 2025, NACM 2026, AIRA 2026, EDUCAUSE 2026</t>
-        </is>
-      </c>
-      <c r="F440" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Planning, budgeting and forecasting software - exhibited at ICMA 2025, NACUBO 2026, GFOA 2026</t>
+        </is>
+      </c>
+      <c r="F440" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="5" t="inlineStr">
         <is>
-          <t>Anaplan</t>
+          <t>Andrews Technology</t>
         </is>
       </c>
       <c r="B441" s="5" t="inlineStr">
         <is>
-          <t>Miami, FL</t>
-        </is>
-      </c>
-      <c r="C441" s="6" t="n">
-        <v>2006</v>
-      </c>
+          <t>Wilmington, NC</t>
+        </is>
+      </c>
+      <c r="C441" s="6" t="n"/>
       <c r="D441" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -37447,26 +37401,22 @@
       </c>
       <c r="E441" s="5" t="inlineStr">
         <is>
-          <t>Planning, budgeting and forecasting software - exhibited at ICMA 2025, NACUBO 2026, GFOA 2026</t>
-        </is>
-      </c>
-      <c r="F441" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+          <t>UKG Ready and NOVAtime time-and-attendance reseller and implementation partner for local government - exhibited at NACo 2026, NRPA 2026, GFOA 2026, WEFTEC 2026</t>
+        </is>
+      </c>
+      <c r="F441" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="19" t="inlineStr">
         <is>
-          <t>Andrews Technology</t>
-        </is>
-      </c>
-      <c r="B442" s="19" t="inlineStr">
-        <is>
-          <t>Wilmington, NC</t>
-        </is>
-      </c>
+          <t>Blitz</t>
+        </is>
+      </c>
+      <c r="B442" s="19" t="n"/>
       <c r="C442" s="20" t="n"/>
       <c r="D442" s="19" t="inlineStr">
         <is>
@@ -37475,22 +37425,26 @@
       </c>
       <c r="E442" s="19" t="inlineStr">
         <is>
-          <t>UKG Ready and NOVAtime time-and-attendance reseller and implementation partner for local government - exhibited at NACo 2026, NRPA 2026, GFOA 2026, WEFTEC 2026</t>
+          <t>AI permit pre-check and plan review - exhibited at ICMA 2025</t>
         </is>
       </c>
       <c r="F442" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 403 for https://blitzpermits.ai/car</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="5" t="inlineStr">
         <is>
-          <t>Blitz</t>
-        </is>
-      </c>
-      <c r="B443" s="5" t="n"/>
+          <t>Box</t>
+        </is>
+      </c>
+      <c r="B443" s="5" t="inlineStr">
+        <is>
+          <t>Redwood City, CA</t>
+        </is>
+      </c>
       <c r="C443" s="6" t="n"/>
       <c r="D443" s="5" t="inlineStr">
         <is>
@@ -37499,24 +37453,24 @@
       </c>
       <c r="E443" s="5" t="inlineStr">
         <is>
-          <t>AI permit pre-check and plan review - exhibited at ICMA 2025</t>
+          <t>Cloud content management and collaboration - exhibited at NACo 2026, EDUCAUSE 2026</t>
         </is>
       </c>
       <c r="F443" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://blitzpermits.ai/car</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="19" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>Card Integrity</t>
         </is>
       </c>
       <c r="B444" s="19" t="inlineStr">
         <is>
-          <t>Redwood City, CA</t>
+          <t>Oakbrook Terrace, IL</t>
         </is>
       </c>
       <c r="C444" s="20" t="n"/>
@@ -37527,27 +37481,25 @@
       </c>
       <c r="E444" s="19" t="inlineStr">
         <is>
-          <t>Cloud content management and collaboration - exhibited at NACo 2026, EDUCAUSE 2026</t>
-        </is>
-      </c>
-      <c r="F444" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Purchasing card audit and compliance monitoring - exhibited at NIGP 2026</t>
+        </is>
+      </c>
+      <c r="F444" s="22" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="5" t="inlineStr">
         <is>
-          <t>Card Integrity</t>
-        </is>
-      </c>
-      <c r="B445" s="5" t="inlineStr">
-        <is>
-          <t>Oakbrook Terrace, IL</t>
-        </is>
-      </c>
-      <c r="C445" s="6" t="n"/>
+          <t>Concourse</t>
+        </is>
+      </c>
+      <c r="B445" s="5" t="n"/>
+      <c r="C445" s="6" t="n">
+        <v>2023</v>
+      </c>
       <c r="D445" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -37555,24 +37507,24 @@
       </c>
       <c r="E445" s="5" t="inlineStr">
         <is>
-          <t>Purchasing card audit and compliance monitoring - exhibited at NIGP 2026</t>
-        </is>
-      </c>
-      <c r="F445" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Government contract and procurement software - exhibited at NIGP 2026</t>
+        </is>
+      </c>
+      <c r="F445" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="19" t="inlineStr">
         <is>
-          <t>Concourse</t>
+          <t>Creatio</t>
         </is>
       </c>
       <c r="B446" s="19" t="n"/>
       <c r="C446" s="20" t="n">
-        <v>2023</v>
+        <v>2002</v>
       </c>
       <c r="D446" s="19" t="inlineStr">
         <is>
@@ -37581,25 +37533,23 @@
       </c>
       <c r="E446" s="19" t="inlineStr">
         <is>
-          <t>Government contract and procurement software - exhibited at NIGP 2026</t>
+          <t>No-code CRM and workflow automation platform - exhibited at ICMA 2025</t>
         </is>
       </c>
       <c r="F446" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="5" t="inlineStr">
         <is>
-          <t>Creatio</t>
+          <t>Dwarpaal INC</t>
         </is>
       </c>
       <c r="B447" s="5" t="n"/>
-      <c r="C447" s="6" t="n">
-        <v>2002</v>
-      </c>
+      <c r="C447" s="6" t="n"/>
       <c r="D447" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -37607,19 +37557,19 @@
       </c>
       <c r="E447" s="5" t="inlineStr">
         <is>
-          <t>No-code CRM and workflow automation platform - exhibited at ICMA 2025</t>
+          <t>IoT building automation and energy management - exhibited at NIGP 2026</t>
         </is>
       </c>
       <c r="F447" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="19" t="inlineStr">
         <is>
-          <t>Dwarpaal INC</t>
+          <t>E-Ring Software Solutions, Inc.</t>
         </is>
       </c>
       <c r="B448" s="19" t="n"/>
@@ -37631,7 +37581,7 @@
       </c>
       <c r="E448" s="19" t="inlineStr">
         <is>
-          <t>IoT building automation and energy management - exhibited at NIGP 2026</t>
+          <t>Software solutions for government agencies - exhibited at NACo 2026</t>
         </is>
       </c>
       <c r="F448" s="21" t="inlineStr">
@@ -37643,7 +37593,7 @@
     <row r="449">
       <c r="A449" s="5" t="inlineStr">
         <is>
-          <t>E-Ring Software Solutions, Inc.</t>
+          <t>ENKON Information Systems (USA) Inc</t>
         </is>
       </c>
       <c r="B449" s="5" t="n"/>
@@ -37655,7 +37605,7 @@
       </c>
       <c r="E449" s="5" t="inlineStr">
         <is>
-          <t>Software solutions for government agencies - exhibited at NACo 2026</t>
+          <t>GIS and land records management software - exhibited at NACo 2026</t>
         </is>
       </c>
       <c r="F449" s="7" t="inlineStr">
@@ -37667,11 +37617,13 @@
     <row r="450">
       <c r="A450" s="19" t="inlineStr">
         <is>
-          <t>ENKON Information Systems (USA) Inc</t>
+          <t>Economic Impact Catalyst</t>
         </is>
       </c>
       <c r="B450" s="19" t="n"/>
-      <c r="C450" s="20" t="n"/>
+      <c r="C450" s="20" t="n">
+        <v>2018</v>
+      </c>
       <c r="D450" s="19" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -37679,25 +37631,23 @@
       </c>
       <c r="E450" s="19" t="inlineStr">
         <is>
-          <t>GIS and land records management software - exhibited at NACo 2026</t>
+          <t>Economic development ecosystem software platform - exhibited at ICMA 2025</t>
         </is>
       </c>
       <c r="F450" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="5" t="inlineStr">
         <is>
-          <t>Economic Impact Catalyst</t>
+          <t>Gordian</t>
         </is>
       </c>
       <c r="B451" s="5" t="n"/>
-      <c r="C451" s="6" t="n">
-        <v>2018</v>
-      </c>
+      <c r="C451" s="6" t="n"/>
       <c r="D451" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -37705,7 +37655,7 @@
       </c>
       <c r="E451" s="5" t="inlineStr">
         <is>
-          <t>Economic development ecosystem software platform - exhibited at ICMA 2025</t>
+          <t>Construction cost data and job order contracting software - exhibited at NIGP 2026, PWX 2026, NLC City Summit 2026</t>
         </is>
       </c>
       <c r="F451" s="7" t="inlineStr">
@@ -37717,11 +37667,13 @@
     <row r="452">
       <c r="A452" s="19" t="inlineStr">
         <is>
-          <t>Gordian</t>
+          <t>ICC Innovation</t>
         </is>
       </c>
       <c r="B452" s="19" t="n"/>
-      <c r="C452" s="20" t="n"/>
+      <c r="C452" s="20" t="n">
+        <v>1994</v>
+      </c>
       <c r="D452" s="19" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -37729,25 +37681,23 @@
       </c>
       <c r="E452" s="19" t="inlineStr">
         <is>
-          <t>Construction cost data and job order contracting software - exhibited at NIGP 2026, PWX 2026, NLC City Summit 2026</t>
+          <t>Code Council digital permitting/code solutions - exhibited at ICMA 2025, IMLA 2026, Maryland Municipal League 2026</t>
         </is>
       </c>
       <c r="F452" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="5" t="inlineStr">
         <is>
-          <t>ICC Innovation</t>
+          <t>ImageSource, Inc.</t>
         </is>
       </c>
       <c r="B453" s="5" t="n"/>
-      <c r="C453" s="6" t="n">
-        <v>1994</v>
-      </c>
+      <c r="C453" s="6" t="n"/>
       <c r="D453" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -37755,23 +37705,29 @@
       </c>
       <c r="E453" s="5" t="inlineStr">
         <is>
-          <t>Code Council digital permitting/code solutions - exhibited at ICMA 2025, IMLA 2026, Maryland Municipal League 2026</t>
+          <t>Content management and workflow automation software - exhibited at ICMA 2025</t>
         </is>
       </c>
       <c r="F453" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="19" t="inlineStr">
         <is>
-          <t>ImageSource, Inc.</t>
-        </is>
-      </c>
-      <c r="B454" s="19" t="n"/>
-      <c r="C454" s="20" t="n"/>
+          <t>Infor</t>
+        </is>
+      </c>
+      <c r="B454" s="19" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="C454" s="20" t="n">
+        <v>2002</v>
+      </c>
       <c r="D454" s="19" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -37779,29 +37735,23 @@
       </c>
       <c r="E454" s="19" t="inlineStr">
         <is>
-          <t>Content management and workflow automation software - exhibited at ICMA 2025</t>
+          <t>ERP and asset management software - exhibited at ICMA 2025, GFOA 2026, Healthcare IT Connect 2026</t>
         </is>
       </c>
       <c r="F454" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="5" t="inlineStr">
         <is>
-          <t>Infor</t>
-        </is>
-      </c>
-      <c r="B455" s="5" t="inlineStr">
-        <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
-      <c r="C455" s="6" t="n">
-        <v>2002</v>
-      </c>
+          <t>Inseer, Inc.</t>
+        </is>
+      </c>
+      <c r="B455" s="5" t="n"/>
+      <c r="C455" s="6" t="n"/>
       <c r="D455" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -37809,19 +37759,19 @@
       </c>
       <c r="E455" s="5" t="inlineStr">
         <is>
-          <t>ERP and asset management software - exhibited at ICMA 2025, GFOA 2026, Healthcare IT Connect 2026</t>
+          <t>AI ergonomic risk assessment software - exhibited at TechConnect 2026</t>
         </is>
       </c>
       <c r="F455" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="19" t="inlineStr">
         <is>
-          <t>Inseer, Inc.</t>
+          <t>IntelliSafe Analytics</t>
         </is>
       </c>
       <c r="B456" s="19" t="n"/>
@@ -37833,7 +37783,7 @@
       </c>
       <c r="E456" s="19" t="inlineStr">
         <is>
-          <t>AI ergonomic risk assessment software - exhibited at TechConnect 2026</t>
+          <t>Safety analytics and risk prediction software - exhibited at TechConnect 2026</t>
         </is>
       </c>
       <c r="F456" s="21" t="inlineStr">
@@ -37845,7 +37795,7 @@
     <row r="457">
       <c r="A457" s="5" t="inlineStr">
         <is>
-          <t>IntelliSafe Analytics</t>
+          <t>Intelligent Clinical Systems, LLC</t>
         </is>
       </c>
       <c r="B457" s="5" t="n"/>
@@ -37857,7 +37807,7 @@
       </c>
       <c r="E457" s="5" t="inlineStr">
         <is>
-          <t>Safety analytics and risk prediction software - exhibited at TechConnect 2026</t>
+          <t>Clinical health technology software systems - exhibited at TechConnect 2026</t>
         </is>
       </c>
       <c r="F457" s="7" t="inlineStr">
@@ -37869,7 +37819,7 @@
     <row r="458">
       <c r="A458" s="19" t="inlineStr">
         <is>
-          <t>Intelligent Clinical Systems, LLC</t>
+          <t>Johnson Controls OpenBlue</t>
         </is>
       </c>
       <c r="B458" s="19" t="n"/>
@@ -37881,7 +37831,7 @@
       </c>
       <c r="E458" s="19" t="inlineStr">
         <is>
-          <t>Clinical health technology software systems - exhibited at TechConnect 2026</t>
+          <t>Smart building operations software platform - exhibited at TechConnect 2026</t>
         </is>
       </c>
       <c r="F458" s="21" t="inlineStr">
@@ -37893,7 +37843,7 @@
     <row r="459">
       <c r="A459" s="5" t="inlineStr">
         <is>
-          <t>Johnson Controls OpenBlue</t>
+          <t>KnarrTek Inc.</t>
         </is>
       </c>
       <c r="B459" s="5" t="n"/>
@@ -37905,7 +37855,7 @@
       </c>
       <c r="E459" s="5" t="inlineStr">
         <is>
-          <t>Smart building operations software platform - exhibited at TechConnect 2026</t>
+          <t>Real-time materials and operations tracking software - exhibited at TechConnect 2026</t>
         </is>
       </c>
       <c r="F459" s="7" t="inlineStr">
@@ -37917,7 +37867,7 @@
     <row r="460">
       <c r="A460" s="19" t="inlineStr">
         <is>
-          <t>KnarrTek Inc.</t>
+          <t>LandApp by LandGate</t>
         </is>
       </c>
       <c r="B460" s="19" t="n"/>
@@ -37929,7 +37879,7 @@
       </c>
       <c r="E460" s="19" t="inlineStr">
         <is>
-          <t>Real-time materials and operations tracking software - exhibited at TechConnect 2026</t>
+          <t>Land and property data analytics platform - exhibited at ICMA 2025</t>
         </is>
       </c>
       <c r="F460" s="21" t="inlineStr">
@@ -37941,7 +37891,7 @@
     <row r="461">
       <c r="A461" s="5" t="inlineStr">
         <is>
-          <t>LandApp by LandGate</t>
+          <t>LexisNexis VitalChek</t>
         </is>
       </c>
       <c r="B461" s="5" t="n"/>
@@ -37953,7 +37903,7 @@
       </c>
       <c r="E461" s="5" t="inlineStr">
         <is>
-          <t>Land and property data analytics platform - exhibited at ICMA 2025</t>
+          <t>Online vital records ordering platform - exhibited at ICMA 2025</t>
         </is>
       </c>
       <c r="F461" s="7" t="inlineStr">
@@ -37965,7 +37915,7 @@
     <row r="462">
       <c r="A462" s="19" t="inlineStr">
         <is>
-          <t>LexisNexis VitalChek</t>
+          <t>MCCi</t>
         </is>
       </c>
       <c r="B462" s="19" t="n"/>
@@ -37977,7 +37927,7 @@
       </c>
       <c r="E462" s="19" t="inlineStr">
         <is>
-          <t>Online vital records ordering platform - exhibited at ICMA 2025</t>
+          <t>Document management and process automation for government - exhibited at ICMA 2025, GMIS International 2026</t>
         </is>
       </c>
       <c r="F462" s="21" t="inlineStr">
@@ -37989,7 +37939,7 @@
     <row r="463">
       <c r="A463" s="5" t="inlineStr">
         <is>
-          <t>MCCi</t>
+          <t>Mitel</t>
         </is>
       </c>
       <c r="B463" s="5" t="n"/>
@@ -38001,7 +37951,7 @@
       </c>
       <c r="E463" s="5" t="inlineStr">
         <is>
-          <t>Document management and process automation for government - exhibited at ICMA 2025, GMIS International 2026</t>
+          <t>Business phone and unified communications systems - exhibited at NIGP 2026</t>
         </is>
       </c>
       <c r="F463" s="7" t="inlineStr">
@@ -38013,7 +37963,7 @@
     <row r="464">
       <c r="A464" s="19" t="inlineStr">
         <is>
-          <t>Mitel</t>
+          <t>MyGovernmentOnline(MGO)-SCPDC</t>
         </is>
       </c>
       <c r="B464" s="19" t="n"/>
@@ -38025,7 +37975,7 @@
       </c>
       <c r="E464" s="19" t="inlineStr">
         <is>
-          <t>Business phone and unified communications systems - exhibited at NIGP 2026</t>
+          <t>Permitting, licensing and inspections software - exhibited at NACo 2026</t>
         </is>
       </c>
       <c r="F464" s="21" t="inlineStr">
@@ -38037,11 +37987,17 @@
     <row r="465">
       <c r="A465" s="5" t="inlineStr">
         <is>
-          <t>MyGovernmentOnline(MGO)-SCPDC</t>
-        </is>
-      </c>
-      <c r="B465" s="5" t="n"/>
-      <c r="C465" s="6" t="n"/>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="B465" s="5" t="inlineStr">
+        <is>
+          <t>Montreal, Canada</t>
+        </is>
+      </c>
+      <c r="C465" s="6" t="n">
+        <v>2003</v>
+      </c>
       <c r="D465" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -38049,29 +38005,23 @@
       </c>
       <c r="E465" s="5" t="inlineStr">
         <is>
-          <t>Permitting, licensing and inspections software - exhibited at NACo 2026</t>
-        </is>
-      </c>
-      <c r="F465" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Payment processing platform - exhibited at ICMA 2025</t>
+        </is>
+      </c>
+      <c r="F465" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="19" t="inlineStr">
         <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="B466" s="19" t="inlineStr">
-        <is>
-          <t>Montreal, Canada</t>
-        </is>
-      </c>
-      <c r="C466" s="20" t="n">
-        <v>2003</v>
-      </c>
+          <t>OfferioAI by Blu AI Technologies</t>
+        </is>
+      </c>
+      <c r="B466" s="19" t="n"/>
+      <c r="C466" s="20" t="n"/>
       <c r="D466" s="19" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -38079,19 +38029,19 @@
       </c>
       <c r="E466" s="19" t="inlineStr">
         <is>
-          <t>Payment processing platform - exhibited at ICMA 2025</t>
-        </is>
-      </c>
-      <c r="F466" s="22" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>AI-driven procurement and bid software - exhibited at NIGP 2026</t>
+        </is>
+      </c>
+      <c r="F466" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="5" t="inlineStr">
         <is>
-          <t>OfferioAI by Blu AI Technologies</t>
+          <t>Ohpynez</t>
         </is>
       </c>
       <c r="B467" s="5" t="n"/>
@@ -38103,7 +38053,7 @@
       </c>
       <c r="E467" s="5" t="inlineStr">
         <is>
-          <t>AI-driven procurement and bid software - exhibited at NIGP 2026</t>
+          <t>Social polling platform for community engagement - exhibited at ICMA 2025, NACo 2026, NLC City Summit 2026, 3CMA 2026</t>
         </is>
       </c>
       <c r="F467" s="7" t="inlineStr">
@@ -38115,7 +38065,7 @@
     <row r="468">
       <c r="A468" s="19" t="inlineStr">
         <is>
-          <t>Ohpynez</t>
+          <t>Oracle NetSuite for Government</t>
         </is>
       </c>
       <c r="B468" s="19" t="n"/>
@@ -38127,7 +38077,7 @@
       </c>
       <c r="E468" s="19" t="inlineStr">
         <is>
-          <t>Social polling platform for community engagement - exhibited at ICMA 2025, NACo 2026, NLC City Summit 2026, 3CMA 2026</t>
+          <t>Cloud ERP software for government - exhibited at ICMA 2025</t>
         </is>
       </c>
       <c r="F468" s="21" t="inlineStr">
@@ -38139,7 +38089,7 @@
     <row r="469">
       <c r="A469" s="5" t="inlineStr">
         <is>
-          <t>Oracle NetSuite for Government</t>
+          <t>ParkZilla</t>
         </is>
       </c>
       <c r="B469" s="5" t="n"/>
@@ -38151,7 +38101,7 @@
       </c>
       <c r="E469" s="5" t="inlineStr">
         <is>
-          <t>Cloud ERP software for government - exhibited at ICMA 2025</t>
+          <t>Parking permit and enforcement software - exhibited at ICMA 2025</t>
         </is>
       </c>
       <c r="F469" s="7" t="inlineStr">
@@ -38163,7 +38113,7 @@
     <row r="470">
       <c r="A470" s="19" t="inlineStr">
         <is>
-          <t>ParkZilla</t>
+          <t>Partake</t>
         </is>
       </c>
       <c r="B470" s="19" t="n"/>
@@ -38175,7 +38125,7 @@
       </c>
       <c r="E470" s="19" t="inlineStr">
         <is>
-          <t>Parking permit and enforcement software - exhibited at ICMA 2025</t>
+          <t>Digital community engagement platform for cities - exhibited at ICMA 2025</t>
         </is>
       </c>
       <c r="F470" s="21" t="inlineStr">
@@ -38187,10 +38137,14 @@
     <row r="471">
       <c r="A471" s="5" t="inlineStr">
         <is>
-          <t>Partake</t>
-        </is>
-      </c>
-      <c r="B471" s="5" t="n"/>
+          <t>Procore</t>
+        </is>
+      </c>
+      <c r="B471" s="5" t="inlineStr">
+        <is>
+          <t>Carpinteria, CA</t>
+        </is>
+      </c>
       <c r="C471" s="6" t="n"/>
       <c r="D471" s="5" t="inlineStr">
         <is>
@@ -38199,26 +38153,22 @@
       </c>
       <c r="E471" s="5" t="inlineStr">
         <is>
-          <t>Digital community engagement platform for cities - exhibited at ICMA 2025</t>
-        </is>
-      </c>
-      <c r="F471" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Construction project management software - exhibited at ICMA 2025, PWX 2026</t>
+        </is>
+      </c>
+      <c r="F471" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="19" t="inlineStr">
         <is>
-          <t>Procore</t>
-        </is>
-      </c>
-      <c r="B472" s="19" t="inlineStr">
-        <is>
-          <t>Carpinteria, CA</t>
-        </is>
-      </c>
+          <t>Proofpoint Inc</t>
+        </is>
+      </c>
+      <c r="B472" s="19" t="n"/>
       <c r="C472" s="20" t="n"/>
       <c r="D472" s="19" t="inlineStr">
         <is>
@@ -38227,19 +38177,19 @@
       </c>
       <c r="E472" s="19" t="inlineStr">
         <is>
-          <t>Construction project management software - exhibited at ICMA 2025, PWX 2026</t>
-        </is>
-      </c>
-      <c r="F472" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+          <t>Email security and cybersecurity software - exhibited at NACo 2026, EDUCAUSE 2026</t>
+        </is>
+      </c>
+      <c r="F472" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="5" t="inlineStr">
         <is>
-          <t>Proofpoint Inc</t>
+          <t>Qualtrics</t>
         </is>
       </c>
       <c r="B473" s="5" t="n"/>
@@ -38251,7 +38201,7 @@
       </c>
       <c r="E473" s="5" t="inlineStr">
         <is>
-          <t>Email security and cybersecurity software - exhibited at NACo 2026, EDUCAUSE 2026</t>
+          <t>Survey and experience management software - exhibited at ICMA 2025</t>
         </is>
       </c>
       <c r="F473" s="7" t="inlineStr">
@@ -38263,7 +38213,7 @@
     <row r="474">
       <c r="A474" s="19" t="inlineStr">
         <is>
-          <t>Qualtrics</t>
+          <t>RADICL</t>
         </is>
       </c>
       <c r="B474" s="19" t="n"/>
@@ -38275,19 +38225,19 @@
       </c>
       <c r="E474" s="19" t="inlineStr">
         <is>
-          <t>Survey and experience management software - exhibited at ICMA 2025</t>
+          <t>Cybersecurity protection platform for defense suppliers - exhibited at TechConnect 2026</t>
         </is>
       </c>
       <c r="F474" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="5" t="inlineStr">
         <is>
-          <t>RADICL</t>
+          <t>RFXPremier</t>
         </is>
       </c>
       <c r="B475" s="5" t="n"/>
@@ -38299,7 +38249,7 @@
       </c>
       <c r="E475" s="5" t="inlineStr">
         <is>
-          <t>Cybersecurity protection platform for defense suppliers - exhibited at TechConnect 2026</t>
+          <t>RFP and solicitation management software - exhibited at NIGP 2026</t>
         </is>
       </c>
       <c r="F475" s="7" t="inlineStr">
@@ -38311,11 +38261,17 @@
     <row r="476">
       <c r="A476" s="19" t="inlineStr">
         <is>
-          <t>RFXPremier</t>
-        </is>
-      </c>
-      <c r="B476" s="19" t="n"/>
-      <c r="C476" s="20" t="n"/>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="B476" s="19" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="C476" s="20" t="n">
+        <v>1999</v>
+      </c>
       <c r="D476" s="19" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -38323,29 +38279,23 @@
       </c>
       <c r="E476" s="19" t="inlineStr">
         <is>
-          <t>RFP and solicitation management software - exhibited at NIGP 2026</t>
-        </is>
-      </c>
-      <c r="F476" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>CRM and case management cloud software - exhibited at NACo 2026, NIGP 2026, NASWA 2025, NASCIO 2026, APHSA 2026, NatCon 2026, EDUCAUSE 2026, Healthcare IT Connect 2026, MESC 2026</t>
+        </is>
+      </c>
+      <c r="F476" s="22" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="5" t="inlineStr">
         <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="B477" s="5" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="C477" s="6" t="n">
-        <v>1999</v>
-      </c>
+          <t>SentinelOne</t>
+        </is>
+      </c>
+      <c r="B477" s="5" t="n"/>
+      <c r="C477" s="6" t="n"/>
       <c r="D477" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -38353,19 +38303,19 @@
       </c>
       <c r="E477" s="5" t="inlineStr">
         <is>
-          <t>CRM and case management cloud software - exhibited at NACo 2026, NIGP 2026, NASWA 2025, NASCIO 2026, APHSA 2026, NatCon 2026, EDUCAUSE 2026, Healthcare IT Connect 2026, MESC 2026</t>
-        </is>
-      </c>
-      <c r="F477" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Endpoint detection and response security software - exhibited at NACo 2026</t>
+        </is>
+      </c>
+      <c r="F477" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="19" t="inlineStr">
         <is>
-          <t>SentinelOne</t>
+          <t>SimForge</t>
         </is>
       </c>
       <c r="B478" s="19" t="n"/>
@@ -38377,19 +38327,19 @@
       </c>
       <c r="E478" s="19" t="inlineStr">
         <is>
-          <t>Endpoint detection and response security software - exhibited at NACo 2026</t>
+          <t>Simulation software for engineering and defense - exhibited at TechConnect 2026</t>
         </is>
       </c>
       <c r="F478" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="5" t="inlineStr">
         <is>
-          <t>SimForge</t>
+          <t>Sotaog</t>
         </is>
       </c>
       <c r="B479" s="5" t="n"/>
@@ -38401,7 +38351,7 @@
       </c>
       <c r="E479" s="5" t="inlineStr">
         <is>
-          <t>Simulation software for engineering and defense - exhibited at TechConnect 2026</t>
+          <t>Industrial AI analytics and monitoring platform - exhibited at TechConnect 2026</t>
         </is>
       </c>
       <c r="F479" s="7" t="inlineStr">
@@ -38413,7 +38363,7 @@
     <row r="480">
       <c r="A480" s="19" t="inlineStr">
         <is>
-          <t>Sotaog</t>
+          <t>Status Solutions Network</t>
         </is>
       </c>
       <c r="B480" s="19" t="n"/>
@@ -38425,19 +38375,19 @@
       </c>
       <c r="E480" s="19" t="inlineStr">
         <is>
-          <t>Industrial AI analytics and monitoring platform - exhibited at TechConnect 2026</t>
+          <t>Mass notification and situational awareness software - exhibited at NACo 2026</t>
         </is>
       </c>
       <c r="F480" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="5" t="inlineStr">
         <is>
-          <t>Status Solutions Network</t>
+          <t>Surety 2000</t>
         </is>
       </c>
       <c r="B481" s="5" t="n"/>
@@ -38449,19 +38399,19 @@
       </c>
       <c r="E481" s="5" t="inlineStr">
         <is>
-          <t>Mass notification and situational awareness software - exhibited at NACo 2026</t>
+          <t>Electronic bid bond verification platform - exhibited at NIGP 2026</t>
         </is>
       </c>
       <c r="F481" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="19" t="inlineStr">
         <is>
-          <t>Surety 2000</t>
+          <t>Systems &amp; Methods, Inc.</t>
         </is>
       </c>
       <c r="B482" s="19" t="n"/>
@@ -38473,19 +38423,19 @@
       </c>
       <c r="E482" s="19" t="inlineStr">
         <is>
-          <t>Electronic bid bond verification platform - exhibited at NIGP 2026</t>
+          <t>Child support and government payment processing software - exhibited at ICMA 2025</t>
         </is>
       </c>
       <c r="F482" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="5" t="inlineStr">
         <is>
-          <t>Systems &amp; Methods, Inc.</t>
+          <t>TOOTRiS Child Care Solutions</t>
         </is>
       </c>
       <c r="B483" s="5" t="n"/>
@@ -38497,19 +38447,19 @@
       </c>
       <c r="E483" s="5" t="inlineStr">
         <is>
-          <t>Child support and government payment processing software - exhibited at ICMA 2025</t>
+          <t>Child care benefits and booking platform - exhibited at NACo 2026</t>
         </is>
       </c>
       <c r="F483" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="19" t="inlineStr">
         <is>
-          <t>TOOTRiS Child Care Solutions</t>
+          <t>Threefold AI</t>
         </is>
       </c>
       <c r="B484" s="19" t="n"/>
@@ -38521,7 +38471,7 @@
       </c>
       <c r="E484" s="19" t="inlineStr">
         <is>
-          <t>Child care benefits and booking platform - exhibited at NACo 2026</t>
+          <t>AI resident service platform for local government - exhibited at ICMA 2025</t>
         </is>
       </c>
       <c r="F484" s="21" t="inlineStr">
@@ -38533,7 +38483,7 @@
     <row r="485">
       <c r="A485" s="5" t="inlineStr">
         <is>
-          <t>Threefold AI</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="B485" s="5" t="n"/>
@@ -38545,19 +38495,19 @@
       </c>
       <c r="E485" s="5" t="inlineStr">
         <is>
-          <t>AI resident service platform for local government - exhibited at ICMA 2025</t>
+          <t>Asset management software (Cityworks), positioning technology - exhibited at ICMA 2025, NRPA 2026, PWX 2026, AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F485" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="19" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>VerityPay</t>
         </is>
       </c>
       <c r="B486" s="19" t="n"/>
@@ -38569,19 +38519,19 @@
       </c>
       <c r="E486" s="19" t="inlineStr">
         <is>
-          <t>Asset management software (Cityworks), positioning technology - exhibited at ICMA 2025, NRPA 2026, PWX 2026, AWWA ACE 2026</t>
+          <t>SMS-based digital payment collection platform - exhibited at NACo 2026</t>
         </is>
       </c>
       <c r="F486" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="5" t="inlineStr">
         <is>
-          <t>VerityPay</t>
+          <t>eBridge Procurement</t>
         </is>
       </c>
       <c r="B487" s="5" t="n"/>
@@ -38593,7 +38543,7 @@
       </c>
       <c r="E487" s="5" t="inlineStr">
         <is>
-          <t>SMS-based digital payment collection platform - exhibited at NACo 2026</t>
+          <t>E-procurement bid posting and management platform - exhibited at NIGP 2026</t>
         </is>
       </c>
       <c r="F487" s="7" t="inlineStr">
@@ -38605,7 +38555,7 @@
     <row r="488">
       <c r="A488" s="19" t="inlineStr">
         <is>
-          <t>eBridge Procurement</t>
+          <t>nCase Technologies LLC</t>
         </is>
       </c>
       <c r="B488" s="19" t="n"/>
@@ -38617,7 +38567,7 @@
       </c>
       <c r="E488" s="19" t="inlineStr">
         <is>
-          <t>E-procurement bid posting and management platform - exhibited at NIGP 2026</t>
+          <t>Case management software for agencies - exhibited at NACo 2026</t>
         </is>
       </c>
       <c r="F488" s="21" t="inlineStr">
@@ -38626,32 +38576,8 @@
         </is>
       </c>
     </row>
-    <row r="489">
-      <c r="A489" s="5" t="inlineStr">
-        <is>
-          <t>nCase Technologies LLC</t>
-        </is>
-      </c>
-      <c r="B489" s="5" t="n"/>
-      <c r="C489" s="6" t="n"/>
-      <c r="D489" s="5" t="inlineStr">
-        <is>
-          <t>Suppliers &amp; Services</t>
-        </is>
-      </c>
-      <c r="E489" s="5" t="inlineStr">
-        <is>
-          <t>Case management software for agencies - exhibited at NACo 2026</t>
-        </is>
-      </c>
-      <c r="F489" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F489"/>
+  <autoFilter ref="A1:F488"/>
   <dataValidations count="1">
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid category" error="Pick one of: Citizen Services, Permitting &amp; Licensing, Finance &amp; ERP, Procurement &amp; Payments, HR &amp; Workforce, Cemetery Management, IT &amp; AI Platforms, Strategy &amp; Performance, Elections, Elections &amp; Voting, Libraries, Animal Services, Suppliers &amp; Services" type="list">
       <formula1>"Citizen Services,Permitting &amp; Licensing,Finance &amp; ERP,Procurement &amp; Payments,HR &amp; Workforce,Cemetery Management,IT &amp; AI Platforms,Strategy &amp; Performance,Elections,Elections &amp; Voting,Libraries,Animal Services,Suppliers &amp; Services"</formula1>
@@ -38708,7 +38634,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/27/26)</t>
+          <t>Hiring AEs? (9/28/26)</t>
         </is>
       </c>
     </row>
@@ -42990,7 +42916,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/27/26)</t>
+          <t>Hiring AEs? (9/28/26)</t>
         </is>
       </c>
     </row>
@@ -43880,9 +43806,9 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -44264,7 +44190,7 @@
       </c>
       <c r="F44" s="35" t="inlineStr">
         <is>
-          <t>Yes - Regional Account Manager (Remote USA)</t>
+          <t>Yes - Sr. Regional Account Manager (Remote USA)</t>
         </is>
       </c>
     </row>
@@ -45970,9 +45896,9 @@
           <t>Single sign-on, rostering and usage analytics for public school districts - exhibited at CoSN 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F101" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -46280,9 +46206,9 @@
           <t>Library, technology asset, and facilities management software for K-12 school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F112" s="33" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Inside Sales Account Executive only</t>
+      <c r="F112" s="34" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -47047,7 +46973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F192"/>
+  <dimension ref="A1:F191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -47086,7 +47012,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/27/26)</t>
+          <t>Hiring AEs? (9/28/26)</t>
         </is>
       </c>
     </row>
@@ -52295,12 +52221,12 @@
     <row r="178">
       <c r="A178" s="37" t="inlineStr">
         <is>
-          <t>INIT Innovations in Transportation, Inc.</t>
+          <t>INTANGLES USA INC</t>
         </is>
       </c>
       <c r="B178" s="37" t="n"/>
       <c r="C178" s="38" t="n">
-        <v>1983</v>
+        <v>2014</v>
       </c>
       <c r="D178" s="37" t="inlineStr">
         <is>
@@ -52309,24 +52235,28 @@
       </c>
       <c r="E178" s="37" t="inlineStr">
         <is>
-          <t>Transit ITS, fare collection, scheduling software - exhibited at APTA 2026</t>
+          <t>AI predictive fleet analytics platform - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F178" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 403 for https://www.intangles.ai/ca</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>INTANGLES USA INC</t>
-        </is>
-      </c>
-      <c r="B179" s="5" t="n"/>
+          <t>Indra Group</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>Madrid, Spain</t>
+        </is>
+      </c>
       <c r="C179" s="6" t="n">
-        <v>2014</v>
+        <v>1993</v>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
@@ -52335,29 +52265,23 @@
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>AI predictive fleet analytics platform - exhibited at APTA 2026</t>
+          <t>Ticketing, traffic and transit management systems - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.intangles.ai/ca</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="37" t="inlineStr">
         <is>
-          <t>Indra Group</t>
-        </is>
-      </c>
-      <c r="B180" s="37" t="inlineStr">
-        <is>
-          <t>Madrid, Spain</t>
-        </is>
-      </c>
-      <c r="C180" s="38" t="n">
-        <v>1993</v>
-      </c>
+          <t>Intellicene</t>
+        </is>
+      </c>
+      <c r="B180" s="37" t="n"/>
+      <c r="C180" s="38" t="n"/>
       <c r="D180" s="37" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -52365,19 +52289,19 @@
       </c>
       <c r="E180" s="37" t="inlineStr">
         <is>
-          <t>Ticketing, traffic and transit management systems - exhibited at APTA 2026</t>
-        </is>
-      </c>
-      <c r="F180" s="40" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Security and intelligence analytics software - exhibited at APTA 2026</t>
+        </is>
+      </c>
+      <c r="F180" s="39" t="inlineStr">
+        <is>
+          <t>Yes - Enterprise Sales Executive – New L (2 Locations)</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>Intellicene</t>
+          <t>Lux Modus</t>
         </is>
       </c>
       <c r="B181" s="5" t="n"/>
@@ -52389,19 +52313,19 @@
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>Security and intelligence analytics software - exhibited at APTA 2026</t>
-        </is>
-      </c>
-      <c r="F181" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Enterprise Sales Executive – New L (2 Locations)</t>
+          <t>LiDAR 3D digital twin capture for transit - exhibited at APTA 2026</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="37" t="inlineStr">
         <is>
-          <t>Lux Modus</t>
+          <t>MOEV Inc.</t>
         </is>
       </c>
       <c r="B182" s="37" t="n"/>
@@ -52413,7 +52337,7 @@
       </c>
       <c r="E182" s="37" t="inlineStr">
         <is>
-          <t>LiDAR 3D digital twin capture for transit - exhibited at APTA 2026</t>
+          <t>Smart EV charging management software - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F182" s="40" t="inlineStr">
@@ -52425,7 +52349,7 @@
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>MOEV Inc.</t>
+          <t>Onward Health</t>
         </is>
       </c>
       <c r="B183" s="5" t="n"/>
@@ -52437,7 +52361,7 @@
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>Smart EV charging management software - exhibited at APTA 2026</t>
+          <t>Medical transportation ride management software - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
@@ -52449,7 +52373,7 @@
     <row r="184">
       <c r="A184" s="37" t="inlineStr">
         <is>
-          <t>Onward Health</t>
+          <t>Pulse Transit Software</t>
         </is>
       </c>
       <c r="B184" s="37" t="n"/>
@@ -52461,7 +52385,7 @@
       </c>
       <c r="E184" s="37" t="inlineStr">
         <is>
-          <t>Medical transportation ride management software - exhibited at APTA 2026</t>
+          <t>Transit operations software - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F184" s="40" t="inlineStr">
@@ -52473,11 +52397,13 @@
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>Pulse Transit Software</t>
+          <t>PureTech Systems, Inc.</t>
         </is>
       </c>
       <c r="B185" s="5" t="n"/>
-      <c r="C185" s="6" t="n"/>
+      <c r="C185" s="6" t="n">
+        <v>2004</v>
+      </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -52485,25 +52411,23 @@
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>Transit operations software - exhibited at APTA 2026</t>
+          <t>AI video analytics perimeter security software - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="37" t="inlineStr">
         <is>
-          <t>PureTech Systems, Inc.</t>
+          <t>Redstone Technologies LLC</t>
         </is>
       </c>
       <c r="B186" s="37" t="n"/>
-      <c r="C186" s="38" t="n">
-        <v>2004</v>
-      </c>
+      <c r="C186" s="38" t="n"/>
       <c r="D186" s="37" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -52511,19 +52435,19 @@
       </c>
       <c r="E186" s="37" t="inlineStr">
         <is>
-          <t>AI video analytics perimeter security software - exhibited at APTA 2026</t>
+          <t>Rail/transit software, AI and asset monitoring - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F186" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>Redstone Technologies LLC</t>
+          <t>Strategic Mapping</t>
         </is>
       </c>
       <c r="B187" s="5" t="n"/>
@@ -52535,7 +52459,7 @@
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>Rail/transit software, AI and asset monitoring - exhibited at APTA 2026</t>
+          <t>Transit CAD/AVL, APC, passenger information systems - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
@@ -52547,7 +52471,7 @@
     <row r="188">
       <c r="A188" s="37" t="inlineStr">
         <is>
-          <t>Strategic Mapping</t>
+          <t>TSO Mobile</t>
         </is>
       </c>
       <c r="B188" s="37" t="n"/>
@@ -52559,23 +52483,29 @@
       </c>
       <c r="E188" s="37" t="inlineStr">
         <is>
-          <t>Transit CAD/AVL, APC, passenger information systems - exhibited at APTA 2026</t>
-        </is>
-      </c>
-      <c r="F188" s="40" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>GPS fleet tracking and telematics software - exhibited at APTA 2026</t>
+        </is>
+      </c>
+      <c r="F188" s="39" t="inlineStr">
+        <is>
+          <t>Yes - Sales Account Executive – Mid-Mark</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>TSO Mobile</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="n"/>
-      <c r="C189" s="6" t="n"/>
+          <t>The Mobility House</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="n">
+        <v>2009</v>
+      </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -52583,29 +52513,23 @@
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>GPS fleet tracking and telematics software - exhibited at APTA 2026</t>
-        </is>
-      </c>
-      <c r="F189" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Sales Account Executive – Mid-Mark</t>
+          <t>EV fleet charge management software - exhibited at APTA 2026</t>
+        </is>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="37" t="inlineStr">
         <is>
-          <t>The Mobility House</t>
-        </is>
-      </c>
-      <c r="B190" s="37" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="C190" s="38" t="n">
-        <v>2009</v>
-      </c>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="B190" s="37" t="n"/>
+      <c r="C190" s="38" t="n"/>
       <c r="D190" s="37" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -52613,19 +52537,19 @@
       </c>
       <c r="E190" s="37" t="inlineStr">
         <is>
-          <t>EV fleet charge management software - exhibited at APTA 2026</t>
+          <t>On-demand mobility platform for agency partnerships - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F190" s="40" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>Uber Technologies, Inc.</t>
+          <t>Uptale USA, Inc.</t>
         </is>
       </c>
       <c r="B191" s="5" t="n"/>
@@ -52637,7 +52561,7 @@
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>On-demand mobility platform for agency partnerships - exhibited at APTA 2026</t>
+          <t>Immersive VR training software platform - exhibited at APTA 2026</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
@@ -52646,32 +52570,8 @@
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="37" t="inlineStr">
-        <is>
-          <t>Uptale USA, Inc.</t>
-        </is>
-      </c>
-      <c r="B192" s="37" t="n"/>
-      <c r="C192" s="38" t="n"/>
-      <c r="D192" s="37" t="inlineStr">
-        <is>
-          <t>Suppliers &amp; Services</t>
-        </is>
-      </c>
-      <c r="E192" s="37" t="inlineStr">
-        <is>
-          <t>Immersive VR training software platform - exhibited at APTA 2026</t>
-        </is>
-      </c>
-      <c r="F192" s="40" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F192"/>
+  <autoFilter ref="A1:F191"/>
   <dataValidations count="1">
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid category" error="Pick one of: Fare &amp; Payments, Fleet &amp; Operations, Rider Experience, Demand-Response &amp; AV, Parking &amp; Curb, Suppliers &amp; Services" type="list">
       <formula1>"Fare &amp; Payments,Fleet &amp; Operations,Rider Experience,Demand-Response &amp; AV,Parking &amp; Curb,Suppliers &amp; Services"</formula1>
@@ -52728,7 +52628,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/27/26)</t>
+          <t>Hiring AEs? (9/28/26)</t>
         </is>
       </c>
     </row>
@@ -56286,7 +56186,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/27/26)</t>
+          <t>Hiring AEs? (9/28/26)</t>
         </is>
       </c>
     </row>
@@ -58672,7 +58572,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (C1 - (Dallas, TX, United)</t>
+          <t>Yes - Enterprise Account Executive (C1 - (New York, New York)</t>
         </is>
       </c>
     </row>
@@ -59810,7 +59710,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/27/26)</t>
+          <t>Hiring AEs? (9/28/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -296,8 +296,8 @@
     <xf numFmtId="1" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/28/26)</t>
+          <t>Hiring AEs? (9/29/26)</t>
         </is>
       </c>
     </row>
@@ -5982,9 +5982,9 @@
           <t>Assistive AI for 911 centers: transcription, translation, text-to-911, and video</t>
         </is>
       </c>
-      <c r="F171" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+      <c r="F171" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -9458,9 +9458,9 @@
           <t>Digital forensics and investigation management software - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F289" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Sales Operations &amp; GTM Systems Man only</t>
+      <c r="F289" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -10292,9 +10292,9 @@
           <t>Endpoint management and IT automation software - exhibited at NSA 2026, GMIS International 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F323" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F323" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/28/26)</t>
+          <t>Hiring AEs? (9/29/26)</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/28/26)</t>
+          <t>Hiring AEs? (9/29/26)</t>
         </is>
       </c>
     </row>
@@ -15090,9 +15090,9 @@
           <t>Multi-model collaborative AI workspace for university and college faculty, staff, and students - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F26" s="70" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F26" s="71" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -16714,7 +16714,7 @@
       </c>
       <c r="F86" s="70" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Customer Success Manager only</t>
+          <t>Sales (non-AE) - Business Development Representativ only</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/28/26)</t>
+          <t>Hiring AEs? (9/29/26)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/28/26)</t>
+          <t>Hiring AEs? (9/29/26)</t>
         </is>
       </c>
     </row>
@@ -22664,7 +22664,7 @@
       </c>
       <c r="F177" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (US | Massachusetts)</t>
+          <t>Yes - Account Executive I, SMG (US | Massachusetts)</t>
         </is>
       </c>
     </row>
@@ -23650,7 +23650,7 @@
       </c>
       <c r="F210" s="16" t="inlineStr">
         <is>
-          <t>Yes - Regional Account Executive, Energy (Ottawa, Ontario)</t>
+          <t>Yes - Account Executive Install Base (Ja (Tokyo, Tokyo)</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/28/26)</t>
+          <t>Hiring AEs? (9/29/26)</t>
         </is>
       </c>
     </row>
@@ -26210,9 +26210,9 @@
           <t>CodeRED public alerting and critical event management for local jurisdictions</t>
         </is>
       </c>
-      <c r="F56" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F56" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -26754,7 +26754,7 @@
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - board is another company's - not read</t>
         </is>
       </c>
     </row>
@@ -26812,7 +26812,7 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Business Development Representativ only</t>
+          <t>Sales (non-AE) - Commercial Counsel, Revenue only</t>
         </is>
       </c>
     </row>
@@ -26842,7 +26842,7 @@
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (US | Massachusetts)</t>
+          <t>Yes - Account Executive I, SMG (US | Massachusetts)</t>
         </is>
       </c>
     </row>
@@ -30946,7 +30946,7 @@
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -31868,7 +31868,7 @@
       </c>
       <c r="F248" s="23" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Associate Director, Client Success only</t>
+          <t>Sales (non-AE) - Director, Labor Sales only</t>
         </is>
       </c>
     </row>
@@ -34222,7 +34222,7 @@
       </c>
       <c r="F329" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -38634,7 +38634,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/28/26)</t>
+          <t>Hiring AEs? (9/29/26)</t>
         </is>
       </c>
     </row>
@@ -38844,7 +38844,7 @@
       </c>
       <c r="F8" s="27" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Sales Development Representative only</t>
+          <t>Sales (non-AE) - Salesforce &amp; RevOps Systems Admini only</t>
         </is>
       </c>
     </row>
@@ -42916,7 +42916,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/28/26)</t>
+          <t>Hiring AEs? (9/29/26)</t>
         </is>
       </c>
     </row>
@@ -43806,9 +43806,9 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -45298,9 +45298,9 @@
           <t>K-12 ERP, nutrition, payments and forms platform for districts</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Solutions Consultant only</t>
         </is>
       </c>
     </row>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/28/26)</t>
+          <t>Hiring AEs? (9/29/26)</t>
         </is>
       </c>
     </row>
@@ -47042,7 +47042,7 @@
       </c>
       <c r="F2" s="39" t="inlineStr">
         <is>
-          <t>Yes - Account Manager - East Coast (2 Locations)</t>
+          <t>Unknown - HTTP 502 for https://cubic.wd1.myworkday</t>
         </is>
       </c>
     </row>
@@ -47100,7 +47100,7 @@
           <t>Mobile fare payment app covering 200+ North American agencies</t>
         </is>
       </c>
-      <c r="F4" s="40" t="inlineStr">
+      <c r="F4" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -47160,7 +47160,7 @@
           <t>Automated fare collection plus parking and rail signalling systems (US office Lowell, MA)</t>
         </is>
       </c>
-      <c r="F6" s="40" t="inlineStr">
+      <c r="F6" s="39" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.scheidt-bachman</t>
         </is>
@@ -47220,7 +47220,7 @@
           <t>Account-based ticketing and open-loop EMV fare collection in 150+ cities (BPC Group)</t>
         </is>
       </c>
-      <c r="F8" s="40" t="inlineStr">
+      <c r="F8" s="39" t="inlineStr">
         <is>
           <t>Unknown - board is another company's - not read</t>
         </is>
@@ -47280,7 +47280,7 @@
           <t>KubaPay cloud fare collection and account-based ticketing in 500+ cities (ICM group, not Cubic)</t>
         </is>
       </c>
-      <c r="F10" s="40" t="inlineStr">
+      <c r="F10" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -47340,7 +47340,7 @@
           <t>Automated fare collection and tolling/ITS for US agencies (LA, Bay Area, DC); Samsung SDS lineage</t>
         </is>
       </c>
-      <c r="F12" s="40" t="inlineStr">
+      <c r="F12" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -47398,7 +47398,7 @@
           <t>Fareboxes, validators, and the Universal Platform for automated fare management</t>
         </is>
       </c>
-      <c r="F14" s="40" t="inlineStr">
+      <c r="F14" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -47456,7 +47456,7 @@
           <t>Transit scheduling, fare and paratransit software for public operators</t>
         </is>
       </c>
-      <c r="F16" s="40" t="inlineStr">
+      <c r="F16" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -47516,7 +47516,7 @@
           <t>Tolling operations and back-office payment services for toll agencies</t>
         </is>
       </c>
-      <c r="F18" s="40" t="inlineStr">
+      <c r="F18" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -47576,7 +47576,7 @@
           <t>Account-based fare collection and validators for public transit operators</t>
         </is>
       </c>
-      <c r="F20" s="39" t="inlineStr">
+      <c r="F20" s="40" t="inlineStr">
         <is>
           <t>Yes - Senior Enterprise Account Executiv (Spain, Spain)</t>
         </is>
@@ -47636,7 +47636,7 @@
           <t>Bus ITS: CAD/AVL, real-time passenger info, and fleet health</t>
         </is>
       </c>
-      <c r="F22" s="40" t="inlineStr">
+      <c r="F22" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -47696,7 +47696,7 @@
           <t>Real-time transit data: arrival predictions and on-time performance</t>
         </is>
       </c>
-      <c r="F24" s="39" t="inlineStr">
+      <c r="F24" s="40" t="inlineStr">
         <is>
           <t>Yes - Senior Account Manager (United States)</t>
         </is>
@@ -47756,7 +47756,7 @@
           <t>myAvail enterprise transit management ITS and CAD/AVL for mid-size US agencies</t>
         </is>
       </c>
-      <c r="F26" s="40" t="inlineStr">
+      <c r="F26" s="39" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://availtec.com/career</t>
         </is>
@@ -47816,7 +47816,7 @@
           <t>IVU.suite planning, scheduling, dispatch, and ticketing for transit and rail operators</t>
         </is>
       </c>
-      <c r="F28" s="40" t="inlineStr">
+      <c r="F28" s="39" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.ivu.com/career</t>
         </is>
@@ -47876,7 +47876,7 @@
           <t>Transit dispatch, CAD/AVL, and communications software (Modaxo brand, ex-Trapeze ITS)</t>
         </is>
       </c>
-      <c r="F30" s="40" t="inlineStr">
+      <c r="F30" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -47936,7 +47936,7 @@
           <t>Consat Telematics real-time CAD/AVL, passenger info, and electromobility analytics (NA office Sudbury ON)</t>
         </is>
       </c>
-      <c r="F32" s="40" t="inlineStr">
+      <c r="F32" s="39" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.consat.com/care</t>
         </is>
@@ -47996,7 +47996,7 @@
           <t>Transit performance data warehousing, BI, and automated NTD reporting (Modaxo brand) - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F34" s="40" t="inlineStr">
+      <c r="F34" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -48050,7 +48050,7 @@
           <t>Cloud CAD/AVL and in-vehicle tech for transit agencies and campus systems (SDVOSB)</t>
         </is>
       </c>
-      <c r="F36" s="40" t="inlineStr">
+      <c r="F36" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48110,7 +48110,7 @@
           <t>IBM Maximo consulting plus Mobile Informer EAM for transit agencies, airports, and utilities</t>
         </is>
       </c>
-      <c r="F38" s="40" t="inlineStr">
+      <c r="F38" s="39" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.interlocsolutio</t>
         </is>
@@ -48142,7 +48142,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -48170,7 +48170,7 @@
           <t>Trainwise onboard train control/monitoring and Fleetwise wayside fleet management for transit</t>
         </is>
       </c>
-      <c r="F40" s="40" t="inlineStr">
+      <c r="F40" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48230,7 +48230,7 @@
           <t>Rail terminal management, track inspection, and crew compliance for short lines and commuter rail</t>
         </is>
       </c>
-      <c r="F42" s="40" t="inlineStr">
+      <c r="F42" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48290,7 +48290,7 @@
           <t>Ultra-wideband train positioning, worker protection, and ATP for transit agencies (NYC MTA)</t>
         </is>
       </c>
-      <c r="F44" s="40" t="inlineStr">
+      <c r="F44" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48350,7 +48350,7 @@
           <t>CylusOne rail OT cybersecurity: threat detection for signaling, trackside, and onboard networks</t>
         </is>
       </c>
-      <c r="F46" s="40" t="inlineStr">
+      <c r="F46" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48408,7 +48408,7 @@
           <t>ConnX Maestro unified communications and contact center for transit agencies (SEPTA)</t>
         </is>
       </c>
-      <c r="F48" s="40" t="inlineStr">
+      <c r="F48" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48466,7 +48466,7 @@
           <t>Non-invasive sensors and cloud analytics for elevator, escalator, and HVAC uptime in transit stations</t>
         </is>
       </c>
-      <c r="F50" s="40" t="inlineStr">
+      <c r="F50" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48524,7 +48524,7 @@
           <t>Virtual Optical Fiber high-speed data offload between transit vehicles and depots</t>
         </is>
       </c>
-      <c r="F52" s="40" t="inlineStr">
+      <c r="F52" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48584,7 +48584,7 @@
           <t>AI smart inspection for rail infrastructure: sensor robot plus defect detection and predictive maintenance</t>
         </is>
       </c>
-      <c r="F54" s="40" t="inlineStr">
+      <c r="F54" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48640,7 +48640,7 @@
           <t>Mobile video surveillance, DVRs, and MotoTrax analytics for transit, school, and municipal fleets - exhibited at CTAA EXPO 2026, NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F56" s="39" t="inlineStr">
+      <c r="F56" s="40" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -48700,7 +48700,7 @@
           <t>Onboard transit systems: Horizon CCTV, NetSpire passenger info, iConnex real-time (US in Buffalo NY)</t>
         </is>
       </c>
-      <c r="F58" s="40" t="inlineStr">
+      <c r="F58" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48760,7 +48760,7 @@
           <t>Intelligent video, AI stop-arm analytics, and cloud safety platforms for transit and school districts - exhibited at CTAA EXPO 2026, NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F60" s="40" t="inlineStr">
+      <c r="F60" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48820,7 +48820,7 @@
           <t>AI dashcams, MDVRs, and fleet video telematics for transit, school bus, and commercial fleets (US: Houston)</t>
         </is>
       </c>
-      <c r="F62" s="40" t="inlineStr">
+      <c r="F62" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48880,7 +48880,7 @@
           <t>3D AI people-flow sensors for passenger counting, queue, and dwell in transit hubs and airports</t>
         </is>
       </c>
-      <c r="F64" s="40" t="inlineStr">
+      <c r="F64" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48940,7 +48940,7 @@
           <t>Automatic passenger counting hardware and analysis software for bus, rail, and paratransit</t>
         </is>
       </c>
-      <c r="F66" s="40" t="inlineStr">
+      <c r="F66" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -49000,7 +49000,7 @@
           <t>Video telematics and driver safety for municipal and transit fleets - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
-      <c r="F68" s="40" t="inlineStr">
+      <c r="F68" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49032,7 +49032,7 @@
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive, Mid-Market (USA)</t>
+          <t>Yes - Enterprise Core Account Executive  (Remote)</t>
         </is>
       </c>
     </row>
@@ -49060,7 +49060,7 @@
           <t>Telematics devices and fleet tracking software for public fleets</t>
         </is>
       </c>
-      <c r="F70" s="40" t="inlineStr">
+      <c r="F70" s="39" t="inlineStr">
         <is>
           <t>Unknown - no jobs parsed from iCIMS portal</t>
         </is>
@@ -49120,7 +49120,7 @@
           <t>FleetWave fleet asset management for public sector fleets</t>
         </is>
       </c>
-      <c r="F72" s="40" t="inlineStr">
+      <c r="F72" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49180,7 +49180,7 @@
           <t>FleetCommander motor pool and vehicle sharing for agencies</t>
         </is>
       </c>
-      <c r="F74" s="40" t="inlineStr">
+      <c r="F74" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -49240,7 +49240,7 @@
           <t>Fleet data analytics and benchmarking for public and utility fleets</t>
         </is>
       </c>
-      <c r="F76" s="40" t="inlineStr">
+      <c r="F76" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -49300,7 +49300,7 @@
           <t>Fleet automation and motor pool platform for public agencies</t>
         </is>
       </c>
-      <c r="F78" s="40" t="inlineStr">
+      <c r="F78" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49360,7 +49360,7 @@
           <t>Onboard surveillance and video management for transit fleets</t>
         </is>
       </c>
-      <c r="F80" s="40" t="inlineStr">
+      <c r="F80" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -49480,7 +49480,7 @@
           <t>On-demand transit and shared mobility software for public agencies</t>
         </is>
       </c>
-      <c r="F84" s="40" t="inlineStr">
+      <c r="F84" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -49540,7 +49540,7 @@
           <t>Parking meters, kiosks and transit fare systems for cities</t>
         </is>
       </c>
-      <c r="F86" s="40" t="inlineStr">
+      <c r="F86" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49600,7 +49600,7 @@
           <t>Mobile parking payments for city and municipal parking operators</t>
         </is>
       </c>
-      <c r="F88" s="39" t="inlineStr">
+      <c r="F88" s="40" t="inlineStr">
         <is>
           <t>Yes - Corporate Sales Executive</t>
         </is>
@@ -49660,7 +49660,7 @@
           <t>Parking access and revenue control systems for public garages</t>
         </is>
       </c>
-      <c r="F90" s="40" t="inlineStr">
+      <c r="F90" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49720,7 +49720,7 @@
           <t>Automated enforcement: school-zone speed, red-light, and bus-lane cameras - exhibited at North Carolina Sheriffs' Association 2026</t>
         </is>
       </c>
-      <c r="F92" s="39" t="inlineStr">
+      <c r="F92" s="40" t="inlineStr">
         <is>
           <t>Yes - Mass Market Account Executive (California_Remote)</t>
         </is>
@@ -49780,7 +49780,7 @@
           <t>Multimodal trip planning app plus a paid agency suite (white-label apps, sponsored Royale, rider data) - exhibited at CTAA EXPO 2026, NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F94" s="40" t="inlineStr">
+      <c r="F94" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49840,7 +49840,7 @@
           <t>ePaper Digital Bus Stop, SmartStop kiosks, and CPAM content management for transit agencies</t>
         </is>
       </c>
-      <c r="F96" s="40" t="inlineStr">
+      <c r="F96" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -49960,7 +49960,7 @@
           <t>Bus destination displays, controllers, and next-stop passenger information systems</t>
         </is>
       </c>
-      <c r="F100" s="40" t="inlineStr">
+      <c r="F100" s="39" t="inlineStr">
         <is>
           <t>Unknown - HTTP 202 for https://www.hanoverdisplays</t>
         </is>
@@ -50018,7 +50018,7 @@
           <t>TRACC travel-time and accessibility analysis plus transport datasets for government transport agencies</t>
         </is>
       </c>
-      <c r="F102" s="40" t="inlineStr">
+      <c r="F102" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50078,7 +50078,7 @@
           <t>Solar smart bus stops with edge AI plus the ORA platform: signage, lane enforcement, passenger counting</t>
         </is>
       </c>
-      <c r="F104" s="40" t="inlineStr">
+      <c r="F104" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50138,7 +50138,7 @@
           <t>Real-time transit display screens and rider information for agencies and cities</t>
         </is>
       </c>
-      <c r="F106" s="40" t="inlineStr">
+      <c r="F106" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50198,7 +50198,7 @@
           <t>Elevated automated transit pods on prefabricated guideways (ex-skyTran team) for cities and campuses</t>
         </is>
       </c>
-      <c r="F108" s="40" t="inlineStr">
+      <c r="F108" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50258,7 +50258,7 @@
           <t>On-demand microtransit software with rider/driver apps and AI dispatch for large agencies - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F110" s="39" t="inlineStr">
+      <c r="F110" s="40" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -50318,7 +50318,7 @@
           <t>Assisted-mobility platform and driver network delivering ADA paratransit and door-through-door trips - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F112" s="40" t="inlineStr">
+      <c r="F112" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50378,7 +50378,7 @@
           <t>Transit management software for paratransit, demand-response, microtransit, and taxi fleets - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F114" s="40" t="inlineStr">
+      <c r="F114" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50438,7 +50438,7 @@
           <t>Autonomous vehicle technology and driverless shuttle service for transit agencies and cities</t>
         </is>
       </c>
-      <c r="F116" s="40" t="inlineStr">
+      <c r="F116" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -50498,7 +50498,7 @@
           <t>flowride.ai SAE Level-4 automated driving software retrofitted onto full-size electric transit buses</t>
         </is>
       </c>
-      <c r="F118" s="40" t="inlineStr">
+      <c r="F118" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50558,7 +50558,7 @@
           <t>Assisted senior and accessible transportation platform serving agency paratransit overflow in 35+ metros</t>
         </is>
       </c>
-      <c r="F120" s="40" t="inlineStr">
+      <c r="F120" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50618,7 +50618,7 @@
           <t>White-label multimodal TDM and commute platform for regional agencies, employers, and campuses</t>
         </is>
       </c>
-      <c r="F122" s="40" t="inlineStr">
+      <c r="F122" s="39" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.rideshark.com/c</t>
         </is>
@@ -50670,7 +50670,7 @@
           <t>TripMaster paratransit scheduling and dispatch software for public transit providers</t>
         </is>
       </c>
-      <c r="F124" s="40" t="inlineStr">
+      <c r="F124" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50728,7 +50728,7 @@
           <t>Demand-responsive transit dispatch and booking software for transit agencies - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F126" s="40" t="inlineStr">
+      <c r="F126" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50788,7 +50788,7 @@
           <t>Electric on-demand shuttle service contracted by cities and transit agencies - exhibited at WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F128" s="40" t="inlineStr">
+      <c r="F128" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -50848,7 +50848,7 @@
           <t>On-demand ridepooling and mobility analytics software for public transit authorities</t>
         </is>
       </c>
-      <c r="F130" s="40" t="inlineStr">
+      <c r="F130" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50908,7 +50908,7 @@
           <t>Ridepooling operations and autonomous shuttle services for public transport partners</t>
         </is>
       </c>
-      <c r="F132" s="40" t="inlineStr">
+      <c r="F132" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50960,7 +50960,7 @@
           <t>ADA paratransit eligibility, call center and mobility management technology for agencies</t>
         </is>
       </c>
-      <c r="F134" s="40" t="inlineStr">
+      <c r="F134" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51020,7 +51020,7 @@
           <t>Whoosh autonomous cable-driven transit pods for cities and campuses</t>
         </is>
       </c>
-      <c r="F136" s="40" t="inlineStr">
+      <c r="F136" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51080,7 +51080,7 @@
           <t>Autonomous shuttle vehicles for public transport and campus deployments</t>
         </is>
       </c>
-      <c r="F138" s="40" t="inlineStr">
+      <c r="F138" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51140,7 +51140,7 @@
           <t>Electric and autonomous buses sold to public transit operators worldwide</t>
         </is>
       </c>
-      <c r="F140" s="40" t="inlineStr">
+      <c r="F140" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51200,7 +51200,7 @@
           <t>Automated people mover and group rapid transit systems for public authorities</t>
         </is>
       </c>
-      <c r="F142" s="40" t="inlineStr">
+      <c r="F142" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -51260,7 +51260,7 @@
           <t>Autonomy software powering driverless shuttles for transit and airport operators</t>
         </is>
       </c>
-      <c r="F144" s="40" t="inlineStr">
+      <c r="F144" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -51320,7 +51320,7 @@
           <t>Autonomous shuttles for public transport agencies, airports and campuses</t>
         </is>
       </c>
-      <c r="F146" s="40" t="inlineStr">
+      <c r="F146" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51380,7 +51380,7 @@
           <t>Leading mobile parking payments app (EasyPark Group)</t>
         </is>
       </c>
-      <c r="F148" s="40" t="inlineStr">
+      <c r="F148" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -51440,7 +51440,7 @@
           <t>Computer vision curb management and automated loading-zone payments</t>
         </is>
       </c>
-      <c r="F150" s="40" t="inlineStr">
+      <c r="F150" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -51500,7 +51500,7 @@
           <t>Gateless LPR parking operations (GLIDEPARCS) for private lots, universities, and some municipalities</t>
         </is>
       </c>
-      <c r="F152" s="40" t="inlineStr">
+      <c r="F152" s="39" t="inlineStr">
         <is>
           <t>Unknown - page too small - likely JS-rendered</t>
         </is>
@@ -51560,7 +51560,7 @@
           <t>Towing lifecycle software for city towing programs and impound management (ex-AutoReturn + TSD)</t>
         </is>
       </c>
-      <c r="F154" s="40" t="inlineStr">
+      <c r="F154" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -51620,7 +51620,7 @@
           <t>Sentry solar smart kiosks and vision-based automated parking enforcement</t>
         </is>
       </c>
-      <c r="F156" s="40" t="inlineStr">
+      <c r="F156" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51680,7 +51680,7 @@
           <t>Single-space smart parking meters and pay stations for municipalities</t>
         </is>
       </c>
-      <c r="F158" s="40" t="inlineStr">
+      <c r="F158" s="39" t="inlineStr">
         <is>
           <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
@@ -51740,7 +51740,7 @@
           <t>Wireless parking occupancy sensors for city and campus parking</t>
         </is>
       </c>
-      <c r="F160" s="40" t="inlineStr">
+      <c r="F160" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51800,7 +51800,7 @@
           <t>Smart parking sensors and LoRaWAN networks for cities</t>
         </is>
       </c>
-      <c r="F162" s="40" t="inlineStr">
+      <c r="F162" s="39" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -51860,7 +51860,7 @@
           <t>Parking payments, permits and enforcement software for municipalities</t>
         </is>
       </c>
-      <c r="F164" s="40" t="inlineStr">
+      <c r="F164" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51920,7 +51920,7 @@
           <t>Parking citation processing and permit services for California cities</t>
         </is>
       </c>
-      <c r="F166" s="40" t="inlineStr">
+      <c r="F166" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51980,7 +51980,7 @@
           <t>Parking citation, permit and enforcement management software for agencies</t>
         </is>
       </c>
-      <c r="F168" s="40" t="inlineStr">
+      <c r="F168" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52036,7 +52036,7 @@
           <t>Control room video wall visualization software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F170" s="40" t="inlineStr">
+      <c r="F170" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -52088,7 +52088,7 @@
           <t>Transit fare collection and ticketing software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F172" s="40" t="inlineStr">
+      <c r="F172" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52136,7 +52136,7 @@
           <t>Infrastructure engineering and asset software - exhibited at APTA 2026, AWWA ACE 2026</t>
         </is>
       </c>
-      <c r="F174" s="40" t="inlineStr">
+      <c r="F174" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52188,7 +52188,7 @@
           <t>Fuel and fleet management systems - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F176" s="40" t="inlineStr">
+      <c r="F176" s="39" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -52238,7 +52238,7 @@
           <t>AI predictive fleet analytics platform - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F178" s="40" t="inlineStr">
+      <c r="F178" s="39" t="inlineStr">
         <is>
           <t>Unknown - HTTP 403 for https://www.intangles.ai/ca</t>
         </is>
@@ -52292,7 +52292,7 @@
           <t>Security and intelligence analytics software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F180" s="39" t="inlineStr">
+      <c r="F180" s="40" t="inlineStr">
         <is>
           <t>Yes - Enterprise Sales Executive – New L (2 Locations)</t>
         </is>
@@ -52340,7 +52340,7 @@
           <t>Smart EV charging management software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F182" s="40" t="inlineStr">
+      <c r="F182" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52388,7 +52388,7 @@
           <t>Transit operations software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F184" s="40" t="inlineStr">
+      <c r="F184" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52438,7 +52438,7 @@
           <t>Rail/transit software, AI and asset monitoring - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F186" s="40" t="inlineStr">
+      <c r="F186" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52486,7 +52486,7 @@
           <t>GPS fleet tracking and telematics software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F188" s="39" t="inlineStr">
+      <c r="F188" s="40" t="inlineStr">
         <is>
           <t>Yes - Sales Account Executive – Mid-Mark</t>
         </is>
@@ -52540,7 +52540,7 @@
           <t>On-demand mobility platform for agency partnerships - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F190" s="40" t="inlineStr">
+      <c r="F190" s="39" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52628,7 +52628,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/28/26)</t>
+          <t>Hiring AEs? (9/29/26)</t>
         </is>
       </c>
     </row>
@@ -56186,7 +56186,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/28/26)</t>
+          <t>Hiring AEs? (9/29/26)</t>
         </is>
       </c>
     </row>
@@ -57822,7 +57822,7 @@
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.elenium.com/car</t>
         </is>
       </c>
     </row>
@@ -58602,7 +58602,7 @@
       </c>
       <c r="F82" s="53" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Senior Enterprise Solutions Archit only</t>
+          <t>Sales (non-AE) - USAF and USSF (US Space Force) Str only</t>
         </is>
       </c>
     </row>
@@ -59048,9 +59048,9 @@
           <t>Computer-vision checkout-free parking payment platform (drive-in/drive-out billing) plus parking operations and revenue management for airports; owner of SP+.</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Associate Account Executive (Cleve (Cleveland, Ohio, U)</t>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -59710,7 +59710,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/28/26)</t>
+          <t>Hiring AEs? (9/29/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -296,8 +296,8 @@
     <xf numFmtId="1" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/29/26)</t>
+          <t>Hiring AEs? (9/30/26)</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="F167" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Manager (Remote, US (TN/KY))</t>
+          <t>Yes - Account Manager (Remote, US (West))</t>
         </is>
       </c>
     </row>
@@ -6012,9 +6012,9 @@
           <t>Defibrillators, monitors, and EMS software (ePCR, dispatch, billing)</t>
         </is>
       </c>
-      <c r="F172" s="8" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive - TherOx (SS02)  (6 Locations)</t>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 502 for https://zoll.wd5.myworkdayj</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="F209" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 404 for https://pratus.disastertech</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/29/26)</t>
+          <t>Hiring AEs? (9/30/26)</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/29/26)</t>
+          <t>Hiring AEs? (9/30/26)</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>Yes - Junior Account Manager</t>
+          <t>Yes - Account Manager</t>
         </is>
       </c>
     </row>
@@ -14858,9 +14858,9 @@
           <t>VALT video observation and recording software for nursing simulation labs, clinical skills training, courtrooms, and child advocacy centers - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F18" s="69" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F18" s="70" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Regional Representative - Sales only</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/29/26)</t>
+          <t>Hiring AEs? (9/30/26)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/29/26)</t>
+          <t>Hiring AEs? (9/30/26)</t>
         </is>
       </c>
     </row>
@@ -22664,7 +22664,7 @@
       </c>
       <c r="F177" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive I, SMG (US | Massachusetts)</t>
+          <t>Yes - Account Executive, SMG (US | Massachusetts)</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/29/26)</t>
+          <t>Hiring AEs? (9/30/26)</t>
         </is>
       </c>
     </row>
@@ -25086,7 +25086,7 @@
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.revize.com/care</t>
         </is>
       </c>
     </row>
@@ -26842,7 +26842,7 @@
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t>Yes - Account Executive I, SMG (US | Massachusetts)</t>
+          <t>Yes - Account Executive, SMG (US | Massachusetts)</t>
         </is>
       </c>
     </row>
@@ -28636,9 +28636,9 @@
           <t>Aerial imagery and property data analytics for county assessors, GIS, and insurers - exhibited at IAAO 2026</t>
         </is>
       </c>
-      <c r="F139" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -29584,7 +29584,7 @@
       </c>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>Yes - Mid Market Account Executive (Boston, MA)</t>
+          <t>Yes - Enterprise Account Executive - Pub (Georgia)</t>
         </is>
       </c>
     </row>
@@ -29734,7 +29734,7 @@
       </c>
       <c r="F176" s="22" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (United States)</t>
+          <t>Yes - Account Executive (Canada | Remote)</t>
         </is>
       </c>
     </row>
@@ -30532,7 +30532,7 @@
       </c>
       <c r="F203" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (United States)</t>
+          <t>Yes - Account Executive (Canada | Remote)</t>
         </is>
       </c>
     </row>
@@ -31808,7 +31808,7 @@
       </c>
       <c r="F246" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://passportworkforce.c</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -32428,9 +32428,9 @@
           <t>License verification and workforce compliance for agencies and regulators</t>
         </is>
       </c>
-      <c r="F267" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Sales Executive - Central Region ( (Remote - US)</t>
+      <c r="F267" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sr. Customer Success Manager - Gov only</t>
         </is>
       </c>
     </row>
@@ -32816,7 +32816,7 @@
       </c>
       <c r="F280" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - page too small - likely JS-rendered</t>
         </is>
       </c>
     </row>
@@ -38634,7 +38634,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/29/26)</t>
+          <t>Hiring AEs? (9/30/26)</t>
         </is>
       </c>
     </row>
@@ -42916,7 +42916,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/29/26)</t>
+          <t>Hiring AEs? (9/30/26)</t>
         </is>
       </c>
     </row>
@@ -42976,7 +42976,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>Yes - Sales Executive, Cross-Sell (North (Remote Worker - N/)</t>
+          <t>Yes - Sales Executive - Central Region</t>
         </is>
       </c>
     </row>
@@ -43480,7 +43480,7 @@
       </c>
       <c r="F20" s="35" t="inlineStr">
         <is>
-          <t>Yes - Commercial Account Executive - Cen (Dallas, Texas)</t>
+          <t>Yes - Commercial Account Executive - Cen (Denver, Colorado)</t>
         </is>
       </c>
     </row>
@@ -43806,9 +43806,9 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -44190,7 +44190,7 @@
       </c>
       <c r="F44" s="35" t="inlineStr">
         <is>
-          <t>Yes - Sr. Regional Account Manager (Remote USA)</t>
+          <t>Yes - Regional Account Manager- Future O (Remote USA)</t>
         </is>
       </c>
     </row>
@@ -45268,9 +45268,9 @@
           <t>Cloud SIS and LMS for K-12 districts and charter networks</t>
         </is>
       </c>
-      <c r="F80" s="35" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive</t>
+      <c r="F80" s="34" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/29/26)</t>
+          <t>Hiring AEs? (9/30/26)</t>
         </is>
       </c>
     </row>
@@ -47042,7 +47042,7 @@
       </c>
       <c r="F2" s="39" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 502 for https://cubic.wd1.myworkday</t>
+          <t>Yes - Account Manager - East Coast (2 Locations)</t>
         </is>
       </c>
     </row>
@@ -47100,7 +47100,7 @@
           <t>Mobile fare payment app covering 200+ North American agencies</t>
         </is>
       </c>
-      <c r="F4" s="39" t="inlineStr">
+      <c r="F4" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -47160,7 +47160,7 @@
           <t>Automated fare collection plus parking and rail signalling systems (US office Lowell, MA)</t>
         </is>
       </c>
-      <c r="F6" s="39" t="inlineStr">
+      <c r="F6" s="40" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.scheidt-bachman</t>
         </is>
@@ -47220,7 +47220,7 @@
           <t>Account-based ticketing and open-loop EMV fare collection in 150+ cities (BPC Group)</t>
         </is>
       </c>
-      <c r="F8" s="39" t="inlineStr">
+      <c r="F8" s="40" t="inlineStr">
         <is>
           <t>Unknown - board is another company's - not read</t>
         </is>
@@ -47280,7 +47280,7 @@
           <t>KubaPay cloud fare collection and account-based ticketing in 500+ cities (ICM group, not Cubic)</t>
         </is>
       </c>
-      <c r="F10" s="39" t="inlineStr">
+      <c r="F10" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -47340,7 +47340,7 @@
           <t>Automated fare collection and tolling/ITS for US agencies (LA, Bay Area, DC); Samsung SDS lineage</t>
         </is>
       </c>
-      <c r="F12" s="39" t="inlineStr">
+      <c r="F12" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -47398,7 +47398,7 @@
           <t>Fareboxes, validators, and the Universal Platform for automated fare management</t>
         </is>
       </c>
-      <c r="F14" s="39" t="inlineStr">
+      <c r="F14" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -47456,7 +47456,7 @@
           <t>Transit scheduling, fare and paratransit software for public operators</t>
         </is>
       </c>
-      <c r="F16" s="39" t="inlineStr">
+      <c r="F16" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -47516,7 +47516,7 @@
           <t>Tolling operations and back-office payment services for toll agencies</t>
         </is>
       </c>
-      <c r="F18" s="39" t="inlineStr">
+      <c r="F18" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -47546,9 +47546,9 @@
           <t>Check-in/be-out mobile fare payment for public transport authorities</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Sales &amp; Business Development Manag</t>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Head of Strategic Accounts only</t>
         </is>
       </c>
     </row>
@@ -47576,7 +47576,7 @@
           <t>Account-based fare collection and validators for public transit operators</t>
         </is>
       </c>
-      <c r="F20" s="40" t="inlineStr">
+      <c r="F20" s="39" t="inlineStr">
         <is>
           <t>Yes - Senior Enterprise Account Executiv (Spain, Spain)</t>
         </is>
@@ -47636,7 +47636,7 @@
           <t>Bus ITS: CAD/AVL, real-time passenger info, and fleet health</t>
         </is>
       </c>
-      <c r="F22" s="39" t="inlineStr">
+      <c r="F22" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -47696,7 +47696,7 @@
           <t>Real-time transit data: arrival predictions and on-time performance</t>
         </is>
       </c>
-      <c r="F24" s="40" t="inlineStr">
+      <c r="F24" s="39" t="inlineStr">
         <is>
           <t>Yes - Senior Account Manager (United States)</t>
         </is>
@@ -47756,7 +47756,7 @@
           <t>myAvail enterprise transit management ITS and CAD/AVL for mid-size US agencies</t>
         </is>
       </c>
-      <c r="F26" s="39" t="inlineStr">
+      <c r="F26" s="40" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://availtec.com/career</t>
         </is>
@@ -47816,7 +47816,7 @@
           <t>IVU.suite planning, scheduling, dispatch, and ticketing for transit and rail operators</t>
         </is>
       </c>
-      <c r="F28" s="39" t="inlineStr">
+      <c r="F28" s="40" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.ivu.com/career</t>
         </is>
@@ -47876,7 +47876,7 @@
           <t>Transit dispatch, CAD/AVL, and communications software (Modaxo brand, ex-Trapeze ITS)</t>
         </is>
       </c>
-      <c r="F30" s="39" t="inlineStr">
+      <c r="F30" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -47936,7 +47936,7 @@
           <t>Consat Telematics real-time CAD/AVL, passenger info, and electromobility analytics (NA office Sudbury ON)</t>
         </is>
       </c>
-      <c r="F32" s="39" t="inlineStr">
+      <c r="F32" s="40" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.consat.com/care</t>
         </is>
@@ -47996,7 +47996,7 @@
           <t>Transit performance data warehousing, BI, and automated NTD reporting (Modaxo brand) - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F34" s="39" t="inlineStr">
+      <c r="F34" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -48050,7 +48050,7 @@
           <t>Cloud CAD/AVL and in-vehicle tech for transit agencies and campus systems (SDVOSB)</t>
         </is>
       </c>
-      <c r="F36" s="39" t="inlineStr">
+      <c r="F36" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48110,7 +48110,7 @@
           <t>IBM Maximo consulting plus Mobile Informer EAM for transit agencies, airports, and utilities</t>
         </is>
       </c>
-      <c r="F38" s="39" t="inlineStr">
+      <c r="F38" s="40" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.interlocsolutio</t>
         </is>
@@ -48142,7 +48142,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -48170,7 +48170,7 @@
           <t>Trainwise onboard train control/monitoring and Fleetwise wayside fleet management for transit</t>
         </is>
       </c>
-      <c r="F40" s="39" t="inlineStr">
+      <c r="F40" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48230,7 +48230,7 @@
           <t>Rail terminal management, track inspection, and crew compliance for short lines and commuter rail</t>
         </is>
       </c>
-      <c r="F42" s="39" t="inlineStr">
+      <c r="F42" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48290,7 +48290,7 @@
           <t>Ultra-wideband train positioning, worker protection, and ATP for transit agencies (NYC MTA)</t>
         </is>
       </c>
-      <c r="F44" s="39" t="inlineStr">
+      <c r="F44" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48350,7 +48350,7 @@
           <t>CylusOne rail OT cybersecurity: threat detection for signaling, trackside, and onboard networks</t>
         </is>
       </c>
-      <c r="F46" s="39" t="inlineStr">
+      <c r="F46" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48408,7 +48408,7 @@
           <t>ConnX Maestro unified communications and contact center for transit agencies (SEPTA)</t>
         </is>
       </c>
-      <c r="F48" s="39" t="inlineStr">
+      <c r="F48" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48466,7 +48466,7 @@
           <t>Non-invasive sensors and cloud analytics for elevator, escalator, and HVAC uptime in transit stations</t>
         </is>
       </c>
-      <c r="F50" s="39" t="inlineStr">
+      <c r="F50" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48524,7 +48524,7 @@
           <t>Virtual Optical Fiber high-speed data offload between transit vehicles and depots</t>
         </is>
       </c>
-      <c r="F52" s="39" t="inlineStr">
+      <c r="F52" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48584,7 +48584,7 @@
           <t>AI smart inspection for rail infrastructure: sensor robot plus defect detection and predictive maintenance</t>
         </is>
       </c>
-      <c r="F54" s="39" t="inlineStr">
+      <c r="F54" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48640,7 +48640,7 @@
           <t>Mobile video surveillance, DVRs, and MotoTrax analytics for transit, school, and municipal fleets - exhibited at CTAA EXPO 2026, NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F56" s="40" t="inlineStr">
+      <c r="F56" s="39" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -48700,7 +48700,7 @@
           <t>Onboard transit systems: Horizon CCTV, NetSpire passenger info, iConnex real-time (US in Buffalo NY)</t>
         </is>
       </c>
-      <c r="F58" s="39" t="inlineStr">
+      <c r="F58" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48760,7 +48760,7 @@
           <t>Intelligent video, AI stop-arm analytics, and cloud safety platforms for transit and school districts - exhibited at CTAA EXPO 2026, NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F60" s="39" t="inlineStr">
+      <c r="F60" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48820,7 +48820,7 @@
           <t>AI dashcams, MDVRs, and fleet video telematics for transit, school bus, and commercial fleets (US: Houston)</t>
         </is>
       </c>
-      <c r="F62" s="39" t="inlineStr">
+      <c r="F62" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -48880,7 +48880,7 @@
           <t>3D AI people-flow sensors for passenger counting, queue, and dwell in transit hubs and airports</t>
         </is>
       </c>
-      <c r="F64" s="39" t="inlineStr">
+      <c r="F64" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -48940,7 +48940,7 @@
           <t>Automatic passenger counting hardware and analysis software for bus, rail, and paratransit</t>
         </is>
       </c>
-      <c r="F66" s="39" t="inlineStr">
+      <c r="F66" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -49000,7 +49000,7 @@
           <t>Video telematics and driver safety for municipal and transit fleets - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
-      <c r="F68" s="39" t="inlineStr">
+      <c r="F68" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49060,7 +49060,7 @@
           <t>Telematics devices and fleet tracking software for public fleets</t>
         </is>
       </c>
-      <c r="F70" s="39" t="inlineStr">
+      <c r="F70" s="40" t="inlineStr">
         <is>
           <t>Unknown - no jobs parsed from iCIMS portal</t>
         </is>
@@ -49120,7 +49120,7 @@
           <t>FleetWave fleet asset management for public sector fleets</t>
         </is>
       </c>
-      <c r="F72" s="39" t="inlineStr">
+      <c r="F72" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49180,7 +49180,7 @@
           <t>FleetCommander motor pool and vehicle sharing for agencies</t>
         </is>
       </c>
-      <c r="F74" s="39" t="inlineStr">
+      <c r="F74" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -49240,7 +49240,7 @@
           <t>Fleet data analytics and benchmarking for public and utility fleets</t>
         </is>
       </c>
-      <c r="F76" s="39" t="inlineStr">
+      <c r="F76" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -49300,7 +49300,7 @@
           <t>Fleet automation and motor pool platform for public agencies</t>
         </is>
       </c>
-      <c r="F78" s="39" t="inlineStr">
+      <c r="F78" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49360,7 +49360,7 @@
           <t>Onboard surveillance and video management for transit fleets</t>
         </is>
       </c>
-      <c r="F80" s="39" t="inlineStr">
+      <c r="F80" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -49480,7 +49480,7 @@
           <t>On-demand transit and shared mobility software for public agencies</t>
         </is>
       </c>
-      <c r="F84" s="39" t="inlineStr">
+      <c r="F84" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -49540,7 +49540,7 @@
           <t>Parking meters, kiosks and transit fare systems for cities</t>
         </is>
       </c>
-      <c r="F86" s="39" t="inlineStr">
+      <c r="F86" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49600,7 +49600,7 @@
           <t>Mobile parking payments for city and municipal parking operators</t>
         </is>
       </c>
-      <c r="F88" s="40" t="inlineStr">
+      <c r="F88" s="39" t="inlineStr">
         <is>
           <t>Yes - Corporate Sales Executive</t>
         </is>
@@ -49660,7 +49660,7 @@
           <t>Parking access and revenue control systems for public garages</t>
         </is>
       </c>
-      <c r="F90" s="39" t="inlineStr">
+      <c r="F90" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49720,7 +49720,7 @@
           <t>Automated enforcement: school-zone speed, red-light, and bus-lane cameras - exhibited at North Carolina Sheriffs' Association 2026</t>
         </is>
       </c>
-      <c r="F92" s="40" t="inlineStr">
+      <c r="F92" s="39" t="inlineStr">
         <is>
           <t>Yes - Mass Market Account Executive (California_Remote)</t>
         </is>
@@ -49780,7 +49780,7 @@
           <t>Multimodal trip planning app plus a paid agency suite (white-label apps, sponsored Royale, rider data) - exhibited at CTAA EXPO 2026, NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F94" s="39" t="inlineStr">
+      <c r="F94" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -49840,7 +49840,7 @@
           <t>ePaper Digital Bus Stop, SmartStop kiosks, and CPAM content management for transit agencies</t>
         </is>
       </c>
-      <c r="F96" s="39" t="inlineStr">
+      <c r="F96" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -49960,7 +49960,7 @@
           <t>Bus destination displays, controllers, and next-stop passenger information systems</t>
         </is>
       </c>
-      <c r="F100" s="39" t="inlineStr">
+      <c r="F100" s="40" t="inlineStr">
         <is>
           <t>Unknown - HTTP 202 for https://www.hanoverdisplays</t>
         </is>
@@ -50018,7 +50018,7 @@
           <t>TRACC travel-time and accessibility analysis plus transport datasets for government transport agencies</t>
         </is>
       </c>
-      <c r="F102" s="39" t="inlineStr">
+      <c r="F102" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50078,7 +50078,7 @@
           <t>Solar smart bus stops with edge AI plus the ORA platform: signage, lane enforcement, passenger counting</t>
         </is>
       </c>
-      <c r="F104" s="39" t="inlineStr">
+      <c r="F104" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50138,7 +50138,7 @@
           <t>Real-time transit display screens and rider information for agencies and cities</t>
         </is>
       </c>
-      <c r="F106" s="39" t="inlineStr">
+      <c r="F106" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50198,7 +50198,7 @@
           <t>Elevated automated transit pods on prefabricated guideways (ex-skyTran team) for cities and campuses</t>
         </is>
       </c>
-      <c r="F108" s="39" t="inlineStr">
+      <c r="F108" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50258,7 +50258,7 @@
           <t>On-demand microtransit software with rider/driver apps and AI dispatch for large agencies - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F110" s="40" t="inlineStr">
+      <c r="F110" s="39" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -50318,7 +50318,7 @@
           <t>Assisted-mobility platform and driver network delivering ADA paratransit and door-through-door trips - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F112" s="39" t="inlineStr">
+      <c r="F112" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50378,7 +50378,7 @@
           <t>Transit management software for paratransit, demand-response, microtransit, and taxi fleets - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F114" s="39" t="inlineStr">
+      <c r="F114" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50438,7 +50438,7 @@
           <t>Autonomous vehicle technology and driverless shuttle service for transit agencies and cities</t>
         </is>
       </c>
-      <c r="F116" s="39" t="inlineStr">
+      <c r="F116" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -50498,7 +50498,7 @@
           <t>flowride.ai SAE Level-4 automated driving software retrofitted onto full-size electric transit buses</t>
         </is>
       </c>
-      <c r="F118" s="39" t="inlineStr">
+      <c r="F118" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50558,7 +50558,7 @@
           <t>Assisted senior and accessible transportation platform serving agency paratransit overflow in 35+ metros</t>
         </is>
       </c>
-      <c r="F120" s="39" t="inlineStr">
+      <c r="F120" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50618,7 +50618,7 @@
           <t>White-label multimodal TDM and commute platform for regional agencies, employers, and campuses</t>
         </is>
       </c>
-      <c r="F122" s="39" t="inlineStr">
+      <c r="F122" s="40" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://www.rideshark.com/c</t>
         </is>
@@ -50670,7 +50670,7 @@
           <t>TripMaster paratransit scheduling and dispatch software for public transit providers</t>
         </is>
       </c>
-      <c r="F124" s="39" t="inlineStr">
+      <c r="F124" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50728,7 +50728,7 @@
           <t>Demand-responsive transit dispatch and booking software for transit agencies - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F126" s="39" t="inlineStr">
+      <c r="F126" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50788,7 +50788,7 @@
           <t>Electric on-demand shuttle service contracted by cities and transit agencies - exhibited at WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F128" s="39" t="inlineStr">
+      <c r="F128" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -50848,7 +50848,7 @@
           <t>On-demand ridepooling and mobility analytics software for public transit authorities</t>
         </is>
       </c>
-      <c r="F130" s="39" t="inlineStr">
+      <c r="F130" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -50908,7 +50908,7 @@
           <t>Ridepooling operations and autonomous shuttle services for public transport partners</t>
         </is>
       </c>
-      <c r="F132" s="39" t="inlineStr">
+      <c r="F132" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -50960,7 +50960,7 @@
           <t>ADA paratransit eligibility, call center and mobility management technology for agencies</t>
         </is>
       </c>
-      <c r="F134" s="39" t="inlineStr">
+      <c r="F134" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51020,7 +51020,7 @@
           <t>Whoosh autonomous cable-driven transit pods for cities and campuses</t>
         </is>
       </c>
-      <c r="F136" s="39" t="inlineStr">
+      <c r="F136" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51080,7 +51080,7 @@
           <t>Autonomous shuttle vehicles for public transport and campus deployments</t>
         </is>
       </c>
-      <c r="F138" s="39" t="inlineStr">
+      <c r="F138" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51140,7 +51140,7 @@
           <t>Electric and autonomous buses sold to public transit operators worldwide</t>
         </is>
       </c>
-      <c r="F140" s="39" t="inlineStr">
+      <c r="F140" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51200,7 +51200,7 @@
           <t>Automated people mover and group rapid transit systems for public authorities</t>
         </is>
       </c>
-      <c r="F142" s="39" t="inlineStr">
+      <c r="F142" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -51260,7 +51260,7 @@
           <t>Autonomy software powering driverless shuttles for transit and airport operators</t>
         </is>
       </c>
-      <c r="F144" s="39" t="inlineStr">
+      <c r="F144" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -51320,7 +51320,7 @@
           <t>Autonomous shuttles for public transport agencies, airports and campuses</t>
         </is>
       </c>
-      <c r="F146" s="39" t="inlineStr">
+      <c r="F146" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51380,7 +51380,7 @@
           <t>Leading mobile parking payments app (EasyPark Group)</t>
         </is>
       </c>
-      <c r="F148" s="39" t="inlineStr">
+      <c r="F148" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -51440,7 +51440,7 @@
           <t>Computer vision curb management and automated loading-zone payments</t>
         </is>
       </c>
-      <c r="F150" s="39" t="inlineStr">
+      <c r="F150" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -51500,7 +51500,7 @@
           <t>Gateless LPR parking operations (GLIDEPARCS) for private lots, universities, and some municipalities</t>
         </is>
       </c>
-      <c r="F152" s="39" t="inlineStr">
+      <c r="F152" s="40" t="inlineStr">
         <is>
           <t>Unknown - page too small - likely JS-rendered</t>
         </is>
@@ -51560,7 +51560,7 @@
           <t>Towing lifecycle software for city towing programs and impound management (ex-AutoReturn + TSD)</t>
         </is>
       </c>
-      <c r="F154" s="39" t="inlineStr">
+      <c r="F154" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -51620,7 +51620,7 @@
           <t>Sentry solar smart kiosks and vision-based automated parking enforcement</t>
         </is>
       </c>
-      <c r="F156" s="39" t="inlineStr">
+      <c r="F156" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51680,7 +51680,7 @@
           <t>Single-space smart parking meters and pay stations for municipalities</t>
         </is>
       </c>
-      <c r="F158" s="39" t="inlineStr">
+      <c r="F158" s="40" t="inlineStr">
         <is>
           <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
@@ -51740,7 +51740,7 @@
           <t>Wireless parking occupancy sensors for city and campus parking</t>
         </is>
       </c>
-      <c r="F160" s="39" t="inlineStr">
+      <c r="F160" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51800,7 +51800,7 @@
           <t>Smart parking sensors and LoRaWAN networks for cities</t>
         </is>
       </c>
-      <c r="F162" s="39" t="inlineStr">
+      <c r="F162" s="40" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -51860,7 +51860,7 @@
           <t>Parking payments, permits and enforcement software for municipalities</t>
         </is>
       </c>
-      <c r="F164" s="39" t="inlineStr">
+      <c r="F164" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51920,7 +51920,7 @@
           <t>Parking citation processing and permit services for California cities</t>
         </is>
       </c>
-      <c r="F166" s="39" t="inlineStr">
+      <c r="F166" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -51980,7 +51980,7 @@
           <t>Parking citation, permit and enforcement management software for agencies</t>
         </is>
       </c>
-      <c r="F168" s="39" t="inlineStr">
+      <c r="F168" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52036,7 +52036,7 @@
           <t>Control room video wall visualization software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F170" s="39" t="inlineStr">
+      <c r="F170" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -52088,7 +52088,7 @@
           <t>Transit fare collection and ticketing software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F172" s="39" t="inlineStr">
+      <c r="F172" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52136,7 +52136,7 @@
           <t>Infrastructure engineering and asset software - exhibited at APTA 2026, AWWA ACE 2026</t>
         </is>
       </c>
-      <c r="F174" s="39" t="inlineStr">
+      <c r="F174" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52188,7 +52188,7 @@
           <t>Fuel and fleet management systems - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F176" s="39" t="inlineStr">
+      <c r="F176" s="40" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -52238,7 +52238,7 @@
           <t>AI predictive fleet analytics platform - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F178" s="39" t="inlineStr">
+      <c r="F178" s="40" t="inlineStr">
         <is>
           <t>Unknown - HTTP 403 for https://www.intangles.ai/ca</t>
         </is>
@@ -52292,7 +52292,7 @@
           <t>Security and intelligence analytics software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F180" s="40" t="inlineStr">
+      <c r="F180" s="39" t="inlineStr">
         <is>
           <t>Yes - Enterprise Sales Executive – New L (2 Locations)</t>
         </is>
@@ -52340,7 +52340,7 @@
           <t>Smart EV charging management software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F182" s="39" t="inlineStr">
+      <c r="F182" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52388,7 +52388,7 @@
           <t>Transit operations software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F184" s="39" t="inlineStr">
+      <c r="F184" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52438,7 +52438,7 @@
           <t>Rail/transit software, AI and asset monitoring - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F186" s="39" t="inlineStr">
+      <c r="F186" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52486,7 +52486,7 @@
           <t>GPS fleet tracking and telematics software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F188" s="40" t="inlineStr">
+      <c r="F188" s="39" t="inlineStr">
         <is>
           <t>Yes - Sales Account Executive – Mid-Mark</t>
         </is>
@@ -52540,7 +52540,7 @@
           <t>On-demand mobility platform for agency partnerships - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F190" s="39" t="inlineStr">
+      <c r="F190" s="40" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -52628,7 +52628,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/29/26)</t>
+          <t>Hiring AEs? (9/30/26)</t>
         </is>
       </c>
     </row>
@@ -54126,9 +54126,9 @@
           <t>Grid software, ADMS and transmission equipment for public and investor utilities</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -56186,7 +56186,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/29/26)</t>
+          <t>Hiring AEs? (9/30/26)</t>
         </is>
       </c>
     </row>
@@ -56598,7 +56598,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -57822,7 +57822,7 @@
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.elenium.com/car</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -58572,7 +58572,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (C1 - (New York, New York)</t>
+          <t>Yes - Enterprise Account Executive (C1 - (Austin, TX, United)</t>
         </is>
       </c>
     </row>
@@ -59048,9 +59048,9 @@
           <t>Computer-vision checkout-free parking payment platform (drive-in/drive-out billing) plus parking operations and revenue management for airports; owner of SP+.</t>
         </is>
       </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Associate Account Executive (Cleve (Cleveland, Ohio, U)</t>
         </is>
       </c>
     </row>
@@ -59710,7 +59710,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/29/26)</t>
+          <t>Hiring AEs? (9/30/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -286,9 +286,9 @@
     <xf numFmtId="1" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/30/26)</t>
+          <t>Hiring AEs? (10/1/26)</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.365labs.com/car</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="F167" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Manager (Remote, US (West))</t>
+          <t>Yes - Account Manager (Remote, US (TN/KY))</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Director, Customer Solutions Engin only</t>
+          <t>Sales (non-AE) - Join our Go-To-Market Talent Commu only</t>
         </is>
       </c>
     </row>
@@ -5982,9 +5982,9 @@
           <t>Assistive AI for 911 centers: transcription, translation, text-to-911, and video</t>
         </is>
       </c>
-      <c r="F171" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -6012,9 +6012,9 @@
           <t>Defibrillators, monitors, and EMS software (ePCR, dispatch, billing)</t>
         </is>
       </c>
-      <c r="F172" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - HTTP 502 for https://zoll.wd5.myworkdayj</t>
+      <c r="F172" s="8" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive - TherOx (SS02)  (6 Locations)</t>
         </is>
       </c>
     </row>
@@ -8786,9 +8786,9 @@
           <t>Community corrections supervision and electronic monitoring for courts</t>
         </is>
       </c>
-      <c r="F265" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F265" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Regional Sales Manager - Southwest (remote, remote, US)</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/30/26)</t>
+          <t>Hiring AEs? (10/1/26)</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="F14" s="64" t="inlineStr">
         <is>
-          <t>Yes - Strategic Account Executive, Marke (Remote – United St)</t>
+          <t>Yes - Commercial Account Executive, Truv (Remote – United St)</t>
         </is>
       </c>
     </row>
@@ -12718,9 +12718,9 @@
           <t>Digital substance use disorder prevention, intervention, and recovery support platform for treatment providers, state and county health agencies, drug courts, and Medicaid plans - exhibited at NatCon 2026, NACCHO 360 2026</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Senior Customer Success Consultant only</t>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -12856,9 +12856,9 @@
           <t>Crisis response, closed-loop referral, care management, and bed board software for behavioral health agencies - exhibited at NatCon 2026</t>
         </is>
       </c>
-      <c r="F64" s="65" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - VP of Customer Success only</t>
+      <c r="F64" s="64" t="inlineStr">
+        <is>
+          <t>Yes - Senior Sales Account Executive (Long Beach (Hybrid)</t>
         </is>
       </c>
     </row>
@@ -12934,9 +12934,9 @@
           <t>Human services EHR and care coordination software for behavioral health, residential, vocational rehab, and food assistance providers - exhibited at NatCon 2026</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Customer Success Manager only</t>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Senior Account Executive (Remote)</t>
         </is>
       </c>
     </row>
@@ -13654,7 +13654,7 @@
       </c>
       <c r="F94" s="63" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 504 for https://eccovia.com/careers</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/30/26)</t>
+          <t>Hiring AEs? (10/1/26)</t>
         </is>
       </c>
     </row>
@@ -14828,9 +14828,9 @@
           <t>Peer review, group work, and AI feedback tools that plug into university learning management systems - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive (Texas) (US Remote)</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/30/26)</t>
+          <t>Hiring AEs? (10/1/26)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/30/26)</t>
+          <t>Hiring AEs? (10/1/26)</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - page too small - likely JS-rendered</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/30/26)</t>
+          <t>Hiring AEs? (10/1/26)</t>
         </is>
       </c>
     </row>
@@ -24846,7 +24846,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://zencity.io/careers</t>
+          <t>Unknown - HTTP 403 for https://zencity.io/careers</t>
         </is>
       </c>
     </row>
@@ -26332,7 +26332,7 @@
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t>Yes - Outbound Sales Representative-iWor</t>
+          <t>Yes - Account Executive - GovTech Softwa</t>
         </is>
       </c>
     </row>
@@ -28636,9 +28636,9 @@
           <t>Aerial imagery and property data analytics for county assessors, GIS, and insurers - exhibited at IAAO 2026</t>
         </is>
       </c>
-      <c r="F139" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F139" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -32428,9 +32428,9 @@
           <t>License verification and workforce compliance for agencies and regulators</t>
         </is>
       </c>
-      <c r="F267" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Sr. Customer Success Manager - Gov only</t>
+      <c r="F267" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -32816,7 +32816,7 @@
       </c>
       <c r="F280" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page too small - likely JS-rendered</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -33814,9 +33814,9 @@
           <t>Policy and rulemaking workflow: draft, route, approve, and track regulations for agencies</t>
         </is>
       </c>
-      <c r="F315" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Strategic Account Executive - West (Remote)</t>
+      <c r="F315" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Customer Success Lead only</t>
         </is>
       </c>
     </row>
@@ -38634,7 +38634,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/30/26)</t>
+          <t>Hiring AEs? (10/1/26)</t>
         </is>
       </c>
     </row>
@@ -42916,7 +42916,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/30/26)</t>
+          <t>Hiring AEs? (10/1/26)</t>
         </is>
       </c>
     </row>
@@ -42946,7 +42946,7 @@
       </c>
       <c r="F2" s="33" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Director, GTM Finance only</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -42976,7 +42976,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>Yes - Sales Executive - Central Region</t>
+          <t>Yes - Sales Executive - Pacific Northwes (Remote Worker - N/)</t>
         </is>
       </c>
     </row>
@@ -43004,7 +43004,7 @@
           <t>AI gun detection layered onto existing school security cameras</t>
         </is>
       </c>
-      <c r="F4" s="34" t="inlineStr">
+      <c r="F4" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -43064,7 +43064,7 @@
           <t>Monitors school email/docs for self-harm and threat signals - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F6" s="34" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -43096,7 +43096,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - New Business Executive - Strategic only</t>
+          <t>Sales (non-AE) - Customer Success Manager - Mid Mar only</t>
         </is>
       </c>
     </row>
@@ -43124,7 +43124,7 @@
           <t>Cloud web filtering and student safety monitoring - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F8" s="35" t="inlineStr">
+      <c r="F8" s="34" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Large/Enterpris (United States of A)</t>
         </is>
@@ -43184,7 +43184,7 @@
           <t>Web filtering and student safety monitoring for school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F10" s="35" t="inlineStr">
+      <c r="F10" s="34" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Austin, Texas, Uni)</t>
         </is>
@@ -43244,7 +43244,7 @@
           <t>Student wellbeing, filtering and safety monitoring for school districts</t>
         </is>
       </c>
-      <c r="F12" s="34" t="inlineStr">
+      <c r="F12" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -43304,7 +43304,7 @@
           <t>AI web filtering and student threat detection for K-12 districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F14" s="33" t="inlineStr">
+      <c r="F14" s="35" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -43362,7 +43362,7 @@
           <t>Real-time AI content filtering and self-harm detection for schools - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F16" s="34" t="inlineStr">
+      <c r="F16" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -43420,7 +43420,7 @@
           <t>Mass notification and emergency response app for schools and campuses</t>
         </is>
       </c>
-      <c r="F18" s="34" t="inlineStr">
+      <c r="F18" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -43478,7 +43478,7 @@
           <t>Cloud video security and sensors for schools and public agencies</t>
         </is>
       </c>
-      <c r="F20" s="35" t="inlineStr">
+      <c r="F20" s="34" t="inlineStr">
         <is>
           <t>Yes - Commercial Account Executive - Cen (Denver, Colorado)</t>
         </is>
@@ -43538,7 +43538,7 @@
           <t>AI gun detection and emergency notification for schools and campuses</t>
         </is>
       </c>
-      <c r="F22" s="34" t="inlineStr">
+      <c r="F22" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -43598,7 +43598,7 @@
           <t>Computer vision threat and weapon detection for schools and public facilities</t>
         </is>
       </c>
-      <c r="F24" s="34" t="inlineStr">
+      <c r="F24" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -43658,7 +43658,7 @@
           <t>AI-based weapons screening gateways for schools, venues and public buildings</t>
         </is>
       </c>
-      <c r="F26" s="35" t="inlineStr">
+      <c r="F26" s="34" t="inlineStr">
         <is>
           <t>Yes - Regional Sales Manager (Boston, Massachuse)</t>
         </is>
@@ -43718,7 +43718,7 @@
           <t>Anonymous reporting and crisis support platform for K-12 schools</t>
         </is>
       </c>
-      <c r="F28" s="34" t="inlineStr">
+      <c r="F28" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -43776,7 +43776,7 @@
           <t>Visitor screening and sex-offender check kiosks for schools</t>
         </is>
       </c>
-      <c r="F30" s="34" t="inlineStr">
+      <c r="F30" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -43836,7 +43836,7 @@
           <t>Emergency mass notification hardware and software for schools and agencies - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F32" s="35" t="inlineStr">
+      <c r="F32" s="34" t="inlineStr">
         <is>
           <t>Yes - Regional Account Manager - Educati (Baltimore, MD)</t>
         </is>
@@ -43894,7 +43894,7 @@
           <t>FlySense vape and bullying sensors for school bathrooms and hallways</t>
         </is>
       </c>
-      <c r="F34" s="34" t="inlineStr">
+      <c r="F34" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -43952,7 +43952,7 @@
           <t>Multi-sensor vape, gunshot and aggression detection for schools</t>
         </is>
       </c>
-      <c r="F36" s="34" t="inlineStr">
+      <c r="F36" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -44012,7 +44012,7 @@
           <t>Cloud security, content filtering, and student safety monitoring for Google Workspace and Microsoft 365 in K-12 districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F38" s="34" t="inlineStr">
+      <c r="F38" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -44072,7 +44072,7 @@
           <t>Gamified phishing simulation and security awareness training built only for K-12 districts, staff and students - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F40" s="34" t="inlineStr">
+      <c r="F40" s="33" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -44128,7 +44128,7 @@
           <t>Web filtering, classroom management, self-harm and threat detection and parent engagement software for K-12 school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F42" s="34" t="inlineStr">
+      <c r="F42" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -44188,7 +44188,7 @@
           <t>Vetted small-vehicle student rides supplementing district bus fleets - exhibited at NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F44" s="35" t="inlineStr">
+      <c r="F44" s="34" t="inlineStr">
         <is>
           <t>Yes - Regional Account Manager- Future O (Remote USA)</t>
         </is>
@@ -44248,7 +44248,7 @@
           <t>Longtime standard for school bus routing and planning software</t>
         </is>
       </c>
-      <c r="F46" s="35" t="inlineStr">
+      <c r="F46" s="34" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -44308,7 +44308,7 @@
           <t>Student transportation routing and fleet software for districts - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F48" s="34" t="inlineStr">
+      <c r="F48" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -44368,7 +44368,7 @@
           <t>School bus operations, driver pay and dispatch software for districts</t>
         </is>
       </c>
-      <c r="F50" s="34" t="inlineStr">
+      <c r="F50" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -44428,7 +44428,7 @@
           <t>School bus tracking and communication app sold to districts</t>
         </is>
       </c>
-      <c r="F52" s="34" t="inlineStr">
+      <c r="F52" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -44488,7 +44488,7 @@
           <t>Contracted school bus transportation services for K-12 districts - exhibited at NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F54" s="34" t="inlineStr">
+      <c r="F54" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -44548,7 +44548,7 @@
           <t>Contracted school bus transportation for K-12 districts nationwide</t>
         </is>
       </c>
-      <c r="F56" s="34" t="inlineStr">
+      <c r="F56" s="33" t="inlineStr">
         <is>
           <t>Unknown - network error: Exceeded 30 redirects.</t>
         </is>
@@ -44608,7 +44608,7 @@
           <t>Bus video, audio and fleet electronics for school districts</t>
         </is>
       </c>
-      <c r="F58" s="34" t="inlineStr">
+      <c r="F58" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -44668,7 +44668,7 @@
           <t>School buses and electric Jouley buses for K-12 districts - exhibited at NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F60" s="34" t="inlineStr">
+      <c r="F60" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -44728,7 +44728,7 @@
           <t>All-electric school buses and trucks for school districts</t>
         </is>
       </c>
-      <c r="F62" s="34" t="inlineStr">
+      <c r="F62" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -44788,7 +44788,7 @@
           <t>Electric school bus fleet-as-a-service subscriptions for districts</t>
         </is>
       </c>
-      <c r="F64" s="34" t="inlineStr">
+      <c r="F64" s="33" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -44848,7 +44848,7 @@
           <t>Student information system giant plus enrollment, comms, and analytics - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F66" s="34" t="inlineStr">
+      <c r="F66" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -44908,7 +44908,7 @@
           <t>K-12 HR, absence and substitute management, and operations software</t>
         </is>
       </c>
-      <c r="F68" s="34" t="inlineStr">
+      <c r="F68" s="33" t="inlineStr">
         <is>
           <t>Unknown - HTTP 403 for https://careers.frontlineed</t>
         </is>
@@ -44968,7 +44968,7 @@
           <t>Thrillshare K-12 communications: district websites, apps, notifications, branding - exhibited at NLC City Summit 2026, CoSN 2026</t>
         </is>
       </c>
-      <c r="F70" s="34" t="inlineStr">
+      <c r="F70" s="33" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://api.lever.co/v0/pos</t>
         </is>
@@ -45028,7 +45028,7 @@
           <t>Digital flyer distribution and parent communication for K-12 districts</t>
         </is>
       </c>
-      <c r="F72" s="34" t="inlineStr">
+      <c r="F72" s="33" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://app.trinethire.com/</t>
         </is>
@@ -45088,7 +45088,7 @@
           <t>Student information system and school business/ERP suite for K-12 districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F74" s="33" t="inlineStr">
+      <c r="F74" s="35" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Technical Special only</t>
         </is>
@@ -45148,7 +45148,7 @@
           <t>SIS, ERP and gradebook for K-12 districts and state agencies</t>
         </is>
       </c>
-      <c r="F76" s="34" t="inlineStr">
+      <c r="F76" s="33" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -45208,7 +45208,7 @@
           <t>Genesis SIS and parent portal for New Jersey-area public districts</t>
         </is>
       </c>
-      <c r="F78" s="34" t="inlineStr">
+      <c r="F78" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -45268,7 +45268,7 @@
           <t>Cloud SIS and LMS for K-12 districts and charter networks</t>
         </is>
       </c>
-      <c r="F80" s="34" t="inlineStr">
+      <c r="F80" s="33" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -45298,9 +45298,9 @@
           <t>K-12 ERP, nutrition, payments and forms platform for districts</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Solutions Consultant only</t>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive (Austin, Texas)</t>
         </is>
       </c>
     </row>
@@ -45328,7 +45328,7 @@
           <t>K-12 finance, HR and payroll ERP for California school agencies</t>
         </is>
       </c>
-      <c r="F82" s="34" t="inlineStr">
+      <c r="F82" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -45388,7 +45388,7 @@
           <t>School nutrition, inventory and POS software for districts and states</t>
         </is>
       </c>
-      <c r="F84" s="34" t="inlineStr">
+      <c r="F84" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -45446,7 +45446,7 @@
           <t>School bus routing, fleet and student transportation software for districts</t>
         </is>
       </c>
-      <c r="F86" s="35" t="inlineStr">
+      <c r="F86" s="34" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -45506,7 +45506,7 @@
           <t>Enrollment, school choice and behavior management for public districts</t>
         </is>
       </c>
-      <c r="F88" s="34" t="inlineStr">
+      <c r="F88" s="33" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -45566,7 +45566,7 @@
           <t>Website, CMS and mass communications platform for school districts</t>
         </is>
       </c>
-      <c r="F90" s="33" t="inlineStr">
+      <c r="F90" s="35" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -45626,7 +45626,7 @@
           <t>Family engagement, attendance and communications platform for districts</t>
         </is>
       </c>
-      <c r="F92" s="35" t="inlineStr">
+      <c r="F92" s="34" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Future Opportun (Remote)</t>
         </is>
@@ -45686,7 +45686,7 @@
           <t>Absence, substitute placement and time tracking for school districts</t>
         </is>
       </c>
-      <c r="F94" s="35" t="inlineStr">
+      <c r="F94" s="34" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Remote Worker - N/)</t>
         </is>
@@ -45746,7 +45746,7 @@
           <t>K-12 hiring, applicant tracking and talent matching for districts</t>
         </is>
       </c>
-      <c r="F96" s="33" t="inlineStr">
+      <c r="F96" s="35" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -45806,7 +45806,7 @@
           <t>Facility use request and scheduling software for K-12 districts</t>
         </is>
       </c>
-      <c r="F98" s="34" t="inlineStr">
+      <c r="F98" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -45866,7 +45866,7 @@
           <t>School safety, threat assessment and preparedness software for districts</t>
         </is>
       </c>
-      <c r="F100" s="34" t="inlineStr">
+      <c r="F100" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -45926,7 +45926,7 @@
           <t>District identity, rostering and application access platform for K-12 - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F102" s="34" t="inlineStr">
+      <c r="F102" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -45984,7 +45984,7 @@
           <t>Cafeteria point-of-sale, free and reduced meal eligibility, and claims reporting software for K-12 school nutrition programs - exhibited at SNA ANC 2027</t>
         </is>
       </c>
-      <c r="F104" s="34" t="inlineStr">
+      <c r="F104" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -46036,7 +46036,7 @@
           <t>Chromebook checkout, device inventory, and student login security for K-12 districts running Google Workspace - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F106" s="34" t="inlineStr">
+      <c r="F106" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -46092,7 +46092,7 @@
           <t>AI point-of-sale and dining operations software for K-12 school nutrition programs and campus dining - exhibited at SNA ANC 2027</t>
         </is>
       </c>
-      <c r="F108" s="34" t="inlineStr">
+      <c r="F108" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -46150,7 +46150,7 @@
           <t>Data warehouse and analytics platform that unifies SIS, LMS, assessment, and attendance data for K-12 schools and districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F110" s="34" t="inlineStr">
+      <c r="F110" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -46206,9 +46206,9 @@
           <t>Library, technology asset, and facilities management software for K-12 school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F112" s="34" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F112" s="35" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Inside Sales Account Executive only</t>
         </is>
       </c>
     </row>
@@ -46264,7 +46264,7 @@
           <t>Classroom communication and engagement app connecting K-12 teachers, students, and families - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F114" s="33" t="inlineStr">
+      <c r="F114" s="35" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Revenue Product Lead only</t>
         </is>
@@ -46314,7 +46314,7 @@
           <t>AI browser extension that generates lesson plans, quizzes, and student feedback inside Google Workspace and LMS tools for teachers and school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F116" s="35" t="inlineStr">
+      <c r="F116" s="34" t="inlineStr">
         <is>
           <t>Yes - Mid-Market Account Executive (Remote)</t>
         </is>
@@ -46372,7 +46372,7 @@
           <t>Behavior referral and discipline management software plus a student dismissal board for K-12 school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F118" s="34" t="inlineStr">
+      <c r="F118" s="33" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -46426,7 +46426,7 @@
           <t>IT help desk ticketing, device asset management and facilities service software built for K-12 school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F120" s="34" t="inlineStr">
+      <c r="F120" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -46480,7 +46480,7 @@
           <t>Free keyboarding, digital citizenship and AI literacy curriculum for K-12 schools, with a paid ad-free district edition - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F122" s="34" t="inlineStr">
+      <c r="F122" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -46538,7 +46538,7 @@
           <t>AI platform for K-12 districts giving teachers lesson and assessment generation tools and students guided AI, with district-level policy and privacy controls - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F124" s="33" t="inlineStr">
+      <c r="F124" s="35" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Senior Customer Success Manager -  only</t>
         </is>
@@ -46596,7 +46596,7 @@
           <t>Handwriting and annotation app that lets students write on assignments inside Google Classroom or Canvas and submit back to the LMS, sold to schools - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F126" s="34" t="inlineStr">
+      <c r="F126" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -46648,7 +46648,7 @@
           <t>Free and reduced meal application processing, cafeteria point-of-sale and school fee payment software for K-12 districts and state education agencies - exhibited at SNA ANC 2027</t>
         </is>
       </c>
-      <c r="F128" s="34" t="inlineStr">
+      <c r="F128" s="33" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -46704,7 +46704,7 @@
           <t>Browser-delivered virtual computer labs, classroom AI safety controls and work-based learning software for school districts and colleges - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F130" s="35" t="inlineStr">
+      <c r="F130" s="34" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -46760,7 +46760,7 @@
           <t>School district financial management, school nutrition and student data software for K-12 districts - exhibited at SNA ANC 2027</t>
         </is>
       </c>
-      <c r="F132" s="34" t="inlineStr">
+      <c r="F132" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -46818,7 +46818,7 @@
           <t>Identity and access management, rostering and access governance for K-12 school districts and universities - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F134" s="34" t="inlineStr">
+      <c r="F134" s="33" t="inlineStr">
         <is>
           <t>Unknown - board is another company's - not read</t>
         </is>
@@ -46870,7 +46870,7 @@
           <t>AI math tutoring platform with a teacher dashboard for K-12 schools and districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F136" s="34" t="inlineStr">
+      <c r="F136" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -46922,7 +46922,7 @@
           <t>Web research, annotation and writing platform licensed by schools and districts for students and teachers - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F138" s="34" t="inlineStr">
+      <c r="F138" s="33" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/30/26)</t>
+          <t>Hiring AEs? (10/1/26)</t>
         </is>
       </c>
     </row>
@@ -47312,7 +47312,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.modeshift.com/c</t>
+          <t>Unknown - HTTP 403 for https://www.modeshift.com/c</t>
         </is>
       </c>
     </row>
@@ -47696,9 +47696,9 @@
           <t>Real-time transit data: arrival predictions and on-time performance</t>
         </is>
       </c>
-      <c r="F24" s="39" t="inlineStr">
-        <is>
-          <t>Yes - Senior Account Manager (United States)</t>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -47908,7 +47908,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.enghouse.com/ca</t>
+          <t>Unknown - HTTP 403 for https://www.enghouse.com/ca</t>
         </is>
       </c>
     </row>
@@ -49902,7 +49902,7 @@
       </c>
       <c r="F98" s="41" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Sales Backoffice Specialist with G only</t>
+          <t>Sales (non-AE) - Sales Backoffice Specialist only</t>
         </is>
       </c>
     </row>
@@ -49962,7 +49962,7 @@
       </c>
       <c r="F100" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.hanoverdisplays</t>
+          <t>Unknown - HTTP 403 for https://www.hanoverdisplays</t>
         </is>
       </c>
     </row>
@@ -50350,7 +50350,7 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://qryde.com/employmen</t>
+          <t>Unknown - HTTP 403 for https://qryde.com/employmen</t>
         </is>
       </c>
     </row>
@@ -52628,7 +52628,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/30/26)</t>
+          <t>Hiring AEs? (10/1/26)</t>
         </is>
       </c>
     </row>
@@ -54126,9 +54126,9 @@
           <t>Grid software, ADMS and transmission equipment for public and investor utilities</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -56186,7 +56186,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/30/26)</t>
+          <t>Hiring AEs? (10/1/26)</t>
         </is>
       </c>
     </row>
@@ -56598,7 +56598,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -59646,9 +59646,9 @@
           <t>Web-based capital program and construction project management software (cost, contracts, documents, scheduling) used by airport owner-operators and public agencies.</t>
         </is>
       </c>
-      <c r="F117" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -59710,7 +59710,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (9/30/26)</t>
+          <t>Hiring AEs? (10/1/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -286,9 +286,9 @@
     <xf numFmtId="1" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/1/26)</t>
+          <t>Hiring AEs? (10/2/26)</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.axon.com/career</t>
         </is>
       </c>
     </row>
@@ -2070,9 +2070,9 @@
           <t>License plate readers, gunshot detection, and drone-as-first-responder (Aerodome)</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Senior Deal Desk Analyst only</t>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.carbyne.com/car</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/1/26)</t>
+          <t>Hiring AEs? (10/2/26)</t>
         </is>
       </c>
     </row>
@@ -13654,7 +13654,7 @@
       </c>
       <c r="F94" s="63" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 504 for https://eccovia.com/careers</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/1/26)</t>
+          <t>Hiring AEs? (10/2/26)</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/1/26)</t>
+          <t>Hiring AEs? (10/2/26)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/1/26)</t>
+          <t>Hiring AEs? (10/2/26)</t>
         </is>
       </c>
     </row>
@@ -17594,9 +17594,9 @@
           <t>AI recycling-sorting robots and real-time bale/line data</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive - Climate Tech ( (Remote East Coast )</t>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="F120" s="16" t="inlineStr">
         <is>
-          <t>Yes - Account Executive - Government (Ca (Remote)</t>
+          <t>Yes - Account Executive - Government (Te (Remote)</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/1/26)</t>
+          <t>Hiring AEs? (10/2/26)</t>
         </is>
       </c>
     </row>
@@ -25504,9 +25504,9 @@
           <t>Citizen identity and digital service portals (CitizenOne) plus digital trust/signatures (Notarius)</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Représentant du développement des  only</t>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -31808,7 +31808,7 @@
       </c>
       <c r="F246" s="21" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - HTTP 403 for https://passportworkforce.c</t>
         </is>
       </c>
     </row>
@@ -38634,7 +38634,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/1/26)</t>
+          <t>Hiring AEs? (10/2/26)</t>
         </is>
       </c>
     </row>
@@ -42916,7 +42916,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/1/26)</t>
+          <t>Hiring AEs? (10/2/26)</t>
         </is>
       </c>
     </row>
@@ -42946,7 +42946,7 @@
       </c>
       <c r="F2" s="33" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Sales (non-AE) - Director, GTM Finance only</t>
         </is>
       </c>
     </row>
@@ -42976,7 +42976,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>Yes - Sales Executive - Pacific Northwes (Remote Worker - N/)</t>
+          <t>Yes - Sales Executive - Central Region</t>
         </is>
       </c>
     </row>
@@ -43004,7 +43004,7 @@
           <t>AI gun detection layered onto existing school security cameras</t>
         </is>
       </c>
-      <c r="F4" s="33" t="inlineStr">
+      <c r="F4" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -43064,7 +43064,7 @@
           <t>Monitors school email/docs for self-harm and threat signals - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F6" s="33" t="inlineStr">
+      <c r="F6" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -43124,7 +43124,7 @@
           <t>Cloud web filtering and student safety monitoring - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F8" s="34" t="inlineStr">
+      <c r="F8" s="35" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Large/Enterpris (United States of A)</t>
         </is>
@@ -43184,7 +43184,7 @@
           <t>Web filtering and student safety monitoring for school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F10" s="34" t="inlineStr">
+      <c r="F10" s="35" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Austin, Texas, Uni)</t>
         </is>
@@ -43244,7 +43244,7 @@
           <t>Student wellbeing, filtering and safety monitoring for school districts</t>
         </is>
       </c>
-      <c r="F12" s="33" t="inlineStr">
+      <c r="F12" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -43304,7 +43304,7 @@
           <t>AI web filtering and student threat detection for K-12 districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F14" s="35" t="inlineStr">
+      <c r="F14" s="33" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -43362,7 +43362,7 @@
           <t>Real-time AI content filtering and self-harm detection for schools - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F16" s="33" t="inlineStr">
+      <c r="F16" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -43420,7 +43420,7 @@
           <t>Mass notification and emergency response app for schools and campuses</t>
         </is>
       </c>
-      <c r="F18" s="33" t="inlineStr">
+      <c r="F18" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -43478,7 +43478,7 @@
           <t>Cloud video security and sensors for schools and public agencies</t>
         </is>
       </c>
-      <c r="F20" s="34" t="inlineStr">
+      <c r="F20" s="35" t="inlineStr">
         <is>
           <t>Yes - Commercial Account Executive - Cen (Denver, Colorado)</t>
         </is>
@@ -43538,7 +43538,7 @@
           <t>AI gun detection and emergency notification for schools and campuses</t>
         </is>
       </c>
-      <c r="F22" s="33" t="inlineStr">
+      <c r="F22" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -43598,7 +43598,7 @@
           <t>Computer vision threat and weapon detection for schools and public facilities</t>
         </is>
       </c>
-      <c r="F24" s="33" t="inlineStr">
+      <c r="F24" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -43658,7 +43658,7 @@
           <t>AI-based weapons screening gateways for schools, venues and public buildings</t>
         </is>
       </c>
-      <c r="F26" s="34" t="inlineStr">
+      <c r="F26" s="35" t="inlineStr">
         <is>
           <t>Yes - Regional Sales Manager (Boston, Massachuse)</t>
         </is>
@@ -43718,7 +43718,7 @@
           <t>Anonymous reporting and crisis support platform for K-12 schools</t>
         </is>
       </c>
-      <c r="F28" s="33" t="inlineStr">
+      <c r="F28" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -43776,7 +43776,7 @@
           <t>Visitor screening and sex-offender check kiosks for schools</t>
         </is>
       </c>
-      <c r="F30" s="33" t="inlineStr">
+      <c r="F30" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -43836,7 +43836,7 @@
           <t>Emergency mass notification hardware and software for schools and agencies - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F32" s="34" t="inlineStr">
+      <c r="F32" s="35" t="inlineStr">
         <is>
           <t>Yes - Regional Account Manager - Educati (Baltimore, MD)</t>
         </is>
@@ -43894,7 +43894,7 @@
           <t>FlySense vape and bullying sensors for school bathrooms and hallways</t>
         </is>
       </c>
-      <c r="F34" s="33" t="inlineStr">
+      <c r="F34" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -43952,7 +43952,7 @@
           <t>Multi-sensor vape, gunshot and aggression detection for schools</t>
         </is>
       </c>
-      <c r="F36" s="33" t="inlineStr">
+      <c r="F36" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -44012,7 +44012,7 @@
           <t>Cloud security, content filtering, and student safety monitoring for Google Workspace and Microsoft 365 in K-12 districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F38" s="33" t="inlineStr">
+      <c r="F38" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -44072,7 +44072,7 @@
           <t>Gamified phishing simulation and security awareness training built only for K-12 districts, staff and students - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F40" s="33" t="inlineStr">
+      <c r="F40" s="34" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -44128,7 +44128,7 @@
           <t>Web filtering, classroom management, self-harm and threat detection and parent engagement software for K-12 school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F42" s="33" t="inlineStr">
+      <c r="F42" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -44188,7 +44188,7 @@
           <t>Vetted small-vehicle student rides supplementing district bus fleets - exhibited at NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F44" s="34" t="inlineStr">
+      <c r="F44" s="35" t="inlineStr">
         <is>
           <t>Yes - Regional Account Manager- Future O (Remote USA)</t>
         </is>
@@ -44248,7 +44248,7 @@
           <t>Longtime standard for school bus routing and planning software</t>
         </is>
       </c>
-      <c r="F46" s="34" t="inlineStr">
+      <c r="F46" s="35" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -44308,7 +44308,7 @@
           <t>Student transportation routing and fleet software for districts - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F48" s="33" t="inlineStr">
+      <c r="F48" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -44368,7 +44368,7 @@
           <t>School bus operations, driver pay and dispatch software for districts</t>
         </is>
       </c>
-      <c r="F50" s="33" t="inlineStr">
+      <c r="F50" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -44428,7 +44428,7 @@
           <t>School bus tracking and communication app sold to districts</t>
         </is>
       </c>
-      <c r="F52" s="33" t="inlineStr">
+      <c r="F52" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -44488,7 +44488,7 @@
           <t>Contracted school bus transportation services for K-12 districts - exhibited at NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F54" s="33" t="inlineStr">
+      <c r="F54" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -44548,7 +44548,7 @@
           <t>Contracted school bus transportation for K-12 districts nationwide</t>
         </is>
       </c>
-      <c r="F56" s="33" t="inlineStr">
+      <c r="F56" s="34" t="inlineStr">
         <is>
           <t>Unknown - network error: Exceeded 30 redirects.</t>
         </is>
@@ -44608,7 +44608,7 @@
           <t>Bus video, audio and fleet electronics for school districts</t>
         </is>
       </c>
-      <c r="F58" s="33" t="inlineStr">
+      <c r="F58" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -44668,7 +44668,7 @@
           <t>School buses and electric Jouley buses for K-12 districts - exhibited at NAPT Summit 2026</t>
         </is>
       </c>
-      <c r="F60" s="33" t="inlineStr">
+      <c r="F60" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -44728,7 +44728,7 @@
           <t>All-electric school buses and trucks for school districts</t>
         </is>
       </c>
-      <c r="F62" s="33" t="inlineStr">
+      <c r="F62" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -44788,7 +44788,7 @@
           <t>Electric school bus fleet-as-a-service subscriptions for districts</t>
         </is>
       </c>
-      <c r="F64" s="33" t="inlineStr">
+      <c r="F64" s="34" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -44848,7 +44848,7 @@
           <t>Student information system giant plus enrollment, comms, and analytics - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F66" s="33" t="inlineStr">
+      <c r="F66" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -44908,7 +44908,7 @@
           <t>K-12 HR, absence and substitute management, and operations software</t>
         </is>
       </c>
-      <c r="F68" s="33" t="inlineStr">
+      <c r="F68" s="34" t="inlineStr">
         <is>
           <t>Unknown - HTTP 403 for https://careers.frontlineed</t>
         </is>
@@ -44968,7 +44968,7 @@
           <t>Thrillshare K-12 communications: district websites, apps, notifications, branding - exhibited at NLC City Summit 2026, CoSN 2026</t>
         </is>
       </c>
-      <c r="F70" s="33" t="inlineStr">
+      <c r="F70" s="34" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://api.lever.co/v0/pos</t>
         </is>
@@ -45028,7 +45028,7 @@
           <t>Digital flyer distribution and parent communication for K-12 districts</t>
         </is>
       </c>
-      <c r="F72" s="33" t="inlineStr">
+      <c r="F72" s="34" t="inlineStr">
         <is>
           <t>Unknown - HTTP 404 for https://app.trinethire.com/</t>
         </is>
@@ -45088,7 +45088,7 @@
           <t>Student information system and school business/ERP suite for K-12 districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F74" s="35" t="inlineStr">
+      <c r="F74" s="33" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Technical Special only</t>
         </is>
@@ -45148,7 +45148,7 @@
           <t>SIS, ERP and gradebook for K-12 districts and state agencies</t>
         </is>
       </c>
-      <c r="F76" s="33" t="inlineStr">
+      <c r="F76" s="34" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -45208,7 +45208,7 @@
           <t>Genesis SIS and parent portal for New Jersey-area public districts</t>
         </is>
       </c>
-      <c r="F78" s="33" t="inlineStr">
+      <c r="F78" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -45268,7 +45268,7 @@
           <t>Cloud SIS and LMS for K-12 districts and charter networks</t>
         </is>
       </c>
-      <c r="F80" s="33" t="inlineStr">
+      <c r="F80" s="34" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -45328,7 +45328,7 @@
           <t>K-12 finance, HR and payroll ERP for California school agencies</t>
         </is>
       </c>
-      <c r="F82" s="33" t="inlineStr">
+      <c r="F82" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -45388,7 +45388,7 @@
           <t>School nutrition, inventory and POS software for districts and states</t>
         </is>
       </c>
-      <c r="F84" s="33" t="inlineStr">
+      <c r="F84" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -45446,7 +45446,7 @@
           <t>School bus routing, fleet and student transportation software for districts</t>
         </is>
       </c>
-      <c r="F86" s="34" t="inlineStr">
+      <c r="F86" s="35" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -45506,7 +45506,7 @@
           <t>Enrollment, school choice and behavior management for public districts</t>
         </is>
       </c>
-      <c r="F88" s="33" t="inlineStr">
+      <c r="F88" s="34" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -45566,7 +45566,7 @@
           <t>Website, CMS and mass communications platform for school districts</t>
         </is>
       </c>
-      <c r="F90" s="35" t="inlineStr">
+      <c r="F90" s="33" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -45626,7 +45626,7 @@
           <t>Family engagement, attendance and communications platform for districts</t>
         </is>
       </c>
-      <c r="F92" s="34" t="inlineStr">
+      <c r="F92" s="35" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Future Opportun (Remote)</t>
         </is>
@@ -45686,7 +45686,7 @@
           <t>Absence, substitute placement and time tracking for school districts</t>
         </is>
       </c>
-      <c r="F94" s="34" t="inlineStr">
+      <c r="F94" s="35" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Remote Worker - N/)</t>
         </is>
@@ -45746,7 +45746,7 @@
           <t>K-12 hiring, applicant tracking and talent matching for districts</t>
         </is>
       </c>
-      <c r="F96" s="35" t="inlineStr">
+      <c r="F96" s="33" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -45806,7 +45806,7 @@
           <t>Facility use request and scheduling software for K-12 districts</t>
         </is>
       </c>
-      <c r="F98" s="33" t="inlineStr">
+      <c r="F98" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -45866,7 +45866,7 @@
           <t>School safety, threat assessment and preparedness software for districts</t>
         </is>
       </c>
-      <c r="F100" s="33" t="inlineStr">
+      <c r="F100" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -45926,7 +45926,7 @@
           <t>District identity, rostering and application access platform for K-12 - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F102" s="33" t="inlineStr">
+      <c r="F102" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -45984,7 +45984,7 @@
           <t>Cafeteria point-of-sale, free and reduced meal eligibility, and claims reporting software for K-12 school nutrition programs - exhibited at SNA ANC 2027</t>
         </is>
       </c>
-      <c r="F104" s="33" t="inlineStr">
+      <c r="F104" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -46036,7 +46036,7 @@
           <t>Chromebook checkout, device inventory, and student login security for K-12 districts running Google Workspace - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F106" s="33" t="inlineStr">
+      <c r="F106" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -46092,7 +46092,7 @@
           <t>AI point-of-sale and dining operations software for K-12 school nutrition programs and campus dining - exhibited at SNA ANC 2027</t>
         </is>
       </c>
-      <c r="F108" s="33" t="inlineStr">
+      <c r="F108" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -46150,7 +46150,7 @@
           <t>Data warehouse and analytics platform that unifies SIS, LMS, assessment, and attendance data for K-12 schools and districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F110" s="33" t="inlineStr">
+      <c r="F110" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -46208,7 +46208,7 @@
       </c>
       <c r="F112" s="35" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Inside Sales Account Executive only</t>
+          <t>Yes - Expression of Interest: Outside Sa (Remote - USA)</t>
         </is>
       </c>
     </row>
@@ -46264,7 +46264,7 @@
           <t>Classroom communication and engagement app connecting K-12 teachers, students, and families - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F114" s="35" t="inlineStr">
+      <c r="F114" s="33" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Revenue Product Lead only</t>
         </is>
@@ -46314,7 +46314,7 @@
           <t>AI browser extension that generates lesson plans, quizzes, and student feedback inside Google Workspace and LMS tools for teachers and school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F116" s="34" t="inlineStr">
+      <c r="F116" s="35" t="inlineStr">
         <is>
           <t>Yes - Mid-Market Account Executive (Remote)</t>
         </is>
@@ -46372,7 +46372,7 @@
           <t>Behavior referral and discipline management software plus a student dismissal board for K-12 school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F118" s="33" t="inlineStr">
+      <c r="F118" s="34" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
@@ -46426,7 +46426,7 @@
           <t>IT help desk ticketing, device asset management and facilities service software built for K-12 school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F120" s="33" t="inlineStr">
+      <c r="F120" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -46480,7 +46480,7 @@
           <t>Free keyboarding, digital citizenship and AI literacy curriculum for K-12 schools, with a paid ad-free district edition - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F122" s="33" t="inlineStr">
+      <c r="F122" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -46538,7 +46538,7 @@
           <t>AI platform for K-12 districts giving teachers lesson and assessment generation tools and students guided AI, with district-level policy and privacy controls - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F124" s="35" t="inlineStr">
+      <c r="F124" s="33" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Senior Customer Success Manager -  only</t>
         </is>
@@ -46596,7 +46596,7 @@
           <t>Handwriting and annotation app that lets students write on assignments inside Google Classroom or Canvas and submit back to the LMS, sold to schools - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F126" s="33" t="inlineStr">
+      <c r="F126" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -46648,7 +46648,7 @@
           <t>Free and reduced meal application processing, cafeteria point-of-sale and school fee payment software for K-12 districts and state education agencies - exhibited at SNA ANC 2027</t>
         </is>
       </c>
-      <c r="F128" s="33" t="inlineStr">
+      <c r="F128" s="34" t="inlineStr">
         <is>
           <t>Unknown - page scan found no listings</t>
         </is>
@@ -46704,7 +46704,7 @@
           <t>Browser-delivered virtual computer labs, classroom AI safety controls and work-based learning software for school districts and colleges - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F130" s="34" t="inlineStr">
+      <c r="F130" s="35" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -46760,7 +46760,7 @@
           <t>School district financial management, school nutrition and student data software for K-12 districts - exhibited at SNA ANC 2027</t>
         </is>
       </c>
-      <c r="F132" s="33" t="inlineStr">
+      <c r="F132" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -46818,7 +46818,7 @@
           <t>Identity and access management, rostering and access governance for K-12 school districts and universities - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F134" s="33" t="inlineStr">
+      <c r="F134" s="34" t="inlineStr">
         <is>
           <t>Unknown - board is another company's - not read</t>
         </is>
@@ -46870,7 +46870,7 @@
           <t>AI math tutoring platform with a teacher dashboard for K-12 schools and districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F136" s="33" t="inlineStr">
+      <c r="F136" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -46922,7 +46922,7 @@
           <t>Web research, annotation and writing platform licensed by schools and districts for students and teachers - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F138" s="33" t="inlineStr">
+      <c r="F138" s="34" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/1/26)</t>
+          <t>Hiring AEs? (10/2/26)</t>
         </is>
       </c>
     </row>
@@ -52628,7 +52628,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/1/26)</t>
+          <t>Hiring AEs? (10/2/26)</t>
         </is>
       </c>
     </row>
@@ -54126,9 +54126,9 @@
           <t>Grid software, ADMS and transmission equipment for public and investor utilities</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -54186,9 +54186,9 @@
           <t>Metering, CIS, billing and grid analytics for public power utilities</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 301 for https://www.oracle.com/corp</t>
         </is>
       </c>
     </row>
@@ -56186,7 +56186,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/1/26)</t>
+          <t>Hiring AEs? (10/2/26)</t>
         </is>
       </c>
     </row>
@@ -57670,9 +57670,9 @@
           <t>Baggage handling systems and terminal logistics for airports</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -58572,7 +58572,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (C1 - (Austin, TX, United)</t>
+          <t>Yes - Enterprise Account Executive (C1 - (Chicago, IL, Unite)</t>
         </is>
       </c>
     </row>
@@ -58722,7 +58722,7 @@
       </c>
       <c r="F86" s="51" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.axon.com/career</t>
         </is>
       </c>
     </row>
@@ -59710,7 +59710,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/1/26)</t>
+          <t>Hiring AEs? (10/2/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/2/26)</t>
+          <t>Hiring AEs? (10/3/26)</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>Yes - Account Executive, Federal Civilia (US Remote)</t>
+          <t>Yes - Senior Account Executive, Corporat (2 Locations)</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/2/26)</t>
+          <t>Hiring AEs? (10/3/26)</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/2/26)</t>
+          <t>Hiring AEs? (10/3/26)</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/2/26)</t>
+          <t>Hiring AEs? (10/3/26)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/2/26)</t>
+          <t>Hiring AEs? (10/3/26)</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/2/26)</t>
+          <t>Hiring AEs? (10/3/26)</t>
         </is>
       </c>
     </row>
@@ -26210,9 +26210,9 @@
           <t>CodeRED public alerting and critical event management for local jurisdictions</t>
         </is>
       </c>
-      <c r="F56" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F56" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -32428,9 +32428,9 @@
           <t>License verification and workforce compliance for agencies and regulators</t>
         </is>
       </c>
-      <c r="F267" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F267" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sr. Customer Success Manager - Gov only</t>
         </is>
       </c>
     </row>
@@ -33078,7 +33078,7 @@
       </c>
       <c r="F289" s="7" t="inlineStr">
         <is>
-          <t>Unknown - board is another company's - not read</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -33104,9 +33104,9 @@
           <t>Deathcare technology suite including cemetery and memorial management software</t>
         </is>
       </c>
-      <c r="F290" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F290" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -38634,7 +38634,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/2/26)</t>
+          <t>Hiring AEs? (10/3/26)</t>
         </is>
       </c>
     </row>
@@ -39766,9 +39766,9 @@
           <t>Club and league management platform for youth soccer organizations</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -42916,7 +42916,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/2/26)</t>
+          <t>Hiring AEs? (10/3/26)</t>
         </is>
       </c>
     </row>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/2/26)</t>
+          <t>Hiring AEs? (10/3/26)</t>
         </is>
       </c>
     </row>
@@ -52628,7 +52628,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/2/26)</t>
+          <t>Hiring AEs? (10/3/26)</t>
         </is>
       </c>
     </row>
@@ -54126,9 +54126,9 @@
           <t>Grid software, ADMS and transmission equipment for public and investor utilities</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -54186,9 +54186,9 @@
           <t>Metering, CIS, billing and grid analytics for public power utilities</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - HTTP 301 for https://www.oracle.com/corp</t>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -56186,7 +56186,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/2/26)</t>
+          <t>Hiring AEs? (10/3/26)</t>
         </is>
       </c>
     </row>
@@ -57822,7 +57822,7 @@
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -58510,9 +58510,9 @@
           <t>Biometric identity, TSA PreCheck enrollment and airport boarding systems</t>
         </is>
       </c>
-      <c r="F79" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Key Account Manager - Smart Biomet</t>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sales Manager - Smart Biometrics only</t>
         </is>
       </c>
     </row>
@@ -58572,7 +58572,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (C1 - (Chicago, IL, Unite)</t>
+          <t>Yes - Enterprise Account Executive (C1 - (Dallas, TX, United)</t>
         </is>
       </c>
     </row>
@@ -59710,7 +59710,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/2/26)</t>
+          <t>Hiring AEs? (10/3/26)</t>
         </is>
       </c>
     </row>
@@ -60226,7 +60226,7 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (Stat (United States)</t>
+          <t>Yes - Enterprise Account Executive (Stat (New York, New York)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/3/26)</t>
+          <t>Hiring AEs? (10/4/26)</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 404 for https://careers.jobscore.co</t>
         </is>
       </c>
     </row>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="F251" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/3/26)</t>
+          <t>Hiring AEs? (10/4/26)</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/3/26)</t>
+          <t>Hiring AEs? (10/4/26)</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/3/26)</t>
+          <t>Hiring AEs? (10/4/26)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/3/26)</t>
+          <t>Hiring AEs? (10/4/26)</t>
         </is>
       </c>
     </row>
@@ -18542,7 +18542,7 @@
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/3/26)</t>
+          <t>Hiring AEs? (10/4/26)</t>
         </is>
       </c>
     </row>
@@ -26210,9 +26210,9 @@
           <t>CodeRED public alerting and critical event management for local jurisdictions</t>
         </is>
       </c>
-      <c r="F56" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F56" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -26242,7 +26242,7 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -30184,7 +30184,7 @@
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -30736,7 +30736,7 @@
       </c>
       <c r="F210" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - board is another company's - not read</t>
         </is>
       </c>
     </row>
@@ -33078,7 +33078,7 @@
       </c>
       <c r="F289" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - board is another company's - not read</t>
         </is>
       </c>
     </row>
@@ -33104,9 +33104,9 @@
           <t>Deathcare technology suite including cemetery and memorial management software</t>
         </is>
       </c>
-      <c r="F290" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+      <c r="F290" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -37266,7 +37266,7 @@
       </c>
       <c r="F436" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -37510,9 +37510,9 @@
           <t>Government contract and procurement software - exhibited at NIGP 2026</t>
         </is>
       </c>
-      <c r="F445" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F445" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Founding Account Executive (New York City)</t>
         </is>
       </c>
     </row>
@@ -37932,7 +37932,7 @@
       </c>
       <c r="F462" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -37954,9 +37954,9 @@
           <t>Business phone and unified communications systems - exhibited at NIGP 2026</t>
         </is>
       </c>
-      <c r="F463" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F463" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Hunter / Account Executive (2 Locations)</t>
         </is>
       </c>
     </row>
@@ -38634,7 +38634,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/3/26)</t>
+          <t>Hiring AEs? (10/4/26)</t>
         </is>
       </c>
     </row>
@@ -39526,9 +39526,9 @@
           <t>Club and league operations platform for youth sports organizations</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -39766,9 +39766,9 @@
           <t>Club and league management platform for youth soccer organizations</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -42916,7 +42916,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/3/26)</t>
+          <t>Hiring AEs? (10/4/26)</t>
         </is>
       </c>
     </row>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/3/26)</t>
+          <t>Hiring AEs? (10/4/26)</t>
         </is>
       </c>
     </row>
@@ -49932,7 +49932,7 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -52628,7 +52628,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/3/26)</t>
+          <t>Hiring AEs? (10/4/26)</t>
         </is>
       </c>
     </row>
@@ -53918,7 +53918,7 @@
       </c>
       <c r="F44" s="45" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://www.itron.com/compa</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -53978,7 +53978,7 @@
       </c>
       <c r="F46" s="45" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -54338,7 +54338,7 @@
       </c>
       <c r="F58" s="45" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -54788,7 +54788,7 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 404 for https://www.anterix.com/car</t>
         </is>
       </c>
     </row>
@@ -56186,7 +56186,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/3/26)</t>
+          <t>Hiring AEs? (10/4/26)</t>
         </is>
       </c>
     </row>
@@ -58572,7 +58572,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (C1 - (Dallas, TX, United)</t>
+          <t>Yes - Enterprise Account Executive (C1 - (Chicago, IL, Unite)</t>
         </is>
       </c>
     </row>
@@ -59710,7 +59710,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/3/26)</t>
+          <t>Hiring AEs? (10/4/26)</t>
         </is>
       </c>
     </row>
@@ -60226,7 +60226,7 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (Stat (New York, New York)</t>
+          <t>Yes - Enterprise Account Executive (Stat (United States)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/4/26)</t>
+          <t>Hiring AEs? (10/5/26)</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://careers.jobscore.co</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/4/26)</t>
+          <t>Hiring AEs? (10/5/26)</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/4/26)</t>
+          <t>Hiring AEs? (10/5/26)</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/4/26)</t>
+          <t>Hiring AEs? (10/5/26)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/4/26)</t>
+          <t>Hiring AEs? (10/5/26)</t>
         </is>
       </c>
     </row>
@@ -23650,7 +23650,7 @@
       </c>
       <c r="F210" s="16" t="inlineStr">
         <is>
-          <t>Yes - Account Executive Install Base (Ja (Tokyo, Tokyo)</t>
+          <t>Yes - Account Executive - New Business ( (Paris, Île-de-Fran)</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/4/26)</t>
+          <t>Hiring AEs? (10/5/26)</t>
         </is>
       </c>
     </row>
@@ -25594,9 +25594,9 @@
           <t>Interpretation management and delivery platform (video/phone) used by courts and agencies</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive, SMB (United States (Rem)</t>
         </is>
       </c>
     </row>
@@ -29346,7 +29346,7 @@
       </c>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>Yes - (Remote) Sr Account Executive (26 Locations)</t>
+          <t>Yes - Account Executive (5 Locations)</t>
         </is>
       </c>
     </row>
@@ -30796,7 +30796,7 @@
       </c>
       <c r="F212" s="22" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (London)</t>
+          <t>Yes - Account Executive (Singapore, Singapo)</t>
         </is>
       </c>
     </row>
@@ -38634,7 +38634,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/4/26)</t>
+          <t>Hiring AEs? (10/5/26)</t>
         </is>
       </c>
     </row>
@@ -42916,7 +42916,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/4/26)</t>
+          <t>Hiring AEs? (10/5/26)</t>
         </is>
       </c>
     </row>
@@ -42976,7 +42976,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>Yes - Sales Executive - Central Region</t>
+          <t>Yes - Sales Executive, Cross-Sell (Utah  (Remote Worker - N/)</t>
         </is>
       </c>
     </row>
@@ -45686,9 +45686,9 @@
           <t>Absence, substitute placement and time tracking for school districts</t>
         </is>
       </c>
-      <c r="F94" s="35" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive (Remote Worker - N/)</t>
+      <c r="F94" s="34" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/4/26)</t>
+          <t>Hiring AEs? (10/5/26)</t>
         </is>
       </c>
     </row>
@@ -49932,7 +49932,7 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -52628,7 +52628,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/4/26)</t>
+          <t>Hiring AEs? (10/5/26)</t>
         </is>
       </c>
     </row>
@@ -53918,7 +53918,7 @@
       </c>
       <c r="F44" s="45" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - HTTP 404 for https://www.itron.com/compa</t>
         </is>
       </c>
     </row>
@@ -53978,7 +53978,7 @@
       </c>
       <c r="F46" s="45" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -54608,7 +54608,7 @@
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Sales Engineer only</t>
+          <t>Sales (non-AE) - Senior Client Success Manager only</t>
         </is>
       </c>
     </row>
@@ -56186,7 +56186,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/4/26)</t>
+          <t>Hiring AEs? (10/5/26)</t>
         </is>
       </c>
     </row>
@@ -57670,9 +57670,9 @@
           <t>Baggage handling systems and terminal logistics for airports</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -57702,7 +57702,7 @@
       </c>
       <c r="F52" s="51" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -57822,7 +57822,7 @@
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -58572,7 +58572,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (C1 - (Chicago, IL, Unite)</t>
+          <t>Yes - Enterprise Account Executive (C1 - (Austin, TX, United)</t>
         </is>
       </c>
     </row>
@@ -59050,7 +59050,7 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>Yes - Associate Account Executive (Cleve (Cleveland, Ohio, U)</t>
+          <t>Yes - Associate Account Executive (Atlan (Atlanta, Georgia, )</t>
         </is>
       </c>
     </row>
@@ -59710,7 +59710,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/4/26)</t>
+          <t>Hiring AEs? (10/5/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/5/26)</t>
+          <t>Hiring AEs? (10/6/26)</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Sr. Manager, FP&amp;A &amp; Sales Operatio only</t>
+          <t>Sales (non-AE) - Senior Customer Success Manager -  only</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -3330,9 +3330,9 @@
           <t>Drone-as-first-responder software and hardware auto-launching to 911 calls</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sales Development Representative ( only</t>
         </is>
       </c>
     </row>
@@ -5892,9 +5892,9 @@
           <t>Incident records and ePCR data platform for EMS and fire agencies - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
-      <c r="F168" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F168" s="8" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/5/26)</t>
+          <t>Hiring AEs? (10/6/26)</t>
         </is>
       </c>
     </row>
@@ -11800,7 +11800,7 @@
       </c>
       <c r="F26" s="65" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - GTM Strategy &amp; Operations Lead only</t>
+          <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/5/26)</t>
+          <t>Hiring AEs? (10/6/26)</t>
         </is>
       </c>
     </row>
@@ -15036,9 +15036,9 @@
           <t>Academic scheduling, course demand analytics, and room and event management software for colleges and universities - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F24" s="71" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive (Expansion) (Overland Park, KS,)</t>
+      <c r="F24" s="70" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Director of Client Success only</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/5/26)</t>
+          <t>Hiring AEs? (10/6/26)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/5/26)</t>
+          <t>Hiring AEs? (10/6/26)</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
@@ -23830,7 +23830,7 @@
       </c>
       <c r="F216" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/5/26)</t>
+          <t>Hiring AEs? (10/6/26)</t>
         </is>
       </c>
     </row>
@@ -24636,7 +24636,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive - Col</t>
+          <t>Yes - Account Executive - New Logo - Nor</t>
         </is>
       </c>
     </row>
@@ -27230,9 +27230,9 @@
           <t>AI permitting and plan review: automated GIS/code compliance checks (Hernando County cut reviews 30 days to 2)</t>
         </is>
       </c>
-      <c r="F91" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -28104,7 +28104,7 @@
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive - CES (London)</t>
+          <t>Yes - Business Development Manager (Brisbane)</t>
         </is>
       </c>
     </row>
@@ -29522,9 +29522,9 @@
           <t>Digital services and payments platform for state and local government - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Client Success Manager (Northeast  only</t>
         </is>
       </c>
     </row>
@@ -30796,7 +30796,7 @@
       </c>
       <c r="F212" s="22" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Singapore, Singapo)</t>
+          <t>Yes - Account Executive (London)</t>
         </is>
       </c>
     </row>
@@ -33506,9 +33506,9 @@
           <t>ChatGPT and the API, sold to public sector including named state and local government roles</t>
         </is>
       </c>
-      <c r="F304" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Account Director, Large Enterprise only</t>
+      <c r="F304" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Business Development Manager, Prod (Munich, Germany)</t>
         </is>
       </c>
     </row>
@@ -36186,9 +36186,9 @@
           <t>Web-based mapping, demographic, and consumer data visualization application for university and public library patrons - exhibited at PLA 2026</t>
         </is>
       </c>
-      <c r="F397" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Senior Account Executive - B2B Saa</t>
+      <c r="F397" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -38634,7 +38634,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/5/26)</t>
+          <t>Hiring AEs? (10/6/26)</t>
         </is>
       </c>
     </row>
@@ -41472,9 +41472,9 @@
           <t>Weather data, alerting and decision tools for government agencies</t>
         </is>
       </c>
-      <c r="F96" s="27" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F96" s="28" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -42916,7 +42916,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/5/26)</t>
+          <t>Hiring AEs? (10/6/26)</t>
         </is>
       </c>
     </row>
@@ -42976,7 +42976,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>Yes - Sales Executive, Cross-Sell (Utah  (Remote Worker - N/)</t>
+          <t>Yes - Sales Executive - Central Region (Remote Worker - N/)</t>
         </is>
       </c>
     </row>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/5/26)</t>
+          <t>Hiring AEs? (10/6/26)</t>
         </is>
       </c>
     </row>
@@ -50170,7 +50170,7 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive, Western Europe (Paris)</t>
+          <t>Yes - Principal Account Manager (Berlin)</t>
         </is>
       </c>
     </row>
@@ -52628,7 +52628,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/5/26)</t>
+          <t>Hiring AEs? (10/6/26)</t>
         </is>
       </c>
     </row>
@@ -54338,7 +54338,7 @@
       </c>
       <c r="F58" s="45" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -56186,7 +56186,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/5/26)</t>
+          <t>Hiring AEs? (10/6/26)</t>
         </is>
       </c>
     </row>
@@ -57702,7 +57702,7 @@
       </c>
       <c r="F52" s="51" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -58572,7 +58572,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (C1 - (Austin, TX, United)</t>
+          <t>Yes - Enterprise Account Executive (C1 - (Dallas, TX, United)</t>
         </is>
       </c>
     </row>
@@ -59710,7 +59710,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/5/26)</t>
+          <t>Hiring AEs? (10/6/26)</t>
         </is>
       </c>
     </row>
@@ -60226,7 +60226,7 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (Stat (United States)</t>
+          <t>Yes - Enterprise Account Executive (Stat (New York, New York)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/6/26)</t>
+          <t>Hiring AEs? (10/7/26)</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
+          <t>Unknown - HTTP 202 for https://www.365labs.com/car</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive, France (London)</t>
+          <t>Yes - Account Executive, Benelux (London)</t>
         </is>
       </c>
     </row>
@@ -3960,9 +3960,9 @@
           <t>Data platform unifying CAD/RMS/community data for officer context at dispatch</t>
         </is>
       </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>Yes - Regional Sales Manager FL area for</t>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="F181" s="10" t="inlineStr">
         <is>
-          <t>Yes - Mid-Market Account Executive</t>
+          <t>Yes - Enterprise Account Executive</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="F235" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.keefegroup.com/</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/6/26)</t>
+          <t>Hiring AEs? (10/7/26)</t>
         </is>
       </c>
     </row>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Solutions Consultant only</t>
+          <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/6/26)</t>
+          <t>Hiring AEs? (10/7/26)</t>
         </is>
       </c>
     </row>
@@ -14916,9 +14916,9 @@
           <t>No-code IT service management, asset management, project portfolio, and integration platform for universities, school districts, and government agencies - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F20" s="69" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F20" s="71" t="inlineStr">
+        <is>
+          <t>Yes - Enterprise Sales Executive, NY/PA (New York)</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/6/26)</t>
+          <t>Hiring AEs? (10/7/26)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/6/26)</t>
+          <t>Hiring AEs? (10/7/26)</t>
         </is>
       </c>
     </row>
@@ -18922,7 +18922,7 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Lead Salesforce Developer only</t>
+          <t>Sales (non-AE) - Vice President, Revenue Operations only</t>
         </is>
       </c>
     </row>
@@ -21282,9 +21282,9 @@
           <t>Water quality and level monitoring instruments for agencies and utilities - exhibited at AWWA ACE 2026, WEFTEC 2026, StormCon 2026</t>
         </is>
       </c>
-      <c r="F130" s="16" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F130" s="15" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 403 for https://in-situ.com/careers</t>
         </is>
       </c>
     </row>
@@ -23650,7 +23650,7 @@
       </c>
       <c r="F210" s="16" t="inlineStr">
         <is>
-          <t>Yes - Account Executive - New Business ( (Paris, Île-de-Fran)</t>
+          <t>Yes - Account Executive (new business de (Paris, Île-de-Fran)</t>
         </is>
       </c>
     </row>
@@ -23830,7 +23830,7 @@
       </c>
       <c r="F216" s="15" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/6/26)</t>
+          <t>Hiring AEs? (10/7/26)</t>
         </is>
       </c>
     </row>
@@ -24846,7 +24846,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://zencity.io/careers</t>
+          <t>Unknown - HTTP 202 for https://zencity.io/careers</t>
         </is>
       </c>
     </row>
@@ -30796,7 +30796,7 @@
       </c>
       <c r="F212" s="22" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (London)</t>
+          <t>Yes - Account Executive (Singapore, Singapo)</t>
         </is>
       </c>
     </row>
@@ -30944,9 +30944,9 @@
           <t>Grantmaking and grants management platform for public funders</t>
         </is>
       </c>
-      <c r="F217" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F217" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sr. Customer Success Manager only</t>
         </is>
       </c>
     </row>
@@ -31808,7 +31808,7 @@
       </c>
       <c r="F246" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://passportworkforce.c</t>
+          <t>Unknown - HTTP 202 for https://passportworkforce.c</t>
         </is>
       </c>
     </row>
@@ -34746,9 +34746,9 @@
           <t>Digital ballot scanning, tabulation and audit systems for election offices</t>
         </is>
       </c>
-      <c r="F347" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F347" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -35138,7 +35138,7 @@
       </c>
       <c r="F360" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://www.easyvotesolutio</t>
+          <t>Unknown - HTTP 401 for https://www.easyvotesolutio</t>
         </is>
       </c>
     </row>
@@ -38634,7 +38634,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/6/26)</t>
+          <t>Hiring AEs? (10/7/26)</t>
         </is>
       </c>
     </row>
@@ -39048,7 +39048,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Shreveport, LA)</t>
+          <t>Yes - Account Executive (Memphis, TN)</t>
         </is>
       </c>
     </row>
@@ -39586,9 +39586,9 @@
           <t>Youth sports program, camp and league management software</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive (INDIANAPOLIS, IN)</t>
         </is>
       </c>
     </row>
@@ -40186,9 +40186,9 @@
           <t>Campground reservation and management software for public and private campgrounds</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Manager, Account Management only</t>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -42916,7 +42916,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/6/26)</t>
+          <t>Hiring AEs? (10/7/26)</t>
         </is>
       </c>
     </row>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/6/26)</t>
+          <t>Hiring AEs? (10/7/26)</t>
         </is>
       </c>
     </row>
@@ -47312,7 +47312,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.modeshift.com/c</t>
+          <t>Unknown - HTTP 202 for https://www.modeshift.com/c</t>
         </is>
       </c>
     </row>
@@ -47578,7 +47578,7 @@
       </c>
       <c r="F20" s="39" t="inlineStr">
         <is>
-          <t>Yes - Senior Enterprise Account Executiv (Spain, Spain)</t>
+          <t>Yes - Technical Account Manager (Abu Dhabi, United )</t>
         </is>
       </c>
     </row>
@@ -47908,7 +47908,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.enghouse.com/ca</t>
+          <t>Unknown - HTTP 202 for https://www.enghouse.com/ca</t>
         </is>
       </c>
     </row>
@@ -49962,7 +49962,7 @@
       </c>
       <c r="F100" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.hanoverdisplays</t>
+          <t>Unknown - HTTP 202 for https://www.hanoverdisplays</t>
         </is>
       </c>
     </row>
@@ -50228,9 +50228,9 @@
           <t>AI microtransit and ADA paratransit operations: scheduling, dispatch, rider app, analytics - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Senior Customer Success Manager only</t>
         </is>
       </c>
     </row>
@@ -50350,7 +50350,7 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://qryde.com/employmen</t>
+          <t>Unknown - HTTP 202 for https://qryde.com/employmen</t>
         </is>
       </c>
     </row>
@@ -52240,7 +52240,7 @@
       </c>
       <c r="F178" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.intangles.ai/ca</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -52628,7 +52628,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/6/26)</t>
+          <t>Hiring AEs? (10/7/26)</t>
         </is>
       </c>
     </row>
@@ -53138,7 +53138,7 @@
       </c>
       <c r="F18" s="45" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -54338,7 +54338,7 @@
       </c>
       <c r="F58" s="45" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 504 for https://www.sedata.com/care</t>
         </is>
       </c>
     </row>
@@ -56186,7 +56186,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/6/26)</t>
+          <t>Hiring AEs? (10/7/26)</t>
         </is>
       </c>
     </row>
@@ -59710,7 +59710,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/6/26)</t>
+          <t>Hiring AEs? (10/7/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/7/26)</t>
+          <t>Hiring AEs? (10/8/26)</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>Yes - Account Executive with German (Poland Offsite (ZP)</t>
+          <t>Yes - Senior Account Executive - Cyberse (Texas, US Offsite,)</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.365labs.com/car</t>
+          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.milestonesys.co</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.briefcam.com/ca</t>
         </is>
       </c>
     </row>
@@ -6582,9 +6582,9 @@
           <t>911 call routing, Viper call handling and NG911 for PSAPs</t>
         </is>
       </c>
-      <c r="F191" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - HTTP 504 for https://leotechnologies.com</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/7/26)</t>
+          <t>Hiring AEs? (10/8/26)</t>
         </is>
       </c>
     </row>
@@ -13772,9 +13772,9 @@
           <t>Case management, intake, referral, and grant tracking software for public and nonprofit human services programs - exhibited at NatCon 2026, NACCHO 360 2026</t>
         </is>
       </c>
-      <c r="F98" s="64" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F98" s="63" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 403 for https://www.planstreet.com/</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/7/26)</t>
+          <t>Hiring AEs? (10/8/26)</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/7/26)</t>
+          <t>Hiring AEs? (10/8/26)</t>
         </is>
       </c>
     </row>
@@ -17220,7 +17220,7 @@
       </c>
       <c r="F10" s="75" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.affordablehousi</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/7/26)</t>
+          <t>Hiring AEs? (10/8/26)</t>
         </is>
       </c>
     </row>
@@ -23650,7 +23650,7 @@
       </c>
       <c r="F210" s="16" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (new business de (Paris, Île-de-Fran)</t>
+          <t>Yes - Senior Account Executive Net New - (Düsseldorf, North )</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/7/26)</t>
+          <t>Hiring AEs? (10/8/26)</t>
         </is>
       </c>
     </row>
@@ -24846,7 +24846,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://zencity.io/careers</t>
+          <t>Unknown - HTTP 403 for https://zencity.io/careers</t>
         </is>
       </c>
     </row>
@@ -24936,7 +24936,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://publicinput.com/car</t>
         </is>
       </c>
     </row>
@@ -28014,7 +28014,7 @@
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Account Director only</t>
+          <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
       </c>
     </row>
@@ -28306,9 +28306,9 @@
           <t>Local government ERP: financials, property tax, assessing, utility billing - Michigan standard going national - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F128" s="22" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F128" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -29524,7 +29524,7 @@
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Client Success Manager (Northeast  only</t>
+          <t>Sales (non-AE) - Client Success Manager (Northeast) only</t>
         </is>
       </c>
     </row>
@@ -30004,7 +30004,7 @@
       </c>
       <c r="F185" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive/Enterprise Accou</t>
+          <t>Yes - Support Account Manager</t>
         </is>
       </c>
     </row>
@@ -30886,7 +30886,7 @@
       </c>
       <c r="F215" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (United States)</t>
+          <t>Yes - Enterprise Account Executive – Hea (United States)</t>
         </is>
       </c>
     </row>
@@ -31306,7 +31306,7 @@
       </c>
       <c r="F229" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Credit Unions/B (Remote)</t>
+          <t>Yes - Sr. Account Executive (AI Solution (Remote)</t>
         </is>
       </c>
     </row>
@@ -31808,7 +31808,7 @@
       </c>
       <c r="F246" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://passportworkforce.c</t>
+          <t>Unknown - HTTP 403 for https://passportworkforce.c</t>
         </is>
       </c>
     </row>
@@ -35138,7 +35138,7 @@
       </c>
       <c r="F360" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 401 for https://www.easyvotesolutio</t>
+          <t>Unknown - HTTP 404 for https://www.easyvotesolutio</t>
         </is>
       </c>
     </row>
@@ -37510,9 +37510,9 @@
           <t>Government contract and procurement software - exhibited at NIGP 2026</t>
         </is>
       </c>
-      <c r="F445" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Founding Account Executive (New York City)</t>
+      <c r="F445" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - ruled out of scope by owner on 2026-08-24</t>
         </is>
       </c>
     </row>
@@ -38634,7 +38634,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/7/26)</t>
+          <t>Hiring AEs? (10/8/26)</t>
         </is>
       </c>
     </row>
@@ -40694,7 +40694,7 @@
       </c>
       <c r="F70" s="28" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 504 for https://www.weathermatic.co</t>
         </is>
       </c>
     </row>
@@ -42916,7 +42916,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/7/26)</t>
+          <t>Hiring AEs? (10/8/26)</t>
         </is>
       </c>
     </row>
@@ -42976,7 +42976,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>Yes - Sales Executive - Central Region (Remote Worker - N/)</t>
+          <t>Yes - Sales Executive, Cross-Sell (Utah  (Remote Worker - N/)</t>
         </is>
       </c>
     </row>
@@ -43806,9 +43806,9 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/7/26)</t>
+          <t>Hiring AEs? (10/8/26)</t>
         </is>
       </c>
     </row>
@@ -47312,7 +47312,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.modeshift.com/c</t>
+          <t>Unknown - HTTP 403 for https://www.modeshift.com/c</t>
         </is>
       </c>
     </row>
@@ -47908,7 +47908,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.enghouse.com/ca</t>
+          <t>Unknown - HTTP 403 for https://www.enghouse.com/ca</t>
         </is>
       </c>
     </row>
@@ -49032,7 +49032,7 @@
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Core Account Executive  (Remote)</t>
+          <t>Yes - Account Executive, Mid-Market (USA)</t>
         </is>
       </c>
     </row>
@@ -49962,7 +49962,7 @@
       </c>
       <c r="F100" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.hanoverdisplays</t>
+          <t>Unknown - HTTP 403 for https://www.hanoverdisplays</t>
         </is>
       </c>
     </row>
@@ -50350,7 +50350,7 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://qryde.com/employmen</t>
+          <t>Unknown - HTTP 403 for https://qryde.com/employmen</t>
         </is>
       </c>
     </row>
@@ -52628,7 +52628,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/7/26)</t>
+          <t>Hiring AEs? (10/8/26)</t>
         </is>
       </c>
     </row>
@@ -53798,7 +53798,7 @@
       </c>
       <c r="F40" s="45" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.ledvance.com/en</t>
         </is>
       </c>
     </row>
@@ -54338,7 +54338,7 @@
       </c>
       <c r="F58" s="45" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 504 for https://www.sedata.com/care</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -54994,9 +54994,9 @@
           <t>Utility billing and customer information software for small and mid-size municipal water, sewer, and multi-service utilities - exhibited at AWWA ACE 2026, GFOA 2026</t>
         </is>
       </c>
-      <c r="F80" s="46" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F80" s="45" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 403 for https://cusi.com/careers/</t>
         </is>
       </c>
     </row>
@@ -56186,7 +56186,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/7/26)</t>
+          <t>Hiring AEs? (10/8/26)</t>
         </is>
       </c>
     </row>
@@ -57822,7 +57822,7 @@
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -57970,9 +57970,9 @@
           <t>Airport IQ operations, property and lease management software for airports</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Senior Account Executive</t>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -58032,7 +58032,7 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.grab.careers/en</t>
         </is>
       </c>
     </row>
@@ -58572,7 +58572,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (C1 - (Dallas, TX, United)</t>
+          <t>Yes - Enterprise Account Executive (C1 - (Austin, TX, United)</t>
         </is>
       </c>
     </row>
@@ -59710,7 +59710,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/7/26)</t>
+          <t>Hiring AEs? (10/8/26)</t>
         </is>
       </c>
     </row>
@@ -60226,7 +60226,7 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (Stat (New York, New York)</t>
+          <t>Yes - Enterprise Account Executive (Stat (United States)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/9/26)</t>
+          <t>Hiring AEs? (10/10/26)</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive - Public Sector  (Las Vegas, Nevada)</t>
+          <t>Yes - Account Executive (Sweden)</t>
         </is>
       </c>
     </row>
@@ -4788,9 +4788,9 @@
           <t>Software for first responder agencies - exhibited at IACP 2026, APCO 2026</t>
         </is>
       </c>
-      <c r="F131" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive (United States)</t>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - robots.txt asks crawlers not to read www</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.carbyne.com/car</t>
+          <t>Unknown - HTTP 403 for https://www.axon.com/career</t>
         </is>
       </c>
     </row>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="F225" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://www.cpcjail.com/car</t>
+          <t>Unknown - HTTP 404 for https://cpcjail.com/careers</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://scramsystems.dejobs</t>
+          <t>Unknown - robots.txt on scramsystems.dejobs.org an</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="F235" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.keefegroup.com/</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/9/26)</t>
+          <t>Hiring AEs? (10/10/26)</t>
         </is>
       </c>
     </row>
@@ -12498,7 +12498,7 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on streamlineh</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/9/26)</t>
+          <t>Hiring AEs? (10/10/26)</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/9/26)</t>
+          <t>Hiring AEs? (10/10/26)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/9/26)</t>
+          <t>Hiring AEs? (10/10/26)</t>
         </is>
       </c>
     </row>
@@ -17476,7 +17476,7 @@
       </c>
       <c r="F2" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.rubicon</t>
         </is>
       </c>
     </row>
@@ -18042,9 +18042,9 @@
           <t>AI robotics and recovery analytics for material recovery facilities</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -19252,7 +19252,7 @@
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://one.network/careers</t>
+          <t>Unknown - robots.txt asks crawlers not to read one</t>
         </is>
       </c>
     </row>
@@ -21282,9 +21282,9 @@
           <t>Water quality and level monitoring instruments for agencies and utilities - exhibited at AWWA ACE 2026, WEFTEC 2026, StormCon 2026</t>
         </is>
       </c>
-      <c r="F130" s="15" t="inlineStr">
-        <is>
-          <t>Unknown - HTTP 403 for https://in-situ.com/careers</t>
+      <c r="F130" s="16" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.syrinix.com/car</t>
+          <t>Unknown - HTTP 403 for https://www.badgermeter.com</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="F202" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - robots.txt asks crawlers not to read www</t>
         </is>
       </c>
     </row>
@@ -23560,7 +23560,7 @@
       </c>
       <c r="F207" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://careers.jacobs.com</t>
+          <t>Unknown - robots.txt on careers.jacobs.com answere</t>
         </is>
       </c>
     </row>
@@ -23650,7 +23650,7 @@
       </c>
       <c r="F210" s="16" t="inlineStr">
         <is>
-          <t>Yes - Senior Account Executive Net New - (Düsseldorf, North )</t>
+          <t>Yes - Strategic Account Executive – Aero (Warsaw, Mazovia)</t>
         </is>
       </c>
     </row>
@@ -23830,7 +23830,7 @@
       </c>
       <c r="F216" s="15" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 504 for https://eptura.com/careers</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/9/26)</t>
+          <t>Hiring AEs? (10/10/26)</t>
         </is>
       </c>
     </row>
@@ -25056,7 +25056,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.revize.com/care</t>
+          <t>Unknown - robots.txt asks crawlers not to read www</t>
         </is>
       </c>
     </row>
@@ -29524,9 +29524,9 @@
           <t>Bill presentment and payments for governments and utilities (public co) - exhibited at GFOA 2026, NAHRO 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F169" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - network error: robots.txt on www.payment</t>
         </is>
       </c>
     </row>
@@ -29646,7 +29646,7 @@
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 405 for https://planetbids.com/care</t>
+          <t>Unknown - HTTP 405 for https://files-prod01.planet</t>
         </is>
       </c>
     </row>
@@ -30768,7 +30768,7 @@
       </c>
       <c r="F211" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (London)</t>
+          <t>Yes - Account Executive (Denmark)</t>
         </is>
       </c>
     </row>
@@ -31218,7 +31218,7 @@
       </c>
       <c r="F226" s="21" t="inlineStr">
         <is>
-          <t>Unknown - board is another company's - not read</t>
+          <t>Unknown - robots.txt asks crawlers not to read www</t>
         </is>
       </c>
     </row>
@@ -32522,7 +32522,7 @@
       </c>
       <c r="F270" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://harrislocalgov.com/</t>
+          <t>Unknown - HTTP 404 for https://www.harrislocalgov.</t>
         </is>
       </c>
     </row>
@@ -32788,7 +32788,7 @@
       </c>
       <c r="F279" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - robots.txt asks crawlers not to read rec</t>
         </is>
       </c>
     </row>
@@ -34222,7 +34222,7 @@
       </c>
       <c r="F329" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.maxar.c</t>
         </is>
       </c>
     </row>
@@ -35750,7 +35750,7 @@
       </c>
       <c r="F381" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Strategic Account Director only</t>
+          <t>Sales (non-AE) - Strategic Account Director -Wester only</t>
         </is>
       </c>
     </row>
@@ -37212,7 +37212,7 @@
       </c>
       <c r="F434" s="21" t="inlineStr">
         <is>
-          <t>Unknown - board is another company's - not read</t>
+          <t>Unknown - network error: robots.txt on careers.act</t>
         </is>
       </c>
     </row>
@@ -38606,7 +38606,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/9/26)</t>
+          <t>Hiring AEs? (10/10/26)</t>
         </is>
       </c>
     </row>
@@ -42888,7 +42888,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/9/26)</t>
+          <t>Hiring AEs? (10/10/26)</t>
         </is>
       </c>
     </row>
@@ -43008,7 +43008,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.evolvtechnology</t>
+          <t>Unknown - HTTP 403 for https://evolv.com/careers</t>
         </is>
       </c>
     </row>
@@ -44522,7 +44522,7 @@
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>Unknown - network error: Exceeded 30 redirects.</t>
+          <t>Unknown - more than 10 redirects from https://www.</t>
         </is>
       </c>
     </row>
@@ -45570,7 +45570,7 @@
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>Yes - Sales Executive (Remote Worker - N/)</t>
+          <t>Yes - Senior Account Executive — Payment</t>
         </is>
       </c>
     </row>
@@ -46984,7 +46984,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/9/26)</t>
+          <t>Hiring AEs? (10/10/26)</t>
         </is>
       </c>
     </row>
@@ -48114,7 +48114,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - more than 10 redirects from https://wi-t</t>
         </is>
       </c>
     </row>
@@ -48734,7 +48734,7 @@
       </c>
       <c r="F60" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.gatekee</t>
         </is>
       </c>
     </row>
@@ -49062,9 +49062,9 @@
           <t>Fleet maintenance software for cities, counties and transit agencies</t>
         </is>
       </c>
-      <c r="F71" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive (Remote Worker)</t>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -51624,7 +51624,7 @@
       </c>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>Yes - Junior B2B Account Executive (Prague)</t>
+          <t>Yes - B2B Account Manager (Oslo)</t>
         </is>
       </c>
     </row>
@@ -51654,7 +51654,7 @@
       </c>
       <c r="F158" s="40" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - network error: robots.txt on www.pom.com</t>
         </is>
       </c>
     </row>
@@ -52600,7 +52600,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/9/26)</t>
+          <t>Hiring AEs? (10/10/26)</t>
         </is>
       </c>
     </row>
@@ -54578,9 +54578,9 @@
           <t>DERMS and virtual power plant programs for utilities including public power</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Senior Client Success Manager only</t>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -55262,7 +55262,7 @@
       </c>
       <c r="F90" s="47" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Head of Sales only</t>
+          <t>Sales (non-AE) - Intern, Business Development Assoc only</t>
         </is>
       </c>
     </row>
@@ -56066,7 +56066,7 @@
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://sifinetworks.com/co</t>
+          <t>Unknown - HTTP 404 for http://www.arclinkfiber.com</t>
         </is>
       </c>
     </row>
@@ -56158,7 +56158,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/9/26)</t>
+          <t>Hiring AEs? (10/10/26)</t>
         </is>
       </c>
     </row>
@@ -57642,9 +57642,9 @@
           <t>Baggage handling systems and terminal logistics for airports</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -57824,7 +57824,7 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page too small - likely JS-rendered</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -58452,9 +58452,9 @@
           <t>Explosive and chemical trace detection instruments for aviation security</t>
         </is>
       </c>
-      <c r="F78" s="52" t="inlineStr">
-        <is>
-          <t>Yes - Sales Account Manager</t>
+      <c r="F78" s="51" t="inlineStr">
+        <is>
+          <t>Unknown - robots.txt asks crawlers not to read wor</t>
         </is>
       </c>
     </row>
@@ -58484,7 +58484,7 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Sales Manager - Smart Biometrics only</t>
+          <t>Sales (non-AE) - Business Operations and Leadership only</t>
         </is>
       </c>
     </row>
@@ -58572,9 +58572,9 @@
           <t>Airport threat detection AI and biometric travel systems for government</t>
         </is>
       </c>
-      <c r="F82" s="53" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - USAF and USSF (US Space Force) Str only</t>
+      <c r="F82" s="51" t="inlineStr">
+        <is>
+          <t>Unknown - robots.txt asks crawlers not to read int</t>
         </is>
       </c>
     </row>
@@ -58962,7 +58962,7 @@
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - robots.txt asks crawlers not to read www</t>
         </is>
       </c>
     </row>
@@ -59682,7 +59682,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/9/26)</t>
+          <t>Hiring AEs? (10/10/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/10/26)</t>
+          <t>Hiring AEs? (10/13/26)</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - HTTP 404 for https://api.ashbyhq.com/pos</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/10/26)</t>
+          <t>Hiring AEs? (10/13/26)</t>
         </is>
       </c>
     </row>
@@ -12498,7 +12498,7 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: robots.txt on streamlineh</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>Yes - Senior Account Executive (Remote)</t>
+          <t>Yes - Account Executive (Remote)</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/10/26)</t>
+          <t>Hiring AEs? (10/13/26)</t>
         </is>
       </c>
     </row>
@@ -16600,9 +16600,9 @@
           <t>Argos reporting, FormFusion document automation and IntelleCheck payment software built for higher education administrative systems - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F82" s="69" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F82" s="71" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive (Houston, Texas, Un)</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/10/26)</t>
+          <t>Hiring AEs? (10/13/26)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/10/26)</t>
+          <t>Hiring AEs? (10/13/26)</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="F120" s="16" t="inlineStr">
         <is>
-          <t>Yes - Account Executive - Government Wes (Remote)</t>
+          <t>Yes - Account Executive - Government (We (Remote)</t>
         </is>
       </c>
     </row>
@@ -21282,9 +21282,9 @@
           <t>Water quality and level monitoring instruments for agencies and utilities - exhibited at AWWA ACE 2026, WEFTEC 2026, StormCon 2026</t>
         </is>
       </c>
-      <c r="F130" s="16" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F130" s="15" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 403 for https://in-situ.com/careers</t>
         </is>
       </c>
     </row>
@@ -22464,7 +22464,7 @@
       </c>
       <c r="F170" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 404 for https://baseform.com/np4/ca</t>
         </is>
       </c>
     </row>
@@ -23650,7 +23650,7 @@
       </c>
       <c r="F210" s="16" t="inlineStr">
         <is>
-          <t>Yes - Strategic Account Executive – Aero (Warsaw, Mazovia)</t>
+          <t>Yes - Senior Account Executive, Aerospac (Itasca, Illinois)</t>
         </is>
       </c>
     </row>
@@ -23830,7 +23830,7 @@
       </c>
       <c r="F216" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 504 for https://eptura.com/careers/</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/10/26)</t>
+          <t>Hiring AEs? (10/13/26)</t>
         </is>
       </c>
     </row>
@@ -26180,9 +26180,9 @@
           <t>CodeRED public alerting and critical event management for local jurisdictions</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -27986,7 +27986,7 @@
       </c>
       <c r="F117" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Customer Success Manager only</t>
+          <t>Sales (non-AE) - Account Director only</t>
         </is>
       </c>
     </row>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="F120" s="22" t="inlineStr">
         <is>
-          <t>Yes - Business Development Manager (Brisbane)</t>
+          <t>Yes - Account Manager - Medical Billing (Amersham)</t>
         </is>
       </c>
     </row>
@@ -28188,9 +28188,9 @@
           <t>Procurement, budgeting, and grants suite - Bonfire, Questica, eCivis (formerly GTY) - exhibited at NACUBO 2026, GFOA 2026</t>
         </is>
       </c>
-      <c r="F124" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Solutions Consultant only</t>
+      <c r="F124" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive - Payments (United States)</t>
         </is>
       </c>
     </row>
@@ -28368,9 +28368,9 @@
           <t>Cloud treasury: debt management, GASB 87/96 lease accounting, and cash management for gov finance - exhibited at NACUBO 2026, GFOA 2026</t>
         </is>
       </c>
-      <c r="F130" s="22" t="inlineStr">
-        <is>
-          <t>Yes - Enterprise Account Executive (Charlotte, NC)</t>
+      <c r="F130" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 404 for https://boards-api.greenhou</t>
         </is>
       </c>
     </row>
@@ -29524,9 +29524,9 @@
           <t>Bill presentment and payments for governments and utilities (public co) - exhibited at GFOA 2026, NAHRO 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - network error: robots.txt on www.payment</t>
+      <c r="F169" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -30768,7 +30768,7 @@
       </c>
       <c r="F211" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Denmark)</t>
+          <t>Yes - Account Executive (London)</t>
         </is>
       </c>
     </row>
@@ -38606,7 +38606,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/10/26)</t>
+          <t>Hiring AEs? (10/13/26)</t>
         </is>
       </c>
     </row>
@@ -39020,7 +39020,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Memphis, TN)</t>
+          <t>Yes - Account Executive (Wildomar, CA)</t>
         </is>
       </c>
     </row>
@@ -42888,7 +42888,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/10/26)</t>
+          <t>Hiring AEs? (10/13/26)</t>
         </is>
       </c>
     </row>
@@ -45418,9 +45418,9 @@
           <t>School bus routing, fleet and student transportation software for districts</t>
         </is>
       </c>
-      <c r="F86" s="35" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F86" s="34" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -46984,7 +46984,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/10/26)</t>
+          <t>Hiring AEs? (10/13/26)</t>
         </is>
       </c>
     </row>
@@ -47162,9 +47162,9 @@
           <t>Contactless open-loop transit payment infrastructure for 400+ providers in 30+ countries</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Senior Business Development Manage (London)</t>
         </is>
       </c>
     </row>
@@ -47400,7 +47400,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.pptexce</t>
         </is>
       </c>
     </row>
@@ -47548,9 +47548,9 @@
           <t>Account-based fare collection and validators for public transit operators</t>
         </is>
       </c>
-      <c r="F20" s="39" t="inlineStr">
-        <is>
-          <t>Yes - Technical Account Manager (Abu Dhabi, United )</t>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -51174,7 +51174,7 @@
       </c>
       <c r="F142" s="40" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -52600,7 +52600,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/10/26)</t>
+          <t>Hiring AEs? (10/13/26)</t>
         </is>
       </c>
     </row>
@@ -54310,7 +54310,7 @@
       </c>
       <c r="F58" s="45" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -54938,7 +54938,7 @@
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.advance</t>
         </is>
       </c>
     </row>
@@ -56158,7 +56158,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/10/26)</t>
+          <t>Hiring AEs? (10/13/26)</t>
         </is>
       </c>
     </row>
@@ -57642,9 +57642,9 @@
           <t>Baggage handling systems and terminal logistics for airports</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -58242,9 +58242,9 @@
           <t>Ascento Guard autonomous outdoor security robot sold as robot-as-a-service: wheeled-legged patrol unit with thermal/RGB cameras plus AI software for perimeter patrol, intruder detection and site inspection.</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Business Development: French-Speak only</t>
         </is>
       </c>
     </row>
@@ -58544,7 +58544,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (C1 - (Austin, TX, United)</t>
+          <t>Yes - Enterprise Account Executive (C1 - (New York, New York)</t>
         </is>
       </c>
     </row>
@@ -59682,7 +59682,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/10/26)</t>
+          <t>Hiring AEs? (10/13/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/13/26)</t>
+          <t>Hiring AEs? (10/14/26)</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
+          <t>Unknown - robots.txt on www.365labs.com answered H</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Account Director, Public Sector (D only</t>
+          <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
       </c>
     </row>
@@ -5382,9 +5382,9 @@
           <t>FBI-certified mobile fingerprint scanners for police and government</t>
         </is>
       </c>
-      <c r="F151" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -8758,7 +8758,7 @@
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -10612,9 +10612,9 @@
           <t>DigiTICKET electronic citation software - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F336" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F336" s="4" t="inlineStr">
+        <is>
+          <t>Unknown - network error: robots.txt on saltustechn</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/13/26)</t>
+          <t>Hiring AEs? (10/14/26)</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/13/26)</t>
+          <t>Hiring AEs? (10/14/26)</t>
         </is>
       </c>
     </row>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 504 for https://www.graydi.us/caree</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/13/26)</t>
+          <t>Hiring AEs? (10/14/26)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/13/26)</t>
+          <t>Hiring AEs? (10/14/26)</t>
         </is>
       </c>
     </row>
@@ -20742,9 +20742,9 @@
           <t>AI pipe-failure prediction for main replacement planning - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
-      <c r="F112" s="16" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F112" s="15" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -23830,7 +23830,7 @@
       </c>
       <c r="F216" s="15" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 504 for https://eptura.com/careers/</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/13/26)</t>
+          <t>Hiring AEs? (10/14/26)</t>
         </is>
       </c>
     </row>
@@ -24846,7 +24846,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://zencity.io/careers</t>
+          <t>Unknown - robots.txt on zencity.io answered HTTP 2</t>
         </is>
       </c>
     </row>
@@ -26180,9 +26180,9 @@
           <t>CodeRED public alerting and critical event management for local jurisdictions</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -31780,7 +31780,7 @@
       </c>
       <c r="F245" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://passportworkforce.c</t>
+          <t>Unknown - robots.txt on passportworkforce.com answ</t>
         </is>
       </c>
     </row>
@@ -38606,7 +38606,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/13/26)</t>
+          <t>Hiring AEs? (10/14/26)</t>
         </is>
       </c>
     </row>
@@ -39020,7 +39020,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Wildomar, CA)</t>
+          <t>Yes - Account Executive (Fresno, CA)</t>
         </is>
       </c>
     </row>
@@ -41386,7 +41386,7 @@
       </c>
       <c r="F94" s="29" t="inlineStr">
         <is>
-          <t>Yes - Sales Executive (2 Locations)</t>
+          <t>Yes - Account Executive - Agriculture (4 Locations)</t>
         </is>
       </c>
     </row>
@@ -42192,9 +42192,9 @@
           <t>Event management SaaS: vendor applications, ticketing, maps, and sponsors for festivals and city events</t>
         </is>
       </c>
-      <c r="F121" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Enterprise Account Executive</t>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Account Strategist only</t>
         </is>
       </c>
     </row>
@@ -42888,7 +42888,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/13/26)</t>
+          <t>Hiring AEs? (10/14/26)</t>
         </is>
       </c>
     </row>
@@ -43452,7 +43452,7 @@
       </c>
       <c r="F20" s="35" t="inlineStr">
         <is>
-          <t>Yes - Commercial Account Executive - Cen (Denver, Colorado)</t>
+          <t>Yes - Commercial Account Executive - Cen (Denver, CO)</t>
         </is>
       </c>
     </row>
@@ -46984,7 +46984,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/13/26)</t>
+          <t>Hiring AEs? (10/14/26)</t>
         </is>
       </c>
     </row>
@@ -47284,7 +47284,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.modeshift.com/c</t>
+          <t>Unknown - robots.txt on www.modeshift.com answered</t>
         </is>
       </c>
     </row>
@@ -47400,7 +47400,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: robots.txt on www.pptexce</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.enghouse.com/ca</t>
+          <t xml:space="preserve">Unknown - robots.txt on www.enghouse.com answered </t>
         </is>
       </c>
     </row>
@@ -49872,9 +49872,9 @@
           <t>Destination signs, LED/LCD passenger displays, onboard infotainment, and CCTV for bus and rail</t>
         </is>
       </c>
-      <c r="F98" s="41" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Sales Backoffice Specialist only</t>
+      <c r="F98" s="39" t="inlineStr">
+        <is>
+          <t>Yes - Area Sales Manager - Middle German</t>
         </is>
       </c>
     </row>
@@ -49934,7 +49934,7 @@
       </c>
       <c r="F100" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.hanoverdisplays</t>
+          <t>Unknown - robots.txt on www.hanoverdisplays.com an</t>
         </is>
       </c>
     </row>
@@ -50322,7 +50322,7 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://qryde.com/employmen</t>
+          <t>Unknown - robots.txt on qryde.com answered HTTP 20</t>
         </is>
       </c>
     </row>
@@ -51382,9 +51382,9 @@
           <t>Smart single-space parking meters and enforcement systems</t>
         </is>
       </c>
-      <c r="F149" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F149" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Regional Account Executive (San Diego, Califor)</t>
         </is>
       </c>
     </row>
@@ -52600,7 +52600,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/13/26)</t>
+          <t>Hiring AEs? (10/14/26)</t>
         </is>
       </c>
     </row>
@@ -54218,9 +54218,9 @@
           <t>SCADA, ADMS and outage management for municipal utilities and co-ops</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -54938,7 +54938,7 @@
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: robots.txt on www.advance</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -56158,7 +56158,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/13/26)</t>
+          <t>Hiring AEs? (10/14/26)</t>
         </is>
       </c>
     </row>
@@ -57794,7 +57794,7 @@
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.elenium</t>
         </is>
       </c>
     </row>
@@ -58544,7 +58544,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (C1 - (New York, New York)</t>
+          <t>Yes - Enterprise Account Executive (C1 - (Dallas, TX, United)</t>
         </is>
       </c>
     </row>
@@ -59682,7 +59682,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/13/26)</t>
+          <t>Hiring AEs? (10/14/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/14/26)</t>
+          <t>Hiring AEs? (10/15/26)</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Customer Success Manager only</t>
+          <t>Sales (non-AE) - Account Director, Financial Instit only</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 500 for https://safience.io/careers</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Manager (Auror London Offic)</t>
+          <t>Yes - Enterprise Account Manager (12-mon (Auror London Offic)</t>
         </is>
       </c>
     </row>
@@ -10612,9 +10612,9 @@
           <t>DigiTICKET electronic citation software - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F336" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - network error: robots.txt on saltustechn</t>
+      <c r="F336" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/14/26)</t>
+          <t>Hiring AEs? (10/15/26)</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/14/26)</t>
+          <t>Hiring AEs? (10/15/26)</t>
         </is>
       </c>
     </row>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="F22" s="70" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Sales Support - Keyholder only</t>
+          <t>Sales (non-AE) - Sales Support only</t>
         </is>
       </c>
     </row>
@@ -16338,7 +16338,7 @@
       </c>
       <c r="F72" s="70" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Senior Solutions Engineer only</t>
+          <t>Sales (non-AE) - Vice President, Sales only</t>
         </is>
       </c>
     </row>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 504 for https://www.graydi.us/caree</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/14/26)</t>
+          <t>Hiring AEs? (10/15/26)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/14/26)</t>
+          <t>Hiring AEs? (10/15/26)</t>
         </is>
       </c>
     </row>
@@ -19732,7 +19732,7 @@
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.q-free.com/care</t>
         </is>
       </c>
     </row>
@@ -20832,9 +20832,9 @@
           <t>AI defect detection and coding for sewer inspection video - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F115" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive, Enterprise (Remote)</t>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Revenue Operations Analyst only</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="F120" s="16" t="inlineStr">
         <is>
-          <t>Yes - Account Executive - Government (We (Remote)</t>
+          <t>Yes - Account Executive - Engineering Fi (Remote)</t>
         </is>
       </c>
     </row>
@@ -23022,9 +23022,9 @@
           <t>Unity AIoT fleet intelligence (incl. MiX Telematics, Fleet Complete) for enterprise and gov fleets</t>
         </is>
       </c>
-      <c r="F189" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F189" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -23650,7 +23650,7 @@
       </c>
       <c r="F210" s="16" t="inlineStr">
         <is>
-          <t>Yes - Senior Account Executive, Aerospac (Itasca, Illinois)</t>
+          <t>Yes - Sales Executive - Industrial Intel (Düsseldorf, North )</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/14/26)</t>
+          <t>Hiring AEs? (10/15/26)</t>
         </is>
       </c>
     </row>
@@ -26062,7 +26062,7 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.civicplus.com/c</t>
         </is>
       </c>
     </row>
@@ -26150,9 +26150,9 @@
           <t>Emergency and routine mass notification for cities, counties and schools</t>
         </is>
       </c>
-      <c r="F54" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Customer Success Manager only</t>
+      <c r="F54" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Saas Account Executive</t>
         </is>
       </c>
     </row>
@@ -30768,7 +30768,7 @@
       </c>
       <c r="F211" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (London)</t>
+          <t>Yes - Account Executive (Singapore, Singapo)</t>
         </is>
       </c>
     </row>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="F328" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.planet.</t>
         </is>
       </c>
     </row>
@@ -34720,7 +34720,7 @@
       </c>
       <c r="F346" s="21" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -38606,7 +38606,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/14/26)</t>
+          <t>Hiring AEs? (10/15/26)</t>
         </is>
       </c>
     </row>
@@ -39020,7 +39020,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Fresno, CA)</t>
+          <t>Yes - Account Executive (Marble Falls, TX)</t>
         </is>
       </c>
     </row>
@@ -42888,7 +42888,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/14/26)</t>
+          <t>Hiring AEs? (10/15/26)</t>
         </is>
       </c>
     </row>
@@ -44044,9 +44044,9 @@
           <t>Gamified phishing simulation and security awareness training built only for K-12 districts, staff and students - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F40" s="34" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F40" s="35" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive - West (United States (Rem)</t>
         </is>
       </c>
     </row>
@@ -46984,7 +46984,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/14/26)</t>
+          <t>Hiring AEs? (10/15/26)</t>
         </is>
       </c>
     </row>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown - robots.txt on www.enghouse.com answered </t>
+          <t>Unknown - HTTP 202 for https://www.enghouse.com/ca</t>
         </is>
       </c>
     </row>
@@ -50200,9 +50200,9 @@
           <t>AI microtransit and ADA paratransit operations: scheduling, dispatch, rider app, analytics - exhibited at CTAA EXPO 2026</t>
         </is>
       </c>
-      <c r="F109" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Senior Customer Success Manager only</t>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -52162,7 +52162,7 @@
       </c>
       <c r="F176" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -52600,7 +52600,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/14/26)</t>
+          <t>Hiring AEs? (10/15/26)</t>
         </is>
       </c>
     </row>
@@ -56158,7 +56158,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/14/26)</t>
+          <t>Hiring AEs? (10/15/26)</t>
         </is>
       </c>
     </row>
@@ -58544,7 +58544,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (C1 - (Dallas, TX, United)</t>
+          <t>Yes - Enterprise Account Executive (C1 - (Chicago, IL, Unite)</t>
         </is>
       </c>
     </row>
@@ -59168,9 +59168,9 @@
           <t>Cloud parking OS and reservations for airports, cities and venues</t>
         </is>
       </c>
-      <c r="F102" s="53" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Estimator, Inside Sales only</t>
+      <c r="F102" s="51" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -59682,7 +59682,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/14/26)</t>
+          <t>Hiring AEs? (10/15/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/15/26)</t>
+          <t>Hiring AEs? (10/16/26)</t>
         </is>
       </c>
     </row>
@@ -1650,9 +1650,9 @@
           <t>Satellite vegetation intelligence for wildfire risk at utilities and agencies</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Enterprise Account Executive, Cana (Remote, Canada)</t>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>Yes - Strategic Account Executive (CO, N (CO, NM, UT)</t>
+          <t>Yes - Strategic Account Executive - NJ/N (New Jersey, New Yo)</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Unknown - robots.txt on www.365labs.com answered H</t>
+          <t>Unknown - HTTP 403 for https://www.365labs.com/car</t>
         </is>
       </c>
     </row>
@@ -3870,9 +3870,9 @@
           <t>OfficerTRAK off-duty detail management: scheduling, billing, insurance - exhibited at NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F99" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Business Development Manager - Mid (Charlotte, North C)</t>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 500 for https://safience.io/careers</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -4350,9 +4350,9 @@
           <t>Cyber-over-RF counter-drone detect, track, and mitigate systems for LE, prisons, and infrastructure</t>
         </is>
       </c>
-      <c r="F115" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -4470,9 +4470,9 @@
           <t>AI ALPR mobile patrol units, speed enforcement, and officer safety systems for LE and municipalities</t>
         </is>
       </c>
-      <c r="F119" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 404 for https://www.ekin.com/about/</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/15/26)</t>
+          <t>Hiring AEs? (10/16/26)</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - page too small - likely JS-rendered</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/15/26)</t>
+          <t>Hiring AEs? (10/16/26)</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/15/26)</t>
+          <t>Hiring AEs? (10/16/26)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/15/26)</t>
+          <t>Hiring AEs? (10/16/26)</t>
         </is>
       </c>
     </row>
@@ -18920,9 +18920,9 @@
           <t>School bus stop-arm cameras with violator-funded safety programs</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Vice President, Revenue Operations only</t>
         </is>
       </c>
     </row>
@@ -23920,7 +23920,7 @@
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.ejward.</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/15/26)</t>
+          <t>Hiring AEs? (10/16/26)</t>
         </is>
       </c>
     </row>
@@ -24846,7 +24846,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>Unknown - robots.txt on zencity.io answered HTTP 2</t>
+          <t>Unknown - HTTP 403 for https://zencity.io/careers</t>
         </is>
       </c>
     </row>
@@ -30768,7 +30768,7 @@
       </c>
       <c r="F211" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Singapore, Singapo)</t>
+          <t>Yes - Account Executive (Denmark)</t>
         </is>
       </c>
     </row>
@@ -31780,7 +31780,7 @@
       </c>
       <c r="F245" s="7" t="inlineStr">
         <is>
-          <t>Unknown - robots.txt on passportworkforce.com answ</t>
+          <t>Unknown - HTTP 403 for https://passportworkforce.c</t>
         </is>
       </c>
     </row>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="F328" s="21" t="inlineStr">
         <is>
-          <t>Unknown - network error: robots.txt on www.planet.</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -38606,7 +38606,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/15/26)</t>
+          <t>Hiring AEs? (10/16/26)</t>
         </is>
       </c>
     </row>
@@ -39020,7 +39020,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Marble Falls, TX)</t>
+          <t>Yes - Account Executive (West Hollywood, CA)</t>
         </is>
       </c>
     </row>
@@ -42192,9 +42192,9 @@
           <t>Event management SaaS: vendor applications, ticketing, maps, and sponsors for festivals and city events</t>
         </is>
       </c>
-      <c r="F121" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Account Strategist only</t>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Sales &amp; Business Development Manag</t>
         </is>
       </c>
     </row>
@@ -42888,7 +42888,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/15/26)</t>
+          <t>Hiring AEs? (10/16/26)</t>
         </is>
       </c>
     </row>
@@ -43778,9 +43778,9 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -46984,7 +46984,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/15/26)</t>
+          <t>Hiring AEs? (10/16/26)</t>
         </is>
       </c>
     </row>
@@ -47284,7 +47284,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Unknown - robots.txt on www.modeshift.com answered</t>
+          <t>Unknown - HTTP 403 for https://www.modeshift.com/c</t>
         </is>
       </c>
     </row>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.enghouse.com/ca</t>
+          <t>Unknown - HTTP 403 for https://www.enghouse.com/ca</t>
         </is>
       </c>
     </row>
@@ -49934,7 +49934,7 @@
       </c>
       <c r="F100" s="40" t="inlineStr">
         <is>
-          <t>Unknown - robots.txt on www.hanoverdisplays.com an</t>
+          <t>Unknown - HTTP 403 for https://www.hanoverdisplays</t>
         </is>
       </c>
     </row>
@@ -50142,7 +50142,7 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>Yes - Principal Account Manager (Berlin)</t>
+          <t>Yes - Account Executive (Remix) (New York City)</t>
         </is>
       </c>
     </row>
@@ -50322,7 +50322,7 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Unknown - robots.txt on qryde.com answered HTTP 20</t>
+          <t>Unknown - HTTP 403 for https://qryde.com/employmen</t>
         </is>
       </c>
     </row>
@@ -52600,7 +52600,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/15/26)</t>
+          <t>Hiring AEs? (10/16/26)</t>
         </is>
       </c>
     </row>
@@ -53258,9 +53258,9 @@
           <t>Aluminum and steel lighting poles for municipal and DOT projects</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -55260,9 +55260,9 @@
           <t>Solid-state transformers and grid power electronics, sold to data centre and solar-plus-storage developers</t>
         </is>
       </c>
-      <c r="F90" s="47" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Intern, Business Development Assoc only</t>
+      <c r="F90" s="46" t="inlineStr">
+        <is>
+          <t>Yes - Senior Technical Account Manager (Scotts Valley)</t>
         </is>
       </c>
     </row>
@@ -56158,7 +56158,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/15/26)</t>
+          <t>Hiring AEs? (10/16/26)</t>
         </is>
       </c>
     </row>
@@ -57794,7 +57794,7 @@
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
-          <t>Unknown - network error: robots.txt on www.elenium</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -58544,7 +58544,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (C1 - (Chicago, IL, Unite)</t>
+          <t>Yes - Enterprise Account Executive (C1 - (Dallas, TX, United)</t>
         </is>
       </c>
     </row>
@@ -59682,7 +59682,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/15/26)</t>
+          <t>Hiring AEs? (10/16/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/16/26)</t>
+          <t>Hiring AEs? (10/17/26)</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>Yes - Senior Account Executive, Corporat (2 Locations)</t>
+          <t>Yes - Account Executive, Federal Civilia (VA - Hybrid)</t>
         </is>
       </c>
     </row>
@@ -3720,9 +3720,9 @@
           <t>Training LMS, scheduling, and readiness software (TargetSolutions, Guardian Tracking) - exhibited at IAFC FRI 2026, APCO 2026</t>
         </is>
       </c>
-      <c r="F94" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/16/26)</t>
+          <t>Hiring AEs? (10/17/26)</t>
         </is>
       </c>
     </row>
@@ -13562,9 +13562,9 @@
           <t>Social care coordination network connecting health and social service referrals for govs and payers - exhibited at MESC 2026</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Strategic Sales Director (United States)</t>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Customer Success Executive - Flori only</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/16/26)</t>
+          <t>Hiring AEs? (10/17/26)</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/16/26)</t>
+          <t>Hiring AEs? (10/17/26)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/16/26)</t>
+          <t>Hiring AEs? (10/17/26)</t>
         </is>
       </c>
     </row>
@@ -23650,7 +23650,7 @@
       </c>
       <c r="F210" s="16" t="inlineStr">
         <is>
-          <t>Yes - Sales Executive - Industrial Intel (Düsseldorf, North )</t>
+          <t>Yes - Senior Account Executive – Enterpr (London, England)</t>
         </is>
       </c>
     </row>
@@ -23920,7 +23920,7 @@
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: robots.txt on www.ejward.</t>
+          <t>Unknown - HTTP 404 for https://www.wardfuel.com/as</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/16/26)</t>
+          <t>Hiring AEs? (10/17/26)</t>
         </is>
       </c>
     </row>
@@ -26784,7 +26784,7 @@
       </c>
       <c r="F76" s="23" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Commercial Counsel, Revenue only</t>
+          <t>Sales (non-AE) - Account Director only</t>
         </is>
       </c>
     </row>
@@ -28608,9 +28608,9 @@
           <t>Aerial imagery and property data analytics for county assessors, GIS, and insurers - exhibited at IAAO 2026</t>
         </is>
       </c>
-      <c r="F138" s="22" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F138" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -29524,9 +29524,9 @@
           <t>Bill presentment and payments for governments and utilities (public co) - exhibited at GFOA 2026, NAHRO 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F169" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - network error: robots.txt on www.payment</t>
         </is>
       </c>
     </row>
@@ -31278,7 +31278,7 @@
       </c>
       <c r="F228" s="22" t="inlineStr">
         <is>
-          <t>Yes - Sr. Account Executive (AI Solution (Remote)</t>
+          <t>Yes - Sr. Account Executive (Tolling) (Remote)</t>
         </is>
       </c>
     </row>
@@ -31892,9 +31892,9 @@
           <t>Payroll and HR software - exhibited at AB Show 2026</t>
         </is>
       </c>
-      <c r="F249" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F249" s="9" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -38606,7 +38606,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/16/26)</t>
+          <t>Hiring AEs? (10/17/26)</t>
         </is>
       </c>
     </row>
@@ -39020,7 +39020,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (West Hollywood, CA)</t>
+          <t>Yes - Account Executive (Glendale, AZ)</t>
         </is>
       </c>
     </row>
@@ -42252,9 +42252,9 @@
           <t>Venue and event management for convention centers and public authorities</t>
         </is>
       </c>
-      <c r="F123" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Director of Solutions Engineering only</t>
+      <c r="F123" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Senior Account Manager (Germany)</t>
         </is>
       </c>
     </row>
@@ -42888,7 +42888,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/16/26)</t>
+          <t>Hiring AEs? (10/17/26)</t>
         </is>
       </c>
     </row>
@@ -43778,9 +43778,9 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -43810,7 +43810,7 @@
       </c>
       <c r="F32" s="35" t="inlineStr">
         <is>
-          <t>Yes - Regional Account Manager - Educati (Baltimore, MD)</t>
+          <t>Yes - Account Manager (Baltimore, MD)</t>
         </is>
       </c>
     </row>
@@ -46510,9 +46510,9 @@
           <t>AI platform for K-12 districts giving teachers lesson and assessment generation tools and students guided AI, with district-level policy and privacy controls - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F124" s="33" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Senior Customer Success Manager -  only</t>
+      <c r="F124" s="34" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -46984,7 +46984,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/16/26)</t>
+          <t>Hiring AEs? (10/17/26)</t>
         </is>
       </c>
     </row>
@@ -52600,7 +52600,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/16/26)</t>
+          <t>Hiring AEs? (10/17/26)</t>
         </is>
       </c>
     </row>
@@ -56158,7 +56158,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/16/26)</t>
+          <t>Hiring AEs? (10/17/26)</t>
         </is>
       </c>
     </row>
@@ -58544,7 +58544,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (C1 - (Dallas, TX, United)</t>
+          <t>Yes - Senior Enterprise Account Executiv (Dallas, TX, United)</t>
         </is>
       </c>
     </row>
@@ -59682,7 +59682,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/16/26)</t>
+          <t>Hiring AEs? (10/17/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/17/26)</t>
+          <t>Hiring AEs? (10/18/26)</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/17/26)</t>
+          <t>Hiring AEs? (10/18/26)</t>
         </is>
       </c>
     </row>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="F8" s="63" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - page too small - likely JS-rendered</t>
         </is>
       </c>
     </row>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="F22" s="63" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -13802,9 +13802,9 @@
           <t>HCBS, Medicaid waiver and homelessness systems for public agencies - exhibited at USAging 2026</t>
         </is>
       </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive I - Personal Car (Overland Park, KS)</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/17/26)</t>
+          <t>Hiring AEs? (10/18/26)</t>
         </is>
       </c>
     </row>
@@ -14512,7 +14512,7 @@
       </c>
       <c r="F6" s="69" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -16630,7 +16630,7 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/17/26)</t>
+          <t>Hiring AEs? (10/18/26)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/17/26)</t>
+          <t>Hiring AEs? (10/18/26)</t>
         </is>
       </c>
     </row>
@@ -22320,7 +22320,7 @@
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 504 for https://streametric.io/care</t>
         </is>
       </c>
     </row>
@@ -22376,7 +22376,7 @@
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/17/26)</t>
+          <t>Hiring AEs? (10/18/26)</t>
         </is>
       </c>
     </row>
@@ -29524,9 +29524,9 @@
           <t>Bill presentment and payments for governments and utilities (public co) - exhibited at GFOA 2026, NAHRO 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - network error: robots.txt on www.payment</t>
+      <c r="F169" s="10" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -30768,7 +30768,7 @@
       </c>
       <c r="F211" s="10" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Denmark)</t>
+          <t>Yes - Account Executive (United States)</t>
         </is>
       </c>
     </row>
@@ -37152,7 +37152,7 @@
       </c>
       <c r="F432" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -37320,7 +37320,7 @@
       </c>
       <c r="F438" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -37582,7 +37582,7 @@
       </c>
       <c r="F448" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -38606,7 +38606,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/17/26)</t>
+          <t>Hiring AEs? (10/18/26)</t>
         </is>
       </c>
     </row>
@@ -42888,7 +42888,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/17/26)</t>
+          <t>Hiring AEs? (10/18/26)</t>
         </is>
       </c>
     </row>
@@ -43336,7 +43336,7 @@
       </c>
       <c r="F16" s="34" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - page too small - likely JS-rendered</t>
         </is>
       </c>
     </row>
@@ -43542,7 +43542,7 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 410 for https://actuate.ai/careers</t>
         </is>
       </c>
     </row>
@@ -43750,7 +43750,7 @@
       </c>
       <c r="F30" s="34" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -44702,7 +44702,7 @@
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - network error: robots.txt on lionlion.ca</t>
         </is>
       </c>
     </row>
@@ -46984,7 +46984,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/17/26)</t>
+          <t>Hiring AEs? (10/18/26)</t>
         </is>
       </c>
     </row>
@@ -48944,7 +48944,7 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -50620,7 +50620,7 @@
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -50908,7 +50908,7 @@
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -51980,7 +51980,7 @@
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -52600,7 +52600,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/17/26)</t>
+          <t>Hiring AEs? (10/18/26)</t>
         </is>
       </c>
     </row>
@@ -52750,7 +52750,7 @@
       </c>
       <c r="F6" s="45" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -53110,7 +53110,7 @@
       </c>
       <c r="F18" s="45" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -56158,7 +56158,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/17/26)</t>
+          <t>Hiring AEs? (10/18/26)</t>
         </is>
       </c>
     </row>
@@ -57794,7 +57794,7 @@
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.elenium</t>
         </is>
       </c>
     </row>
@@ -57854,7 +57854,7 @@
       </c>
       <c r="F58" s="51" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -58544,7 +58544,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Yes - Senior Enterprise Account Executiv (Dallas, TX, United)</t>
+          <t>Yes - Senior Enterprise Account Executiv (Chicago, IL, Unite)</t>
         </is>
       </c>
     </row>
@@ -59682,7 +59682,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/17/26)</t>
+          <t>Hiring AEs? (10/18/26)</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -22,17 +22,17 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Public Safety'!$A$1:$F$379</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Public Works'!$A$1:$F$252</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Public Works'!$A$1:$F$253</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'General Gov'!$A$1:$F$576</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Parks &amp; Rec'!$A$1:$F$144</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'K-12 Schools'!$A$1:$F$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'K-12 Schools'!$A$1:$F$170</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Transit &amp; Parking'!$A$1:$F$195</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Utilities &amp; Energy'!$A$1:$F$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Airports &amp; Aviation'!$A$1:$F$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Courts &amp; Justice'!$A$1:$F$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Health &amp; Human Services'!$A$1:$F$139</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Higher Education'!$A$1:$F$122</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Housing &amp; Community Dev'!$A$1:$F$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Housing &amp; Community Dev'!$A$1:$F$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -230,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -246,9 +246,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -357,6 +357,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="25" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -942,7 +943,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/19/26)</t>
+          <t>Hiring AEs? (10/20/26)</t>
         </is>
       </c>
     </row>
@@ -1120,9 +1121,9 @@
           <t>Wildfire spread modeling and risk analytics used by CAL FIRE and major utilities</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Senior Customer Success Manager -  only</t>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1181,7 @@
           <t>Exterior retardant/foam systems and app-based wildfire defense for homes and HOAs</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>Yes - Territory Manager - LA (Los Angeles, CA)</t>
         </is>
@@ -1210,9 +1211,9 @@
           <t>Evacuation management and real-time incident mapping for fire and emergency agencies - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1331,7 @@
           <t>Actively tethered situational awareness drones with unlimited flight time for fire/PS</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Engineer only</t>
         </is>
@@ -1414,7 +1415,7 @@
           <t>Cloud fire and EMS records management for departments of all sizes</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -2004,9 +2005,9 @@
           <t>Deccan International sells deployment-planning, move-up and run-card software to fire and EMS departments - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2127,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2209,7 @@
           <t>Radios, 911 call handling, CAD, and video security (Avigilon) for public safety - exhibited at Michigan Sheriffs Association 2026, IAFC FRI 2026, APCO 2026, Illinois Chapter of APCO 2026</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="9" t="inlineStr">
         <is>
           <t>Yes - Senior Account Executive - Cyberse (Texas, US Offsite,)</t>
         </is>
@@ -2268,7 +2269,7 @@
           <t>Autonomous drones for police DFR programs and public-sector inspection - exhibited at NLC City Summit 2026, IAFC FRI 2026, APTA 2026</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F47" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -2328,7 +2329,7 @@
           <t>Cloud-native CAD and records management (RMS) for law enforcement - exhibited at APCO 2026</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="9" t="inlineStr">
         <is>
           <t>Yes - Strategic Account Executive - NJ/N (New Jersey, New Yo)</t>
         </is>
@@ -2448,7 +2449,7 @@
           <t>AI analysis of body-camera audio for officer professionalism and supervision</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="9" t="inlineStr">
         <is>
           <t>Yes - Senior Account Executive, Southwes (United States)</t>
         </is>
@@ -2568,7 +2569,7 @@
           <t>CAD/RMS and growing public safety suite via acquisitions - exhibited at APCO 2026</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive - ECC (U.S. (Remote))</t>
         </is>
@@ -2628,7 +2629,7 @@
           <t>Browser-based CAD, RMS, mobile, and jail software for police and fire/EMS - exhibited at APCO 2026, Illinois Chapter of APCO 2026</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F59" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -2718,7 +2719,7 @@
           <t>Incident reporting and case management for law enforcement, campus, and healthcare security - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F62" s="11" t="inlineStr">
+      <c r="F62" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -2868,7 +2869,7 @@
           <t>Mobile forensics and investigative intelligence (UFED, Pathfinder) - Nasdaq: CLBT</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="F67" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -2928,7 +2929,7 @@
           <t>XRY/XAMN mobile device forensics for law enforcement and military</t>
         </is>
       </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="F69" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -3078,7 +3079,7 @@
           <t>Blockchain intelligence for crypto tracing and fraud, sold to LE and regulators</t>
         </is>
       </c>
-      <c r="F74" s="11" t="inlineStr">
+      <c r="F74" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Account Director, Financial Instit only</t>
         </is>
@@ -3108,7 +3109,7 @@
           <t>Digital investigation suite for cleansing and evidencing comms data (UK + US LE)</t>
         </is>
       </c>
-      <c r="F75" s="9" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -3318,7 +3319,7 @@
           <t>aiWARE public safety apps: iDEMS evidence management, Redact, Track (Nasdaq: VERI)</t>
         </is>
       </c>
-      <c r="F82" s="11" t="inlineStr">
+      <c r="F82" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales &amp; Business Operations Coordi only</t>
         </is>
@@ -3348,7 +3349,7 @@
           <t>Real-time AI event detection (First Alert) for first responders and government</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="F83" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Federal Civilia (VA - Hybrid)</t>
         </is>
@@ -3468,7 +3469,7 @@
           <t>Anonymous tips, alerting, and community engagement for 1,400+ agencies (CitizenObserver)</t>
         </is>
       </c>
-      <c r="F87" s="10" t="inlineStr">
+      <c r="F87" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -3498,7 +3499,7 @@
           <t>Drone-as-first-responder software and hardware auto-launching to 911 calls</t>
         </is>
       </c>
-      <c r="F88" s="11" t="inlineStr">
+      <c r="F88" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Development Representative ( only</t>
         </is>
@@ -3588,7 +3589,7 @@
           <t>Counter-UAS detection and defeat systems for military, LE, and infrastructure (ASX: DRO)</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>Yes - Business Development Manager (Milan, Milano, Ita)</t>
         </is>
@@ -3648,7 +3649,7 @@
           <t>Spot and Stretch robots; Spot widely used by bomb squads and hazmat teams (Hyundai)</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F93" s="9" t="inlineStr">
         <is>
           <t>Yes - Senior Sales Executive (2 Locations)</t>
         </is>
@@ -3828,7 +3829,7 @@
           <t>Live-fire ranges and FATS virtual training systems (ex-Meggitt, lineage to 1926)</t>
         </is>
       </c>
-      <c r="F99" s="10" t="inlineStr">
+      <c r="F99" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -4098,7 +4099,7 @@
           <t>Online application and recruiting platform for police and civil service hiring</t>
         </is>
       </c>
-      <c r="F108" s="11" t="inlineStr">
+      <c r="F108" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -4188,7 +4189,7 @@
           <t>AIoT smart city and public safety solutions: AI video, IoT sensors, and managed connectivity - exhibited at NRPA 2026</t>
         </is>
       </c>
-      <c r="F111" s="10" t="inlineStr">
+      <c r="F111" s="9" t="inlineStr">
         <is>
           <t>Yes - Sales Director</t>
         </is>
@@ -4308,7 +4309,7 @@
           <t>Iris recognition biometrics for access control, corrections, national ID, and border programs (ex-LG)</t>
         </is>
       </c>
-      <c r="F115" s="10" t="inlineStr">
+      <c r="F115" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -4488,7 +4489,7 @@
           <t>EnforceAir RF-cyber drone takeover landing rogue drones safely for LE, prisons, and events (NA HQ McLean VA) - exhibited at AAAE 2027</t>
         </is>
       </c>
-      <c r="F121" s="10" t="inlineStr">
+      <c r="F121" s="9" t="inlineStr">
         <is>
           <t>Yes - Sales Executive - Airports Sector (McLean, Virginia)</t>
         </is>
@@ -4518,7 +4519,7 @@
           <t>Cyber-over-RF counter-drone detect, track, and mitigate systems for LE, prisons, and infrastructure</t>
         </is>
       </c>
-      <c r="F122" s="11" t="inlineStr">
+      <c r="F122" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -4932,7 +4933,7 @@
           <t>Vehicle history data tools for police - exhibited at IACP 2026, APCO 2026, Illinois Chapter of APCO 2026</t>
         </is>
       </c>
-      <c r="F137" s="9" t="inlineStr">
+      <c r="F137" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Manager - Revenue Operations &amp; Ana only</t>
         </is>
@@ -4980,7 +4981,7 @@
           <t>Platform for legal data requests to companies - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F139" s="10" t="inlineStr">
+      <c r="F139" s="9" t="inlineStr">
         <is>
           <t>Yes - Strategic Account Executive (Remote (Boston, MA)</t>
         </is>
@@ -5040,7 +5041,7 @@
           <t>AI video redaction and privacy software - exhibited at IACP 2026, ASBO School Business 2026</t>
         </is>
       </c>
-      <c r="F141" s="10" t="inlineStr">
+      <c r="F141" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -5580,7 +5581,7 @@
           <t>Data integration and investigative analytics for police and government</t>
         </is>
       </c>
-      <c r="F159" s="9" t="inlineStr">
+      <c r="F159" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Forward Deployed Enablement Engine only</t>
         </is>
@@ -6024,9 +6025,9 @@
           <t>Sells Pro ATE automated speed-camera enforcement systems, with AI violation processing and ticketing back-office services, to police departments, cities and counties - exhibited at Maryland Municipal League 2026, North Carolina Sheriffs' Association 2026</t>
         </is>
       </c>
-      <c r="F174" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F174" s="8" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6099,7 @@
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6171,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6199,7 @@
           <t>ePCR, records, and analytics connecting EMS, fire, and hospitals - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
-      <c r="F181" s="10" t="inlineStr">
+      <c r="F181" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Remote, US (TN/KY))</t>
         </is>
@@ -6258,7 +6259,7 @@
           <t>Intelligent 911 platform streaming device location and data to dispatch - exhibited at APCO 2026, IAFC FRI 2026, Illinois Chapter of APCO 2026</t>
         </is>
       </c>
-      <c r="F183" s="9" t="inlineStr">
+      <c r="F183" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Join our Go-To-Market Talent Commu only</t>
         </is>
@@ -6590,7 +6591,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6619,7 @@
           <t>Pediatric emergency dosing system and app for EMS agencies</t>
         </is>
       </c>
-      <c r="F195" s="10" t="inlineStr">
+      <c r="F195" s="9" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive</t>
         </is>
@@ -6738,7 +6739,7 @@
           <t>Mobile incident command and response for fire/EMS departments - exhibited at IAFC FRI 2026</t>
         </is>
       </c>
-      <c r="F199" s="10" t="inlineStr">
+      <c r="F199" s="9" t="inlineStr">
         <is>
           <t>Yes - Regional Account Executive</t>
         </is>
@@ -6918,7 +6919,7 @@
           <t>911 call routing, Viper call handling and NG911 for PSAPs - exhibited at APCO 2026, Illinois Chapter of APCO 2026</t>
         </is>
       </c>
-      <c r="F205" s="10" t="inlineStr">
+      <c r="F205" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -7038,7 +7039,7 @@
           <t>AI triage and quality assurance for emergency dispatch centers</t>
         </is>
       </c>
-      <c r="F209" s="9" t="inlineStr">
+      <c r="F209" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - GTM Engineer only</t>
         </is>
@@ -7228,7 +7229,7 @@
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7257,7 @@
           <t>Mass notification and critical event management platform - exhibited at Connecticut Conference of Municipalities 2026</t>
         </is>
       </c>
-      <c r="F217" s="10" t="inlineStr">
+      <c r="F217" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (United Kingdom)</t>
         </is>
@@ -7376,7 +7377,7 @@
           <t>SARA situational awareness and mass notification for schools, senior living, and gov facilities</t>
         </is>
       </c>
-      <c r="F221" s="9" t="inlineStr">
+      <c r="F221" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -7730,9 +7731,9 @@
           <t>Sells P25 two-way radios, base stations and repeaters to public safety agencies and first responders - exhibited at APCO 2026</t>
         </is>
       </c>
-      <c r="F233" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F233" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Regional Sales Manager (Remote Worker - N/)</t>
         </is>
       </c>
     </row>
@@ -7754,9 +7755,9 @@
           <t>HigherGround sells call recording, live 911 call streaming and quality assurance software to public safety communications centers and contact centers - exhibited at APCO 2026, Illinois Chapter of APCO 2026</t>
         </is>
       </c>
-      <c r="F234" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F234" s="8" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7805,7 @@
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -7826,9 +7827,9 @@
           <t>Makes DiagnostX over-the-air analyzers and software that monitor two-way radio health for public safety agencies and their radio technicians - exhibited at APCO 2026</t>
         </is>
       </c>
-      <c r="F237" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F237" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7877,7 @@
       </c>
       <c r="F239" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7901,7 @@
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -7922,9 +7923,9 @@
           <t>Syniverse provides mobile messaging, connectivity and private wireless network services to first responders and government agencies - exhibited at APCO 2026</t>
         </is>
       </c>
-      <c r="F241" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F241" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Sales Director (Hong Kong)</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8163,7 @@
           <t>CID Net inmate calling (450+ facilities), facility monitoring, and family apps</t>
         </is>
       </c>
-      <c r="F249" s="9" t="inlineStr">
+      <c r="F249" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -8284,7 +8285,7 @@
       </c>
       <c r="F253" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9261,7 @@
           <t>Data and case-management tools for state corrections and supervision agencies</t>
         </is>
       </c>
-      <c r="F286" s="11" t="inlineStr">
+      <c r="F286" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - State Partnerships Manager only</t>
         </is>
@@ -9410,7 +9411,7 @@
           <t>Community corrections supervision and electronic monitoring for courts</t>
         </is>
       </c>
-      <c r="F291" s="10" t="inlineStr">
+      <c r="F291" s="9" t="inlineStr">
         <is>
           <t>Yes - Regional Sales Manager - Southwest (remote, remote, US)</t>
         </is>
@@ -9530,7 +9531,7 @@
       </c>
       <c r="F295" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10209,7 @@
           <t>AI police report writing and investigation software - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F320" s="11" t="inlineStr">
+      <c r="F320" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -10232,9 +10233,9 @@
           <t>Public safety CAD, RMS, jail software - exhibited at IACP 2026, APCO 2026</t>
         </is>
       </c>
-      <c r="F321" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F321" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10573,7 @@
       </c>
       <c r="F335" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10597,7 @@
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -10690,9 +10691,9 @@
           <t>Justice and public safety records software - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F340" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F340" s="10" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -10916,7 +10917,7 @@
           <t>Endpoint management and IT automation software - exhibited at NSA 2026, GMIS International 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F349" s="9" t="inlineStr">
+      <c r="F349" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -11060,9 +11061,9 @@
           <t>First responder peer support and wellness app - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F355" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F355" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -11134,7 +11135,7 @@
       </c>
       <c r="F358" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11187,7 @@
       </c>
       <c r="F360" s="4" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 522 for https://renvizon.com/career</t>
         </is>
       </c>
     </row>
@@ -11236,7 +11237,7 @@
           <t>DigiTICKET electronic citation software - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F362" s="11" t="inlineStr">
+      <c r="F362" s="10" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -11504,7 +11505,7 @@
       </c>
       <c r="F373" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11713,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/19/26)</t>
+          <t>Hiring AEs? (10/20/26)</t>
         </is>
       </c>
     </row>
@@ -11908,7 +11909,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11933,7 @@
       </c>
       <c r="F10" s="63" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11954,9 +11955,9 @@
           <t>Innovaccer sells a healthcare data and AI platform to health systems and payers, and to state agencies for Medicaid, public health and health information exchange - exhibited at Healthcare IT Connect 2026</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Yes - 4426-Senior Account Executive- Sal (Noida)</t>
         </is>
       </c>
     </row>
@@ -11980,7 +11981,7 @@
       </c>
       <c r="F12" s="63" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -12050,9 +12051,9 @@
           <t>Sells health data platforms, interoperability and health information exchange software to state and local health and human services agencies - exhibited at Healthcare IT Connect 2026</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -12098,9 +12099,9 @@
           <t>Patagonia Health sells electronic health record, practice management and billing software to public health departments and state health agencies - exhibited at NACCHO 360 2026</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -12148,7 +12149,7 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -12326,7 +12327,7 @@
           <t>Curam social program management for state health and human services - exhibited at Healthcare IT Connect 2026, APHSA 2026, SALGBA 2026</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>Yes - Commercial Account Executive, Truv (Remote – United St)</t>
         </is>
@@ -12686,9 +12687,9 @@
           <t>SNAP and EBT benefits mobile app for recipients, plus Propel for States tooling for state benefits agencies - exhibited at APHSA 2026</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Customer Success Manager only</t>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -13024,7 +13025,7 @@
       </c>
       <c r="F50" s="63" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13049,7 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -13096,7 +13097,7 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -13118,9 +13119,9 @@
           <t>Sells income, employment and asset verification software to state and local agencies that run Medicaid, SNAP and other benefit programs - exhibited at APHSA 2026, Healthcare IT Connect 2026</t>
         </is>
       </c>
-      <c r="F54" s="63" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F54" s="64" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Solutions Architect only</t>
         </is>
       </c>
     </row>
@@ -13142,9 +13143,9 @@
           <t>Verato sells cloud master data management and identity resolution software to healthcare organizations and state and local Medicaid and human services agencies - exhibited at Healthcare IT Connect 2026, MESC 2026</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Customer Success Manager, Growth P only</t>
         </is>
       </c>
     </row>
@@ -13166,9 +13167,9 @@
           <t>Sells payment accuracy, risk adjustment and data exchange software to health plans and to state Medicaid and federal health agencies - exhibited at NHCAA 2025</t>
         </is>
       </c>
-      <c r="F56" s="63" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F56" s="64" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Team Lead, Revenue Cycle only</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13481,7 @@
           <t>Care coordination and PDMP network software (PMP AWARxE, OpenBeds) for states, counties, and health systems (Appriss lineage)</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="F67" s="9" t="inlineStr">
         <is>
           <t>Yes - Bamboo Bridge Strategic Account Ma</t>
         </is>
@@ -14038,7 +14039,7 @@
           <t>Human services EHR and care coordination software for behavioral health, residential, vocational rehab, and food assistance providers - exhibited at NatCon 2026</t>
         </is>
       </c>
-      <c r="F87" s="10" t="inlineStr">
+      <c r="F87" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Remote)</t>
         </is>
@@ -14248,7 +14249,7 @@
           <t>AI clinical documentation and chart auditing platform purpose-built for behavioral health providers including CCBHCs and human services organizations - exhibited at NatCon 2026</t>
         </is>
       </c>
-      <c r="F95" s="9" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - VP of Revenue only</t>
         </is>
@@ -14280,7 +14281,7 @@
       </c>
       <c r="F96" s="63" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://greenspacehealth.co</t>
         </is>
       </c>
     </row>
@@ -14302,7 +14303,7 @@
           <t>Accredited continuing-education, AI practice simulation and certification platform for behavioral health clinicians and the organizations that employ them - exhibited at NatCon 2026</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -14590,7 +14591,7 @@
       </c>
       <c r="F108" s="63" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14615,7 @@
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -14666,7 +14667,7 @@
           <t>Social care coordination network connecting health and social service referrals for govs and payers - exhibited at MESC 2026</t>
         </is>
       </c>
-      <c r="F111" s="9" t="inlineStr">
+      <c r="F111" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Executive - Flori only</t>
         </is>
@@ -14786,7 +14787,7 @@
           <t>Clarity HMIS and homelessness response systems for counties and CoCs</t>
         </is>
       </c>
-      <c r="F115" s="9" t="inlineStr">
+      <c r="F115" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
@@ -14900,9 +14901,9 @@
           <t>Pear Suite sells care management and billing software for community health workers to states, community-based organizations, hubs and health plans - exhibited at NACCHO 360 2026</t>
         </is>
       </c>
-      <c r="F119" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Community Partnership Manager (Acc only</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15525,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/19/26)</t>
+          <t>Hiring AEs? (10/20/26)</t>
         </is>
       </c>
     </row>
@@ -15692,7 +15693,7 @@
           <t>Course evaluation, survey, and AI feedback analysis software - Blue, MLY, and Metrics That Matter - for universities and corporate learning teams - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Manager</t>
         </is>
@@ -15980,7 +15981,7 @@
           <t>Peer review, group work, and AI feedback tools that plug into university learning management systems - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Texas) (US Remote)</t>
         </is>
@@ -16158,7 +16159,7 @@
           <t>Canvas learning management system plus assessment and credentialing software for universities, school districts, and government training programs - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>Yes - Senior Account Executive - Canvas  (US-REMOTE)</t>
         </is>
@@ -16772,7 +16773,7 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -17038,7 +17039,7 @@
           <t>Residence life and student housing management software covering applications, room assignment, billing and community programming for universities and colleges - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="F55" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, EMEA (UK - Remote)</t>
         </is>
@@ -17624,7 +17625,7 @@
           <t>Degree planning, advising, transfer pathway and registration software for public universities, community colleges and private institutions - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Solutions Consultant only</t>
         </is>
@@ -17956,7 +17957,7 @@
       </c>
       <c r="F90" s="69" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -17978,9 +17979,9 @@
           <t>Delinea sells privileged access management and identity security software, including Secret Server and Privilege Manager, to universities and public sector agencies - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Enterprise Account Manager (Home Office (Italy)</t>
         </is>
       </c>
     </row>
@@ -18004,7 +18005,7 @@
       </c>
       <c r="F92" s="69" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -18028,7 +18029,7 @@
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -18052,7 +18053,7 @@
       </c>
       <c r="F94" s="69" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -18074,9 +18075,9 @@
           <t>ESET sells endpoint protection and other cybersecurity software to schools, universities, governments and businesses - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -18100,7 +18101,7 @@
       </c>
       <c r="F96" s="69" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18125,7 @@
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -18146,9 +18147,9 @@
           <t>Hyland sells content management and document automation software to colleges and universities for admissions, financial aid, HR and registrar offices - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F98" s="69" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F98" s="71" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive - Strategic</t>
         </is>
       </c>
     </row>
@@ -18172,7 +18173,7 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -18196,7 +18197,7 @@
       </c>
       <c r="F100" s="69" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t xml:space="preserve">Unknown - robots.txt on corp.kaltura.com answered </t>
         </is>
       </c>
     </row>
@@ -18218,9 +18219,9 @@
           <t>IT infrastructure, network and cloud monitoring software sold to colleges, universities, public-sector agencies and businesses - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F101" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -18242,9 +18243,9 @@
           <t>Mentimeter sells live polling, quiz and survey software for lectures and meetings, with discounted and campus-wide plans for schools and universities - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F102" s="69" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F102" s="71" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -18268,7 +18269,7 @@
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -18290,9 +18291,9 @@
           <t>Panopto sells video capture and video management software for lecture recording to colleges and universities - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F104" s="69" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F104" s="71" t="inlineStr">
+        <is>
+          <t>Yes - Account Manager, Americas (Remote - US)</t>
         </is>
       </c>
     </row>
@@ -18340,7 +18341,7 @@
       </c>
       <c r="F106" s="69" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -18364,7 +18365,7 @@
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -18386,9 +18387,9 @@
           <t>Sells identity security software that automates user provisioning, access reviews and access control to colleges, universities and other large organizations - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F108" s="69" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F108" s="71" t="inlineStr">
+        <is>
+          <t>Yes - Commercial Account Executive (Remote (New York, )</t>
         </is>
       </c>
     </row>
@@ -18410,9 +18411,9 @@
           <t>Exam and interview integrity software that gives universities, employers and testing programs evidence reports for human review of assessments - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -18436,7 +18437,7 @@
       </c>
       <c r="F110" s="69" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -18458,9 +18459,9 @@
           <t>Sells cybersecurity software and managed detection and response services to K-12 schools, colleges and universities - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F111" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive (via third party (Morocco)</t>
         </is>
       </c>
     </row>
@@ -18512,7 +18513,7 @@
           <t>Student billing, payments, net price calculator, and pre-collections software for colleges and universities - exhibited at NACUBO 2026, NASFAA 2026</t>
         </is>
       </c>
-      <c r="F113" s="9" t="inlineStr">
+      <c r="F113" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Business Development Representativ only</t>
         </is>
@@ -18740,7 +18741,7 @@
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -18762,9 +18763,9 @@
           <t>Sells financial reporting, ACFR preparation and audit software to higher education finance teams and government agencies - exhibited at NACUBO 2026, GFOA 2026</t>
         </is>
       </c>
-      <c r="F122" s="69" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F122" s="71" t="inlineStr">
+        <is>
+          <t>Yes - Senior Account Executive (London)</t>
         </is>
       </c>
     </row>
@@ -18787,7 +18788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -18826,7 +18827,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/19/26)</t>
+          <t>Hiring AEs? (10/20/26)</t>
         </is>
       </c>
     </row>
@@ -19096,7 +19097,7 @@
           <t>Grant and program administration software for affordable housing, disaster recovery, vouchers and energy rebate programs run by local and state agencies - exhibited at NAHRO 2026, NCSHA 2026</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>Yes - Technical Account Manager, Strateg (Atlanta)</t>
         </is>
@@ -19149,12 +19150,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Housing Choice Voucher, public housing and grants management software for public housing authorities - exhibited at NAHRO 2026</t>
+          <t>Housing Choice Voucher, public housing and grants management software for public housing authorities - exhibited at NAHRO 2026, NCSHA 2026</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -19176,9 +19177,9 @@
           <t>Sells Housing Forge, a software platform for public housing authorities and state housing agencies that covers applications, waitlists, screening and voucher administration - exhibited at NAHRO 2026</t>
         </is>
       </c>
-      <c r="F14" s="75" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F14" s="76" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -19257,49 +19258,43 @@
     <row r="18">
       <c r="A18" s="73" t="inlineStr">
         <is>
-          <t>Localintel</t>
-        </is>
-      </c>
-      <c r="B18" s="73" t="inlineStr">
-        <is>
-          <t>Calgary, Canada</t>
-        </is>
-      </c>
-      <c r="C18" s="74" t="n">
-        <v>2016</v>
-      </c>
+          <t>HDS Companies</t>
+        </is>
+      </c>
+      <c r="B18" s="73" t="n"/>
+      <c r="C18" s="74" t="n"/>
       <c r="D18" s="73" t="inlineStr">
         <is>
-          <t>Planning &amp; Economic Development</t>
+          <t>Housing &amp; Assistance</t>
         </is>
       </c>
       <c r="E18" s="73" t="inlineStr">
         <is>
-          <t>Community data, mapping, and publishable content tools for economic development, planning, and communications teams in cities and counties - exhibited at IEDC 2026</t>
+          <t>Housing finance software for housing finance agencies: multifamily and Section 8 contract administration, single-family programs, loan servicing, grants and compliance - exhibited at NCSHA 2026</t>
         </is>
       </c>
       <c r="F18" s="75" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Resimplifi</t>
+          <t>HOTB Software Solutions</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Planning &amp; Economic Development</t>
+          <t>Housing &amp; Assistance</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Automatically maintained commercial sites and buildings listing database for economic development organizations - exhibited at IEDC 2026</t>
+          <t>Cloud software for government assistance programs: grant management, loan reservation and down payment assistance, and LIHEAP energy program administration - exhibited at NCSHA 2026</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -19311,11 +19306,17 @@
     <row r="20">
       <c r="A20" s="73" t="inlineStr">
         <is>
-          <t>GIS WebTech</t>
-        </is>
-      </c>
-      <c r="B20" s="73" t="n"/>
-      <c r="C20" s="74" t="n"/>
+          <t>Localintel</t>
+        </is>
+      </c>
+      <c r="B20" s="73" t="inlineStr">
+        <is>
+          <t>Calgary, Canada</t>
+        </is>
+      </c>
+      <c r="C20" s="74" t="n">
+        <v>2016</v>
+      </c>
       <c r="D20" s="73" t="inlineStr">
         <is>
           <t>Planning &amp; Economic Development</t>
@@ -19323,7 +19324,7 @@
       </c>
       <c r="E20" s="73" t="inlineStr">
         <is>
-          <t>GURU site selection, property data and property tax mapping platform for economic development organizations and assessor offices - exhibited at IEDC 2026</t>
+          <t>Community data, mapping, and publishable content tools for economic development, planning, and communications teams in cities and counties - exhibited at IEDC 2026</t>
         </is>
       </c>
       <c r="F20" s="75" t="inlineStr">
@@ -19335,7 +19336,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>PolicyMap</t>
+          <t>Resimplifi</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
@@ -19347,17 +19348,65 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>Automatically maintained commercial sites and buildings listing database for economic development organizations - exhibited at IEDC 2026</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="73" t="inlineStr">
+        <is>
+          <t>GIS WebTech</t>
+        </is>
+      </c>
+      <c r="B22" s="73" t="n"/>
+      <c r="C22" s="74" t="n"/>
+      <c r="D22" s="73" t="inlineStr">
+        <is>
+          <t>Planning &amp; Economic Development</t>
+        </is>
+      </c>
+      <c r="E22" s="73" t="inlineStr">
+        <is>
+          <t>GURU site selection, property data and property tax mapping platform for economic development organizations and assessor offices - exhibited at IEDC 2026</t>
+        </is>
+      </c>
+      <c r="F22" s="75" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>PolicyMap</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Planning &amp; Economic Development</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t>Online mapping and neighborhood data platform sold to state and local agencies, public libraries and universities for planning, community development and grant work - exhibited at PLA 2026</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F21"/>
+  <autoFilter ref="A1:F23"/>
   <dataValidations count="1">
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid category" error="Pick one of: Housing &amp; Assistance, Planning &amp; Economic Development, Suppliers &amp; Services" type="list">
       <formula1>"Housing &amp; Assistance,Planning &amp; Economic Development,Suppliers &amp; Services"</formula1>
@@ -19375,7 +19424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F252"/>
+  <dimension ref="A1:F253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -19414,7 +19463,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/19/26)</t>
+          <t>Hiring AEs? (10/20/26)</t>
         </is>
       </c>
     </row>
@@ -19472,7 +19521,7 @@
           <t>Routing, in-cab fleet tech, and resident apps for waste operations - exhibited at SWANA WASTECON 2025</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
@@ -19532,7 +19581,7 @@
           <t>AI robotic sorting systems for recycling facilities (MRFs) - exhibited at SWANA WASTECON 2025, WasteExpo 2027</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Director, Commercial Origination &amp; only</t>
         </is>
@@ -20010,7 +20059,7 @@
           <t>AI robotics and recovery analytics for material recovery facilities</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -20186,7 +20235,7 @@
           <t>Waste collection route optimization and sensor platform for municipalities</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -20734,7 +20783,7 @@
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20811,7 @@
           <t>Traffic signal controllers, cabinets, and intersection management systems</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F47" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -20824,7 +20873,7 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Technical Customer Success Manager only</t>
+          <t>Yes - Enterprise Account Executive, Opti (California)</t>
         </is>
       </c>
     </row>
@@ -20882,7 +20931,7 @@
           <t>AI stop-sign and speed safety cameras for local streets - exhibited at Maryland Municipal League 2026</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (College Park, MD)</t>
         </is>
@@ -20942,7 +20991,7 @@
           <t>Speed, volume, and congestion analytics for public works and police</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Manager</t>
         </is>
@@ -21062,7 +21111,7 @@
           <t>Vehicle-mounted lidar + AI for pavement condition, sidewalk ADA, and street asset inventories - exhibited at NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="9" t="inlineStr">
         <is>
           <t>Yes - Senior Account Executive (Boston, Massachuse)</t>
         </is>
@@ -21362,7 +21411,7 @@
           <t>Vehicle-captured 360 street imagery and lidar with AI analytics for local governments and utilities</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="F67" s="9" t="inlineStr">
         <is>
           <t>Yes - Senior Account Manager Poland (Remote job)</t>
         </is>
@@ -21662,7 +21711,7 @@
           <t>Connected-vehicle ITS and the Glance smart-city platform: signal monitoring, preemption, school beacons - exhibited at IAFC FRI 2026, APTA 2026, ITS America 2026</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -22580,53 +22629,47 @@
       </c>
       <c r="F108" s="15" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Xylem</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>Washington, DC</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="n">
-        <v>2011</v>
-      </c>
+          <t>Oculus Rail</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n"/>
+      <c r="C109" s="6" t="n"/>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Streets</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>Water infrastructure: pumps, treatment, smart meters (Sensus), and analytics - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
-        </is>
-      </c>
-      <c r="F109" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Executive Sales Representative - N (12 Locations)</t>
+          <t>Blocked railroad crossing sensors and data: a municipal dashboard, app and API giving municipalities, transportation agencies and first responders real-time crossing status - exhibited at NLC City Summit 2026</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>Badger Meter</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>Milwaukee, WI</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="C110" s="14" t="n">
-        <v>1905</v>
+        <v>2011</v>
       </c>
       <c r="D110" s="13" t="inlineStr">
         <is>
@@ -22635,28 +22678,28 @@
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>Water meters and ORION AMI networks for utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+          <t>Water infrastructure: pumps, treatment, smart meters (Sensus), and analytics - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F110" s="16" t="inlineStr">
         <is>
-          <t>Yes - Municipal Account Manager- South (3 Locations)</t>
+          <t>Yes - Executive Sales Representative - N (12 Locations)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Mueller Water Products</t>
+          <t>Badger Meter</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Milwaukee, WI</t>
         </is>
       </c>
       <c r="C111" s="6" t="n">
-        <v>1857</v>
+        <v>1905</v>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
@@ -22665,28 +22708,28 @@
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>Hydrants, valves, and acoustic leak detection for water systems - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
-        </is>
-      </c>
-      <c r="F111" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Jr. Sales Representative (Remote - Tennessee)</t>
+          <t>Water meters and ORION AMI networks for utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sales Enablement Analyst Intern only</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>120Water</t>
+          <t>Mueller Water Products</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>Zionsville, IN</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="C112" s="14" t="n">
-        <v>2016</v>
+        <v>1857</v>
       </c>
       <c r="D112" s="13" t="inlineStr">
         <is>
@@ -22695,28 +22738,28 @@
       </c>
       <c r="E112" s="13" t="inlineStr">
         <is>
-          <t>Lead service line inventories, sampling, and compliance software - exhibited at AWWA ACE 2026</t>
-        </is>
-      </c>
-      <c r="F112" s="15" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Hydrants, valves, and acoustic leak detection for water systems - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+        </is>
+      </c>
+      <c r="F112" s="16" t="inlineStr">
+        <is>
+          <t>Yes - Jr. Sales Representative (Remote - Tennessee)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Klir</t>
+          <t>120Water</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Dublin, Ireland</t>
+          <t>Zionsville, IN</t>
         </is>
       </c>
       <c r="C113" s="6" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
@@ -22725,28 +22768,28 @@
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>Permitting, compliance, and workflow software for water utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
-        </is>
-      </c>
-      <c r="F113" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Senior Customer Success Manager only</t>
+          <t>Lead service line inventories, sampling, and compliance software - exhibited at AWWA ACE 2026</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>VODA.ai</t>
+          <t>Klir</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Dublin, Ireland</t>
         </is>
       </c>
       <c r="C114" s="14" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D114" s="13" t="inlineStr">
         <is>
@@ -22755,28 +22798,28 @@
       </c>
       <c r="E114" s="13" t="inlineStr">
         <is>
-          <t>AI pipe-failure prediction for main replacement planning - exhibited at AWWA ACE 2026</t>
+          <t>Permitting, compliance, and workflow software for water utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F114" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>KETOS</t>
+          <t>VODA.ai</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="C115" s="6" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
@@ -22785,7 +22828,7 @@
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>Automated water quality monitoring as a service</t>
+          <t>AI pipe-failure prediction for main replacement planning - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
@@ -22797,16 +22840,16 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>ASTERRA</t>
+          <t>KETOS</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="C116" s="14" t="n">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="D116" s="13" t="inlineStr">
         <is>
@@ -22815,7 +22858,7 @@
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>Satellite-based leak detection and underground pipe assessment - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+          <t>Automated water quality monitoring as a service</t>
         </is>
       </c>
       <c r="F116" s="15" t="inlineStr">
@@ -22827,16 +22870,16 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>ASTERRA</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="C117" s="6" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
@@ -22845,28 +22888,28 @@
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>AI defect detection and coding for sewer inspection video - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
-        </is>
-      </c>
-      <c r="F117" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Revenue Operations Analyst only</t>
+          <t>Satellite-based leak detection and underground pipe assessment - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>RedZone Robotics</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Walnut Creek, CA</t>
         </is>
       </c>
       <c r="C118" s="14" t="n">
-        <v>1987</v>
+        <v>2019</v>
       </c>
       <c r="D118" s="13" t="inlineStr">
         <is>
@@ -22875,28 +22918,28 @@
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>Robotic sewer inspection and condition assessment services - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
-        </is>
-      </c>
-      <c r="F118" s="16" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>AI defect detection and coding for sewer inspection video - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+        </is>
+      </c>
+      <c r="F118" s="17" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Revenue Operations Analyst only</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Forerunner</t>
+          <t>RedZone Robotics</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Brooklyn, NY</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="C119" s="6" t="n">
-        <v>2019</v>
+        <v>1987</v>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
@@ -22905,28 +22948,28 @@
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>Floodplain management software: NFIP/CRS compliance, elevation certificates; $26.3M Series B - exhibited at StormCon 2026, ICC 2026, NLC City Summit 2026</t>
-        </is>
-      </c>
-      <c r="F119" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive (Portland, ME)</t>
+          <t>Robotic sewer inspection and condition assessment services - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>ISeeChange</t>
+          <t>Forerunner</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
-          <t>New Orleans, LA</t>
+          <t>Brooklyn, NY</t>
         </is>
       </c>
       <c r="C120" s="14" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="D120" s="13" t="inlineStr">
         <is>
@@ -22935,28 +22978,28 @@
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>Community climate and flood reporting paired with sensor data for cities and utilities</t>
-        </is>
-      </c>
-      <c r="F120" s="15" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Floodplain management software: NFIP/CRS compliance, elevation certificates; $26.3M Series B - exhibited at StormCon 2026, ICC 2026, NLC City Summit 2026</t>
+        </is>
+      </c>
+      <c r="F120" s="16" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive (Portland, ME)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>VAPAR</t>
+          <t>ISeeChange</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Sydney, Australia</t>
+          <t>New Orleans, LA</t>
         </is>
       </c>
       <c r="C121" s="6" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
@@ -22965,28 +23008,28 @@
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>AI CCTV sewer and stormwater pipe condition assessment for councils and utilities - exhibited at WEFTEC 2026</t>
-        </is>
-      </c>
-      <c r="F121" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Community climate and flood reporting paired with sensor data for cities and utilities</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>CivilGrid</t>
+          <t>VAPAR</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Sydney, Australia</t>
         </is>
       </c>
       <c r="C122" s="14" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="D122" s="13" t="inlineStr">
         <is>
@@ -22995,28 +23038,28 @@
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>Underground utility, geotech, and environmental records aggregated into one map for capital projects</t>
+          <t>AI CCTV sewer and stormwater pipe condition assessment for councils and utilities - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F122" s="16" t="inlineStr">
         <is>
-          <t>Yes - Account Executive - Engineering Fi (Remote)</t>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Master Meter</t>
+          <t>CivilGrid</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Mansfield, TX</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="C123" s="6" t="n">
-        <v>1980</v>
+        <v>2021</v>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
@@ -23025,28 +23068,28 @@
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>Octave ultrasonic water meters, Allegro AMI networks, and Harmony meter data management (Arad Ltd.) - exhibited at NLC City Summit 2026, AWWA ACE 2026</t>
-        </is>
-      </c>
-      <c r="F123" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Underground utility, geotech, and environmental records aggregated into one map for capital projects</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Business Development Representativ only</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>Banyan Water</t>
+          <t>Master Meter</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Mansfield, TX</t>
         </is>
       </c>
       <c r="C124" s="14" t="n">
-        <v>2011</v>
+        <v>1980</v>
       </c>
       <c r="D124" s="13" t="inlineStr">
         <is>
@@ -23055,28 +23098,28 @@
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>Water use analytics and leak detection for municipal and campus grounds</t>
-        </is>
-      </c>
-      <c r="F124" s="16" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Octave ultrasonic water meters, Allegro AMI networks, and Harmony meter data management (Arad Ltd.) - exhibited at NLC City Summit 2026, AWWA ACE 2026</t>
+        </is>
+      </c>
+      <c r="F124" s="15" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Neptune Technology Group</t>
+          <t>Banyan Water</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Tallassee, Alabama</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="C125" s="6" t="n">
-        <v>1892</v>
+        <v>2011</v>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
@@ -23085,28 +23128,28 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>Water meters and AMI networks for municipal water utilities - exhibited at AWWA ACE 2026</t>
-        </is>
-      </c>
-      <c r="F125" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - HTTP 403 for https://www.neptunetg.com/c</t>
+          <t>Water use analytics and leak detection for municipal and campus grounds</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>Kamstrup</t>
+          <t>Neptune Technology Group</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
         <is>
-          <t>Skanderborg, Denmark</t>
+          <t>Tallassee, Alabama</t>
         </is>
       </c>
       <c r="C126" s="14" t="n">
-        <v>1946</v>
+        <v>1892</v>
       </c>
       <c r="D126" s="13" t="inlineStr">
         <is>
@@ -23115,28 +23158,28 @@
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>Smart water and heat metering systems sold to US municipal utilities</t>
+          <t>Water meters and AMI networks for municipal water utilities - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F126" s="15" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 403 for https://www.neptunetg.com/c</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Diehl Metering</t>
+          <t>Kamstrup</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Nuremberg, Germany</t>
+          <t>Skanderborg, Denmark</t>
         </is>
       </c>
       <c r="C127" s="6" t="n">
-        <v>1864</v>
+        <v>1946</v>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
@@ -23145,7 +23188,7 @@
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>Smart water meters and AMI for municipal and district water utilities - exhibited at AWWA ACE 2026</t>
+          <t>Smart water and heat metering systems sold to US municipal utilities</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
@@ -23157,16 +23200,16 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>Zenner USA</t>
+          <t>Diehl Metering</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
         <is>
-          <t>Banning, California</t>
+          <t>Nuremberg, Germany</t>
         </is>
       </c>
       <c r="C128" s="14" t="n">
-        <v>1903</v>
+        <v>1864</v>
       </c>
       <c r="D128" s="13" t="inlineStr">
         <is>
@@ -23175,28 +23218,28 @@
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>Water meters, AMR/AMI and metering services for municipal utilities - exhibited at AWWA ACE 2026</t>
+          <t>Smart water meters and AMI for municipal and district water utilities - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F128" s="15" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Innovyze (Autodesk Water)</t>
+          <t>Zenner USA</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Portland, Oregon</t>
+          <t>Banning, California</t>
         </is>
       </c>
       <c r="C129" s="6" t="n">
-        <v>1996</v>
+        <v>1903</v>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
@@ -23205,28 +23248,28 @@
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>Hydraulic modeling and asset analytics for water and wastewater utilities</t>
+          <t>Water meters, AMR/AMI and metering services for municipal utilities - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>Aquatic Informatics (Veralto)</t>
+          <t>Innovyze (Autodesk Water)</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
         <is>
-          <t>Vancouver, British Columbia, Canada</t>
+          <t>Portland, Oregon</t>
         </is>
       </c>
       <c r="C130" s="14" t="n">
-        <v>2003</v>
+        <v>1996</v>
       </c>
       <c r="D130" s="13" t="inlineStr">
         <is>
@@ -23235,28 +23278,28 @@
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>Water data management (AQUARIUS, WaterTrax) for utilities and environmental agencies - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+          <t>Hydraulic modeling and asset analytics for water and wastewater utilities</t>
         </is>
       </c>
       <c r="F130" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Hach (Veralto)</t>
+          <t>Aquatic Informatics (Veralto)</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Loveland, Colorado</t>
+          <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
       <c r="C131" s="6" t="n">
-        <v>1947</v>
+        <v>2003</v>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
@@ -23265,7 +23308,7 @@
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>Water quality instrumentation and analytics for municipal water and wastewater plants - exhibited at WEFTEC 2026</t>
+          <t>Water data management (AQUARIUS, WaterTrax) for utilities and environmental agencies - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
@@ -23277,16 +23320,16 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>In-Situ</t>
+          <t>Hach (Veralto)</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
         <is>
-          <t>Fort Collins, Colorado</t>
+          <t>Loveland, Colorado</t>
         </is>
       </c>
       <c r="C132" s="14" t="n">
-        <v>1976</v>
+        <v>1947</v>
       </c>
       <c r="D132" s="13" t="inlineStr">
         <is>
@@ -23295,28 +23338,28 @@
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>Water quality and level monitoring instruments for agencies and utilities - exhibited at AWWA ACE 2026, WEFTEC 2026, StormCon 2026</t>
+          <t>Water quality instrumentation and analytics for municipal water and wastewater plants - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F132" s="15" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://in-situ.com/careers</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>FATHOM (Global Water Innovations)</t>
+          <t>In-Situ</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Phoenix, Arizona</t>
+          <t>Fort Collins, Colorado</t>
         </is>
       </c>
       <c r="C133" s="6" t="n">
-        <v>2011</v>
+        <v>1976</v>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
@@ -23325,28 +23368,28 @@
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>Utility billing, metering data and customer platform for water utilities</t>
+          <t>Water quality and level monitoring instruments for agencies and utilities - exhibited at AWWA ACE 2026, WEFTEC 2026, StormCon 2026</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 403 for https://in-situ.com/careers</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>WaterSmart Software (VertexOne)</t>
+          <t>FATHOM (Global Water Innovations)</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
         <is>
-          <t>San Francisco, California</t>
+          <t>Phoenix, Arizona</t>
         </is>
       </c>
       <c r="C134" s="14" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="D134" s="13" t="inlineStr">
         <is>
@@ -23355,28 +23398,28 @@
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>Customer engagement and water use analytics for municipal water utilities</t>
+          <t>Utility billing, metering data and customer platform for water utilities</t>
         </is>
       </c>
       <c r="F134" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Gutermann</t>
+          <t>WaterSmart Software (VertexOne)</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Schwerzenbach, Switzerland</t>
+          <t>San Francisco, California</t>
         </is>
       </c>
       <c r="C135" s="6" t="n">
-        <v>1950</v>
+        <v>2009</v>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
@@ -23385,28 +23428,28 @@
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>Acoustic leak detection and district metering systems for water utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+          <t>Customer engagement and water use analytics for municipal water utilities</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>Ovarro</t>
+          <t>Gutermann</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
         <is>
-          <t>Taunton, United Kingdom</t>
+          <t>Schwerzenbach, Switzerland</t>
         </is>
       </c>
       <c r="C136" s="14" t="n">
-        <v>2021</v>
+        <v>1950</v>
       </c>
       <c r="D136" s="13" t="inlineStr">
         <is>
@@ -23415,28 +23458,28 @@
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>Leak detection, RTUs and network monitoring for water utilities</t>
+          <t>Acoustic leak detection and district metering systems for water utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F136" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>FIDO Tech</t>
+          <t>Ovarro</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Oxford, United Kingdom</t>
+          <t>Taunton, United Kingdom</t>
         </is>
       </c>
       <c r="C137" s="6" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
@@ -23445,7 +23488,7 @@
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>AI acoustic leak detection service for water utilities and municipalities - exhibited at AWWA ACE 2026</t>
+          <t>Leak detection, RTUs and network monitoring for water utilities</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
@@ -23457,16 +23500,16 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>Aquarius Spectrum</t>
+          <t>FIDO Tech</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
         <is>
-          <t>Yokneam, Israel</t>
+          <t>Oxford, United Kingdom</t>
         </is>
       </c>
       <c r="C138" s="14" t="n">
-        <v>2009</v>
+        <v>2016</v>
       </c>
       <c r="D138" s="13" t="inlineStr">
         <is>
@@ -23475,28 +23518,28 @@
       </c>
       <c r="E138" s="13" t="inlineStr">
         <is>
-          <t>Fixed acoustic leak monitoring sensors for municipal water networks</t>
+          <t>AI acoustic leak detection service for water utilities and municipalities - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F138" s="15" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Syrinix</t>
+          <t>Aquarius Spectrum</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Norwich, United Kingdom</t>
+          <t>Yokneam, Israel</t>
         </is>
       </c>
       <c r="C139" s="6" t="n">
-        <v>2004</v>
+        <v>2009</v>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
@@ -23505,28 +23548,28 @@
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>Pressure transient and pipeline monitoring hardware for water utilities</t>
+          <t>Fixed acoustic leak monitoring sensors for municipal water networks</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.badgermeter.com</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>Electro Scan</t>
+          <t>Syrinix</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
         <is>
-          <t>Sacramento, California</t>
+          <t>Norwich, United Kingdom</t>
         </is>
       </c>
       <c r="C140" s="14" t="n">
-        <v>2011</v>
+        <v>2004</v>
       </c>
       <c r="D140" s="13" t="inlineStr">
         <is>
@@ -23535,28 +23578,28 @@
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>Machine-based pipe defect and leak assessment for municipal sewer and water - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+          <t>Pressure transient and pipeline monitoring hardware for water utilities</t>
         </is>
       </c>
       <c r="F140" s="15" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - HTTP 403 for https://www.badgermeter.com</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>CUES (SPX)</t>
+          <t>Electro Scan</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Orlando, Florida</t>
+          <t>Sacramento, California</t>
         </is>
       </c>
       <c r="C141" s="6" t="n">
-        <v>1964</v>
+        <v>2011</v>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
@@ -23565,28 +23608,28 @@
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>Sewer inspection cameras, trucks and software for municipal collection systems - exhibited at Maryland Municipal League 2026, WEFTEC 2026</t>
-        </is>
-      </c>
-      <c r="F141" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Machine-based pipe defect and leak assessment for municipal sewer and water - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+        </is>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>Envirosight</t>
+          <t>CUES (SPX)</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
         <is>
-          <t>Randolph, New Jersey</t>
+          <t>Orlando, Florida</t>
         </is>
       </c>
       <c r="C142" s="14" t="n">
-        <v>2001</v>
+        <v>1964</v>
       </c>
       <c r="D142" s="13" t="inlineStr">
         <is>
@@ -23595,28 +23638,28 @@
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>Sewer inspection crawlers and push cameras for municipal wastewater agencies - exhibited at WEFTEC 2026</t>
-        </is>
-      </c>
-      <c r="F142" s="15" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Sewer inspection cameras, trucks and software for municipal collection systems - exhibited at Maryland Municipal League 2026, WEFTEC 2026</t>
+        </is>
+      </c>
+      <c r="F142" s="16" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>WinCan</t>
+          <t>Envirosight</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Dietikon, Switzerland</t>
+          <t>Randolph, New Jersey</t>
         </is>
       </c>
       <c r="C143" s="6" t="n">
-        <v>1989</v>
+        <v>2001</v>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
@@ -23625,7 +23668,7 @@
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>Sewer inspection data and reporting software for municipalities and contractors - exhibited at WEFTEC 2026</t>
+          <t>Sewer inspection crawlers and push cameras for municipal wastewater agencies - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
@@ -23637,16 +23680,16 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>SmartCover Systems</t>
+          <t>WinCan</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
         <is>
-          <t>Escondido, California</t>
+          <t>Dietikon, Switzerland</t>
         </is>
       </c>
       <c r="C144" s="14" t="n">
-        <v>2002</v>
+        <v>1989</v>
       </c>
       <c r="D144" s="13" t="inlineStr">
         <is>
@@ -23655,7 +23698,7 @@
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>Remote sewer level and overflow monitoring for municipal collection systems - exhibited at WEFTEC 2026</t>
+          <t>Sewer inspection data and reporting software for municipalities and contractors - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F144" s="15" t="inlineStr">
@@ -23667,16 +23710,16 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>ADS Environmental Services (IDEX)</t>
+          <t>SmartCover Systems</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Huntsville, Alabama</t>
+          <t>Escondido, California</t>
         </is>
       </c>
       <c r="C145" s="6" t="n">
-        <v>1975</v>
+        <v>2002</v>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
@@ -23685,28 +23728,28 @@
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>Sewer flow monitoring and I&amp;I analytics for municipal wastewater utilities - exhibited at WEFTEC 2026, StormCon 2026</t>
+          <t>Remote sewer level and overflow monitoring for municipal collection systems - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>InfoSense</t>
+          <t>ADS Environmental Services (IDEX)</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
         <is>
-          <t>Charlotte, North Carolina</t>
+          <t>Huntsville, Alabama</t>
         </is>
       </c>
       <c r="C146" s="14" t="n">
-        <v>2010</v>
+        <v>1975</v>
       </c>
       <c r="D146" s="13" t="inlineStr">
         <is>
@@ -23715,28 +23758,28 @@
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>SL-RAT acoustic sewer line assessment tools for municipal sewer agencies - exhibited at WEFTEC 2026</t>
+          <t>Sewer flow monitoring and I&amp;I analytics for municipal wastewater utilities - exhibited at WEFTEC 2026, StormCon 2026</t>
         </is>
       </c>
       <c r="F146" s="15" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Aquasight</t>
+          <t>InfoSense</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Troy, Michigan</t>
+          <t>Charlotte, North Carolina</t>
         </is>
       </c>
       <c r="C147" s="6" t="n">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
@@ -23745,28 +23788,28 @@
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>AI operations and forecasting software for water and wastewater utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
-        </is>
-      </c>
-      <c r="F147" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>SL-RAT acoustic sewer line assessment tools for municipal sewer agencies - exhibited at WEFTEC 2026</t>
+        </is>
+      </c>
+      <c r="F147" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>Pani Energy</t>
+          <t>Aquasight</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>Victoria, British Columbia, Canada</t>
+          <t>Troy, Michigan</t>
         </is>
       </c>
       <c r="C148" s="14" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="D148" s="13" t="inlineStr">
         <is>
@@ -23775,28 +23818,28 @@
       </c>
       <c r="E148" s="13" t="inlineStr">
         <is>
-          <t>AI performance software for water treatment and desalination operators</t>
-        </is>
-      </c>
-      <c r="F148" s="15" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>AI operations and forecasting software for water and wastewater utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+        </is>
+      </c>
+      <c r="F148" s="16" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Transcend</t>
+          <t>Pani Energy</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>New York, New York</t>
+          <t>Victoria, British Columbia, Canada</t>
         </is>
       </c>
       <c r="C149" s="6" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
@@ -23805,28 +23848,28 @@
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>Generative design software for water and wastewater treatment plant projects</t>
-        </is>
-      </c>
-      <c r="F149" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+          <t>AI performance software for water treatment and desalination operators</t>
+        </is>
+      </c>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>KISTERS</t>
+          <t>Transcend</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
         <is>
-          <t>Aachen, Germany</t>
+          <t>New York, New York</t>
         </is>
       </c>
       <c r="C150" s="14" t="n">
-        <v>1963</v>
+        <v>2016</v>
       </c>
       <c r="D150" s="13" t="inlineStr">
         <is>
@@ -23835,28 +23878,28 @@
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
-          <t>Hydrological and water data management systems for agencies and utilities</t>
-        </is>
-      </c>
-      <c r="F150" s="15" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Generative design software for water and wastewater treatment plant projects</t>
+        </is>
+      </c>
+      <c r="F150" s="17" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>Watchtower Robotics</t>
+          <t>KISTERS</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>Boston, Massachusetts</t>
+          <t>Aachen, Germany</t>
         </is>
       </c>
       <c r="C151" s="6" t="n">
-        <v>2018</v>
+        <v>1963</v>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
@@ -23865,28 +23908,28 @@
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>In-pipe leak detection robots for municipal water distribution systems</t>
+          <t>Hydrological and water data management systems for agencies and utilities</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>Trihedral Engineering</t>
+          <t>Watchtower Robotics</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
         <is>
-          <t>Bedford, Nova Scotia, Canada</t>
+          <t>Boston, Massachusetts</t>
         </is>
       </c>
       <c r="C152" s="14" t="n">
-        <v>1986</v>
+        <v>2018</v>
       </c>
       <c r="D152" s="13" t="inlineStr">
         <is>
@@ -23895,28 +23938,28 @@
       </c>
       <c r="E152" s="13" t="inlineStr">
         <is>
-          <t>VTScada SCADA software for municipal water and wastewater systems - exhibited at WEFTEC 2026, AWWA ACE 2026</t>
+          <t>In-pipe leak detection robots for municipal water distribution systems</t>
         </is>
       </c>
       <c r="F152" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>BlueConduit</t>
+          <t>Trihedral Engineering</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Ann Arbor, Michigan</t>
+          <t>Bedford, Nova Scotia, Canada</t>
         </is>
       </c>
       <c r="C153" s="6" t="n">
-        <v>2019</v>
+        <v>1986</v>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
@@ -23925,24 +23968,24 @@
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>Machine learning lead service line inventory and prediction for water utilities - exhibited at AWWA ACE 2026</t>
+          <t>VTScada SCADA software for municipal water and wastewater systems - exhibited at WEFTEC 2026, AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>Trinnex</t>
+          <t>BlueConduit</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
         <is>
-          <t>Boston, Massachusetts</t>
+          <t>Ann Arbor, Michigan</t>
         </is>
       </c>
       <c r="C154" s="14" t="n">
@@ -23955,19 +23998,19 @@
       </c>
       <c r="E154" s="13" t="inlineStr">
         <is>
-          <t>LeadCAST lead service line and digital delivery software for water utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+          <t>Machine learning lead service line inventory and prediction for water utilities - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F154" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Opti (OptiRTC)</t>
+          <t>Trinnex</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
@@ -23976,7 +24019,7 @@
         </is>
       </c>
       <c r="C155" s="6" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
@@ -23985,28 +24028,28 @@
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>Continuous monitoring and adaptive control for municipal stormwater systems</t>
+          <t>LeadCAST lead service line and digital delivery software for water utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>2NDNATURE</t>
+          <t>Opti (OptiRTC)</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
         <is>
-          <t>Santa Cruz, California</t>
+          <t>Boston, Massachusetts</t>
         </is>
       </c>
       <c r="C156" s="14" t="n">
-        <v>2003</v>
+        <v>2011</v>
       </c>
       <c r="D156" s="13" t="inlineStr">
         <is>
@@ -24015,7 +24058,7 @@
       </c>
       <c r="E156" s="13" t="inlineStr">
         <is>
-          <t>Stormwater program and MS4 compliance software for municipalities</t>
+          <t>Continuous monitoring and adaptive control for municipal stormwater systems</t>
         </is>
       </c>
       <c r="F156" s="15" t="inlineStr">
@@ -24027,15 +24070,17 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Muni-Link</t>
+          <t>2NDNATURE</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Bellwood, PA</t>
-        </is>
-      </c>
-      <c r="C157" s="6" t="n"/>
+          <t>Santa Cruz, California</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="n">
+        <v>2003</v>
+      </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
           <t>Water</t>
@@ -24043,24 +24088,24 @@
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>Cloud utility billing, payments, and service order software for municipal water and wastewater utilities - exhibited at GFOA 2026</t>
+          <t>Stormwater program and MS4 compliance software for municipalities</t>
         </is>
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>NJBSoft</t>
+          <t>Muni-Link</t>
         </is>
       </c>
       <c r="B158" s="13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ</t>
+          <t>Bellwood, PA</t>
         </is>
       </c>
       <c r="C158" s="14" t="n"/>
@@ -24071,29 +24116,27 @@
       </c>
       <c r="E158" s="13" t="inlineStr">
         <is>
-          <t>SAMS environmental compliance platform for water, wastewater, stormwater, cross-connection, and air quality reporting at municipal utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
-        </is>
-      </c>
-      <c r="F158" s="16" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Cloud utility billing, payments, and service order software for municipal water and wastewater utilities - exhibited at GFOA 2026</t>
+        </is>
+      </c>
+      <c r="F158" s="15" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Nobel Systems, Inc.</t>
+          <t>NJBSoft</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Redlands, CA</t>
-        </is>
-      </c>
-      <c r="C159" s="6" t="n">
-        <v>1992</v>
-      </c>
+          <t>Phoenix, AZ</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="n"/>
       <c r="D159" s="5" t="inlineStr">
         <is>
           <t>Water</t>
@@ -24101,28 +24144,28 @@
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>GeoViewer GIS asset management, field operations, and pressure monitoring software for water districts and municipal utilities - exhibited at AWWA ACE 2026</t>
-        </is>
-      </c>
-      <c r="F159" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>SAMS environmental compliance platform for water, wastewater, stormwater, cross-connection, and air quality reporting at municipal utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+        </is>
+      </c>
+      <c r="F159" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>Specific Energy</t>
+          <t>Nobel Systems, Inc.</t>
         </is>
       </c>
       <c r="B160" s="13" t="inlineStr">
         <is>
-          <t>Georgetown, TX</t>
+          <t>Redlands, CA</t>
         </is>
       </c>
       <c r="C160" s="14" t="n">
-        <v>2010</v>
+        <v>1992</v>
       </c>
       <c r="D160" s="13" t="inlineStr">
         <is>
@@ -24131,7 +24174,7 @@
       </c>
       <c r="E160" s="13" t="inlineStr">
         <is>
-          <t>Pump station control and optimization analytics for municipal water and wastewater utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+          <t>GeoViewer GIS asset management, field operations, and pressure monitoring software for water districts and municipal utilities - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F160" s="15" t="inlineStr">
@@ -24143,16 +24186,16 @@
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Aquanuity, Inc.</t>
+          <t>Specific Energy</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO</t>
+          <t>Georgetown, TX</t>
         </is>
       </c>
       <c r="C161" s="6" t="n">
-        <v>2022</v>
+        <v>2010</v>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
@@ -24161,23 +24204,29 @@
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>AquaTwin digital twin software for water and sewer hydraulic modeling, surge analysis, and asset management, sold to water utilities and engineering consultants - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
-        </is>
-      </c>
-      <c r="F161" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Pump station control and optimization analytics for municipal water and wastewater utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+        </is>
+      </c>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>Spout</t>
-        </is>
-      </c>
-      <c r="B162" s="13" t="n"/>
-      <c r="C162" s="14" t="n"/>
+          <t>Aquanuity, Inc.</t>
+        </is>
+      </c>
+      <c r="B162" s="13" t="inlineStr">
+        <is>
+          <t>Greenwood Village, CO</t>
+        </is>
+      </c>
+      <c r="C162" s="14" t="n">
+        <v>2022</v>
+      </c>
       <c r="D162" s="13" t="inlineStr">
         <is>
           <t>Water</t>
@@ -24185,29 +24234,23 @@
       </c>
       <c r="E162" s="13" t="inlineStr">
         <is>
-          <t>Automated text, voice, email, and mail notification software that turns AMI meter data into leak alerts and service outage messages for water utilities - exhibited at AWWA ACE 2026</t>
-        </is>
-      </c>
-      <c r="F162" s="15" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>AquaTwin digital twin software for water and sewer hydraulic modeling, surge analysis, and asset management, sold to water utilities and engineering consultants - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+        </is>
+      </c>
+      <c r="F162" s="16" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>Waterly, Inc.</t>
-        </is>
-      </c>
-      <c r="B163" s="5" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="n">
-        <v>2017</v>
-      </c>
+          <t>Spout</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="n"/>
+      <c r="C163" s="6" t="n"/>
       <c r="D163" s="5" t="inlineStr">
         <is>
           <t>Water</t>
@@ -24215,28 +24258,28 @@
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>Operations data logging, sampling, and regulatory compliance reporting software for water and wastewater systems - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+          <t>Automated text, voice, email, and mail notification software that turns AMI meter data into leak alerts and service outage messages for water utilities - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>Daupler</t>
+          <t>Waterly, Inc.</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
         <is>
-          <t>Kansas City, MO</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="C164" s="14" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D164" s="13" t="inlineStr">
         <is>
@@ -24245,28 +24288,28 @@
       </c>
       <c r="E164" s="13" t="inlineStr">
         <is>
-          <t>After-hours call intake, incident triage and crew dispatch software for water, sewer and electric utilities and public works departments - exhibited at AWWA ACE 2026</t>
-        </is>
-      </c>
-      <c r="F164" s="16" t="inlineStr">
-        <is>
-          <t>Yes - Account Manager</t>
+          <t>Operations data logging, sampling, and regulatory compliance reporting software for water and wastewater systems - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+        </is>
+      </c>
+      <c r="F164" s="15" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>Kando</t>
+          <t>Daupler</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Tel Aviv, Israel</t>
+          <t>Kansas City, MO</t>
         </is>
       </c>
       <c r="C165" s="6" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
@@ -24275,27 +24318,29 @@
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>IoT sensor and AI wastewater monitoring platform that traces upstream pollution events for water authorities and treatment plants - exhibited at AWWA ACE 2026</t>
-        </is>
-      </c>
-      <c r="F165" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>After-hours call intake, incident triage and crew dispatch software for water, sewer and electric utilities and public works departments - exhibited at AWWA ACE 2026</t>
+        </is>
+      </c>
+      <c r="F165" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Manager</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>RL Core Technologies</t>
+          <t>Kando</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
         <is>
-          <t>Edmonton, Canada</t>
-        </is>
-      </c>
-      <c r="C166" s="14" t="n"/>
+          <t>Tel Aviv, Israel</t>
+        </is>
+      </c>
+      <c r="C166" s="14" t="n">
+        <v>2011</v>
+      </c>
       <c r="D166" s="13" t="inlineStr">
         <is>
           <t>Water</t>
@@ -24303,24 +24348,24 @@
       </c>
       <c r="E166" s="13" t="inlineStr">
         <is>
-          <t>Reinforcement learning control software that automatically optimizes chemical dosing and process settings at drinking water and wastewater plants - exhibited at AWWA ACE 2026</t>
+          <t>IoT sensor and AI wastewater monitoring platform that traces upstream pollution events for water authorities and treatment plants - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F166" s="15" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>STREAMETRIC</t>
+          <t>RL Core Technologies</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>Raleigh, NC</t>
+          <t>Edmonton, Canada</t>
         </is>
       </c>
       <c r="C167" s="6" t="n"/>
@@ -24331,25 +24376,27 @@
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>Cloud SCADA monitoring, alarming and analytics software for water and wastewater utilities, treatment plants and lift stations - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+          <t>Reinforcement learning control software that automatically optimizes chemical dosing and process settings at drinking water and wastewater plants - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 504 for https://streametric.io/care</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>Watura</t>
-        </is>
-      </c>
-      <c r="B168" s="13" t="n"/>
-      <c r="C168" s="14" t="n">
-        <v>2010</v>
-      </c>
+          <t>STREAMETRIC</t>
+        </is>
+      </c>
+      <c r="B168" s="13" t="inlineStr">
+        <is>
+          <t>Raleigh, NC</t>
+        </is>
+      </c>
+      <c r="C168" s="14" t="n"/>
       <c r="D168" s="13" t="inlineStr">
         <is>
           <t>Water</t>
@@ -24357,28 +24404,24 @@
       </c>
       <c r="E168" s="13" t="inlineStr">
         <is>
-          <t>Subscription online training and CEU tracking platform for water and wastewater operators pursuing state licensure - exhibited at AWWA ACE 2026</t>
+          <t>Cloud SCADA monitoring, alarming and analytics software for water and wastewater utilities, treatment plants and lift stations - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F168" s="15" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 403 for https://streametric.io/care</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>Delta Bravo AI</t>
-        </is>
-      </c>
-      <c r="B169" s="5" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC</t>
-        </is>
-      </c>
+          <t>Watura</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="n"/>
       <c r="C169" s="6" t="n">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
@@ -24387,28 +24430,28 @@
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>Agentic AI products for water and wastewater utilities covering treatment decision support, workforce readiness and environmental permit compliance - exhibited at AWWA ACE 2026</t>
+          <t>Subscription online training and CEU tracking platform for water and wastewater operators pursuing state licensure - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>SwiftComply</t>
+          <t>Delta Bravo AI</t>
         </is>
       </c>
       <c r="B170" s="13" t="inlineStr">
         <is>
-          <t>Dublin, Ireland</t>
+          <t>Fort Mill, SC</t>
         </is>
       </c>
       <c r="C170" s="14" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D170" s="13" t="inlineStr">
         <is>
@@ -24417,7 +24460,7 @@
       </c>
       <c r="E170" s="13" t="inlineStr">
         <is>
-          <t>Regulatory compliance software for water utilities covering backflow prevention, stormwater MS4, industrial pretreatment and fats, oils and grease programs - exhibited at AWWA ACE 2026</t>
+          <t>Agentic AI products for water and wastewater utilities covering treatment decision support, workforce readiness and environmental permit compliance - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F170" s="15" t="inlineStr">
@@ -24429,16 +24472,16 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>WI.Plat Co., Ltd.</t>
+          <t>SwiftComply</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>Daejeon, South Korea</t>
+          <t>Dublin, Ireland</t>
         </is>
       </c>
       <c r="C171" s="6" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
@@ -24447,27 +24490,29 @@
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>AI acoustic leak detection sensors and non-revenue-water loss management platform for municipal water utilities - exhibited at AWWA ACE 2026</t>
+          <t>Regulatory compliance software for water utilities covering backflow prevention, stormwater MS4, industrial pretreatment and fats, oils and grease programs - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>Baseform</t>
+          <t>WI.Plat Co., Ltd.</t>
         </is>
       </c>
       <c r="B172" s="13" t="inlineStr">
         <is>
-          <t>Lisbon, Portugal</t>
-        </is>
-      </c>
-      <c r="C172" s="14" t="n"/>
+          <t>Daejeon, South Korea</t>
+        </is>
+      </c>
+      <c r="C172" s="14" t="n">
+        <v>2020</v>
+      </c>
       <c r="D172" s="13" t="inlineStr">
         <is>
           <t>Water</t>
@@ -24475,25 +24520,27 @@
       </c>
       <c r="E172" s="13" t="inlineStr">
         <is>
-          <t>Network data analytics software for water utilities covering leakage, infiltration, energy use and capital planning - exhibited at AWWA ACE 2026</t>
+          <t>AI acoustic leak detection sensors and non-revenue-water loss management platform for municipal water utilities - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F172" s="15" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://baseform.com/np4/ca</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>LeakZon</t>
-        </is>
-      </c>
-      <c r="B173" s="5" t="n"/>
-      <c r="C173" s="6" t="n">
-        <v>2023</v>
-      </c>
+          <t>Baseform</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>Lisbon, Portugal</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="n"/>
       <c r="D173" s="5" t="inlineStr">
         <is>
           <t>Water</t>
@@ -24501,28 +24548,24 @@
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>AI water loss and non-revenue water analytics that detect leaks, bursts and consumption anomalies from utility meter and SCADA data - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+          <t>Network data analytics software for water utilities covering leakage, infiltration, energy use and capital planning - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 404 for https://baseform.com/np4/ca</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="13" t="inlineStr">
         <is>
-          <t>TeamSolve</t>
-        </is>
-      </c>
-      <c r="B174" s="13" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
+          <t>LeakZon</t>
+        </is>
+      </c>
+      <c r="B174" s="13" t="n"/>
       <c r="C174" s="14" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D174" s="13" t="inlineStr">
         <is>
@@ -24531,7 +24574,7 @@
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>AI knowledge assistant and computerized maintenance management software for water and wastewater utility operations teams - exhibited at AWWA ACE 2026</t>
+          <t>AI water loss and non-revenue water analytics that detect leaks, bursts and consumption anomalies from utility meter and SCADA data - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F174" s="15" t="inlineStr">
@@ -24543,11 +24586,17 @@
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>Tova Earth</t>
-        </is>
-      </c>
-      <c r="B175" s="5" t="n"/>
-      <c r="C175" s="6" t="n"/>
+          <t>TeamSolve</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="n">
+        <v>2022</v>
+      </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
           <t>Water</t>
@@ -24555,7 +24604,7 @@
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>Physics-informed AI forecasting of water supply, quality and drought risk for water utilities and infrastructure operators - exhibited at AWWA ACE 2026</t>
+          <t>AI knowledge assistant and computerized maintenance management software for water and wastewater utility operations teams - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F175" s="7" t="inlineStr">
@@ -24567,7 +24616,7 @@
     <row r="176">
       <c r="A176" s="13" t="inlineStr">
         <is>
-          <t>SimpliScada</t>
+          <t>Tova Earth</t>
         </is>
       </c>
       <c r="B176" s="13" t="n"/>
@@ -24579,7 +24628,7 @@
       </c>
       <c r="E176" s="13" t="inlineStr">
         <is>
-          <t>Sells cloud SCADA software for monitoring and controlling water and wastewater systems to municipal water utilities and oil and gas operators - exhibited at WEFTEC 2026</t>
+          <t>Physics-informed AI forecasting of water supply, quality and drought risk for water utilities and infrastructure operators - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F176" s="15" t="inlineStr">
@@ -24591,7 +24640,7 @@
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>Hyfi</t>
+          <t>SimpliScada</t>
         </is>
       </c>
       <c r="B177" s="5" t="n"/>
@@ -24603,7 +24652,7 @@
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>Wireless water level monitors, flood alerts and data dashboards for city public works, county drain offices and state DOTs managing stormwater and flooding - exhibited at StormCon 2026</t>
+          <t>Sells cloud SCADA software for monitoring and controlling water and wastewater systems to municipal water utilities and oil and gas operators - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
@@ -24615,7 +24664,7 @@
     <row r="178">
       <c r="A178" s="13" t="inlineStr">
         <is>
-          <t>Locus Technologies</t>
+          <t>Hyfi</t>
         </is>
       </c>
       <c r="B178" s="13" t="n"/>
@@ -24627,7 +24676,7 @@
       </c>
       <c r="E178" s="13" t="inlineStr">
         <is>
-          <t>Cloud software for environmental compliance, EHS and water quality data management, sold to municipal water utilities and government agencies - exhibited at AWWA ACE 2026</t>
+          <t>Wireless water level monitors, flood alerts and data dashboards for city public works, county drain offices and state DOTs managing stormwater and flooding - exhibited at StormCon 2026</t>
         </is>
       </c>
       <c r="F178" s="15" t="inlineStr">
@@ -24639,7 +24688,7 @@
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>inCTRL Solutions</t>
+          <t>Locus Technologies</t>
         </is>
       </c>
       <c r="B179" s="5" t="n"/>
@@ -24651,19 +24700,19 @@
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>Sells water and wastewater plant software for monitoring, analytics, simulation and process control to municipal utilities - exhibited at WEFTEC 2026</t>
-        </is>
-      </c>
-      <c r="F179" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Cloud software for environmental compliance, EHS and water quality data management, sold to municipal water utilities and government agencies - exhibited at AWWA ACE 2026</t>
+        </is>
+      </c>
+      <c r="F179" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="13" t="inlineStr">
         <is>
-          <t>Infinitii AI</t>
+          <t>inCTRL Solutions</t>
         </is>
       </c>
       <c r="B180" s="13" t="n"/>
@@ -24675,19 +24724,19 @@
       </c>
       <c r="E180" s="13" t="inlineStr">
         <is>
-          <t>Sells predictive analytics and flow-monitoring software for water, wastewater and stormwater systems to municipalities and utilities - exhibited at WEFTEC 2026</t>
+          <t>Sells water and wastewater plant software for monitoring, analytics, simulation and process control to municipal utilities - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F180" s="15" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>LabWare, Inc</t>
+          <t>Infinitii AI</t>
         </is>
       </c>
       <c r="B181" s="5" t="n"/>
@@ -24699,7 +24748,7 @@
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>Sells laboratory information management software, including LabWare WATER, a cloud LIMS for sampling, testing and compliance at municipal water utilities - exhibited at WEFTEC 2026</t>
+          <t>Sells predictive analytics and flow-monitoring software for water, wastewater and stormwater systems to municipalities and utilities - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
@@ -24711,7 +24760,7 @@
     <row r="182">
       <c r="A182" s="13" t="inlineStr">
         <is>
-          <t>Myriota</t>
+          <t>LabWare, Inc</t>
         </is>
       </c>
       <c r="B182" s="13" t="n"/>
@@ -24723,7 +24772,7 @@
       </c>
       <c r="E182" s="13" t="inlineStr">
         <is>
-          <t>Sells satellite IoT connectivity and sensor devices, such as water tank monitors, to government agencies and local councils - exhibited at WEFTEC 2026</t>
+          <t>Sells laboratory information management software, including LabWare WATER, a cloud LIMS for sampling, testing and compliance at municipal water utilities - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F182" s="15" t="inlineStr">
@@ -24735,46 +24784,40 @@
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>Esri</t>
-        </is>
-      </c>
-      <c r="B183" s="5" t="inlineStr">
-        <is>
-          <t>Redlands, CA</t>
-        </is>
-      </c>
-      <c r="C183" s="6" t="n">
-        <v>1969</v>
-      </c>
+          <t>Myriota</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="n"/>
+      <c r="C183" s="6" t="n"/>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>Fleet &amp; Asset Mgmt</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>ArcGIS - the mapping and asset data backbone of most public works departments - exhibited at NLC City Summit 2026, AWWA ACE 2026, IAAO 2026, NASCIO 2026, WEFTEC 2026, IAFC FRI 2026, APCO 2026, APTA 2026, NRPA 2026</t>
+          <t>Sells satellite IoT connectivity and sensor devices, such as water tank monitors, to government agencies and local councils - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page too small - likely JS-rendered</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="13" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Redlands, CA</t>
         </is>
       </c>
       <c r="C184" s="14" t="n">
-        <v>2015</v>
+        <v>1969</v>
       </c>
       <c r="D184" s="13" t="inlineStr">
         <is>
@@ -24783,28 +24826,28 @@
       </c>
       <c r="E184" s="13" t="inlineStr">
         <is>
-          <t>IoT telematics and video safety for government fleets (public co) - exhibited at NLC City Summit 2026, PRIMA 2026, NAFA I&amp;E 2026, NAPT Summit 2026, SWANA WASTECON 2025, APTA 2026</t>
-        </is>
-      </c>
-      <c r="F184" s="16" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>ArcGIS - the mapping and asset data backbone of most public works departments - exhibited at NLC City Summit 2026, AWWA ACE 2026, IAAO 2026, NASCIO 2026, WEFTEC 2026, IAFC FRI 2026, APCO 2026, APTA 2026, NRPA 2026</t>
+        </is>
+      </c>
+      <c r="F184" s="15" t="inlineStr">
+        <is>
+          <t>Unknown - page too small - likely JS-rendered</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>Geotab</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>Oakville, ON, Canada</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="C185" s="6" t="n">
-        <v>2000</v>
+        <v>2015</v>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
@@ -24813,28 +24856,28 @@
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>Fleet telematics with one of the largest municipal footprints - exhibited at NAFA I&amp;E 2026, ITS America 2026</t>
-        </is>
-      </c>
-      <c r="F185" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Business Development Manager - Mob (Denver, Colorado -)</t>
+          <t>IoT telematics and video safety for government fleets (public co) - exhibited at NLC City Summit 2026, PRIMA 2026, NAFA I&amp;E 2026, NAPT Summit 2026, SWANA WASTECON 2025, APTA 2026</t>
+        </is>
+      </c>
+      <c r="F185" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="13" t="inlineStr">
         <is>
-          <t>Cartegraph</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
         <is>
-          <t>Dubuque, IA</t>
+          <t>Oakville, ON, Canada</t>
         </is>
       </c>
       <c r="C186" s="14" t="n">
-        <v>1994</v>
+        <v>2000</v>
       </c>
       <c r="D186" s="13" t="inlineStr">
         <is>
@@ -24843,28 +24886,28 @@
       </c>
       <c r="E186" s="13" t="inlineStr">
         <is>
-          <t>Asset and work order management for DPWs (part of OpenGov)</t>
+          <t>Fleet telematics with one of the largest municipal footprints - exhibited at NAFA I&amp;E 2026, ITS America 2026</t>
         </is>
       </c>
       <c r="F186" s="16" t="inlineStr">
         <is>
-          <t>Yes - Account Executive, SMG (US | Massachusetts)</t>
+          <t>Yes - Business Development Manager - Mob (Denver, Colorado -)</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>Brightly</t>
+          <t>Cartegraph</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>Cary, NC</t>
+          <t>Dubuque, IA</t>
         </is>
       </c>
       <c r="C187" s="6" t="n">
-        <v>1999</v>
+        <v>1994</v>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
@@ -24873,28 +24916,28 @@
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>Asset management ex-Dude Solutions, now Siemens-owned</t>
-        </is>
-      </c>
-      <c r="F187" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Asset and work order management for DPWs (part of OpenGov)</t>
+        </is>
+      </c>
+      <c r="F187" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive, SMG (US | Massachusetts)</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="13" t="inlineStr">
         <is>
-          <t>TerraGo Technologies</t>
+          <t>Brightly</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
         <is>
-          <t>Sterling, VA</t>
+          <t>Cary, NC</t>
         </is>
       </c>
       <c r="C188" s="14" t="n">
-        <v>2005</v>
+        <v>1999</v>
       </c>
       <c r="D188" s="13" t="inlineStr">
         <is>
@@ -24903,7 +24946,7 @@
       </c>
       <c r="E188" s="13" t="inlineStr">
         <is>
-          <t>Field data collection, asset management, and streetlight operations software for cities and utilities - exhibited at AWWA ACE 2026</t>
+          <t>Asset management ex-Dude Solutions, now Siemens-owned</t>
         </is>
       </c>
       <c r="F188" s="15" t="inlineStr">
@@ -24915,16 +24958,16 @@
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>AssetWorks</t>
+          <t>TerraGo Technologies</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>Berwyn, PA</t>
+          <t>Sterling, VA</t>
         </is>
       </c>
       <c r="C189" s="6" t="n">
-        <v>1991</v>
+        <v>2005</v>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
@@ -24933,7 +24976,7 @@
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>Fleet, fuel, and enterprise asset management software for governments and universities (Volaris) - exhibited at NAFA I&amp;E 2026, NRPA 2026</t>
+          <t>Field data collection, asset management, and streetlight operations software for cities and utilities - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
@@ -24945,16 +24988,16 @@
     <row r="190">
       <c r="A190" s="13" t="inlineStr">
         <is>
-          <t>FMX</t>
+          <t>AssetWorks</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
         <is>
-          <t>Columbus, OH</t>
+          <t>Berwyn, PA</t>
         </is>
       </c>
       <c r="C190" s="14" t="n">
-        <v>2012</v>
+        <v>1991</v>
       </c>
       <c r="D190" s="13" t="inlineStr">
         <is>
@@ -24963,7 +25006,7 @@
       </c>
       <c r="E190" s="13" t="inlineStr">
         <is>
-          <t>Cloud CMMS: work orders and preventive maintenance for K-12, local gov, and park &amp; rec facilities - exhibited at NACUBO 2026, GFOA 2026, GMIS International 2026, NRPA 2026, ASBO School Business 2026</t>
+          <t>Fleet, fuel, and enterprise asset management software for governments and universities (Volaris) - exhibited at NAFA I&amp;E 2026, NRPA 2026</t>
         </is>
       </c>
       <c r="F190" s="15" t="inlineStr">
@@ -24975,16 +25018,16 @@
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>PSD Citywide</t>
+          <t>FMX</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>London, ON, Canada</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="C191" s="6" t="n">
-        <v>2005</v>
+        <v>2012</v>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
@@ -24993,7 +25036,7 @@
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>Enterprise asset management, GIS, and budgeting software plus advisory for local governments</t>
+          <t>Cloud CMMS: work orders and preventive maintenance for K-12, local gov, and park &amp; rec facilities - exhibited at NACUBO 2026, GFOA 2026, GMIS International 2026, NRPA 2026, ASBO School Business 2026</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
@@ -25005,16 +25048,16 @@
     <row r="192">
       <c r="A192" s="13" t="inlineStr">
         <is>
-          <t>CityReporter (Noratek)</t>
+          <t>PSD Citywide</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
         <is>
-          <t>Prince George, BC, Canada</t>
+          <t>London, ON, Canada</t>
         </is>
       </c>
       <c r="C192" s="14" t="n">
-        <v>1999</v>
+        <v>2005</v>
       </c>
       <c r="D192" s="13" t="inlineStr">
         <is>
@@ -25023,28 +25066,28 @@
       </c>
       <c r="E192" s="13" t="inlineStr">
         <is>
-          <t>Mobile inspection software: facilities, parks, roads, and fire prevention for small munis</t>
+          <t>Enterprise asset management, GIS, and budgeting software plus advisory for local governments</t>
         </is>
       </c>
       <c r="F192" s="15" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://www.cityreportersof</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>Tenzing One</t>
+          <t>CityReporter (Noratek)</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>Naperville, IL</t>
+          <t>Prince George, BC, Canada</t>
         </is>
       </c>
       <c r="C193" s="6" t="n">
-        <v>2023</v>
+        <v>1999</v>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
@@ -25053,28 +25096,28 @@
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>Capital project management (PMIS): RFIs, change orders, budgets for public owners</t>
+          <t>Mobile inspection software: facilities, parks, roads, and fire prevention for small munis</t>
         </is>
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 404 for https://www.cityreportersof</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="13" t="inlineStr">
         <is>
-          <t>Aurigo Software</t>
+          <t>Tenzing One</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Naperville, IL</t>
         </is>
       </c>
       <c r="C194" s="14" t="n">
-        <v>2003</v>
+        <v>2023</v>
       </c>
       <c r="D194" s="13" t="inlineStr">
         <is>
@@ -25083,28 +25126,28 @@
       </c>
       <c r="E194" s="13" t="inlineStr">
         <is>
-          <t>Masterworks capital program and construction management for DOTs, cities, water, and transit - exhibited at NACE 2026, ICMA 2026</t>
+          <t>Capital project management (PMIS): RFIs, change orders, budgets for public owners</t>
         </is>
       </c>
       <c r="F194" s="15" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.aurigo.com/care</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>FASTER (Transit Technologies)</t>
+          <t>Aurigo Software</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="C195" s="6" t="n">
-        <v>1981</v>
+        <v>2003</v>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
@@ -25113,28 +25156,28 @@
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>FASTER Web fleet maintenance and management, the government fleet standard</t>
+          <t>Masterworks capital program and construction management for DOTs, cities, water, and transit - exhibited at NACE 2026, ICMA 2026</t>
         </is>
       </c>
       <c r="F195" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://fasterasset.com/car</t>
+          <t>Unknown - HTTP 403 for https://www.aurigo.com/care</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="13" t="inlineStr">
         <is>
-          <t>Fleetio</t>
+          <t>FASTER (Transit Technologies)</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
         <is>
-          <t>Birmingham, AL</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="C196" s="14" t="n">
-        <v>2012</v>
+        <v>1981</v>
       </c>
       <c r="D196" s="13" t="inlineStr">
         <is>
@@ -25143,28 +25186,28 @@
       </c>
       <c r="E196" s="13" t="inlineStr">
         <is>
-          <t>Fleet maintenance SaaS: work orders, inspections, fuel for commercial and gov fleets - exhibited at NAFA I&amp;E 2026</t>
-        </is>
-      </c>
-      <c r="F196" s="16" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive, Mid-Market (Remote)</t>
+          <t>FASTER Web fleet maintenance and management, the government fleet standard</t>
+        </is>
+      </c>
+      <c r="F196" s="15" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 404 for https://fasterasset.com/car</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>Fleetio</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Birmingham, AL</t>
         </is>
       </c>
       <c r="C197" s="6" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
@@ -25173,28 +25216,28 @@
       </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>AI fleet platform: telematics, dashcams, spend - with a dedicated public-sector offering - exhibited at NAFA I&amp;E 2026, SWANA WASTECON 2025, APTA 2026, NAPT Summit 2026</t>
-        </is>
-      </c>
-      <c r="F197" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive, CMRL - MX (Mexico City - Hybr)</t>
+          <t>Fleet maintenance SaaS: work orders, inspections, fuel for commercial and gov fleets - exhibited at NAFA I&amp;E 2026</t>
+        </is>
+      </c>
+      <c r="F197" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive, Mid-Market (Remote)</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="13" t="inlineStr">
         <is>
-          <t>Powerfleet</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="B198" s="13" t="inlineStr">
         <is>
-          <t>Woodcliff Lake, NJ</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="C198" s="14" t="n">
-        <v>1993</v>
+        <v>2013</v>
       </c>
       <c r="D198" s="13" t="inlineStr">
         <is>
@@ -25203,28 +25246,28 @@
       </c>
       <c r="E198" s="13" t="inlineStr">
         <is>
-          <t>Unity AIoT fleet intelligence (incl. MiX Telematics, Fleet Complete) for enterprise and gov fleets</t>
-        </is>
-      </c>
-      <c r="F198" s="17" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+          <t>AI fleet platform: telematics, dashcams, spend - with a dedicated public-sector offering - exhibited at NAFA I&amp;E 2026, SWANA WASTECON 2025, APTA 2026, NAPT Summit 2026</t>
+        </is>
+      </c>
+      <c r="F198" s="16" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive, CMRL - MX (Mexico City - Hybr)</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>Forward Thinking Systems</t>
+          <t>Powerfleet</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>Commack, NY</t>
+          <t>Woodcliff Lake, NJ</t>
         </is>
       </c>
       <c r="C199" s="6" t="n">
-        <v>2005</v>
+        <v>1993</v>
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
@@ -25233,7 +25276,7 @@
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>IntelliHub telematics, FleetCam video, and routing for commercial and government fleets</t>
+          <t>Unity AIoT fleet intelligence (incl. MiX Telematics, Fleet Complete) for enterprise and gov fleets</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr">
@@ -25245,16 +25288,16 @@
     <row r="200">
       <c r="A200" s="13" t="inlineStr">
         <is>
-          <t>Azuga</t>
+          <t>Forward Thinking Systems</t>
         </is>
       </c>
       <c r="B200" s="13" t="inlineStr">
         <is>
-          <t>Fremont, CA</t>
+          <t>Commack, NY</t>
         </is>
       </c>
       <c r="C200" s="14" t="n">
-        <v>2012</v>
+        <v>2005</v>
       </c>
       <c r="D200" s="13" t="inlineStr">
         <is>
@@ -25263,7 +25306,7 @@
       </c>
       <c r="E200" s="13" t="inlineStr">
         <is>
-          <t>GPS fleet tracking and driver safety telematics for SMB and government fleets (Bridgestone)</t>
+          <t>IntelliHub telematics, FleetCam video, and routing for commercial and government fleets</t>
         </is>
       </c>
       <c r="F200" s="15" t="inlineStr">
@@ -25275,16 +25318,16 @@
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>NEXGEN Asset Management</t>
+          <t>Azuga</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Fremont, CA</t>
         </is>
       </c>
       <c r="C201" s="6" t="n">
-        <v>2004</v>
+        <v>2012</v>
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
@@ -25293,7 +25336,7 @@
       </c>
       <c r="E201" s="5" t="inlineStr">
         <is>
-          <t>Cloud EAM/CMMS with asset planning and 311 for public works and water utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
+          <t>GPS fleet tracking and driver safety telematics for SMB and government fleets (Bridgestone)</t>
         </is>
       </c>
       <c r="F201" s="7" t="inlineStr">
@@ -25305,16 +25348,16 @@
     <row r="202">
       <c r="A202" s="13" t="inlineStr">
         <is>
-          <t>MaintStar</t>
+          <t>NEXGEN Asset Management</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="C202" s="14" t="n">
-        <v>1984</v>
+        <v>2004</v>
       </c>
       <c r="D202" s="13" t="inlineStr">
         <is>
@@ -25323,7 +25366,7 @@
       </c>
       <c r="E202" s="13" t="inlineStr">
         <is>
-          <t>EAM/CMMS and land management software for cities, counties, and transit</t>
+          <t>Cloud EAM/CMMS with asset planning and 311 for public works and water utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
       <c r="F202" s="15" t="inlineStr">
@@ -25335,16 +25378,16 @@
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>MaintainX</t>
+          <t>MaintStar</t>
         </is>
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="C203" s="6" t="n">
-        <v>2018</v>
+        <v>1984</v>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
@@ -25353,28 +25396,28 @@
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>Mobile-first CMMS unicorn for maintenance ops, with a growing government vertical - exhibited at NRPA 2026, IFMA World Workplace 2026</t>
-        </is>
-      </c>
-      <c r="F203" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Emerging Account Executive (Denver)</t>
+          <t>EAM/CMMS and land management software for cities, counties, and transit</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="13" t="inlineStr">
         <is>
-          <t>Novotx</t>
+          <t>MaintainX</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
         <is>
-          <t>Elk Ridge, UT</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="C204" s="14" t="n">
-        <v>2004</v>
+        <v>2018</v>
       </c>
       <c r="D204" s="13" t="inlineStr">
         <is>
@@ -25383,28 +25426,28 @@
       </c>
       <c r="E204" s="13" t="inlineStr">
         <is>
-          <t>Elements XS ArcGIS-native asset and work management for utilities and local gov (acquired by Accela, Feb 2026) - exhibited at AWWA ACE 2026</t>
-        </is>
-      </c>
-      <c r="F204" s="15" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Mobile-first CMMS unicorn for maintenance ops, with a growing government vertical - exhibited at NRPA 2026, IFMA World Workplace 2026</t>
+        </is>
+      </c>
+      <c r="F204" s="16" t="inlineStr">
+        <is>
+          <t>Yes - Enterprise Account Executive (LATA (Miami)</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>VUEWorks</t>
+          <t>Novotx</t>
         </is>
       </c>
       <c r="B205" s="5" t="inlineStr">
         <is>
-          <t>Orlando, FL</t>
+          <t>Elk Ridge, UT</t>
         </is>
       </c>
       <c r="C205" s="6" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
@@ -25413,7 +25456,7 @@
       </c>
       <c r="E205" s="5" t="inlineStr">
         <is>
-          <t>GIS-integrated enterprise asset management for DOTs and public works (AtkinsRealis)</t>
+          <t>Elements XS ArcGIS-native asset and work management for utilities and local gov (acquired by Accela, Feb 2026) - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F205" s="7" t="inlineStr">
@@ -25425,16 +25468,16 @@
     <row r="206">
       <c r="A206" s="13" t="inlineStr">
         <is>
-          <t>Infotech</t>
+          <t>VUEWorks</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
         <is>
-          <t>Gainesville, FL</t>
+          <t>Orlando, FL</t>
         </is>
       </c>
       <c r="C206" s="14" t="n">
-        <v>1977</v>
+        <v>2003</v>
       </c>
       <c r="D206" s="13" t="inlineStr">
         <is>
@@ -25443,28 +25486,28 @@
       </c>
       <c r="E206" s="13" t="inlineStr">
         <is>
-          <t>Bid Express e-bidding and Appia construction administration for DOTs and local agencies</t>
+          <t>GIS-integrated enterprise asset management for DOTs and public works (AtkinsRealis)</t>
         </is>
       </c>
       <c r="F206" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>RTVision</t>
+          <t>Infotech</t>
         </is>
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>Little Falls, MN</t>
+          <t>Gainesville, FL</t>
         </is>
       </c>
       <c r="C207" s="6" t="n">
-        <v>2001</v>
+        <v>1977</v>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
@@ -25473,7 +25516,7 @@
       </c>
       <c r="E207" s="5" t="inlineStr">
         <is>
-          <t>OneOffice project, right-of-way, and e-permitting software for county highway departments - exhibited at NACE 2026</t>
+          <t>Bid Express e-bidding and Appia construction administration for DOTs and local agencies</t>
         </is>
       </c>
       <c r="F207" s="7" t="inlineStr">
@@ -25485,16 +25528,16 @@
     <row r="208">
       <c r="A208" s="13" t="inlineStr">
         <is>
-          <t>AtlasView</t>
+          <t>RTVision</t>
         </is>
       </c>
       <c r="B208" s="13" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Little Falls, MN</t>
         </is>
       </c>
       <c r="C208" s="14" t="n">
-        <v>2022</v>
+        <v>2001</v>
       </c>
       <c r="D208" s="13" t="inlineStr">
         <is>
@@ -25503,28 +25546,28 @@
       </c>
       <c r="E208" s="13" t="inlineStr">
         <is>
-          <t>Infrastructure asset management SaaS: condition, budgeting/forecasting, public dashboards</t>
+          <t>OneOffice project, right-of-way, and e-permitting software for county highway departments - exhibited at NACE 2026</t>
         </is>
       </c>
       <c r="F208" s="15" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>AtomAI Solutions</t>
+          <t>AtlasView</t>
         </is>
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="C209" s="6" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
@@ -25533,28 +25576,28 @@
       </c>
       <c r="E209" s="5" t="inlineStr">
         <is>
-          <t>Atom asset/maintenance management and Coordinate ROW/project coordination (ex-SADA, ex-dotMaps)</t>
+          <t>Infrastructure asset management SaaS: condition, budgeting/forecasting, public dashboards</t>
         </is>
       </c>
       <c r="F209" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="13" t="inlineStr">
         <is>
-          <t>Projectmates</t>
+          <t>AtomAI Solutions</t>
         </is>
       </c>
       <c r="B210" s="13" t="inlineStr">
         <is>
-          <t>Richardson, TX</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="C210" s="14" t="n">
-        <v>1995</v>
+        <v>2023</v>
       </c>
       <c r="D210" s="13" t="inlineStr">
         <is>
@@ -25563,28 +25606,28 @@
       </c>
       <c r="E210" s="13" t="inlineStr">
         <is>
-          <t>Owner-side construction program management for K-12, government, and institutional capital projects</t>
+          <t>Atom asset/maintenance management and Coordinate ROW/project coordination (ex-SADA, ex-dotMaps)</t>
         </is>
       </c>
       <c r="F210" s="15" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.projectmates.co</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>inLogic</t>
+          <t>Projectmates</t>
         </is>
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>Marietta, GA</t>
+          <t>Richardson, TX</t>
         </is>
       </c>
       <c r="C211" s="6" t="n">
-        <v>2001</v>
+        <v>1995</v>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
@@ -25593,28 +25636,28 @@
       </c>
       <c r="E211" s="5" t="inlineStr">
         <is>
-          <t>RFTrack RFID fixed-asset tracking software and hardware for gov, defense, and education - exhibited at GFOA 2026</t>
+          <t>Owner-side construction program management for K-12, government, and institutional capital projects</t>
         </is>
       </c>
       <c r="F211" s="7" t="inlineStr">
         <is>
-          <t>Unknown - robots.txt asks crawlers not to read www</t>
+          <t>Unknown - HTTP 403 for https://www.projectmates.co</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="13" t="inlineStr">
         <is>
-          <t>Collective Data</t>
+          <t>inLogic</t>
         </is>
       </c>
       <c r="B212" s="13" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA</t>
+          <t>Marietta, GA</t>
         </is>
       </c>
       <c r="C212" s="14" t="n">
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="D212" s="13" t="inlineStr">
         <is>
@@ -25623,27 +25666,29 @@
       </c>
       <c r="E212" s="13" t="inlineStr">
         <is>
-          <t>collectiveFleet low-code fleet, equipment, and motor pool management for police and municipal fleets</t>
-        </is>
-      </c>
-      <c r="F212" s="17" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+          <t>RFTrack RFID fixed-asset tracking software and hardware for gov, defense, and education - exhibited at GFOA 2026</t>
+        </is>
+      </c>
+      <c r="F212" s="15" t="inlineStr">
+        <is>
+          <t>Unknown - robots.txt asks crawlers not to read www</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>Oversite</t>
+          <t>Collective Data</t>
         </is>
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t>Nashville, TN</t>
-        </is>
-      </c>
-      <c r="C213" s="6" t="n"/>
+          <t>Cedar Rapids, IA</t>
+        </is>
+      </c>
+      <c r="C213" s="6" t="n">
+        <v>1998</v>
+      </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
           <t>Fleet &amp; Asset Mgmt</t>
@@ -25651,24 +25696,24 @@
       </c>
       <c r="E213" s="5" t="inlineStr">
         <is>
-          <t>Construction inspection and CEI field capture with AI-assisted inspections for DOTs and agencies</t>
-        </is>
-      </c>
-      <c r="F213" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>collectiveFleet low-code fleet, equipment, and motor pool management for police and municipal fleets</t>
+        </is>
+      </c>
+      <c r="F213" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="13" t="inlineStr">
         <is>
-          <t>Modelve</t>
+          <t>Oversite</t>
         </is>
       </c>
       <c r="B214" s="13" t="inlineStr">
         <is>
-          <t>Melbourne, Australia</t>
+          <t>Nashville, TN</t>
         </is>
       </c>
       <c r="C214" s="14" t="n"/>
@@ -25679,7 +25724,7 @@
       </c>
       <c r="E214" s="13" t="inlineStr">
         <is>
-          <t>Asset investment planning: evidence-based capital and renewal scenario modeling for public owners</t>
+          <t>Construction inspection and CEI field capture with AI-assisted inspections for DOTs and agencies</t>
         </is>
       </c>
       <c r="F214" s="15" t="inlineStr">
@@ -25691,17 +25736,15 @@
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>Octave</t>
+          <t>Modelve</t>
         </is>
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>Huntsville, AL</t>
-        </is>
-      </c>
-      <c r="C215" s="6" t="n">
-        <v>2026</v>
-      </c>
+          <t>Melbourne, Australia</t>
+        </is>
+      </c>
+      <c r="C215" s="6" t="n"/>
       <c r="D215" s="5" t="inlineStr">
         <is>
           <t>Fleet &amp; Asset Mgmt</t>
@@ -25709,28 +25752,28 @@
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>Hexagon spin-off: geospatial, EAM, project controls, physical security, and public-safety CAD (~7,200 staff) - exhibited at APCO 2026, APTA 2026, Illinois Chapter of APCO 2026</t>
+          <t>Asset investment planning: evidence-based capital and renewal scenario modeling for public owners</t>
         </is>
       </c>
       <c r="F215" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="13" t="inlineStr">
         <is>
-          <t>Jacobs</t>
+          <t>Octave</t>
         </is>
       </c>
       <c r="B216" s="13" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>Huntsville, AL</t>
         </is>
       </c>
       <c r="C216" s="14" t="n">
-        <v>1947</v>
+        <v>2026</v>
       </c>
       <c r="D216" s="13" t="inlineStr">
         <is>
@@ -25739,28 +25782,28 @@
       </c>
       <c r="E216" s="13" t="inlineStr">
         <is>
-          <t>Global engineering and program management for public infrastructure (47K staff, $12B rev); owns StreetLight transportation analytics - exhibited at AWWA ACE 2026, WEFTEC 2026, SWANA WASTECON 2025, AAAE 2027, APTA 2026</t>
+          <t>Hexagon spin-off: geospatial, EAM, project controls, physical security, and public-safety CAD (~7,200 staff) - exhibited at APCO 2026, APTA 2026, Illinois Chapter of APCO 2026</t>
         </is>
       </c>
       <c r="F216" s="15" t="inlineStr">
         <is>
-          <t>Unknown - robots.txt on careers.jacobs.com answere</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>Cityworks (Trimble)</t>
+          <t>Jacobs</t>
         </is>
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>Sandy, Utah</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="C217" s="6" t="n">
-        <v>1996</v>
+        <v>1947</v>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
@@ -25769,28 +25812,28 @@
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>GIS-centric asset and work order management for cities and utilities</t>
+          <t>Global engineering and program management for public infrastructure (47K staff, $12B rev); owns StreetLight transportation analytics - exhibited at AWWA ACE 2026, WEFTEC 2026, SWANA WASTECON 2025, AAAE 2027, APTA 2026</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - robots.txt on careers.jacobs.com answere</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="13" t="inlineStr">
         <is>
-          <t>Accruent</t>
+          <t>Cityworks (Trimble)</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
         <is>
-          <t>Austin, Texas</t>
+          <t>Sandy, Utah</t>
         </is>
       </c>
       <c r="C218" s="14" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="D218" s="13" t="inlineStr">
         <is>
@@ -25799,28 +25842,28 @@
       </c>
       <c r="E218" s="13" t="inlineStr">
         <is>
-          <t>Facilities, EAM and CMMS software for public agencies and schools - exhibited at EDUCAUSE 2026, IFMA World Workplace 2026</t>
+          <t>GIS-centric asset and work order management for cities and utilities</t>
         </is>
       </c>
       <c r="F218" s="15" t="inlineStr">
         <is>
-          <t>Unknown - board is another company's - not read</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>IFS (Ultimo)</t>
+          <t>Accruent</t>
         </is>
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>Linkoping, Sweden</t>
+          <t>Austin, Texas</t>
         </is>
       </c>
       <c r="C219" s="6" t="n">
-        <v>1983</v>
+        <v>1995</v>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
@@ -25829,28 +25872,28 @@
       </c>
       <c r="E219" s="5" t="inlineStr">
         <is>
-          <t>Enterprise asset and field service management for utilities and municipalities</t>
-        </is>
-      </c>
-      <c r="F219" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Senior Account Executive – Enterpr (London, England)</t>
+          <t>Facilities, EAM and CMMS software for public agencies and schools - exhibited at EDUCAUSE 2026, IFMA World Workplace 2026</t>
+        </is>
+      </c>
+      <c r="F219" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - board is another company's - not read</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="13" t="inlineStr">
         <is>
-          <t>Limble</t>
+          <t>IFS (Ultimo)</t>
         </is>
       </c>
       <c r="B220" s="13" t="inlineStr">
         <is>
-          <t>Lehi, Utah</t>
+          <t>Linkoping, Sweden</t>
         </is>
       </c>
       <c r="C220" s="14" t="n">
-        <v>2015</v>
+        <v>1983</v>
       </c>
       <c r="D220" s="13" t="inlineStr">
         <is>
@@ -25859,28 +25902,28 @@
       </c>
       <c r="E220" s="13" t="inlineStr">
         <is>
-          <t>Cloud CMMS for municipal facilities, water plants and public works</t>
-        </is>
-      </c>
-      <c r="F220" s="17" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Sales Talent Community – AM &amp; AE R only</t>
+          <t>Enterprise asset and field service management for utilities and municipalities</t>
+        </is>
+      </c>
+      <c r="F220" s="16" t="inlineStr">
+        <is>
+          <t>Yes - Senior Account Executive – Enterpr (London, England)</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>UpKeep</t>
+          <t>Limble</t>
         </is>
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles, California</t>
+          <t>Lehi, Utah</t>
         </is>
       </c>
       <c r="C221" s="6" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
@@ -25889,28 +25932,28 @@
       </c>
       <c r="E221" s="5" t="inlineStr">
         <is>
-          <t>Mobile CMMS for municipal maintenance, water and facilities teams</t>
-        </is>
-      </c>
-      <c r="F221" s="10" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Cloud CMMS for municipal facilities, water plants and public works</t>
+        </is>
+      </c>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="13" t="inlineStr">
         <is>
-          <t>eMaint (Fluke Reliability)</t>
+          <t>UpKeep</t>
         </is>
       </c>
       <c r="B222" s="13" t="inlineStr">
         <is>
-          <t>Marlton, New Jersey</t>
+          <t>Los Angeles, California</t>
         </is>
       </c>
       <c r="C222" s="14" t="n">
-        <v>1986</v>
+        <v>2014</v>
       </c>
       <c r="D222" s="13" t="inlineStr">
         <is>
@@ -25919,28 +25962,28 @@
       </c>
       <c r="E222" s="13" t="inlineStr">
         <is>
-          <t>CMMS for public works, water districts and government facilities</t>
-        </is>
-      </c>
-      <c r="F222" s="15" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Mobile CMMS for municipal maintenance, water and facilities teams</t>
+        </is>
+      </c>
+      <c r="F222" s="16" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>Fiix (Rockwell Automation)</t>
+          <t>eMaint (Fluke Reliability)</t>
         </is>
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>Toronto, Ontario</t>
+          <t>Marlton, New Jersey</t>
         </is>
       </c>
       <c r="C223" s="6" t="n">
-        <v>2008</v>
+        <v>1986</v>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
@@ -25949,28 +25992,28 @@
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>Cloud maintenance management for utilities and municipal operations</t>
-        </is>
-      </c>
-      <c r="F223" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+          <t>CMMS for public works, water districts and government facilities</t>
+        </is>
+      </c>
+      <c r="F223" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="13" t="inlineStr">
         <is>
-          <t>GPS Insight</t>
+          <t>Fiix (Rockwell Automation)</t>
         </is>
       </c>
       <c r="B224" s="13" t="inlineStr">
         <is>
-          <t>Scottsdale, Arizona</t>
+          <t>Toronto, Ontario</t>
         </is>
       </c>
       <c r="C224" s="14" t="n">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="D224" s="13" t="inlineStr">
         <is>
@@ -25979,28 +26022,28 @@
       </c>
       <c r="E224" s="13" t="inlineStr">
         <is>
-          <t>Fleet tracking and field service management for local government fleets</t>
-        </is>
-      </c>
-      <c r="F224" s="15" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Cloud maintenance management for utilities and municipal operations</t>
+        </is>
+      </c>
+      <c r="F224" s="17" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>Eptura</t>
+          <t>GPS Insight</t>
         </is>
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia</t>
+          <t>Scottsdale, Arizona</t>
         </is>
       </c>
       <c r="C225" s="6" t="n">
-        <v>2022</v>
+        <v>2004</v>
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
@@ -26009,7 +26052,7 @@
       </c>
       <c r="E225" s="5" t="inlineStr">
         <is>
-          <t>Facility, space and asset management software incl. government campuses</t>
+          <t>Fleet tracking and field service management for local government fleets</t>
         </is>
       </c>
       <c r="F225" s="7" t="inlineStr">
@@ -26021,16 +26064,16 @@
     <row r="226">
       <c r="A226" s="13" t="inlineStr">
         <is>
-          <t>Fulcrum (Spatial Networks)</t>
+          <t>Eptura</t>
         </is>
       </c>
       <c r="B226" s="13" t="inlineStr">
         <is>
-          <t>St. Petersburg, Florida</t>
+          <t>Atlanta, Georgia</t>
         </is>
       </c>
       <c r="C226" s="14" t="n">
-        <v>2001</v>
+        <v>2022</v>
       </c>
       <c r="D226" s="13" t="inlineStr">
         <is>
@@ -26039,7 +26082,7 @@
       </c>
       <c r="E226" s="13" t="inlineStr">
         <is>
-          <t>Mobile field inspection and asset data collection for public works - exhibited at WEFTEC 2026</t>
+          <t>Facility, space and asset management software incl. government campuses</t>
         </is>
       </c>
       <c r="F226" s="15" t="inlineStr">
@@ -26051,16 +26094,16 @@
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>Sedaru</t>
+          <t>Fulcrum (Spatial Networks)</t>
         </is>
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>Irvine, California</t>
+          <t>St. Petersburg, Florida</t>
         </is>
       </c>
       <c r="C227" s="6" t="n">
-        <v>2016</v>
+        <v>2001</v>
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
@@ -26069,28 +26112,28 @@
       </c>
       <c r="E227" s="5" t="inlineStr">
         <is>
-          <t>Water utility asset, work order and field ops platform for municipalities</t>
+          <t>Mobile field inspection and asset data collection for public works - exhibited at WEFTEC 2026</t>
         </is>
       </c>
       <c r="F227" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="13" t="inlineStr">
         <is>
-          <t>E.J. Ward</t>
+          <t>Sedaru</t>
         </is>
       </c>
       <c r="B228" s="13" t="inlineStr">
         <is>
-          <t>San Antonio, Texas</t>
+          <t>Irvine, California</t>
         </is>
       </c>
       <c r="C228" s="14" t="n">
-        <v>1971</v>
+        <v>2016</v>
       </c>
       <c r="D228" s="13" t="inlineStr">
         <is>
@@ -26099,28 +26142,28 @@
       </c>
       <c r="E228" s="13" t="inlineStr">
         <is>
-          <t>Fuel management and vehicle ID systems for municipal and state fleets</t>
+          <t>Water utility asset, work order and field ops platform for municipalities</t>
         </is>
       </c>
       <c r="F228" s="15" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://www.wardfuel.com/as</t>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>Sawatch Labs</t>
+          <t>E.J. Ward</t>
         </is>
       </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
-          <t>Denver, Colorado</t>
+          <t>San Antonio, Texas</t>
         </is>
       </c>
       <c r="C229" s="6" t="n">
-        <v>2015</v>
+        <v>1971</v>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
@@ -26129,28 +26172,28 @@
       </c>
       <c r="E229" s="5" t="inlineStr">
         <is>
-          <t>EV fleet transition analytics for city, county and state fleets</t>
+          <t>Fuel management and vehicle ID systems for municipal and state fleets</t>
         </is>
       </c>
       <c r="F229" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 404 for https://www.wardfuel.com/as</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="13" t="inlineStr">
         <is>
-          <t>VertiGIS</t>
+          <t>Sawatch Labs</t>
         </is>
       </c>
       <c r="B230" s="13" t="inlineStr">
         <is>
-          <t>Vancouver, British Columbia</t>
+          <t>Denver, Colorado</t>
         </is>
       </c>
       <c r="C230" s="14" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="D230" s="13" t="inlineStr">
         <is>
@@ -26159,28 +26202,28 @@
       </c>
       <c r="E230" s="13" t="inlineStr">
         <is>
-          <t>GIS-based asset and work management for local government and utilities - exhibited at AWWA ACE 2026</t>
-        </is>
-      </c>
-      <c r="F230" s="16" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive, Utilities (Homeoffice)</t>
+          <t>EV fleet transition analytics for city, county and state fleets</t>
+        </is>
+      </c>
+      <c r="F230" s="15" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
-          <t>Kahua</t>
+          <t>VertiGIS</t>
         </is>
       </c>
       <c r="B231" s="5" t="inlineStr">
         <is>
-          <t>Alpharetta, GA</t>
+          <t>Vancouver, British Columbia</t>
         </is>
       </c>
       <c r="C231" s="6" t="n">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
@@ -26189,28 +26232,28 @@
       </c>
       <c r="E231" s="5" t="inlineStr">
         <is>
-          <t>Capital program and construction project management software for infrastructure owners including federal, state, and local agencies - exhibited at AWWA ACE 2026</t>
-        </is>
-      </c>
-      <c r="F231" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>GIS-based asset and work management for local government and utilities - exhibited at AWWA ACE 2026</t>
+        </is>
+      </c>
+      <c r="F231" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive, Utilities (Homeoffice)</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="13" t="inlineStr">
         <is>
-          <t>KloudGin</t>
+          <t>Kahua</t>
         </is>
       </c>
       <c r="B232" s="13" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA</t>
+          <t>Alpharetta, GA</t>
         </is>
       </c>
       <c r="C232" s="14" t="n">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="D232" s="13" t="inlineStr">
         <is>
@@ -26219,28 +26262,28 @@
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>Combined field service and enterprise asset management cloud for water, gas and electric utilities and municipal public works departments - exhibited at AWWA ACE 2026</t>
-        </is>
-      </c>
-      <c r="F232" s="17" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+          <t>Capital program and construction project management software for infrastructure owners including federal, state, and local agencies - exhibited at AWWA ACE 2026</t>
+        </is>
+      </c>
+      <c r="F232" s="15" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>Fieldman</t>
+          <t>KloudGin</t>
         </is>
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>Sawyer, MI</t>
+          <t>Sunnyvale, CA</t>
         </is>
       </c>
       <c r="C233" s="6" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
@@ -26249,27 +26292,29 @@
       </c>
       <c r="E233" s="5" t="inlineStr">
         <is>
-          <t>Field work order and asset management software for local governments and utilities running smart meter and infrastructure projects - exhibited at AWWA ACE 2026</t>
-        </is>
-      </c>
-      <c r="F233" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Combined field service and enterprise asset management cloud for water, gas and electric utilities and municipal public works departments - exhibited at AWWA ACE 2026</t>
+        </is>
+      </c>
+      <c r="F233" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="13" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Fieldman</t>
         </is>
       </c>
       <c r="B234" s="13" t="inlineStr">
         <is>
-          <t>North Vancouver, Canada</t>
-        </is>
-      </c>
-      <c r="C234" s="14" t="n"/>
+          <t>Sawyer, MI</t>
+        </is>
+      </c>
+      <c r="C234" s="14" t="n">
+        <v>2019</v>
+      </c>
       <c r="D234" s="13" t="inlineStr">
         <is>
           <t>Fleet &amp; Asset Mgmt</t>
@@ -26277,7 +26322,7 @@
       </c>
       <c r="E234" s="13" t="inlineStr">
         <is>
-          <t>Mobile field service and workforce management software for municipal water, gas, electric, fiber and sanitation utilities - exhibited at AWWA ACE 2026</t>
+          <t>Field work order and asset management software for local governments and utilities running smart meter and infrastructure projects - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F234" s="15" t="inlineStr">
@@ -26289,10 +26334,14 @@
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
         <is>
-          <t>RedBeam</t>
-        </is>
-      </c>
-      <c r="B235" s="5" t="n"/>
+          <t>ServiceLink</t>
+        </is>
+      </c>
+      <c r="B235" s="5" t="inlineStr">
+        <is>
+          <t>North Vancouver, Canada</t>
+        </is>
+      </c>
       <c r="C235" s="6" t="n"/>
       <c r="D235" s="5" t="inlineStr">
         <is>
@@ -26301,7 +26350,7 @@
       </c>
       <c r="E235" s="5" t="inlineStr">
         <is>
-          <t>RedBeam sells asset and inventory tracking software, including RFID tracking, to government agencies, schools and businesses - exhibited at GFOA 2026</t>
+          <t>Mobile field service and workforce management software for municipal water, gas, electric, fiber and sanitation utilities - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
       <c r="F235" s="7" t="inlineStr">
@@ -26313,19 +26362,19 @@
     <row r="236">
       <c r="A236" s="13" t="inlineStr">
         <is>
-          <t>Baseline Telematics</t>
+          <t>RedBeam</t>
         </is>
       </c>
       <c r="B236" s="13" t="n"/>
       <c r="C236" s="14" t="n"/>
       <c r="D236" s="13" t="inlineStr">
         <is>
-          <t>Suppliers &amp; Services</t>
+          <t>Fleet &amp; Asset Mgmt</t>
         </is>
       </c>
       <c r="E236" s="13" t="inlineStr">
         <is>
-          <t>Fleet telematics and GPS software platform - exhibited at PWX 2026</t>
+          <t>RedBeam sells asset and inventory tracking software, including RFID tracking, to government agencies, schools and businesses - exhibited at GFOA 2026</t>
         </is>
       </c>
       <c r="F236" s="15" t="inlineStr">
@@ -26337,7 +26386,7 @@
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
         <is>
-          <t>Decision Optimization Technology</t>
+          <t>Baseline Telematics</t>
         </is>
       </c>
       <c r="B237" s="5" t="n"/>
@@ -26349,7 +26398,7 @@
       </c>
       <c r="E237" s="5" t="inlineStr">
         <is>
-          <t>Route and operations optimization software - exhibited at PWX 2026, GFOA 2026</t>
+          <t>Fleet telematics and GPS software platform - exhibited at PWX 2026</t>
         </is>
       </c>
       <c r="F237" s="7" t="inlineStr">
@@ -26361,7 +26410,7 @@
     <row r="238">
       <c r="A238" s="13" t="inlineStr">
         <is>
-          <t>EYERIDE</t>
+          <t>Decision Optimization Technology</t>
         </is>
       </c>
       <c r="B238" s="13" t="n"/>
@@ -26373,7 +26422,7 @@
       </c>
       <c r="E238" s="13" t="inlineStr">
         <is>
-          <t>Fleet video telematics and driver monitoring software - exhibited at PWX 2026</t>
+          <t>Route and operations optimization software - exhibited at PWX 2026, GFOA 2026</t>
         </is>
       </c>
       <c r="F238" s="15" t="inlineStr">
@@ -26385,7 +26434,7 @@
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
         <is>
-          <t>EdgeAI</t>
+          <t>EYERIDE</t>
         </is>
       </c>
       <c r="B239" s="5" t="n"/>
@@ -26397,19 +26446,19 @@
       </c>
       <c r="E239" s="5" t="inlineStr">
         <is>
-          <t>Edge AI video analytics technology - exhibited at PWX 2026</t>
-        </is>
-      </c>
-      <c r="F239" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Fleet video telematics and driver monitoring software - exhibited at PWX 2026</t>
+        </is>
+      </c>
+      <c r="F239" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="13" t="inlineStr">
         <is>
-          <t>FASTER</t>
+          <t>EdgeAI</t>
         </is>
       </c>
       <c r="B240" s="13" t="n"/>
@@ -26421,7 +26470,7 @@
       </c>
       <c r="E240" s="13" t="inlineStr">
         <is>
-          <t>Fleet maintenance management software - exhibited at PWX 2026</t>
+          <t>Edge AI video analytics technology - exhibited at PWX 2026</t>
         </is>
       </c>
       <c r="F240" s="15" t="inlineStr">
@@ -26433,7 +26482,7 @@
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>InfraHub</t>
+          <t>FASTER</t>
         </is>
       </c>
       <c r="B241" s="5" t="n"/>
@@ -26445,7 +26494,7 @@
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure management software platform - exhibited at PWX 2026</t>
+          <t>Fleet maintenance management software - exhibited at PWX 2026</t>
         </is>
       </c>
       <c r="F241" s="7" t="inlineStr">
@@ -26457,7 +26506,7 @@
     <row r="242">
       <c r="A242" s="13" t="inlineStr">
         <is>
-          <t>Noti-FLY Inc</t>
+          <t>InfraHub</t>
         </is>
       </c>
       <c r="B242" s="13" t="n"/>
@@ -26469,7 +26518,7 @@
       </c>
       <c r="E242" s="13" t="inlineStr">
         <is>
-          <t>Construction notification SMS platform for agencies - exhibited at PWX 2026</t>
+          <t>Infrastructure management software platform - exhibited at PWX 2026</t>
         </is>
       </c>
       <c r="F242" s="15" t="inlineStr">
@@ -26481,7 +26530,7 @@
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>Omen AI</t>
+          <t>Noti-FLY Inc</t>
         </is>
       </c>
       <c r="B243" s="5" t="n"/>
@@ -26493,7 +26542,7 @@
       </c>
       <c r="E243" s="5" t="inlineStr">
         <is>
-          <t>AI monitoring and analytics software - exhibited at PWX 2026</t>
+          <t>Construction notification SMS platform for agencies - exhibited at PWX 2026</t>
         </is>
       </c>
       <c r="F243" s="7" t="inlineStr">
@@ -26505,7 +26554,7 @@
     <row r="244">
       <c r="A244" s="13" t="inlineStr">
         <is>
-          <t>PreCise MRM, LLC</t>
+          <t>Omen AI</t>
         </is>
       </c>
       <c r="B244" s="13" t="n"/>
@@ -26517,7 +26566,7 @@
       </c>
       <c r="E244" s="13" t="inlineStr">
         <is>
-          <t>GPS/AVL fleet telematics for public works - exhibited at PWX 2026</t>
+          <t>AI monitoring and analytics software - exhibited at PWX 2026</t>
         </is>
       </c>
       <c r="F244" s="15" t="inlineStr">
@@ -26529,7 +26578,7 @@
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
         <is>
-          <t>Roadway Management Technologies</t>
+          <t>PreCise MRM, LLC</t>
         </is>
       </c>
       <c r="B245" s="5" t="n"/>
@@ -26541,7 +26590,7 @@
       </c>
       <c r="E245" s="5" t="inlineStr">
         <is>
-          <t>Roadway and infrastructure management software - exhibited at PWX 2026</t>
+          <t>GPS/AVL fleet telematics for public works - exhibited at PWX 2026</t>
         </is>
       </c>
       <c r="F245" s="7" t="inlineStr">
@@ -26553,13 +26602,11 @@
     <row r="246">
       <c r="A246" s="13" t="inlineStr">
         <is>
-          <t>Route4Me</t>
+          <t>Roadway Management Technologies</t>
         </is>
       </c>
       <c r="B246" s="13" t="n"/>
-      <c r="C246" s="14" t="n">
-        <v>2009</v>
-      </c>
+      <c r="C246" s="14" t="n"/>
       <c r="D246" s="13" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -26567,23 +26614,25 @@
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>Route optimization and planning software - exhibited at PWX 2026</t>
+          <t>Roadway and infrastructure management software - exhibited at PWX 2026</t>
         </is>
       </c>
       <c r="F246" s="15" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
         <is>
-          <t>SoilFLO</t>
+          <t>Route4Me</t>
         </is>
       </c>
       <c r="B247" s="5" t="n"/>
-      <c r="C247" s="6" t="n"/>
+      <c r="C247" s="6" t="n">
+        <v>2009</v>
+      </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -26591,7 +26640,7 @@
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>Soil and excavated material tracking software - exhibited at PWX 2026</t>
+          <t>Route optimization and planning software - exhibited at PWX 2026</t>
         </is>
       </c>
       <c r="F247" s="7" t="inlineStr">
@@ -26603,17 +26652,11 @@
     <row r="248">
       <c r="A248" s="13" t="inlineStr">
         <is>
-          <t>TrackVia</t>
-        </is>
-      </c>
-      <c r="B248" s="13" t="inlineStr">
-        <is>
-          <t>Denver, CO</t>
-        </is>
-      </c>
-      <c r="C248" s="14" t="n">
-        <v>2006</v>
-      </c>
+          <t>SoilFLO</t>
+        </is>
+      </c>
+      <c r="B248" s="13" t="n"/>
+      <c r="C248" s="14" t="n"/>
       <c r="D248" s="13" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -26621,23 +26664,29 @@
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>Low-code workflow application platform - exhibited at PWX 2026</t>
-        </is>
-      </c>
-      <c r="F248" s="16" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+          <t>Soil and excavated material tracking software - exhibited at PWX 2026</t>
+        </is>
+      </c>
+      <c r="F248" s="15" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>VUEWorks®, An AtkinsRéalis Technology</t>
-        </is>
-      </c>
-      <c r="B249" s="5" t="n"/>
-      <c r="C249" s="6" t="n"/>
+          <t>TrackVia</t>
+        </is>
+      </c>
+      <c r="B249" s="5" t="inlineStr">
+        <is>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="C249" s="6" t="n">
+        <v>2006</v>
+      </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
           <t>Suppliers &amp; Services</t>
@@ -26645,19 +26694,19 @@
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
-          <t>GIS-centric enterprise asset management software - exhibited at PWX 2026</t>
-        </is>
-      </c>
-      <c r="F249" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Low-code workflow application platform - exhibited at PWX 2026</t>
+        </is>
+      </c>
+      <c r="F249" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="13" t="inlineStr">
         <is>
-          <t>Verizon Connect</t>
+          <t>VUEWorks®, An AtkinsRéalis Technology</t>
         </is>
       </c>
       <c r="B250" s="13" t="n"/>
@@ -26669,19 +26718,19 @@
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>Fleet telematics and GPS tracking software - exhibited at PWX 2026</t>
-        </is>
-      </c>
-      <c r="F250" s="17" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+          <t>GIS-centric enterprise asset management software - exhibited at PWX 2026</t>
+        </is>
+      </c>
+      <c r="F250" s="15" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>Virtual Project Manager</t>
+          <t>Verizon Connect</t>
         </is>
       </c>
       <c r="B251" s="5" t="n"/>
@@ -26693,19 +26742,19 @@
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>Construction project management software - exhibited at PWX 2026</t>
-        </is>
-      </c>
-      <c r="F251" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Fleet telematics and GPS tracking software - exhibited at PWX 2026</t>
+        </is>
+      </c>
+      <c r="F251" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="13" t="inlineStr">
         <is>
-          <t>Wrangler.ai</t>
+          <t>Virtual Project Manager</t>
         </is>
       </c>
       <c r="B252" s="13" t="n"/>
@@ -26717,17 +26766,41 @@
       </c>
       <c r="E252" s="13" t="inlineStr">
         <is>
+          <t>Construction project management software - exhibited at PWX 2026</t>
+        </is>
+      </c>
+      <c r="F252" s="15" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="inlineStr">
+        <is>
+          <t>Wrangler.ai</t>
+        </is>
+      </c>
+      <c r="B253" s="5" t="n"/>
+      <c r="C253" s="6" t="n"/>
+      <c r="D253" s="5" t="inlineStr">
+        <is>
+          <t>Suppliers &amp; Services</t>
+        </is>
+      </c>
+      <c r="E253" s="5" t="inlineStr">
+        <is>
           <t>AI software for infrastructure data - exhibited at PWX 2026</t>
         </is>
       </c>
-      <c r="F252" s="15" t="inlineStr">
+      <c r="F253" s="7" t="inlineStr">
         <is>
           <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F252"/>
+  <autoFilter ref="A1:F253"/>
   <dataValidations count="1">
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid category" error="Pick one of: Waste &amp; Recycling, Streets, Water, Fleet &amp; Asset Mgmt, Suppliers &amp; Services" type="list">
       <formula1>"Waste &amp; Recycling,Streets,Water,Fleet &amp; Asset Mgmt,Suppliers &amp; Services"</formula1>
@@ -26784,7 +26857,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/19/26)</t>
+          <t>Hiring AEs? (10/20/26)</t>
         </is>
       </c>
     </row>
@@ -26842,7 +26915,7 @@
           <t>Resident communications (govDelivery), meeting and agenda management, digital services; destination marketing as Simpleview, now Granicus Destinations - exhibited at 3CMA 2026, GMIS International 2026, APHSA 2026, ICC 2026, NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive - New Logo - Nor</t>
         </is>
@@ -27022,7 +27095,7 @@
           <t>Turnkey 'library of things' sharing programs sold to cities, property managers, and employers</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -28150,7 +28223,7 @@
           <t>Workflow automation, online forms and eSignature for state/local agencies - exhibited at Healthcare IT Connect 2026</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Development Representative only</t>
         </is>
@@ -28300,7 +28373,7 @@
       </c>
       <c r="F52" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -28508,7 +28581,7 @@
           <t>Cloud apps for permits, code enforcement and citizen requests in small cities</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F59" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive - GovTech Softwa</t>
         </is>
@@ -28566,7 +28639,7 @@
           <t>GIS, asset and citizen-facing software for small and rural local governments</t>
         </is>
       </c>
-      <c r="F61" s="9" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -28986,7 +29059,7 @@
       </c>
       <c r="F76" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -29008,9 +29081,9 @@
           <t>Incode sells biometric identity verification software that public agencies use to verify citizens applying for services and benefits, and also sells it to banks and businesses - exhibited at NASWA 2025</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Senior Technical Account Manager (United States)</t>
         </is>
       </c>
     </row>
@@ -29082,7 +29155,7 @@
       </c>
       <c r="F80" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -29104,9 +29177,9 @@
           <t>Sells identity verification and fraud prevention software to state and local government agencies that deliver benefits and services - exhibited at NASWA 2025, Healthcare IT Connect 2026</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive Director, Gaming (New Jersey - Remot)</t>
         </is>
       </c>
     </row>
@@ -29128,9 +29201,9 @@
           <t>Sells cloud contact center software, including a FedRAMP-authorized Government Edition, to government agencies, higher education institutions and businesses - exhibited at NASCIO 2026</t>
         </is>
       </c>
-      <c r="F82" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F82" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Enterprise Account Executive - Mix (Phoenix)</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29227,7 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -29308,7 +29381,7 @@
           <t>Permitting, budgeting, procurement, and asset management cloud suite (Cox-owned) - exhibited at GFOA 2026, NLC City Summit 2026, NACE 2026, AWWA ACE 2026, GMIS International 2026, Maryland Municipal League 2026, WEFTEC 2026, NRPA 2026, ICC 2026, ASBO School Business 2026</t>
         </is>
       </c>
-      <c r="F89" s="10" t="inlineStr">
+      <c r="F89" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, SMG (US | Massachusetts)</t>
         </is>
@@ -29368,7 +29441,7 @@
           <t>AI permitting and licensing platform: 24/7 resident assistant, AI code-compliance review - exhibited at NLC City Summit 2026, Maryland Municipal League 2026, ICC 2026</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>Yes - Business Development Manager (New York, NY)</t>
         </is>
@@ -29428,7 +29501,7 @@
           <t>Special event, film, and complex permit approval workflow SaaS for cities - exhibited at NRPA 2026</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F93" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -29788,7 +29861,7 @@
           <t>ProjectDox electronic plan review for building, fire, planning, and public works agencies - exhibited at ICMA 2026, ICC 2026</t>
         </is>
       </c>
-      <c r="F105" s="10" t="inlineStr">
+      <c r="F105" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (GovTech SaaS)</t>
         </is>
@@ -30308,7 +30381,7 @@
           <t>Electronic plan review software for building and public works departments - exhibited at ICC 2026</t>
         </is>
       </c>
-      <c r="F123" s="10" t="inlineStr">
+      <c r="F123" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -30480,7 +30553,7 @@
           <t>Objective Build planning and building consent software for government regulators</t>
         </is>
       </c>
-      <c r="F129" s="9" t="inlineStr">
+      <c r="F129" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Account Director only</t>
         </is>
@@ -30650,7 +30723,7 @@
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -30674,7 +30747,7 @@
       </c>
       <c r="F136" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -30750,7 +30823,7 @@
           <t>The govtech giant: ERP, courts, public safety, permitting, and payments - exhibited at GFOA 2026, NLC City Summit 2026, PSHRA 2026, AWWA ACE 2026, IAAO 2026, NASCIO 2026, GMIS International 2026, NACM 2026, APPA Probation 2026, Iowa State Association of Counties 2026, Maryland Municipal League 2026, IAFC FRI 2026, APCO 2026, NAPT Summit 2026, Connecticut Conference of Municipalities 2026, Illinois Chapter of APCO 2026, ICC 2026, ASBO School Business 2026, NACVSO 2026</t>
         </is>
       </c>
-      <c r="F139" s="10" t="inlineStr">
+      <c r="F139" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -30870,7 +30943,7 @@
           <t>Local government ERP: financials, property tax, assessing, utility billing - Michigan standard going national - exhibited at GFOA 2026, ICMA 2026</t>
         </is>
       </c>
-      <c r="F143" s="10" t="inlineStr">
+      <c r="F143" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -30930,7 +31003,7 @@
           <t>PE-backed govtech rollup: courts, land records, tax/CAMA, licensing, and citizen payments - exhibited at APPA Probation 2026, IAAO 2026, NASWA 2025, 3CMA 2026, ICMA 2026</t>
         </is>
       </c>
-      <c r="F145" s="10" t="inlineStr">
+      <c r="F145" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive</t>
         </is>
@@ -30990,7 +31063,7 @@
           <t>AI workflow for county assessors: deed processing, exemptions, taxpayer communication (YC S17) - exhibited at NLC City Summit 2026, IAAO 2026</t>
         </is>
       </c>
-      <c r="F147" s="10" t="inlineStr">
+      <c r="F147" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive</t>
         </is>
@@ -31050,7 +31123,7 @@
           <t>VIP public-sector ERP for Ohio-area local governments; 100% employee-owned - exhibited at GFOA 2026, NRPA 2026</t>
         </is>
       </c>
-      <c r="F149" s="9" t="inlineStr">
+      <c r="F149" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -31818,7 +31891,7 @@
           <t>Cloud ERP for cities and counties covering finance, budgeting, utility billing, payroll, permitting, licensing and code enforcement, built on Oracle NetSuite - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F175" s="10" t="inlineStr">
+      <c r="F175" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -32020,9 +32093,9 @@
           <t>Sells lease and subscription accounting software, including GASB 87 and GASB 96 compliance tools, to local governments, public colleges and companies - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F182" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F182" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Director of Sales Enablement only</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32119,7 @@
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -32068,9 +32141,9 @@
           <t>Kyriba sells cloud treasury, cash forecasting and payments software to federal, state and local government finance teams - exhibited at NACUBO 2026</t>
         </is>
       </c>
-      <c r="F184" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F184" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Strategic Account Executive (New York)</t>
         </is>
       </c>
     </row>
@@ -32116,9 +32189,9 @@
           <t>Sells Sage Intacct cloud accounting software with fund accounting, grant tracking and budgeting to government agencies and special districts - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F186" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F186" s="22" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -32140,9 +32213,9 @@
           <t>Sells revenue recognition and billing software, including IT chargeback and cost recovery software for public sector shared services - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F187" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F187" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -32260,7 +32333,7 @@
           <t>Bill presentment and payments for governments and utilities (public co) - exhibited at GFOA 2026, NAHRO 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F191" s="10" t="inlineStr">
+      <c r="F191" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -32440,7 +32513,7 @@
           <t>Source-to-contract procurement ecosystem (BidNet Direct, Periscope S2G; ex-mdf commerce)</t>
         </is>
       </c>
-      <c r="F197" s="10" t="inlineStr">
+      <c r="F197" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Canada | Remote)</t>
         </is>
@@ -32620,7 +32693,7 @@
           <t>Hosted e-payment portals (tax, tag, court, utility) for county tax commissioners - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F203" s="9" t="inlineStr">
+      <c r="F203" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -32740,7 +32813,7 @@
           <t>Supplier onboarding and payee identity verification preventing payments fraud for gov and higher-ed - exhibited at GFOA 2026, ASBO School Business 2026</t>
         </is>
       </c>
-      <c r="F207" s="10" t="inlineStr">
+      <c r="F207" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -32800,7 +32873,7 @@
           <t>Online surplus auction marketplace for 7,500+ governments and schools</t>
         </is>
       </c>
-      <c r="F209" s="9" t="inlineStr">
+      <c r="F209" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -32892,7 +32965,7 @@
       </c>
       <c r="F212" s="21" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -33154,7 +33227,7 @@
           <t>Expense management and payment software - exhibited at NIGP 2026, NACUBO 2026</t>
         </is>
       </c>
-      <c r="F221" s="10" t="inlineStr">
+      <c r="F221" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive - Midmarket (rem (Atlanta, GA)</t>
         </is>
@@ -33502,9 +33575,9 @@
           <t>Source-to-pay suite with public sector practice serving states and agencies</t>
         </is>
       </c>
-      <c r="F233" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive (United States)</t>
+      <c r="F233" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive (Denmark)</t>
         </is>
       </c>
     </row>
@@ -34268,9 +34341,9 @@
           <t>Business identity, firmographic and supplier-risk data and web-based due-diligence tools sold to federal, state and local agencies for vendor vetting and procurement - exhibited at NAMPI 2026</t>
         </is>
       </c>
-      <c r="F259" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F259" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive III, Tier 2 Bank (Remote - United St)</t>
         </is>
       </c>
     </row>
@@ -34318,7 +34391,7 @@
       </c>
       <c r="F261" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -34430,7 +34503,7 @@
           <t>Pension, OPEB, and labor cost analytics for governments</t>
         </is>
       </c>
-      <c r="F265" s="10" t="inlineStr">
+      <c r="F265" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive</t>
         </is>
@@ -34490,7 +34563,7 @@
           <t>Benefits administration and enrollment built exclusively for public-sector employers - exhibited at SALGBA 2026, ASBO School Business 2026</t>
         </is>
       </c>
-      <c r="F267" s="9" t="inlineStr">
+      <c r="F267" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -34670,7 +34743,7 @@
           <t>Digital heart health app and monitoring - exhibited at NACo 2026, PSHRA 2026, SALGBA 2026, NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F273" s="9" t="inlineStr">
+      <c r="F273" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Director, Labor Sales only</t>
         </is>
@@ -34724,7 +34797,7 @@
           <t>Payroll and HR software - exhibited at AB Show 2026</t>
         </is>
       </c>
-      <c r="F275" s="9" t="inlineStr">
+      <c r="F275" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -34844,7 +34917,7 @@
           <t>Pension, unemployment insurance and workforce systems for state agencies - exhibited at SNA ANC 2027, NASWA 2025</t>
         </is>
       </c>
-      <c r="F279" s="10" t="inlineStr">
+      <c r="F279" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -34904,7 +34977,7 @@
           <t>Employee benefits, enrollment and HR services for public sector employers - exhibited at ASBO School Business 2026</t>
         </is>
       </c>
-      <c r="F281" s="10" t="inlineStr">
+      <c r="F281" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Denver, Colorado)</t>
         </is>
@@ -35202,7 +35275,7 @@
           <t>Document-driven workflow for government procurement, budget and HR processes</t>
         </is>
       </c>
-      <c r="F291" s="9" t="inlineStr">
+      <c r="F291" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
@@ -35444,7 +35517,7 @@
       </c>
       <c r="F299" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -35540,9 +35613,9 @@
           <t>Benefits administration software and services for public sector employers, including municipalities, state agencies and universities - exhibited at SALGBA 2026</t>
         </is>
       </c>
-      <c r="F303" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F303" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Manager, Finance GTM (Remote) only</t>
         </is>
       </c>
     </row>
@@ -35564,9 +35637,9 @@
           <t>Online technology skills training platform with courses, hands-on labs and skill assessments, sold to state and local agencies, federal teams and universities - exhibited at NASCIO 2026</t>
         </is>
       </c>
-      <c r="F304" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F304" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Enterprise Account Executive (2 Locations)</t>
         </is>
       </c>
     </row>
@@ -35614,7 +35687,7 @@
       </c>
       <c r="F306" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -35638,7 +35711,7 @@
       </c>
       <c r="F307" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -35662,7 +35735,7 @@
       </c>
       <c r="F308" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -36384,7 +36457,7 @@
           <t>Work management and collaboration software - exhibited at NACo 2026</t>
         </is>
       </c>
-      <c r="F333" s="10" t="inlineStr">
+      <c r="F333" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -36436,7 +36509,7 @@
           <t>Cybersecurity software and network security platforms - exhibited at IACP 2026, NASCIO 2026, CoSN 2026, EDUCAUSE 2026, ITS America 2026</t>
         </is>
       </c>
-      <c r="F335" s="10" t="inlineStr">
+      <c r="F335" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -36496,7 +36569,7 @@
           <t>Claude, sold to state and local agencies through GSA and cooperative vehicles alongside its commercial business</t>
         </is>
       </c>
-      <c r="F337" s="10" t="inlineStr">
+      <c r="F337" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, AI Native (New York City, NY;)</t>
         </is>
@@ -36666,7 +36739,7 @@
           <t>Symmetri AI operations platform for critical infrastructure operators in water, energy, telecom and healthcare - exhibited at AWWA ACE 2026</t>
         </is>
       </c>
-      <c r="F343" s="9" t="inlineStr">
+      <c r="F343" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Technical Sales Engineer only</t>
         </is>
@@ -36762,9 +36835,9 @@
           <t>Sells cloud-based patch management, vulnerability remediation and endpoint management software to government agencies, universities and companies - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F347" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F347" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive - SLED, Texas an</t>
         </is>
       </c>
     </row>
@@ -36786,9 +36859,9 @@
           <t>Sells the Alteryx One data preparation and analytics platform to state government agencies, K-12 institutions and higher education for reporting, auditing and data integration - exhibited at NACUBO 2026</t>
         </is>
       </c>
-      <c r="F348" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F348" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive (United Kingdom - R)</t>
         </is>
       </c>
     </row>
@@ -36812,7 +36885,7 @@
       </c>
       <c r="F349" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -36834,9 +36907,9 @@
           <t>Agentless cybersecurity platform that gives state and local agencies, universities and school districts visibility into connected IT, OT and IoT assets and their vulnerabilities - exhibited at NASCIO 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F350" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F350" s="22" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -36858,9 +36931,9 @@
           <t>Jira, Confluence and Jira Service Management work-tracking and collaboration software, including a FedRAMP Moderate Atlassian Government Cloud, sold to federal, state and local government agencies - exhibited at NASCIO 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F351" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F351" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -36882,9 +36955,9 @@
           <t>Sells a hybrid data and AI platform for storing, governing and analyzing data to government agencies at the federal, state and local level and to large enterprises - exhibited at NASCIO 2026, MESC 2026</t>
         </is>
       </c>
-      <c r="F352" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F352" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Enterprise Account Executive (Canada &gt; Ontario &gt;)</t>
         </is>
       </c>
     </row>
@@ -36908,7 +36981,7 @@
       </c>
       <c r="F353" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -36930,9 +37003,9 @@
           <t>Sells backup, data protection and cyber recovery software, as SaaS or on premises, to federal, state and local governments, schools and universities, and large enterprises - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F354" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F354" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -36954,9 +37027,9 @@
           <t>Microsoft 365 tenant management and security software for state and local government IT departments, universities and enterprises - exhibited at NASCIO 2026</t>
         </is>
       </c>
-      <c r="F355" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F355" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Enterprise Account Executive - Ita (Italy)</t>
         </is>
       </c>
     </row>
@@ -36980,7 +37053,7 @@
       </c>
       <c r="F356" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -37004,7 +37077,7 @@
       </c>
       <c r="F357" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -37026,9 +37099,9 @@
           <t>Sells the Falcon cybersecurity platform (endpoint, identity and cloud security, SIEM) to state and local government agencies, K-12 and higher education - exhibited at NASCIO 2026</t>
         </is>
       </c>
-      <c r="F358" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F358" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Corporate Account Executive, Kolka (India - Remote)</t>
         </is>
       </c>
     </row>
@@ -37050,9 +37123,9 @@
           <t>Sells privileged access management, password management, DNS filtering and SASE software to local government, K-12 and higher education IT teams and to MSPs - exhibited at GMIS International 2026</t>
         </is>
       </c>
-      <c r="F359" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F359" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -37076,7 +37149,7 @@
       </c>
       <c r="F360" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -37100,7 +37173,7 @@
       </c>
       <c r="F361" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -37124,7 +37197,7 @@
       </c>
       <c r="F362" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -37146,9 +37219,9 @@
           <t>Sells network visibility software and appliances that feed traffic to security tools, for state and local governments and universities - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F363" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F363" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -37172,7 +37245,7 @@
       </c>
       <c r="F364" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -37218,9 +37291,9 @@
           <t>Sells address verification, geocoding and address data software to government agencies and private companies - exhibited at Healthcare IT Connect 2026</t>
         </is>
       </c>
-      <c r="F366" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F366" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive (SMB)</t>
         </is>
       </c>
     </row>
@@ -37242,9 +37315,9 @@
           <t>Sells a vulnerability discovery, bug bounty and pentesting platform to state and local government agencies, schools and universities - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F367" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F367" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Vice President, Partnership Sales only</t>
         </is>
       </c>
     </row>
@@ -37266,9 +37339,9 @@
           <t>Managed endpoint detection and response, identity protection and 24/7 security monitoring for K-12 districts, colleges and state and local governments - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F368" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F368" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive II, Mid-Market (United States of A)</t>
         </is>
       </c>
     </row>
@@ -37314,9 +37387,9 @@
           <t>KYND sells cyber risk monitoring and reporting software to public entity risk pools and their member organizations - exhibited at PRIMA 2026</t>
         </is>
       </c>
-      <c r="F370" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F370" s="22" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -37340,7 +37413,7 @@
       </c>
       <c r="F371" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 403 for https://lumu.io/careers/</t>
         </is>
       </c>
     </row>
@@ -37410,9 +37483,9 @@
           <t>Identity and access management software, including single sign-on and multifactor authentication, for state and local agencies and educational institutions - exhibited at NASCIO 2026</t>
         </is>
       </c>
-      <c r="F374" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F374" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -37458,9 +37531,9 @@
           <t>Orchestry sells Microsoft 365 governance and management software to government agencies and universities - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F376" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F376" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Senior Account Executive - US</t>
         </is>
       </c>
     </row>
@@ -37484,7 +37557,7 @@
       </c>
       <c r="F377" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -37508,7 +37581,7 @@
       </c>
       <c r="F378" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -37604,7 +37677,7 @@
       </c>
       <c r="F382" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -37650,9 +37723,9 @@
           <t>Sells endpoint allowlisting, ringfencing and Zero Trust security software to state and local governments, schools and businesses - exhibited at GMIS International 2026</t>
         </is>
       </c>
-      <c r="F384" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F384" s="22" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -37698,9 +37771,9 @@
           <t>Sells automated software testing tools to state and local government agencies, K-12 schools and higher education - exhibited at GMIS International 2026</t>
         </is>
       </c>
-      <c r="F386" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F386" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Sr. Account Executive (US - Austin)</t>
         </is>
       </c>
     </row>
@@ -37722,9 +37795,9 @@
           <t>Sells cloud object storage for backups, archives and surveillance video to state and local governments, municipalities and school systems - exhibited at GMIS International 2026</t>
         </is>
       </c>
-      <c r="F387" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F387" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -37746,9 +37819,9 @@
           <t>Sells endpoint security, device tracking and secure remote access software to federal, state and local government agencies and schools - exhibited at APCO 2026</t>
         </is>
       </c>
-      <c r="F388" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F388" s="22" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -37772,7 +37845,7 @@
       </c>
       <c r="F389" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -37794,9 +37867,9 @@
           <t>Sells legal operations software for matters, contracts, intake, spend and reporting to in-house legal teams, including city and other government legal departments - exhibited at IMLA 2026</t>
         </is>
       </c>
-      <c r="F390" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F390" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Business Development Representativ only</t>
         </is>
       </c>
     </row>
@@ -37818,9 +37891,9 @@
           <t>Sells a platform for building and running AI agents to enterprises, healthcare organizations and government agencies - exhibited at Healthcare IT Connect 2026</t>
         </is>
       </c>
-      <c r="F391" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F391" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sales Development Representative only</t>
         </is>
       </c>
     </row>
@@ -37902,9 +37975,9 @@
           <t>Strategic planning, performance measurement, and public dashboards built for local government - exhibited at GFOA 2026</t>
         </is>
       </c>
-      <c r="F394" s="22" t="inlineStr">
-        <is>
-          <t>Yes - Senior Account Executive - Public  (Canada)</t>
+      <c r="F394" s="21" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -37932,7 +38005,7 @@
           <t>Strategic plan and KPI reporting (balanced scorecard) for local governments and enterprises</t>
         </is>
       </c>
-      <c r="F395" s="10" t="inlineStr">
+      <c r="F395" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -37992,7 +38065,7 @@
           <t>Location and foot-traffic analytics with an active city/county economic development vertical</t>
         </is>
       </c>
-      <c r="F397" s="10" t="inlineStr">
+      <c r="F397" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (United States, Rem)</t>
         </is>
@@ -38843,7 +38916,7 @@
     <row r="427">
       <c r="A427" s="5" t="inlineStr">
         <is>
-          <t>Dominion Voting Systems</t>
+          <t>Liberty Vote</t>
         </is>
       </c>
       <c r="B427" s="5" t="inlineStr">
@@ -38861,7 +38934,7 @@
       </c>
       <c r="E427" s="5" t="inlineStr">
         <is>
-          <t>Voting systems, tabulators and election management software for jurisdictions</t>
+          <t>Voting systems, tabulators and election management software for jurisdictions - exhibited at NASS Winter/Summer 2026</t>
         </is>
       </c>
       <c r="F427" s="7" t="inlineStr">
@@ -38984,7 +39057,7 @@
           <t>Open-source voting systems and risk-limiting audit tools for election offices</t>
         </is>
       </c>
-      <c r="F431" s="10" t="inlineStr">
+      <c r="F431" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Field Sales (United States)</t>
         </is>
@@ -39834,7 +39907,7 @@
       </c>
       <c r="F460" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -39972,7 +40045,7 @@
           <t>WorldCat shared cataloging, discovery, resource sharing, and library management systems for public, academic, school, and research libraries - exhibited at PLA 2026</t>
         </is>
       </c>
-      <c r="F465" s="9" t="inlineStr">
+      <c r="F465" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Strategic Account Director -Wester only</t>
         </is>
@@ -41348,7 +41421,7 @@
       </c>
       <c r="F515" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -42270,7 +42343,7 @@
           <t>Business phone and unified communications systems - exhibited at NIGP 2026</t>
         </is>
       </c>
-      <c r="F551" s="10" t="inlineStr">
+      <c r="F551" s="9" t="inlineStr">
         <is>
           <t>Yes - Hunter / Account Executive (2 Locations)</t>
         </is>
@@ -42324,7 +42397,7 @@
           <t>Payment processing platform - exhibited at ICMA 2025</t>
         </is>
       </c>
-      <c r="F553" s="10" t="inlineStr">
+      <c r="F553" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -42444,9 +42517,9 @@
           <t>Digital community engagement platform for cities - exhibited at ICMA 2025, NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F558" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F558" s="22" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -42472,7 +42545,7 @@
           <t>Construction project management software - exhibited at ICMA 2025, PWX 2026</t>
         </is>
       </c>
-      <c r="F559" s="9" t="inlineStr">
+      <c r="F559" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -42546,7 +42619,7 @@
       </c>
       <c r="F562" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -42862,9 +42935,9 @@
           <t>E-procurement bid posting and management platform - exhibited at NIGP 2026</t>
         </is>
       </c>
-      <c r="F575" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F575" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -42950,7 +43023,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/19/26)</t>
+          <t>Hiring AEs? (10/20/26)</t>
         </is>
       </c>
     </row>
@@ -43008,7 +43081,7 @@
           <t>Parks &amp; rec program management and booking platform founded by early Uber employees - exhibited at NRPA 2026</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive (San Francisco, CA)</t>
         </is>
@@ -43362,9 +43435,9 @@
           <t>Parks and recreation management software; brands NextRec (formerly PerfectMind), Vermont Systems, RecDesk and ePACT - exhibited at AB Show 2026, NRPA 2026</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive (Glendale, AZ)</t>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sales Development Representative only</t>
         </is>
       </c>
     </row>
@@ -43602,7 +43675,7 @@
           <t>Team and league management apps for youth sports, with a business tier for rec orgs - exhibited at NRPA 2026</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Remote)</t>
         </is>
@@ -43842,7 +43915,7 @@
           <t>Club and league operations platform for youth sports organizations</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -43902,7 +43975,7 @@
           <t>Youth sports program, camp and league management software</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (INDIANAPOLIS, IN)</t>
         </is>
@@ -44082,7 +44155,7 @@
           <t>Club and league management platform for youth soccer organizations</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -44232,9 +44305,9 @@
           <t>Player evaluations and tryout management for youth sports orgs</t>
         </is>
       </c>
-      <c r="F44" s="28" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F44" s="27" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -44442,7 +44515,7 @@
           <t>Campground, park and license reservation systems for state park agencies</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Platform Solutions Engineer only</t>
         </is>
@@ -44474,7 +44547,7 @@
       </c>
       <c r="F52" s="28" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -44798,7 +44871,7 @@
           <t>Sports facility and program management for municipal and community facilities</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -44918,7 +44991,7 @@
           <t>AI drowning-detection and lifeguard assist for public aquatic centers</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -45098,7 +45171,7 @@
           <t>Central irrigation control and smart controllers for municipal parks</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="F73" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -45158,7 +45231,7 @@
           <t>WeatherTRAK smart irrigation and water management for public agencies</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F75" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -45638,7 +45711,7 @@
           <t>Weather safety platform: WBGT heat monitoring, lightning alerts, stations and sirens for parks and athletics - exhibited at NRPA 2026</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, SLED (Perry Weather Offi)</t>
         </is>
@@ -46296,7 +46369,7 @@
           <t>Short-term rental market data for tourism offices and city agencies</t>
         </is>
       </c>
-      <c r="F113" s="10" t="inlineStr">
+      <c r="F113" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Barcelona)</t>
         </is>
@@ -46536,7 +46609,7 @@
           <t>Event management SaaS: vendor applications, ticketing, maps, and sponsors for festivals and city events - exhibited at NRPA 2026</t>
         </is>
       </c>
-      <c r="F121" s="10" t="inlineStr">
+      <c r="F121" s="9" t="inlineStr">
         <is>
           <t>Yes - Sales &amp; Business Development Manag</t>
         </is>
@@ -46596,7 +46669,7 @@
           <t>Venue and event management for convention centers and public authorities</t>
         </is>
       </c>
-      <c r="F123" s="10" t="inlineStr">
+      <c r="F123" s="9" t="inlineStr">
         <is>
           <t>Yes - Senior Account Manager (Germany)</t>
         </is>
@@ -46776,7 +46849,7 @@
           <t>Venue management, ticketing and POS for aquatic centers and attractions</t>
         </is>
       </c>
-      <c r="F129" s="10" t="inlineStr">
+      <c r="F129" s="9" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive - AME (Austin, Texas)</t>
         </is>
@@ -46832,7 +46905,7 @@
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -47217,7 +47290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F162"/>
+  <dimension ref="A1:F170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -47256,7 +47329,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/19/26)</t>
+          <t>Hiring AEs? (10/20/26)</t>
         </is>
       </c>
     </row>
@@ -47314,7 +47387,7 @@
           <t>CrisisAlert wearable panic buttons for school staff; 18M+ people covered</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Yes - Sales Executive - Central Region (Remote Worker - N/)</t>
         </is>
@@ -47434,7 +47507,7 @@
           <t>Device filtering, classroom management, and student wellness (Beacon) - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager - Mid Mar only</t>
         </is>
@@ -47910,7 +47983,7 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - HTTP 410 for https://actuate.ai/careers</t>
         </is>
       </c>
     </row>
@@ -47968,7 +48041,7 @@
           <t>AI weapons detection and screening for schools and public buildings</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -48146,7 +48219,7 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -48492,9 +48565,9 @@
           <t>Student web filtering, device asset tracking, behavior alerts and classroom management software sold to K-12 school districts for school-issued devices - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -48516,9 +48589,9 @@
           <t>Sells battery-free digital locks and cloud-based access management software to schools, municipalities, utilities and property owners - exhibited at APCO 2026</t>
         </is>
       </c>
-      <c r="F44" s="34" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F44" s="35" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -48606,7 +48679,7 @@
           <t>School bus telematics, electronic inspections, and ridership tracking</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F47" s="9" t="inlineStr">
         <is>
           <t>Yes - Sales Account Executive – Mid-Mark</t>
         </is>
@@ -49118,7 +49191,7 @@
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>Unknown - network error: robots.txt on lionlion.ca</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -49232,7 +49305,7 @@
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -49256,7 +49329,7 @@
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -49280,7 +49353,7 @@
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -49428,7 +49501,7 @@
           <t>Thrillshare K-12 communications: district websites, apps, notifications, branding - exhibited at NLC City Summit 2026, CoSN 2026, ICMA 2026</t>
         </is>
       </c>
-      <c r="F75" s="9" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Development Representative only</t>
         </is>
@@ -49548,7 +49621,7 @@
           <t>Student information system and school business/ERP suite for K-12 districts - exhibited at CoSN 2026, ASBO School Business 2026</t>
         </is>
       </c>
-      <c r="F79" s="9" t="inlineStr">
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Technical Special only</t>
         </is>
@@ -49700,7 +49773,7 @@
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -49938,7 +50011,7 @@
       </c>
       <c r="F92" s="35" t="inlineStr">
         <is>
-          <t>Yes - Account Executive, Southern Califo (Remote Southern Ca)</t>
+          <t>Yes - Account Manager, Ohio (Remote Ohio)</t>
         </is>
       </c>
     </row>
@@ -50026,7 +50099,7 @@
           <t>Website, CMS and mass communications platform for school districts</t>
         </is>
       </c>
-      <c r="F95" s="9" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -50086,7 +50159,7 @@
           <t>Family engagement, attendance and communications platform for districts</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Future Opportun (Remote)</t>
         </is>
@@ -50206,7 +50279,7 @@
           <t>K-12 hiring, applicant tracking and talent matching for districts</t>
         </is>
       </c>
-      <c r="F101" s="9" t="inlineStr">
+      <c r="F101" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -50666,7 +50739,7 @@
           <t>Library, technology asset, and facilities management software for K-12 school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F117" s="10" t="inlineStr">
+      <c r="F117" s="9" t="inlineStr">
         <is>
           <t>Yes - Expression of Interest: Outside Sa (Remote - USA)</t>
         </is>
@@ -50724,7 +50797,7 @@
           <t>Classroom communication and engagement app connecting K-12 teachers, students, and families - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F119" s="9" t="inlineStr">
+      <c r="F119" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Revenue Product Lead only</t>
         </is>
@@ -50774,7 +50847,7 @@
           <t>AI browser extension that generates lesson plans, quizzes, and student feedback inside Google Workspace and LMS tools for teachers and school districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F121" s="10" t="inlineStr">
+      <c r="F121" s="9" t="inlineStr">
         <is>
           <t>Yes - Mid-Market Account Executive (Remote)</t>
         </is>
@@ -51164,7 +51237,7 @@
           <t>Browser-delivered virtual computer labs, classroom AI safety controls and work-based learning software for school districts and colleges - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F135" s="10" t="inlineStr">
+      <c r="F135" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -51458,7 +51531,7 @@
       </c>
       <c r="F146" s="34" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -51504,9 +51577,9 @@
           <t>Sells Apple device management and security software to K-12 school districts, universities and businesses - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F148" s="34" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F148" s="35" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive | SMB | New Logo (Minneapolis, MN)</t>
         </is>
       </c>
     </row>
@@ -51600,9 +51673,9 @@
           <t>Sells a digital K-12 curriculum and instruction platform, with print materials and assessment tools, to schools and school districts - exhibited at NSBA 2026</t>
         </is>
       </c>
-      <c r="F152" s="34" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F152" s="35" t="inlineStr">
+        <is>
+          <t>Yes - Field Account Executive, Los Angel (Los Angeles, CA)</t>
         </is>
       </c>
     </row>
@@ -51674,7 +51747,7 @@
       </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -51696,9 +51769,9 @@
           <t>School finance software for K-12 districts that ties fees, payments, activity fund accounting and disbursements to one platform - exhibited at ASBO School Business 2026</t>
         </is>
       </c>
-      <c r="F156" s="34" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F156" s="33" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -51720,9 +51793,9 @@
           <t>Digital ticketing, live streaming, athletic websites and stats tools for high school athletic programs, under the GoFan, NFHS Network and MaxPreps brands - exhibited at ASBO School Business 2026</t>
         </is>
       </c>
-      <c r="F157" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive (New York, NY)</t>
         </is>
       </c>
     </row>
@@ -51770,7 +51843,7 @@
       </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -51792,9 +51865,9 @@
           <t>Goalbook Toolkit, software that helps special education teachers write IEPs and plan specially designed instruction, sold to school districts - exhibited at CEC Convention 2027</t>
         </is>
       </c>
-      <c r="F160" s="34" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F160" s="33" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Customer Success, Southern Califor only</t>
         </is>
       </c>
     </row>
@@ -51842,12 +51915,204 @@
       </c>
       <c r="F162" s="34" t="inlineStr">
         <is>
+          <t>None found</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Account Tree</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="n"/>
+      <c r="C163" s="6" t="n"/>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>Operations &amp; SIS</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>Student activity fund software for K-12 school districts that routes requests, approvals and backup documents and keeps an audit trail - exhibited at ASBO School Business 2026</t>
+        </is>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="31" t="inlineStr">
+        <is>
+          <t>Divot Assets</t>
+        </is>
+      </c>
+      <c r="B164" s="31" t="n"/>
+      <c r="C164" s="32" t="n"/>
+      <c r="D164" s="31" t="inlineStr">
+        <is>
+          <t>Operations &amp; SIS</t>
+        </is>
+      </c>
+      <c r="E164" s="31" t="inlineStr">
+        <is>
+          <t>Fixed asset tracking software for K-12 school districts, plus physical inventory audits, barcode asset tags and consulting - exhibited at ASBO School Business 2026</t>
+        </is>
+      </c>
+      <c r="F164" s="34" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>EFUNDS for Schools</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="n"/>
+      <c r="C165" s="6" t="n"/>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>Operations &amp; SIS</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>Payment processing software for K-12 schools and districts, covering online, point-of-sale, fee and recurring payments across departments - exhibited at ASBO School Business 2026</t>
+        </is>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="31" t="inlineStr">
+        <is>
+          <t>Helios Ed</t>
+        </is>
+      </c>
+      <c r="B166" s="31" t="n"/>
+      <c r="C166" s="32" t="n"/>
+      <c r="D166" s="31" t="inlineStr">
+        <is>
+          <t>Operations &amp; SIS</t>
+        </is>
+      </c>
+      <c r="E166" s="31" t="inlineStr">
+        <is>
+          <t>K-12 HR and workforce management software for school districts, covering hiring, onboarding, absences, timesheets and form approvals - exhibited at ASBO School Business 2026</t>
+        </is>
+      </c>
+      <c r="F166" s="34" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>Journify Learning Inc</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="n"/>
+      <c r="C167" s="6" t="n"/>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>Operations &amp; SIS</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>AI platform for special education teams that builds IEP-aligned assessments and tracks student progress and reports for schools and districts - exhibited at CEC Convention 2027</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="31" t="inlineStr">
+        <is>
+          <t>Learning Ally</t>
+        </is>
+      </c>
+      <c r="B168" s="31" t="n"/>
+      <c r="C168" s="32" t="n"/>
+      <c r="D168" s="31" t="inlineStr">
+        <is>
+          <t>Operations &amp; SIS</t>
+        </is>
+      </c>
+      <c r="E168" s="31" t="inlineStr">
+        <is>
+          <t>Human-read audiobook library and reading app for students with dyslexia, low vision or reading difficulties, sold to schools and districts and to families - exhibited at CEC Convention 2027</t>
+        </is>
+      </c>
+      <c r="F168" s="34" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>Let's Go Learn</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="n"/>
+      <c r="C169" s="6" t="n"/>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>Operations &amp; SIS</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>Online diagnostic assessments and personalized math and reading instruction for K-12 special education and intervention, sold to schools and districts - exhibited at CEC Convention 2027</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - no ATS on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="31" t="inlineStr">
+        <is>
+          <t>SC Strategic Solutions</t>
+        </is>
+      </c>
+      <c r="B170" s="31" t="n"/>
+      <c r="C170" s="32" t="n"/>
+      <c r="D170" s="31" t="inlineStr">
+        <is>
+          <t>Operations &amp; SIS</t>
+        </is>
+      </c>
+      <c r="E170" s="31" t="inlineStr">
+        <is>
+          <t>Records management software with document archiving, e-forms, workflows and scanning services for school districts and municipalities - exhibited at ASBO School Business 2026</t>
+        </is>
+      </c>
+      <c r="F170" s="34" t="inlineStr">
+        <is>
           <t>Unknown - no ATS on file</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F162"/>
+  <autoFilter ref="A1:F170"/>
   <dataValidations count="1">
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid category" error="Pick one of: School Safety, Transportation, Operations &amp; SIS, Suppliers &amp; Services" type="list">
       <formula1>"School Safety,Transportation,Operations &amp; SIS,Suppliers &amp; Services"</formula1>
@@ -51904,7 +52169,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/19/26)</t>
+          <t>Hiring AEs? (10/20/26)</t>
         </is>
       </c>
     </row>
@@ -51962,9 +52227,9 @@
           <t>Justride fare payments SaaS used by hundreds of agencies - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Customer Success Manager - UK only</t>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Salesforce Contractor only</t>
         </is>
       </c>
     </row>
@@ -52082,7 +52347,7 @@
           <t>Contactless open-loop transit payment infrastructure for 400+ providers in 30+ countries - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Yes - Senior Business Development Manage (London)</t>
         </is>
@@ -52438,7 +52703,7 @@
           <t>Check-in/be-out mobile fare payment for public transport authorities</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Head of Strategic Accounts only</t>
         </is>
@@ -52500,7 +52765,7 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t xml:space="preserve">Unknown - network error: robots.txt on moovit.com </t>
         </is>
       </c>
     </row>
@@ -52546,9 +52811,9 @@
           <t>Sells the ZIG hands-free ticketing, fare validation and passenger counting platform to transit agencies, cities and venues - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -52726,7 +52991,7 @@
           <t>HASTUS scheduling, run-cutting, and rostering for transit agencies and postal operators - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Director, Strategic Business Devel only</t>
         </is>
@@ -52786,7 +53051,7 @@
           <t>Holding group of ~34 transit software brands under Constellation (Trapeze, Vontas, TransTrack, TripSpark, TransLoc) - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>Yes - Sales Director (Italy - Signa)</t>
         </is>
@@ -53020,7 +53285,7 @@
           <t>iMarq mobile asset maintenance and MRO platform for transit, rail, and fleets - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -53200,7 +53465,7 @@
           <t>SCADA systems and the SentientQ automation platform for rail transit, LRT, and utilities - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="9" t="inlineStr">
         <is>
           <t>Yes - Business Development Manager</t>
         </is>
@@ -53702,7 +53967,7 @@
       </c>
       <c r="F62" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.gatekee</t>
         </is>
       </c>
     </row>
@@ -53730,7 +53995,7 @@
           <t>Enterprise IP video surveillance and AI analytics for transit, banking, and government - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F63" s="9" t="inlineStr">
         <is>
           <t>Yes - Regional Sales Manager - Transit S</t>
         </is>
@@ -53970,7 +54235,7 @@
           <t>AI dashcam and driver coaching for public fleets</t>
         </is>
       </c>
-      <c r="F71" s="10" t="inlineStr">
+      <c r="F71" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive, Mid-Market (USA)</t>
         </is>
@@ -54062,7 +54327,7 @@
       </c>
       <c r="F74" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.chevinf</t>
         </is>
       </c>
     </row>
@@ -54090,7 +54355,7 @@
           <t>Fleet maintenance management software for transit and government fleets</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F75" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -54210,7 +54475,7 @@
           <t>Digital vehicle inspections and maintenance for municipal fleets</t>
         </is>
       </c>
-      <c r="F79" s="9" t="inlineStr">
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Operations Manager, Customer Succe only</t>
         </is>
@@ -54662,7 +54927,7 @@
       </c>
       <c r="F94" s="39" t="inlineStr">
         <is>
-          <t>Yes - Mass Market Account Executive (California_Remote)</t>
+          <t>Yes - Mass Market Account Executive (Arizona_Remote)</t>
         </is>
       </c>
     </row>
@@ -54750,7 +55015,7 @@
           <t>Solar e-paper real-time passenger information displays and cloud CMS for bus stops and stations - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -54902,7 +55167,7 @@
       </c>
       <c r="F102" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.hanoverdisplays</t>
+          <t>Unknown - network error: robots.txt on www.hanover</t>
         </is>
       </c>
     </row>
@@ -55108,7 +55373,7 @@
           <t>On-demand transit, paratransit, and network planning software for agencies - exhibited at CTAA EXPO 2026, APTA 2026</t>
         </is>
       </c>
-      <c r="F109" s="10" t="inlineStr">
+      <c r="F109" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (Remix) (New York City)</t>
         </is>
@@ -55168,9 +55433,9 @@
           <t>AI microtransit and ADA paratransit operations: scheduling, dispatch, rider app, analytics - exhibited at CTAA EXPO 2026, APTA 2026</t>
         </is>
       </c>
-      <c r="F111" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive (Remote - Canada or)</t>
         </is>
       </c>
     </row>
@@ -56970,7 +57235,7 @@
       </c>
       <c r="F172" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -57078,7 +57343,7 @@
       </c>
       <c r="F176" s="40" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -57124,9 +57389,9 @@
           <t>Infrastructure engineering and asset software - exhibited at APTA 2026, AWWA ACE 2026</t>
         </is>
       </c>
-      <c r="F178" s="40" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F178" s="39" t="inlineStr">
+        <is>
+          <t>Yes - Technical Account Manager (United Kingdom - R)</t>
         </is>
       </c>
     </row>
@@ -57354,7 +57619,7 @@
       </c>
       <c r="F187" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -57452,7 +57717,7 @@
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -57616,7 +57881,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/19/26)</t>
+          <t>Hiring AEs? (10/20/26)</t>
         </is>
       </c>
     </row>
@@ -57734,7 +57999,7 @@
           <t>Autonomous off-grid solar streetlights with remote monitoring; 1,000+ municipalities, 43 states (French parent)</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -57976,7 +58241,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - HTTP 403 for https://evluma.com/about/ca</t>
         </is>
       </c>
     </row>
@@ -58334,7 +58599,7 @@
           <t>Adaptive smart street lighting sensors and CMS for municipalities</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -58874,7 +59139,7 @@
           <t>Exterior LED site and streetscape lighting for public projects</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -58934,7 +59199,7 @@
           <t>Pole-mounted sensors + AI (Gridscope) detecting grid faults, vegetation strikes, and wildfire-risk events</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
@@ -58994,7 +59259,7 @@
           <t>Satellite + AI vegetation management (IVMS) and climate/asset risk SaaS for utilities</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Business Analyst - Customer Succes only</t>
         </is>
@@ -59054,7 +59319,7 @@
           <t>EV ARC transportable solar EV charging and storage for government fleets (Nasdaq: BEEM; ex-Envision Solar)</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -59174,7 +59439,7 @@
           <t>Metering, CIS, billing and grid analytics for public power utilities</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -59234,7 +59499,7 @@
           <t>SCADA, ADMS and outage management for municipal utilities and co-ops</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="F55" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -59354,7 +59619,7 @@
           <t>Smart grid AMI and grid analytics for public power utilities and co-ops - exhibited at APPA Public Power 2026</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Office &amp; Sales Support Coordinator only</t>
         </is>
@@ -59834,7 +60099,7 @@
           <t>Utility bill management and energy analytics for cities, counties and schools</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F75" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive</t>
         </is>
@@ -60072,7 +60337,7 @@
           <t>Outage notification, billing, and omnichannel customer communication platform for investor-owned, municipal, and cooperative utilities - exhibited at APPA Public Power 2026</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="F83" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Executive (US - Remote)</t>
         </is>
@@ -60486,7 +60751,7 @@
           <t>Geospatial network design and field software for telecom and public utilities</t>
         </is>
       </c>
-      <c r="F97" s="9" t="inlineStr">
+      <c r="F97" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Engineer only</t>
         </is>
@@ -60606,7 +60871,7 @@
           <t>Broadband grant, challenge process and mapping software for state broadband offices</t>
         </is>
       </c>
-      <c r="F101" s="9" t="inlineStr">
+      <c r="F101" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Product Solutions Engineer only</t>
         </is>
@@ -61174,7 +61439,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/19/26)</t>
+          <t>Hiring AEs? (10/20/26)</t>
         </is>
       </c>
     </row>
@@ -61644,7 +61909,7 @@
           <t>Aviation design and simulation software (AviPLAN, AeroTURN, GuideSIGN) used by airport planners for aircraft movement, apron layout and airside safety analysis. - exhibited at AAAE 2027</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Manager</t>
         </is>
@@ -61912,7 +62177,7 @@
       </c>
       <c r="F26" s="51" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.damarel</t>
         </is>
       </c>
     </row>
@@ -62060,7 +62325,7 @@
           <t>Airport weather observation systems and runway condition sensors for airports - exhibited at NACE 2026</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -62120,7 +62385,7 @@
           <t>Bird-strike avoidance radar and wildlife management systems for airports</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -62240,7 +62505,7 @@
           <t>ARINC airport systems portfolio: vMUSE common-use passenger processing, SelfPass biometrics, self bag drop, AODB/resource management, FIDS and airport communications sold to airport authorities.</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -62478,7 +62743,7 @@
           <t>Passenger flow, queue measurement and airport revenue software for airport operators</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="9" t="inlineStr">
         <is>
           <t>Yes - Sales Director Americas (US-based within th)</t>
         </is>
@@ -62598,7 +62863,7 @@
           <t>Gate, docking guidance and apron systems for airport operators</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -62658,9 +62923,9 @@
           <t>Baggage handling systems and terminal logistics for airports</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -62778,7 +63043,7 @@
           <t>Self-service kiosks, bag drop and passenger processing for airports</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="F55" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -63258,7 +63523,7 @@
           <t>Ascento Guard autonomous outdoor security robot sold as robot-as-a-service: wheeled-legged patrol unit with thermal/RGB cameras plus AI software for perimeter patrol, intruder detection and site inspection.</t>
         </is>
       </c>
-      <c r="F71" s="9" t="inlineStr">
+      <c r="F71" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Business Development: French-Speak only</t>
         </is>
@@ -63498,7 +63763,7 @@
           <t>Biometric identity, TSA PreCheck enrollment and airport boarding systems</t>
         </is>
       </c>
-      <c r="F79" s="9" t="inlineStr">
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Business Operations and Leadership only</t>
         </is>
@@ -63558,9 +63823,9 @@
           <t>Biometric identity lanes operated under airport and TSA agreements</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
-        <is>
-          <t>Yes - Senior Enterprise Account Executiv (Chicago, IL, Unite)</t>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Senior Enterprise Account Executiv (Dallas, TX, United)</t>
         </is>
       </c>
     </row>
@@ -63678,7 +63943,7 @@
           <t>Perimeter intrusion detection and fence sensors for airports and utilities</t>
         </is>
       </c>
-      <c r="F85" s="10" t="inlineStr">
+      <c r="F85" s="9" t="inlineStr">
         <is>
           <t>Yes - Business Development Manager (Ottawa, Ontario, C)</t>
         </is>
@@ -63916,7 +64181,7 @@
           <t>Automated vehicle inspection portals for airports, borders and government</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F93" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -64036,7 +64301,7 @@
           <t>Computer-vision checkout-free parking payment platform (drive-in/drive-out billing) plus parking operations and revenue management for airports; owner of SP+. - exhibited at AAAE 2027</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="9" t="inlineStr">
         <is>
           <t>Yes - Associate Account Executive (Atlan (Atlanta, Georgia, )</t>
         </is>
@@ -64214,7 +64479,7 @@
           <t>Airport parking reservations and demand channel for airport operators</t>
         </is>
       </c>
-      <c r="F103" s="10" t="inlineStr">
+      <c r="F103" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -64274,7 +64539,7 @@
           <t>Full-service automated parking operations for cities and airports</t>
         </is>
       </c>
-      <c r="F105" s="9" t="inlineStr">
+      <c r="F105" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - Sales Enablement Manager only</t>
         </is>
@@ -64394,7 +64659,7 @@
           <t>AVI readers and ground transportation management systems for airports</t>
         </is>
       </c>
-      <c r="F109" s="10" t="inlineStr">
+      <c r="F109" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -64486,7 +64751,7 @@
       </c>
       <c r="F112" s="51" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - network error: robots.txt on www.smartpa</t>
         </is>
       </c>
     </row>
@@ -64698,7 +64963,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/19/26)</t>
+          <t>Hiring AEs? (10/20/26)</t>
         </is>
       </c>
     </row>
@@ -65034,7 +65299,7 @@
           <t>Digital courtroom recording and speech recognition systems for courts</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
@@ -65152,7 +65417,7 @@
           <t>Criminal justice data collection and public dashboards for counties and states</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
@@ -65212,7 +65477,7 @@
           <t>Cloud ediscovery and litigation platform for law firms, corporations, county DAs, and state AGs - exhibited at IMLA 2026, NASCIO 2026</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>Yes - Enterprise Account Executive (Stat (United States)</t>
         </is>
@@ -65272,7 +65537,7 @@
           <t>PROSECUTORbyKarpel case management software for prosecutor offices - exhibited at IMLA 2026</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>Yes - Account Manager (Remote Worker - N/)</t>
         </is>
@@ -65414,9 +65679,9 @@
           <t>Legal case management software sold to law firms and to state and municipal legal departments, prosecutors and public defenders - exhibited at IMLA 2026</t>
         </is>
       </c>
-      <c r="F26" s="58" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F26" s="57" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -65438,9 +65703,9 @@
           <t>Cloud document and email management software for legal teams in state and local government agencies and higher education institutions - exhibited at IMLA 2026</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive, Public Sector (Remote - US)</t>
         </is>
       </c>
     </row>
@@ -65464,7 +65729,7 @@
       </c>
       <c r="F28" s="58" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -65796,7 +66061,7 @@
       </c>
       <c r="F40" s="58" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/22/26)</t>
+          <t>Hiring AEs? (10/23/26)</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Sweden)</t>
+          <t>Yes - Account Executive - Public Sector  (Las Vegas, Nevada)</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Sales Recruiter (Contract) only</t>
+          <t>Sales (non-AE) - Account Director, Pathfinder (Nati only</t>
         </is>
       </c>
     </row>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="F241" s="9" t="inlineStr">
         <is>
-          <t>Yes - Sales Director (Hong Kong)</t>
+          <t>Yes - Sr Account Executive (United States (Rem)</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="F261" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.guard1.</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.guard1.</t>
         </is>
       </c>
     </row>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/22/26)</t>
+          <t>Hiring AEs? (10/23/26)</t>
         </is>
       </c>
     </row>
@@ -16149,7 +16149,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/22/26)</t>
+          <t>Hiring AEs? (10/23/26)</t>
         </is>
       </c>
     </row>
@@ -17201,7 +17201,7 @@
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://writesea.com/career</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -18627,9 +18627,9 @@
           <t>Conversational AI agent platform sold to universities for admissions, financial aid and student support, and to banks, insurers, retailers and healthcare organizations - exhibited at NACUBO 2026</t>
         </is>
       </c>
-      <c r="F92" s="70" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F92" s="69" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -19451,7 +19451,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/22/26)</t>
+          <t>Hiring AEs? (10/23/26)</t>
         </is>
       </c>
     </row>
@@ -20663,7 +20663,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/22/26)</t>
+          <t>Hiring AEs? (10/23/26)</t>
         </is>
       </c>
     </row>
@@ -25999,9 +25999,9 @@
           <t>Sells satellite IoT connectivity and sensor devices, such as water tank monitors, to government agencies and local councils - exhibited at WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F183" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F183" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -27107,7 +27107,7 @@
       </c>
       <c r="F220" s="16" t="inlineStr">
         <is>
-          <t>Yes - Account Executive – Strategic Acco (Itasca, Illinois)</t>
+          <t>Yes - Sales Director - Net New - Europe  (Staines-upon-Thame)</t>
         </is>
       </c>
     </row>
@@ -28057,7 +28057,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/22/26)</t>
+          <t>Hiring AEs? (10/23/26)</t>
         </is>
       </c>
     </row>
@@ -29661,9 +29661,9 @@
           <t>CodeRED public alerting and critical event management for local jurisdictions</t>
         </is>
       </c>
-      <c r="F55" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -33249,7 +33249,7 @@
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.mtwsolu</t>
         </is>
       </c>
     </row>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="F255" s="7" t="inlineStr">
         <is>
-          <t>Unknown - robots.txt on xpressbillpay.com answered</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -36155,7 +36155,7 @@
       </c>
       <c r="F282" s="22" t="inlineStr">
         <is>
-          <t>Yes - Business Development Manager (NYC Headquarters)</t>
+          <t>Yes - Enterprise Account Executive (US-Remote)</t>
         </is>
       </c>
     </row>
@@ -36419,7 +36419,7 @@
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>Yes - Account Manager (Denver, Colorado)</t>
+          <t>Yes - Account Manager (3 Locations)</t>
         </is>
       </c>
     </row>
@@ -38611,9 +38611,9 @@
           <t>Sells privileged access management, password management, DNS filtering and SASE software to local government, K-12 and higher education IT teams and to MSPs - exhibited at GMIS International 2026</t>
         </is>
       </c>
-      <c r="F371" s="9" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F371" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 504 for https://www.cyberfox.com/ca</t>
         </is>
       </c>
     </row>
@@ -38827,9 +38827,9 @@
           <t>Managed endpoint detection and response, identity protection and 24/7 security monitoring for K-12 districts, colleges and state and local governments - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F380" s="22" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive II, Mid-Market (United States of A)</t>
+      <c r="F380" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Director, Revenue Readiness only</t>
         </is>
       </c>
     </row>
@@ -44551,7 +44551,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/22/26)</t>
+          <t>Hiring AEs? (10/23/26)</t>
         </is>
       </c>
     </row>
@@ -44761,7 +44761,7 @@
       </c>
       <c r="F8" s="27" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Salesforce &amp; RevOps Systems Admini only</t>
+          <t>Sales (non-AE) - Sales Development Representative only</t>
         </is>
       </c>
     </row>
@@ -47403,7 +47403,7 @@
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>Yes - Account Executive - Agriculture (4 Locations)</t>
+          <t>Yes - SaaS Account Executive - Weather (5 Locations)</t>
         </is>
       </c>
     </row>
@@ -48929,7 +48929,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/22/26)</t>
+          <t>Hiring AEs? (10/23/26)</t>
         </is>
       </c>
     </row>
@@ -53175,7 +53175,7 @@
       </c>
       <c r="F148" s="35" t="inlineStr">
         <is>
-          <t>Yes - Account Executive | SMB | New Logo (Minneapolis, MN)</t>
+          <t>Yes - Account Executive, Commercial, ANZ (Sydney, Australia)</t>
         </is>
       </c>
     </row>
@@ -53765,7 +53765,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/22/26)</t>
+          <t>Hiring AEs? (10/23/26)</t>
         </is>
       </c>
     </row>
@@ -53915,7 +53915,7 @@
       </c>
       <c r="F6" s="40" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 401 for https://www.scheidt-bachman</t>
+          <t>Unknown - HTTP 404 for https://www.scheidt-bachman</t>
         </is>
       </c>
     </row>
@@ -55557,7 +55557,7 @@
       </c>
       <c r="F62" s="40" t="inlineStr">
         <is>
-          <t>Unknown - network error: robots.txt on www.gatekee</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -58921,7 +58921,7 @@
       </c>
       <c r="F176" s="39" t="inlineStr">
         <is>
-          <t>Yes - Account Manager, Enterprise (2 Locations)</t>
+          <t>Yes - Support Account Manager, Enterpris (Ireland Dublin Off)</t>
         </is>
       </c>
     </row>
@@ -59411,7 +59411,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/22/26)</t>
+          <t>Hiring AEs? (10/23/26)</t>
         </is>
       </c>
     </row>
@@ -62993,7 +62993,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/22/26)</t>
+          <t>Hiring AEs? (10/23/26)</t>
         </is>
       </c>
     </row>
@@ -64477,9 +64477,9 @@
           <t>Baggage handling systems and terminal logistics for airports</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -65349,7 +65349,7 @@
       </c>
       <c r="F80" s="52" t="inlineStr">
         <is>
-          <t>Yes - Senior Enterprise Account Executiv (New York, New York)</t>
+          <t>Yes - Senior Enterprise Account Executiv (Austin, TX, United)</t>
         </is>
       </c>
     </row>
@@ -66305,7 +66305,7 @@
       </c>
       <c r="F112" s="51" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -66487,7 +66487,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/22/26)</t>
+          <t>Hiring AEs? (10/23/26)</t>
         </is>
       </c>
     </row>
@@ -66633,7 +66633,7 @@
       </c>
       <c r="F6" s="58" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://www.tybera.com/care</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/23/26)</t>
+          <t>Hiring AEs? (10/24/26)</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 502 for https://www.bullard.com/car</t>
         </is>
       </c>
     </row>
@@ -3049,9 +3049,9 @@
           <t>Threat intelligence and OSINT platform for enterprises and public safety</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Sales Director - New England (Remote in the Unit)</t>
         </is>
       </c>
     </row>
@@ -3499,9 +3499,9 @@
           <t>Drone-as-first-responder software and hardware auto-launching to 911 calls</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Sales Development Representative ( only</t>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - board is another company's - not read</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="F261" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: robots.txt on www.guard1.</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -10665,9 +10665,9 @@
           <t>Public safety CAD, RMS, jail software - exhibited at IACP 2026, APCO 2026</t>
         </is>
       </c>
-      <c r="F339" s="9" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F339" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 503 for https://www.cis.com/careers</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>Unknown - network error: robots.txt on www.guard1.</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11669,9 +11669,9 @@
           <t>DigiTICKET electronic citation software - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F380" s="10" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F380" s="4" t="inlineStr">
+        <is>
+          <t>Unknown - network error: robots.txt on saltustechn</t>
         </is>
       </c>
     </row>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/23/26)</t>
+          <t>Hiring AEs? (10/24/26)</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="F58" s="64" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Senior Solutions Consultant - Risk only</t>
+          <t>Sales (non-AE) - Revenue Integrity Analyst only</t>
         </is>
       </c>
     </row>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -16149,7 +16149,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/23/26)</t>
+          <t>Hiring AEs? (10/24/26)</t>
         </is>
       </c>
     </row>
@@ -16343,9 +16343,9 @@
           <t>AI enrollment engagement platform that personalizes web, email, SMS, and voice outreach to prospective students for colleges and independent schools - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F8" s="69" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F8" s="70" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -18115,7 +18115,7 @@
       </c>
       <c r="F72" s="70" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Vice President, Sales only</t>
+          <t>Sales (non-AE) - Sales Development Representative only</t>
         </is>
       </c>
     </row>
@@ -19451,7 +19451,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/23/26)</t>
+          <t>Hiring AEs? (10/24/26)</t>
         </is>
       </c>
     </row>
@@ -20663,7 +20663,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/23/26)</t>
+          <t>Hiring AEs? (10/24/26)</t>
         </is>
       </c>
     </row>
@@ -27107,7 +27107,7 @@
       </c>
       <c r="F220" s="16" t="inlineStr">
         <is>
-          <t>Yes - Sales Director - Net New - Europe  (Staines-upon-Thame)</t>
+          <t>Yes - Senior Account Executive – Strateg (Itasca, Illinois)</t>
         </is>
       </c>
     </row>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="F226" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 504 for https://eptura.com/careers</t>
         </is>
       </c>
     </row>
@@ -28057,7 +28057,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/23/26)</t>
+          <t>Hiring AEs? (10/24/26)</t>
         </is>
       </c>
     </row>
@@ -30207,7 +30207,7 @@
       </c>
       <c r="F74" s="21" t="inlineStr">
         <is>
-          <t>Unknown - board is another company's - not read</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -33749,9 +33749,9 @@
           <t>Bill presentment and payments for governments and utilities (public co) - exhibited at GFOA 2026, NAHRO 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F200" s="22" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F200" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -34993,7 +34993,7 @@
       </c>
       <c r="F242" s="22" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (United States)</t>
+          <t>Yes - Account Executive (Singapore, Singapo)</t>
         </is>
       </c>
     </row>
@@ -35501,9 +35501,9 @@
           <t>Cash and digital payments for child support, tolls and government billers</t>
         </is>
       </c>
-      <c r="F259" s="9" t="inlineStr">
-        <is>
-          <t>Yes - Sr. Account Executive (Tolling) (Remote)</t>
+      <c r="F259" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Vice President, Accounting only</t>
         </is>
       </c>
     </row>
@@ -36003,9 +36003,9 @@
           <t>Benefits administration and enrollment built exclusively for public-sector employers - exhibited at SALGBA 2026, ASBO School Business 2026</t>
         </is>
       </c>
-      <c r="F277" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F277" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown - robots.txt on www.mybentek.com answered </t>
         </is>
       </c>
     </row>
@@ -36747,7 +36747,7 @@
       </c>
       <c r="F302" s="23" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Sr. Customer Success Manager - Gov only</t>
+          <t>Sales (non-AE) - Manager of Customer Success (Remot only</t>
         </is>
       </c>
     </row>
@@ -38087,9 +38087,9 @@
           <t>ChatGPT and the API, sold to public sector including named state and local government roles - exhibited at NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F350" s="22" t="inlineStr">
-        <is>
-          <t>Yes - Business Development Manager, Prod (Munich, Germany)</t>
+      <c r="F350" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Backend Software Engineer, GTM Inn only</t>
         </is>
       </c>
     </row>
@@ -38611,9 +38611,9 @@
           <t>Sells privileged access management, password management, DNS filtering and SASE software to local government, K-12 and higher education IT teams and to MSPs - exhibited at GMIS International 2026</t>
         </is>
       </c>
-      <c r="F371" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - HTTP 504 for https://www.cyberfox.com/ca</t>
+      <c r="F371" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -40487,7 +40487,7 @@
       </c>
       <c r="F442" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://contentactive.com/c</t>
+          <t>Unknown - network error: robots.txt on contentacti</t>
         </is>
       </c>
     </row>
@@ -42305,7 +42305,7 @@
       </c>
       <c r="F506" s="22" t="inlineStr">
         <is>
-          <t>Yes - Regional Sales Manager, K12 &amp; Publ</t>
+          <t>Yes - Sr Account Executive, AMC</t>
         </is>
       </c>
     </row>
@@ -44551,7 +44551,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/23/26)</t>
+          <t>Hiring AEs? (10/24/26)</t>
         </is>
       </c>
     </row>
@@ -44759,9 +44759,9 @@
           <t>SmartRec activity registration and facility management platform - exhibited at NRPA 2026, Washington Recreation and Park Association 2026</t>
         </is>
       </c>
-      <c r="F8" s="27" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Sales Development Representative only</t>
+      <c r="F8" s="29" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive (Montreal, Quebec, )</t>
         </is>
       </c>
     </row>
@@ -48929,7 +48929,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/23/26)</t>
+          <t>Hiring AEs? (10/24/26)</t>
         </is>
       </c>
     </row>
@@ -48989,7 +48989,7 @@
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Yes - Sales Executive - Central Region (Remote Worker - N/)</t>
+          <t>Yes - Sales Executive - Pacific Northwes (Remote Worker - N/)</t>
         </is>
       </c>
     </row>
@@ -50277,7 +50277,7 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>Yes - Sales Account Executive – Mid-Mark</t>
+          <t>Yes - Strategic Sales Director - Enterpr</t>
         </is>
       </c>
     </row>
@@ -52191,9 +52191,9 @@
           <t>Digital hall pass, tardy tracking, behavior management, and campus engagement platform for K-12 schools and districts - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F112" s="35" t="inlineStr">
-        <is>
-          <t>Yes - Account Manager (INTERNAL APPLICAN</t>
+      <c r="F112" s="33" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Entry Level Sales Opportunity - SD only</t>
         </is>
       </c>
     </row>
@@ -53765,7 +53765,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/23/26)</t>
+          <t>Hiring AEs? (10/24/26)</t>
         </is>
       </c>
     </row>
@@ -55557,7 +55557,7 @@
       </c>
       <c r="F62" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.gatekee</t>
         </is>
       </c>
     </row>
@@ -56785,7 +56785,7 @@
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Unknown - robots.txt on basemap.co.uk answered HTT</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -59271,7 +59271,7 @@
       </c>
       <c r="F190" s="39" t="inlineStr">
         <is>
-          <t>Yes - Sales Account Executive – Mid-Mark</t>
+          <t>Yes - Strategic Sales Director - Enterpr</t>
         </is>
       </c>
     </row>
@@ -59411,7 +59411,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/23/26)</t>
+          <t>Hiring AEs? (10/24/26)</t>
         </is>
       </c>
     </row>
@@ -61749,7 +61749,7 @@
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -62993,7 +62993,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/23/26)</t>
+          <t>Hiring AEs? (10/24/26)</t>
         </is>
       </c>
     </row>
@@ -64477,9 +64477,9 @@
           <t>Baggage handling systems and terminal logistics for airports</t>
         </is>
       </c>
-      <c r="F51" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -65349,7 +65349,7 @@
       </c>
       <c r="F80" s="52" t="inlineStr">
         <is>
-          <t>Yes - Senior Enterprise Account Executiv (Austin, TX, United)</t>
+          <t>Yes - Senior Enterprise Account Executiv (New York, New York)</t>
         </is>
       </c>
     </row>
@@ -65527,9 +65527,9 @@
           <t>Passive airspace monitoring sensors for airports and government agencies</t>
         </is>
       </c>
-      <c r="F86" s="51" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F86" s="53" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Director of Business Development - only</t>
         </is>
       </c>
     </row>
@@ -66487,7 +66487,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/23/26)</t>
+          <t>Hiring AEs? (10/24/26)</t>
         </is>
       </c>
     </row>
@@ -66633,7 +66633,7 @@
       </c>
       <c r="F6" s="58" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.tybera.com/care</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -230,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -358,6 +358,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="25" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -943,7 +944,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/24/26)</t>
+          <t>Hiring AEs? (10/25/26)</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1804,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 502 for https://www.bullard.com/car</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6712,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6952,7 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7974,7 @@
       </c>
       <c r="F243" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10048,7 @@
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10144,7 @@
       </c>
       <c r="F318" s="4" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -10213,9 +10214,9 @@
           <t>Mobile core and radio network products, including the iNAC managed access system that blocks contraband cellphones in correctional facilities - exhibited at ACA Congress 2026</t>
         </is>
       </c>
-      <c r="F321" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F321" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10264,7 @@
       </c>
       <c r="F323" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -10665,9 +10666,9 @@
           <t>Public safety CAD, RMS, jail software - exhibited at IACP 2026, APCO 2026</t>
         </is>
       </c>
-      <c r="F339" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - HTTP 503 for https://www.cis.com/careers</t>
+      <c r="F339" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -11469,9 +11470,9 @@
           <t>Enterprise database, cloud and ERP software - exhibited at IACP 2026, NSA 2026, GFOA 2026, PSHRA 2026, NatCon 2026, APTA 2026, ICC 2026, ASBO School Business 2026</t>
         </is>
       </c>
-      <c r="F372" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F372" s="10" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -11669,9 +11670,9 @@
           <t>DigiTICKET electronic citation software - exhibited at IACP 2026</t>
         </is>
       </c>
-      <c r="F380" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - network error: robots.txt on saltustechn</t>
+      <c r="F380" s="10" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -12145,7 +12146,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/24/26)</t>
+          <t>Hiring AEs? (10/25/26)</t>
         </is>
       </c>
     </row>
@@ -12605,7 +12606,7 @@
       </c>
       <c r="F20" s="63" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -12627,9 +12628,9 @@
           <t>Roving and stationary air pollution and greenhouse gas sensor network with Aclima Pro analytics software for governments, companies and communities</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Vice President, Business Developme only</t>
         </is>
       </c>
     </row>
@@ -12777,9 +12778,9 @@
           <t>AI decision and case platforms for state health and human services</t>
         </is>
       </c>
-      <c r="F26" s="63" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F26" s="64" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13410,7 @@
       </c>
       <c r="F48" s="63" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -13803,9 +13804,9 @@
           <t>MCase case management for child welfare and human services agencies - exhibited at APHSA 2026</t>
         </is>
       </c>
-      <c r="F64" s="63" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F64" s="64" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -14131,7 +14132,7 @@
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -15479,7 +15480,7 @@
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -16149,7 +16150,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/24/26)</t>
+          <t>Hiring AEs? (10/25/26)</t>
         </is>
       </c>
     </row>
@@ -19199,7 +19200,7 @@
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -19225,9 +19226,9 @@
           <t>Tuition payment plans, billing, cashiering, and payment processing software for colleges and universities - exhibited at NACUBO 2026</t>
         </is>
       </c>
-      <c r="F116" s="69" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F116" s="70" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - CRM Solutions Architect only</t>
         </is>
       </c>
     </row>
@@ -19451,7 +19452,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/24/26)</t>
+          <t>Hiring AEs? (10/25/26)</t>
         </is>
       </c>
     </row>
@@ -19899,7 +19900,7 @@
       </c>
       <c r="F18" s="75" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -19971,7 +19972,7 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -20019,7 +20020,7 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20044,7 @@
       </c>
       <c r="F24" s="75" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -20091,7 +20092,7 @@
       </c>
       <c r="F26" s="75" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -20115,7 +20116,7 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20140,7 @@
       </c>
       <c r="F28" s="75" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -20161,9 +20162,9 @@
           <t>MRI Software sells public housing software for HUD compliance reporting, voucher management, waitlists and resident portals to public housing agencies - exhibited at NAHRO 2026</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive (Cleveland, Ohio Of)</t>
         </is>
       </c>
     </row>
@@ -20361,7 +20362,7 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -20505,7 +20506,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -20527,9 +20528,9 @@
           <t>JobsEQ labor market data and analytics platform, including a Housing Demand tool, for economic development, workforce development, education and corporate users</t>
         </is>
       </c>
-      <c r="F44" s="75" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F44" s="77" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Sales Development Representative only</t>
         </is>
       </c>
     </row>
@@ -20575,9 +20576,9 @@
           <t>Economic impact modeling software and data used by governments, economic development organizations and other industries</t>
         </is>
       </c>
-      <c r="F46" s="75" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F46" s="76" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -20663,7 +20664,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/24/26)</t>
+          <t>Hiring AEs? (10/25/26)</t>
         </is>
       </c>
     </row>
@@ -27287,7 +27288,7 @@
       </c>
       <c r="F226" s="15" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 504 for https://eptura.com/careers</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -28057,7 +28058,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/24/26)</t>
+          <t>Hiring AEs? (10/25/26)</t>
         </is>
       </c>
     </row>
@@ -32065,9 +32066,9 @@
           <t>License portability platform that helps state licensing boards process out-of-state credentials for military families and veterans</t>
         </is>
       </c>
-      <c r="F141" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F141" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -33581,9 +33582,9 @@
           <t>AI workflow software for county assessor offices: homestead exemption monitoring, application vetting and property transfer automation</t>
         </is>
       </c>
-      <c r="F194" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F194" s="22" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -33749,9 +33750,9 @@
           <t>Bill presentment and payments for governments and utilities (public co) - exhibited at GFOA 2026, NAHRO 2026, EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F200" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+      <c r="F200" s="22" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -34669,7 +34670,7 @@
       </c>
       <c r="F231" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - board is another company's - not read</t>
         </is>
       </c>
     </row>
@@ -34993,7 +34994,7 @@
       </c>
       <c r="F242" s="22" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Singapore, Singapo)</t>
+          <t>Yes - Account Executive (United States)</t>
         </is>
       </c>
     </row>
@@ -35023,7 +35024,7 @@
       </c>
       <c r="F243" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -35855,7 +35856,7 @@
       </c>
       <c r="F272" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -36003,9 +36004,9 @@
           <t>Benefits administration and enrollment built exclusively for public-sector employers - exhibited at SALGBA 2026, ASBO School Business 2026</t>
         </is>
       </c>
-      <c r="F277" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown - robots.txt on www.mybentek.com answered </t>
+      <c r="F277" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -37247,7 +37248,7 @@
       </c>
       <c r="F321" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -39427,9 +39428,9 @@
           <t>AI agents for state government staff and public-facing AI concierges that help residents complete permits and licenses - exhibited at NCSL Legislative Summit 2026</t>
         </is>
       </c>
-      <c r="F405" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F405" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -39453,7 +39454,7 @@
       </c>
       <c r="F406" s="21" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -39475,9 +39476,9 @@
           <t>AI governance platform that discovers AI tool use, enforces AI policy and runs governed AI workflows for state and local agencies</t>
         </is>
       </c>
-      <c r="F407" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F407" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -40487,7 +40488,7 @@
       </c>
       <c r="F442" s="21" t="inlineStr">
         <is>
-          <t>Unknown - network error: robots.txt on contentacti</t>
+          <t>Unknown - HTTP 404 for https://contentactive.com/c</t>
         </is>
       </c>
     </row>
@@ -40757,7 +40758,7 @@
       </c>
       <c r="F451" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -43649,9 +43650,9 @@
           <t>Content management and workflow automation software - exhibited at ICMA 2025</t>
         </is>
       </c>
-      <c r="F556" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F556" s="22" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -44551,7 +44552,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/24/26)</t>
+          <t>Hiring AEs? (10/25/26)</t>
         </is>
       </c>
     </row>
@@ -46183,7 +46184,7 @@
       </c>
       <c r="F56" s="28" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -47253,7 +47254,7 @@
       </c>
       <c r="F92" s="28" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -48929,7 +48930,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/24/26)</t>
+          <t>Hiring AEs? (10/25/26)</t>
         </is>
       </c>
     </row>
@@ -49289,7 +49290,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -50185,9 +50186,9 @@
           <t>Enterprise browser with built-in security, data protection and CIPA content filtering, sold to K-12 districts among other industries - exhibited at NASCIO 2026</t>
         </is>
       </c>
-      <c r="F44" s="34" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F44" s="35" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -53557,9 +53558,9 @@
           <t>Fixed asset tracking software for K-12 school districts, plus physical inventory audits, barcode asset tags and consulting - exhibited at ASBO School Business 2026</t>
         </is>
       </c>
-      <c r="F164" s="34" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F164" s="35" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -53607,7 +53608,7 @@
       </c>
       <c r="F166" s="34" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -53677,9 +53678,9 @@
           <t>Online diagnostic assessments and personalized math and reading instruction for K-12 special education and intervention, sold to schools and districts - exhibited at CEC Convention 2027</t>
         </is>
       </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -53765,7 +53766,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/24/26)</t>
+          <t>Hiring AEs? (10/25/26)</t>
         </is>
       </c>
     </row>
@@ -55407,7 +55408,7 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -58945,9 +58946,9 @@
           <t>Transit CAD/AVL and asset management software - exhibited at APTA 2026</t>
         </is>
       </c>
-      <c r="F177" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F177" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -59411,7 +59412,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/24/26)</t>
+          <t>Hiring AEs? (10/25/26)</t>
         </is>
       </c>
     </row>
@@ -61451,7 +61452,7 @@
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -61749,7 +61750,7 @@
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -62097,7 +62098,7 @@
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -62993,7 +62994,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/24/26)</t>
+          <t>Hiring AEs? (10/25/26)</t>
         </is>
       </c>
     </row>
@@ -65349,7 +65350,7 @@
       </c>
       <c r="F80" s="52" t="inlineStr">
         <is>
-          <t>Yes - Senior Enterprise Account Executiv (New York, New York)</t>
+          <t>Yes - Senior Enterprise Account Executiv (Austin, TX, United)</t>
         </is>
       </c>
     </row>
@@ -66213,9 +66214,9 @@
           <t>Parking access and revenue control systems for airports and cities</t>
         </is>
       </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - no ATS on file</t>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -66487,7 +66488,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/24/26)</t>
+          <t>Hiring AEs? (10/25/26)</t>
         </is>
       </c>
     </row>
@@ -66997,7 +66998,7 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Unknown - no ATS on file</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -944,7 +944,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/27/26)</t>
+          <t>Hiring AEs? (10/28/26)</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>Yes - Account Executive - Public Sector  (Las Vegas, Nevada)</t>
+          <t>Yes - Enterprise Account Executive - Cor (California)</t>
         </is>
       </c>
     </row>
@@ -6290,9 +6290,9 @@
           <t>Sells Pro ATE automated speed-camera enforcement systems, with AI violation processing and ticketing back-office services, to police departments, cities and counties - exhibited at Maryland Municipal League 2026, North Carolina Sheriffs' Association 2026</t>
         </is>
       </c>
-      <c r="F185" s="9" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 404 for https://altumint.com/career</t>
         </is>
       </c>
     </row>
@@ -9106,9 +9106,9 @@
           <t>Verus AI platform transcribing and analyzing inmate calls for threat and contraband investigations - exhibited at ACA Congress 2026</t>
         </is>
       </c>
-      <c r="F285" s="9" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F285" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -12506,7 +12506,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/27/26)</t>
+          <t>Hiring AEs? (10/28/26)</t>
         </is>
       </c>
     </row>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/27/26)</t>
+          <t>Hiring AEs? (10/28/26)</t>
         </is>
       </c>
     </row>
@@ -19812,7 +19812,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/27/26)</t>
+          <t>Hiring AEs? (10/28/26)</t>
         </is>
       </c>
     </row>
@@ -20524,7 +20524,7 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Cleveland, Ohio Of)</t>
+          <t>Yes - Account Executive I (Cleveland, Ohio Of)</t>
         </is>
       </c>
     </row>
@@ -21048,7 +21048,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/27/26)</t>
+          <t>Hiring AEs? (10/28/26)</t>
         </is>
       </c>
     </row>
@@ -21166,9 +21166,9 @@
           <t>AI robotic sorting systems for recycling facilities (MRFs) - exhibited at SWANA WASTECON 2025, WasteExpo 2027</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Director, Commercial Origination &amp; only</t>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -22200,9 +22200,9 @@
           <t>Carts, containers and compactors supplied to municipal waste programs</t>
         </is>
       </c>
-      <c r="F40" s="15" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>Yes - Outside Sales Representative (4 Locations)</t>
         </is>
       </c>
     </row>
@@ -24506,9 +24506,9 @@
           <t>Permitting, compliance, and workflow software for water utilities - exhibited at AWWA ACE 2026, WEFTEC 2026</t>
         </is>
       </c>
-      <c r="F119" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Senior Customer Success Manager only</t>
         </is>
       </c>
     </row>
@@ -26114,7 +26114,7 @@
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://streametric.io/care</t>
+          <t>Unknown - HTTP 504 for https://streametric.io/care</t>
         </is>
       </c>
     </row>
@@ -26596,7 +26596,7 @@
       </c>
       <c r="F191" s="9" t="inlineStr">
         <is>
-          <t>Yes - Key Account Executive (Remote) (Remote - Australia)</t>
+          <t>Yes - Business Development Manager - Mon (Monterrey, Nuevo L)</t>
         </is>
       </c>
     </row>
@@ -27792,7 +27792,7 @@
       </c>
       <c r="F231" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://eptura.com/careers</t>
         </is>
       </c>
     </row>
@@ -28610,7 +28610,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/27/26)</t>
+          <t>Hiring AEs? (10/28/26)</t>
         </is>
       </c>
     </row>
@@ -28670,7 +28670,7 @@
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Yes - Account Executive - New Logo - Nor</t>
+          <t>Yes - Associate Account Executive</t>
         </is>
       </c>
     </row>
@@ -28758,9 +28758,9 @@
           <t>Community surveys, benchmarking, and budget simulation (owns National Research Center)</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive (Madison, WI)</t>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (London)</t>
+          <t>Yes - Account Executive (San Francisco)</t>
         </is>
       </c>
     </row>
@@ -35246,7 +35246,7 @@
       </c>
       <c r="F232" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - board is another company's - not read</t>
         </is>
       </c>
     </row>
@@ -35570,7 +35570,7 @@
       </c>
       <c r="F243" s="9" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Denmark)</t>
+          <t>Yes - Account Executive (United States)</t>
         </is>
       </c>
     </row>
@@ -38260,7 +38260,7 @@
       </c>
       <c r="F337" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: robots.txt on www.tribute</t>
+          <t>Unknown - board is another company's - not read</t>
         </is>
       </c>
     </row>
@@ -38286,9 +38286,9 @@
           <t>Deathcare technology suite including cemetery and memorial management software</t>
         </is>
       </c>
-      <c r="F338" s="21" t="inlineStr">
-        <is>
-          <t>Unknown - network error: robots.txt on www.tribute</t>
+      <c r="F338" s="23" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -40268,9 +40268,9 @@
           <t>Policy and rulemaking workflow: draft, route, approve, and track regulations for agencies</t>
         </is>
       </c>
-      <c r="F416" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Customer Success Lead only</t>
+      <c r="F416" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Enterprise Sales Lead, Southeast (Southeast)</t>
         </is>
       </c>
     </row>
@@ -41638,9 +41638,9 @@
           <t>Ballot tracking, electronic ballot delivery and election tools for jurisdictions</t>
         </is>
       </c>
-      <c r="F463" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F463" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 404 for https://www.enhancedvoting.</t>
         </is>
       </c>
     </row>
@@ -45248,7 +45248,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/27/26)</t>
+          <t>Hiring AEs? (10/28/26)</t>
         </is>
       </c>
     </row>
@@ -46190,9 +46190,9 @@
           <t>Club and league operations platform for youth sports organizations</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - network error: robots.txt on home.playme</t>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -46430,9 +46430,9 @@
           <t>Club and league management platform for youth soccer organizations</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - network error: robots.txt on byga.net di</t>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -48126,7 +48126,7 @@
       </c>
       <c r="F98" s="29" t="inlineStr">
         <is>
-          <t>Yes - SaaS Account Executive - Weather (5 Locations)</t>
+          <t>Yes - Account Manager - Agriculture (4 Locations)</t>
         </is>
       </c>
     </row>
@@ -49626,7 +49626,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/27/26)</t>
+          <t>Hiring AEs? (10/28/26)</t>
         </is>
       </c>
     </row>
@@ -50488,9 +50488,9 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F30" s="34" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -51484,7 +51484,7 @@
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>Unknown - network error: robots.txt on lionlion.ca</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -54462,7 +54462,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/27/26)</t>
+          <t>Hiring AEs? (10/28/26)</t>
         </is>
       </c>
     </row>
@@ -56584,7 +56584,7 @@
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Customer Success Manager only</t>
+          <t>Sales (non-AE) - Customer Success Manager (Client S only</t>
         </is>
       </c>
     </row>
@@ -56912,9 +56912,9 @@
           <t>Fare collection and transit operations systems for agencies</t>
         </is>
       </c>
-      <c r="F84" s="41" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Solution Architect only</t>
+      <c r="F84" s="40" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -60108,7 +60108,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/27/26)</t>
+          <t>Hiring AEs? (10/28/26)</t>
         </is>
       </c>
     </row>
@@ -61452,7 +61452,7 @@
       </c>
       <c r="F46" s="46" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Customer Success Manager only</t>
+          <t>Sales (non-AE) - Customer Success Manager (CA or TX only</t>
         </is>
       </c>
     </row>
@@ -62350,9 +62350,9 @@
           <t>Utility bill management and energy analytics for cities, counties and schools</t>
         </is>
       </c>
-      <c r="F76" s="47" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive</t>
+      <c r="F76" s="45" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -64338,7 +64338,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/27/26)</t>
+          <t>Hiring AEs? (10/28/26)</t>
         </is>
       </c>
     </row>
@@ -66694,7 +66694,7 @@
       </c>
       <c r="F80" s="52" t="inlineStr">
         <is>
-          <t>Yes - Senior Enterprise Account Executiv (Dallas, TX, United)</t>
+          <t>Yes - Senior Enterprise Account Executiv (New York, New York)</t>
         </is>
       </c>
     </row>
@@ -67832,7 +67832,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/27/26)</t>
+          <t>Hiring AEs? (10/28/26)</t>
         </is>
       </c>
     </row>
@@ -68572,9 +68572,9 @@
           <t>Legal case management software sold to law firms and to state and municipal legal departments, prosecutors and public defenders - exhibited at IMLA 2026</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -944,7 +944,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/28/26)</t>
+          <t>Hiring AEs? (10/29/26)</t>
         </is>
       </c>
     </row>
@@ -2504,9 +2504,9 @@
           <t>License plate readers, gunshot detection, and drone-as-first-responder (Aerodome) - exhibited at ITS America 2026, FDIC International 2026, TRB 2027</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Principal Sales Operations Busines only</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="F197" s="9" t="inlineStr">
         <is>
-          <t>Yes - Sales Executive, Strategic Account (Seattle, WA)</t>
+          <t>Yes - Strategic Account Manager, Hospita (2 Locations)</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>Unknown - board is another company's - not read</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -11827,7 +11827,7 @@
       </c>
       <c r="E387" s="5" t="inlineStr">
         <is>
-          <t>Enterprise database, cloud and ERP software - exhibited at IACP 2026, NSA 2026, GFOA 2026, PSHRA 2026, NatCon 2026, APTA 2026, ICC 2026, ASBO School Business 2026, DISTRIBUTECH 2026</t>
+          <t>Enterprise database, cloud and ERP software - exhibited at IACP 2026, NSA 2026, GFOA 2026, PSHRA 2026, NatCon 2026, APTA 2026, ICC 2026, ASBO School Business 2026, DISTRIBUTECH 2026, APA California Chapter 2026</t>
         </is>
       </c>
       <c r="F387" s="11" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/28/26)</t>
+          <t>Hiring AEs? (10/29/26)</t>
         </is>
       </c>
     </row>
@@ -12577,7 +12577,7 @@
       </c>
       <c r="E4" s="61" t="inlineStr">
         <is>
-          <t>Casetivity-based public health software - immunization information systems, electronic disease surveillance, early intervention, lead poisoning prevention and vital records - for state and local public health agencies - exhibited at AIRA 2026</t>
+          <t>Casetivity-based public health software - immunization information systems, electronic disease surveillance, early intervention, lead poisoning prevention and vital records - for state and local public health agencies - exhibited at AIRA 2026, Pennsylvania Chapter of the APA 2026</t>
         </is>
       </c>
       <c r="F4" s="63" t="inlineStr">
@@ -13170,7 +13170,7 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Yes - Commercial Account Executive, Truv (Remote – United St)</t>
+          <t>Yes - Account Executive, Springbuk (Remote – United St)</t>
         </is>
       </c>
     </row>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/28/26)</t>
+          <t>Hiring AEs? (10/29/26)</t>
         </is>
       </c>
     </row>
@@ -16966,9 +16966,9 @@
           <t>Peer review, group work, and AI feedback tools that plug into university learning management systems - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive (Texas) (US Remote)</t>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -17726,9 +17726,9 @@
           <t>Scaffold platform for LMS migration, course archiving, and data warehousing across LMS, SIS, and CRM systems at colleges and universities - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F44" s="71" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F44" s="70" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -19586,9 +19586,9 @@
           <t>Tuition payment plans, billing, cashiering, and payment processing software for colleges and universities - exhibited at NACUBO 2026</t>
         </is>
       </c>
-      <c r="F116" s="70" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - CRM Solutions Architect only</t>
+      <c r="F116" s="71" t="inlineStr">
+        <is>
+          <t>Yes - Senior Account Manager- G&amp;A/SGO -  (Remote)</t>
         </is>
       </c>
     </row>
@@ -19750,7 +19750,7 @@
       </c>
       <c r="F122" s="71" t="inlineStr">
         <is>
-          <t>Yes - Senior Account Executive (London)</t>
+          <t>Yes - Account Executive - Denmark (2 Locations)</t>
         </is>
       </c>
     </row>
@@ -19812,7 +19812,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/28/26)</t>
+          <t>Hiring AEs? (10/29/26)</t>
         </is>
       </c>
     </row>
@@ -21048,7 +21048,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/28/26)</t>
+          <t>Hiring AEs? (10/29/26)</t>
         </is>
       </c>
     </row>
@@ -22998,7 +22998,7 @@
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>Yes - (Mid-Level) Account Manager Nether (Zaltbommel, Gelder)</t>
+          <t>Yes - Account Manager Netherlands (Zaltbommel, Gelder)</t>
         </is>
       </c>
     </row>
@@ -24776,9 +24776,9 @@
           <t>Underground utility, geotech, and environmental records aggregated into one map for capital projects</t>
         </is>
       </c>
-      <c r="F128" s="17" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Strategic Customer Success Manager only</t>
+      <c r="F128" s="16" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive - Engineering Fi (Remote)</t>
         </is>
       </c>
     </row>
@@ -26114,7 +26114,7 @@
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 504 for https://streametric.io/care</t>
+          <t>Unknown - HTTP 404 for https://streametric.io/care</t>
         </is>
       </c>
     </row>
@@ -26531,7 +26531,7 @@
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>ArcGIS - the mapping and asset data backbone of most public works departments - exhibited at NLC City Summit 2026, AWWA ACE 2026, IAAO 2026, NASCIO 2026, WEFTEC 2026, IAFC FRI 2026, APCO 2026, APTA 2026, NRPA 2026, IAEM 2026, NCSL Legislative Summit 2026, URISA GIS-Pro 2026, NSGIC 2026, DISTRIBUTECH 2026, FDIC International 2026, FDIC International 2027, TRB 2027, DISTRIBUTECH 2027</t>
+          <t>ArcGIS - the mapping and asset data backbone of most public works departments - exhibited at NLC City Summit 2026, AWWA ACE 2026, IAAO 2026, NASCIO 2026, WEFTEC 2026, IAFC FRI 2026, APCO 2026, APTA 2026, NRPA 2026, IAEM 2026, NCSL Legislative Summit 2026, URISA GIS-Pro 2026, NSGIC 2026, DISTRIBUTECH 2026, FDIC International 2026, FDIC International 2027, TRB 2027, DISTRIBUTECH 2027, APA Texas Chapter 2026</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
@@ -26956,7 +26956,7 @@
       </c>
       <c r="F203" s="9" t="inlineStr">
         <is>
-          <t>Yes - Account Executive, CMRL - MX (Mexico City - Hybr)</t>
+          <t>Yes - Account Executive, Enterprise - Mo (United States - Re)</t>
         </is>
       </c>
     </row>
@@ -27612,7 +27612,7 @@
       </c>
       <c r="F225" s="9" t="inlineStr">
         <is>
-          <t>Yes - Senior Account Executive – Strateg (Itasca, Illinois)</t>
+          <t>Yes - Customer Account Manager, Manufact (Itasca, Illinois)</t>
         </is>
       </c>
     </row>
@@ -27792,7 +27792,7 @@
       </c>
       <c r="F231" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://eptura.com/careers</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -28610,7 +28610,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/28/26)</t>
+          <t>Hiring AEs? (10/29/26)</t>
         </is>
       </c>
     </row>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>AI assistant trained on a government's institutional knowledge; $3.5M seed backed by Granicus founders - exhibited at GFOA 2026, AWWA ACE 2026, GMIS International 2026</t>
+          <t>AI assistant trained on a government's institutional knowledge; $3.5M seed backed by Granicus founders - exhibited at GFOA 2026, AWWA ACE 2026, GMIS International 2026, APA California Chapter 2026</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -30031,7 +30031,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Interactive document feedback and public comment tool for agencies</t>
+          <t>Interactive document feedback and public comment tool for agencies - exhibited at APA California Chapter 2026, APA Colorado Chapter 2026</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -30531,7 +30531,7 @@
       </c>
       <c r="E66" s="19" t="inlineStr">
         <is>
-          <t>Community engagement and stakeholder relationship management platform for councils, transportation agencies, and infrastructure project owners - exhibited at 3CMA 2026</t>
+          <t>Community engagement and stakeholder relationship management platform for councils, transportation agencies, and infrastructure project owners - exhibited at 3CMA 2026, APA California Chapter 2026</t>
         </is>
       </c>
       <c r="F66" s="21" t="inlineStr">
@@ -31125,7 +31125,7 @@
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Permitting, licensing, and code enforcement platform for state and local government - exhibited at NLC City Summit 2026, ICMA 2026, NRPA 2026, ICC 2026</t>
+          <t>Permitting, licensing, and code enforcement platform for state and local government - exhibited at NLC City Summit 2026, ICMA 2026, NRPA 2026, ICC 2026, APA California Chapter 2026, APA - Illinois Chapter 2026, APA Virginia Chapter 2026</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -31155,7 +31155,7 @@
       </c>
       <c r="E90" s="19" t="inlineStr">
         <is>
-          <t>Permitting, budgeting, procurement, and asset management cloud suite (Cox-owned) - exhibited at GFOA 2026, NLC City Summit 2026, NACE 2026, AWWA ACE 2026, GMIS International 2026, Maryland Municipal League 2026, WEFTEC 2026, NRPA 2026, ICC 2026, ASBO School Business 2026</t>
+          <t>Permitting, budgeting, procurement, and asset management cloud suite (Cox-owned) - exhibited at GFOA 2026, NLC City Summit 2026, NACE 2026, AWWA ACE 2026, GMIS International 2026, Maryland Municipal League 2026, WEFTEC 2026, NRPA 2026, ICC 2026, ASBO School Business 2026, APA Texas Chapter 2026</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
@@ -31215,7 +31215,7 @@
       </c>
       <c r="E92" s="19" t="inlineStr">
         <is>
-          <t>AI permitting and licensing platform: 24/7 resident assistant, AI code-compliance review - exhibited at NLC City Summit 2026, Maryland Municipal League 2026, ICC 2026</t>
+          <t>AI permitting and licensing platform: 24/7 resident assistant, AI code-compliance review - exhibited at NLC City Summit 2026, Maryland Municipal League 2026, ICC 2026, APA Colorado Chapter 2026, APA Minnesota Chapter 2026, APA Texas Chapter 2026, APA Virginia Chapter 2026, APA Washington Chapter 2026, APA Wisconsin Chapter 2026, American Planning Association Ohio Chapter 2026, Georgia Planning Association 2026, Joint Montana &amp; Idaho Chapter Conference 2026, NY Upstate Chapter of the APA 2026, Pennsylvania Chapter of the APA 2026</t>
         </is>
       </c>
       <c r="F92" s="22" t="inlineStr">
@@ -31545,7 +31545,7 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>AI permitting and plan review: automated GIS/code compliance checks (Hernando County cut reviews 30 days to 2)</t>
+          <t>AI permitting and plan review: automated GIS/code compliance checks (Hernando County cut reviews 30 days to 2) - exhibited at APA Maryland 2026, APA Washington Chapter 2026</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
@@ -31575,7 +31575,7 @@
       </c>
       <c r="E104" s="19" t="inlineStr">
         <is>
-          <t>AI-native land-use permit management: reads applications, flags issues, drafts review reports (YC S26) - exhibited at NLC City Summit 2026</t>
+          <t>AI-native land-use permit management: reads applications, flags issues, drafts review reports (YC S26) - exhibited at NLC City Summit 2026, APA California Chapter 2026, APA Oklahoma Chapter 2026</t>
         </is>
       </c>
       <c r="F104" s="21" t="inlineStr">
@@ -31668,9 +31668,9 @@
           <t>Agent-native AI 'GovOS' for local gov permitting, licensing, and procurement (~$55M Series A, ex-DeepMind) - exhibited at ICMA 2026, NIGP 2026, ICC 2026, NLC City Summit 2026</t>
         </is>
       </c>
-      <c r="F107" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Sales Engineer only</t>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive, State (Remote)</t>
         </is>
       </c>
     </row>
@@ -32357,7 +32357,7 @@
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>AI planning and building code assessment tools sold to councils and cities - exhibited at ICMA 2026, Smart Cities Connect 2026, ICC 2026</t>
+          <t>AI planning and building code assessment tools sold to councils and cities - exhibited at ICMA 2026, Smart Cities Connect 2026, ICC 2026, APA California Chapter 2026</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
@@ -32519,7 +32519,7 @@
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>Sells AI site-feasibility software to home builders and AI permit intake and plan review software to local government planning and permitting departments - exhibited at ICMA 2026</t>
+          <t>Sells AI site-feasibility software to home builders and AI permit intake and plan review software to local government planning and permitting departments - exhibited at ICMA 2026, APA California Chapter 2026</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
@@ -32639,7 +32639,7 @@
       </c>
       <c r="E142" s="19" t="inlineStr">
         <is>
-          <t>Permitting and entitlements software for city, county and state planning departments: guided applicant intake, auto-drafted review checklists, jurisdiction fee calculators and a searchable staff answer base</t>
+          <t>Permitting and entitlements software for city, county and state planning departments: guided applicant intake, auto-drafted review checklists, jurisdiction fee calculators and a searchable staff answer base - exhibited at APA California Chapter 2026</t>
         </is>
       </c>
       <c r="F142" s="22" t="inlineStr">
@@ -32669,7 +32669,7 @@
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>The govtech giant: ERP, courts, public safety, permitting, and payments - exhibited at GFOA 2026, NLC City Summit 2026, PSHRA 2026, AWWA ACE 2026, IAAO 2026, NASCIO 2026, GMIS International 2026, NACM 2026, APPA Probation 2026, Iowa State Association of Counties 2026, Maryland Municipal League 2026, IAFC FRI 2026, APCO 2026, NAPT Summit 2026, Connecticut Conference of Municipalities 2026, Illinois Chapter of APCO 2026, ICC 2026, ASBO School Business 2026, NACVSO 2026, ACA Congress 2026, FDIC International 2026</t>
+          <t>The govtech giant: ERP, courts, public safety, permitting, and payments - exhibited at GFOA 2026, NLC City Summit 2026, PSHRA 2026, AWWA ACE 2026, IAAO 2026, NASCIO 2026, GMIS International 2026, NACM 2026, APPA Probation 2026, Iowa State Association of Counties 2026, Maryland Municipal League 2026, IAFC FRI 2026, APCO 2026, NAPT Summit 2026, Connecticut Conference of Municipalities 2026, Illinois Chapter of APCO 2026, ICC 2026, ASBO School Business 2026, NACVSO 2026, ACA Congress 2026, FDIC International 2026, APA Colorado Chapter 2026, APA - Illinois Chapter 2026, APA Minnesota Chapter 2026, APA Texas Chapter 2026, APA Virginia Chapter 2026, APA Wisconsin Chapter 2026, American Planning Association Ohio Chapter 2026, Georgia Planning Association 2026, Michigan Association of Planning 2026</t>
         </is>
       </c>
       <c r="F143" s="9" t="inlineStr">
@@ -35570,7 +35570,7 @@
       </c>
       <c r="F243" s="9" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (United States)</t>
+          <t>Yes - Account Executive (Denmark)</t>
         </is>
       </c>
     </row>
@@ -37322,9 +37322,9 @@
           <t>License verification and workforce compliance for agencies and regulators</t>
         </is>
       </c>
-      <c r="F303" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Manager of Customer Success (Remot only</t>
+      <c r="F303" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -37444,7 +37444,7 @@
       </c>
       <c r="F307" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://www.harrislocalgov.</t>
+          <t>Unknown - HTTP 503 for https://www.harrislocalgov.</t>
         </is>
       </c>
     </row>
@@ -39404,9 +39404,9 @@
           <t>Sells a vulnerability discovery, bug bounty and pentesting platform to state and local government agencies, schools and universities - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F381" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Applications Engineer, GTM Systems only</t>
+      <c r="F381" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive – Commercial, En (San Francisco)</t>
         </is>
       </c>
     </row>
@@ -40270,7 +40270,7 @@
       </c>
       <c r="F416" s="22" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Sales Lead, Southeast (Southeast)</t>
+          <t>Yes - Enterprise Sales Lead, Northeast (Northeast)</t>
         </is>
       </c>
     </row>
@@ -40355,7 +40355,7 @@
       </c>
       <c r="E419" s="5" t="inlineStr">
         <is>
-          <t>Demographic data, mapping, and visualization with 500K+ variables for gov, academia, and planning</t>
+          <t>Demographic data, mapping, and visualization with 500K+ variables for gov, academia, and planning - exhibited at NY Upstate Chapter of the APA 2026</t>
         </is>
       </c>
       <c r="F419" s="7" t="inlineStr">
@@ -40704,7 +40704,7 @@
       </c>
       <c r="F431" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: robots.txt on www.maxar.c</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -44319,7 +44319,7 @@
       </c>
       <c r="E561" s="5" t="inlineStr">
         <is>
-          <t>Code Council digital permitting/code solutions - exhibited at ICMA 2025, IMLA 2026, Maryland Municipal League 2026</t>
+          <t>Code Council digital permitting/code solutions - exhibited at ICMA 2025, IMLA 2026, Maryland Municipal League 2026, APA California Chapter 2026, APA Texas Chapter 2026</t>
         </is>
       </c>
       <c r="F561" s="7" t="inlineStr">
@@ -45248,7 +45248,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/28/26)</t>
+          <t>Hiring AEs? (10/29/26)</t>
         </is>
       </c>
     </row>
@@ -48126,7 +48126,7 @@
       </c>
       <c r="F98" s="29" t="inlineStr">
         <is>
-          <t>Yes - Account Manager - Agriculture (4 Locations)</t>
+          <t>Yes - SaaS Account Executive - Weather (United Kingdom - R)</t>
         </is>
       </c>
     </row>
@@ -48932,9 +48932,9 @@
           <t>Event management SaaS: vendor applications, ticketing, maps, and sponsors for festivals and city events - exhibited at NRPA 2026</t>
         </is>
       </c>
-      <c r="F125" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Account Strategist only</t>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Sales &amp; Business Development Manag</t>
         </is>
       </c>
     </row>
@@ -49626,7 +49626,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/28/26)</t>
+          <t>Hiring AEs? (10/29/26)</t>
         </is>
       </c>
     </row>
@@ -50488,9 +50488,9 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F30" s="35" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F30" s="34" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -51484,7 +51484,7 @@
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on lionlion.ca</t>
         </is>
       </c>
     </row>
@@ -52186,7 +52186,7 @@
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -52890,7 +52890,7 @@
       </c>
       <c r="F112" s="33" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Entry Level Sales Opportunity - SD only</t>
+          <t>Sales (non-AE) - Sales Development Representative - only</t>
         </is>
       </c>
     </row>
@@ -53364,9 +53364,9 @@
           <t>AI platform for K-12 districts giving teachers lesson and assessment generation tools and students guided AI, with district-level policy and privacy controls - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F129" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive (K12 Education)  (Alabama)</t>
         </is>
       </c>
     </row>
@@ -54462,7 +54462,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/28/26)</t>
+          <t>Hiring AEs? (10/29/26)</t>
         </is>
       </c>
     </row>
@@ -54966,9 +54966,9 @@
           <t>Check-in/be-out mobile fare payment for public transport authorities</t>
         </is>
       </c>
-      <c r="F18" s="41" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Head of Strategic Accounts only</t>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -56254,7 +56254,7 @@
       </c>
       <c r="F62" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.gatekee</t>
         </is>
       </c>
     </row>
@@ -57627,7 +57627,7 @@
       </c>
       <c r="E108" s="37" t="inlineStr">
         <is>
-          <t>On-demand transit, paratransit, and network planning software for agencies - exhibited at CTAA EXPO 2026, APTA 2026</t>
+          <t>On-demand transit, paratransit, and network planning software for agencies - exhibited at CTAA EXPO 2026, APTA 2026, APA Texas Chapter 2026</t>
         </is>
       </c>
       <c r="F108" s="39" t="inlineStr">
@@ -60108,7 +60108,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/28/26)</t>
+          <t>Hiring AEs? (10/29/26)</t>
         </is>
       </c>
     </row>
@@ -61452,7 +61452,7 @@
       </c>
       <c r="F46" s="46" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Customer Success Manager (CA or TX only</t>
+          <t>Sales (non-AE) - Customer Success Manager only</t>
         </is>
       </c>
     </row>
@@ -64338,7 +64338,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/28/26)</t>
+          <t>Hiring AEs? (10/29/26)</t>
         </is>
       </c>
     </row>
@@ -65822,9 +65822,9 @@
           <t>Baggage handling systems and terminal logistics for airports</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -66694,7 +66694,7 @@
       </c>
       <c r="F80" s="52" t="inlineStr">
         <is>
-          <t>Yes - Senior Enterprise Account Executiv (New York, New York)</t>
+          <t>Yes - Senior Enterprise Account Executiv (Chicago, IL, Unite)</t>
         </is>
       </c>
     </row>
@@ -67832,7 +67832,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/28/26)</t>
+          <t>Hiring AEs? (10/29/26)</t>
         </is>
       </c>
     </row>
@@ -68572,9 +68572,9 @@
           <t>Legal case management software sold to law firms and to state and municipal legal departments, prosecutors and public defenders - exhibited at IMLA 2026</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -230,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -358,7 +358,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="25" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -944,7 +943,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/29/26)</t>
+          <t>Hiring AEs? (10/30/26)</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2955,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - robots.txt on www.365labs.com answered H</t>
         </is>
       </c>
     </row>
@@ -12506,7 +12505,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/29/26)</t>
+          <t>Hiring AEs? (10/30/26)</t>
         </is>
       </c>
     </row>
@@ -16510,7 +16509,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/29/26)</t>
+          <t>Hiring AEs? (10/30/26)</t>
         </is>
       </c>
     </row>
@@ -16966,9 +16965,9 @@
           <t>Peer review, group work, and AI feedback tools that plug into university learning management systems - exhibited at EDUCAUSE 2026</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - Customer Success Manager North Ame only</t>
         </is>
       </c>
     </row>
@@ -19812,7 +19811,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/29/26)</t>
+          <t>Hiring AEs? (10/30/26)</t>
         </is>
       </c>
     </row>
@@ -20888,9 +20887,9 @@
           <t>JobsEQ labor market data and analytics platform, including a Housing Demand tool, for economic development, workforce development, education and corporate users</t>
         </is>
       </c>
-      <c r="F44" s="77" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Sales Development Representative only</t>
+      <c r="F44" s="76" t="inlineStr">
+        <is>
+          <t>Yes - Account Executive (Richmond, VA)</t>
         </is>
       </c>
     </row>
@@ -21048,7 +21047,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/29/26)</t>
+          <t>Hiring AEs? (10/30/26)</t>
         </is>
       </c>
     </row>
@@ -26866,7 +26865,7 @@
       </c>
       <c r="F200" s="15" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 403 for https://www.aurigo.com/care</t>
+          <t>Unknown - HTTP 404 for https://www.aurigo.com/care</t>
         </is>
       </c>
     </row>
@@ -26956,7 +26955,7 @@
       </c>
       <c r="F203" s="9" t="inlineStr">
         <is>
-          <t>Yes - Account Executive, Enterprise - Mo (United States - Re)</t>
+          <t>Yes - Account Executive, Mid-Market - MX (Mexico City - Hybr)</t>
         </is>
       </c>
     </row>
@@ -27346,7 +27345,7 @@
       </c>
       <c r="F216" s="15" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - robots.txt on www.projectmates.com answe</t>
         </is>
       </c>
     </row>
@@ -27792,7 +27791,7 @@
       </c>
       <c r="F231" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 403 for https://eptura.com/careers</t>
         </is>
       </c>
     </row>
@@ -28610,7 +28609,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/29/26)</t>
+          <t>Hiring AEs? (10/30/26)</t>
         </is>
       </c>
     </row>
@@ -28878,9 +28877,9 @@
           <t>AI resident feedback: surveys, sentiment analytics, and engagement for cities and police - exhibited at 3CMA 2026</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - robots.txt on zencity.io answered HTTP 2</t>
         </is>
       </c>
     </row>
@@ -32332,7 +32331,7 @@
       </c>
       <c r="F130" s="22" t="inlineStr">
         <is>
-          <t>Yes - Strategic Account Executive (New Zealand)</t>
+          <t>Yes - Business Development Manager (Reading)</t>
         </is>
       </c>
     </row>
@@ -35222,7 +35221,7 @@
       </c>
       <c r="F231" s="9" t="inlineStr">
         <is>
-          <t>Yes - Account Executive - Midmarket (rem (United States (Wes)</t>
+          <t>Yes - Account Executive - Midmarket (Dal (Dallas, TX)</t>
         </is>
       </c>
     </row>
@@ -35246,7 +35245,7 @@
       </c>
       <c r="F232" s="21" t="inlineStr">
         <is>
-          <t>Unknown - board is another company's - not read</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -36108,7 +36107,7 @@
       </c>
       <c r="F261" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -36702,7 +36701,7 @@
       </c>
       <c r="F282" s="21" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://passportworkforce.c</t>
+          <t>Unknown - robots.txt on passportworkforce.com answ</t>
         </is>
       </c>
     </row>
@@ -37656,7 +37655,7 @@
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (2 Locations)</t>
+          <t>Yes - Regional Sales Director - APAC (Remote - Australia)</t>
         </is>
       </c>
     </row>
@@ -39046,7 +39045,7 @@
       </c>
       <c r="F366" s="22" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive (Canada &gt; Ontario &gt;)</t>
+          <t>Yes - Account Executive - SLED (6 Locations)</t>
         </is>
       </c>
     </row>
@@ -44796,7 +44795,7 @@
       </c>
       <c r="F580" s="21" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - robots.txt on www.proofpoint.com answere</t>
         </is>
       </c>
     </row>
@@ -45248,7 +45247,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/29/26)</t>
+          <t>Hiring AEs? (10/30/26)</t>
         </is>
       </c>
     </row>
@@ -49626,7 +49625,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/29/26)</t>
+          <t>Hiring AEs? (10/30/26)</t>
         </is>
       </c>
     </row>
@@ -50342,7 +50341,7 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>Yes - Regional Sales Manager (Boston, Massachuse)</t>
+          <t>Yes - Regional Sales Manager (District of Columb)</t>
         </is>
       </c>
     </row>
@@ -50488,9 +50487,9 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F30" s="34" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -50518,9 +50517,9 @@
           <t>Emergency mass notification hardware and software for schools and agencies - exhibited at EDUCAUSE 2026, IAEM 2026</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>Yes - Account Manager (Baltimore, MD)</t>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
         </is>
       </c>
     </row>
@@ -52186,7 +52185,7 @@
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -54086,9 +54085,9 @@
           <t>Digital ticketing, live streaming, athletic websites and stats tools for high school athletic programs, under the GoFan, NFHS Network and MaxPreps brands - exhibited at ASBO School Business 2026</t>
         </is>
       </c>
-      <c r="F157" s="9" t="inlineStr">
-        <is>
-          <t>Yes - Account Executive (New York, NY)</t>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -54462,7 +54461,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/29/26)</t>
+          <t>Hiring AEs? (10/30/26)</t>
         </is>
       </c>
     </row>
@@ -54762,7 +54761,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - robots.txt on www.modeshift.com answered</t>
         </is>
       </c>
     </row>
@@ -55400,7 +55399,7 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - HTTP 202 for https://www.enghouse.com/ca</t>
         </is>
       </c>
     </row>
@@ -57424,7 +57423,7 @@
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - robots.txt on www.hanoverdisplays.com an</t>
         </is>
       </c>
     </row>
@@ -57812,7 +57811,7 @@
       </c>
       <c r="F114" s="40" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - robots.txt on qryde.com answered HTTP 20</t>
         </is>
       </c>
     </row>
@@ -60108,7 +60107,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/29/26)</t>
+          <t>Hiring AEs? (10/30/26)</t>
         </is>
       </c>
     </row>
@@ -64338,7 +64337,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/29/26)</t>
+          <t>Hiring AEs? (10/30/26)</t>
         </is>
       </c>
     </row>
@@ -64750,7 +64749,7 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Senior Sales Operations Analyst only</t>
+          <t>Sales (non-AE) - Lead Sales Engineer only</t>
         </is>
       </c>
     </row>
@@ -65822,9 +65821,9 @@
           <t>Baggage handling systems and terminal logistics for airports</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>Sales (non-AE) - sales roles, none AE</t>
         </is>
       </c>
     </row>
@@ -66694,7 +66693,7 @@
       </c>
       <c r="F80" s="52" t="inlineStr">
         <is>
-          <t>Yes - Senior Enterprise Account Executiv (Chicago, IL, Unite)</t>
+          <t>Yes - Senior Enterprise Account Executiv (Dallas, TX, United)</t>
         </is>
       </c>
     </row>
@@ -67832,7 +67831,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/29/26)</t>
+          <t>Hiring AEs? (10/30/26)</t>
         </is>
       </c>
     </row>
@@ -68622,7 +68621,7 @@
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Customer Success Manager - LegalFi only</t>
+          <t>Sales (non-AE) - Mid-Market Customer Success Manage only</t>
         </is>
       </c>
     </row>

--- a/exports/GovTech_Company_Tracker.xlsx
+++ b/exports/GovTech_Company_Tracker.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/30/26)</t>
+          <t>Hiring AEs? (10/31/26)</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Yes - Senior Account Executive - Cyberse (Texas, US Offsite,)</t>
+          <t>Yes - Senior Account Executive (Arizona) (Phoenix, AZ, More.)</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>Yes - Strategic Account Executive - NJ/N (New Jersey, New Yo)</t>
+          <t>Yes - Regional Account Executive - NJ/NY (New Jersey, New Yo)</t>
         </is>
       </c>
     </row>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="F192" s="8" t="inlineStr">
         <is>
-          <t>Yes - Account Manager (Remote, US (TN/KY))</t>
+          <t>Yes - Account Manager (Remote, US (West))</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12505,7 @@
       </c>
       <c r="F1" s="60" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/30/26)</t>
+          <t>Hiring AEs? (10/31/26)</t>
         </is>
       </c>
     </row>
@@ -14223,9 +14223,9 @@
           <t>Foster care, adoption and child welfare software for county/state agencies - exhibited at APHSA 2026</t>
         </is>
       </c>
-      <c r="F66" s="64" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F66" s="63" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on streamlineh</t>
         </is>
       </c>
     </row>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="F1" s="66" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/30/26)</t>
+          <t>Hiring AEs? (10/31/26)</t>
         </is>
       </c>
     </row>
@@ -17863,9 +17863,9 @@
           <t>Wi-Fi-based space occupancy analytics and planning software for colleges and universities - exhibited at NACUBO 2026</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - page scan found no listings</t>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -19811,7 +19811,7 @@
       </c>
       <c r="F1" s="72" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/30/26)</t>
+          <t>Hiring AEs? (10/31/26)</t>
         </is>
       </c>
     </row>
@@ -21047,7 +21047,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/30/26)</t>
+          <t>Hiring AEs? (10/31/26)</t>
         </is>
       </c>
     </row>
@@ -21255,9 +21255,9 @@
           <t>Smart bin fill-level sensors and collection route optimization</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Unknown - HTTP 404 for https://www.sensoneo.com/ca</t>
         </is>
       </c>
     </row>
@@ -24627,7 +24627,7 @@
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>Sales (non-AE) - Revenue Operations Analyst only</t>
+          <t>Sales (non-AE) - Sales Development Representative only</t>
         </is>
       </c>
     </row>
@@ -27345,7 +27345,7 @@
       </c>
       <c r="F216" s="15" t="inlineStr">
         <is>
-          <t>Unknown - robots.txt on www.projectmates.com answe</t>
+          <t>Unknown - HTTP 502 for https://www.projectmates.co</t>
         </is>
       </c>
     </row>
@@ -27611,7 +27611,7 @@
       </c>
       <c r="F225" s="9" t="inlineStr">
         <is>
-          <t>Yes - Customer Account Manager, Manufact (Itasca, Illinois)</t>
+          <t>Yes - Strategic Account Manager, Manufac (Itasca, Illinois)</t>
         </is>
       </c>
     </row>
@@ -28371,7 +28371,7 @@
       </c>
       <c r="F253" s="7" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -28609,7 +28609,7 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/30/26)</t>
+          <t>Hiring AEs? (10/31/26)</t>
         </is>
       </c>
     </row>
@@ -28879,7 +28879,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>Unknown - robots.txt on zencity.io answered HTTP 2</t>
+          <t xml:space="preserve">Unknown - network error: robots.txt on zencity.io </t>
         </is>
       </c>
     </row>
@@ -30955,7 +30955,7 @@
       </c>
       <c r="F82" s="22" t="inlineStr">
         <is>
-          <t>Yes - Enterprise Account Executive, Fina (Richmond)</t>
+          <t>Yes - Enterprise Account Executive, Fina (Boston)</t>
         </is>
       </c>
     </row>
@@ -31669,7 +31669,7 @@
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>Yes - Account Executive, State (Remote)</t>
+          <t>Yes - Account Executive, Gov (Remote)</t>
         </is>
       </c>
     </row>
@@ -33801,7 +33801,7 @@
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: robots.txt on www.mtwsolu</t>
+          <t>Unknown - page too small - likely JS-rendered</t>
         </is>
       </c>
     </row>
@@ -35569,7 +35569,7 @@
       </c>
       <c r="F243" s="9" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Denmark)</t>
+          <t>Yes - Account Executive (Singapore, Singapo)</t>
         </is>
       </c>
     </row>
@@ -36107,7 +36107,7 @@
       </c>
       <c r="F261" s="7" t="inlineStr">
         <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -36579,9 +36579,9 @@
           <t>Benefits administration and enrollment built exclusively for public-sector employers - exhibited at SALGBA 2026, ASBO School Business 2026</t>
         </is>
       </c>
-      <c r="F278" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F278" s="21" t="inlineStr">
+        <is>
+          <t>Unknown - network error: robots.txt on www.mybente</t>
         </is>
       </c>
     </row>
@@ -39427,9 +39427,9 @@
           <t>Managed endpoint detection and response, identity protection and 24/7 security monitoring for K-12 districts, colleges and state and local governments - exhibited at CoSN 2026</t>
         </is>
       </c>
-      <c r="F382" s="23" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - Director, Revenue Readiness only</t>
+      <c r="F382" s="22" t="inlineStr">
+        <is>
+          <t>Yes - Technical Account Manager II (United States of A)</t>
         </is>
       </c>
     </row>
@@ -40237,9 +40237,9 @@
           <t>Strategic plan and KPI reporting (balanced scorecard) for local governments and enterprises</t>
         </is>
       </c>
-      <c r="F415" s="9" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F415" s="7" t="inlineStr">
+        <is>
+          <t>None found</t>
         </is>
       </c>
     </row>
@@ -41099,7 +41099,7 @@
       </c>
       <c r="F445" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 404 for https://runbeck.net/careers</t>
+          <t xml:space="preserve">Unknown - robots.txt on runbeck.net answered HTTP </t>
         </is>
       </c>
     </row>
@@ -44795,7 +44795,7 @@
       </c>
       <c r="F580" s="21" t="inlineStr">
         <is>
-          <t>Unknown - robots.txt on www.proofpoint.com answere</t>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -45247,7 +45247,7 @@
       </c>
       <c r="F1" s="24" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/30/26)</t>
+          <t>Hiring AEs? (10/31/26)</t>
         </is>
       </c>
     </row>
@@ -47529,9 +47529,9 @@
           <t>WeatherTRAK smart irrigation and water management for public agencies</t>
         </is>
       </c>
-      <c r="F78" s="28" t="inlineStr">
-        <is>
-          <t>Unknown - HTTP 404 for https://www.hydropoint.com/</t>
+      <c r="F78" s="29" t="inlineStr">
+        <is>
+          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
         </is>
       </c>
     </row>
@@ -49625,7 +49625,7 @@
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/30/26)</t>
+          <t>Hiring AEs? (10/31/26)</t>
         </is>
       </c>
     </row>
@@ -50487,9 +50487,9 @@
           <t>InformaCast mass notification and paging for school districts</t>
         </is>
       </c>
-      <c r="F30" s="35" t="inlineStr">
-        <is>
-          <t>Yes - AE-type role (page scan) [page scan - verify]</t>
+      <c r="F30" s="34" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -50517,9 +50517,9 @@
           <t>Emergency mass notification hardware and software for schools and agencies - exhibited at EDUCAUSE 2026, IAEM 2026</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>Unknown - network error: HTTPSConnectionPool(host=</t>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Account Manager (Baltimore, MD)</t>
         </is>
       </c>
     </row>
@@ -54037,9 +54037,9 @@
           <t>School payment and fundraising platform for K-12 districts, schools, PTOs and booster clubs, covering student fees, ticketing and stores - exhibited at ASBO School Business 2026</t>
         </is>
       </c>
-      <c r="F155" s="7" t="inlineStr">
-        <is>
-          <t>None found</t>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>Yes - District Account Executive</t>
         </is>
       </c>
     </row>
@@ -54461,7 +54461,7 @@
       </c>
       <c r="F1" s="36" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/30/26)</t>
+          <t>Hiring AEs? (10/31/26)</t>
         </is>
       </c>
     </row>
@@ -54761,7 +54761,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Unknown - robots.txt on www.modeshift.com answered</t>
+          <t>Unknown - network error: robots.txt on www.modeshi</t>
         </is>
       </c>
     </row>
@@ -54877,7 +54877,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Unknown - page scan found no listings</t>
+          <t>Unknown - network error: robots.txt on www.pptexce</t>
         </is>
       </c>
     </row>
@@ -55399,7 +55399,7 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Unknown - HTTP 202 for https://www.enghouse.com/ca</t>
+          <t>Unknown - network error: robots.txt on www.enghous</t>
         </is>
       </c>
     </row>
@@ -57423,7 +57423,7 @@
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Unknown - robots.txt on www.hanoverdisplays.com an</t>
+          <t>Unknown - network error: robots.txt on www.hanover</t>
         </is>
       </c>
     </row>
@@ -57631,7 +57631,7 @@
       </c>
       <c r="F108" s="39" t="inlineStr">
         <is>
-          <t>Yes - Account Executive (Remix) (New York City)</t>
+          <t>Yes - Account Executive (Remix) (San Francisco)</t>
         </is>
       </c>
     </row>
@@ -57811,7 +57811,7 @@
       </c>
       <c r="F114" s="40" t="inlineStr">
         <is>
-          <t>Unknown - robots.txt on qryde.com answered HTTP 20</t>
+          <t>Unknown - network error: robots.txt on qryde.com d</t>
         </is>
       </c>
     </row>
@@ -60107,7 +60107,7 @@
       </c>
       <c r="F1" s="42" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/30/26)</t>
+          <t>Hiring AEs? (10/31/26)</t>
         </is>
       </c>
     </row>
@@ -64337,7 +64337,7 @@
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/30/26)</t>
+          <t>Hiring AEs? (10/31/26)</t>
         </is>
       </c>
     </row>
@@ -65821,9 +65821,9 @@
           <t>Baggage handling systems and terminal logistics for airports</t>
         </is>
       </c>
-      <c r="F51" s="11" t="inlineStr">
-        <is>
-          <t>Sales (non-AE) - sales roles, none AE</t>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Unknown - page scan found no listings</t>
         </is>
       </c>
     </row>
@@ -66693,7 +66693,7 @@
       </c>
       <c r="F80" s="52" t="inlineStr">
         <is>
-          <t>Yes - Senior Enterprise Account Executiv (Dallas, TX, United)</t>
+          <t>Yes - Senior Enterprise Account Executiv (Chicago, IL, Unite)</t>
         </is>
       </c>
     </row>
@@ -67831,7 +67831,7 @@
       </c>
       <c r="F1" s="54" t="inlineStr">
         <is>
-          <t>Hiring AEs? (10/30/26)</t>
+          <t>Hiring AEs? (10/31/26)</t>
         </is>
       </c>
     </row>
